--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -14,16 +14,21 @@
     <sheet name="Скрин" sheetId="5" r:id="rId5"/>
     <sheet name="Факторы" sheetId="6" r:id="rId6"/>
     <sheet name="Инфо" sheetId="7" r:id="rId7"/>
+    <sheet name="_данные" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Скрин!$A$4:$Q$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$Q$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="223">
+  <si>
+    <t>DELL</t>
+  </si>
   <si>
     <t>Открытые позиции</t>
   </si>
@@ -79,12 +84,21 @@
     <t>Динамика</t>
   </si>
   <si>
+    <t>Dell Technologies</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>confirmed</t>
+  </si>
+  <si>
     <t>Итого</t>
   </si>
   <si>
-    <t>Пока нет открытых позиций — лестница только начинает набираться.</t>
-  </si>
-  <si>
     <t>Закрытые сделки</t>
   </si>
   <si>
@@ -187,22 +201,46 @@
     <t>Статус</t>
   </si>
   <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>Dell Technologies</t>
-  </si>
-  <si>
-    <t>Information Technology</t>
+    <t>MU</t>
+  </si>
+  <si>
+    <t>Micron Technology</t>
   </si>
   <si>
     <t>проходит</t>
   </si>
   <si>
-    <t>MU</t>
-  </si>
-  <si>
-    <t>Micron Technology</t>
+    <t>SNDK</t>
+  </si>
+  <si>
+    <t>Sandisk</t>
+  </si>
+  <si>
+    <t>VLO</t>
+  </si>
+  <si>
+    <t>Valero Energy</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>Western Digital</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>Marathon Petroleum</t>
+  </si>
+  <si>
+    <t>OXY</t>
+  </si>
+  <si>
+    <t>Occidental Petroleum</t>
   </si>
   <si>
     <t>HPE</t>
@@ -211,55 +249,133 @@
     <t>Hewlett Packard Enterprise</t>
   </si>
   <si>
-    <t>SNDK</t>
-  </si>
-  <si>
-    <t>Sandisk</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>Marvell Technology</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>Palo Alto Networks</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>Advanced Micro Devices</t>
-  </si>
-  <si>
     <t>NTAP</t>
   </si>
   <si>
     <t>NetApp</t>
   </si>
   <si>
-    <t>MRNA</t>
-  </si>
-  <si>
-    <t>Moderna</t>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>Expedia Group</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>EOG Resources</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>Teradyne</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>APA Corporation</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>Humana</t>
   </si>
   <si>
     <t>Health Care</t>
   </si>
   <si>
-    <t>STX</t>
-  </si>
-  <si>
-    <t>Seagate Technology</t>
-  </si>
-  <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>Phillips 66</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>Nvidia</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>Diamondback Energy</t>
+  </si>
+  <si>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>Centene Corporation</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class A)</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class C)</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>CF Industries</t>
+  </si>
+  <si>
+    <t>Materials</t>
   </si>
   <si>
     <t>FTNT</t>
@@ -268,115 +384,67 @@
     <t>Fortinet</t>
   </si>
   <si>
-    <t>VLO</t>
-  </si>
-  <si>
-    <t>Valero Energy</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>CrowdStrike</t>
-  </si>
-  <si>
-    <t>MPC</t>
-  </si>
-  <si>
-    <t>Marathon Petroleum</t>
-  </si>
-  <si>
-    <t>CNC</t>
-  </si>
-  <si>
-    <t>Centene Corporation</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>Datadog</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>Applied Materials</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>Lam Research</t>
-  </si>
-  <si>
-    <t>CRL</t>
-  </si>
-  <si>
-    <t>Charles River Laboratories</t>
-  </si>
-  <si>
-    <t>LITE</t>
-  </si>
-  <si>
-    <t>Lumentum</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>Intel</t>
-  </si>
-  <si>
-    <t>WDC</t>
-  </si>
-  <si>
-    <t>Western Digital</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>State Street Corporation</t>
-  </si>
-  <si>
-    <t>Financials</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>Expedia Group</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>Teradyne</t>
-  </si>
-  <si>
-    <t>BBY</t>
-  </si>
-  <si>
-    <t>Best Buy</t>
-  </si>
-  <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>Phillips 66</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>Arista Networks</t>
+    <t>TROW</t>
+  </si>
+  <si>
+    <t>T. Rowe Price</t>
+  </si>
+  <si>
+    <t>RDDT</t>
+  </si>
+  <si>
+    <t>Reddit</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>Booking Holdings</t>
+  </si>
+  <si>
+    <t>RJF</t>
+  </si>
+  <si>
+    <t>Raymond James Financial</t>
+  </si>
+  <si>
+    <t>CINF</t>
+  </si>
+  <si>
+    <t>Cincinnati Financial</t>
+  </si>
+  <si>
+    <t>DVN</t>
+  </si>
+  <si>
+    <t>Devon Energy</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>Altria</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>SCHW</t>
+  </si>
+  <si>
+    <t>Charles Schwab Corporation</t>
+  </si>
+  <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>Supermicro</t>
   </si>
   <si>
     <t>ZBRA</t>
@@ -385,70 +453,10 @@
     <t>Zebra Technologies</t>
   </si>
   <si>
-    <t>HPQ</t>
-  </si>
-  <si>
-    <t>HP Inc.</t>
-  </si>
-  <si>
-    <t>TGT</t>
-  </si>
-  <si>
-    <t>Target Corporation</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>AXON</t>
-  </si>
-  <si>
-    <t>Axon Enterprise</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
-    <t>Block, Inc.</t>
-  </si>
-  <si>
-    <t>BAX</t>
-  </si>
-  <si>
-    <t>Baxter International</t>
-  </si>
-  <si>
-    <t>SWK</t>
-  </si>
-  <si>
-    <t>Stanley Black &amp; Decker</t>
-  </si>
-  <si>
-    <t>ABNB</t>
-  </si>
-  <si>
-    <t>Airbnb</t>
-  </si>
-  <si>
-    <t>BNY</t>
-  </si>
-  <si>
-    <t>BNY Mellon</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>APA Corporation</t>
-  </si>
-  <si>
-    <t>IQV</t>
-  </si>
-  <si>
-    <t>IQVIA</t>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>Waters Corporation</t>
   </si>
   <si>
     <t>Факторы и самообучение</t>
@@ -511,7 +519,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-08-25 01:45 UTC · данные на 2026-08-24 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-08-25 22:49 UTC · данные на 2026-08-25 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -520,15 +528,15 @@
     <t>Бенчмарк SPY</t>
   </si>
   <si>
+    <t>Макс. просадка</t>
+  </si>
+  <si>
+    <t>Sharpe</t>
+  </si>
+  <si>
     <t>—</t>
   </si>
   <si>
-    <t>Макс. просадка</t>
-  </si>
-  <si>
-    <t>Sharpe</t>
-  </si>
-  <si>
     <t>Сделок закрыто</t>
   </si>
   <si>
@@ -580,6 +588,9 @@
     <t>Эта строка считается формулой: поправь «Тек. цена» на листе «Позиции» — значение пересчитается.</t>
   </si>
   <si>
+    <t>Распределение по секторам</t>
+  </si>
+  <si>
     <t>Как это работает и чему не стоит верить</t>
   </si>
   <si>
@@ -589,7 +600,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-08-25 01:45 UTC</t>
+    <t>2026-08-25 22:49 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -604,7 +615,7 @@
     <t>Прошли фильтры</t>
   </si>
   <si>
-    <t>501</t>
+    <t>499</t>
   </si>
   <si>
     <t>Кандидат дня</t>
@@ -613,9 +624,6 @@
     <t>Проверка Alpha Vantage</t>
   </si>
   <si>
-    <t>confirmed</t>
-  </si>
-  <si>
     <t>Комментарий проверки</t>
   </si>
   <si>
@@ -625,19 +633,22 @@
     <t>Запросов AV использовано</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Источник цен</t>
+  </si>
+  <si>
+    <t>yfinance</t>
+  </si>
+  <si>
+    <t>Фундаментал на дату</t>
+  </si>
+  <si>
+    <t>Версия состояния</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>Источник цен</t>
-  </si>
-  <si>
-    <t>yfinance</t>
-  </si>
-  <si>
-    <t>Фундаментал на дату</t>
-  </si>
-  <si>
-    <t>Версия состояния</t>
   </si>
   <si>
     <t>Регламент данных</t>
@@ -692,12 +703,12 @@
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00%"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.00%"/>
     <numFmt numFmtId="169" formatCode="0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -766,13 +777,19 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF8B6D00"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -782,6 +799,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF334E68"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFDE7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -858,15 +881,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -880,14 +903,15 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -897,6 +921,642 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Секторы портфеля</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Секторы</c:v>
+          </c:tx>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" baseline="0">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showPercent val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Сводка!$B$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Information Technology</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Сводка!$C$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>485.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" baseline="0">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Капитал портфеля</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Портфель</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="0B5FFF"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Капитал!$A$5:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2026-08-24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2026-08-25</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Капитал!$D$5:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>10000.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10009.01</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>S&amp;P 500 (SPY)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="7B8794"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Капитал!$A$5:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2026-08-24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2026-08-25</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Капитал!$F$5:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10031.96</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50020001"/>
+        <c:axId val="50020002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50020001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50020002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50020002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="$#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50020001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1200" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Капитал во времени</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Портфель</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="0B5FFF"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Капитал!$A$5:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2026-08-24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2026-08-25</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Капитал!$D$5:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>10000.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10009.01</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>S&amp;P 500 (SPY)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="7B8794"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Капитал!$A$5:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2026-08-24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2026-08-25</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Капитал!$F$5:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10031.96</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50030001"/>
+        <c:axId val="50030002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50030001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50030002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50030002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="D9E2EC"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="$#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50030001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1184,219 +1844,242 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:H29"/>
+  <dimension ref="A2:H33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="9" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="9" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="4">
-        <v>10000</v>
+        <v>10009.01</v>
       </c>
       <c r="D6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H6" s="7">
+        <v>0.0009010000000000407</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.003195999999999977</v>
+      </c>
+      <c r="H6" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>0</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0</v>
+      <c r="F9" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H9" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C13" s="10">
-        <v>10000</v>
+        <v>9523.809999999999</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C14" s="10">
-        <v>0</v>
+        <v>485.2</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C15" s="10">
-        <v>10000</v>
+        <v>10009.01</v>
       </c>
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
       </c>
     </row>
-    <row r="17" spans="2:3">
+    <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C18" s="11">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C19" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:3">
+    <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
+    <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C26" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="B28" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
-        <v>10000.0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3">
+        <v>10009.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="B29" s="13" t="s">
-        <v>184</v>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="B31" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="30" customHeight="1">
+      <c r="A32" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="10">
+        <v>485.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
@@ -1413,94 +2096,206 @@
     <col min="15" max="16" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="30" customHeight="1">
-      <c r="A4" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="13" t="s">
+      <c r="B5" s="9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="C5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="10">
+        <v>443.1115</v>
+      </c>
+      <c r="F5" s="16">
+        <v>1.074651</v>
+      </c>
+      <c r="G5" s="10">
+        <v>476.19</v>
+      </c>
+      <c r="H5" s="17">
+        <v>451.5</v>
+      </c>
+      <c r="I5" s="10">
+        <f>F5*H5</f>
+        <v>485.2049265</v>
+      </c>
+      <c r="J5" s="10">
+        <f>I5-G5</f>
+        <v>9.014926500000001</v>
+      </c>
+      <c r="K5" s="18">
+        <f>IFERROR(J5/G5,0)</f>
+        <v>0.018931364581364584</v>
+      </c>
+      <c r="L5" s="11">
+        <v>0</v>
+      </c>
+      <c r="M5" s="11">
+        <f>MAX(0,21-L5)</f>
+        <v>21</v>
+      </c>
+      <c r="N5" s="19">
+        <v>2.927623067210654</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F6" s="12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G6" s="10">
         <f>SUM(G5:G5)</f>
-        <v>0</v>
+        <v>476.19</v>
       </c>
       <c r="I6" s="10">
         <f>SUM(I5:I5)</f>
-        <v>0</v>
+        <v>485.2</v>
       </c>
       <c r="J6" s="10">
         <f>SUM(J5:J5)</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="15">
+        <v>9.009999999999991</v>
+      </c>
+      <c r="K6" s="18">
         <f>IFERROR(J6/G6,0)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:P5"/>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8B4B4"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFA7E8C0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF9FB3C8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DA7ABA51-AAAA-BBBB-0002-000000000001}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0002-000000000001}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF9FB3C8"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>M5</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+      <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
+          <x14:colorSeries rgb="FF0B5FFF"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'_данные'!B1:BI1</xm:f>
+              <xm:sqref>P5</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1526,64 +2321,64 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1593,7 +2388,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1605,37 +2400,37 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="16" t="s">
-        <v>38</v>
+      <c r="A5" s="15" t="s">
+        <v>42</v>
       </c>
       <c r="B5" s="10">
         <v>10000</v>
@@ -1654,8 +2449,30 @@
         <v>10000</v>
       </c>
     </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="10">
+        <v>9523.809999999999</v>
+      </c>
+      <c r="C6" s="10">
+        <v>485.2</v>
+      </c>
+      <c r="D6" s="10">
+        <f>B6+C6</f>
+        <v>10009.01</v>
+      </c>
+      <c r="E6" s="11">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <v>10031.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1680,65 +2497,65 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -1746,52 +2563,52 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E5" s="10">
-        <v>433.1900024414062</v>
-      </c>
-      <c r="F5" s="17">
-        <v>2.927623067210654</v>
-      </c>
-      <c r="G5" s="18">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18">
-        <v>0</v>
-      </c>
-      <c r="I5" s="18">
-        <v>0</v>
-      </c>
-      <c r="J5" s="18">
-        <v>2.927623067210654</v>
-      </c>
-      <c r="K5" s="18">
-        <v>0</v>
-      </c>
-      <c r="L5" s="18">
-        <v>0</v>
-      </c>
-      <c r="M5" s="19">
-        <v>0</v>
-      </c>
-      <c r="N5" s="19">
-        <v>0</v>
-      </c>
-      <c r="O5" s="19">
-        <v>2.65325152696871</v>
+        <v>932.969970703125</v>
+      </c>
+      <c r="F5" s="16">
+        <v>1.809956883354321</v>
+      </c>
+      <c r="G5" s="19">
+        <v>0.1411051627135557</v>
+      </c>
+      <c r="H5" s="19">
+        <v>1.679910500336321</v>
+      </c>
+      <c r="I5" s="19">
+        <v>4.206596031118561</v>
+      </c>
+      <c r="J5" s="19">
+        <v>2.388861015961299</v>
+      </c>
+      <c r="K5" s="19">
+        <v>20.560751</v>
+      </c>
+      <c r="L5" s="19">
+        <v>10.204899</v>
+      </c>
+      <c r="M5" s="20">
+        <v>0.66638</v>
+      </c>
+      <c r="N5" s="20">
+        <v>3.457</v>
+      </c>
+      <c r="O5" s="20">
+        <v>1.233213131675055</v>
       </c>
       <c r="P5" s="11">
-        <v>48.12217305711359</v>
+        <v>50.78068810064901</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -1799,52 +2616,52 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E6" s="10">
-        <v>910.4299926757812</v>
-      </c>
-      <c r="F6" s="17">
-        <v>2.643241101110455</v>
-      </c>
-      <c r="G6" s="18">
-        <v>0</v>
-      </c>
-      <c r="H6" s="18">
-        <v>0</v>
-      </c>
-      <c r="I6" s="18">
-        <v>0</v>
-      </c>
-      <c r="J6" s="18">
-        <v>2.643241101110455</v>
-      </c>
-      <c r="K6" s="18">
-        <v>0</v>
-      </c>
-      <c r="L6" s="18">
-        <v>0</v>
-      </c>
-      <c r="M6" s="19">
-        <v>0</v>
-      </c>
-      <c r="N6" s="19">
-        <v>0</v>
-      </c>
-      <c r="O6" s="19">
-        <v>1.163936978037537</v>
+        <v>1480.77001953125</v>
+      </c>
+      <c r="F6" s="16">
+        <v>1.658898522944298</v>
+      </c>
+      <c r="G6" s="19">
+        <v>-0.297947721659126</v>
+      </c>
+      <c r="H6" s="19">
+        <v>1.878861151632597</v>
+      </c>
+      <c r="I6" s="19">
+        <v>4.026096567149331</v>
+      </c>
+      <c r="J6" s="19">
+        <v>2.248843554871623</v>
+      </c>
+      <c r="K6" s="19">
+        <v>20.248442</v>
+      </c>
+      <c r="L6" s="19">
+        <v>14.137921</v>
+      </c>
+      <c r="M6" s="20">
+        <v>0.9164</v>
+      </c>
+      <c r="N6" s="20">
+        <v>3.716</v>
+      </c>
+      <c r="O6" s="20">
+        <v>1.319065924696162</v>
       </c>
       <c r="P6" s="11">
-        <v>48.50420618541599</v>
+        <v>49.17336527482853</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -1852,52 +2669,52 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="10">
+        <v>340.4100036621094</v>
+      </c>
+      <c r="F7" s="16">
+        <v>1.130429211953938</v>
+      </c>
+      <c r="G7" s="19">
+        <v>0.72925464828006</v>
+      </c>
+      <c r="H7" s="19">
+        <v>-0.3048721710887977</v>
+      </c>
+      <c r="I7" s="19">
+        <v>2.983550662811328</v>
+      </c>
+      <c r="J7" s="19">
+        <v>1.801127536068069</v>
+      </c>
+      <c r="K7" s="19">
+        <v>14.4347105</v>
+      </c>
+      <c r="L7" s="19">
+        <v>3.9847977</v>
+      </c>
+      <c r="M7" s="20">
+        <v>0.27637</v>
+      </c>
+      <c r="N7" s="20">
+        <v>0.517</v>
+      </c>
+      <c r="O7" s="20">
+        <v>0.7225162000965759</v>
+      </c>
+      <c r="P7" s="11">
+        <v>63.05356909428822</v>
+      </c>
+      <c r="Q7" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="10">
-        <v>52.43000030517578</v>
-      </c>
-      <c r="F7" s="17">
-        <v>2.503268744489996</v>
-      </c>
-      <c r="G7" s="18">
-        <v>0</v>
-      </c>
-      <c r="H7" s="18">
-        <v>0</v>
-      </c>
-      <c r="I7" s="18">
-        <v>0</v>
-      </c>
-      <c r="J7" s="18">
-        <v>2.503268744489996</v>
-      </c>
-      <c r="K7" s="18">
-        <v>0</v>
-      </c>
-      <c r="L7" s="18">
-        <v>0</v>
-      </c>
-      <c r="M7" s="19">
-        <v>0</v>
-      </c>
-      <c r="N7" s="19">
-        <v>0</v>
-      </c>
-      <c r="O7" s="19">
-        <v>1.646122947151413</v>
-      </c>
-      <c r="P7" s="11">
-        <v>50.99046117728734</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1905,52 +2722,52 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E8" s="10">
-        <v>1493.119995117188</v>
-      </c>
-      <c r="F8" s="17">
-        <v>2.411341743866761</v>
-      </c>
-      <c r="G8" s="18">
+        <v>450.75</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1.129536240330068</v>
+      </c>
+      <c r="G8" s="19">
+        <v>-0.6552990140462744</v>
+      </c>
+      <c r="H8" s="19">
+        <v>1.918440052485617</v>
+      </c>
+      <c r="I8" s="19">
+        <v>3.032907322180939</v>
+      </c>
+      <c r="J8" s="19">
+        <v>1.305266110318017</v>
+      </c>
+      <c r="K8" s="19">
+        <v>17.067032</v>
+      </c>
+      <c r="L8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="18">
-        <v>0</v>
-      </c>
-      <c r="I8" s="18">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18">
-        <v>2.411341743866761</v>
-      </c>
-      <c r="K8" s="18">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18">
-        <v>0</v>
-      </c>
-      <c r="M8" s="19">
-        <v>0</v>
-      </c>
-      <c r="N8" s="19">
-        <v>0</v>
-      </c>
-      <c r="O8" s="19">
-        <v>1.240273698022266</v>
+      <c r="M8" s="20">
+        <v>1.30853</v>
+      </c>
+      <c r="N8" s="20">
+        <v>0.438</v>
+      </c>
+      <c r="O8" s="20">
+        <v>0.6671592836018609</v>
       </c>
       <c r="P8" s="11">
-        <v>49.65261358881916</v>
+        <v>43.49420375949914</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1958,52 +2775,52 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>56</v>
-      </c>
       <c r="E9" s="10">
-        <v>229.2899932861328</v>
-      </c>
-      <c r="F9" s="17">
-        <v>2.344826632872142</v>
-      </c>
-      <c r="G9" s="18">
-        <v>0</v>
-      </c>
-      <c r="H9" s="18">
-        <v>0</v>
-      </c>
-      <c r="I9" s="18">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18">
-        <v>2.344826632872142</v>
-      </c>
-      <c r="K9" s="18">
-        <v>0</v>
-      </c>
-      <c r="L9" s="18">
-        <v>0</v>
-      </c>
-      <c r="M9" s="19">
-        <v>0</v>
-      </c>
-      <c r="N9" s="19">
-        <v>0</v>
-      </c>
-      <c r="O9" s="19">
-        <v>1.94975401620419</v>
+        <v>354.8800048828125</v>
+      </c>
+      <c r="F9" s="16">
+        <v>1.008458897306455</v>
+      </c>
+      <c r="G9" s="19">
+        <v>0.7230916879797831</v>
+      </c>
+      <c r="H9" s="19">
+        <v>-0.385889491053161</v>
+      </c>
+      <c r="I9" s="19">
+        <v>2.543797486452658</v>
+      </c>
+      <c r="J9" s="19">
+        <v>1.688113802359707</v>
+      </c>
+      <c r="K9" s="19">
+        <v>12.56133</v>
+      </c>
+      <c r="L9" s="19">
+        <v>5.3778367</v>
+      </c>
+      <c r="M9" s="20">
+        <v>0.42099</v>
+      </c>
+      <c r="N9" s="20">
+        <v>0.537</v>
+      </c>
+      <c r="O9" s="20">
+        <v>0.829125157126803</v>
       </c>
       <c r="P9" s="11">
-        <v>52.93087457868494</v>
+        <v>66.00522059337668</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2011,52 +2828,52 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E10" s="10">
-        <v>350.8999938964844</v>
-      </c>
-      <c r="F10" s="17">
-        <v>2.228082689538791</v>
-      </c>
-      <c r="G10" s="18">
-        <v>0</v>
-      </c>
-      <c r="H10" s="18">
-        <v>0</v>
-      </c>
-      <c r="I10" s="18">
-        <v>0</v>
-      </c>
-      <c r="J10" s="18">
-        <v>2.228082689538791</v>
-      </c>
-      <c r="K10" s="18">
-        <v>0</v>
-      </c>
-      <c r="L10" s="18">
-        <v>0</v>
-      </c>
-      <c r="M10" s="19">
-        <v>0</v>
-      </c>
-      <c r="N10" s="19">
-        <v>0</v>
-      </c>
-      <c r="O10" s="19">
-        <v>1.434438708077896</v>
+        <v>58.40999984741211</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0.9262865832288399</v>
+      </c>
+      <c r="G10" s="19">
+        <v>0.6355114639003794</v>
+      </c>
+      <c r="H10" s="19">
+        <v>0.6239334098844196</v>
+      </c>
+      <c r="I10" s="19">
+        <v>3.304463564487919</v>
+      </c>
+      <c r="J10" s="19">
+        <v>0.279934189714778</v>
+      </c>
+      <c r="K10" s="19">
+        <v>18.105423</v>
+      </c>
+      <c r="L10" s="19">
+        <v>1.7959902</v>
+      </c>
+      <c r="M10" s="20">
+        <v>0.10629</v>
+      </c>
+      <c r="N10" s="20">
+        <v>0.534</v>
+      </c>
+      <c r="O10" s="20">
+        <v>0.1349067886734578</v>
       </c>
       <c r="P10" s="11">
-        <v>48.50221508567612</v>
+        <v>53.00057263604817</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2064,52 +2881,52 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E11" s="10">
-        <v>456.7449951171875</v>
-      </c>
-      <c r="F11" s="17">
-        <v>1.996587708354377</v>
-      </c>
-      <c r="G11" s="18">
-        <v>0</v>
-      </c>
-      <c r="H11" s="18">
-        <v>0</v>
-      </c>
-      <c r="I11" s="18">
-        <v>0</v>
-      </c>
-      <c r="J11" s="18">
-        <v>1.996587708354377</v>
-      </c>
-      <c r="K11" s="18">
-        <v>0</v>
-      </c>
-      <c r="L11" s="18">
-        <v>0</v>
-      </c>
-      <c r="M11" s="19">
-        <v>0</v>
-      </c>
-      <c r="N11" s="19">
-        <v>0</v>
-      </c>
-      <c r="O11" s="19">
-        <v>1.323219638542117</v>
+        <v>53.43999862670898</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0.8861173700944488</v>
+      </c>
+      <c r="G11" s="19">
+        <v>0.304959259686968</v>
+      </c>
+      <c r="H11" s="19">
+        <v>-0.604597401341887</v>
+      </c>
+      <c r="I11" s="19">
+        <v>1.463737124114395</v>
+      </c>
+      <c r="J11" s="19">
+        <v>2.420727913022236</v>
+      </c>
+      <c r="K11" s="19">
+        <v>48.999996</v>
+      </c>
+      <c r="L11" s="19">
+        <v>2.743159</v>
+      </c>
+      <c r="M11" s="20">
+        <v>0.06315</v>
+      </c>
+      <c r="N11" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="O11" s="20">
+        <v>1.663799782449941</v>
       </c>
       <c r="P11" s="11">
-        <v>42.45523546943802</v>
+        <v>53.59705945698387</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -2117,52 +2934,52 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E12" s="10">
-        <v>186.8600006103516</v>
-      </c>
-      <c r="F12" s="17">
-        <v>1.975017261269628</v>
-      </c>
-      <c r="G12" s="18">
+        <v>451.5</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0.8204379203607901</v>
+      </c>
+      <c r="G12" s="19">
+        <v>-1.276312485328304</v>
+      </c>
+      <c r="H12" s="19">
+        <v>-0.5342797424893034</v>
+      </c>
+      <c r="I12" s="19">
+        <v>3.12929742928239</v>
+      </c>
+      <c r="J12" s="19">
+        <v>2.891689957297495</v>
+      </c>
+      <c r="K12" s="19">
+        <v>884.0612</v>
+      </c>
+      <c r="L12" s="19">
+        <v>-200.27277</v>
+      </c>
+      <c r="M12" s="20">
         <v>0</v>
       </c>
-      <c r="H12" s="18">
-        <v>0</v>
-      </c>
-      <c r="I12" s="18">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18">
-        <v>1.975017261269628</v>
-      </c>
-      <c r="K12" s="18">
-        <v>0</v>
-      </c>
-      <c r="L12" s="18">
-        <v>0</v>
-      </c>
-      <c r="M12" s="19">
-        <v>0</v>
-      </c>
-      <c r="N12" s="19">
-        <v>0</v>
-      </c>
-      <c r="O12" s="19">
-        <v>0.8739438169897173</v>
+      <c r="N12" s="20">
+        <v>0.875</v>
+      </c>
+      <c r="O12" s="20">
+        <v>2.787321986323046</v>
       </c>
       <c r="P12" s="11">
-        <v>50.33060678343458</v>
+        <v>52.43236515943332</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -2170,52 +2987,52 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="E13" s="10">
-        <v>138.8899993896484</v>
-      </c>
-      <c r="F13" s="17">
-        <v>1.926929807705512</v>
-      </c>
-      <c r="G13" s="18">
-        <v>0</v>
-      </c>
-      <c r="H13" s="18">
-        <v>0</v>
-      </c>
-      <c r="I13" s="18">
-        <v>0</v>
-      </c>
-      <c r="J13" s="18">
-        <v>1.926929807705512</v>
-      </c>
-      <c r="K13" s="18">
-        <v>0</v>
-      </c>
-      <c r="L13" s="18">
-        <v>0</v>
-      </c>
-      <c r="M13" s="19">
-        <v>0</v>
-      </c>
-      <c r="N13" s="19">
-        <v>0</v>
-      </c>
-      <c r="O13" s="19">
-        <v>1.761781603920499</v>
+        <v>187.4299926757812</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0.76891160352956</v>
+      </c>
+      <c r="G13" s="19">
+        <v>-0.4056392750220561</v>
+      </c>
+      <c r="H13" s="19">
+        <v>1.27195723742807</v>
+      </c>
+      <c r="I13" s="19">
+        <v>-0.1487202202604564</v>
+      </c>
+      <c r="J13" s="19">
+        <v>1.98307369906076</v>
+      </c>
+      <c r="K13" s="19">
+        <v>30.285252</v>
+      </c>
+      <c r="L13" s="19">
+        <v>27.10866</v>
+      </c>
+      <c r="M13" s="20">
+        <v>1.06734</v>
+      </c>
+      <c r="N13" s="20">
+        <v>0.125</v>
+      </c>
+      <c r="O13" s="20">
+        <v>0.8920817885495846</v>
       </c>
       <c r="P13" s="11">
-        <v>68.82090494360882</v>
+        <v>50.92537543410591</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -2223,52 +3040,52 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E14" s="10">
-        <v>794.6500244140625</v>
-      </c>
-      <c r="F14" s="17">
-        <v>1.911603056571496</v>
-      </c>
-      <c r="G14" s="18">
-        <v>0</v>
-      </c>
-      <c r="H14" s="18">
-        <v>0</v>
-      </c>
-      <c r="I14" s="18">
-        <v>0</v>
-      </c>
-      <c r="J14" s="18">
-        <v>1.911603056571496</v>
-      </c>
-      <c r="K14" s="18">
-        <v>0</v>
-      </c>
-      <c r="L14" s="18">
-        <v>0</v>
-      </c>
-      <c r="M14" s="19">
-        <v>0</v>
-      </c>
-      <c r="N14" s="19">
-        <v>0</v>
-      </c>
-      <c r="O14" s="19">
-        <v>0.955335838763572</v>
+        <v>337.9700012207031</v>
+      </c>
+      <c r="F14" s="16">
+        <v>0.715275223135537</v>
+      </c>
+      <c r="G14" s="19">
+        <v>-0.1074817459894137</v>
+      </c>
+      <c r="H14" s="19">
+        <v>1.241839716939916</v>
+      </c>
+      <c r="I14" s="19">
+        <v>0.6713684345102916</v>
+      </c>
+      <c r="J14" s="19">
+        <v>1.121181841736128</v>
+      </c>
+      <c r="K14" s="19">
+        <v>20.24627</v>
+      </c>
+      <c r="L14" s="19">
+        <v>33.66005</v>
+      </c>
+      <c r="M14" s="20">
+        <v>0.89489</v>
+      </c>
+      <c r="N14" s="20">
+        <v>0.14</v>
+      </c>
+      <c r="O14" s="20">
+        <v>0.7132158909244706</v>
       </c>
       <c r="P14" s="11">
-        <v>43.24681730723569</v>
+        <v>68.29007185783232</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -2276,52 +3093,52 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E15" s="10">
-        <v>386.6099853515625</v>
-      </c>
-      <c r="F15" s="17">
-        <v>1.788136975206289</v>
-      </c>
-      <c r="G15" s="18">
-        <v>0</v>
-      </c>
-      <c r="H15" s="18">
-        <v>0</v>
-      </c>
-      <c r="I15" s="18">
-        <v>0</v>
-      </c>
-      <c r="J15" s="18">
-        <v>1.788136975206289</v>
-      </c>
-      <c r="K15" s="18">
-        <v>0</v>
-      </c>
-      <c r="L15" s="18">
-        <v>0</v>
-      </c>
-      <c r="M15" s="19">
-        <v>0</v>
-      </c>
-      <c r="N15" s="19">
-        <v>0</v>
-      </c>
-      <c r="O15" s="19">
-        <v>1.149979316410551</v>
+        <v>146.8300018310547</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0.6828121821255917</v>
+      </c>
+      <c r="G15" s="19">
+        <v>0.6102249595302855</v>
+      </c>
+      <c r="H15" s="19">
+        <v>0.5715130155458599</v>
+      </c>
+      <c r="I15" s="19">
+        <v>1.562733350737734</v>
+      </c>
+      <c r="J15" s="19">
+        <v>0.4081881258979367</v>
+      </c>
+      <c r="K15" s="19">
+        <v>11.680406</v>
+      </c>
+      <c r="L15" s="19">
+        <v>2.5993288</v>
+      </c>
+      <c r="M15" s="20">
+        <v>0.22507</v>
+      </c>
+      <c r="N15" s="20">
+        <v>0.587</v>
+      </c>
+      <c r="O15" s="20">
+        <v>0.2050783188428775</v>
       </c>
       <c r="P15" s="11">
-        <v>53.79195071588038</v>
+        <v>54.32109127269014</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -2329,52 +3146,52 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E16" s="10">
-        <v>151.9900054931641</v>
-      </c>
-      <c r="F16" s="17">
-        <v>1.715569729322309</v>
-      </c>
-      <c r="G16" s="18">
-        <v>0</v>
-      </c>
-      <c r="H16" s="18">
-        <v>0</v>
-      </c>
-      <c r="I16" s="18">
-        <v>0</v>
-      </c>
-      <c r="J16" s="18">
-        <v>1.715569729322309</v>
-      </c>
-      <c r="K16" s="18">
-        <v>0</v>
-      </c>
-      <c r="L16" s="18">
-        <v>0</v>
-      </c>
-      <c r="M16" s="19">
-        <v>0</v>
-      </c>
-      <c r="N16" s="19">
-        <v>0</v>
-      </c>
-      <c r="O16" s="19">
-        <v>1.010449848688718</v>
+        <v>366.4299926757812</v>
+      </c>
+      <c r="F16" s="16">
+        <v>0.6797400188617937</v>
+      </c>
+      <c r="G16" s="19">
+        <v>-1.08262537420069</v>
+      </c>
+      <c r="H16" s="19">
+        <v>0.6932659455068273</v>
+      </c>
+      <c r="I16" s="19">
+        <v>3.615274867663105</v>
+      </c>
+      <c r="J16" s="19">
+        <v>0.9630663819860936</v>
+      </c>
+      <c r="K16" s="19">
+        <v>51.539547</v>
+      </c>
+      <c r="L16" s="19">
+        <v>18.169596</v>
+      </c>
+      <c r="M16" s="20">
+        <v>0.36465</v>
+      </c>
+      <c r="N16" s="20">
+        <v>1.039</v>
+      </c>
+      <c r="O16" s="20">
+        <v>0.113884902430992</v>
       </c>
       <c r="P16" s="11">
-        <v>44.16000885554509</v>
+        <v>46.26722336147129</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -2382,52 +3199,52 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E17" s="10">
-        <v>346</v>
-      </c>
-      <c r="F17" s="17">
-        <v>1.672889251711891</v>
-      </c>
-      <c r="G17" s="18">
-        <v>0</v>
-      </c>
-      <c r="H17" s="18">
-        <v>0</v>
-      </c>
-      <c r="I17" s="18">
-        <v>0</v>
-      </c>
-      <c r="J17" s="18">
-        <v>1.672889251711891</v>
-      </c>
-      <c r="K17" s="18">
-        <v>0</v>
-      </c>
-      <c r="L17" s="18">
-        <v>0</v>
-      </c>
-      <c r="M17" s="19">
-        <v>0</v>
-      </c>
-      <c r="N17" s="19">
-        <v>0</v>
-      </c>
-      <c r="O17" s="19">
-        <v>0.76800953419441</v>
+        <v>41.34999847412109</v>
+      </c>
+      <c r="F17" s="16">
+        <v>0.6787269380675097</v>
+      </c>
+      <c r="G17" s="19">
+        <v>0.9986491788407921</v>
+      </c>
+      <c r="H17" s="19">
+        <v>0.6094621501467751</v>
+      </c>
+      <c r="I17" s="19">
+        <v>-0.228424555888388</v>
+      </c>
+      <c r="J17" s="19">
+        <v>0.8701011008727886</v>
+      </c>
+      <c r="K17" s="19">
+        <v>9.159914000000001</v>
+      </c>
+      <c r="L17" s="19">
+        <v>2.14564</v>
+      </c>
+      <c r="M17" s="20">
+        <v>0.26659</v>
+      </c>
+      <c r="N17" s="20">
+        <v>0.092</v>
+      </c>
+      <c r="O17" s="20">
+        <v>0.4647013278671024</v>
       </c>
       <c r="P17" s="11">
-        <v>68.02404277435744</v>
+        <v>58.27812268635797</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -2435,52 +3252,52 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="E18" s="10">
-        <v>190.6799926757812</v>
-      </c>
-      <c r="F18" s="17">
-        <v>1.615636897060923</v>
-      </c>
-      <c r="G18" s="18">
-        <v>0</v>
-      </c>
-      <c r="H18" s="18">
-        <v>0</v>
-      </c>
-      <c r="I18" s="18">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18">
-        <v>1.615636897060923</v>
-      </c>
-      <c r="K18" s="18">
-        <v>0</v>
-      </c>
-      <c r="L18" s="18">
-        <v>0</v>
-      </c>
-      <c r="M18" s="19">
-        <v>0</v>
-      </c>
-      <c r="N18" s="19">
-        <v>0</v>
-      </c>
-      <c r="O18" s="19">
-        <v>1.177147260974738</v>
+        <v>257.6199951171875</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0.6744109008100192</v>
+      </c>
+      <c r="G18" s="19">
+        <v>1.158776322034968</v>
+      </c>
+      <c r="H18" s="19">
+        <v>0.3596891130938242</v>
+      </c>
+      <c r="I18" s="19">
+        <v>0.009309850889890559</v>
+      </c>
+      <c r="J18" s="19">
+        <v>0.7848641609752969</v>
+      </c>
+      <c r="K18" s="19">
+        <v>5.083822</v>
+      </c>
+      <c r="L18" s="19">
+        <v>2.0850062</v>
+      </c>
+      <c r="M18" s="20">
+        <v>0.46113998</v>
+      </c>
+      <c r="N18" s="20">
+        <v>0.118</v>
+      </c>
+      <c r="O18" s="20">
+        <v>0.2405278269640074</v>
       </c>
       <c r="P18" s="11">
-        <v>42.01199624206358</v>
+        <v>49.95465390985286</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -2488,52 +3305,52 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E19" s="10">
-        <v>362.5199890136719</v>
-      </c>
-      <c r="F19" s="17">
-        <v>1.524297500739992</v>
-      </c>
-      <c r="G19" s="18">
-        <v>0</v>
-      </c>
-      <c r="H19" s="18">
-        <v>0</v>
-      </c>
-      <c r="I19" s="18">
-        <v>0</v>
-      </c>
-      <c r="J19" s="18">
-        <v>1.524297500739992</v>
-      </c>
-      <c r="K19" s="18">
-        <v>0</v>
-      </c>
-      <c r="L19" s="18">
-        <v>0</v>
-      </c>
-      <c r="M19" s="19">
-        <v>0</v>
-      </c>
-      <c r="N19" s="19">
-        <v>0</v>
-      </c>
-      <c r="O19" s="19">
-        <v>0.8924383427038787</v>
+        <v>389.7099914550781</v>
+      </c>
+      <c r="F19" s="16">
+        <v>0.6351126751106471</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0.4746478020487309</v>
+      </c>
+      <c r="H19" s="19">
+        <v>-0.2835410288834002</v>
+      </c>
+      <c r="I19" s="19">
+        <v>0.2562199099090978</v>
+      </c>
+      <c r="J19" s="19">
+        <v>1.750568684101711</v>
+      </c>
+      <c r="K19" s="19">
+        <v>35.8304</v>
+      </c>
+      <c r="L19" s="19">
+        <v>2.4162972</v>
+      </c>
+      <c r="M19" s="20">
+        <v>0.06893000000000001</v>
+      </c>
+      <c r="N19" s="20">
+        <v>0.262</v>
+      </c>
+      <c r="O19" s="20">
+        <v>1.24812962729863</v>
       </c>
       <c r="P19" s="11">
-        <v>72.85363619293068</v>
+        <v>55.47224371317206</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -2541,52 +3358,52 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E20" s="10">
-        <v>65.65000152587891</v>
-      </c>
-      <c r="F20" s="17">
-        <v>1.39785626987297</v>
-      </c>
-      <c r="G20" s="18">
-        <v>0</v>
-      </c>
-      <c r="H20" s="18">
-        <v>0</v>
-      </c>
-      <c r="I20" s="18">
-        <v>0</v>
-      </c>
-      <c r="J20" s="18">
-        <v>1.39785626987297</v>
-      </c>
-      <c r="K20" s="18">
-        <v>0</v>
-      </c>
-      <c r="L20" s="18">
-        <v>0</v>
-      </c>
-      <c r="M20" s="19">
-        <v>0</v>
-      </c>
-      <c r="N20" s="19">
-        <v>0</v>
-      </c>
-      <c r="O20" s="19">
-        <v>0.5147669888035027</v>
+        <v>236.8999938964844</v>
+      </c>
+      <c r="F20" s="16">
+        <v>0.6115370746568929</v>
+      </c>
+      <c r="G20" s="19">
+        <v>0.06892234601185927</v>
+      </c>
+      <c r="H20" s="19">
+        <v>-0.54467699511111</v>
+      </c>
+      <c r="I20" s="19">
+        <v>2.512241193631993</v>
+      </c>
+      <c r="J20" s="19">
+        <v>1.167311468621045</v>
+      </c>
+      <c r="K20" s="19">
+        <v>110.99082</v>
+      </c>
+      <c r="L20" s="19">
+        <v>3.064414</v>
+      </c>
+      <c r="M20" s="20">
+        <v>0.23452999</v>
+      </c>
+      <c r="N20" s="20">
+        <v>0.531</v>
+      </c>
+      <c r="O20" s="20">
+        <v>0.5540709449331289</v>
       </c>
       <c r="P20" s="11">
-        <v>52.01048816945075</v>
+        <v>67.96142812231727</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -2594,52 +3411,52 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="E21" s="10">
-        <v>225.7700042724609</v>
-      </c>
-      <c r="F21" s="17">
-        <v>1.328564471421659</v>
-      </c>
-      <c r="G21" s="18">
-        <v>0</v>
-      </c>
-      <c r="H21" s="18">
-        <v>0</v>
-      </c>
-      <c r="I21" s="18">
-        <v>0</v>
-      </c>
-      <c r="J21" s="18">
-        <v>1.328564471421659</v>
-      </c>
-      <c r="K21" s="18">
-        <v>0</v>
-      </c>
-      <c r="L21" s="18">
-        <v>0</v>
-      </c>
-      <c r="M21" s="19">
-        <v>0</v>
-      </c>
-      <c r="N21" s="19">
-        <v>0</v>
-      </c>
-      <c r="O21" s="19">
-        <v>1.200165755226059</v>
+        <v>1058.880004882812</v>
+      </c>
+      <c r="F21" s="16">
+        <v>0.6020778892080503</v>
+      </c>
+      <c r="G21" s="19">
+        <v>0.3556011439311419</v>
+      </c>
+      <c r="H21" s="19">
+        <v>0.8458479961101603</v>
+      </c>
+      <c r="I21" s="19">
+        <v>1.024034813371229</v>
+      </c>
+      <c r="J21" s="19">
+        <v>0.4344344166516113</v>
+      </c>
+      <c r="K21" s="19">
+        <v>16.004324</v>
+      </c>
+      <c r="L21" s="19">
+        <v>2.8622644</v>
+      </c>
+      <c r="M21" s="20">
+        <v>0.16902</v>
+      </c>
+      <c r="N21" s="20">
+        <v>0.425</v>
+      </c>
+      <c r="O21" s="20">
+        <v>0.1849489060627247</v>
       </c>
       <c r="P21" s="11">
-        <v>40.22839901593114</v>
+        <v>54.17918145182254</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -2647,52 +3464,52 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E22" s="10">
-        <v>484.1900024414062</v>
-      </c>
-      <c r="F22" s="17">
-        <v>1.299849221937076</v>
-      </c>
-      <c r="G22" s="18">
-        <v>0</v>
-      </c>
-      <c r="H22" s="18">
-        <v>0</v>
-      </c>
-      <c r="I22" s="18">
-        <v>0</v>
-      </c>
-      <c r="J22" s="18">
-        <v>1.299849221937076</v>
-      </c>
-      <c r="K22" s="18">
-        <v>0</v>
-      </c>
-      <c r="L22" s="18">
-        <v>0</v>
-      </c>
-      <c r="M22" s="19">
-        <v>0</v>
-      </c>
-      <c r="N22" s="19">
-        <v>0</v>
-      </c>
-      <c r="O22" s="19">
-        <v>0.2991844486375093</v>
+        <v>213.0500030517578</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0.5951011955216278</v>
+      </c>
+      <c r="G22" s="19">
+        <v>-1.338461785426528</v>
+      </c>
+      <c r="H22" s="19">
+        <v>2.078256102926562</v>
+      </c>
+      <c r="I22" s="19">
+        <v>2.806787311422478</v>
+      </c>
+      <c r="J22" s="19">
+        <v>0.1868586956819133</v>
+      </c>
+      <c r="K22" s="19">
+        <v>32.883278</v>
+      </c>
+      <c r="L22" s="19">
+        <v>25.833954</v>
+      </c>
+      <c r="M22" s="20">
+        <v>1.14288</v>
+      </c>
+      <c r="N22" s="20">
+        <v>0.852</v>
+      </c>
+      <c r="O22" s="20">
+        <v>0.1060920104233294</v>
       </c>
       <c r="P22" s="11">
-        <v>41.81854373917025</v>
+        <v>49.6092897474399</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -2700,52 +3517,52 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E23" s="10">
-        <v>310.1700134277344</v>
-      </c>
-      <c r="F23" s="17">
-        <v>1.276976108768788</v>
-      </c>
-      <c r="G23" s="18">
-        <v>0</v>
-      </c>
-      <c r="H23" s="18">
-        <v>0</v>
-      </c>
-      <c r="I23" s="18">
-        <v>0</v>
-      </c>
-      <c r="J23" s="18">
-        <v>1.276976108768788</v>
-      </c>
-      <c r="K23" s="18">
-        <v>0</v>
-      </c>
-      <c r="L23" s="18">
-        <v>0</v>
-      </c>
-      <c r="M23" s="19">
-        <v>0</v>
-      </c>
-      <c r="N23" s="19">
-        <v>0</v>
-      </c>
-      <c r="O23" s="19">
-        <v>0.2827026579511238</v>
+        <v>199.8899993896484</v>
+      </c>
+      <c r="F23" s="16">
+        <v>0.5922233698450092</v>
+      </c>
+      <c r="G23" s="19">
+        <v>0.561347890123932</v>
+      </c>
+      <c r="H23" s="19">
+        <v>0.0970884411429475</v>
+      </c>
+      <c r="I23" s="19">
+        <v>1.717140484071832</v>
+      </c>
+      <c r="J23" s="19">
+        <v>0.4732527330377264</v>
+      </c>
+      <c r="K23" s="19">
+        <v>40.156254</v>
+      </c>
+      <c r="L23" s="19">
+        <v>1.5220274</v>
+      </c>
+      <c r="M23" s="20">
+        <v>0.034930002</v>
+      </c>
+      <c r="N23" s="20">
+        <v>0.525</v>
+      </c>
+      <c r="O23" s="20">
+        <v>0.1784389954547307</v>
       </c>
       <c r="P23" s="11">
-        <v>47.20316216932195</v>
+        <v>50.42557745600141</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -2753,52 +3570,52 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E24" s="10">
-        <v>298.5799865722656</v>
-      </c>
-      <c r="F24" s="17">
-        <v>1.265890125100229</v>
-      </c>
-      <c r="G24" s="18">
-        <v>0</v>
-      </c>
-      <c r="H24" s="18">
-        <v>0</v>
-      </c>
-      <c r="I24" s="18">
-        <v>0</v>
-      </c>
-      <c r="J24" s="18">
-        <v>1.265890125100229</v>
-      </c>
-      <c r="K24" s="18">
-        <v>0</v>
-      </c>
-      <c r="L24" s="18">
-        <v>0</v>
-      </c>
-      <c r="M24" s="19">
-        <v>0</v>
-      </c>
-      <c r="N24" s="19">
-        <v>0</v>
-      </c>
-      <c r="O24" s="19">
-        <v>0.8259538819162733</v>
+        <v>65</v>
+      </c>
+      <c r="F24" s="16">
+        <v>0.5907221505626017</v>
+      </c>
+      <c r="G24" s="19">
+        <v>1.175622071073703</v>
+      </c>
+      <c r="H24" s="19">
+        <v>-0.5327402912596072</v>
+      </c>
+      <c r="I24" s="19">
+        <v>-0.5389901628995794</v>
+      </c>
+      <c r="J24" s="19">
+        <v>1.506897088301099</v>
+      </c>
+      <c r="K24" s="19">
+        <v>12.357601</v>
+      </c>
+      <c r="L24" s="19">
+        <v>1.4373919</v>
+      </c>
+      <c r="M24" s="20">
+        <v>-0.20358999</v>
+      </c>
+      <c r="N24" s="20">
+        <v>0.046</v>
+      </c>
+      <c r="O24" s="20">
+        <v>0.5341043577672937</v>
       </c>
       <c r="P24" s="11">
-        <v>77.41667014026935</v>
+        <v>50.06441216106845</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -2806,52 +3623,52 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="E25" s="10">
-        <v>830.1699829101562</v>
-      </c>
-      <c r="F25" s="17">
-        <v>1.230931428907135</v>
-      </c>
-      <c r="G25" s="18">
-        <v>0</v>
-      </c>
-      <c r="H25" s="18">
-        <v>0</v>
-      </c>
-      <c r="I25" s="18">
-        <v>0</v>
-      </c>
-      <c r="J25" s="18">
-        <v>1.230931428907135</v>
-      </c>
-      <c r="K25" s="18">
-        <v>0</v>
-      </c>
-      <c r="L25" s="18">
-        <v>0</v>
-      </c>
-      <c r="M25" s="19">
-        <v>0</v>
-      </c>
-      <c r="N25" s="19">
-        <v>0</v>
-      </c>
-      <c r="O25" s="19">
-        <v>0.230373641220772</v>
+        <v>129.7200012207031</v>
+      </c>
+      <c r="F25" s="16">
+        <v>0.5869418715181554</v>
+      </c>
+      <c r="G25" s="19">
+        <v>0.3568150294101221</v>
+      </c>
+      <c r="H25" s="19">
+        <v>0.8874455070737253</v>
+      </c>
+      <c r="I25" s="19">
+        <v>0.6313896241094424</v>
+      </c>
+      <c r="J25" s="19">
+        <v>0.5444251410342369</v>
+      </c>
+      <c r="K25" s="19">
+        <v>16.303185</v>
+      </c>
+      <c r="L25" s="19">
+        <v>4.0541053</v>
+      </c>
+      <c r="M25" s="20">
+        <v>0.30667</v>
+      </c>
+      <c r="N25" s="20">
+        <v>0.377</v>
+      </c>
+      <c r="O25" s="20">
+        <v>0.2837209035437687</v>
       </c>
       <c r="P25" s="11">
-        <v>49.56568936263437</v>
+        <v>68.25626598140605</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -2859,52 +3676,52 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E26" s="10">
-        <v>87.26000213623047</v>
-      </c>
-      <c r="F26" s="17">
-        <v>1.163551174438297</v>
-      </c>
-      <c r="G26" s="18">
-        <v>0</v>
-      </c>
-      <c r="H26" s="18">
-        <v>0</v>
-      </c>
-      <c r="I26" s="18">
-        <v>0</v>
-      </c>
-      <c r="J26" s="18">
-        <v>1.163551174438297</v>
-      </c>
-      <c r="K26" s="18">
-        <v>0</v>
-      </c>
-      <c r="L26" s="18">
-        <v>0</v>
-      </c>
-      <c r="M26" s="19">
-        <v>0</v>
-      </c>
-      <c r="N26" s="19">
-        <v>0</v>
-      </c>
-      <c r="O26" s="19">
-        <v>1</v>
+        <v>199.8899993896484</v>
+      </c>
+      <c r="F26" s="16">
+        <v>0.5642709524720174</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0.5728138826097362</v>
+      </c>
+      <c r="H26" s="19">
+        <v>-0.06908867602196844</v>
+      </c>
+      <c r="I26" s="19">
+        <v>2.415351960752095</v>
+      </c>
+      <c r="J26" s="19">
+        <v>0.1579872086059146</v>
+      </c>
+      <c r="K26" s="19">
+        <v>19.755836</v>
+      </c>
+      <c r="L26" s="19">
+        <v>2.098037</v>
+      </c>
+      <c r="M26" s="20">
+        <v>0.12231</v>
+      </c>
+      <c r="N26" s="20">
+        <v>0.535</v>
+      </c>
+      <c r="O26" s="20">
+        <v>0.09788111313823489</v>
       </c>
       <c r="P26" s="11">
-        <v>37.22597026274396</v>
+        <v>58.91739530015754</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -2912,52 +3729,52 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="E27" s="10">
-        <v>435.3800048828125</v>
-      </c>
-      <c r="F27" s="17">
-        <v>1.151472477282855</v>
-      </c>
-      <c r="G27" s="18">
-        <v>0</v>
-      </c>
-      <c r="H27" s="18">
-        <v>0</v>
-      </c>
-      <c r="I27" s="18">
-        <v>0</v>
-      </c>
-      <c r="J27" s="18">
-        <v>1.151472477282855</v>
-      </c>
-      <c r="K27" s="18">
-        <v>0</v>
-      </c>
-      <c r="L27" s="18">
-        <v>0</v>
-      </c>
-      <c r="M27" s="19">
-        <v>0</v>
-      </c>
-      <c r="N27" s="19">
-        <v>0</v>
-      </c>
-      <c r="O27" s="19">
-        <v>0.5537477457285238</v>
+        <v>216.7700042724609</v>
+      </c>
+      <c r="F27" s="16">
+        <v>0.5637359580004875</v>
+      </c>
+      <c r="G27" s="19">
+        <v>0.3452907642059501</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0.8001987998031764</v>
+      </c>
+      <c r="I27" s="19">
+        <v>0.4732064398512328</v>
+      </c>
+      <c r="J27" s="19">
+        <v>0.6303935427007451</v>
+      </c>
+      <c r="K27" s="19">
+        <v>17.306387</v>
+      </c>
+      <c r="L27" s="19">
+        <v>3.1574755</v>
+      </c>
+      <c r="M27" s="20">
+        <v>0.17969999</v>
+      </c>
+      <c r="N27" s="20">
+        <v>0.28</v>
+      </c>
+      <c r="O27" s="20">
+        <v>0.2982677473624069</v>
       </c>
       <c r="P27" s="11">
-        <v>40.76303867334101</v>
+        <v>52.74212183763184</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -2965,52 +3782,52 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E28" s="10">
-        <v>190.9199981689453</v>
-      </c>
-      <c r="F28" s="17">
-        <v>1.134638967683542</v>
-      </c>
-      <c r="G28" s="18">
-        <v>0</v>
-      </c>
-      <c r="H28" s="18">
-        <v>0</v>
-      </c>
-      <c r="I28" s="18">
-        <v>0</v>
-      </c>
-      <c r="J28" s="18">
-        <v>1.134638967683542</v>
-      </c>
-      <c r="K28" s="18">
-        <v>0</v>
-      </c>
-      <c r="L28" s="18">
-        <v>0</v>
-      </c>
-      <c r="M28" s="19">
-        <v>0</v>
-      </c>
-      <c r="N28" s="19">
-        <v>0</v>
-      </c>
-      <c r="O28" s="19">
-        <v>0.543612955996025</v>
+        <v>346.9599914550781</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0.5463950366355268</v>
+      </c>
+      <c r="G28" s="19">
+        <v>-0.3026541063380147</v>
+      </c>
+      <c r="H28" s="19">
+        <v>1.453871687245511</v>
+      </c>
+      <c r="I28" s="19">
+        <v>1.455283430456029</v>
+      </c>
+      <c r="J28" s="19">
+        <v>0.1847694405238303</v>
+      </c>
+      <c r="K28" s="19">
+        <v>17.464125</v>
+      </c>
+      <c r="L28" s="19">
+        <v>6.838651</v>
+      </c>
+      <c r="M28" s="20">
+        <v>0.48676</v>
+      </c>
+      <c r="N28" s="20">
+        <v>0.242</v>
+      </c>
+      <c r="O28" s="20">
+        <v>0.1174384195201885</v>
       </c>
       <c r="P28" s="11">
-        <v>59.32691505676462</v>
+        <v>48.73101448655449</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -3018,52 +3835,52 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="E29" s="10">
-        <v>339.125</v>
-      </c>
-      <c r="F29" s="17">
-        <v>1.118028567070168</v>
-      </c>
-      <c r="G29" s="18">
-        <v>0</v>
-      </c>
-      <c r="H29" s="18">
-        <v>0</v>
-      </c>
-      <c r="I29" s="18">
-        <v>0</v>
-      </c>
-      <c r="J29" s="18">
-        <v>1.118028567070168</v>
-      </c>
-      <c r="K29" s="18">
-        <v>0</v>
-      </c>
-      <c r="L29" s="18">
-        <v>0</v>
-      </c>
-      <c r="M29" s="19">
-        <v>0</v>
-      </c>
-      <c r="N29" s="19">
-        <v>0</v>
-      </c>
-      <c r="O29" s="19">
-        <v>0.8067067544728903</v>
+        <v>369.6600036621094</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0.5369847906027814</v>
+      </c>
+      <c r="G29" s="19">
+        <v>1.091200655903261</v>
+      </c>
+      <c r="H29" s="19">
+        <v>0.1101459112354547</v>
+      </c>
+      <c r="I29" s="19">
+        <v>-0.3352804504404189</v>
+      </c>
+      <c r="J29" s="19">
+        <v>0.7746006119633412</v>
+      </c>
+      <c r="K29" s="19">
+        <v>9.963699999999999</v>
+      </c>
+      <c r="L29" s="19">
+        <v>2.3337615</v>
+      </c>
+      <c r="M29" s="20">
+        <v>0.26511</v>
+      </c>
+      <c r="N29" s="20">
+        <v>0.003</v>
+      </c>
+      <c r="O29" s="20">
+        <v>0.2197789981031173</v>
       </c>
       <c r="P29" s="11">
-        <v>69.20991473594977</v>
+        <v>53.19665050439053</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -3071,52 +3888,52 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="E30" s="10">
-        <v>364.8999938964844</v>
-      </c>
-      <c r="F30" s="17">
-        <v>1.116983241369677</v>
-      </c>
-      <c r="G30" s="18">
-        <v>0</v>
-      </c>
-      <c r="H30" s="18">
-        <v>0</v>
-      </c>
-      <c r="I30" s="18">
-        <v>0</v>
-      </c>
-      <c r="J30" s="18">
-        <v>1.116983241369677</v>
-      </c>
-      <c r="K30" s="18">
-        <v>0</v>
-      </c>
-      <c r="L30" s="18">
-        <v>0</v>
-      </c>
-      <c r="M30" s="19">
-        <v>0</v>
-      </c>
-      <c r="N30" s="19">
-        <v>0</v>
-      </c>
-      <c r="O30" s="19">
-        <v>0.146115547815765</v>
+        <v>343.3399963378906</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0.5297181734312539</v>
+      </c>
+      <c r="G30" s="19">
+        <v>-0.2917499460294181</v>
+      </c>
+      <c r="H30" s="19">
+        <v>1.453871687245511</v>
+      </c>
+      <c r="I30" s="19">
+        <v>1.455283430456029</v>
+      </c>
+      <c r="J30" s="19">
+        <v>0.1182757362009909</v>
+      </c>
+      <c r="K30" s="19">
+        <v>17.298695</v>
+      </c>
+      <c r="L30" s="19">
+        <v>6.770473</v>
+      </c>
+      <c r="M30" s="20">
+        <v>0.48676</v>
+      </c>
+      <c r="N30" s="20">
+        <v>0.242</v>
+      </c>
+      <c r="O30" s="20">
+        <v>0.1057141321154904</v>
       </c>
       <c r="P30" s="11">
-        <v>45.86882377045316</v>
+        <v>47.33975978251333</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -3124,52 +3941,52 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E31" s="10">
-        <v>87.48000335693359</v>
-      </c>
-      <c r="F31" s="17">
-        <v>1.089533725542335</v>
-      </c>
-      <c r="G31" s="18">
-        <v>0</v>
-      </c>
-      <c r="H31" s="18">
-        <v>0</v>
-      </c>
-      <c r="I31" s="18">
-        <v>0</v>
-      </c>
-      <c r="J31" s="18">
-        <v>1.089533725542335</v>
-      </c>
-      <c r="K31" s="18">
-        <v>0</v>
-      </c>
-      <c r="L31" s="18">
-        <v>0</v>
-      </c>
-      <c r="M31" s="19">
-        <v>0</v>
-      </c>
-      <c r="N31" s="19">
-        <v>0</v>
-      </c>
-      <c r="O31" s="19">
-        <v>0.4350794988589382</v>
+        <v>127.2600021362305</v>
+      </c>
+      <c r="F31" s="16">
+        <v>0.4936836947371027</v>
+      </c>
+      <c r="G31" s="19">
+        <v>0.6458174147154766</v>
+      </c>
+      <c r="H31" s="19">
+        <v>0.432781060607519</v>
+      </c>
+      <c r="I31" s="19">
+        <v>0.3540288428030787</v>
+      </c>
+      <c r="J31" s="19">
+        <v>0.4621295958337271</v>
+      </c>
+      <c r="K31" s="19">
+        <v>9.616072000000001</v>
+      </c>
+      <c r="L31" s="19">
+        <v>3.4084976</v>
+      </c>
+      <c r="M31" s="20">
+        <v>0.29867</v>
+      </c>
+      <c r="N31" s="20">
+        <v>0.176</v>
+      </c>
+      <c r="O31" s="20">
+        <v>0.3363639065753112</v>
       </c>
       <c r="P31" s="11">
-        <v>57.18028259137401</v>
+        <v>60.06848028604878</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -3177,52 +3994,52 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="E32" s="10">
-        <v>241.9600067138672</v>
-      </c>
-      <c r="F32" s="17">
-        <v>1.065283081012613</v>
-      </c>
-      <c r="G32" s="18">
-        <v>0</v>
-      </c>
-      <c r="H32" s="18">
-        <v>0</v>
-      </c>
-      <c r="I32" s="18">
-        <v>0</v>
-      </c>
-      <c r="J32" s="18">
-        <v>1.065283081012613</v>
-      </c>
-      <c r="K32" s="18">
-        <v>0</v>
-      </c>
-      <c r="L32" s="18">
-        <v>0</v>
-      </c>
-      <c r="M32" s="19">
-        <v>0</v>
-      </c>
-      <c r="N32" s="19">
-        <v>0</v>
-      </c>
-      <c r="O32" s="19">
-        <v>0.5822419332516657</v>
+        <v>153.6600036621094</v>
+      </c>
+      <c r="F32" s="16">
+        <v>0.479476579540434</v>
+      </c>
+      <c r="G32" s="19">
+        <v>-1.877249539822365</v>
+      </c>
+      <c r="H32" s="19">
+        <v>1.758964460615154</v>
+      </c>
+      <c r="I32" s="19">
+        <v>0.3182836657213104</v>
+      </c>
+      <c r="J32" s="19">
+        <v>1.850559254917194</v>
+      </c>
+      <c r="K32" s="19">
+        <v>54.282146</v>
+      </c>
+      <c r="L32" s="19">
+        <v>71.89688</v>
+      </c>
+      <c r="M32" s="20">
+        <v>1.17442</v>
+      </c>
+      <c r="N32" s="20">
+        <v>0.256</v>
+      </c>
+      <c r="O32" s="20">
+        <v>1.042536179787998</v>
       </c>
       <c r="P32" s="11">
-        <v>75.86365996659075</v>
+        <v>46.38067291804938</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -3230,52 +4047,52 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="E33" s="10">
-        <v>188.1499938964844</v>
-      </c>
-      <c r="F33" s="17">
-        <v>1.059151742172855</v>
-      </c>
-      <c r="G33" s="18">
-        <v>0</v>
-      </c>
-      <c r="H33" s="18">
-        <v>0</v>
-      </c>
-      <c r="I33" s="18">
-        <v>0</v>
-      </c>
-      <c r="J33" s="18">
-        <v>1.059151742172855</v>
-      </c>
-      <c r="K33" s="18">
-        <v>0</v>
-      </c>
-      <c r="L33" s="18">
-        <v>0</v>
-      </c>
-      <c r="M33" s="19">
-        <v>0</v>
-      </c>
-      <c r="N33" s="19">
-        <v>0</v>
-      </c>
-      <c r="O33" s="19">
-        <v>0.4764968488259695</v>
+        <v>112.870002746582</v>
+      </c>
+      <c r="F33" s="16">
+        <v>0.469396824720007</v>
+      </c>
+      <c r="G33" s="19">
+        <v>0.6818833135656812</v>
+      </c>
+      <c r="H33" s="19">
+        <v>0.6287894397638343</v>
+      </c>
+      <c r="I33" s="19">
+        <v>-0.1751734853969869</v>
+      </c>
+      <c r="J33" s="19">
+        <v>0.4463683117296403</v>
+      </c>
+      <c r="K33" s="19">
+        <v>11.196411</v>
+      </c>
+      <c r="L33" s="19">
+        <v>2.1772428</v>
+      </c>
+      <c r="M33" s="20">
+        <v>0.19399999</v>
+      </c>
+      <c r="N33" s="20">
+        <v>0.107</v>
+      </c>
+      <c r="O33" s="20">
+        <v>0.2228426400134897</v>
       </c>
       <c r="P33" s="11">
-        <v>51.3815664185782</v>
+        <v>49.07170722100347</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -3283,52 +4100,52 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="E34" s="10">
-        <v>363.2999877929688</v>
-      </c>
-      <c r="F34" s="17">
-        <v>1.043383515169131</v>
-      </c>
-      <c r="G34" s="18">
-        <v>0</v>
-      </c>
-      <c r="H34" s="18">
-        <v>0</v>
-      </c>
-      <c r="I34" s="18">
-        <v>0</v>
-      </c>
-      <c r="J34" s="18">
-        <v>1.043383515169131</v>
-      </c>
-      <c r="K34" s="18">
-        <v>0</v>
-      </c>
-      <c r="L34" s="18">
-        <v>0</v>
-      </c>
-      <c r="M34" s="19">
-        <v>0</v>
-      </c>
-      <c r="N34" s="19">
-        <v>0</v>
-      </c>
-      <c r="O34" s="19">
-        <v>0.5705515143087754</v>
+        <v>162.4499969482422</v>
+      </c>
+      <c r="F34" s="16">
+        <v>0.4654127043023902</v>
+      </c>
+      <c r="G34" s="19">
+        <v>-0.5758934002812983</v>
+      </c>
+      <c r="H34" s="19">
+        <v>1.369553352432538</v>
+      </c>
+      <c r="I34" s="19">
+        <v>1.952411925208389</v>
+      </c>
+      <c r="J34" s="19">
+        <v>0.009768658324623303</v>
+      </c>
+      <c r="K34" s="19">
+        <v>35.594406</v>
+      </c>
+      <c r="L34" s="19">
+        <v>8.938188</v>
+      </c>
+      <c r="M34" s="20">
+        <v>0.30712</v>
+      </c>
+      <c r="N34" s="20">
+        <v>0.611</v>
+      </c>
+      <c r="O34" s="20">
+        <v>0.1433698962181122</v>
       </c>
       <c r="P34" s="11">
-        <v>64.55257609146807</v>
+        <v>49.57575928897391</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -3336,52 +4153,52 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E35" s="10">
-        <v>28.57999992370605</v>
-      </c>
-      <c r="F35" s="17">
-        <v>0.9333851933765743</v>
-      </c>
-      <c r="G35" s="18">
+        <v>213.7799987792969</v>
+      </c>
+      <c r="F35" s="16">
+        <v>0.446466482716136</v>
+      </c>
+      <c r="G35" s="19">
+        <v>0.1534000000694478</v>
+      </c>
+      <c r="H35" s="19">
+        <v>1.132904211800141</v>
+      </c>
+      <c r="I35" s="19">
+        <v>0.2283188730840903</v>
+      </c>
+      <c r="J35" s="19">
+        <v>0.2765753292755094</v>
+      </c>
+      <c r="K35" s="19">
+        <v>23.318033</v>
+      </c>
+      <c r="L35" s="19">
+        <v>-14.997891</v>
+      </c>
+      <c r="M35" s="20">
         <v>0</v>
       </c>
-      <c r="H35" s="18">
-        <v>0</v>
-      </c>
-      <c r="I35" s="18">
-        <v>0</v>
-      </c>
-      <c r="J35" s="18">
-        <v>0.9333851933765743</v>
-      </c>
-      <c r="K35" s="18">
-        <v>0</v>
-      </c>
-      <c r="L35" s="18">
-        <v>0</v>
-      </c>
-      <c r="M35" s="19">
-        <v>0</v>
-      </c>
-      <c r="N35" s="19">
-        <v>0</v>
-      </c>
-      <c r="O35" s="19">
-        <v>0.6020340195723306</v>
+      <c r="N35" s="20">
+        <v>0.081</v>
+      </c>
+      <c r="O35" s="20">
+        <v>0.3199161865620579</v>
       </c>
       <c r="P35" s="11">
-        <v>52.51493649488436</v>
+        <v>64.26839155120049</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -3389,52 +4206,52 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="E36" s="10">
-        <v>169.8899993896484</v>
-      </c>
-      <c r="F36" s="17">
-        <v>0.8915177014178642</v>
-      </c>
-      <c r="G36" s="18">
-        <v>0</v>
-      </c>
-      <c r="H36" s="18">
-        <v>0</v>
-      </c>
-      <c r="I36" s="18">
-        <v>0</v>
-      </c>
-      <c r="J36" s="18">
-        <v>0.8915177014178642</v>
-      </c>
-      <c r="K36" s="18">
-        <v>0</v>
-      </c>
-      <c r="L36" s="18">
-        <v>0</v>
-      </c>
-      <c r="M36" s="19">
-        <v>0</v>
-      </c>
-      <c r="N36" s="19">
-        <v>0</v>
-      </c>
-      <c r="O36" s="19">
-        <v>0.5247171790671665</v>
+        <v>174.7100067138672</v>
+      </c>
+      <c r="F36" s="16">
+        <v>0.4322510603569443</v>
+      </c>
+      <c r="G36" s="19">
+        <v>0.5368950783305056</v>
+      </c>
+      <c r="H36" s="19">
+        <v>0.5945270320387294</v>
+      </c>
+      <c r="I36" s="19">
+        <v>0.0123304280898874</v>
+      </c>
+      <c r="J36" s="19">
+        <v>0.4023373821154242</v>
+      </c>
+      <c r="K36" s="19">
+        <v>15.270527</v>
+      </c>
+      <c r="L36" s="19">
+        <v>2.6730006</v>
+      </c>
+      <c r="M36" s="20">
+        <v>0.18416001</v>
+      </c>
+      <c r="N36" s="20">
+        <v>0.151</v>
+      </c>
+      <c r="O36" s="20">
+        <v>0.1319085595271483</v>
       </c>
       <c r="P36" s="11">
-        <v>79.36512889929674</v>
+        <v>50.09074654604255</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -3442,52 +4259,52 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="E37" s="10">
-        <v>597.5900268554688</v>
-      </c>
-      <c r="F37" s="17">
-        <v>0.8636944523279921</v>
-      </c>
-      <c r="G37" s="18">
-        <v>0</v>
-      </c>
-      <c r="H37" s="18">
-        <v>0</v>
-      </c>
-      <c r="I37" s="18">
-        <v>0</v>
-      </c>
-      <c r="J37" s="18">
-        <v>0.8636944523279922</v>
-      </c>
-      <c r="K37" s="18">
-        <v>0</v>
-      </c>
-      <c r="L37" s="18">
-        <v>0</v>
-      </c>
-      <c r="M37" s="19">
-        <v>0</v>
-      </c>
-      <c r="N37" s="19">
-        <v>0</v>
-      </c>
-      <c r="O37" s="19">
-        <v>0.4112743798648562</v>
+        <v>171.4199981689453</v>
+      </c>
+      <c r="F37" s="16">
+        <v>0.4306319469932199</v>
+      </c>
+      <c r="G37" s="19">
+        <v>0.9039922035122165</v>
+      </c>
+      <c r="H37" s="19">
+        <v>0.2335474389445495</v>
+      </c>
+      <c r="I37" s="19">
+        <v>0.6837145595313986</v>
+      </c>
+      <c r="J37" s="19">
+        <v>-0.005032525754307548</v>
+      </c>
+      <c r="K37" s="19">
+        <v>7.9410954</v>
+      </c>
+      <c r="L37" s="19">
+        <v>1.5754024</v>
+      </c>
+      <c r="M37" s="20">
+        <v>0.21484</v>
+      </c>
+      <c r="N37" s="20">
+        <v>0.316</v>
+      </c>
+      <c r="O37" s="20">
+        <v>0.0786836852825421</v>
       </c>
       <c r="P37" s="11">
-        <v>52.79087242304367</v>
+        <v>43.75440853527889</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -3495,52 +4312,52 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="E38" s="10">
-        <v>81.37999725341797</v>
-      </c>
-      <c r="F38" s="17">
-        <v>0.859198572216901</v>
-      </c>
-      <c r="G38" s="18">
-        <v>0</v>
-      </c>
-      <c r="H38" s="18">
-        <v>0</v>
-      </c>
-      <c r="I38" s="18">
-        <v>0</v>
-      </c>
-      <c r="J38" s="18">
-        <v>0.859198572216901</v>
-      </c>
-      <c r="K38" s="18">
-        <v>0</v>
-      </c>
-      <c r="L38" s="18">
-        <v>0</v>
-      </c>
-      <c r="M38" s="19">
-        <v>0</v>
-      </c>
-      <c r="N38" s="19">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19">
-        <v>0.6035467439097137</v>
+        <v>46.90999984741211</v>
+      </c>
+      <c r="F38" s="16">
+        <v>0.4214809690581295</v>
+      </c>
+      <c r="G38" s="19">
+        <v>0.4704959025733791</v>
+      </c>
+      <c r="H38" s="19">
+        <v>0.07046152471131609</v>
+      </c>
+      <c r="I38" s="19">
+        <v>1.41063650916965</v>
+      </c>
+      <c r="J38" s="19">
+        <v>0.1704044691094643</v>
+      </c>
+      <c r="K38" s="19">
+        <v>10.484783</v>
+      </c>
+      <c r="L38" s="19">
+        <v>1.3284671</v>
+      </c>
+      <c r="M38" s="20">
+        <v>0.11522</v>
+      </c>
+      <c r="N38" s="20">
+        <v>0.642</v>
+      </c>
+      <c r="O38" s="20">
+        <v>0.09728310964733433</v>
       </c>
       <c r="P38" s="11">
-        <v>53.17081448589917</v>
+        <v>55.41943106438682</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -3548,52 +4365,52 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="E39" s="10">
-        <v>26.48999977111816</v>
-      </c>
-      <c r="F39" s="17">
-        <v>0.8458227045310803</v>
-      </c>
-      <c r="G39" s="18">
+        <v>68.06999969482422</v>
+      </c>
+      <c r="F39" s="16">
+        <v>0.4082626384251519</v>
+      </c>
+      <c r="G39" s="19">
+        <v>0.5078777743715293</v>
+      </c>
+      <c r="H39" s="19">
+        <v>1.335916108729087</v>
+      </c>
+      <c r="I39" s="19">
+        <v>-0.5911526511284643</v>
+      </c>
+      <c r="J39" s="19">
+        <v>0.0353105886689701</v>
+      </c>
+      <c r="K39" s="19">
+        <v>13.916667</v>
+      </c>
+      <c r="L39" s="19">
+        <v>-42.84731</v>
+      </c>
+      <c r="M39" s="20">
         <v>0</v>
       </c>
-      <c r="H39" s="18">
-        <v>0</v>
-      </c>
-      <c r="I39" s="18">
-        <v>0</v>
-      </c>
-      <c r="J39" s="18">
-        <v>0.8458227045310803</v>
-      </c>
-      <c r="K39" s="18">
-        <v>0</v>
-      </c>
-      <c r="L39" s="18">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19">
-        <v>0.2472620589611176</v>
+      <c r="N39" s="20">
+        <v>0.012</v>
+      </c>
+      <c r="O39" s="20">
+        <v>0.01437727940312072</v>
       </c>
       <c r="P39" s="11">
-        <v>57.48551490986506</v>
+        <v>50.16306347391859</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -3601,52 +4418,52 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="E40" s="10">
-        <v>98.51000213623047</v>
-      </c>
-      <c r="F40" s="17">
-        <v>0.8344397195398325</v>
-      </c>
-      <c r="G40" s="18">
-        <v>0</v>
-      </c>
-      <c r="H40" s="18">
-        <v>0</v>
-      </c>
-      <c r="I40" s="18">
-        <v>0</v>
-      </c>
-      <c r="J40" s="18">
-        <v>0.8344397195398325</v>
-      </c>
-      <c r="K40" s="18">
-        <v>0</v>
-      </c>
-      <c r="L40" s="18">
-        <v>0</v>
-      </c>
-      <c r="M40" s="19">
-        <v>0</v>
-      </c>
-      <c r="N40" s="19">
-        <v>0</v>
-      </c>
-      <c r="O40" s="19">
-        <v>0.153258094705423</v>
+        <v>112.2699966430664</v>
+      </c>
+      <c r="F40" s="16">
+        <v>0.401508448608237</v>
+      </c>
+      <c r="G40" s="19">
+        <v>0.02982011516877862</v>
+      </c>
+      <c r="H40" s="19">
+        <v>1.249493192438245</v>
+      </c>
+      <c r="I40" s="19">
+        <v>0.1792183728511779</v>
+      </c>
+      <c r="J40" s="19">
+        <v>0.1776878667345517</v>
+      </c>
+      <c r="K40" s="19">
+        <v>20.440647</v>
+      </c>
+      <c r="L40" s="19">
+        <v>4.4703617</v>
+      </c>
+      <c r="M40" s="20">
+        <v>0.20273</v>
+      </c>
+      <c r="N40" s="20">
+        <v>0.209</v>
+      </c>
+      <c r="O40" s="20">
+        <v>0.2135030904411721</v>
       </c>
       <c r="P40" s="11">
-        <v>52.83416844507703</v>
+        <v>67.13988651183436</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -3654,52 +4471,52 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="E41" s="10">
-        <v>190.2100067138672</v>
-      </c>
-      <c r="F41" s="17">
-        <v>0.8135795256808406</v>
-      </c>
-      <c r="G41" s="18">
-        <v>0</v>
-      </c>
-      <c r="H41" s="18">
-        <v>0</v>
-      </c>
-      <c r="I41" s="18">
-        <v>0</v>
-      </c>
-      <c r="J41" s="18">
-        <v>0.8135795256808406</v>
-      </c>
-      <c r="K41" s="18">
-        <v>0</v>
-      </c>
-      <c r="L41" s="18">
-        <v>0</v>
-      </c>
-      <c r="M41" s="19">
-        <v>0</v>
-      </c>
-      <c r="N41" s="19">
-        <v>0</v>
-      </c>
-      <c r="O41" s="19">
-        <v>0.5469258956581013</v>
+        <v>67.91999816894531</v>
+      </c>
+      <c r="F41" s="16">
+        <v>0.3959369122197662</v>
+      </c>
+      <c r="G41" s="19">
+        <v>0.4782631507053702</v>
+      </c>
+      <c r="H41" s="19">
+        <v>0.5511183194325295</v>
+      </c>
+      <c r="I41" s="19">
+        <v>0.2691043413223938</v>
+      </c>
+      <c r="J41" s="19">
+        <v>0.2477091198388789</v>
+      </c>
+      <c r="K41" s="19">
+        <v>14.819383</v>
+      </c>
+      <c r="L41" s="19">
+        <v>6.1583524</v>
+      </c>
+      <c r="M41" s="20">
+        <v>0.46598998</v>
+      </c>
+      <c r="N41" s="20">
+        <v>0.057</v>
+      </c>
+      <c r="O41" s="20">
+        <v>0.1265410373532643</v>
       </c>
       <c r="P41" s="11">
-        <v>73.45705869486477</v>
+        <v>65.29564911795941</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -3707,52 +4524,52 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="E42" s="10">
-        <v>162.1399993896484</v>
-      </c>
-      <c r="F42" s="17">
-        <v>0.810185697057813</v>
-      </c>
-      <c r="G42" s="18">
-        <v>0</v>
-      </c>
-      <c r="H42" s="18">
-        <v>0</v>
-      </c>
-      <c r="I42" s="18">
-        <v>0</v>
-      </c>
-      <c r="J42" s="18">
-        <v>0.810185697057813</v>
-      </c>
-      <c r="K42" s="18">
-        <v>0</v>
-      </c>
-      <c r="L42" s="18">
-        <v>0</v>
-      </c>
-      <c r="M42" s="19">
-        <v>0</v>
-      </c>
-      <c r="N42" s="19">
-        <v>0</v>
-      </c>
-      <c r="O42" s="19">
-        <v>0.4145017079571061</v>
+        <v>38.45999908447266</v>
+      </c>
+      <c r="F42" s="16">
+        <v>0.3959216649113371</v>
+      </c>
+      <c r="G42" s="19">
+        <v>-0.1424155317128326</v>
+      </c>
+      <c r="H42" s="19">
+        <v>-0.4492650758349748</v>
+      </c>
+      <c r="I42" s="19">
+        <v>3.726301659006618</v>
+      </c>
+      <c r="J42" s="19">
+        <v>-0.02660885155687352</v>
+      </c>
+      <c r="K42" s="19">
+        <v>11.418831</v>
+      </c>
+      <c r="L42" s="19">
+        <v>2.1043499</v>
+      </c>
+      <c r="M42" s="20">
+        <v>0.21465999</v>
+      </c>
+      <c r="N42" s="20">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="O42" s="20">
+        <v>0.2354641863577085</v>
       </c>
       <c r="P42" s="11">
-        <v>58.63147031095819</v>
+        <v>62.08161803052544</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -3760,52 +4577,52 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="E43" s="10">
-        <v>42.95999908447266</v>
-      </c>
-      <c r="F43" s="17">
-        <v>0.7734985035655443</v>
-      </c>
-      <c r="G43" s="18">
-        <v>0</v>
-      </c>
-      <c r="H43" s="18">
-        <v>0</v>
-      </c>
-      <c r="I43" s="18">
-        <v>0</v>
-      </c>
-      <c r="J43" s="18">
-        <v>0.7734985035655443</v>
-      </c>
-      <c r="K43" s="18">
-        <v>0</v>
-      </c>
-      <c r="L43" s="18">
-        <v>0</v>
-      </c>
-      <c r="M43" s="19">
-        <v>0</v>
-      </c>
-      <c r="N43" s="19">
-        <v>0</v>
-      </c>
-      <c r="O43" s="19">
-        <v>0.5164324530672304</v>
+        <v>360.5199890136719</v>
+      </c>
+      <c r="F43" s="16">
+        <v>0.3883297648567724</v>
+      </c>
+      <c r="G43" s="19">
+        <v>0.1745054589838901</v>
+      </c>
+      <c r="H43" s="19">
+        <v>-0.2017379700313818</v>
+      </c>
+      <c r="I43" s="19">
+        <v>0.5362618455560154</v>
+      </c>
+      <c r="J43" s="19">
+        <v>1.019911142786829</v>
+      </c>
+      <c r="K43" s="19">
+        <v>33.79535</v>
+      </c>
+      <c r="L43" s="19">
+        <v>5.012071</v>
+      </c>
+      <c r="M43" s="20">
+        <v>0.15286</v>
+      </c>
+      <c r="N43" s="20">
+        <v>0.204</v>
+      </c>
+      <c r="O43" s="20">
+        <v>0.5287282627930578</v>
       </c>
       <c r="P43" s="11">
-        <v>66.58373799904871</v>
+        <v>62.70182944574525</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -3813,52 +4630,52 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E44" s="10">
-        <v>260.239990234375</v>
-      </c>
-      <c r="F44" s="17">
-        <v>0.7492101444876392</v>
-      </c>
-      <c r="G44" s="18">
-        <v>0</v>
-      </c>
-      <c r="H44" s="18">
-        <v>0</v>
-      </c>
-      <c r="I44" s="18">
-        <v>0</v>
-      </c>
-      <c r="J44" s="18">
-        <v>0.7492101444876392</v>
-      </c>
-      <c r="K44" s="18">
-        <v>0</v>
-      </c>
-      <c r="L44" s="18">
-        <v>0</v>
-      </c>
-      <c r="M44" s="19">
-        <v>0</v>
-      </c>
-      <c r="N44" s="19">
-        <v>0</v>
-      </c>
-      <c r="O44" s="19">
-        <v>0.6033515750650456</v>
+        <v>414.4400024414062</v>
+      </c>
+      <c r="F44" s="16">
+        <v>0.3764487284951614</v>
+      </c>
+      <c r="G44" s="19">
+        <v>-0.7682020816136508</v>
+      </c>
+      <c r="H44" s="19">
+        <v>-0.4657021273019426</v>
+      </c>
+      <c r="I44" s="19">
+        <v>4.026096567149331</v>
+      </c>
+      <c r="J44" s="19">
+        <v>0.3980679991078087</v>
+      </c>
+      <c r="K44" s="19">
+        <v>104.25127</v>
+      </c>
+      <c r="L44" s="19">
+        <v>2.6367822</v>
+      </c>
+      <c r="M44" s="20">
+        <v>0.019199999</v>
+      </c>
+      <c r="N44" s="20">
+        <v>1.134</v>
+      </c>
+      <c r="O44" s="20">
+        <v>0.2701195769101918</v>
       </c>
       <c r="P44" s="11">
-        <v>72.82661914800588</v>
+        <v>61.39262480015049</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3872,7 +4689,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DA7ABA51-AAAA-BBBB-0004-000000000001}</x14:id>
+          <x14:id>{DA7ABA51-AAAA-BBBB-0005-000000000001}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3894,7 +4711,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0004-000000000001}">
+          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0005-000000000001}">
             <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -3924,101 +4741,101 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="19">
+        <v>150</v>
+      </c>
+      <c r="B6" s="20">
         <v>0.3</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="19">
+        <v>152</v>
+      </c>
+      <c r="B7" s="20">
         <v>0.25</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" s="19">
+        <v>154</v>
+      </c>
+      <c r="B8" s="20">
         <v>0.15</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="19">
+        <v>156</v>
+      </c>
+      <c r="B9" s="20">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B10" s="19">
+        <v>158</v>
+      </c>
+      <c r="B10" s="20">
         <f>SUM(B6:B9)</f>
         <v>1.0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4058,7 +4875,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DA7ABA51-AAAA-BBBB-0005-000000000001}</x14:id>
+          <x14:id>{DA7ABA51-AAAA-BBBB-0006-000000000001}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4068,7 +4885,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0005-000000000001}">
+          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0006-000000000001}">
             <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4097,173 +4914,173 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>196</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
-      <c r="A23" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="B23" s="20"/>
+      <c r="A23" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
-      <c r="A24" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="B24" s="20"/>
+      <c r="A24" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
-      <c r="A25" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="B25" s="20"/>
+      <c r="A25" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
-      <c r="A26" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="B26" s="20"/>
+      <c r="A26" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
-      <c r="A27" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="B27" s="20"/>
+      <c r="A27" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B27" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4275,4 +5092,199 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BI1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:61">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>465.1912841796875</v>
+      </c>
+      <c r="C1">
+        <v>434.5918579101562</v>
+      </c>
+      <c r="D1">
+        <v>420.3853149414062</v>
+      </c>
+      <c r="E1">
+        <v>421.3537292480469</v>
+      </c>
+      <c r="F1">
+        <v>393.7393798828125</v>
+      </c>
+      <c r="G1">
+        <v>400.1088256835938</v>
+      </c>
+      <c r="H1">
+        <v>381.1501770019531</v>
+      </c>
+      <c r="I1">
+        <v>369.2198791503906</v>
+      </c>
+      <c r="J1">
+        <v>390.8042297363281</v>
+      </c>
+      <c r="K1">
+        <v>394.9174194335938</v>
+      </c>
+      <c r="L1">
+        <v>408.3951416015625</v>
+      </c>
+      <c r="M1">
+        <v>403.4133605957031</v>
+      </c>
+      <c r="N1">
+        <v>418.6282348632812</v>
+      </c>
+      <c r="O1">
+        <v>408.8244323730469</v>
+      </c>
+      <c r="P1">
+        <v>418.0192260742188</v>
+      </c>
+      <c r="Q1">
+        <v>427.0742797851562</v>
+      </c>
+      <c r="R1">
+        <v>433.3439025878906</v>
+      </c>
+      <c r="S1">
+        <v>408.7745361328125</v>
+      </c>
+      <c r="T1">
+        <v>398.8309326171875</v>
+      </c>
+      <c r="U1">
+        <v>413.9259948730469</v>
+      </c>
+      <c r="V1">
+        <v>430.7481994628906</v>
+      </c>
+      <c r="W1">
+        <v>424.5484619140625</v>
+      </c>
+      <c r="X1">
+        <v>393.6694946289062</v>
+      </c>
+      <c r="Y1">
+        <v>411.1206359863281</v>
+      </c>
+      <c r="Z1">
+        <v>416.5915832519531</v>
+      </c>
+      <c r="AA1">
+        <v>431.2573547363281</v>
+      </c>
+      <c r="AB1">
+        <v>449.4772644042969</v>
+      </c>
+      <c r="AC1">
+        <v>434.2524108886719</v>
+      </c>
+      <c r="AD1">
+        <v>426.4053649902344</v>
+      </c>
+      <c r="AE1">
+        <v>456.7851867675781</v>
+      </c>
+      <c r="AF1">
+        <v>411.9991760253906</v>
+      </c>
+      <c r="AG1">
+        <v>390.7343444824219</v>
+      </c>
+      <c r="AH1">
+        <v>395.6861267089844</v>
+      </c>
+      <c r="AI1">
+        <v>381.25</v>
+      </c>
+      <c r="AJ1">
+        <v>404.1499938964844</v>
+      </c>
+      <c r="AK1">
+        <v>441.7999877929688</v>
+      </c>
+      <c r="AL1">
+        <v>439.3399963378906</v>
+      </c>
+      <c r="AM1">
+        <v>437.5</v>
+      </c>
+      <c r="AN1">
+        <v>426.9100036621094</v>
+      </c>
+      <c r="AO1">
+        <v>392.1000061035156</v>
+      </c>
+      <c r="AP1">
+        <v>369.6400146484375</v>
+      </c>
+      <c r="AQ1">
+        <v>404.8099975585938</v>
+      </c>
+      <c r="AR1">
+        <v>405.3699951171875</v>
+      </c>
+      <c r="AS1">
+        <v>429.0199890136719</v>
+      </c>
+      <c r="AT1">
+        <v>467.2699890136719</v>
+      </c>
+      <c r="AU1">
+        <v>462.7000122070312</v>
+      </c>
+      <c r="AV1">
+        <v>437.6499938964844</v>
+      </c>
+      <c r="AW1">
+        <v>453.7699890136719</v>
+      </c>
+      <c r="AX1">
+        <v>457.8800048828125</v>
+      </c>
+      <c r="AY1">
+        <v>440.9700012207031</v>
+      </c>
+      <c r="AZ1">
+        <v>484.5</v>
+      </c>
+      <c r="BA1">
+        <v>494.510009765625</v>
+      </c>
+      <c r="BB1">
+        <v>490.8099975585938</v>
+      </c>
+      <c r="BC1">
+        <v>479.8099975585938</v>
+      </c>
+      <c r="BD1">
+        <v>468.6499938964844</v>
+      </c>
+      <c r="BE1">
+        <v>437.5499877929688</v>
+      </c>
+      <c r="BF1">
+        <v>434.7799987792969</v>
+      </c>
+      <c r="BG1">
+        <v>442.0799865722656</v>
+      </c>
+      <c r="BH1">
+        <v>433.1900024414062</v>
+      </c>
+      <c r="BI1">
+        <v>451.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -17,7 +17,7 @@
     <sheet name="_данные" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$Q$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,11 +25,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="223">
   <si>
     <t>DELL</t>
   </si>
   <si>
+    <t>MU</t>
+  </si>
+  <si>
     <t>Открытые позиции</t>
   </si>
   <si>
@@ -96,6 +99,12 @@
     <t>confirmed</t>
   </si>
   <si>
+    <t>Micron Technology</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
     <t>Итого</t>
   </si>
   <si>
@@ -201,12 +210,6 @@
     <t>Статус</t>
   </si>
   <si>
-    <t>MU</t>
-  </si>
-  <si>
-    <t>Micron Technology</t>
-  </si>
-  <si>
     <t>проходит</t>
   </si>
   <si>
@@ -216,6 +219,12 @@
     <t>Sandisk</t>
   </si>
   <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>Western Digital</t>
+  </si>
+  <si>
     <t>VLO</t>
   </si>
   <si>
@@ -225,12 +234,6 @@
     <t>Energy</t>
   </si>
   <si>
-    <t>WDC</t>
-  </si>
-  <si>
-    <t>Western Digital</t>
-  </si>
-  <si>
     <t>MPC</t>
   </si>
   <si>
@@ -270,25 +273,34 @@
     <t>EOG Resources</t>
   </si>
   <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>APA Corporation</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
     <t>TER</t>
   </si>
   <si>
     <t>Teradyne</t>
   </si>
   <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>APA Corporation</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
-    <t>Financials</t>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>Health Care</t>
   </si>
   <si>
     <t>HUM</t>
@@ -297,7 +309,10 @@
     <t>Humana</t>
   </si>
   <si>
-    <t>Health Care</t>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
   </si>
   <si>
     <t>PSX</t>
@@ -306,10 +321,40 @@
     <t>Phillips 66</t>
   </si>
   <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>Diamondback Energy</t>
+  </si>
+  <si>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>Centene Corporation</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
   </si>
   <si>
     <t>NVDA</t>
@@ -318,34 +363,13 @@
     <t>Nvidia</t>
   </si>
   <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>Diamondback Energy</t>
-  </si>
-  <si>
-    <t>CNC</t>
-  </si>
-  <si>
-    <t>Centene Corporation</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>CF Industries</t>
+  </si>
+  <si>
+    <t>Materials</t>
   </si>
   <si>
     <t>GOOGL</t>
@@ -357,10 +381,10 @@
     <t>Communication Services</t>
   </si>
   <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
+    <t>SCHW</t>
+  </si>
+  <si>
+    <t>Charles Schwab Corporation</t>
   </si>
   <si>
     <t>GOOG</t>
@@ -369,19 +393,16 @@
     <t>Alphabet Inc. (Class C)</t>
   </si>
   <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>CF Industries</t>
-  </si>
-  <si>
-    <t>Materials</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
+    <t>CINF</t>
+  </si>
+  <si>
+    <t>Cincinnati Financial</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>Booking Holdings</t>
   </si>
   <si>
     <t>TROW</t>
@@ -390,36 +411,24 @@
     <t>T. Rowe Price</t>
   </si>
   <si>
-    <t>RDDT</t>
-  </si>
-  <si>
-    <t>Reddit</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>Booking Holdings</t>
-  </si>
-  <si>
     <t>RJF</t>
   </si>
   <si>
     <t>Raymond James Financial</t>
   </si>
   <si>
-    <t>CINF</t>
-  </si>
-  <si>
-    <t>Cincinnati Financial</t>
-  </si>
-  <si>
     <t>DVN</t>
   </si>
   <si>
     <t>Devon Energy</t>
   </si>
   <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
     <t>MO</t>
   </si>
   <si>
@@ -429,22 +438,22 @@
     <t>Consumer Staples</t>
   </si>
   <si>
-    <t>SCHW</t>
-  </si>
-  <si>
-    <t>Charles Schwab Corporation</t>
-  </si>
-  <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>Supermicro</t>
+    <t>FFIV</t>
+  </si>
+  <si>
+    <t>F5, Inc.</t>
+  </si>
+  <si>
+    <t>NUE</t>
+  </si>
+  <si>
+    <t>Nucor</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>Seagate Technology</t>
   </si>
   <si>
     <t>ZBRA</t>
@@ -453,12 +462,6 @@
     <t>Zebra Technologies</t>
   </si>
   <si>
-    <t>WAT</t>
-  </si>
-  <si>
-    <t>Waters Corporation</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -519,7 +522,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-08-25 22:49 UTC · данные на 2026-08-25 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-08-27 03:22 UTC · данные на 2026-08-26 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -600,7 +603,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-08-25 22:49 UTC</t>
+    <t>2026-08-27 03:22 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -633,7 +636,7 @@
     <t>Запросов AV использовано</t>
   </si>
   <si>
-    <t>4</t>
+    <t>2</t>
   </si>
   <si>
     <t>Источник цен</t>
@@ -646,9 +649,6 @@
   </si>
   <si>
     <t>Версия состояния</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>Регламент данных</t>
@@ -992,7 +992,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>485.2</c:v>
+                  <c:v>981.3399999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1081,29 +1081,35 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$6</c:f>
+              <c:f>Капитал!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2026-08-25</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026-08-26</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$6</c:f>
+              <c:f>Капитал!$D$5:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>10009.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10028.53</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1128,29 +1134,35 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$6</c:f>
+              <c:f>Капитал!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2026-08-25</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026-08-26</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$6</c:f>
+              <c:f>Капитал!$F$5:$F$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>10031.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10034.19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1290,29 +1302,35 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$6</c:f>
+              <c:f>Капитал!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2026-08-25</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026-08-26</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$6</c:f>
+              <c:f>Капитал!$D$5:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>10009.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10028.53</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1337,29 +1355,35 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$6</c:f>
+              <c:f>Капитал!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2026-08-25</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026-08-26</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$6</c:f>
+              <c:f>Капитал!$F$5:$F$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>10031.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10034.19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1854,37 +1878,37 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="4">
-        <v>10009.01</v>
+        <v>10028.53</v>
       </c>
       <c r="D6" s="5">
-        <v>0.0009010000000000407</v>
+        <v>0.002852999999999994</v>
       </c>
       <c r="F6" s="5">
-        <v>0.003195999999999977</v>
+        <v>0.003419000000000061</v>
       </c>
       <c r="H6" s="6">
         <v>0</v>
@@ -1892,64 +1916,64 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H9" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C13" s="10">
-        <v>9523.809999999999</v>
+        <v>9047.189999999999</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C14" s="10">
-        <v>485.2</v>
+        <v>981.3399999999999</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C15" s="10">
-        <v>10009.01</v>
+        <v>10028.53</v>
       </c>
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -1957,7 +1981,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -1965,15 +1989,15 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C18" s="11">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C19" s="11">
         <v>1</v>
@@ -1981,7 +2005,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -1989,85 +2013,85 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C26" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
-        <v>10009.01</v>
+        <v>10028.529999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33" s="10">
-        <v>485.2</v>
+        <v>981.3399999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2078,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -2098,62 +2122,62 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -2161,13 +2185,13 @@
         <v>0</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="10">
         <v>443.1115</v>
@@ -2179,58 +2203,109 @@
         <v>476.19</v>
       </c>
       <c r="H5" s="17">
-        <v>451.5</v>
+        <v>463.82</v>
       </c>
       <c r="I5" s="10">
         <f>F5*H5</f>
-        <v>485.2049265</v>
+        <v>498.44462682</v>
       </c>
       <c r="J5" s="10">
         <f>I5-G5</f>
-        <v>9.014926500000001</v>
+        <v>22.25462682</v>
       </c>
       <c r="K5" s="18">
         <f>IFERROR(J5/G5,0)</f>
-        <v>0.018931364581364584</v>
+        <v>0.04673476305676305</v>
       </c>
       <c r="L5" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N5" s="19">
         <v>2.927623067210654</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F6" s="12" t="s">
-        <v>23</v>
+      <c r="A6" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="10">
+        <v>926.2029</v>
+      </c>
+      <c r="F6" s="16">
+        <v>0.5145960000000001</v>
       </c>
       <c r="G6" s="10">
-        <f>SUM(G5:G5)</f>
-        <v>476.19</v>
+        <v>476.62</v>
+      </c>
+      <c r="H6" s="17">
+        <v>938.4</v>
       </c>
       <c r="I6" s="10">
-        <f>SUM(I5:I5)</f>
-        <v>485.2</v>
+        <f>F6*H6</f>
+        <v>482.8968864</v>
       </c>
       <c r="J6" s="10">
-        <f>SUM(J5:J5)</f>
-        <v>9.009999999999991</v>
+        <f>I6-G6</f>
+        <v>6.2768864000000235</v>
       </c>
       <c r="K6" s="18">
         <f>IFERROR(J6/G6,0)</f>
+        <v>0.013169582476606151</v>
+      </c>
+      <c r="L6" s="11">
         <v>0</v>
       </c>
+      <c r="M6" s="11">
+        <f>MAX(0,21-L6)</f>
+        <v>21</v>
+      </c>
+      <c r="N6" s="19">
+        <v>1.809956883354321</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="10">
+        <f>SUM(G5:G6)</f>
+        <v>952.81</v>
+      </c>
+      <c r="I7" s="10">
+        <f>SUM(I5:I6)</f>
+        <v>981.3399999999999</v>
+      </c>
+      <c r="J7" s="10">
+        <f>SUM(J5:J6)</f>
+        <v>28.529999999999973</v>
+      </c>
+      <c r="K7" s="18">
+        <f>IFERROR(J7/G7,0)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P5"/>
-  <conditionalFormatting sqref="K5">
+  <autoFilter ref="A4:P6"/>
+  <conditionalFormatting sqref="K5:K6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -2242,7 +2317,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5">
+  <conditionalFormatting sqref="M5:M6">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -2271,12 +2346,28 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M5</xm:sqref>
+          <xm:sqref>M5:M6</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
+          <x14:colorSeries rgb="FF0B5FFF"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'_данные'!B2:BI2</xm:f>
+              <xm:sqref>P6</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
           <x14:colorSeries rgb="FF0B5FFF"/>
           <x14:colorNegative theme="5"/>
@@ -2321,64 +2412,64 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2388,7 +2479,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2400,37 +2491,37 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B5" s="10">
         <v>10000</v>
@@ -2451,7 +2542,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="10">
         <v>9523.809999999999</v>
@@ -2468,6 +2559,27 @@
       </c>
       <c r="F6" s="10">
         <v>10031.96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="10">
+        <v>9047.190000000001</v>
+      </c>
+      <c r="C7" s="10">
+        <v>981.34</v>
+      </c>
+      <c r="D7" s="10">
+        <f>B7+C7</f>
+        <v>10028.53</v>
+      </c>
+      <c r="E7" s="11">
+        <v>2</v>
+      </c>
+      <c r="F7" s="10">
+        <v>10034.19</v>
       </c>
     </row>
   </sheetData>
@@ -2497,65 +2609,65 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2563,19 +2675,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="10">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="F5" s="16">
-        <v>1.809956883354321</v>
+        <v>1.779817379234556</v>
       </c>
       <c r="G5" s="19">
         <v>0.1411051627135557</v>
@@ -2587,7 +2699,7 @@
         <v>4.206596031118561</v>
       </c>
       <c r="J5" s="19">
-        <v>2.388861015961299</v>
+        <v>2.288396002228748</v>
       </c>
       <c r="K5" s="19">
         <v>20.560751</v>
@@ -2602,13 +2714,13 @@
         <v>3.457</v>
       </c>
       <c r="O5" s="20">
-        <v>1.233213131675055</v>
+        <v>1.188668163099826</v>
       </c>
       <c r="P5" s="11">
-        <v>50.78068810064901</v>
+        <v>51.33878640604577</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2616,19 +2728,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="10">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="F6" s="16">
-        <v>1.658898522944298</v>
+        <v>1.655247920227722</v>
       </c>
       <c r="G6" s="19">
         <v>-0.297947721659126</v>
@@ -2640,7 +2752,7 @@
         <v>4.026096567149331</v>
       </c>
       <c r="J6" s="19">
-        <v>2.248843554871623</v>
+        <v>2.236674879149703</v>
       </c>
       <c r="K6" s="19">
         <v>20.248442</v>
@@ -2655,13 +2767,13 @@
         <v>3.716</v>
       </c>
       <c r="O6" s="20">
-        <v>1.319065924696162</v>
+        <v>1.37099526161495</v>
       </c>
       <c r="P6" s="11">
-        <v>49.17336527482853</v>
+        <v>49.95678524752179</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -2669,52 +2781,52 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="E7" s="10">
-        <v>340.4100036621094</v>
+        <v>468.8800048828125</v>
       </c>
       <c r="F7" s="16">
-        <v>1.130429211953938</v>
+        <v>1.163412432007916</v>
       </c>
       <c r="G7" s="19">
-        <v>0.72925464828006</v>
+        <v>-0.6552990140462744</v>
       </c>
       <c r="H7" s="19">
-        <v>-0.3048721710887977</v>
+        <v>1.918440052485617</v>
       </c>
       <c r="I7" s="19">
-        <v>2.983550662811328</v>
+        <v>3.032907322180939</v>
       </c>
       <c r="J7" s="19">
-        <v>1.801127536068069</v>
+        <v>1.418186749244177</v>
       </c>
       <c r="K7" s="19">
-        <v>14.4347105</v>
+        <v>17.067032</v>
       </c>
       <c r="L7" s="19">
-        <v>3.9847977</v>
+        <v>0</v>
       </c>
       <c r="M7" s="20">
-        <v>0.27637</v>
+        <v>1.30853</v>
       </c>
       <c r="N7" s="20">
-        <v>0.517</v>
+        <v>0.438</v>
       </c>
       <c r="O7" s="20">
-        <v>0.7225162000965759</v>
+        <v>0.6127400529348506</v>
       </c>
       <c r="P7" s="11">
-        <v>63.05356909428822</v>
+        <v>46.62055731040271</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2728,46 +2840,46 @@
         <v>67</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E8" s="10">
-        <v>450.75</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="F8" s="16">
-        <v>1.129536240330068</v>
+        <v>1.112720607813069</v>
       </c>
       <c r="G8" s="19">
-        <v>-0.6552990140462744</v>
+        <v>0.72925464828006</v>
       </c>
       <c r="H8" s="19">
-        <v>1.918440052485617</v>
+        <v>-0.3048721710887977</v>
       </c>
       <c r="I8" s="19">
-        <v>3.032907322180939</v>
+        <v>2.983550662811328</v>
       </c>
       <c r="J8" s="19">
-        <v>1.305266110318017</v>
+        <v>1.742098855598504</v>
       </c>
       <c r="K8" s="19">
-        <v>17.067032</v>
+        <v>14.4347105</v>
       </c>
       <c r="L8" s="19">
-        <v>0</v>
+        <v>3.9847977</v>
       </c>
       <c r="M8" s="20">
-        <v>1.30853</v>
+        <v>0.27637</v>
       </c>
       <c r="N8" s="20">
-        <v>0.438</v>
+        <v>0.517</v>
       </c>
       <c r="O8" s="20">
-        <v>0.6671592836018609</v>
+        <v>0.7583396169280157</v>
       </c>
       <c r="P8" s="11">
-        <v>43.49420375949914</v>
+        <v>66.63274974855206</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2775,19 +2887,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>65</v>
-      </c>
       <c r="E9" s="10">
-        <v>354.8800048828125</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="F9" s="16">
-        <v>1.008458897306455</v>
+        <v>0.9931099257187986</v>
       </c>
       <c r="G9" s="19">
         <v>0.7230916879797831</v>
@@ -2799,7 +2911,7 @@
         <v>2.543797486452658</v>
       </c>
       <c r="J9" s="19">
-        <v>1.688113802359707</v>
+        <v>1.636950563734184</v>
       </c>
       <c r="K9" s="19">
         <v>12.56133</v>
@@ -2814,13 +2926,13 @@
         <v>0.537</v>
       </c>
       <c r="O9" s="20">
-        <v>0.829125157126803</v>
+        <v>0.8626363944617035</v>
       </c>
       <c r="P9" s="11">
-        <v>66.00522059337668</v>
+        <v>69.03712736213646</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2828,19 +2940,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E10" s="10">
-        <v>58.40999984741211</v>
+        <v>58.61999893188477</v>
       </c>
       <c r="F10" s="16">
-        <v>0.9262865832288399</v>
+        <v>0.91902097781982</v>
       </c>
       <c r="G10" s="19">
         <v>0.6355114639003794</v>
@@ -2852,7 +2964,7 @@
         <v>3.304463564487919</v>
       </c>
       <c r="J10" s="19">
-        <v>0.279934189714778</v>
+        <v>0.2557155050180444</v>
       </c>
       <c r="K10" s="19">
         <v>18.105423</v>
@@ -2867,13 +2979,13 @@
         <v>0.534</v>
       </c>
       <c r="O10" s="20">
-        <v>0.1349067886734578</v>
+        <v>0.1615700781705602</v>
       </c>
       <c r="P10" s="11">
-        <v>53.00057263604817</v>
+        <v>53.76222199234199</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2881,19 +2993,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="10">
-        <v>53.43999862670898</v>
+        <v>55.22999954223633</v>
       </c>
       <c r="F11" s="16">
-        <v>0.8861173700944488</v>
+        <v>0.8540202321228957</v>
       </c>
       <c r="G11" s="19">
         <v>0.304959259686968</v>
@@ -2905,7 +3017,7 @@
         <v>1.463737124114395</v>
       </c>
       <c r="J11" s="19">
-        <v>2.420727913022236</v>
+        <v>2.313737453117059</v>
       </c>
       <c r="K11" s="19">
         <v>48.999996</v>
@@ -2920,13 +3032,13 @@
         <v>0.4</v>
       </c>
       <c r="O11" s="20">
-        <v>1.663799782449941</v>
+        <v>1.702314936005745</v>
       </c>
       <c r="P11" s="11">
-        <v>53.59705945698387</v>
+        <v>57.87335440339404</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -2937,16 +3049,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="10">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="F12" s="16">
-        <v>0.8204379203607901</v>
+        <v>0.7795572599435281</v>
       </c>
       <c r="G12" s="19">
         <v>-1.276312485328304</v>
@@ -2958,7 +3070,7 @@
         <v>3.12929742928239</v>
       </c>
       <c r="J12" s="19">
-        <v>2.891689957297495</v>
+        <v>2.755421089239955</v>
       </c>
       <c r="K12" s="19">
         <v>884.0612</v>
@@ -2973,13 +3085,13 @@
         <v>0.875</v>
       </c>
       <c r="O12" s="20">
-        <v>2.787321986323046</v>
+        <v>2.774084413624862</v>
       </c>
       <c r="P12" s="11">
-        <v>52.43236515943332</v>
+        <v>55.13348909271769</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -2987,19 +3099,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="10">
-        <v>187.4299926757812</v>
+        <v>193.8500061035156</v>
       </c>
       <c r="F13" s="16">
-        <v>0.76891160352956</v>
+        <v>0.730591145490776</v>
       </c>
       <c r="G13" s="19">
         <v>-0.4056392750220561</v>
@@ -3011,7 +3123,7 @@
         <v>-0.1487202202604564</v>
       </c>
       <c r="J13" s="19">
-        <v>1.98307369906076</v>
+        <v>1.85533883893148</v>
       </c>
       <c r="K13" s="19">
         <v>30.285252</v>
@@ -3026,13 +3138,13 @@
         <v>0.125</v>
       </c>
       <c r="O13" s="20">
-        <v>0.8920817885495846</v>
+        <v>0.9182833866955131</v>
       </c>
       <c r="P13" s="11">
-        <v>50.92537543410591</v>
+        <v>57.14935787629297</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -3040,19 +3152,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E14" s="10">
-        <v>337.9700012207031</v>
+        <v>333.4400024414062</v>
       </c>
       <c r="F14" s="16">
-        <v>0.715275223135537</v>
+        <v>0.7264639818494252</v>
       </c>
       <c r="G14" s="19">
         <v>-0.1074817459894137</v>
@@ -3064,7 +3176,7 @@
         <v>0.6713684345102916</v>
       </c>
       <c r="J14" s="19">
-        <v>1.121181841736128</v>
+        <v>1.158477704115756</v>
       </c>
       <c r="K14" s="19">
         <v>20.24627</v>
@@ -3079,13 +3191,13 @@
         <v>0.14</v>
       </c>
       <c r="O14" s="20">
-        <v>0.7132158909244706</v>
+        <v>0.6436285292134618</v>
       </c>
       <c r="P14" s="11">
-        <v>68.29007185783232</v>
+        <v>64.66898025571628</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -3093,19 +3205,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E15" s="10">
-        <v>146.8300018310547</v>
+        <v>144.8399963378906</v>
       </c>
       <c r="F15" s="16">
-        <v>0.6828121821255917</v>
+        <v>0.6988290824930529</v>
       </c>
       <c r="G15" s="19">
         <v>0.6102249595302855</v>
@@ -3117,7 +3229,7 @@
         <v>1.562733350737734</v>
       </c>
       <c r="J15" s="19">
-        <v>0.4081881258979367</v>
+        <v>0.4615777937894738</v>
       </c>
       <c r="K15" s="19">
         <v>11.680406</v>
@@ -3132,13 +3244,13 @@
         <v>0.587</v>
       </c>
       <c r="O15" s="20">
-        <v>0.2050783188428775</v>
+        <v>0.2003906105262252</v>
       </c>
       <c r="P15" s="11">
-        <v>54.32109127269014</v>
+        <v>51.15227743096032</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -3146,52 +3258,52 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E16" s="10">
-        <v>366.4299926757812</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="F16" s="16">
-        <v>0.6797400188617937</v>
+        <v>0.6896542101523245</v>
       </c>
       <c r="G16" s="19">
-        <v>-1.08262537420069</v>
+        <v>0.9986491788407921</v>
       </c>
       <c r="H16" s="19">
-        <v>0.6932659455068273</v>
+        <v>0.6094621501467751</v>
       </c>
       <c r="I16" s="19">
-        <v>3.615274867663105</v>
+        <v>-0.228424555888388</v>
       </c>
       <c r="J16" s="19">
-        <v>0.9630663819860936</v>
+        <v>0.9065253411555046</v>
       </c>
       <c r="K16" s="19">
-        <v>51.539547</v>
+        <v>9.159914000000001</v>
       </c>
       <c r="L16" s="19">
-        <v>18.169596</v>
+        <v>2.14564</v>
       </c>
       <c r="M16" s="20">
-        <v>0.36465</v>
+        <v>0.26659</v>
       </c>
       <c r="N16" s="20">
-        <v>1.039</v>
+        <v>0.092</v>
       </c>
       <c r="O16" s="20">
-        <v>0.113884902430992</v>
+        <v>0.4999119656741835</v>
       </c>
       <c r="P16" s="11">
-        <v>46.26722336147129</v>
+        <v>57.51035836662003</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -3199,52 +3311,52 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E17" s="10">
-        <v>41.34999847412109</v>
+        <v>261.8099975585938</v>
       </c>
       <c r="F17" s="16">
-        <v>0.6787269380675097</v>
+        <v>0.6786587241238107</v>
       </c>
       <c r="G17" s="19">
-        <v>0.9986491788407921</v>
+        <v>1.158776322034968</v>
       </c>
       <c r="H17" s="19">
-        <v>0.6094621501467751</v>
+        <v>0.3596891130938242</v>
       </c>
       <c r="I17" s="19">
-        <v>-0.228424555888388</v>
+        <v>0.009309850889890559</v>
       </c>
       <c r="J17" s="19">
-        <v>0.8701011008727886</v>
+        <v>0.7990235720212685</v>
       </c>
       <c r="K17" s="19">
-        <v>9.159914000000001</v>
+        <v>5.083822</v>
       </c>
       <c r="L17" s="19">
-        <v>2.14564</v>
+        <v>2.0850062</v>
       </c>
       <c r="M17" s="20">
-        <v>0.26659</v>
+        <v>0.46113998</v>
       </c>
       <c r="N17" s="20">
-        <v>0.092</v>
+        <v>0.118</v>
       </c>
       <c r="O17" s="20">
-        <v>0.4647013278671024</v>
+        <v>0.2636553073069234</v>
       </c>
       <c r="P17" s="11">
-        <v>58.27812268635797</v>
+        <v>53.77724286495333</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -3252,52 +3364,52 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="E18" s="10">
-        <v>257.6199951171875</v>
+        <v>363.1000061035156</v>
       </c>
       <c r="F18" s="16">
-        <v>0.6744109008100192</v>
+        <v>0.6463211235407152</v>
       </c>
       <c r="G18" s="19">
-        <v>1.158776322034968</v>
+        <v>-1.08262537420069</v>
       </c>
       <c r="H18" s="19">
-        <v>0.3596891130938242</v>
+        <v>0.6932659455068273</v>
       </c>
       <c r="I18" s="19">
-        <v>0.009309850889890559</v>
+        <v>3.615274867663105</v>
       </c>
       <c r="J18" s="19">
-        <v>0.7848641609752969</v>
+        <v>0.8516700642491655</v>
       </c>
       <c r="K18" s="19">
-        <v>5.083822</v>
+        <v>51.539547</v>
       </c>
       <c r="L18" s="19">
-        <v>2.0850062</v>
+        <v>18.169596</v>
       </c>
       <c r="M18" s="20">
-        <v>0.46113998</v>
+        <v>0.36465</v>
       </c>
       <c r="N18" s="20">
-        <v>0.118</v>
+        <v>1.039</v>
       </c>
       <c r="O18" s="20">
-        <v>0.2405278269640074</v>
+        <v>0.05955641877465934</v>
       </c>
       <c r="P18" s="11">
-        <v>49.95465390985286</v>
+        <v>45.48261500820713</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -3305,52 +3417,52 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E19" s="10">
-        <v>389.7099914550781</v>
+        <v>128.1199951171875</v>
       </c>
       <c r="F19" s="16">
-        <v>0.6351126751106471</v>
+        <v>0.6258810179742954</v>
       </c>
       <c r="G19" s="19">
-        <v>0.4746478020487309</v>
+        <v>0.3568150294101221</v>
       </c>
       <c r="H19" s="19">
-        <v>-0.2835410288834002</v>
+        <v>0.8874455070737253</v>
       </c>
       <c r="I19" s="19">
-        <v>0.2562199099090978</v>
+        <v>0.6313896241094424</v>
       </c>
       <c r="J19" s="19">
-        <v>1.750568684101711</v>
+        <v>0.6742222958880369</v>
       </c>
       <c r="K19" s="19">
-        <v>35.8304</v>
+        <v>16.303185</v>
       </c>
       <c r="L19" s="19">
-        <v>2.4162972</v>
+        <v>4.0541053</v>
       </c>
       <c r="M19" s="20">
-        <v>0.06893000000000001</v>
+        <v>0.30667</v>
       </c>
       <c r="N19" s="20">
-        <v>0.262</v>
+        <v>0.377</v>
       </c>
       <c r="O19" s="20">
-        <v>1.24812962729863</v>
+        <v>0.2814561993941203</v>
       </c>
       <c r="P19" s="11">
-        <v>55.47224371317206</v>
+        <v>63.50649061776875</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -3358,52 +3470,52 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>65</v>
-      </c>
       <c r="E20" s="10">
-        <v>236.8999938964844</v>
+        <v>391.0599975585938</v>
       </c>
       <c r="F20" s="16">
-        <v>0.6115370746568929</v>
+        <v>0.6155234899676881</v>
       </c>
       <c r="G20" s="19">
-        <v>0.06892234601185927</v>
+        <v>0.4746478020487309</v>
       </c>
       <c r="H20" s="19">
-        <v>-0.54467699511111</v>
+        <v>-0.2835410288834002</v>
       </c>
       <c r="I20" s="19">
-        <v>2.512241193631993</v>
+        <v>0.2562199099090978</v>
       </c>
       <c r="J20" s="19">
-        <v>1.167311468621045</v>
+        <v>1.685271400291847</v>
       </c>
       <c r="K20" s="19">
-        <v>110.99082</v>
+        <v>35.8304</v>
       </c>
       <c r="L20" s="19">
-        <v>3.064414</v>
+        <v>2.4162972</v>
       </c>
       <c r="M20" s="20">
-        <v>0.23452999</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="N20" s="20">
-        <v>0.531</v>
+        <v>0.262</v>
       </c>
       <c r="O20" s="20">
-        <v>0.5540709449331289</v>
+        <v>1.237722478842338</v>
       </c>
       <c r="P20" s="11">
-        <v>67.96142812231727</v>
+        <v>56.21888511116801</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -3411,19 +3523,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" s="10">
-        <v>1058.880004882812</v>
+        <v>1040.4599609375</v>
       </c>
       <c r="F21" s="16">
-        <v>0.6020778892080503</v>
+        <v>0.60775005215091</v>
       </c>
       <c r="G21" s="19">
         <v>0.3556011439311419</v>
@@ -3435,7 +3547,7 @@
         <v>1.024034813371229</v>
       </c>
       <c r="J21" s="19">
-        <v>0.4344344166516113</v>
+        <v>0.4533416264611437</v>
       </c>
       <c r="K21" s="19">
         <v>16.004324</v>
@@ -3450,13 +3562,13 @@
         <v>0.425</v>
       </c>
       <c r="O21" s="20">
-        <v>0.1849489060627247</v>
+        <v>0.1401867758662851</v>
       </c>
       <c r="P21" s="11">
-        <v>54.17918145182254</v>
+        <v>49.88144521980084</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -3464,52 +3576,52 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E22" s="10">
-        <v>213.0500030517578</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="F22" s="16">
-        <v>0.5951011955216278</v>
+        <v>0.6004023149653797</v>
       </c>
       <c r="G22" s="19">
-        <v>-1.338461785426528</v>
+        <v>0.06892234601185927</v>
       </c>
       <c r="H22" s="19">
-        <v>2.078256102926562</v>
+        <v>-0.54467699511111</v>
       </c>
       <c r="I22" s="19">
-        <v>2.806787311422478</v>
+        <v>2.512241193631993</v>
       </c>
       <c r="J22" s="19">
-        <v>0.1868586956819133</v>
+        <v>1.130195602982668</v>
       </c>
       <c r="K22" s="19">
-        <v>32.883278</v>
+        <v>110.99082</v>
       </c>
       <c r="L22" s="19">
-        <v>25.833954</v>
+        <v>3.064414</v>
       </c>
       <c r="M22" s="20">
-        <v>1.14288</v>
+        <v>0.23452999</v>
       </c>
       <c r="N22" s="20">
-        <v>0.852</v>
+        <v>0.531</v>
       </c>
       <c r="O22" s="20">
-        <v>0.1060920104233294</v>
+        <v>0.6146637868472538</v>
       </c>
       <c r="P22" s="11">
-        <v>49.6092897474399</v>
+        <v>71.34710082865476</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -3517,19 +3629,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E23" s="10">
-        <v>199.8899993896484</v>
+        <v>199.8399963378906</v>
       </c>
       <c r="F23" s="16">
-        <v>0.5922233698450092</v>
+        <v>0.5936667758865617</v>
       </c>
       <c r="G23" s="19">
         <v>0.561347890123932</v>
@@ -3541,7 +3653,7 @@
         <v>1.717140484071832</v>
       </c>
       <c r="J23" s="19">
-        <v>0.4732527330377264</v>
+        <v>0.4780640865095683</v>
       </c>
       <c r="K23" s="19">
         <v>40.156254</v>
@@ -3556,13 +3668,13 @@
         <v>0.525</v>
       </c>
       <c r="O23" s="20">
-        <v>0.1784389954547307</v>
+        <v>0.2115004868031256</v>
       </c>
       <c r="P23" s="11">
-        <v>50.42557745600141</v>
+        <v>50.3702857479487</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -3570,19 +3682,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E24" s="10">
-        <v>65</v>
+        <v>65.47000122070312</v>
       </c>
       <c r="F24" s="16">
-        <v>0.5907221505626017</v>
+        <v>0.5835454398311176</v>
       </c>
       <c r="G24" s="19">
         <v>1.175622071073703</v>
@@ -3594,7 +3706,7 @@
         <v>-0.5389901628995794</v>
       </c>
       <c r="J24" s="19">
-        <v>1.506897088301099</v>
+        <v>1.482974719196152</v>
       </c>
       <c r="K24" s="19">
         <v>12.357601</v>
@@ -3609,13 +3721,13 @@
         <v>0.046</v>
       </c>
       <c r="O24" s="20">
-        <v>0.5341043577672937</v>
+        <v>0.5336145075381156</v>
       </c>
       <c r="P24" s="11">
-        <v>50.06441216106845</v>
+        <v>51.47817097291836</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -3623,52 +3735,52 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="E25" s="10">
-        <v>129.7200012207031</v>
+        <v>157.5399932861328</v>
       </c>
       <c r="F25" s="16">
-        <v>0.5869418715181554</v>
+        <v>0.5590552986099251</v>
       </c>
       <c r="G25" s="19">
-        <v>0.3568150294101221</v>
+        <v>-1.877249539822365</v>
       </c>
       <c r="H25" s="19">
-        <v>0.8874455070737253</v>
+        <v>1.758964460615154</v>
       </c>
       <c r="I25" s="19">
-        <v>0.6313896241094424</v>
+        <v>0.3182836657213104</v>
       </c>
       <c r="J25" s="19">
-        <v>0.5444251410342369</v>
+        <v>2.115821651815498</v>
       </c>
       <c r="K25" s="19">
-        <v>16.303185</v>
+        <v>54.282146</v>
       </c>
       <c r="L25" s="19">
-        <v>4.0541053</v>
+        <v>71.89688</v>
       </c>
       <c r="M25" s="20">
-        <v>0.30667</v>
+        <v>1.17442</v>
       </c>
       <c r="N25" s="20">
-        <v>0.377</v>
+        <v>0.256</v>
       </c>
       <c r="O25" s="20">
-        <v>0.2837209035437687</v>
+        <v>1.036716178331158</v>
       </c>
       <c r="P25" s="11">
-        <v>68.25626598140605</v>
+        <v>51.2331295475656</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -3676,52 +3788,52 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E26" s="10">
-        <v>199.8899993896484</v>
+        <v>214.0800018310547</v>
       </c>
       <c r="F26" s="16">
-        <v>0.5642709524720174</v>
+        <v>0.5548357065874343</v>
       </c>
       <c r="G26" s="19">
-        <v>0.5728138826097362</v>
+        <v>0.3452907642059501</v>
       </c>
       <c r="H26" s="19">
-        <v>-0.06908867602196844</v>
+        <v>0.8001987998031764</v>
       </c>
       <c r="I26" s="19">
-        <v>2.415351960752095</v>
+        <v>0.4732064398512328</v>
       </c>
       <c r="J26" s="19">
-        <v>0.1579872086059146</v>
+        <v>0.6007260379905678</v>
       </c>
       <c r="K26" s="19">
-        <v>19.755836</v>
+        <v>17.306387</v>
       </c>
       <c r="L26" s="19">
-        <v>2.098037</v>
+        <v>3.1574755</v>
       </c>
       <c r="M26" s="20">
-        <v>0.12231</v>
+        <v>0.17969999</v>
       </c>
       <c r="N26" s="20">
-        <v>0.535</v>
+        <v>0.28</v>
       </c>
       <c r="O26" s="20">
-        <v>0.09788111313823489</v>
+        <v>0.2456989263064639</v>
       </c>
       <c r="P26" s="11">
-        <v>58.91739530015754</v>
+        <v>49.18336325627639</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -3729,52 +3841,52 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="E27" s="10">
-        <v>216.7700042724609</v>
+        <v>200.2100067138672</v>
       </c>
       <c r="F27" s="16">
-        <v>0.5637359580004875</v>
+        <v>0.5544687926280044</v>
       </c>
       <c r="G27" s="19">
-        <v>0.3452907642059501</v>
+        <v>0.5728138826097362</v>
       </c>
       <c r="H27" s="19">
-        <v>0.8001987998031764</v>
+        <v>-0.06908867602196844</v>
       </c>
       <c r="I27" s="19">
-        <v>0.4732064398512328</v>
+        <v>2.415351960752095</v>
       </c>
       <c r="J27" s="19">
-        <v>0.6303935427007451</v>
+        <v>0.1253133424592044</v>
       </c>
       <c r="K27" s="19">
-        <v>17.306387</v>
+        <v>19.755836</v>
       </c>
       <c r="L27" s="19">
-        <v>3.1574755</v>
+        <v>2.098037</v>
       </c>
       <c r="M27" s="20">
-        <v>0.17969999</v>
+        <v>0.12231</v>
       </c>
       <c r="N27" s="20">
-        <v>0.28</v>
+        <v>0.535</v>
       </c>
       <c r="O27" s="20">
-        <v>0.2982677473624069</v>
+        <v>0.1063242023878324</v>
       </c>
       <c r="P27" s="11">
-        <v>52.74212183763184</v>
+        <v>59.34798776027157</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -3782,52 +3894,52 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="E28" s="10">
-        <v>346.9599914550781</v>
+        <v>371.1499938964844</v>
       </c>
       <c r="F28" s="16">
-        <v>0.5463950366355268</v>
+        <v>0.5399391269044111</v>
       </c>
       <c r="G28" s="19">
-        <v>-0.3026541063380147</v>
+        <v>1.091200655903261</v>
       </c>
       <c r="H28" s="19">
-        <v>1.453871687245511</v>
+        <v>0.1101459112354547</v>
       </c>
       <c r="I28" s="19">
-        <v>1.455283430456029</v>
+        <v>-0.3352804504404189</v>
       </c>
       <c r="J28" s="19">
-        <v>0.1847694405238303</v>
+        <v>0.7844483996354403</v>
       </c>
       <c r="K28" s="19">
-        <v>17.464125</v>
+        <v>9.963699999999999</v>
       </c>
       <c r="L28" s="19">
-        <v>6.838651</v>
+        <v>2.3337615</v>
       </c>
       <c r="M28" s="20">
-        <v>0.48676</v>
+        <v>0.26511</v>
       </c>
       <c r="N28" s="20">
-        <v>0.242</v>
+        <v>0.003</v>
       </c>
       <c r="O28" s="20">
-        <v>0.1174384195201885</v>
+        <v>0.2273877728518141</v>
       </c>
       <c r="P28" s="11">
-        <v>48.73101448655449</v>
+        <v>54.50810671530476</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -3841,46 +3953,46 @@
         <v>111</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="E29" s="10">
-        <v>369.6600036621094</v>
+        <v>209.6600036621094</v>
       </c>
       <c r="F29" s="16">
-        <v>0.5369847906027814</v>
+        <v>0.5362579450829138</v>
       </c>
       <c r="G29" s="19">
-        <v>1.091200655903261</v>
+        <v>-1.338461785426528</v>
       </c>
       <c r="H29" s="19">
-        <v>0.1101459112354547</v>
+        <v>2.078256102926562</v>
       </c>
       <c r="I29" s="19">
-        <v>-0.3352804504404189</v>
+        <v>2.806787311422478</v>
       </c>
       <c r="J29" s="19">
-        <v>0.7746006119633412</v>
+        <v>-0.009285472447133136</v>
       </c>
       <c r="K29" s="19">
-        <v>9.963699999999999</v>
+        <v>32.883278</v>
       </c>
       <c r="L29" s="19">
-        <v>2.3337615</v>
+        <v>25.833954</v>
       </c>
       <c r="M29" s="20">
-        <v>0.26511</v>
+        <v>1.14288</v>
       </c>
       <c r="N29" s="20">
-        <v>0.003</v>
+        <v>0.852</v>
       </c>
       <c r="O29" s="20">
-        <v>0.2197789981031173</v>
+        <v>0.07340831571502826</v>
       </c>
       <c r="P29" s="11">
-        <v>53.19665050439053</v>
+        <v>46.29839347105207</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -3894,46 +4006,46 @@
         <v>113</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E30" s="10">
-        <v>343.3399963378906</v>
+        <v>125.6999969482422</v>
       </c>
       <c r="F30" s="16">
-        <v>0.5297181734312539</v>
+        <v>0.5131019267794631</v>
       </c>
       <c r="G30" s="19">
-        <v>-0.2917499460294181</v>
+        <v>0.6458174147154766</v>
       </c>
       <c r="H30" s="19">
-        <v>1.453871687245511</v>
+        <v>0.432781060607519</v>
       </c>
       <c r="I30" s="19">
-        <v>1.455283430456029</v>
+        <v>0.3540288428030787</v>
       </c>
       <c r="J30" s="19">
-        <v>0.1182757362009909</v>
+        <v>0.5268570359749285</v>
       </c>
       <c r="K30" s="19">
-        <v>17.298695</v>
+        <v>9.616072000000001</v>
       </c>
       <c r="L30" s="19">
-        <v>6.770473</v>
+        <v>3.4084976</v>
       </c>
       <c r="M30" s="20">
-        <v>0.48676</v>
+        <v>0.29867</v>
       </c>
       <c r="N30" s="20">
-        <v>0.242</v>
+        <v>0.176</v>
       </c>
       <c r="O30" s="20">
-        <v>0.1057141321154904</v>
+        <v>0.3195702217273626</v>
       </c>
       <c r="P30" s="11">
-        <v>47.33975978251333</v>
+        <v>57.28106845062105</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -3941,52 +4053,52 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E31" s="10">
-        <v>127.2600021362305</v>
+        <v>342</v>
       </c>
       <c r="F31" s="16">
-        <v>0.4936836947371027</v>
+        <v>0.4926260373746073</v>
       </c>
       <c r="G31" s="19">
-        <v>0.6458174147154766</v>
+        <v>-0.3026541063380147</v>
       </c>
       <c r="H31" s="19">
-        <v>0.432781060607519</v>
+        <v>1.453871687245511</v>
       </c>
       <c r="I31" s="19">
-        <v>0.3540288428030787</v>
+        <v>1.455283430456029</v>
       </c>
       <c r="J31" s="19">
-        <v>0.4621295958337271</v>
+        <v>0.005539442987432119</v>
       </c>
       <c r="K31" s="19">
-        <v>9.616072000000001</v>
+        <v>17.464125</v>
       </c>
       <c r="L31" s="19">
-        <v>3.4084976</v>
+        <v>6.838651</v>
       </c>
       <c r="M31" s="20">
-        <v>0.29867</v>
+        <v>0.48676</v>
       </c>
       <c r="N31" s="20">
-        <v>0.176</v>
+        <v>0.242</v>
       </c>
       <c r="O31" s="20">
-        <v>0.3363639065753112</v>
+        <v>0.094423619884765</v>
       </c>
       <c r="P31" s="11">
-        <v>60.06848028604878</v>
+        <v>45.18771599619804</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -3994,52 +4106,52 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="E32" s="10">
-        <v>153.6600036621094</v>
+        <v>109.3899993896484</v>
       </c>
       <c r="F32" s="16">
-        <v>0.479476579540434</v>
+        <v>0.4833902032451637</v>
       </c>
       <c r="G32" s="19">
-        <v>-1.877249539822365</v>
+        <v>0.02982011516877862</v>
       </c>
       <c r="H32" s="19">
-        <v>1.758964460615154</v>
+        <v>1.249493192438245</v>
       </c>
       <c r="I32" s="19">
-        <v>0.3182836657213104</v>
+        <v>0.1792183728511779</v>
       </c>
       <c r="J32" s="19">
-        <v>1.850559254917194</v>
+        <v>0.4506270488576405</v>
       </c>
       <c r="K32" s="19">
-        <v>54.282146</v>
+        <v>20.440647</v>
       </c>
       <c r="L32" s="19">
-        <v>71.89688</v>
+        <v>4.4703617</v>
       </c>
       <c r="M32" s="20">
-        <v>1.17442</v>
+        <v>0.20273</v>
       </c>
       <c r="N32" s="20">
-        <v>0.256</v>
+        <v>0.209</v>
       </c>
       <c r="O32" s="20">
-        <v>1.042536179787998</v>
+        <v>0.1547209781439263</v>
       </c>
       <c r="P32" s="11">
-        <v>46.38067291804938</v>
+        <v>55.98972868390818</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -4047,52 +4159,52 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="E33" s="10">
-        <v>112.870002746582</v>
+        <v>339.1000061035156</v>
       </c>
       <c r="F33" s="16">
-        <v>0.469396824720007</v>
+        <v>0.4798778592399495</v>
       </c>
       <c r="G33" s="19">
-        <v>0.6818833135656812</v>
+        <v>-0.2917499460294181</v>
       </c>
       <c r="H33" s="19">
-        <v>0.6287894397638343</v>
+        <v>1.453871687245511</v>
       </c>
       <c r="I33" s="19">
-        <v>-0.1751734853969869</v>
+        <v>1.455283430456029</v>
       </c>
       <c r="J33" s="19">
-        <v>0.4463683117296403</v>
+        <v>-0.04785864443669054</v>
       </c>
       <c r="K33" s="19">
-        <v>11.196411</v>
+        <v>17.298695</v>
       </c>
       <c r="L33" s="19">
-        <v>2.1772428</v>
+        <v>6.770473</v>
       </c>
       <c r="M33" s="20">
-        <v>0.19399999</v>
+        <v>0.48676</v>
       </c>
       <c r="N33" s="20">
-        <v>0.107</v>
+        <v>0.242</v>
       </c>
       <c r="O33" s="20">
-        <v>0.2228426400134897</v>
+        <v>0.08469842775952308</v>
       </c>
       <c r="P33" s="11">
-        <v>49.07170722100347</v>
+        <v>44.17840072111089</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -4100,52 +4212,52 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="E34" s="10">
-        <v>162.4499969482422</v>
+        <v>172.3800048828125</v>
       </c>
       <c r="F34" s="16">
-        <v>0.4654127043023902</v>
+        <v>0.4588679794930431</v>
       </c>
       <c r="G34" s="19">
-        <v>-0.5758934002812983</v>
+        <v>0.9039922035122165</v>
       </c>
       <c r="H34" s="19">
-        <v>1.369553352432538</v>
+        <v>0.2335474389445495</v>
       </c>
       <c r="I34" s="19">
-        <v>1.952411925208389</v>
+        <v>0.6837145595313986</v>
       </c>
       <c r="J34" s="19">
-        <v>0.009768658324623303</v>
+        <v>0.08908758257843671</v>
       </c>
       <c r="K34" s="19">
-        <v>35.594406</v>
+        <v>7.9410954</v>
       </c>
       <c r="L34" s="19">
-        <v>8.938188</v>
+        <v>1.5754024</v>
       </c>
       <c r="M34" s="20">
-        <v>0.30712</v>
+        <v>0.21484</v>
       </c>
       <c r="N34" s="20">
-        <v>0.611</v>
+        <v>0.316</v>
       </c>
       <c r="O34" s="20">
-        <v>0.1433698962181122</v>
+        <v>0.06471934417540237</v>
       </c>
       <c r="P34" s="11">
-        <v>49.57575928897391</v>
+        <v>46.20082696898552</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -4153,19 +4265,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E35" s="10">
-        <v>213.7799987792969</v>
+        <v>208.8899993896484</v>
       </c>
       <c r="F35" s="16">
-        <v>0.446466482716136</v>
+        <v>0.4580532307800073</v>
       </c>
       <c r="G35" s="19">
         <v>0.1534000000694478</v>
@@ -4177,7 +4289,7 @@
         <v>0.2283188730840903</v>
       </c>
       <c r="J35" s="19">
-        <v>0.2765753292755094</v>
+        <v>0.315197822821747</v>
       </c>
       <c r="K35" s="19">
         <v>23.318033</v>
@@ -4192,13 +4304,13 @@
         <v>0.081</v>
       </c>
       <c r="O35" s="20">
-        <v>0.3199161865620579</v>
+        <v>0.2604664322848762</v>
       </c>
       <c r="P35" s="11">
-        <v>64.26839155120049</v>
+        <v>57.38759816451733</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -4206,52 +4318,52 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E36" s="10">
-        <v>174.7100067138672</v>
+        <v>112.5500030517578</v>
       </c>
       <c r="F36" s="16">
-        <v>0.4322510603569443</v>
+        <v>0.4514477445269051</v>
       </c>
       <c r="G36" s="19">
-        <v>0.5368950783305056</v>
+        <v>0.6818833135656812</v>
       </c>
       <c r="H36" s="19">
-        <v>0.5945270320387294</v>
+        <v>0.6287894397638343</v>
       </c>
       <c r="I36" s="19">
-        <v>0.0123304280898874</v>
+        <v>-0.1751734853969869</v>
       </c>
       <c r="J36" s="19">
-        <v>0.4023373821154242</v>
+        <v>0.3865380444193006</v>
       </c>
       <c r="K36" s="19">
-        <v>15.270527</v>
+        <v>11.196411</v>
       </c>
       <c r="L36" s="19">
-        <v>2.6730006</v>
+        <v>2.1772428</v>
       </c>
       <c r="M36" s="20">
-        <v>0.18416001</v>
+        <v>0.19399999</v>
       </c>
       <c r="N36" s="20">
-        <v>0.151</v>
+        <v>0.107</v>
       </c>
       <c r="O36" s="20">
-        <v>0.1319085595271483</v>
+        <v>0.213360246531962</v>
       </c>
       <c r="P36" s="11">
-        <v>50.09074654604255</v>
+        <v>48.02508926581249</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -4259,52 +4371,52 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37" s="10">
-        <v>171.4199981689453</v>
+        <v>176.6900024414062</v>
       </c>
       <c r="F37" s="16">
-        <v>0.4306319469932199</v>
+        <v>0.4223171498658832</v>
       </c>
       <c r="G37" s="19">
-        <v>0.9039922035122165</v>
+        <v>0.5368950783305056</v>
       </c>
       <c r="H37" s="19">
-        <v>0.2335474389445495</v>
+        <v>0.5945270320387294</v>
       </c>
       <c r="I37" s="19">
-        <v>0.6837145595313986</v>
+        <v>0.0123304280898874</v>
       </c>
       <c r="J37" s="19">
-        <v>-0.005032525754307548</v>
+        <v>0.3692243471452203</v>
       </c>
       <c r="K37" s="19">
-        <v>7.9410954</v>
+        <v>15.270527</v>
       </c>
       <c r="L37" s="19">
-        <v>1.5754024</v>
+        <v>2.6730006</v>
       </c>
       <c r="M37" s="20">
-        <v>0.21484</v>
+        <v>0.18416001</v>
       </c>
       <c r="N37" s="20">
-        <v>0.316</v>
+        <v>0.151</v>
       </c>
       <c r="O37" s="20">
-        <v>0.0786836852825421</v>
+        <v>0.1240599106134253</v>
       </c>
       <c r="P37" s="11">
-        <v>43.75440853527889</v>
+        <v>53.94136323074993</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -4312,19 +4424,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E38" s="10">
-        <v>46.90999984741211</v>
+        <v>46.83000183105469</v>
       </c>
       <c r="F38" s="16">
-        <v>0.4214809690581295</v>
+        <v>0.4215670414517939</v>
       </c>
       <c r="G38" s="19">
         <v>0.4704959025733791</v>
@@ -4336,7 +4448,7 @@
         <v>1.41063650916965</v>
       </c>
       <c r="J38" s="19">
-        <v>0.1704044691094643</v>
+        <v>0.1706913770883454</v>
       </c>
       <c r="K38" s="19">
         <v>10.484783</v>
@@ -4351,13 +4463,13 @@
         <v>0.642</v>
       </c>
       <c r="O38" s="20">
-        <v>0.09728310964733433</v>
+        <v>0.1123751124611942</v>
       </c>
       <c r="P38" s="11">
-        <v>55.41943106438682</v>
+        <v>55.01372953852868</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -4365,52 +4477,52 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="E39" s="10">
-        <v>68.06999969482422</v>
+        <v>67.56999969482422</v>
       </c>
       <c r="F39" s="16">
-        <v>0.4082626384251519</v>
+        <v>0.4045030192457723</v>
       </c>
       <c r="G39" s="19">
-        <v>0.5078777743715293</v>
+        <v>0.4782631507053702</v>
       </c>
       <c r="H39" s="19">
-        <v>1.335916108729087</v>
+        <v>0.5511183194325295</v>
       </c>
       <c r="I39" s="19">
-        <v>-0.5911526511284643</v>
+        <v>0.2691043413223938</v>
       </c>
       <c r="J39" s="19">
-        <v>0.0353105886689701</v>
+        <v>0.2762628099255658</v>
       </c>
       <c r="K39" s="19">
-        <v>13.916667</v>
+        <v>14.819383</v>
       </c>
       <c r="L39" s="19">
-        <v>-42.84731</v>
+        <v>6.1583524</v>
       </c>
       <c r="M39" s="20">
-        <v>0</v>
+        <v>0.46598998</v>
       </c>
       <c r="N39" s="20">
-        <v>0.012</v>
+        <v>0.057</v>
       </c>
       <c r="O39" s="20">
-        <v>0.01437727940312072</v>
+        <v>0.1262206503785697</v>
       </c>
       <c r="P39" s="11">
-        <v>50.16306347391859</v>
+        <v>63.49985153390229</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -4424,46 +4536,46 @@
         <v>135</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="E40" s="10">
-        <v>112.2699966430664</v>
+        <v>69.12000274658203</v>
       </c>
       <c r="F40" s="16">
-        <v>0.401508448608237</v>
+        <v>0.3893525364836609</v>
       </c>
       <c r="G40" s="19">
-        <v>0.02982011516877862</v>
+        <v>0.5078777743715293</v>
       </c>
       <c r="H40" s="19">
-        <v>1.249493192438245</v>
+        <v>1.335916108729087</v>
       </c>
       <c r="I40" s="19">
-        <v>0.1792183728511779</v>
+        <v>-0.5911526511284643</v>
       </c>
       <c r="J40" s="19">
-        <v>0.1776878667345517</v>
+        <v>-0.02772308446933316</v>
       </c>
       <c r="K40" s="19">
-        <v>20.440647</v>
+        <v>13.916667</v>
       </c>
       <c r="L40" s="19">
-        <v>4.4703617</v>
+        <v>-42.84731</v>
       </c>
       <c r="M40" s="20">
-        <v>0.20273</v>
+        <v>0</v>
       </c>
       <c r="N40" s="20">
-        <v>0.209</v>
+        <v>0.012</v>
       </c>
       <c r="O40" s="20">
-        <v>0.2135030904411721</v>
+        <v>0.02337438150707416</v>
       </c>
       <c r="P40" s="11">
-        <v>67.13988651183436</v>
+        <v>53.68264010487369</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -4471,52 +4583,52 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="E41" s="10">
-        <v>67.91999816894531</v>
+        <v>399.5899963378906</v>
       </c>
       <c r="F41" s="16">
-        <v>0.3959369122197662</v>
+        <v>0.3883284131297825</v>
       </c>
       <c r="G41" s="19">
-        <v>0.4782631507053702</v>
+        <v>-0.06528790904325747</v>
       </c>
       <c r="H41" s="19">
-        <v>0.5511183194325295</v>
+        <v>0.8737030999799198</v>
       </c>
       <c r="I41" s="19">
-        <v>0.2691043413223938</v>
+        <v>-0.2504338946614285</v>
       </c>
       <c r="J41" s="19">
-        <v>0.2477091198388789</v>
+        <v>0.7568469834899803</v>
       </c>
       <c r="K41" s="19">
-        <v>14.819383</v>
+        <v>30.666668</v>
       </c>
       <c r="L41" s="19">
-        <v>6.1583524</v>
+        <v>5.5863585</v>
       </c>
       <c r="M41" s="20">
-        <v>0.46598998</v>
+        <v>0.1983</v>
       </c>
       <c r="N41" s="20">
-        <v>0.057</v>
+        <v>0.109</v>
       </c>
       <c r="O41" s="20">
-        <v>0.1265410373532643</v>
+        <v>0.4345360396672657</v>
       </c>
       <c r="P41" s="11">
-        <v>65.29564911795941</v>
+        <v>50.84487606833143</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -4524,52 +4636,52 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="E42" s="10">
-        <v>38.45999908447266</v>
+        <v>252.8000030517578</v>
       </c>
       <c r="F42" s="16">
-        <v>0.3959216649113371</v>
+        <v>0.3857896599288244</v>
       </c>
       <c r="G42" s="19">
-        <v>-0.1424155317128326</v>
+        <v>0.3891253641163208</v>
       </c>
       <c r="H42" s="19">
-        <v>-0.4492650758349748</v>
+        <v>-0.4238837218824341</v>
       </c>
       <c r="I42" s="19">
-        <v>3.726301659006618</v>
+        <v>0.4794929837705694</v>
       </c>
       <c r="J42" s="19">
-        <v>-0.02660885155687352</v>
+        <v>1.010330111996504</v>
       </c>
       <c r="K42" s="19">
-        <v>11.418831</v>
+        <v>19.462212</v>
       </c>
       <c r="L42" s="19">
-        <v>2.1043499</v>
+        <v>2.5104156</v>
       </c>
       <c r="M42" s="20">
-        <v>0.21465999</v>
+        <v>0.14548999</v>
       </c>
       <c r="N42" s="20">
-        <v>0.9320000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="O42" s="20">
-        <v>0.2354641863577085</v>
+        <v>0.4490836596377112</v>
       </c>
       <c r="P42" s="11">
-        <v>62.08161803052544</v>
+        <v>48.45690543816092</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -4577,52 +4689,52 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E43" s="10">
-        <v>360.5199890136719</v>
+        <v>846.3699951171875</v>
       </c>
       <c r="F43" s="16">
-        <v>0.3883297648567724</v>
+        <v>0.3834396304433089</v>
       </c>
       <c r="G43" s="19">
-        <v>0.1745054589838901</v>
+        <v>-2.83988005355446</v>
       </c>
       <c r="H43" s="19">
-        <v>-0.2017379700313818</v>
+        <v>1.447127732336587</v>
       </c>
       <c r="I43" s="19">
-        <v>0.5362618455560154</v>
+        <v>1.459563130529552</v>
       </c>
       <c r="J43" s="19">
-        <v>1.019911142786829</v>
+        <v>2.182290812820225</v>
       </c>
       <c r="K43" s="19">
-        <v>33.79535</v>
+        <v>3311.0417</v>
       </c>
       <c r="L43" s="19">
-        <v>5.012071</v>
+        <v>162.83812</v>
       </c>
       <c r="M43" s="20">
-        <v>0.15286</v>
+        <v>3.7152898</v>
       </c>
       <c r="N43" s="20">
-        <v>0.204</v>
+        <v>0.485</v>
       </c>
       <c r="O43" s="20">
-        <v>0.5287282627930578</v>
+        <v>1.011262083482543</v>
       </c>
       <c r="P43" s="11">
-        <v>62.70182944574525</v>
+        <v>48.77584128037775</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -4630,52 +4742,52 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="E44" s="10">
-        <v>414.4400024414062</v>
+        <v>359.8399963378906</v>
       </c>
       <c r="F44" s="16">
-        <v>0.3764487284951614</v>
+        <v>0.3806909903718734</v>
       </c>
       <c r="G44" s="19">
-        <v>-0.7682020816136508</v>
+        <v>0.1745054589838901</v>
       </c>
       <c r="H44" s="19">
-        <v>-0.4657021273019426</v>
+        <v>-0.2017379700313818</v>
       </c>
       <c r="I44" s="19">
-        <v>4.026096567149331</v>
+        <v>0.5362618455560154</v>
       </c>
       <c r="J44" s="19">
-        <v>0.3980679991078087</v>
+        <v>0.9944485611704985</v>
       </c>
       <c r="K44" s="19">
-        <v>104.25127</v>
+        <v>33.79535</v>
       </c>
       <c r="L44" s="19">
-        <v>2.6367822</v>
+        <v>5.012071</v>
       </c>
       <c r="M44" s="20">
-        <v>0.019199999</v>
+        <v>0.15286</v>
       </c>
       <c r="N44" s="20">
-        <v>1.134</v>
+        <v>0.204</v>
       </c>
       <c r="O44" s="20">
-        <v>0.2701195769101918</v>
+        <v>0.505543720380274</v>
       </c>
       <c r="P44" s="11">
-        <v>61.39262480015049</v>
+        <v>62.23183759161277</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4741,77 +4853,77 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B6" s="20">
         <v>0.3</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B7" s="20">
         <v>0.25</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B8" s="20">
         <v>0.15</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B9" s="20">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B10" s="20">
         <f>SUM(B6:B9)</f>
@@ -4820,22 +4932,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4914,100 +5026,100 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -5096,7 +5208,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI1"/>
+  <dimension ref="A1:BI2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -5104,184 +5216,369 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>465.1912841796875</v>
+        <v>434.5918579101562</v>
       </c>
       <c r="C1">
-        <v>434.5918579101562</v>
+        <v>420.3853149414062</v>
       </c>
       <c r="D1">
-        <v>420.3853149414062</v>
+        <v>421.3537292480469</v>
       </c>
       <c r="E1">
-        <v>421.3537292480469</v>
+        <v>393.7393798828125</v>
       </c>
       <c r="F1">
-        <v>393.7393798828125</v>
+        <v>400.1088256835938</v>
       </c>
       <c r="G1">
-        <v>400.1088256835938</v>
+        <v>381.1501770019531</v>
       </c>
       <c r="H1">
-        <v>381.1501770019531</v>
+        <v>369.2198791503906</v>
       </c>
       <c r="I1">
-        <v>369.2198791503906</v>
+        <v>390.8042297363281</v>
       </c>
       <c r="J1">
-        <v>390.8042297363281</v>
+        <v>394.9174194335938</v>
       </c>
       <c r="K1">
-        <v>394.9174194335938</v>
+        <v>408.3951416015625</v>
       </c>
       <c r="L1">
-        <v>408.3951416015625</v>
+        <v>403.4133605957031</v>
       </c>
       <c r="M1">
-        <v>403.4133605957031</v>
+        <v>418.6282348632812</v>
       </c>
       <c r="N1">
-        <v>418.6282348632812</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="O1">
-        <v>408.8244323730469</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="P1">
-        <v>418.0192260742188</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="Q1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="R1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="S1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="T1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="U1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="V1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="W1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="X1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="Y1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="Z1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="AA1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="AB1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="AC1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="AD1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="AE1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="AF1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="AG1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="AH1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="AI1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="AJ1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="AK1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="AL1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="AM1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AN1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AO1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AP1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AQ1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AR1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AS1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AT1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AU1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AV1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AW1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AX1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AY1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AZ1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="BA1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="BB1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="BC1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="BD1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="BE1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="BF1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="BG1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="BH1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="BI1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:61">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1063.936279296875</v>
+      </c>
+      <c r="C2">
+        <v>1079.403930664062</v>
+      </c>
+      <c r="D2">
+        <v>995.8468627929688</v>
+      </c>
+      <c r="E2">
+        <v>863.8771362304688</v>
+      </c>
+      <c r="F2">
+        <v>949.134033203125</v>
+      </c>
+      <c r="G2">
+        <v>935.74609375</v>
+      </c>
+      <c r="H2">
+        <v>891.7428588867188</v>
+      </c>
+      <c r="I2">
+        <v>995.7168579101562</v>
+      </c>
+      <c r="J2">
+        <v>981.4590454101562</v>
+      </c>
+      <c r="K2">
+        <v>1087.822631835938</v>
+      </c>
+      <c r="L2">
+        <v>1020.60302734375</v>
+      </c>
+      <c r="M2">
+        <v>1043.029541015625</v>
+      </c>
+      <c r="N2">
+        <v>1133.815551757812</v>
+      </c>
+      <c r="O2">
+        <v>1211.193725585938</v>
+      </c>
+      <c r="P2">
+        <v>1051.608276367188</v>
+      </c>
+      <c r="Q2">
+        <v>1048.348754882812</v>
+      </c>
+      <c r="R2">
+        <v>1213.373413085938</v>
+      </c>
+      <c r="S2">
+        <v>1132.155883789062</v>
+      </c>
+      <c r="T2">
+        <v>1145.103881835938</v>
+      </c>
+      <c r="U2">
+        <v>1154.112548828125</v>
+      </c>
+      <c r="V2">
+        <v>1032.121337890625</v>
+      </c>
+      <c r="W2">
+        <v>975.4099731445312</v>
+      </c>
+      <c r="X2">
+        <v>984.75</v>
+      </c>
+      <c r="Y2">
+        <v>938.3800048828125</v>
+      </c>
+      <c r="Z2">
+        <v>948.7999877929688</v>
+      </c>
+      <c r="AA2">
+        <v>991.6400146484375</v>
+      </c>
+      <c r="AB2">
+        <v>979.2999877929688</v>
+      </c>
+      <c r="AC2">
+        <v>937</v>
+      </c>
+      <c r="AD2">
+        <v>983.1199951171875</v>
+      </c>
+      <c r="AE2">
+        <v>904.280029296875</v>
+      </c>
+      <c r="AF2">
+        <v>853.2000122070312</v>
+      </c>
+      <c r="AG2">
+        <v>848.9500122070312</v>
+      </c>
+      <c r="AH2">
+        <v>865.4600219726562</v>
+      </c>
+      <c r="AI2">
+        <v>970.8200073242188</v>
+      </c>
+      <c r="AJ2">
+        <v>959.47998046875</v>
+      </c>
+      <c r="AK2">
+        <v>990.2100219726562</v>
+      </c>
+      <c r="AL2">
+        <v>920.9500122070312</v>
+      </c>
+      <c r="AM2">
+        <v>900.2000122070312</v>
+      </c>
+      <c r="AN2">
+        <v>820.530029296875</v>
+      </c>
+      <c r="AO2">
+        <v>739</v>
+      </c>
+      <c r="AP2">
+        <v>874.6599731445312</v>
+      </c>
+      <c r="AQ2">
+        <v>823.030029296875</v>
+      </c>
+      <c r="AR2">
+        <v>829.5</v>
+      </c>
+      <c r="AS2">
+        <v>892.6699829101562</v>
+      </c>
+      <c r="AT2">
+        <v>893.1900024414062</v>
+      </c>
+      <c r="AU2">
+        <v>881.469970703125</v>
+      </c>
+      <c r="AV2">
+        <v>877.5700073242188</v>
+      </c>
+      <c r="AW2">
+        <v>861</v>
+      </c>
+      <c r="AX2">
+        <v>868.52001953125</v>
+      </c>
+      <c r="AY2">
+        <v>911.2899780273438</v>
+      </c>
+      <c r="AZ2">
+        <v>949.8300170898438</v>
+      </c>
+      <c r="BA2">
+        <v>971.6599731445312</v>
+      </c>
+      <c r="BB2">
+        <v>1011.75</v>
+      </c>
+      <c r="BC2">
+        <v>940.760009765625</v>
+      </c>
+      <c r="BD2">
+        <v>937.1099853515625</v>
+      </c>
+      <c r="BE2">
+        <v>974.3300170898438</v>
+      </c>
+      <c r="BF2">
+        <v>966.780029296875</v>
+      </c>
+      <c r="BG2">
+        <v>910.4299926757812</v>
+      </c>
+      <c r="BH2">
+        <v>932.969970703125</v>
+      </c>
+      <c r="BI2">
+        <v>938.4000244140625</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -17,7 +17,7 @@
     <sheet name="_данные" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$Q$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="224">
   <si>
     <t>DELL</t>
   </si>
@@ -33,6 +33,9 @@
     <t>MU</t>
   </si>
   <si>
+    <t>SNDK</t>
+  </si>
+  <si>
     <t>Открытые позиции</t>
   </si>
   <si>
@@ -105,6 +108,12 @@
     <t>2026-08-26</t>
   </si>
   <si>
+    <t>Sandisk</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
     <t>Итого</t>
   </si>
   <si>
@@ -213,12 +222,6 @@
     <t>проходит</t>
   </si>
   <si>
-    <t>SNDK</t>
-  </si>
-  <si>
-    <t>Sandisk</t>
-  </si>
-  <si>
     <t>WDC</t>
   </si>
   <si>
@@ -273,27 +276,27 @@
     <t>EOG Resources</t>
   </si>
   <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>Teradyne</t>
+  </si>
+  <si>
     <t>APA</t>
   </si>
   <si>
     <t>APA Corporation</t>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
-    <t>Financials</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>Teradyne</t>
-  </si>
-  <si>
     <t>INCY</t>
   </si>
   <si>
@@ -303,6 +306,18 @@
     <t>Health Care</t>
   </si>
   <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>Phillips 66</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>Diamondback Energy</t>
+  </si>
+  <si>
     <t>HUM</t>
   </si>
   <si>
@@ -315,63 +330,57 @@
     <t>Goldman Sachs</t>
   </si>
   <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>Phillips 66</t>
-  </si>
-  <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>Diamondback Energy</t>
-  </si>
-  <si>
     <t>CNC</t>
   </si>
   <si>
     <t>Centene Corporation</t>
   </si>
   <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>Nvidia</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>CF Industries</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>SCHW</t>
+  </si>
+  <si>
+    <t>Charles Schwab Corporation</t>
+  </si>
+  <si>
     <t>FTNT</t>
   </si>
   <si>
     <t>Fortinet</t>
   </si>
   <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
-  </si>
-  <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>Nvidia</t>
-  </si>
-  <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>CF Industries</t>
-  </si>
-  <si>
-    <t>Materials</t>
-  </si>
-  <si>
     <t>GOOGL</t>
   </si>
   <si>
@@ -381,10 +390,10 @@
     <t>Communication Services</t>
   </si>
   <si>
-    <t>SCHW</t>
-  </si>
-  <si>
-    <t>Charles Schwab Corporation</t>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>Booking Holdings</t>
   </si>
   <si>
     <t>GOOG</t>
@@ -399,12 +408,6 @@
     <t>Cincinnati Financial</t>
   </si>
   <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>Booking Holdings</t>
-  </si>
-  <si>
     <t>TROW</t>
   </si>
   <si>
@@ -417,16 +420,28 @@
     <t>Raymond James Financial</t>
   </si>
   <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
     <t>DVN</t>
   </si>
   <si>
     <t>Devon Energy</t>
   </si>
   <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>Lumentum</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
   </si>
   <si>
     <t>MO</t>
@@ -438,22 +453,10 @@
     <t>Consumer Staples</t>
   </si>
   <si>
-    <t>FFIV</t>
-  </si>
-  <si>
-    <t>F5, Inc.</t>
-  </si>
-  <si>
-    <t>NUE</t>
-  </si>
-  <si>
-    <t>Nucor</t>
-  </si>
-  <si>
-    <t>STX</t>
-  </si>
-  <si>
-    <t>Seagate Technology</t>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>Hasbro</t>
   </si>
   <si>
     <t>ZBRA</t>
@@ -522,7 +525,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-08-27 03:22 UTC · данные на 2026-08-26 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-08-28 06:10 UTC · данные на 2026-08-27 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -603,7 +606,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-08-27 03:22 UTC</t>
+    <t>2026-08-28 06:10 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -708,7 +711,7 @@
     <numFmt numFmtId="168" formatCode="0.00%"/>
     <numFmt numFmtId="169" formatCode="0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -746,6 +749,13 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF0F9960"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFD64545"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -888,30 +898,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -992,7 +1002,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>981.3399999999999</c:v>
+                  <c:v>1446.31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1081,9 +1091,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$7</c:f>
+              <c:f>Капитал!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1093,15 +1103,18 @@
                 <c:pt idx="2">
                   <c:v>2026-08-26</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>2026-08-27</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$7</c:f>
+              <c:f>Капитал!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1110,6 +1123,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>10028.53</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10015.949999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1134,9 +1150,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$7</c:f>
+              <c:f>Капитал!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1146,15 +1162,18 @@
                 <c:pt idx="2">
                   <c:v>2026-08-26</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>2026-08-27</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$7</c:f>
+              <c:f>Капитал!$F$5:$F$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1163,6 +1182,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>10034.19</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10099.94</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1302,9 +1324,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$7</c:f>
+              <c:f>Капитал!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1314,15 +1336,18 @@
                 <c:pt idx="2">
                   <c:v>2026-08-26</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>2026-08-27</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$7</c:f>
+              <c:f>Капитал!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1331,6 +1356,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>10028.53</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10015.949999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1355,9 +1383,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$7</c:f>
+              <c:f>Капитал!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1367,15 +1395,18 @@
                 <c:pt idx="2">
                   <c:v>2026-08-26</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>2026-08-27</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$7</c:f>
+              <c:f>Капитал!$F$5:$F$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1384,6 +1415,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>10034.19</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10099.94</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1878,102 +1912,102 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="4">
-        <v>10028.53</v>
+        <v>10015.95</v>
       </c>
       <c r="D6" s="5">
-        <v>0.002852999999999994</v>
+        <v>0.001594999999999791</v>
       </c>
       <c r="F6" s="5">
-        <v>0.003419000000000061</v>
+        <v>0.009994000000000058</v>
       </c>
       <c r="H6" s="6">
-        <v>0</v>
+        <v>-0.001254421136497541</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H9" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C13" s="10">
-        <v>9047.189999999999</v>
+        <v>8569.639999999999</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C14" s="10">
-        <v>981.3399999999999</v>
+        <v>1446.31</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C15" s="10">
-        <v>10028.53</v>
+        <v>10015.95</v>
       </c>
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -1981,7 +2015,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -1989,15 +2023,15 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C19" s="11">
         <v>1</v>
@@ -2005,7 +2039,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -2013,85 +2047,85 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C26" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
-        <v>10028.529999999999</v>
+        <v>10015.949999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C33" s="10">
-        <v>981.3399999999999</v>
+        <v>1446.31</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2136,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -2122,62 +2156,62 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -2185,13 +2219,13 @@
         <v>0</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="10">
         <v>443.1115</v>
@@ -2203,32 +2237,32 @@
         <v>476.19</v>
       </c>
       <c r="H5" s="17">
-        <v>463.82</v>
+        <v>472.26</v>
       </c>
       <c r="I5" s="10">
         <f>F5*H5</f>
-        <v>498.44462682</v>
+        <v>507.51468126</v>
       </c>
       <c r="J5" s="10">
         <f>I5-G5</f>
-        <v>22.25462682</v>
+        <v>31.324681259999977</v>
       </c>
       <c r="K5" s="18">
         <f>IFERROR(J5/G5,0)</f>
-        <v>0.04673476305676305</v>
+        <v>0.06578189642789638</v>
       </c>
       <c r="L5" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N5" s="19">
         <v>2.927623067210654</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -2236,13 +2270,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="10">
         <v>926.2029</v>
@@ -2254,58 +2288,109 @@
         <v>476.62</v>
       </c>
       <c r="H6" s="17">
-        <v>938.4</v>
+        <v>935.39</v>
       </c>
       <c r="I6" s="10">
         <f>F6*H6</f>
-        <v>482.8968864</v>
+        <v>481.34795244000003</v>
       </c>
       <c r="J6" s="10">
         <f>I6-G6</f>
-        <v>6.2768864000000235</v>
+        <v>4.727952440000024</v>
       </c>
       <c r="K6" s="18">
         <f>IFERROR(J6/G6,0)</f>
-        <v>0.013169582476606151</v>
+        <v>0.00991975250723852</v>
       </c>
       <c r="L6" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N6" s="19">
         <v>1.809956883354321</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F7" s="12" t="s">
-        <v>26</v>
+      <c r="A7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1550.1948</v>
+      </c>
+      <c r="F7" s="16">
+        <v>0.308058</v>
       </c>
       <c r="G7" s="10">
-        <f>SUM(G5:G6)</f>
-        <v>952.81</v>
+        <v>477.55</v>
+      </c>
+      <c r="H7" s="17">
+        <v>1484.95</v>
       </c>
       <c r="I7" s="10">
-        <f>SUM(I5:I6)</f>
-        <v>981.3399999999999</v>
+        <f>F7*H7</f>
+        <v>457.4507271</v>
       </c>
       <c r="J7" s="10">
-        <f>SUM(J5:J6)</f>
-        <v>28.529999999999973</v>
+        <f>I7-G7</f>
+        <v>-20.099272900000017</v>
       </c>
       <c r="K7" s="18">
         <f>IFERROR(J7/G7,0)</f>
+        <v>-0.042088310962202946</v>
+      </c>
+      <c r="L7" s="11">
         <v>0</v>
       </c>
+      <c r="M7" s="11">
+        <f>MAX(0,21-L7)</f>
+        <v>21</v>
+      </c>
+      <c r="N7" s="19">
+        <v>1.655247920227722</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="10">
+        <f>SUM(G5:G7)</f>
+        <v>1430.36</v>
+      </c>
+      <c r="I8" s="10">
+        <f>SUM(I5:I7)</f>
+        <v>1446.31</v>
+      </c>
+      <c r="J8" s="10">
+        <f>SUM(J5:J7)</f>
+        <v>15.949999999999989</v>
+      </c>
+      <c r="K8" s="18">
+        <f>IFERROR(J8/G8,0)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P6"/>
-  <conditionalFormatting sqref="K5:K6">
+  <autoFilter ref="A4:P7"/>
+  <conditionalFormatting sqref="K5:K7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -2317,7 +2402,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M6">
+  <conditionalFormatting sqref="M5:M7">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -2346,12 +2431,28 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M5:M6</xm:sqref>
+          <xm:sqref>M5:M7</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
+          <x14:colorSeries rgb="FF0B5FFF"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'_данные'!B3:BI3</xm:f>
+              <xm:sqref>P7</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
           <x14:colorSeries rgb="FF0B5FFF"/>
           <x14:colorNegative theme="5"/>
@@ -2412,64 +2513,64 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2479,7 +2580,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2491,37 +2592,37 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B5" s="10">
         <v>10000</v>
@@ -2542,7 +2643,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="10">
         <v>9523.809999999999</v>
@@ -2563,7 +2664,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="10">
         <v>9047.190000000001</v>
@@ -2580,6 +2681,27 @@
       </c>
       <c r="F7" s="10">
         <v>10034.19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="10">
+        <v>8569.639999999999</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1446.31</v>
+      </c>
+      <c r="D8" s="10">
+        <f>B8+C8</f>
+        <v>10015.949999999999</v>
+      </c>
+      <c r="E8" s="11">
+        <v>3</v>
+      </c>
+      <c r="F8" s="10">
+        <v>10099.94</v>
       </c>
     </row>
   </sheetData>
@@ -2609,65 +2731,65 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2678,16 +2800,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="10">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="F5" s="16">
-        <v>1.779817379234556</v>
+        <v>1.792182778434668</v>
       </c>
       <c r="G5" s="19">
         <v>0.1411051627135557</v>
@@ -2699,7 +2821,7 @@
         <v>4.206596031118561</v>
       </c>
       <c r="J5" s="19">
-        <v>2.288396002228748</v>
+        <v>2.329613999562457</v>
       </c>
       <c r="K5" s="19">
         <v>20.560751</v>
@@ -2714,13 +2836,13 @@
         <v>3.457</v>
       </c>
       <c r="O5" s="20">
-        <v>1.188668163099826</v>
+        <v>1.252206383903782</v>
       </c>
       <c r="P5" s="11">
-        <v>51.33878640604577</v>
+        <v>50.99361135450471</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2728,19 +2850,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="10">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="F6" s="16">
-        <v>1.655247920227722</v>
+        <v>1.643319592321297</v>
       </c>
       <c r="G6" s="19">
         <v>-0.297947721659126</v>
@@ -2752,7 +2874,7 @@
         <v>4.026096567149331</v>
       </c>
       <c r="J6" s="19">
-        <v>2.236674879149703</v>
+        <v>2.196913786128287</v>
       </c>
       <c r="K6" s="19">
         <v>20.248442</v>
@@ -2767,13 +2889,13 @@
         <v>3.716</v>
       </c>
       <c r="O6" s="20">
-        <v>1.37099526161495</v>
+        <v>1.277879882742097</v>
       </c>
       <c r="P6" s="11">
-        <v>49.95678524752179</v>
+        <v>49.32206344808555</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -2781,19 +2903,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="10">
-        <v>468.8800048828125</v>
+        <v>462</v>
       </c>
       <c r="F7" s="16">
-        <v>1.163412432007916</v>
+        <v>1.135451734784544</v>
       </c>
       <c r="G7" s="19">
         <v>-0.6552990140462744</v>
@@ -2805,7 +2927,7 @@
         <v>3.032907322180939</v>
       </c>
       <c r="J7" s="19">
-        <v>1.418186749244177</v>
+        <v>1.32498442516627</v>
       </c>
       <c r="K7" s="19">
         <v>17.067032</v>
@@ -2820,13 +2942,13 @@
         <v>0.438</v>
       </c>
       <c r="O7" s="20">
-        <v>0.6127400529348506</v>
+        <v>0.6380571425850909</v>
       </c>
       <c r="P7" s="11">
-        <v>46.62055731040271</v>
+        <v>45.58972604624896</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2834,19 +2956,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" s="10">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="F8" s="16">
-        <v>1.112720607813069</v>
+        <v>1.125501889714689</v>
       </c>
       <c r="G8" s="19">
         <v>0.72925464828006</v>
@@ -2858,7 +2980,7 @@
         <v>2.983550662811328</v>
       </c>
       <c r="J8" s="19">
-        <v>1.742098855598504</v>
+        <v>1.784703128603905</v>
       </c>
       <c r="K8" s="19">
         <v>14.4347105</v>
@@ -2873,13 +2995,13 @@
         <v>0.517</v>
       </c>
       <c r="O8" s="20">
-        <v>0.7583396169280157</v>
+        <v>0.7154056556878978</v>
       </c>
       <c r="P8" s="11">
-        <v>66.63274974855206</v>
+        <v>65.34446117965095</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2887,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>68</v>
-      </c>
       <c r="E9" s="10">
-        <v>362.2699890136719</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="F9" s="16">
-        <v>0.9931099257187986</v>
+        <v>0.9871242374955183</v>
       </c>
       <c r="G9" s="19">
         <v>0.7230916879797831</v>
@@ -2911,7 +3033,7 @@
         <v>2.543797486452658</v>
       </c>
       <c r="J9" s="19">
-        <v>1.636950563734184</v>
+        <v>1.616998269656583</v>
       </c>
       <c r="K9" s="19">
         <v>12.56133</v>
@@ -2926,13 +3048,13 @@
         <v>0.537</v>
       </c>
       <c r="O9" s="20">
-        <v>0.8626363944617035</v>
+        <v>0.8198968817491941</v>
       </c>
       <c r="P9" s="11">
-        <v>69.03712736213646</v>
+        <v>69.53991697169518</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2940,19 +3062,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E10" s="10">
-        <v>58.61999893188477</v>
+        <v>59.16999816894531</v>
       </c>
       <c r="F10" s="16">
-        <v>0.91902097781982</v>
+        <v>0.921994895113415</v>
       </c>
       <c r="G10" s="19">
         <v>0.6355114639003794</v>
@@ -2964,7 +3086,7 @@
         <v>3.304463564487919</v>
       </c>
       <c r="J10" s="19">
-        <v>0.2557155050180444</v>
+        <v>0.2656285626633613</v>
       </c>
       <c r="K10" s="19">
         <v>18.105423</v>
@@ -2979,13 +3101,13 @@
         <v>0.534</v>
       </c>
       <c r="O10" s="20">
-        <v>0.1615700781705602</v>
+        <v>0.1612977225370922</v>
       </c>
       <c r="P10" s="11">
-        <v>53.76222199234199</v>
+        <v>55.7832783396745</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2993,19 +3115,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" s="10">
-        <v>55.22999954223633</v>
+        <v>54.40999984741211</v>
       </c>
       <c r="F11" s="16">
-        <v>0.8540202321228957</v>
+        <v>0.8899117460781116</v>
       </c>
       <c r="G11" s="19">
         <v>0.304959259686968</v>
@@ -3017,7 +3139,7 @@
         <v>1.463737124114395</v>
       </c>
       <c r="J11" s="19">
-        <v>2.313737453117059</v>
+        <v>2.433375832967779</v>
       </c>
       <c r="K11" s="19">
         <v>48.999996</v>
@@ -3032,13 +3154,13 @@
         <v>0.4</v>
       </c>
       <c r="O11" s="20">
-        <v>1.702314936005745</v>
+        <v>1.635367091591919</v>
       </c>
       <c r="P11" s="11">
-        <v>57.87335440339404</v>
+        <v>55.35662305230287</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -3046,52 +3168,52 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12" s="10">
-        <v>463.8200073242188</v>
+        <v>190.6399993896484</v>
       </c>
       <c r="F12" s="16">
-        <v>0.7795572599435281</v>
+        <v>0.7770642919120128</v>
       </c>
       <c r="G12" s="19">
-        <v>-1.276312485328304</v>
+        <v>-0.4056392750220561</v>
       </c>
       <c r="H12" s="19">
-        <v>-0.5342797424893034</v>
+        <v>1.27195723742807</v>
       </c>
       <c r="I12" s="19">
-        <v>3.12929742928239</v>
+        <v>-0.1487202202604564</v>
       </c>
       <c r="J12" s="19">
-        <v>2.755421089239955</v>
+        <v>2.010249327002269</v>
       </c>
       <c r="K12" s="19">
-        <v>884.0612</v>
+        <v>30.285252</v>
       </c>
       <c r="L12" s="19">
-        <v>-200.27277</v>
+        <v>27.10866</v>
       </c>
       <c r="M12" s="20">
-        <v>0</v>
+        <v>1.06734</v>
       </c>
       <c r="N12" s="20">
-        <v>0.875</v>
+        <v>0.125</v>
       </c>
       <c r="O12" s="20">
-        <v>2.774084413624862</v>
+        <v>0.9386570571081279</v>
       </c>
       <c r="P12" s="11">
-        <v>55.13348909271769</v>
+        <v>53.49603815967414</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -3099,52 +3221,52 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" s="10">
-        <v>193.8500061035156</v>
+        <v>472.260009765625</v>
       </c>
       <c r="F13" s="16">
-        <v>0.730591145490776</v>
+        <v>0.7583750209260459</v>
       </c>
       <c r="G13" s="19">
-        <v>-0.4056392750220561</v>
+        <v>-1.276312485328304</v>
       </c>
       <c r="H13" s="19">
-        <v>1.27195723742807</v>
+        <v>-0.5342797424893034</v>
       </c>
       <c r="I13" s="19">
-        <v>-0.1487202202604564</v>
+        <v>3.12929742928239</v>
       </c>
       <c r="J13" s="19">
-        <v>1.85533883893148</v>
+        <v>2.684813625848348</v>
       </c>
       <c r="K13" s="19">
-        <v>30.285252</v>
+        <v>884.0612</v>
       </c>
       <c r="L13" s="19">
-        <v>27.10866</v>
+        <v>-200.27277</v>
       </c>
       <c r="M13" s="20">
-        <v>1.06734</v>
+        <v>0</v>
       </c>
       <c r="N13" s="20">
-        <v>0.125</v>
+        <v>0.875</v>
       </c>
       <c r="O13" s="20">
-        <v>0.9182833866955131</v>
+        <v>2.906991234841489</v>
       </c>
       <c r="P13" s="11">
-        <v>57.14935787629297</v>
+        <v>56.93753717145069</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -3152,19 +3274,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" s="10">
-        <v>333.4400024414062</v>
+        <v>318.9200134277344</v>
       </c>
       <c r="F14" s="16">
-        <v>0.7264639818494252</v>
+        <v>0.754351829711011</v>
       </c>
       <c r="G14" s="19">
         <v>-0.1074817459894137</v>
@@ -3176,7 +3298,7 @@
         <v>0.6713684345102916</v>
       </c>
       <c r="J14" s="19">
-        <v>1.158477704115756</v>
+        <v>1.251437196987708</v>
       </c>
       <c r="K14" s="19">
         <v>20.24627</v>
@@ -3191,13 +3313,13 @@
         <v>0.14</v>
       </c>
       <c r="O14" s="20">
-        <v>0.6436285292134618</v>
+        <v>0.4718131728376875</v>
       </c>
       <c r="P14" s="11">
-        <v>64.66898025571628</v>
+        <v>54.93271656777372</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -3205,19 +3327,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" s="10">
-        <v>144.8399963378906</v>
+        <v>144.5</v>
       </c>
       <c r="F15" s="16">
-        <v>0.6988290824930529</v>
+        <v>0.7222288834556412</v>
       </c>
       <c r="G15" s="19">
         <v>0.6102249595302855</v>
@@ -3229,7 +3351,7 @@
         <v>1.562733350737734</v>
       </c>
       <c r="J15" s="19">
-        <v>0.4615777937894738</v>
+        <v>0.5395771303314347</v>
       </c>
       <c r="K15" s="19">
         <v>11.680406</v>
@@ -3244,13 +3366,13 @@
         <v>0.587</v>
       </c>
       <c r="O15" s="20">
-        <v>0.2003906105262252</v>
+        <v>0.2111175269545356</v>
       </c>
       <c r="P15" s="11">
-        <v>51.15227743096032</v>
+        <v>50.60907551652403</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -3258,52 +3380,52 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E16" s="10">
-        <v>41.18999862670898</v>
+        <v>257.6199951171875</v>
       </c>
       <c r="F16" s="16">
-        <v>0.6896542101523245</v>
+        <v>0.7052476116904165</v>
       </c>
       <c r="G16" s="19">
-        <v>0.9986491788407921</v>
+        <v>1.158776322034968</v>
       </c>
       <c r="H16" s="19">
-        <v>0.6094621501467751</v>
+        <v>0.3596891130938242</v>
       </c>
       <c r="I16" s="19">
-        <v>-0.228424555888388</v>
+        <v>0.009309850889890559</v>
       </c>
       <c r="J16" s="19">
-        <v>0.9065253411555046</v>
+        <v>0.8876531972432877</v>
       </c>
       <c r="K16" s="19">
-        <v>9.159914000000001</v>
+        <v>5.083822</v>
       </c>
       <c r="L16" s="19">
-        <v>2.14564</v>
+        <v>2.0850062</v>
       </c>
       <c r="M16" s="20">
-        <v>0.26659</v>
+        <v>0.46113998</v>
       </c>
       <c r="N16" s="20">
-        <v>0.092</v>
+        <v>0.118</v>
       </c>
       <c r="O16" s="20">
-        <v>0.4999119656741835</v>
+        <v>0.2233858402197189</v>
       </c>
       <c r="P16" s="11">
-        <v>57.51035836662003</v>
+        <v>49.68985095422584</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -3311,52 +3433,52 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="E17" s="10">
-        <v>261.8099975585938</v>
+        <v>372.0599975585938</v>
       </c>
       <c r="F17" s="16">
-        <v>0.6786587241238107</v>
+        <v>0.7045980276279548</v>
       </c>
       <c r="G17" s="19">
-        <v>1.158776322034968</v>
+        <v>-1.08262537420069</v>
       </c>
       <c r="H17" s="19">
-        <v>0.3596891130938242</v>
+        <v>0.6932659455068273</v>
       </c>
       <c r="I17" s="19">
-        <v>0.009309850889890559</v>
+        <v>3.615274867663105</v>
       </c>
       <c r="J17" s="19">
-        <v>0.7990235720212685</v>
+        <v>1.04592641120663</v>
       </c>
       <c r="K17" s="19">
-        <v>5.083822</v>
+        <v>51.539547</v>
       </c>
       <c r="L17" s="19">
-        <v>2.0850062</v>
+        <v>18.169596</v>
       </c>
       <c r="M17" s="20">
-        <v>0.46113998</v>
+        <v>0.36465</v>
       </c>
       <c r="N17" s="20">
-        <v>0.118</v>
+        <v>1.039</v>
       </c>
       <c r="O17" s="20">
-        <v>0.2636553073069234</v>
+        <v>0.1187271043196065</v>
       </c>
       <c r="P17" s="11">
-        <v>53.77724286495333</v>
+        <v>48.03608719915346</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -3364,52 +3486,52 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E18" s="10">
-        <v>363.1000061035156</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="F18" s="16">
-        <v>0.6463211235407152</v>
+        <v>0.6992905455405241</v>
       </c>
       <c r="G18" s="19">
-        <v>-1.08262537420069</v>
+        <v>0.9986491788407921</v>
       </c>
       <c r="H18" s="19">
-        <v>0.6932659455068273</v>
+        <v>0.6094621501467751</v>
       </c>
       <c r="I18" s="19">
-        <v>3.615274867663105</v>
+        <v>-0.228424555888388</v>
       </c>
       <c r="J18" s="19">
-        <v>0.8516700642491655</v>
+        <v>0.93864645911617</v>
       </c>
       <c r="K18" s="19">
-        <v>51.539547</v>
+        <v>9.159914000000001</v>
       </c>
       <c r="L18" s="19">
-        <v>18.169596</v>
+        <v>2.14564</v>
       </c>
       <c r="M18" s="20">
-        <v>0.36465</v>
+        <v>0.26659</v>
       </c>
       <c r="N18" s="20">
-        <v>1.039</v>
+        <v>0.092</v>
       </c>
       <c r="O18" s="20">
-        <v>0.05955641877465934</v>
+        <v>0.4764243691300467</v>
       </c>
       <c r="P18" s="11">
-        <v>45.48261500820713</v>
+        <v>61.56592694680431</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -3417,19 +3539,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E19" s="10">
-        <v>128.1199951171875</v>
+        <v>127.7399978637695</v>
       </c>
       <c r="F19" s="16">
-        <v>0.6258810179742954</v>
+        <v>0.6455765765733465</v>
       </c>
       <c r="G19" s="19">
         <v>0.3568150294101221</v>
@@ -3441,7 +3563,7 @@
         <v>0.6313896241094424</v>
       </c>
       <c r="J19" s="19">
-        <v>0.6742222958880369</v>
+        <v>0.7398741578848742</v>
       </c>
       <c r="K19" s="19">
         <v>16.303185</v>
@@ -3456,13 +3578,13 @@
         <v>0.377</v>
       </c>
       <c r="O19" s="20">
-        <v>0.2814561993941203</v>
+        <v>0.2762513991162128</v>
       </c>
       <c r="P19" s="11">
-        <v>63.50649061776875</v>
+        <v>62.39596004953174</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -3470,52 +3592,52 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E20" s="10">
-        <v>391.0599975585938</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="F20" s="16">
-        <v>0.6155234899676881</v>
+        <v>0.6260124248975273</v>
       </c>
       <c r="G20" s="19">
-        <v>0.4746478020487309</v>
+        <v>0.06892234601185927</v>
       </c>
       <c r="H20" s="19">
-        <v>-0.2835410288834002</v>
+        <v>-0.54467699511111</v>
       </c>
       <c r="I20" s="19">
-        <v>0.2562199099090978</v>
+        <v>2.512241193631993</v>
       </c>
       <c r="J20" s="19">
-        <v>1.685271400291847</v>
+        <v>1.215562636089827</v>
       </c>
       <c r="K20" s="19">
-        <v>35.8304</v>
+        <v>110.99082</v>
       </c>
       <c r="L20" s="19">
-        <v>2.4162972</v>
+        <v>3.064414</v>
       </c>
       <c r="M20" s="20">
-        <v>0.06893000000000001</v>
+        <v>0.23452999</v>
       </c>
       <c r="N20" s="20">
-        <v>0.262</v>
+        <v>0.531</v>
       </c>
       <c r="O20" s="20">
-        <v>1.237722478842338</v>
+        <v>0.5927656307260232</v>
       </c>
       <c r="P20" s="11">
-        <v>56.21888511116801</v>
+        <v>67.84167526358479</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -3523,52 +3645,52 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E21" s="10">
-        <v>1040.4599609375</v>
+        <v>200.5200042724609</v>
       </c>
       <c r="F21" s="16">
-        <v>0.60775005215091</v>
+        <v>0.6111153289321913</v>
       </c>
       <c r="G21" s="19">
-        <v>0.3556011439311419</v>
+        <v>0.561347890123932</v>
       </c>
       <c r="H21" s="19">
-        <v>0.8458479961101603</v>
+        <v>0.0970884411429475</v>
       </c>
       <c r="I21" s="19">
-        <v>1.024034813371229</v>
+        <v>1.717140484071832</v>
       </c>
       <c r="J21" s="19">
-        <v>0.4533416264611437</v>
+        <v>0.5362259299950004</v>
       </c>
       <c r="K21" s="19">
-        <v>16.004324</v>
+        <v>40.156254</v>
       </c>
       <c r="L21" s="19">
-        <v>2.8622644</v>
+        <v>1.5220274</v>
       </c>
       <c r="M21" s="20">
-        <v>0.16902</v>
+        <v>0.034930002</v>
       </c>
       <c r="N21" s="20">
-        <v>0.425</v>
+        <v>0.525</v>
       </c>
       <c r="O21" s="20">
-        <v>0.1401867758662851</v>
+        <v>0.2213742934098679</v>
       </c>
       <c r="P21" s="11">
-        <v>49.88144521980084</v>
+        <v>51.15467970531992</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -3576,52 +3698,52 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E22" s="10">
-        <v>242.2299957275391</v>
+        <v>392.6300048828125</v>
       </c>
       <c r="F22" s="16">
-        <v>0.6004023149653797</v>
+        <v>0.6075898505250401</v>
       </c>
       <c r="G22" s="19">
-        <v>0.06892234601185927</v>
+        <v>0.4746478020487309</v>
       </c>
       <c r="H22" s="19">
-        <v>-0.54467699511111</v>
+        <v>-0.2835410288834002</v>
       </c>
       <c r="I22" s="19">
-        <v>2.512241193631993</v>
+        <v>0.2562199099090978</v>
       </c>
       <c r="J22" s="19">
-        <v>1.130195602982668</v>
+        <v>1.658825935483021</v>
       </c>
       <c r="K22" s="19">
-        <v>110.99082</v>
+        <v>35.8304</v>
       </c>
       <c r="L22" s="19">
-        <v>3.064414</v>
+        <v>2.4162972</v>
       </c>
       <c r="M22" s="20">
-        <v>0.23452999</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="N22" s="20">
-        <v>0.531</v>
+        <v>0.262</v>
       </c>
       <c r="O22" s="20">
-        <v>0.6146637868472538</v>
+        <v>1.117192792951127</v>
       </c>
       <c r="P22" s="11">
-        <v>71.34710082865476</v>
+        <v>57.11940373585679</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -3629,52 +3751,52 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E23" s="10">
-        <v>199.8399963378906</v>
+        <v>1040.869995117188</v>
       </c>
       <c r="F23" s="16">
-        <v>0.5936667758865617</v>
+        <v>0.5991689230794568</v>
       </c>
       <c r="G23" s="19">
-        <v>0.561347890123932</v>
+        <v>0.3556011439311419</v>
       </c>
       <c r="H23" s="19">
-        <v>0.0970884411429475</v>
+        <v>0.8458479961101603</v>
       </c>
       <c r="I23" s="19">
-        <v>1.717140484071832</v>
+        <v>1.024034813371229</v>
       </c>
       <c r="J23" s="19">
-        <v>0.4780640865095683</v>
+        <v>0.4247378628896332</v>
       </c>
       <c r="K23" s="19">
-        <v>40.156254</v>
+        <v>16.004324</v>
       </c>
       <c r="L23" s="19">
-        <v>1.5220274</v>
+        <v>2.8622644</v>
       </c>
       <c r="M23" s="20">
-        <v>0.034930002</v>
+        <v>0.16902</v>
       </c>
       <c r="N23" s="20">
-        <v>0.525</v>
+        <v>0.425</v>
       </c>
       <c r="O23" s="20">
-        <v>0.2115004868031256</v>
+        <v>0.1312802350176108</v>
       </c>
       <c r="P23" s="11">
-        <v>50.3702857479487</v>
+        <v>49.97657026255024</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -3682,19 +3804,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" s="10">
-        <v>65.47000122070312</v>
+        <v>65.33000183105469</v>
       </c>
       <c r="F24" s="16">
-        <v>0.5835454398311176</v>
+        <v>0.5938607298607032</v>
       </c>
       <c r="G24" s="19">
         <v>1.175622071073703</v>
@@ -3706,7 +3828,7 @@
         <v>-0.5389901628995794</v>
       </c>
       <c r="J24" s="19">
-        <v>1.482974719196152</v>
+        <v>1.51735901929477</v>
       </c>
       <c r="K24" s="19">
         <v>12.357601</v>
@@ -3721,13 +3843,13 @@
         <v>0.046</v>
       </c>
       <c r="O24" s="20">
-        <v>0.5336145075381156</v>
+        <v>0.5217796731107474</v>
       </c>
       <c r="P24" s="11">
-        <v>51.47817097291836</v>
+        <v>51.01485882539968</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -3735,52 +3857,52 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E25" s="10">
-        <v>157.5399932861328</v>
+        <v>199.7700042724609</v>
       </c>
       <c r="F25" s="16">
-        <v>0.5590552986099251</v>
+        <v>0.5775723685742113</v>
       </c>
       <c r="G25" s="19">
-        <v>-1.877249539822365</v>
+        <v>0.5728138826097362</v>
       </c>
       <c r="H25" s="19">
-        <v>1.758964460615154</v>
+        <v>-0.06908867602196844</v>
       </c>
       <c r="I25" s="19">
-        <v>0.3182836657213104</v>
+        <v>2.415351960752095</v>
       </c>
       <c r="J25" s="19">
-        <v>2.115821651815498</v>
+        <v>0.2023252622798944</v>
       </c>
       <c r="K25" s="19">
-        <v>54.282146</v>
+        <v>19.755836</v>
       </c>
       <c r="L25" s="19">
-        <v>71.89688</v>
+        <v>2.098037</v>
       </c>
       <c r="M25" s="20">
-        <v>1.17442</v>
+        <v>0.12231</v>
       </c>
       <c r="N25" s="20">
-        <v>0.256</v>
+        <v>0.535</v>
       </c>
       <c r="O25" s="20">
-        <v>1.036716178331158</v>
+        <v>0.1042524101517361</v>
       </c>
       <c r="P25" s="11">
-        <v>51.2331295475656</v>
+        <v>58.44099069545236</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -3788,52 +3910,52 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" s="10">
-        <v>214.0800018310547</v>
+        <v>369.3299865722656</v>
       </c>
       <c r="F26" s="16">
-        <v>0.5548357065874343</v>
+        <v>0.5727255966010276</v>
       </c>
       <c r="G26" s="19">
-        <v>0.3452907642059501</v>
+        <v>1.091200655903261</v>
       </c>
       <c r="H26" s="19">
-        <v>0.8001987998031764</v>
+        <v>0.1101459112354547</v>
       </c>
       <c r="I26" s="19">
-        <v>0.4732064398512328</v>
+        <v>-0.3352804504404189</v>
       </c>
       <c r="J26" s="19">
-        <v>0.6007260379905678</v>
+        <v>0.8937366319574954</v>
       </c>
       <c r="K26" s="19">
-        <v>17.306387</v>
+        <v>9.963699999999999</v>
       </c>
       <c r="L26" s="19">
-        <v>3.1574755</v>
+        <v>2.3337615</v>
       </c>
       <c r="M26" s="20">
-        <v>0.17969999</v>
+        <v>0.26511</v>
       </c>
       <c r="N26" s="20">
-        <v>0.28</v>
+        <v>0.003</v>
       </c>
       <c r="O26" s="20">
-        <v>0.2456989263064639</v>
+        <v>0.2154665752855902</v>
       </c>
       <c r="P26" s="11">
-        <v>49.18336325627639</v>
+        <v>52.57038066221627</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -3841,52 +3963,52 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="E27" s="10">
-        <v>200.2100067138672</v>
+        <v>227.9799957275391</v>
       </c>
       <c r="F27" s="16">
-        <v>0.5544687926280044</v>
+        <v>0.56699496670032</v>
       </c>
       <c r="G27" s="19">
-        <v>0.5728138826097362</v>
+        <v>-1.338461785426528</v>
       </c>
       <c r="H27" s="19">
-        <v>-0.06908867602196844</v>
+        <v>2.078256102926562</v>
       </c>
       <c r="I27" s="19">
-        <v>2.415351960752095</v>
+        <v>2.806787311422478</v>
       </c>
       <c r="J27" s="19">
-        <v>0.1253133424592044</v>
+        <v>0.09317126627755401</v>
       </c>
       <c r="K27" s="19">
-        <v>19.755836</v>
+        <v>32.883278</v>
       </c>
       <c r="L27" s="19">
-        <v>2.098037</v>
+        <v>25.833954</v>
       </c>
       <c r="M27" s="20">
-        <v>0.12231</v>
+        <v>1.14288</v>
       </c>
       <c r="N27" s="20">
-        <v>0.535</v>
+        <v>0.852</v>
       </c>
       <c r="O27" s="20">
-        <v>0.1063242023878324</v>
+        <v>0.2345614306171031</v>
       </c>
       <c r="P27" s="11">
-        <v>59.34798776027157</v>
+        <v>61.32156943941269</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -3894,52 +4016,52 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28" s="10">
-        <v>371.1499938964844</v>
+        <v>214.8600006103516</v>
       </c>
       <c r="F28" s="16">
-        <v>0.5399391269044111</v>
+        <v>0.5542918117161544</v>
       </c>
       <c r="G28" s="19">
-        <v>1.091200655903261</v>
+        <v>0.3452907642059501</v>
       </c>
       <c r="H28" s="19">
-        <v>0.1101459112354547</v>
+        <v>0.8001987998031764</v>
       </c>
       <c r="I28" s="19">
-        <v>-0.3352804504404189</v>
+        <v>0.4732064398512328</v>
       </c>
       <c r="J28" s="19">
-        <v>0.7844483996354403</v>
+        <v>0.5989130550863011</v>
       </c>
       <c r="K28" s="19">
-        <v>9.963699999999999</v>
+        <v>17.306387</v>
       </c>
       <c r="L28" s="19">
-        <v>2.3337615</v>
+        <v>3.1574755</v>
       </c>
       <c r="M28" s="20">
-        <v>0.26511</v>
+        <v>0.17969999</v>
       </c>
       <c r="N28" s="20">
-        <v>0.003</v>
+        <v>0.28</v>
       </c>
       <c r="O28" s="20">
-        <v>0.2273877728518141</v>
+        <v>0.2237520476524988</v>
       </c>
       <c r="P28" s="11">
-        <v>54.50810671530476</v>
+        <v>50.2319810346368</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -3947,52 +4069,52 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="E29" s="10">
-        <v>209.6600036621094</v>
+        <v>125.7099990844727</v>
       </c>
       <c r="F29" s="16">
-        <v>0.5362579450829138</v>
+        <v>0.528212307428086</v>
       </c>
       <c r="G29" s="19">
-        <v>-1.338461785426528</v>
+        <v>0.6458174147154766</v>
       </c>
       <c r="H29" s="19">
-        <v>2.078256102926562</v>
+        <v>0.432781060607519</v>
       </c>
       <c r="I29" s="19">
-        <v>2.806787311422478</v>
+        <v>0.3540288428030787</v>
       </c>
       <c r="J29" s="19">
-        <v>-0.009285472447133136</v>
+        <v>0.5772249714703384</v>
       </c>
       <c r="K29" s="19">
-        <v>32.883278</v>
+        <v>9.616072000000001</v>
       </c>
       <c r="L29" s="19">
-        <v>25.833954</v>
+        <v>3.4084976</v>
       </c>
       <c r="M29" s="20">
-        <v>1.14288</v>
+        <v>0.29867</v>
       </c>
       <c r="N29" s="20">
-        <v>0.852</v>
+        <v>0.176</v>
       </c>
       <c r="O29" s="20">
-        <v>0.07340831571502826</v>
+        <v>0.3058211097480845</v>
       </c>
       <c r="P29" s="11">
-        <v>46.29839347105207</v>
+        <v>57.29475165278869</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -4000,52 +4122,52 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="E30" s="10">
-        <v>125.6999969482422</v>
+        <v>108.0500030517578</v>
       </c>
       <c r="F30" s="16">
-        <v>0.5131019267794631</v>
+        <v>0.5160031210762854</v>
       </c>
       <c r="G30" s="19">
-        <v>0.6458174147154766</v>
+        <v>0.02982011516877862</v>
       </c>
       <c r="H30" s="19">
-        <v>0.432781060607519</v>
+        <v>1.249493192438245</v>
       </c>
       <c r="I30" s="19">
-        <v>0.3540288428030787</v>
+        <v>0.1792183728511779</v>
       </c>
       <c r="J30" s="19">
-        <v>0.5268570359749285</v>
+        <v>0.5593367749613797</v>
       </c>
       <c r="K30" s="19">
-        <v>9.616072000000001</v>
+        <v>20.440647</v>
       </c>
       <c r="L30" s="19">
-        <v>3.4084976</v>
+        <v>4.4703617</v>
       </c>
       <c r="M30" s="20">
-        <v>0.29867</v>
+        <v>0.20273</v>
       </c>
       <c r="N30" s="20">
-        <v>0.176</v>
+        <v>0.209</v>
       </c>
       <c r="O30" s="20">
-        <v>0.3195702217273626</v>
+        <v>0.1151960784313726</v>
       </c>
       <c r="P30" s="11">
-        <v>57.28106845062105</v>
+        <v>51.68851803422784</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -4053,52 +4175,52 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>117</v>
+        <v>22</v>
       </c>
       <c r="E31" s="10">
-        <v>342</v>
+        <v>172.7799987792969</v>
       </c>
       <c r="F31" s="16">
-        <v>0.4926260373746073</v>
+        <v>0.5133671518983052</v>
       </c>
       <c r="G31" s="19">
-        <v>-0.3026541063380147</v>
+        <v>-1.877249539822365</v>
       </c>
       <c r="H31" s="19">
-        <v>1.453871687245511</v>
+        <v>1.758964460615154</v>
       </c>
       <c r="I31" s="19">
-        <v>1.455283430456029</v>
+        <v>0.3182836657213104</v>
       </c>
       <c r="J31" s="19">
-        <v>0.005539442987432119</v>
+        <v>1.963527829443432</v>
       </c>
       <c r="K31" s="19">
-        <v>17.464125</v>
+        <v>54.282146</v>
       </c>
       <c r="L31" s="19">
-        <v>6.838651</v>
+        <v>71.89688</v>
       </c>
       <c r="M31" s="20">
-        <v>0.48676</v>
+        <v>1.17442</v>
       </c>
       <c r="N31" s="20">
-        <v>0.242</v>
+        <v>0.256</v>
       </c>
       <c r="O31" s="20">
-        <v>0.094423619884765</v>
+        <v>1.181565725213474</v>
       </c>
       <c r="P31" s="11">
-        <v>45.18771599619804</v>
+        <v>64.73341503859061</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -4112,46 +4234,46 @@
         <v>119</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="E32" s="10">
-        <v>109.3899993896484</v>
+        <v>340.6499938964844</v>
       </c>
       <c r="F32" s="16">
-        <v>0.4833902032451637</v>
+        <v>0.5026889325041735</v>
       </c>
       <c r="G32" s="19">
-        <v>0.02982011516877862</v>
+        <v>-0.3026541063380147</v>
       </c>
       <c r="H32" s="19">
-        <v>1.249493192438245</v>
+        <v>1.453871687245511</v>
       </c>
       <c r="I32" s="19">
-        <v>0.1792183728511779</v>
+        <v>1.455283430456029</v>
       </c>
       <c r="J32" s="19">
-        <v>0.4506270488576405</v>
+        <v>0.03908242675265263</v>
       </c>
       <c r="K32" s="19">
-        <v>20.440647</v>
+        <v>17.464125</v>
       </c>
       <c r="L32" s="19">
-        <v>4.4703617</v>
+        <v>6.838651</v>
       </c>
       <c r="M32" s="20">
-        <v>0.20273</v>
+        <v>0.48676</v>
       </c>
       <c r="N32" s="20">
-        <v>0.209</v>
+        <v>0.242</v>
       </c>
       <c r="O32" s="20">
-        <v>0.1547209781439263</v>
+        <v>0.1096799187683553</v>
       </c>
       <c r="P32" s="11">
-        <v>55.98972868390818</v>
+        <v>44.24473408301287</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -4159,52 +4281,52 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E33" s="10">
-        <v>339.1000061035156</v>
+        <v>202.5599975585938</v>
       </c>
       <c r="F33" s="16">
-        <v>0.4798778592399495</v>
+        <v>0.4915843745559323</v>
       </c>
       <c r="G33" s="19">
-        <v>-0.2917499460294181</v>
+        <v>0.1534000000694478</v>
       </c>
       <c r="H33" s="19">
-        <v>1.453871687245511</v>
+        <v>1.132904211800141</v>
       </c>
       <c r="I33" s="19">
-        <v>1.455283430456029</v>
+        <v>0.2283188730840903</v>
       </c>
       <c r="J33" s="19">
-        <v>-0.04785864443669054</v>
+        <v>0.4269683020748307</v>
       </c>
       <c r="K33" s="19">
-        <v>17.298695</v>
+        <v>23.318033</v>
       </c>
       <c r="L33" s="19">
-        <v>6.770473</v>
+        <v>-14.997891</v>
       </c>
       <c r="M33" s="20">
-        <v>0.48676</v>
+        <v>0</v>
       </c>
       <c r="N33" s="20">
-        <v>0.242</v>
+        <v>0.081</v>
       </c>
       <c r="O33" s="20">
-        <v>0.08469842775952308</v>
+        <v>0.1971765152341145</v>
       </c>
       <c r="P33" s="11">
-        <v>44.17840072111089</v>
+        <v>49.93472899320084</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -4212,52 +4334,52 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="E34" s="10">
-        <v>172.3800048828125</v>
+        <v>337.7099914550781</v>
       </c>
       <c r="F34" s="16">
-        <v>0.4588679794930431</v>
+        <v>0.4893821574552495</v>
       </c>
       <c r="G34" s="19">
-        <v>0.9039922035122165</v>
+        <v>-0.2917499460294181</v>
       </c>
       <c r="H34" s="19">
-        <v>0.2335474389445495</v>
+        <v>1.453871687245511</v>
       </c>
       <c r="I34" s="19">
-        <v>0.6837145595313986</v>
+        <v>1.455283430456029</v>
       </c>
       <c r="J34" s="19">
-        <v>0.08908758257843671</v>
+        <v>-0.01617765038569052</v>
       </c>
       <c r="K34" s="19">
-        <v>7.9410954</v>
+        <v>17.298695</v>
       </c>
       <c r="L34" s="19">
-        <v>1.5754024</v>
+        <v>6.770473</v>
       </c>
       <c r="M34" s="20">
-        <v>0.21484</v>
+        <v>0.48676</v>
       </c>
       <c r="N34" s="20">
-        <v>0.316</v>
+        <v>0.242</v>
       </c>
       <c r="O34" s="20">
-        <v>0.06471934417540237</v>
+        <v>0.1009320247599452</v>
       </c>
       <c r="P34" s="11">
-        <v>46.20082696898552</v>
+        <v>43.16080215417117</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -4265,52 +4387,52 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E35" s="10">
-        <v>208.8899993896484</v>
+        <v>172.5200042724609</v>
       </c>
       <c r="F35" s="16">
-        <v>0.4580532307800073</v>
+        <v>0.4809039774222989</v>
       </c>
       <c r="G35" s="19">
-        <v>0.1534000000694478</v>
+        <v>0.9039922035122165</v>
       </c>
       <c r="H35" s="19">
-        <v>1.132904211800141</v>
+        <v>0.2335474389445495</v>
       </c>
       <c r="I35" s="19">
-        <v>0.2283188730840903</v>
+        <v>0.6837145595313986</v>
       </c>
       <c r="J35" s="19">
-        <v>0.315197822821747</v>
+        <v>0.1625409090092892</v>
       </c>
       <c r="K35" s="19">
-        <v>23.318033</v>
+        <v>7.9410954</v>
       </c>
       <c r="L35" s="19">
-        <v>-14.997891</v>
+        <v>1.5754024</v>
       </c>
       <c r="M35" s="20">
-        <v>0</v>
+        <v>0.21484</v>
       </c>
       <c r="N35" s="20">
-        <v>0.081</v>
+        <v>0.316</v>
       </c>
       <c r="O35" s="20">
-        <v>0.2604664322848762</v>
+        <v>0.0562312412745769</v>
       </c>
       <c r="P35" s="11">
-        <v>57.38759816451733</v>
+        <v>46.56583117268335</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -4318,19 +4440,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36" s="10">
-        <v>112.5500030517578</v>
+        <v>112.3600006103516</v>
       </c>
       <c r="F36" s="16">
-        <v>0.4514477445269051</v>
+        <v>0.4481038184363693</v>
       </c>
       <c r="G36" s="19">
         <v>0.6818833135656812</v>
@@ -4342,7 +4464,7 @@
         <v>-0.1751734853969869</v>
       </c>
       <c r="J36" s="19">
-        <v>0.3865380444193006</v>
+        <v>0.3753916241175147</v>
       </c>
       <c r="K36" s="19">
         <v>11.196411</v>
@@ -4357,13 +4479,13 @@
         <v>0.107</v>
       </c>
       <c r="O36" s="20">
-        <v>0.213360246531962</v>
+        <v>0.1963682428315794</v>
       </c>
       <c r="P36" s="11">
-        <v>48.02508926581249</v>
+        <v>47.37893442425457</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -4371,19 +4493,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E37" s="10">
-        <v>176.6900024414062</v>
+        <v>176.1100006103516</v>
       </c>
       <c r="F37" s="16">
-        <v>0.4223171498658832</v>
+        <v>0.4477617537762071</v>
       </c>
       <c r="G37" s="19">
         <v>0.5368950783305056</v>
@@ -4395,7 +4517,7 @@
         <v>0.0123304280898874</v>
       </c>
       <c r="J37" s="19">
-        <v>0.3692243471452203</v>
+        <v>0.4540396935129666</v>
       </c>
       <c r="K37" s="19">
         <v>15.270527</v>
@@ -4410,13 +4532,13 @@
         <v>0.151</v>
       </c>
       <c r="O37" s="20">
-        <v>0.1240599106134253</v>
+        <v>0.1109681677071694</v>
       </c>
       <c r="P37" s="11">
-        <v>53.94136323074993</v>
+        <v>52.65969001770588</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -4424,52 +4546,52 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E38" s="10">
-        <v>46.83000183105469</v>
+        <v>66.94999694824219</v>
       </c>
       <c r="F38" s="16">
-        <v>0.4215670414517939</v>
+        <v>0.4444939995885323</v>
       </c>
       <c r="G38" s="19">
-        <v>0.4704959025733791</v>
+        <v>0.4782631507053702</v>
       </c>
       <c r="H38" s="19">
-        <v>0.07046152471131609</v>
+        <v>0.5511183194325295</v>
       </c>
       <c r="I38" s="19">
-        <v>1.41063650916965</v>
+        <v>0.2691043413223938</v>
       </c>
       <c r="J38" s="19">
-        <v>0.1706913770883454</v>
+        <v>0.4095660777347659</v>
       </c>
       <c r="K38" s="19">
-        <v>10.484783</v>
+        <v>14.819383</v>
       </c>
       <c r="L38" s="19">
-        <v>1.3284671</v>
+        <v>6.1583524</v>
       </c>
       <c r="M38" s="20">
-        <v>0.11522</v>
+        <v>0.46598998</v>
       </c>
       <c r="N38" s="20">
-        <v>0.642</v>
+        <v>0.057</v>
       </c>
       <c r="O38" s="20">
-        <v>0.1123751124611942</v>
+        <v>0.1195394707171613</v>
       </c>
       <c r="P38" s="11">
-        <v>55.01372953852868</v>
+        <v>60.33429878487841</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -4477,52 +4599,52 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E39" s="10">
-        <v>67.56999969482422</v>
+        <v>47.11999893188477</v>
       </c>
       <c r="F39" s="16">
-        <v>0.4045030192457723</v>
+        <v>0.4401261593221512</v>
       </c>
       <c r="G39" s="19">
-        <v>0.4782631507053702</v>
+        <v>0.4704959025733791</v>
       </c>
       <c r="H39" s="19">
-        <v>0.5511183194325295</v>
+        <v>0.07046152471131609</v>
       </c>
       <c r="I39" s="19">
-        <v>0.2691043413223938</v>
+        <v>1.41063650916965</v>
       </c>
       <c r="J39" s="19">
-        <v>0.2762628099255658</v>
+        <v>0.2325551033228697</v>
       </c>
       <c r="K39" s="19">
-        <v>14.819383</v>
+        <v>10.484783</v>
       </c>
       <c r="L39" s="19">
-        <v>6.1583524</v>
+        <v>1.3284671</v>
       </c>
       <c r="M39" s="20">
-        <v>0.46598998</v>
+        <v>0.11522</v>
       </c>
       <c r="N39" s="20">
-        <v>0.057</v>
+        <v>0.642</v>
       </c>
       <c r="O39" s="20">
-        <v>0.1262206503785697</v>
+        <v>0.1182139356321723</v>
       </c>
       <c r="P39" s="11">
-        <v>63.49985153390229</v>
+        <v>56.2636607939117</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -4530,52 +4652,52 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="E40" s="10">
-        <v>69.12000274658203</v>
+        <v>956.1400146484375</v>
       </c>
       <c r="F40" s="16">
-        <v>0.3893525364836609</v>
+        <v>0.4245403958428556</v>
       </c>
       <c r="G40" s="19">
-        <v>0.5078777743715293</v>
+        <v>-1.802769348549261</v>
       </c>
       <c r="H40" s="19">
-        <v>1.335916108729087</v>
+        <v>-0.4234103737860816</v>
       </c>
       <c r="I40" s="19">
-        <v>-0.5911526511284643</v>
+        <v>4.026096567149331</v>
       </c>
       <c r="J40" s="19">
-        <v>-0.02772308446933316</v>
+        <v>1.557697695939182</v>
       </c>
       <c r="K40" s="19">
-        <v>13.916667</v>
+        <v>25.146631</v>
       </c>
       <c r="L40" s="19">
-        <v>-42.84731</v>
+        <v>15.838706</v>
       </c>
       <c r="M40" s="20">
-        <v>0</v>
+        <v>-2.40027</v>
       </c>
       <c r="N40" s="20">
-        <v>0.012</v>
+        <v>1.093</v>
       </c>
       <c r="O40" s="20">
-        <v>0.02337438150707416</v>
+        <v>0.4123190762901587</v>
       </c>
       <c r="P40" s="11">
-        <v>53.68264010487369</v>
+        <v>58.53148586909911</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -4589,46 +4711,46 @@
         <v>138</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E41" s="10">
-        <v>399.5899963378906</v>
+        <v>129.5200042724609</v>
       </c>
       <c r="F41" s="16">
-        <v>0.3883284131297825</v>
+        <v>0.4067796261324325</v>
       </c>
       <c r="G41" s="19">
-        <v>-0.06528790904325747</v>
+        <v>0.5566183474132383</v>
       </c>
       <c r="H41" s="19">
-        <v>0.8737030999799198</v>
+        <v>0.07245981733422238</v>
       </c>
       <c r="I41" s="19">
-        <v>-0.2504338946614285</v>
+        <v>0.895181571692572</v>
       </c>
       <c r="J41" s="19">
-        <v>0.7568469834899803</v>
+        <v>0.2913397727367323</v>
       </c>
       <c r="K41" s="19">
-        <v>30.666668</v>
+        <v>17.827541</v>
       </c>
       <c r="L41" s="19">
-        <v>5.5863585</v>
+        <v>2.451422</v>
       </c>
       <c r="M41" s="20">
-        <v>0.1983</v>
+        <v>0.1418</v>
       </c>
       <c r="N41" s="20">
-        <v>0.109</v>
+        <v>0.355</v>
       </c>
       <c r="O41" s="20">
-        <v>0.4345360396672657</v>
+        <v>0.1865659603187428</v>
       </c>
       <c r="P41" s="11">
-        <v>50.84487606833143</v>
+        <v>60.65175981935444</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -4642,46 +4764,46 @@
         <v>140</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E42" s="10">
-        <v>252.8000030517578</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="F42" s="16">
-        <v>0.3857896599288244</v>
+        <v>0.405545318087071</v>
       </c>
       <c r="G42" s="19">
-        <v>0.3891253641163208</v>
+        <v>0.5078777743715293</v>
       </c>
       <c r="H42" s="19">
-        <v>-0.4238837218824341</v>
+        <v>1.335916108729087</v>
       </c>
       <c r="I42" s="19">
-        <v>0.4794929837705694</v>
+        <v>-0.5911526511284643</v>
       </c>
       <c r="J42" s="19">
-        <v>1.010330111996504</v>
+        <v>0.0262528542087006</v>
       </c>
       <c r="K42" s="19">
-        <v>19.462212</v>
+        <v>13.916667</v>
       </c>
       <c r="L42" s="19">
-        <v>2.5104156</v>
+        <v>-42.84731</v>
       </c>
       <c r="M42" s="20">
-        <v>0.14548999</v>
+        <v>0</v>
       </c>
       <c r="N42" s="20">
-        <v>0.23</v>
+        <v>0.012</v>
       </c>
       <c r="O42" s="20">
-        <v>0.4490836596377112</v>
+        <v>0.005223064261166366</v>
       </c>
       <c r="P42" s="11">
-        <v>48.45690543816092</v>
+        <v>48.58037047936657</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -4689,52 +4811,52 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="E43" s="10">
-        <v>846.3699951171875</v>
+        <v>94.18000030517578</v>
       </c>
       <c r="F43" s="16">
-        <v>0.3834396304433089</v>
+        <v>0.3945829162829916</v>
       </c>
       <c r="G43" s="19">
-        <v>-2.83988005355446</v>
+        <v>0.1183002349970005</v>
       </c>
       <c r="H43" s="19">
-        <v>1.447127732336587</v>
+        <v>1.28042265176903</v>
       </c>
       <c r="I43" s="19">
-        <v>1.459563130529552</v>
+        <v>0.1172707560089546</v>
       </c>
       <c r="J43" s="19">
-        <v>2.182290812820225</v>
+        <v>0.07132189813430242</v>
       </c>
       <c r="K43" s="19">
-        <v>3311.0417</v>
+        <v>16.65096</v>
       </c>
       <c r="L43" s="19">
-        <v>162.83812</v>
+        <v>19.112581</v>
       </c>
       <c r="M43" s="20">
-        <v>3.7152898</v>
+        <v>1.5956</v>
       </c>
       <c r="N43" s="20">
-        <v>0.485</v>
+        <v>0.162</v>
       </c>
       <c r="O43" s="20">
-        <v>1.011262083482543</v>
+        <v>-0.04679354711075856</v>
       </c>
       <c r="P43" s="11">
-        <v>48.77584128037775</v>
+        <v>55.82354889079078</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -4742,19 +4864,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E44" s="10">
-        <v>359.8399963378906</v>
+        <v>361.1099853515625</v>
       </c>
       <c r="F44" s="16">
-        <v>0.3806909903718734</v>
+        <v>0.3907741504182024</v>
       </c>
       <c r="G44" s="19">
         <v>0.1745054589838901</v>
@@ -4766,7 +4888,7 @@
         <v>0.5362618455560154</v>
       </c>
       <c r="J44" s="19">
-        <v>0.9944485611704985</v>
+        <v>1.028059094658262</v>
       </c>
       <c r="K44" s="19">
         <v>33.79535</v>
@@ -4781,13 +4903,13 @@
         <v>0.204</v>
       </c>
       <c r="O44" s="20">
-        <v>0.505543720380274</v>
+        <v>0.5364421019746508</v>
       </c>
       <c r="P44" s="11">
-        <v>62.23183759161277</v>
+        <v>62.79277933616031</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4853,77 +4975,77 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B6" s="20">
         <v>0.3</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B7" s="20">
         <v>0.25</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B8" s="20">
         <v>0.15</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B9" s="20">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B10" s="20">
         <f>SUM(B6:B9)</f>
@@ -4932,22 +5054,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -5026,171 +5148,171 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -5208,7 +5330,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI2"/>
+  <dimension ref="A1:BI3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -5216,184 +5338,184 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>434.5918579101562</v>
+        <v>420.3853149414062</v>
       </c>
       <c r="C1">
-        <v>420.3853149414062</v>
+        <v>421.3537292480469</v>
       </c>
       <c r="D1">
-        <v>421.3537292480469</v>
+        <v>393.7393798828125</v>
       </c>
       <c r="E1">
-        <v>393.7393798828125</v>
+        <v>400.1088256835938</v>
       </c>
       <c r="F1">
-        <v>400.1088256835938</v>
+        <v>381.1501770019531</v>
       </c>
       <c r="G1">
-        <v>381.1501770019531</v>
+        <v>369.2198791503906</v>
       </c>
       <c r="H1">
-        <v>369.2198791503906</v>
+        <v>390.8042297363281</v>
       </c>
       <c r="I1">
-        <v>390.8042297363281</v>
+        <v>394.9174194335938</v>
       </c>
       <c r="J1">
-        <v>394.9174194335938</v>
+        <v>408.3951416015625</v>
       </c>
       <c r="K1">
-        <v>408.3951416015625</v>
+        <v>403.4133605957031</v>
       </c>
       <c r="L1">
-        <v>403.4133605957031</v>
+        <v>418.6282348632812</v>
       </c>
       <c r="M1">
-        <v>418.6282348632812</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="N1">
-        <v>408.8244323730469</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="O1">
-        <v>418.0192260742188</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="P1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="Q1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="R1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="S1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="T1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="U1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="V1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="W1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="X1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="Y1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="Z1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="AA1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="AB1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="AC1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="AD1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="AE1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="AF1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="AG1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="AH1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="AI1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="AJ1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="AK1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="AL1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AM1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AN1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AO1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AP1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AQ1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AR1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AS1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AT1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AU1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AV1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AW1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AX1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AY1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AZ1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="BA1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="BB1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="BC1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="BD1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="BE1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="BF1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="BG1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="BH1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="BI1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
     </row>
     <row r="2" spans="1:61">
@@ -5401,184 +5523,369 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1063.936279296875</v>
+        <v>1079.403930664062</v>
       </c>
       <c r="C2">
-        <v>1079.403930664062</v>
+        <v>995.8468627929688</v>
       </c>
       <c r="D2">
-        <v>995.8468627929688</v>
+        <v>863.8771362304688</v>
       </c>
       <c r="E2">
-        <v>863.8771362304688</v>
+        <v>949.134033203125</v>
       </c>
       <c r="F2">
-        <v>949.134033203125</v>
+        <v>935.74609375</v>
       </c>
       <c r="G2">
-        <v>935.74609375</v>
+        <v>891.7428588867188</v>
       </c>
       <c r="H2">
-        <v>891.7428588867188</v>
+        <v>995.7168579101562</v>
       </c>
       <c r="I2">
-        <v>995.7168579101562</v>
+        <v>981.4590454101562</v>
       </c>
       <c r="J2">
-        <v>981.4590454101562</v>
+        <v>1087.822631835938</v>
       </c>
       <c r="K2">
-        <v>1087.822631835938</v>
+        <v>1020.60302734375</v>
       </c>
       <c r="L2">
-        <v>1020.60302734375</v>
+        <v>1043.029541015625</v>
       </c>
       <c r="M2">
-        <v>1043.029541015625</v>
+        <v>1133.815551757812</v>
       </c>
       <c r="N2">
-        <v>1133.815551757812</v>
+        <v>1211.193725585938</v>
       </c>
       <c r="O2">
-        <v>1211.193725585938</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="P2">
-        <v>1051.608276367188</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="Q2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="R2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="S2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="T2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="U2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="V2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="W2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="X2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="Y2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="Z2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="AA2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="AB2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="AC2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="AD2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="AE2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="AF2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="AG2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="AH2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="AI2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="AJ2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="AK2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="AL2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="AM2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AN2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="AO2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AP2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AQ2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AR2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AS2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AT2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AU2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AV2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AW2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AX2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AY2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AZ2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="BA2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="BB2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="BC2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="BD2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="BE2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="BF2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="BG2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="BH2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="BI2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:61">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1831.5</v>
+      </c>
+      <c r="C3">
+        <v>1759.680053710938</v>
+      </c>
+      <c r="D3">
+        <v>1559.319946289062</v>
+      </c>
+      <c r="E3">
+        <v>1642</v>
+      </c>
+      <c r="F3">
+        <v>1646.5400390625</v>
+      </c>
+      <c r="G3">
+        <v>1643.22998046875</v>
+      </c>
+      <c r="H3">
+        <v>1881.510009765625</v>
+      </c>
+      <c r="I3">
+        <v>1980.099975585938</v>
+      </c>
+      <c r="J3">
+        <v>2107.860107421875</v>
+      </c>
+      <c r="K3">
+        <v>1991.550048828125</v>
+      </c>
+      <c r="L3">
+        <v>1958.800048828125</v>
+      </c>
+      <c r="M3">
+        <v>2184.75</v>
+      </c>
+      <c r="N3">
+        <v>2273.72998046875</v>
+      </c>
+      <c r="O3">
+        <v>1963.599975585938</v>
+      </c>
+      <c r="P3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="Q3">
+        <v>2335</v>
+      </c>
+      <c r="R3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="S3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="T3">
+        <v>2273.72998046875</v>
+      </c>
+      <c r="U3">
+        <v>2032.219970703125</v>
+      </c>
+      <c r="V3">
+        <v>1745</v>
+      </c>
+      <c r="W3">
+        <v>1744.430053710938</v>
+      </c>
+      <c r="X3">
+        <v>1617.699951171875</v>
+      </c>
+      <c r="Y3">
+        <v>1727.180053710938</v>
+      </c>
+      <c r="Z3">
+        <v>1858.27001953125</v>
+      </c>
+      <c r="AA3">
+        <v>1915.920043945312</v>
+      </c>
+      <c r="AB3">
+        <v>1673.969970703125</v>
+      </c>
+      <c r="AC3">
+        <v>1757.819946289062</v>
+      </c>
+      <c r="AD3">
+        <v>1615</v>
+      </c>
+      <c r="AE3">
+        <v>1411.079956054688</v>
+      </c>
+      <c r="AF3">
+        <v>1354.819946289062</v>
+      </c>
+      <c r="AG3">
+        <v>1390.949951171875</v>
+      </c>
+      <c r="AH3">
+        <v>1589.400024414062</v>
+      </c>
+      <c r="AI3">
+        <v>1599.27001953125</v>
+      </c>
+      <c r="AJ3">
+        <v>1610.329956054688</v>
+      </c>
+      <c r="AK3">
+        <v>1436.56005859375</v>
+      </c>
+      <c r="AL3">
+        <v>1278.22998046875</v>
+      </c>
+      <c r="AM3">
+        <v>1096.099975585938</v>
+      </c>
+      <c r="AN3">
+        <v>1015.890014648438</v>
+      </c>
+      <c r="AO3">
+        <v>1279.9599609375</v>
+      </c>
+      <c r="AP3">
+        <v>1214.829956054688</v>
+      </c>
+      <c r="AQ3">
+        <v>1288.030029296875</v>
+      </c>
+      <c r="AR3">
+        <v>1427.619995117188</v>
+      </c>
+      <c r="AS3">
+        <v>1350.5</v>
+      </c>
+      <c r="AT3">
+        <v>1258.579956054688</v>
+      </c>
+      <c r="AU3">
+        <v>1212.2099609375</v>
+      </c>
+      <c r="AV3">
+        <v>1237.920043945312</v>
+      </c>
+      <c r="AW3">
+        <v>1271.050048828125</v>
+      </c>
+      <c r="AX3">
+        <v>1344.2900390625</v>
+      </c>
+      <c r="AY3">
+        <v>1528.109985351562</v>
+      </c>
+      <c r="AZ3">
+        <v>1641.109985351562</v>
+      </c>
+      <c r="BA3">
+        <v>1786.849975585938</v>
+      </c>
+      <c r="BB3">
+        <v>1625.780029296875</v>
+      </c>
+      <c r="BC3">
+        <v>1568.869995117188</v>
+      </c>
+      <c r="BD3">
+        <v>1600.619995117188</v>
+      </c>
+      <c r="BE3">
+        <v>1596.079956054688</v>
+      </c>
+      <c r="BF3">
+        <v>1493.119995117188</v>
+      </c>
+      <c r="BG3">
+        <v>1480.77001953125</v>
+      </c>
+      <c r="BH3">
+        <v>1499.369995117188</v>
+      </c>
+      <c r="BI3">
+        <v>1484.949951171875</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -17,7 +17,7 @@
     <sheet name="_данные" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$Q$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="226">
   <si>
     <t>DELL</t>
   </si>
@@ -36,6 +36,9 @@
     <t>SNDK</t>
   </si>
   <si>
+    <t>WDC</t>
+  </si>
+  <si>
     <t>Открытые позиции</t>
   </si>
   <si>
@@ -114,6 +117,12 @@
     <t>2026-08-27</t>
   </si>
   <si>
+    <t>Western Digital</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
     <t>Итого</t>
   </si>
   <si>
@@ -222,12 +231,6 @@
     <t>проходит</t>
   </si>
   <si>
-    <t>WDC</t>
-  </si>
-  <si>
-    <t>Western Digital</t>
-  </si>
-  <si>
     <t>VLO</t>
   </si>
   <si>
@@ -255,34 +258,49 @@
     <t>Hewlett Packard Enterprise</t>
   </si>
   <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>Expedia Group</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>EOG Resources</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
     <t>NTAP</t>
   </si>
   <si>
     <t>NetApp</t>
   </si>
   <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>Expedia Group</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>EOG Resources</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
-    <t>Financials</t>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>APA Corporation</t>
   </si>
   <si>
     <t>TER</t>
@@ -291,19 +309,16 @@
     <t>Teradyne</t>
   </si>
   <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>APA Corporation</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>Health Care</t>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>Humana</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>Nvidia</t>
   </si>
   <si>
     <t>PSX</t>
@@ -312,22 +327,49 @@
     <t>Phillips 66</t>
   </si>
   <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
     <t>FANG</t>
   </si>
   <si>
     <t>Diamondback Energy</t>
   </si>
   <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class A)</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class C)</t>
   </si>
   <si>
     <t>CNC</t>
@@ -336,30 +378,6 @@
     <t>Centene Corporation</t>
   </si>
   <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
-  </si>
-  <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>Nvidia</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
-  </si>
-  <si>
     <t>CF</t>
   </si>
   <si>
@@ -369,102 +387,90 @@
     <t>Materials</t>
   </si>
   <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>Booking Holdings</t>
+  </si>
+  <si>
     <t>SCHW</t>
   </si>
   <si>
     <t>Charles Schwab Corporation</t>
   </si>
   <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class A)</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>Booking Holdings</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class C)</t>
-  </si>
-  <si>
     <t>CINF</t>
   </si>
   <si>
     <t>Cincinnati Financial</t>
   </si>
   <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
+  </si>
+  <si>
+    <t>DVN</t>
+  </si>
+  <si>
+    <t>Devon Energy</t>
+  </si>
+  <si>
+    <t>RJF</t>
+  </si>
+  <si>
+    <t>Raymond James Financial</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>Altria</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>Lumentum</t>
+  </si>
+  <si>
+    <t>SWK</t>
+  </si>
+  <si>
+    <t>Stanley Black &amp; Decker</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
     <t>TROW</t>
   </si>
   <si>
     <t>T. Rowe Price</t>
   </si>
   <si>
-    <t>RJF</t>
-  </si>
-  <si>
-    <t>Raymond James Financial</t>
-  </si>
-  <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>DVN</t>
-  </si>
-  <si>
-    <t>Devon Energy</t>
-  </si>
-  <si>
-    <t>LITE</t>
-  </si>
-  <si>
-    <t>Lumentum</t>
-  </si>
-  <si>
     <t>COP</t>
   </si>
   <si>
     <t>ConocoPhillips</t>
   </si>
   <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>Altria</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>HAS</t>
-  </si>
-  <si>
-    <t>Hasbro</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -525,7 +531,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-08-28 06:10 UTC · данные на 2026-08-27 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-08-29 03:44 UTC · данные на 2026-08-28 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -606,7 +612,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-08-28 06:10 UTC</t>
+    <t>2026-08-29 03:44 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -748,14 +754,14 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color rgb="FF0F9960"/>
+      <color rgb="FFD64545"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
-      <color rgb="FFD64545"/>
+      <color rgb="FF0F9960"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1002,7 +1008,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1446.31</c:v>
+                  <c:v>1901.58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1091,9 +1097,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$8</c:f>
+              <c:f>Капитал!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1106,15 +1112,18 @@
                 <c:pt idx="3">
                   <c:v>2026-08-27</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>2026-08-28</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$8</c:f>
+              <c:f>Капитал!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1126,6 +1135,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10015.949999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9994.27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1150,9 +1162,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$8</c:f>
+              <c:f>Капитал!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1165,15 +1177,18 @@
                 <c:pt idx="3">
                   <c:v>2026-08-27</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>2026-08-28</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$8</c:f>
+              <c:f>Капитал!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1185,6 +1200,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10099.94</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10077.02</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1324,9 +1342,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$8</c:f>
+              <c:f>Капитал!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1339,15 +1357,18 @@
                 <c:pt idx="3">
                   <c:v>2026-08-27</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>2026-08-28</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$8</c:f>
+              <c:f>Капитал!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1359,6 +1380,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10015.949999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9994.27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1383,9 +1407,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$8</c:f>
+              <c:f>Капитал!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1398,15 +1422,18 @@
                 <c:pt idx="3">
                   <c:v>2026-08-27</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>2026-08-28</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$8</c:f>
+              <c:f>Капитал!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1418,6 +1445,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10099.94</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10077.02</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1912,102 +1942,102 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="4">
-        <v>10015.95</v>
+        <v>9994.27</v>
       </c>
       <c r="D6" s="5">
-        <v>0.001594999999999791</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.009994000000000058</v>
-      </c>
-      <c r="H6" s="6">
-        <v>-0.001254421136497541</v>
+        <v>-0.0005729999999999347</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.007702000000000098</v>
+      </c>
+      <c r="H6" s="5">
+        <v>-0.003416253428967231</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H9" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C13" s="10">
-        <v>8569.639999999999</v>
+        <v>8092.69</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C14" s="10">
-        <v>1446.31</v>
+        <v>1901.58</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C15" s="10">
-        <v>10015.95</v>
+        <v>9994.27</v>
       </c>
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -2015,7 +2045,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -2023,15 +2053,15 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C18" s="11">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C19" s="11">
         <v>1</v>
@@ -2039,7 +2069,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -2047,85 +2077,85 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C26" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
-        <v>10015.949999999999</v>
+        <v>9994.27</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C33" s="10">
-        <v>1446.31</v>
+        <v>1901.58</v>
       </c>
     </row>
   </sheetData>
@@ -2136,7 +2166,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -2156,62 +2186,62 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -2219,13 +2249,13 @@
         <v>0</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="10">
         <v>443.1115</v>
@@ -2237,32 +2267,32 @@
         <v>476.19</v>
       </c>
       <c r="H5" s="17">
-        <v>472.26</v>
+        <v>456.24</v>
       </c>
       <c r="I5" s="10">
         <f>F5*H5</f>
-        <v>507.51468126</v>
+        <v>490.29877224</v>
       </c>
       <c r="J5" s="10">
         <f>I5-G5</f>
-        <v>31.324681259999977</v>
+        <v>14.108772240000008</v>
       </c>
       <c r="K5" s="18">
         <f>IFERROR(J5/G5,0)</f>
-        <v>0.06578189642789638</v>
+        <v>0.029628451332451348</v>
       </c>
       <c r="L5" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N5" s="19">
         <v>2.927623067210654</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -2270,13 +2300,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="10">
         <v>926.2029</v>
@@ -2288,32 +2318,32 @@
         <v>476.62</v>
       </c>
       <c r="H6" s="17">
-        <v>935.39</v>
+        <v>932.86</v>
       </c>
       <c r="I6" s="10">
         <f>F6*H6</f>
-        <v>481.34795244000003</v>
+        <v>480.04602456000003</v>
       </c>
       <c r="J6" s="10">
         <f>I6-G6</f>
-        <v>4.727952440000024</v>
+        <v>3.4260245600000303</v>
       </c>
       <c r="K6" s="18">
         <f>IFERROR(J6/G6,0)</f>
-        <v>0.00991975250723852</v>
+        <v>0.007188167848600626</v>
       </c>
       <c r="L6" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N6" s="19">
         <v>1.809956883354321</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -2321,13 +2351,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="10">
         <v>1550.1948</v>
@@ -2339,58 +2369,109 @@
         <v>477.55</v>
       </c>
       <c r="H7" s="17">
-        <v>1484.95</v>
+        <v>1484.98</v>
       </c>
       <c r="I7" s="10">
         <f>F7*H7</f>
-        <v>457.4507271</v>
+        <v>457.45996884</v>
       </c>
       <c r="J7" s="10">
         <f>I7-G7</f>
-        <v>-20.099272900000017</v>
+        <v>-20.090031160000024</v>
       </c>
       <c r="K7" s="18">
         <f>IFERROR(J7/G7,0)</f>
-        <v>-0.042088310962202946</v>
+        <v>-0.04206895855931321</v>
       </c>
       <c r="L7" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="11">
         <f>MAX(0,21-L7)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N7" s="19">
         <v>1.655247920227722</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F8" s="12" t="s">
-        <v>29</v>
+      <c r="A8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="10">
+        <v>462.5311</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1.031174</v>
       </c>
       <c r="G8" s="10">
-        <f>SUM(G5:G7)</f>
-        <v>1430.36</v>
+        <v>476.95</v>
+      </c>
+      <c r="H8" s="17">
+        <v>459.45</v>
       </c>
       <c r="I8" s="10">
-        <f>SUM(I5:I7)</f>
-        <v>1446.31</v>
+        <f>F8*H8</f>
+        <v>473.7728943</v>
       </c>
       <c r="J8" s="10">
-        <f>SUM(J5:J7)</f>
-        <v>15.949999999999989</v>
+        <f>I8-G8</f>
+        <v>-3.17710569999997</v>
       </c>
       <c r="K8" s="18">
         <f>IFERROR(J8/G8,0)</f>
+        <v>-0.006661297200964399</v>
+      </c>
+      <c r="L8" s="11">
         <v>0</v>
       </c>
+      <c r="M8" s="11">
+        <f>MAX(0,21-L8)</f>
+        <v>21</v>
+      </c>
+      <c r="N8" s="19">
+        <v>1.135451734784544</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="10">
+        <f>SUM(G5:G8)</f>
+        <v>1907.31</v>
+      </c>
+      <c r="I9" s="10">
+        <f>SUM(I5:I8)</f>
+        <v>1901.58</v>
+      </c>
+      <c r="J9" s="10">
+        <f>SUM(J5:J8)</f>
+        <v>-5.730000000000018</v>
+      </c>
+      <c r="K9" s="18">
+        <f>IFERROR(J9/G9,0)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P7"/>
-  <conditionalFormatting sqref="K5:K7">
+  <autoFilter ref="A4:P8"/>
+  <conditionalFormatting sqref="K5:K8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -2402,7 +2483,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M7">
+  <conditionalFormatting sqref="M5:M8">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -2431,12 +2512,28 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M5:M7</xm:sqref>
+          <xm:sqref>M5:M8</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
+          <x14:colorSeries rgb="FF0B5FFF"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'_данные'!B4:BI4</xm:f>
+              <xm:sqref>P8</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
           <x14:colorSeries rgb="FF0B5FFF"/>
           <x14:colorNegative theme="5"/>
@@ -2513,64 +2610,64 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2580,7 +2677,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2592,37 +2689,37 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B5" s="10">
         <v>10000</v>
@@ -2643,7 +2740,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="10">
         <v>9523.809999999999</v>
@@ -2664,7 +2761,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="10">
         <v>9047.190000000001</v>
@@ -2685,7 +2782,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="10">
         <v>8569.639999999999</v>
@@ -2702,6 +2799,27 @@
       </c>
       <c r="F8" s="10">
         <v>10099.94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="10">
+        <v>8092.69</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1901.58</v>
+      </c>
+      <c r="D9" s="10">
+        <f>B9+C9</f>
+        <v>9994.27</v>
+      </c>
+      <c r="E9" s="11">
+        <v>4</v>
+      </c>
+      <c r="F9" s="10">
+        <v>10077.02</v>
       </c>
     </row>
   </sheetData>
@@ -2731,65 +2849,65 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2800,16 +2918,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="10">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="F5" s="16">
-        <v>1.792182778434668</v>
+        <v>1.797784415791333</v>
       </c>
       <c r="G5" s="19">
         <v>0.1411051627135557</v>
@@ -2821,7 +2939,7 @@
         <v>4.206596031118561</v>
       </c>
       <c r="J5" s="19">
-        <v>2.329613999562457</v>
+        <v>2.348286124084672</v>
       </c>
       <c r="K5" s="19">
         <v>20.560751</v>
@@ -2836,13 +2954,13 @@
         <v>3.457</v>
       </c>
       <c r="O5" s="20">
-        <v>1.252206383903782</v>
+        <v>1.263490084887664</v>
       </c>
       <c r="P5" s="11">
-        <v>50.99361135450471</v>
+        <v>50.68513863125375</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2853,16 +2971,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="10">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="F6" s="16">
-        <v>1.643319592321297</v>
+        <v>1.654426275754993</v>
       </c>
       <c r="G6" s="19">
         <v>-0.297947721659126</v>
@@ -2874,7 +2992,7 @@
         <v>4.026096567149331</v>
       </c>
       <c r="J6" s="19">
-        <v>2.196913786128287</v>
+        <v>2.233936064240608</v>
       </c>
       <c r="K6" s="19">
         <v>20.248442</v>
@@ -2889,13 +3007,13 @@
         <v>3.716</v>
       </c>
       <c r="O6" s="20">
-        <v>1.277879882742097</v>
+        <v>1.337226162656543</v>
       </c>
       <c r="P6" s="11">
-        <v>49.32206344808555</v>
+        <v>49.32350741998839</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -2903,19 +3021,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="10">
-        <v>462</v>
+        <v>459.4500122070312</v>
       </c>
       <c r="F7" s="16">
-        <v>1.135451734784544</v>
+        <v>1.15931561725163</v>
       </c>
       <c r="G7" s="19">
         <v>-0.6552990140462744</v>
@@ -2927,7 +3045,7 @@
         <v>3.032907322180939</v>
       </c>
       <c r="J7" s="19">
-        <v>1.32498442516627</v>
+        <v>1.404530700056557</v>
       </c>
       <c r="K7" s="19">
         <v>17.067032</v>
@@ -2942,13 +3060,13 @@
         <v>0.438</v>
       </c>
       <c r="O7" s="20">
-        <v>0.6380571425850909</v>
+        <v>0.6438674367834341</v>
       </c>
       <c r="P7" s="11">
-        <v>45.58972604624896</v>
+        <v>45.19088940689799</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2956,19 +3074,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E8" s="10">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="F8" s="16">
-        <v>1.125501889714689</v>
+        <v>1.098454348098604</v>
       </c>
       <c r="G8" s="19">
         <v>0.72925464828006</v>
@@ -2980,7 +3098,7 @@
         <v>2.983550662811328</v>
       </c>
       <c r="J8" s="19">
-        <v>1.784703128603905</v>
+        <v>1.694544656550286</v>
       </c>
       <c r="K8" s="19">
         <v>14.4347105</v>
@@ -2995,13 +3113,13 @@
         <v>0.517</v>
       </c>
       <c r="O8" s="20">
-        <v>0.7154056556878978</v>
+        <v>0.7367197024957652</v>
       </c>
       <c r="P8" s="11">
-        <v>65.34446117965095</v>
+        <v>68.0131238164806</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -3009,19 +3127,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="E9" s="10">
-        <v>363.5400085449219</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="F9" s="16">
-        <v>0.9871242374955183</v>
+        <v>0.9607631975098783</v>
       </c>
       <c r="G9" s="19">
         <v>0.7230916879797831</v>
@@ -3033,7 +3151,7 @@
         <v>2.543797486452658</v>
       </c>
       <c r="J9" s="19">
-        <v>1.616998269656583</v>
+        <v>1.529128136371116</v>
       </c>
       <c r="K9" s="19">
         <v>12.56133</v>
@@ -3048,13 +3166,13 @@
         <v>0.537</v>
       </c>
       <c r="O9" s="20">
-        <v>0.8198968817491941</v>
+        <v>0.8730204731174731</v>
       </c>
       <c r="P9" s="11">
-        <v>69.53991697169518</v>
+        <v>71.60800539523845</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3062,19 +3180,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E10" s="10">
-        <v>59.16999816894531</v>
+        <v>59.09999847412109</v>
       </c>
       <c r="F10" s="16">
-        <v>0.921994895113415</v>
+        <v>0.9233041122157448</v>
       </c>
       <c r="G10" s="19">
         <v>0.6355114639003794</v>
@@ -3086,7 +3204,7 @@
         <v>3.304463564487919</v>
       </c>
       <c r="J10" s="19">
-        <v>0.2656285626633613</v>
+        <v>0.2699926196711274</v>
       </c>
       <c r="K10" s="19">
         <v>18.105423</v>
@@ -3101,13 +3219,13 @@
         <v>0.534</v>
       </c>
       <c r="O10" s="20">
-        <v>0.1612977225370922</v>
+        <v>0.1238674065532424</v>
       </c>
       <c r="P10" s="11">
-        <v>55.7832783396745</v>
+        <v>55.45107029702634</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -3115,19 +3233,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" s="10">
-        <v>54.40999984741211</v>
+        <v>52.31000137329102</v>
       </c>
       <c r="F11" s="16">
-        <v>0.8899117460781116</v>
+        <v>0.858013206260223</v>
       </c>
       <c r="G11" s="19">
         <v>0.304959259686968</v>
@@ -3139,7 +3257,7 @@
         <v>1.463737124114395</v>
       </c>
       <c r="J11" s="19">
-        <v>2.433375832967779</v>
+        <v>2.32704736690815</v>
       </c>
       <c r="K11" s="19">
         <v>48.999996</v>
@@ -3154,13 +3272,13 @@
         <v>0.4</v>
       </c>
       <c r="O11" s="20">
-        <v>1.635367091591919</v>
+        <v>1.459307704875608</v>
       </c>
       <c r="P11" s="11">
-        <v>55.35662305230287</v>
+        <v>49.42839765492122</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -3168,52 +3286,52 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E12" s="10">
-        <v>190.6399993896484</v>
+        <v>329.4400024414062</v>
       </c>
       <c r="F12" s="16">
-        <v>0.7770642919120128</v>
+        <v>0.740994503335056</v>
       </c>
       <c r="G12" s="19">
-        <v>-0.4056392750220561</v>
+        <v>-0.1074817459894137</v>
       </c>
       <c r="H12" s="19">
-        <v>1.27195723742807</v>
+        <v>1.241839716939916</v>
       </c>
       <c r="I12" s="19">
-        <v>-0.1487202202604564</v>
+        <v>0.6713684345102916</v>
       </c>
       <c r="J12" s="19">
-        <v>2.010249327002269</v>
+        <v>1.206912775734525</v>
       </c>
       <c r="K12" s="19">
-        <v>30.285252</v>
+        <v>20.24627</v>
       </c>
       <c r="L12" s="19">
-        <v>27.10866</v>
+        <v>33.66005</v>
       </c>
       <c r="M12" s="20">
-        <v>1.06734</v>
+        <v>0.89489</v>
       </c>
       <c r="N12" s="20">
-        <v>0.125</v>
+        <v>0.14</v>
       </c>
       <c r="O12" s="20">
-        <v>0.9386570571081279</v>
+        <v>0.5361519933949572</v>
       </c>
       <c r="P12" s="11">
-        <v>53.49603815967414</v>
+        <v>59.81470138462173</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -3221,52 +3339,52 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E13" s="10">
-        <v>472.260009765625</v>
+        <v>143.3500061035156</v>
       </c>
       <c r="F13" s="16">
-        <v>0.7583750209260459</v>
+        <v>0.7070619988846399</v>
       </c>
       <c r="G13" s="19">
-        <v>-1.276312485328304</v>
+        <v>0.6102249595302855</v>
       </c>
       <c r="H13" s="19">
-        <v>-0.5342797424893034</v>
+        <v>0.5715130155458599</v>
       </c>
       <c r="I13" s="19">
-        <v>3.12929742928239</v>
+        <v>1.562733350737734</v>
       </c>
       <c r="J13" s="19">
-        <v>2.684813625848348</v>
+        <v>0.4890208484280976</v>
       </c>
       <c r="K13" s="19">
-        <v>884.0612</v>
+        <v>11.680406</v>
       </c>
       <c r="L13" s="19">
-        <v>-200.27277</v>
+        <v>2.5993288</v>
       </c>
       <c r="M13" s="20">
-        <v>0</v>
+        <v>0.22507</v>
       </c>
       <c r="N13" s="20">
-        <v>0.875</v>
+        <v>0.587</v>
       </c>
       <c r="O13" s="20">
-        <v>2.906991234841489</v>
+        <v>0.1729137741789912</v>
       </c>
       <c r="P13" s="11">
-        <v>56.93753717145069</v>
+        <v>48.72434899378244</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -3274,52 +3392,52 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E14" s="10">
-        <v>318.9200134277344</v>
+        <v>260.5799865722656</v>
       </c>
       <c r="F14" s="16">
-        <v>0.754351829711011</v>
+        <v>0.6998691224905804</v>
       </c>
       <c r="G14" s="19">
-        <v>-0.1074817459894137</v>
+        <v>1.158776322034968</v>
       </c>
       <c r="H14" s="19">
-        <v>1.241839716939916</v>
+        <v>0.3596891130938242</v>
       </c>
       <c r="I14" s="19">
-        <v>0.6713684345102916</v>
+        <v>0.009309850889890559</v>
       </c>
       <c r="J14" s="19">
-        <v>1.251437196987708</v>
+        <v>0.8697248999105011</v>
       </c>
       <c r="K14" s="19">
-        <v>20.24627</v>
+        <v>5.083822</v>
       </c>
       <c r="L14" s="19">
-        <v>33.66005</v>
+        <v>2.0850062</v>
       </c>
       <c r="M14" s="20">
-        <v>0.89489</v>
+        <v>0.46113998</v>
       </c>
       <c r="N14" s="20">
-        <v>0.14</v>
+        <v>0.118</v>
       </c>
       <c r="O14" s="20">
-        <v>0.4718131728376875</v>
+        <v>0.2272897563519332</v>
       </c>
       <c r="P14" s="11">
-        <v>54.93271656777372</v>
+        <v>52.43996544752573</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -3327,52 +3445,52 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E15" s="10">
-        <v>144.5</v>
+        <v>124.370002746582</v>
       </c>
       <c r="F15" s="16">
-        <v>0.7222288834556412</v>
+        <v>0.6993848123306926</v>
       </c>
       <c r="G15" s="19">
-        <v>0.6102249595302855</v>
+        <v>0.3568150294101221</v>
       </c>
       <c r="H15" s="19">
-        <v>0.5715130155458599</v>
+        <v>0.8874455070737253</v>
       </c>
       <c r="I15" s="19">
-        <v>1.562733350737734</v>
+        <v>0.6313896241094424</v>
       </c>
       <c r="J15" s="19">
-        <v>0.5395771303314347</v>
+        <v>0.9192349437426943</v>
       </c>
       <c r="K15" s="19">
-        <v>11.680406</v>
+        <v>16.303185</v>
       </c>
       <c r="L15" s="19">
-        <v>2.5993288</v>
+        <v>4.0541053</v>
       </c>
       <c r="M15" s="20">
-        <v>0.22507</v>
+        <v>0.30667</v>
       </c>
       <c r="N15" s="20">
-        <v>0.587</v>
+        <v>0.377</v>
       </c>
       <c r="O15" s="20">
-        <v>0.2111175269545356</v>
+        <v>0.2281031585784812</v>
       </c>
       <c r="P15" s="11">
-        <v>50.60907551652403</v>
+        <v>53.46645670416243</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -3380,52 +3498,52 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="E16" s="10">
-        <v>257.6199951171875</v>
+        <v>456.239990234375</v>
       </c>
       <c r="F16" s="16">
-        <v>0.7052476116904165</v>
+        <v>0.6881500402588745</v>
       </c>
       <c r="G16" s="19">
-        <v>1.158776322034968</v>
+        <v>-1.276312485328304</v>
       </c>
       <c r="H16" s="19">
-        <v>0.3596891130938242</v>
+        <v>-0.5342797424893034</v>
       </c>
       <c r="I16" s="19">
-        <v>0.009309850889890559</v>
+        <v>3.12929742928239</v>
       </c>
       <c r="J16" s="19">
-        <v>0.8876531972432877</v>
+        <v>2.450730356957777</v>
       </c>
       <c r="K16" s="19">
-        <v>5.083822</v>
+        <v>884.0612</v>
       </c>
       <c r="L16" s="19">
-        <v>2.0850062</v>
+        <v>-200.27277</v>
       </c>
       <c r="M16" s="20">
-        <v>0.46113998</v>
+        <v>0</v>
       </c>
       <c r="N16" s="20">
-        <v>0.118</v>
+        <v>0.875</v>
       </c>
       <c r="O16" s="20">
-        <v>0.2233858402197189</v>
+        <v>2.095677616236181</v>
       </c>
       <c r="P16" s="11">
-        <v>49.68985095422584</v>
+        <v>52.61314359601702</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -3433,52 +3551,52 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" s="10">
-        <v>372.0599975585938</v>
+        <v>187.0200042724609</v>
       </c>
       <c r="F17" s="16">
-        <v>0.7045980276279548</v>
+        <v>0.6846249323398198</v>
       </c>
       <c r="G17" s="19">
-        <v>-1.08262537420069</v>
+        <v>-0.4056392750220561</v>
       </c>
       <c r="H17" s="19">
-        <v>0.6932659455068273</v>
+        <v>1.27195723742807</v>
       </c>
       <c r="I17" s="19">
-        <v>3.615274867663105</v>
+        <v>-0.1487202202604564</v>
       </c>
       <c r="J17" s="19">
-        <v>1.04592641120663</v>
+        <v>1.702118128428292</v>
       </c>
       <c r="K17" s="19">
-        <v>51.539547</v>
+        <v>30.285252</v>
       </c>
       <c r="L17" s="19">
-        <v>18.169596</v>
+        <v>27.10866</v>
       </c>
       <c r="M17" s="20">
-        <v>0.36465</v>
+        <v>1.06734</v>
       </c>
       <c r="N17" s="20">
-        <v>1.039</v>
+        <v>0.125</v>
       </c>
       <c r="O17" s="20">
-        <v>0.1187271043196065</v>
+        <v>0.9039571069398307</v>
       </c>
       <c r="P17" s="11">
-        <v>48.03608719915346</v>
+        <v>49.64203036326002</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -3486,19 +3604,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E18" s="10">
-        <v>42.38000106811523</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="F18" s="16">
-        <v>0.6992905455405241</v>
+        <v>0.6801183977940611</v>
       </c>
       <c r="G18" s="19">
         <v>0.9986491788407921</v>
@@ -3510,7 +3628,7 @@
         <v>-0.228424555888388</v>
       </c>
       <c r="J18" s="19">
-        <v>0.93864645911617</v>
+        <v>0.8747392999612933</v>
       </c>
       <c r="K18" s="19">
         <v>9.159914000000001</v>
@@ -3525,13 +3643,13 @@
         <v>0.092</v>
       </c>
       <c r="O18" s="20">
-        <v>0.4764243691300467</v>
+        <v>0.4200248016501495</v>
       </c>
       <c r="P18" s="11">
-        <v>61.56592694680431</v>
+        <v>62.08986555933388</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -3539,52 +3657,52 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="E19" s="10">
-        <v>127.7399978637695</v>
+        <v>354.9700012207031</v>
       </c>
       <c r="F19" s="16">
-        <v>0.6455765765733465</v>
+        <v>0.6567454674023766</v>
       </c>
       <c r="G19" s="19">
-        <v>0.3568150294101221</v>
+        <v>-1.08262537420069</v>
       </c>
       <c r="H19" s="19">
-        <v>0.8874455070737253</v>
+        <v>0.6932659455068273</v>
       </c>
       <c r="I19" s="19">
-        <v>0.6313896241094424</v>
+        <v>3.615274867663105</v>
       </c>
       <c r="J19" s="19">
-        <v>0.7398741578848742</v>
+        <v>0.88641787712137</v>
       </c>
       <c r="K19" s="19">
-        <v>16.303185</v>
+        <v>51.539547</v>
       </c>
       <c r="L19" s="19">
-        <v>4.0541053</v>
+        <v>18.169596</v>
       </c>
       <c r="M19" s="20">
-        <v>0.30667</v>
+        <v>0.36465</v>
       </c>
       <c r="N19" s="20">
-        <v>0.377</v>
+        <v>1.039</v>
       </c>
       <c r="O19" s="20">
-        <v>0.2762513991162128</v>
+        <v>0.109596172161899</v>
       </c>
       <c r="P19" s="11">
-        <v>62.39596004953174</v>
+        <v>43.8201951560922</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -3592,52 +3710,52 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E20" s="10">
-        <v>239.8099975585938</v>
+        <v>385.5400085449219</v>
       </c>
       <c r="F20" s="16">
-        <v>0.6260124248975273</v>
+        <v>0.6437277618065194</v>
       </c>
       <c r="G20" s="19">
-        <v>0.06892234601185927</v>
+        <v>0.4746478020487309</v>
       </c>
       <c r="H20" s="19">
-        <v>-0.54467699511111</v>
+        <v>-0.2835410288834002</v>
       </c>
       <c r="I20" s="19">
-        <v>2.512241193631993</v>
+        <v>0.2562199099090978</v>
       </c>
       <c r="J20" s="19">
-        <v>1.215562636089827</v>
+        <v>1.779285639754618</v>
       </c>
       <c r="K20" s="19">
-        <v>110.99082</v>
+        <v>35.8304</v>
       </c>
       <c r="L20" s="19">
-        <v>3.064414</v>
+        <v>2.4162972</v>
       </c>
       <c r="M20" s="20">
-        <v>0.23452999</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="N20" s="20">
-        <v>0.531</v>
+        <v>0.262</v>
       </c>
       <c r="O20" s="20">
-        <v>0.5927656307260232</v>
+        <v>1.0384818383969</v>
       </c>
       <c r="P20" s="11">
-        <v>67.84167526358479</v>
+        <v>51.92526418841503</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -3645,52 +3763,52 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="E21" s="10">
-        <v>200.5200042724609</v>
+        <v>217.5500030517578</v>
       </c>
       <c r="F21" s="16">
-        <v>0.6111153289321913</v>
+        <v>0.6358914994287772</v>
       </c>
       <c r="G21" s="19">
-        <v>0.561347890123932</v>
+        <v>-1.338461785426528</v>
       </c>
       <c r="H21" s="19">
-        <v>0.0970884411429475</v>
+        <v>2.078256102926562</v>
       </c>
       <c r="I21" s="19">
-        <v>1.717140484071832</v>
+        <v>2.806787311422478</v>
       </c>
       <c r="J21" s="19">
-        <v>0.5362259299950004</v>
+        <v>0.3228263753724115</v>
       </c>
       <c r="K21" s="19">
-        <v>40.156254</v>
+        <v>32.883278</v>
       </c>
       <c r="L21" s="19">
-        <v>1.5220274</v>
+        <v>25.833954</v>
       </c>
       <c r="M21" s="20">
-        <v>0.034930002</v>
+        <v>1.14288</v>
       </c>
       <c r="N21" s="20">
-        <v>0.525</v>
+        <v>0.852</v>
       </c>
       <c r="O21" s="20">
-        <v>0.2213742934098679</v>
+        <v>0.2292755810438503</v>
       </c>
       <c r="P21" s="11">
-        <v>51.15467970531992</v>
+        <v>52.34354093262409</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -3698,52 +3816,52 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E22" s="10">
-        <v>392.6300048828125</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="F22" s="16">
-        <v>0.6075898505250401</v>
+        <v>0.6288678535621901</v>
       </c>
       <c r="G22" s="19">
-        <v>0.4746478020487309</v>
+        <v>0.06892234601185927</v>
       </c>
       <c r="H22" s="19">
-        <v>-0.2835410288834002</v>
+        <v>-0.54467699511111</v>
       </c>
       <c r="I22" s="19">
-        <v>0.2562199099090978</v>
+        <v>2.512241193631993</v>
       </c>
       <c r="J22" s="19">
-        <v>1.658825935483021</v>
+        <v>1.225080731638703</v>
       </c>
       <c r="K22" s="19">
-        <v>35.8304</v>
+        <v>110.99082</v>
       </c>
       <c r="L22" s="19">
-        <v>2.4162972</v>
+        <v>3.064414</v>
       </c>
       <c r="M22" s="20">
-        <v>0.06893000000000001</v>
+        <v>0.23452999</v>
       </c>
       <c r="N22" s="20">
-        <v>0.262</v>
+        <v>0.531</v>
       </c>
       <c r="O22" s="20">
-        <v>1.117192792951127</v>
+        <v>0.6010238221719943</v>
       </c>
       <c r="P22" s="11">
-        <v>57.11940373585679</v>
+        <v>70.54639059914102</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -3751,19 +3869,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E23" s="10">
-        <v>1040.869995117188</v>
+        <v>1033.989990234375</v>
       </c>
       <c r="F23" s="16">
-        <v>0.5991689230794568</v>
+        <v>0.6052692400068327</v>
       </c>
       <c r="G23" s="19">
         <v>0.3556011439311419</v>
@@ -3775,7 +3893,7 @@
         <v>1.024034813371229</v>
       </c>
       <c r="J23" s="19">
-        <v>0.4247378628896332</v>
+        <v>0.4450722526475528</v>
       </c>
       <c r="K23" s="19">
         <v>16.004324</v>
@@ -3790,13 +3908,13 @@
         <v>0.425</v>
       </c>
       <c r="O23" s="20">
-        <v>0.1312802350176108</v>
+        <v>0.2145754282246302</v>
       </c>
       <c r="P23" s="11">
-        <v>49.97657026255024</v>
+        <v>48.31938488621898</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -3804,52 +3922,52 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E24" s="10">
-        <v>65.33000183105469</v>
+        <v>197.6699981689453</v>
       </c>
       <c r="F24" s="16">
-        <v>0.5938607298607032</v>
+        <v>0.5772305002286223</v>
       </c>
       <c r="G24" s="19">
-        <v>1.175622071073703</v>
+        <v>0.561347890123932</v>
       </c>
       <c r="H24" s="19">
-        <v>-0.5327402912596072</v>
+        <v>0.0970884411429475</v>
       </c>
       <c r="I24" s="19">
-        <v>-0.5389901628995794</v>
+        <v>1.717140484071832</v>
       </c>
       <c r="J24" s="19">
-        <v>1.51735901929477</v>
+        <v>0.4232765009831034</v>
       </c>
       <c r="K24" s="19">
-        <v>12.357601</v>
+        <v>40.156254</v>
       </c>
       <c r="L24" s="19">
-        <v>1.4373919</v>
+        <v>1.5220274</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.20358999</v>
+        <v>0.034930002</v>
       </c>
       <c r="N24" s="20">
-        <v>0.046</v>
+        <v>0.525</v>
       </c>
       <c r="O24" s="20">
-        <v>0.5217796731107474</v>
+        <v>0.1549079639743987</v>
       </c>
       <c r="P24" s="11">
-        <v>51.01485882539968</v>
+        <v>47.74849169997778</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -3857,52 +3975,52 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E25" s="10">
-        <v>199.7700042724609</v>
+        <v>214.7700042724609</v>
       </c>
       <c r="F25" s="16">
-        <v>0.5775723685742113</v>
+        <v>0.5735185943482911</v>
       </c>
       <c r="G25" s="19">
-        <v>0.5728138826097362</v>
+        <v>0.3452907642059501</v>
       </c>
       <c r="H25" s="19">
-        <v>-0.06908867602196844</v>
+        <v>0.8001987998031764</v>
       </c>
       <c r="I25" s="19">
-        <v>2.415351960752095</v>
+        <v>0.4732064398512328</v>
       </c>
       <c r="J25" s="19">
-        <v>0.2023252622798944</v>
+        <v>0.6630023305267569</v>
       </c>
       <c r="K25" s="19">
-        <v>19.755836</v>
+        <v>17.306387</v>
       </c>
       <c r="L25" s="19">
-        <v>2.098037</v>
+        <v>3.1574755</v>
       </c>
       <c r="M25" s="20">
-        <v>0.12231</v>
+        <v>0.17969999</v>
       </c>
       <c r="N25" s="20">
-        <v>0.535</v>
+        <v>0.28</v>
       </c>
       <c r="O25" s="20">
-        <v>0.1042524101517361</v>
+        <v>0.303902480553556</v>
       </c>
       <c r="P25" s="11">
-        <v>58.44099069545236</v>
+        <v>50.10351300193571</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -3910,52 +4028,52 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="E26" s="10">
-        <v>369.3299865722656</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="F26" s="16">
-        <v>0.5727255966010276</v>
+        <v>0.5723262248347317</v>
       </c>
       <c r="G26" s="19">
-        <v>1.091200655903261</v>
+        <v>-0.3026541063380147</v>
       </c>
       <c r="H26" s="19">
-        <v>0.1101459112354547</v>
+        <v>1.453871687245511</v>
       </c>
       <c r="I26" s="19">
-        <v>-0.3352804504404189</v>
+        <v>1.455283430456029</v>
       </c>
       <c r="J26" s="19">
-        <v>0.8937366319574954</v>
+        <v>0.27120673452118</v>
       </c>
       <c r="K26" s="19">
-        <v>9.963699999999999</v>
+        <v>17.464125</v>
       </c>
       <c r="L26" s="19">
-        <v>2.3337615</v>
+        <v>6.838651</v>
       </c>
       <c r="M26" s="20">
-        <v>0.26511</v>
+        <v>0.48676</v>
       </c>
       <c r="N26" s="20">
-        <v>0.003</v>
+        <v>0.242</v>
       </c>
       <c r="O26" s="20">
-        <v>0.2154665752855902</v>
+        <v>0.1131675735057152</v>
       </c>
       <c r="P26" s="11">
-        <v>52.57038066221627</v>
+        <v>49.26183990788777</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -3963,52 +4081,52 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="E27" s="10">
-        <v>227.9799957275391</v>
+        <v>369.8999938964844</v>
       </c>
       <c r="F27" s="16">
-        <v>0.56699496670032</v>
+        <v>0.5689147855176091</v>
       </c>
       <c r="G27" s="19">
-        <v>-1.338461785426528</v>
+        <v>1.091200655903261</v>
       </c>
       <c r="H27" s="19">
-        <v>2.078256102926562</v>
+        <v>0.1101459112354547</v>
       </c>
       <c r="I27" s="19">
-        <v>2.806787311422478</v>
+        <v>-0.3352804504404189</v>
       </c>
       <c r="J27" s="19">
-        <v>0.09317126627755401</v>
+        <v>0.8810339283461005</v>
       </c>
       <c r="K27" s="19">
-        <v>32.883278</v>
+        <v>9.963699999999999</v>
       </c>
       <c r="L27" s="19">
-        <v>25.833954</v>
+        <v>2.3337615</v>
       </c>
       <c r="M27" s="20">
-        <v>1.14288</v>
+        <v>0.26511</v>
       </c>
       <c r="N27" s="20">
-        <v>0.852</v>
+        <v>0.003</v>
       </c>
       <c r="O27" s="20">
-        <v>0.2345614306171031</v>
+        <v>0.2078763145036941</v>
       </c>
       <c r="P27" s="11">
-        <v>61.32156943941269</v>
+        <v>53.13232931507415</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -4016,52 +4134,52 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E28" s="10">
-        <v>214.8600006103516</v>
+        <v>201.8600006103516</v>
       </c>
       <c r="F28" s="16">
-        <v>0.5542918117161544</v>
+        <v>0.5606985700814503</v>
       </c>
       <c r="G28" s="19">
-        <v>0.3452907642059501</v>
+        <v>0.5728138826097362</v>
       </c>
       <c r="H28" s="19">
-        <v>0.8001987998031764</v>
+        <v>-0.06908867602196844</v>
       </c>
       <c r="I28" s="19">
-        <v>0.4732064398512328</v>
+        <v>2.415351960752095</v>
       </c>
       <c r="J28" s="19">
-        <v>0.5989130550863011</v>
+        <v>0.1460792673040241</v>
       </c>
       <c r="K28" s="19">
-        <v>17.306387</v>
+        <v>19.755836</v>
       </c>
       <c r="L28" s="19">
-        <v>3.1574755</v>
+        <v>2.098037</v>
       </c>
       <c r="M28" s="20">
-        <v>0.17969999</v>
+        <v>0.12231</v>
       </c>
       <c r="N28" s="20">
-        <v>0.28</v>
+        <v>0.535</v>
       </c>
       <c r="O28" s="20">
-        <v>0.2237520476524988</v>
+        <v>0.1002713356176403</v>
       </c>
       <c r="P28" s="11">
-        <v>50.2319810346368</v>
+        <v>61.45434657924219</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -4069,52 +4187,52 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E29" s="10">
-        <v>125.7099990844727</v>
+        <v>342.8800048828125</v>
       </c>
       <c r="F29" s="16">
-        <v>0.528212307428086</v>
+        <v>0.5553664433034561</v>
       </c>
       <c r="G29" s="19">
-        <v>0.6458174147154766</v>
+        <v>-0.2917499460294181</v>
       </c>
       <c r="H29" s="19">
-        <v>0.432781060607519</v>
+        <v>1.453871687245511</v>
       </c>
       <c r="I29" s="19">
-        <v>0.3540288428030787</v>
+        <v>1.455283430456029</v>
       </c>
       <c r="J29" s="19">
-        <v>0.5772249714703384</v>
+        <v>0.2037699691083313</v>
       </c>
       <c r="K29" s="19">
-        <v>9.616072000000001</v>
+        <v>17.298695</v>
       </c>
       <c r="L29" s="19">
-        <v>3.4084976</v>
+        <v>6.770473</v>
       </c>
       <c r="M29" s="20">
-        <v>0.29867</v>
+        <v>0.48676</v>
       </c>
       <c r="N29" s="20">
-        <v>0.176</v>
+        <v>0.242</v>
       </c>
       <c r="O29" s="20">
-        <v>0.3058211097480845</v>
+        <v>0.1024245409463853</v>
       </c>
       <c r="P29" s="11">
-        <v>57.29475165278869</v>
+        <v>47.96194401166649</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -4122,52 +4240,52 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E30" s="10">
-        <v>108.0500030517578</v>
+        <v>64.75</v>
       </c>
       <c r="F30" s="16">
-        <v>0.5160031210762854</v>
+        <v>0.5505942535115145</v>
       </c>
       <c r="G30" s="19">
-        <v>0.02982011516877862</v>
+        <v>1.175622071073703</v>
       </c>
       <c r="H30" s="19">
-        <v>1.249493192438245</v>
+        <v>-0.5327402912596072</v>
       </c>
       <c r="I30" s="19">
-        <v>0.1792183728511779</v>
+        <v>-0.5389901628995794</v>
       </c>
       <c r="J30" s="19">
-        <v>0.5593367749613797</v>
+        <v>1.373137431464142</v>
       </c>
       <c r="K30" s="19">
-        <v>20.440647</v>
+        <v>12.357601</v>
       </c>
       <c r="L30" s="19">
-        <v>4.4703617</v>
+        <v>1.4373919</v>
       </c>
       <c r="M30" s="20">
-        <v>0.20273</v>
+        <v>-0.20358999</v>
       </c>
       <c r="N30" s="20">
-        <v>0.209</v>
+        <v>0.046</v>
       </c>
       <c r="O30" s="20">
-        <v>0.1151960784313726</v>
+        <v>0.4427361510470484</v>
       </c>
       <c r="P30" s="11">
-        <v>51.68851803422784</v>
+        <v>49.04544420755537</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -4175,52 +4293,52 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="E31" s="10">
-        <v>172.7799987792969</v>
+        <v>125.7900009155273</v>
       </c>
       <c r="F31" s="16">
-        <v>0.5133671518983052</v>
+        <v>0.5378714095247294</v>
       </c>
       <c r="G31" s="19">
-        <v>-1.877249539822365</v>
+        <v>0.6458174147154766</v>
       </c>
       <c r="H31" s="19">
-        <v>1.758964460615154</v>
+        <v>0.432781060607519</v>
       </c>
       <c r="I31" s="19">
-        <v>0.3182836657213104</v>
+        <v>0.3540288428030787</v>
       </c>
       <c r="J31" s="19">
-        <v>1.963527829443432</v>
+        <v>0.6094219784591497</v>
       </c>
       <c r="K31" s="19">
-        <v>54.282146</v>
+        <v>9.616072000000001</v>
       </c>
       <c r="L31" s="19">
-        <v>71.89688</v>
+        <v>3.4084976</v>
       </c>
       <c r="M31" s="20">
-        <v>1.17442</v>
+        <v>0.29867</v>
       </c>
       <c r="N31" s="20">
-        <v>0.256</v>
+        <v>0.176</v>
       </c>
       <c r="O31" s="20">
-        <v>1.181565725213474</v>
+        <v>0.2754100407418374</v>
       </c>
       <c r="P31" s="11">
-        <v>64.73341503859061</v>
+        <v>57.41225311678481</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -4228,52 +4346,52 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="E32" s="10">
-        <v>340.6499938964844</v>
+        <v>166</v>
       </c>
       <c r="F32" s="16">
-        <v>0.5026889325041735</v>
+        <v>0.5277123383300487</v>
       </c>
       <c r="G32" s="19">
-        <v>-0.3026541063380147</v>
+        <v>-1.877249539822365</v>
       </c>
       <c r="H32" s="19">
-        <v>1.453871687245511</v>
+        <v>1.758964460615154</v>
       </c>
       <c r="I32" s="19">
-        <v>1.455283430456029</v>
+        <v>0.3182836657213104</v>
       </c>
       <c r="J32" s="19">
-        <v>0.03908242675265263</v>
+        <v>2.011345117549243</v>
       </c>
       <c r="K32" s="19">
-        <v>17.464125</v>
+        <v>54.282146</v>
       </c>
       <c r="L32" s="19">
-        <v>6.838651</v>
+        <v>71.89688</v>
       </c>
       <c r="M32" s="20">
-        <v>0.48676</v>
+        <v>1.17442</v>
       </c>
       <c r="N32" s="20">
-        <v>0.242</v>
+        <v>0.256</v>
       </c>
       <c r="O32" s="20">
-        <v>0.1096799187683553</v>
+        <v>1.100468209085766</v>
       </c>
       <c r="P32" s="11">
-        <v>44.24473408301287</v>
+        <v>57.15310341793203</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -4281,19 +4399,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E33" s="10">
-        <v>202.5599975585938</v>
+        <v>205.6300048828125</v>
       </c>
       <c r="F33" s="16">
-        <v>0.4915843745559323</v>
+        <v>0.5003618612026105</v>
       </c>
       <c r="G33" s="19">
         <v>0.1534000000694478</v>
@@ -4305,7 +4423,7 @@
         <v>0.2283188730840903</v>
       </c>
       <c r="J33" s="19">
-        <v>0.4269683020748307</v>
+        <v>0.4562265908970911</v>
       </c>
       <c r="K33" s="19">
         <v>23.318033</v>
@@ -4320,13 +4438,13 @@
         <v>0.081</v>
       </c>
       <c r="O33" s="20">
-        <v>0.1971765152341145</v>
+        <v>0.2184485787837076</v>
       </c>
       <c r="P33" s="11">
-        <v>49.93472899320084</v>
+        <v>53.11496913141019</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -4334,52 +4452,52 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="E34" s="10">
-        <v>337.7099914550781</v>
+        <v>110.1600036621094</v>
       </c>
       <c r="F34" s="16">
-        <v>0.4893821574552495</v>
+        <v>0.488400798293382</v>
       </c>
       <c r="G34" s="19">
-        <v>-0.2917499460294181</v>
+        <v>0.02982011516877862</v>
       </c>
       <c r="H34" s="19">
-        <v>1.453871687245511</v>
+        <v>1.249493192438245</v>
       </c>
       <c r="I34" s="19">
-        <v>1.455283430456029</v>
+        <v>0.1792183728511779</v>
       </c>
       <c r="J34" s="19">
-        <v>-0.01617765038569052</v>
+        <v>0.4673290323517015</v>
       </c>
       <c r="K34" s="19">
-        <v>17.298695</v>
+        <v>20.440647</v>
       </c>
       <c r="L34" s="19">
-        <v>6.770473</v>
+        <v>4.4703617</v>
       </c>
       <c r="M34" s="20">
-        <v>0.48676</v>
+        <v>0.20273</v>
       </c>
       <c r="N34" s="20">
-        <v>0.242</v>
+        <v>0.209</v>
       </c>
       <c r="O34" s="20">
-        <v>0.1009320247599452</v>
+        <v>0.1646814073625291</v>
       </c>
       <c r="P34" s="11">
-        <v>43.16080215417117</v>
+        <v>57.25670716621179</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -4387,19 +4505,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E35" s="10">
-        <v>172.5200042724609</v>
+        <v>171.9700012207031</v>
       </c>
       <c r="F35" s="16">
-        <v>0.4809039774222989</v>
+        <v>0.4718920772568308</v>
       </c>
       <c r="G35" s="19">
         <v>0.9039922035122165</v>
@@ -4411,7 +4529,7 @@
         <v>0.6837145595313986</v>
       </c>
       <c r="J35" s="19">
-        <v>0.1625409090092892</v>
+        <v>0.1325012417910622</v>
       </c>
       <c r="K35" s="19">
         <v>7.9410954</v>
@@ -4426,13 +4544,13 @@
         <v>0.316</v>
       </c>
       <c r="O35" s="20">
-        <v>0.0562312412745769</v>
+        <v>0.06069710401615924</v>
       </c>
       <c r="P35" s="11">
-        <v>46.56583117268335</v>
+        <v>45.26649137766186</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -4440,52 +4558,52 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E36" s="10">
-        <v>112.3600006103516</v>
+        <v>66.58000183105469</v>
       </c>
       <c r="F36" s="16">
-        <v>0.4481038184363693</v>
+        <v>0.4578852482700356</v>
       </c>
       <c r="G36" s="19">
-        <v>0.6818833135656812</v>
+        <v>0.4782631507053702</v>
       </c>
       <c r="H36" s="19">
-        <v>0.6287894397638343</v>
+        <v>0.5511183194325295</v>
       </c>
       <c r="I36" s="19">
-        <v>-0.1751734853969869</v>
+        <v>0.2691043413223938</v>
       </c>
       <c r="J36" s="19">
-        <v>0.3753916241175147</v>
+        <v>0.454203573339777</v>
       </c>
       <c r="K36" s="19">
-        <v>11.196411</v>
+        <v>14.819383</v>
       </c>
       <c r="L36" s="19">
-        <v>2.1772428</v>
+        <v>6.1583524</v>
       </c>
       <c r="M36" s="20">
-        <v>0.19399999</v>
+        <v>0.46598998</v>
       </c>
       <c r="N36" s="20">
-        <v>0.107</v>
+        <v>0.057</v>
       </c>
       <c r="O36" s="20">
-        <v>0.1963682428315794</v>
+        <v>0.09068192069473491</v>
       </c>
       <c r="P36" s="11">
-        <v>47.37893442425457</v>
+        <v>58.46132139366637</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -4493,52 +4611,52 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="E37" s="10">
-        <v>176.1100006103516</v>
+        <v>356.4500122070312</v>
       </c>
       <c r="F37" s="16">
-        <v>0.4477617537762071</v>
+        <v>0.4431110568312069</v>
       </c>
       <c r="G37" s="19">
-        <v>0.5368950783305056</v>
+        <v>0.1745054589838901</v>
       </c>
       <c r="H37" s="19">
-        <v>0.5945270320387294</v>
+        <v>-0.2017379700313818</v>
       </c>
       <c r="I37" s="19">
-        <v>0.0123304280898874</v>
+        <v>0.5362618455560154</v>
       </c>
       <c r="J37" s="19">
-        <v>0.4540396935129666</v>
+        <v>1.202515449368277</v>
       </c>
       <c r="K37" s="19">
-        <v>15.270527</v>
+        <v>33.79535</v>
       </c>
       <c r="L37" s="19">
-        <v>2.6730006</v>
+        <v>5.012071</v>
       </c>
       <c r="M37" s="20">
-        <v>0.18416001</v>
+        <v>0.15286</v>
       </c>
       <c r="N37" s="20">
-        <v>0.151</v>
+        <v>0.204</v>
       </c>
       <c r="O37" s="20">
-        <v>0.1109681677071694</v>
+        <v>0.5915788601597702</v>
       </c>
       <c r="P37" s="11">
-        <v>52.65969001770588</v>
+        <v>59.3118022855505</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -4546,52 +4664,52 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E38" s="10">
-        <v>66.94999694824219</v>
+        <v>47.34999847412109</v>
       </c>
       <c r="F38" s="16">
-        <v>0.4444939995885323</v>
+        <v>0.4280179324648286</v>
       </c>
       <c r="G38" s="19">
-        <v>0.4782631507053702</v>
+        <v>0.4704959025733791</v>
       </c>
       <c r="H38" s="19">
-        <v>0.5511183194325295</v>
+        <v>0.07046152471131609</v>
       </c>
       <c r="I38" s="19">
-        <v>0.2691043413223938</v>
+        <v>1.41063650916965</v>
       </c>
       <c r="J38" s="19">
-        <v>0.4095660777347659</v>
+        <v>0.1921943471317943</v>
       </c>
       <c r="K38" s="19">
-        <v>14.819383</v>
+        <v>10.484783</v>
       </c>
       <c r="L38" s="19">
-        <v>6.1583524</v>
+        <v>1.3284671</v>
       </c>
       <c r="M38" s="20">
-        <v>0.46598998</v>
+        <v>0.11522</v>
       </c>
       <c r="N38" s="20">
-        <v>0.057</v>
+        <v>0.642</v>
       </c>
       <c r="O38" s="20">
-        <v>0.1195394707171613</v>
+        <v>0.1012142394224811</v>
       </c>
       <c r="P38" s="11">
-        <v>60.33429878487841</v>
+        <v>57.27752671216225</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -4599,52 +4717,52 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E39" s="10">
-        <v>47.11999893188477</v>
+        <v>179.3600006103516</v>
       </c>
       <c r="F39" s="16">
-        <v>0.4401261593221512</v>
+        <v>0.4269702863280952</v>
       </c>
       <c r="G39" s="19">
-        <v>0.4704959025733791</v>
+        <v>0.5368950783305056</v>
       </c>
       <c r="H39" s="19">
-        <v>0.07046152471131609</v>
+        <v>0.5945270320387294</v>
       </c>
       <c r="I39" s="19">
-        <v>1.41063650916965</v>
+        <v>0.0123304280898874</v>
       </c>
       <c r="J39" s="19">
-        <v>0.2325551033228697</v>
+        <v>0.3847348020192604</v>
       </c>
       <c r="K39" s="19">
-        <v>10.484783</v>
+        <v>15.270527</v>
       </c>
       <c r="L39" s="19">
-        <v>1.3284671</v>
+        <v>2.6730006</v>
       </c>
       <c r="M39" s="20">
-        <v>0.11522</v>
+        <v>0.18416001</v>
       </c>
       <c r="N39" s="20">
-        <v>0.642</v>
+        <v>0.151</v>
       </c>
       <c r="O39" s="20">
-        <v>0.1182139356321723</v>
+        <v>0.1802533181435626</v>
       </c>
       <c r="P39" s="11">
-        <v>56.2636607939117</v>
+        <v>58.59623669423807</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -4652,52 +4770,52 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="E40" s="10">
-        <v>956.1400146484375</v>
+        <v>68.65000152587891</v>
       </c>
       <c r="F40" s="16">
-        <v>0.4245403958428556</v>
+        <v>0.4195929056940111</v>
       </c>
       <c r="G40" s="19">
-        <v>-1.802769348549261</v>
+        <v>0.5078777743715293</v>
       </c>
       <c r="H40" s="19">
-        <v>-0.4234103737860816</v>
+        <v>1.335916108729087</v>
       </c>
       <c r="I40" s="19">
-        <v>4.026096567149331</v>
+        <v>-0.5911526511284643</v>
       </c>
       <c r="J40" s="19">
-        <v>1.557697695939182</v>
+        <v>0.07307814623183409</v>
       </c>
       <c r="K40" s="19">
-        <v>25.146631</v>
+        <v>13.916667</v>
       </c>
       <c r="L40" s="19">
-        <v>15.838706</v>
+        <v>-42.84731</v>
       </c>
       <c r="M40" s="20">
-        <v>-2.40027</v>
+        <v>0</v>
       </c>
       <c r="N40" s="20">
-        <v>1.093</v>
+        <v>0.012</v>
       </c>
       <c r="O40" s="20">
-        <v>0.4123190762901587</v>
+        <v>0.02613223193085679</v>
       </c>
       <c r="P40" s="11">
-        <v>58.53148586909911</v>
+        <v>51.90735711255628</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -4705,52 +4823,52 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="E41" s="10">
-        <v>129.5200042724609</v>
+        <v>895</v>
       </c>
       <c r="F41" s="16">
-        <v>0.4067796261324325</v>
+        <v>0.419116335300859</v>
       </c>
       <c r="G41" s="19">
-        <v>0.5566183474132383</v>
+        <v>-1.802769348549261</v>
       </c>
       <c r="H41" s="19">
-        <v>0.07245981733422238</v>
+        <v>-0.4234103737860816</v>
       </c>
       <c r="I41" s="19">
-        <v>0.895181571692572</v>
+        <v>4.026096567149331</v>
       </c>
       <c r="J41" s="19">
-        <v>0.2913397727367323</v>
+        <v>1.539617494132527</v>
       </c>
       <c r="K41" s="19">
-        <v>17.827541</v>
+        <v>25.146631</v>
       </c>
       <c r="L41" s="19">
-        <v>2.451422</v>
+        <v>15.838706</v>
       </c>
       <c r="M41" s="20">
-        <v>0.1418</v>
+        <v>-2.40027</v>
       </c>
       <c r="N41" s="20">
-        <v>0.355</v>
+        <v>1.093</v>
       </c>
       <c r="O41" s="20">
-        <v>0.1865659603187428</v>
+        <v>0.2769114926196754</v>
       </c>
       <c r="P41" s="11">
-        <v>60.65175981935444</v>
+        <v>53.10377755790047</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -4758,52 +4876,52 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E42" s="10">
-        <v>67.66999816894531</v>
+        <v>97.80000305175781</v>
       </c>
       <c r="F42" s="16">
-        <v>0.405545318087071</v>
+        <v>0.4152862432119432</v>
       </c>
       <c r="G42" s="19">
-        <v>0.5078777743715293</v>
+        <v>0.7063363874428802</v>
       </c>
       <c r="H42" s="19">
-        <v>1.335916108729087</v>
+        <v>-0.5861048079063108</v>
       </c>
       <c r="I42" s="19">
-        <v>-0.5911526511284643</v>
+        <v>0.5647011887732123</v>
       </c>
       <c r="J42" s="19">
-        <v>0.0262528542087006</v>
+        <v>0.8840211687989168</v>
       </c>
       <c r="K42" s="19">
-        <v>13.916667</v>
+        <v>24.444168</v>
       </c>
       <c r="L42" s="19">
-        <v>-42.84731</v>
+        <v>1.7058009</v>
       </c>
       <c r="M42" s="20">
-        <v>0</v>
+        <v>0.06886</v>
       </c>
       <c r="N42" s="20">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="O42" s="20">
-        <v>0.005223064261166366</v>
+        <v>0.1555364571332967</v>
       </c>
       <c r="P42" s="11">
-        <v>48.58037047936657</v>
+        <v>50.22244313756962</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -4811,52 +4929,52 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E43" s="10">
-        <v>94.18000030517578</v>
+        <v>111.2399978637695</v>
       </c>
       <c r="F43" s="16">
-        <v>0.3945829162829916</v>
+        <v>0.406154441161592</v>
       </c>
       <c r="G43" s="19">
-        <v>0.1183002349970005</v>
+        <v>0.6818833135656812</v>
       </c>
       <c r="H43" s="19">
-        <v>1.28042265176903</v>
+        <v>0.6287894397638343</v>
       </c>
       <c r="I43" s="19">
-        <v>0.1172707560089546</v>
+        <v>-0.1751734853969869</v>
       </c>
       <c r="J43" s="19">
-        <v>0.07132189813430242</v>
+        <v>0.2355603665349237</v>
       </c>
       <c r="K43" s="19">
-        <v>16.65096</v>
+        <v>11.196411</v>
       </c>
       <c r="L43" s="19">
-        <v>19.112581</v>
+        <v>2.1772428</v>
       </c>
       <c r="M43" s="20">
-        <v>1.5956</v>
+        <v>0.19399999</v>
       </c>
       <c r="N43" s="20">
-        <v>0.162</v>
+        <v>0.107</v>
       </c>
       <c r="O43" s="20">
-        <v>-0.04679354711075856</v>
+        <v>0.2073482183136333</v>
       </c>
       <c r="P43" s="11">
-        <v>55.82354889079078</v>
+        <v>43.65069199188701</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -4864,52 +4982,52 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E44" s="10">
-        <v>361.1099853515625</v>
+        <v>130.3500061035156</v>
       </c>
       <c r="F44" s="16">
-        <v>0.3907741504182024</v>
+        <v>0.404834775201163</v>
       </c>
       <c r="G44" s="19">
-        <v>0.1745054589838901</v>
+        <v>0.5566183474132383</v>
       </c>
       <c r="H44" s="19">
-        <v>-0.2017379700313818</v>
+        <v>0.07245981733422238</v>
       </c>
       <c r="I44" s="19">
-        <v>0.5362618455560154</v>
+        <v>0.895181571692572</v>
       </c>
       <c r="J44" s="19">
-        <v>1.028059094658262</v>
+        <v>0.2848569362991672</v>
       </c>
       <c r="K44" s="19">
-        <v>33.79535</v>
+        <v>17.827541</v>
       </c>
       <c r="L44" s="19">
-        <v>5.012071</v>
+        <v>2.451422</v>
       </c>
       <c r="M44" s="20">
-        <v>0.15286</v>
+        <v>0.1418</v>
       </c>
       <c r="N44" s="20">
-        <v>0.204</v>
+        <v>0.355</v>
       </c>
       <c r="O44" s="20">
-        <v>0.5364421019746508</v>
+        <v>0.1651207293220864</v>
       </c>
       <c r="P44" s="11">
-        <v>62.79277933616031</v>
+        <v>61.98788872475078</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -4975,77 +5093,77 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B6" s="20">
         <v>0.3</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B7" s="20">
         <v>0.25</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B8" s="20">
         <v>0.15</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B9" s="20">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B10" s="20">
         <f>SUM(B6:B9)</f>
@@ -5054,22 +5172,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -5148,171 +5266,171 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -5330,7 +5448,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI3"/>
+  <dimension ref="A1:BI4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -5338,184 +5456,184 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>420.3853149414062</v>
+        <v>421.3537292480469</v>
       </c>
       <c r="C1">
-        <v>421.3537292480469</v>
+        <v>393.7393798828125</v>
       </c>
       <c r="D1">
-        <v>393.7393798828125</v>
+        <v>400.1088256835938</v>
       </c>
       <c r="E1">
-        <v>400.1088256835938</v>
+        <v>381.1501770019531</v>
       </c>
       <c r="F1">
-        <v>381.1501770019531</v>
+        <v>369.2198791503906</v>
       </c>
       <c r="G1">
-        <v>369.2198791503906</v>
+        <v>390.8042297363281</v>
       </c>
       <c r="H1">
-        <v>390.8042297363281</v>
+        <v>394.9174194335938</v>
       </c>
       <c r="I1">
-        <v>394.9174194335938</v>
+        <v>408.3951416015625</v>
       </c>
       <c r="J1">
-        <v>408.3951416015625</v>
+        <v>403.4133605957031</v>
       </c>
       <c r="K1">
-        <v>403.4133605957031</v>
+        <v>418.6282348632812</v>
       </c>
       <c r="L1">
-        <v>418.6282348632812</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="M1">
-        <v>408.8244323730469</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="N1">
-        <v>418.0192260742188</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="O1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="P1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="Q1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="R1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="S1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="T1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="U1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="V1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="W1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="X1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="Y1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="Z1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="AA1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="AB1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="AC1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="AD1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="AE1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="AF1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="AG1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="AH1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="AI1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="AJ1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="AK1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AL1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AM1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AN1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AO1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AP1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AQ1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AR1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AS1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AT1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AU1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AV1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AW1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AX1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AY1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AZ1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="BA1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="BB1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="BC1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="BD1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="BE1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="BF1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="BG1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="BH1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="BI1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
     </row>
     <row r="2" spans="1:61">
@@ -5523,184 +5641,184 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1079.403930664062</v>
+        <v>995.8468627929688</v>
       </c>
       <c r="C2">
-        <v>995.8468627929688</v>
+        <v>863.8771362304688</v>
       </c>
       <c r="D2">
-        <v>863.8771362304688</v>
+        <v>949.134033203125</v>
       </c>
       <c r="E2">
-        <v>949.134033203125</v>
+        <v>935.74609375</v>
       </c>
       <c r="F2">
-        <v>935.74609375</v>
+        <v>891.7428588867188</v>
       </c>
       <c r="G2">
-        <v>891.7428588867188</v>
+        <v>995.7168579101562</v>
       </c>
       <c r="H2">
-        <v>995.7168579101562</v>
+        <v>981.4590454101562</v>
       </c>
       <c r="I2">
-        <v>981.4590454101562</v>
+        <v>1087.822631835938</v>
       </c>
       <c r="J2">
-        <v>1087.822631835938</v>
+        <v>1020.60302734375</v>
       </c>
       <c r="K2">
-        <v>1020.60302734375</v>
+        <v>1043.029541015625</v>
       </c>
       <c r="L2">
-        <v>1043.029541015625</v>
+        <v>1133.815551757812</v>
       </c>
       <c r="M2">
-        <v>1133.815551757812</v>
+        <v>1211.193725585938</v>
       </c>
       <c r="N2">
-        <v>1211.193725585938</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="O2">
-        <v>1051.608276367188</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="P2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="Q2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="R2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="S2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="T2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="U2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="V2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="W2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="X2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="Y2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="Z2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="AA2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="AB2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="AC2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="AD2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="AE2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="AF2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="AG2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="AH2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="AI2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="AJ2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="AK2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="AL2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AM2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="AN2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AO2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AP2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AQ2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AR2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AS2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AT2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AU2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AV2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AW2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AX2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AY2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AZ2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="BA2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="BB2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="BC2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="BD2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="BE2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="BF2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="BG2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="BH2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="BI2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -5708,184 +5826,369 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1831.5</v>
+        <v>1759.680053710938</v>
       </c>
       <c r="C3">
-        <v>1759.680053710938</v>
+        <v>1559.319946289062</v>
       </c>
       <c r="D3">
-        <v>1559.319946289062</v>
+        <v>1642</v>
       </c>
       <c r="E3">
-        <v>1642</v>
+        <v>1646.5400390625</v>
       </c>
       <c r="F3">
-        <v>1646.5400390625</v>
+        <v>1643.22998046875</v>
       </c>
       <c r="G3">
-        <v>1643.22998046875</v>
+        <v>1881.510009765625</v>
       </c>
       <c r="H3">
-        <v>1881.510009765625</v>
+        <v>1980.099975585938</v>
       </c>
       <c r="I3">
-        <v>1980.099975585938</v>
+        <v>2107.860107421875</v>
       </c>
       <c r="J3">
-        <v>2107.860107421875</v>
+        <v>1991.550048828125</v>
       </c>
       <c r="K3">
-        <v>1991.550048828125</v>
+        <v>1958.800048828125</v>
       </c>
       <c r="L3">
-        <v>1958.800048828125</v>
+        <v>2184.75</v>
       </c>
       <c r="M3">
-        <v>2184.75</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="N3">
+        <v>1963.599975585938</v>
+      </c>
+      <c r="O3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="P3">
+        <v>2335</v>
+      </c>
+      <c r="Q3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="R3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="S3">
         <v>2273.72998046875</v>
       </c>
-      <c r="O3">
-        <v>1963.599975585938</v>
-      </c>
-      <c r="P3">
-        <v>1914.4599609375</v>
-      </c>
-      <c r="Q3">
-        <v>2335</v>
-      </c>
-      <c r="R3">
-        <v>2090.7099609375</v>
-      </c>
-      <c r="S3">
-        <v>2050.389892578125</v>
-      </c>
       <c r="T3">
-        <v>2273.72998046875</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="U3">
-        <v>2032.219970703125</v>
+        <v>1745</v>
       </c>
       <c r="V3">
-        <v>1745</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="W3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="X3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="Y3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="Z3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="AA3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="AB3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="AC3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="AD3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="AE3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="AF3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="AG3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="AH3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="AI3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="AJ3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="AK3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="AL3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="AM3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AN3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AO3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AP3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AQ3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AR3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="AS3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AT3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AU3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AV3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AW3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AX3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AY3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AZ3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="BA3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="BB3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="BC3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="BD3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="BE3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="BF3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="BG3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="BH3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="BI3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:61">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>575.3499755859375</v>
+      </c>
+      <c r="C4">
+        <v>511.7200012207031</v>
+      </c>
+      <c r="D4">
+        <v>526.9299926757812</v>
+      </c>
+      <c r="E4">
+        <v>517.719970703125</v>
+      </c>
+      <c r="F4">
+        <v>490.0899963378906</v>
+      </c>
+      <c r="G4">
+        <v>529.2899780273438</v>
+      </c>
+      <c r="H4">
+        <v>562.9299926757812</v>
+      </c>
+      <c r="I4">
+        <v>653.530029296875</v>
+      </c>
+      <c r="J4">
+        <v>681.0800170898438</v>
+      </c>
+      <c r="K4">
+        <v>712.1300048828125</v>
+      </c>
+      <c r="L4">
+        <v>746.22998046875</v>
+      </c>
+      <c r="M4">
+        <v>732.6199951171875</v>
+      </c>
+      <c r="N4">
+        <v>670.75</v>
+      </c>
+      <c r="O4">
+        <v>643.8300170898438</v>
+      </c>
+      <c r="P4">
+        <v>675.3900146484375</v>
+      </c>
+      <c r="Q4">
+        <v>586.4500122070312</v>
+      </c>
+      <c r="R4">
+        <v>651.8800048828125</v>
+      </c>
+      <c r="S4">
+        <v>638.719970703125</v>
+      </c>
+      <c r="T4">
+        <v>598.3699951171875</v>
+      </c>
+      <c r="U4">
+        <v>539</v>
+      </c>
+      <c r="V4">
+        <v>577.4600219726562</v>
+      </c>
+      <c r="W4">
+        <v>532.0999755859375</v>
+      </c>
+      <c r="X4">
+        <v>550.2999877929688</v>
+      </c>
+      <c r="Y4">
+        <v>578.0499877929688</v>
+      </c>
+      <c r="Z4">
+        <v>582.5900268554688</v>
+      </c>
+      <c r="AA4">
+        <v>555.5499877929688</v>
+      </c>
+      <c r="AB4">
+        <v>563.3200073242188</v>
+      </c>
+      <c r="AC4">
+        <v>513.8400268554688</v>
+      </c>
+      <c r="AD4">
+        <v>466.8099975585938</v>
+      </c>
+      <c r="AE4">
+        <v>477.2200012207031</v>
+      </c>
+      <c r="AF4">
+        <v>487.4200134277344</v>
+      </c>
+      <c r="AG4">
+        <v>548.3900146484375</v>
+      </c>
+      <c r="AH4">
+        <v>556.6699829101562</v>
+      </c>
+      <c r="AI4">
+        <v>558.2999877929688</v>
+      </c>
+      <c r="AJ4">
+        <v>519.7999877929688</v>
+      </c>
+      <c r="AK4">
+        <v>497.9200134277344</v>
+      </c>
+      <c r="AL4">
+        <v>463.510009765625</v>
+      </c>
+      <c r="AM4">
+        <v>462.0400085449219</v>
+      </c>
+      <c r="AN4">
+        <v>533.0399780273438</v>
+      </c>
+      <c r="AO4">
+        <v>544.8400268554688</v>
+      </c>
+      <c r="AP4">
+        <v>527.219970703125</v>
+      </c>
+      <c r="AQ4">
+        <v>548.5599975585938</v>
+      </c>
+      <c r="AR4">
+        <v>519.1699829101562</v>
+      </c>
+      <c r="AS4">
+        <v>451.5199890136719</v>
+      </c>
+      <c r="AT4">
+        <v>434.2999877929688</v>
+      </c>
+      <c r="AU4">
+        <v>438.3399963378906</v>
+      </c>
+      <c r="AV4">
+        <v>437.9299926757812</v>
+      </c>
+      <c r="AW4">
+        <v>454.1000061035156</v>
+      </c>
+      <c r="AX4">
+        <v>487.2900085449219</v>
+      </c>
+      <c r="AY4">
+        <v>508.7999877929688</v>
+      </c>
+      <c r="AZ4">
+        <v>536.010009765625</v>
+      </c>
+      <c r="BA4">
+        <v>496.1600036621094</v>
+      </c>
+      <c r="BB4">
+        <v>462.0899963378906</v>
+      </c>
+      <c r="BC4">
+        <v>469.0499877929688</v>
+      </c>
+      <c r="BD4">
+        <v>459.4400024414062</v>
+      </c>
+      <c r="BE4">
+        <v>435.3800048828125</v>
+      </c>
+      <c r="BF4">
+        <v>450.75</v>
+      </c>
+      <c r="BG4">
+        <v>468.8800048828125</v>
+      </c>
+      <c r="BH4">
+        <v>462</v>
+      </c>
+      <c r="BI4">
+        <v>459.4500122070312</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -17,7 +17,7 @@
     <sheet name="_данные" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$Q$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="227">
   <si>
     <t>DELL</t>
   </si>
@@ -39,6 +39,9 @@
     <t>WDC</t>
   </si>
   <si>
+    <t>VLO</t>
+  </si>
+  <si>
     <t>Открытые позиции</t>
   </si>
   <si>
@@ -123,6 +126,15 @@
     <t>2026-08-28</t>
   </si>
   <si>
+    <t>Valero Energy</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
     <t>Итого</t>
   </si>
   <si>
@@ -231,15 +243,6 @@
     <t>проходит</t>
   </si>
   <si>
-    <t>VLO</t>
-  </si>
-  <si>
-    <t>Valero Energy</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>MPC</t>
   </si>
   <si>
@@ -267,6 +270,21 @@
     <t>Consumer Discretionary</t>
   </si>
   <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>Phillips 66</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
     <t>EOG</t>
   </si>
   <si>
@@ -282,13 +300,16 @@
     <t>Financials</t>
   </si>
   <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>Health Care</t>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>APA Corporation</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>Teradyne</t>
   </si>
   <si>
     <t>NTAP</t>
@@ -297,34 +318,34 @@
     <t>NetApp</t>
   </si>
   <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>APA Corporation</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>Teradyne</t>
-  </si>
-  <si>
     <t>HUM</t>
   </si>
   <si>
     <t>Humana</t>
   </si>
   <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>Seagate Technology</t>
+  </si>
+  <si>
     <t>NVDA</t>
   </si>
   <si>
     <t>Nvidia</t>
   </si>
   <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>Phillips 66</t>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>Diamondback Energy</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
   </si>
   <si>
     <t>GS</t>
@@ -333,18 +354,24 @@
     <t>Goldman Sachs</t>
   </si>
   <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>Diamondback Energy</t>
-  </si>
-  <si>
     <t>MS</t>
   </si>
   <si>
     <t>Morgan Stanley</t>
   </si>
   <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>Centene Corporation</t>
+  </si>
+  <si>
     <t>GOOGL</t>
   </si>
   <si>
@@ -354,16 +381,19 @@
     <t>Communication Services</t>
   </si>
   <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>CF Industries</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>SCHW</t>
+  </si>
+  <si>
+    <t>Charles Schwab Corporation</t>
   </si>
   <si>
     <t>GOOG</t>
@@ -372,19 +402,28 @@
     <t>Alphabet Inc. (Class C)</t>
   </si>
   <si>
-    <t>CNC</t>
-  </si>
-  <si>
-    <t>Centene Corporation</t>
-  </si>
-  <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>CF Industries</t>
-  </si>
-  <si>
-    <t>Materials</t>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>Booking Holdings</t>
+  </si>
+  <si>
+    <t>RJF</t>
+  </si>
+  <si>
+    <t>Raymond James Financial</t>
   </si>
   <si>
     <t>FTNT</t>
@@ -393,16 +432,31 @@
     <t>Fortinet</t>
   </si>
   <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>Booking Holdings</t>
-  </si>
-  <si>
-    <t>SCHW</t>
-  </si>
-  <si>
-    <t>Charles Schwab Corporation</t>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>Altria</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>TGT</t>
+  </si>
+  <si>
+    <t>Target Corporation</t>
+  </si>
+  <si>
+    <t>AMP</t>
+  </si>
+  <si>
+    <t>Ameriprise Financial</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>Hasbro</t>
   </si>
   <si>
     <t>CINF</t>
@@ -411,66 +465,12 @@
     <t>Cincinnati Financial</t>
   </si>
   <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
-  </si>
-  <si>
-    <t>DVN</t>
-  </si>
-  <si>
-    <t>Devon Energy</t>
-  </si>
-  <si>
-    <t>RJF</t>
-  </si>
-  <si>
-    <t>Raymond James Financial</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>Altria</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>LITE</t>
-  </si>
-  <si>
-    <t>Lumentum</t>
-  </si>
-  <si>
-    <t>SWK</t>
-  </si>
-  <si>
-    <t>Stanley Black &amp; Decker</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
     <t>TROW</t>
   </si>
   <si>
     <t>T. Rowe Price</t>
   </si>
   <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -531,7 +531,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-08-29 03:44 UTC · данные на 2026-08-28 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-01 01:19 UTC · данные на 2026-08-31 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -612,7 +612,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-08-29 03:44 UTC</t>
+    <t>2026-09-01 01:19 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -655,6 +655,9 @@
   </si>
   <si>
     <t>Фундаментал на дату</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
   </si>
   <si>
     <t>Версия состояния</t>
@@ -754,14 +757,14 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color rgb="FFD64545"/>
+      <color rgb="FF0F9960"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
-      <color rgb="FF0F9960"/>
+      <color rgb="FFD64545"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -992,23 +995,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Сводка!$B$33</c:f>
+              <c:f>Сводка!$B$33:$B$34</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>Information Technology</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Energy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Сводка!$C$33</c:f>
+              <c:f>Сводка!$C$33:$C$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1901.58</c:v>
+                  <c:v>1930.64</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>474.31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1097,9 +1106,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$9</c:f>
+              <c:f>Капитал!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1115,15 +1124,18 @@
                 <c:pt idx="4">
                   <c:v>2026-08-28</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>2026-08-31</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$9</c:f>
+              <c:f>Капитал!$D$5:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1138,6 +1150,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>9994.27</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10021.720000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1162,9 +1177,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$9</c:f>
+              <c:f>Капитал!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1180,15 +1195,18 @@
                 <c:pt idx="4">
                   <c:v>2026-08-28</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>2026-08-31</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$9</c:f>
+              <c:f>Капитал!$F$5:$F$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1203,6 +1221,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>10077.02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10046.89</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1342,9 +1363,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$9</c:f>
+              <c:f>Капитал!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1360,15 +1381,18 @@
                 <c:pt idx="4">
                   <c:v>2026-08-28</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>2026-08-31</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$9</c:f>
+              <c:f>Капитал!$D$5:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1383,6 +1407,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>9994.27</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10021.720000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1407,9 +1434,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$9</c:f>
+              <c:f>Капитал!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1425,15 +1452,18 @@
                 <c:pt idx="4">
                   <c:v>2026-08-28</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>2026-08-31</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$9</c:f>
+              <c:f>Капитал!$F$5:$F$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1448,6 +1478,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>10077.02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10046.89</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1932,7 +1965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:H33"/>
+  <dimension ref="A2:H34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -1952,7 +1985,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>169</v>
@@ -1966,15 +1999,15 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="4">
-        <v>9994.27</v>
+        <v>10021.72</v>
       </c>
       <c r="D6" s="5">
-        <v>-0.0005729999999999347</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0.007702000000000098</v>
-      </c>
-      <c r="H6" s="5">
+        <v>0.002171999999999841</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.004688999999999943</v>
+      </c>
+      <c r="H6" s="6">
         <v>-0.003416253428967231</v>
       </c>
     </row>
@@ -2003,7 +2036,7 @@
         <v>173</v>
       </c>
       <c r="H9" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="2:8">
@@ -2013,26 +2046,26 @@
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C13" s="10">
-        <v>8092.69</v>
+        <v>7616.77</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14" s="10">
-        <v>1901.58</v>
+        <v>2404.95</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C15" s="10">
-        <v>9994.27</v>
+        <v>10021.72</v>
       </c>
     </row>
     <row r="16" spans="2:8">
@@ -2056,7 +2089,7 @@
         <v>180</v>
       </c>
       <c r="C18" s="11">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2120,7 +2153,7 @@
         <v>188</v>
       </c>
       <c r="C26" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2129,7 +2162,7 @@
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
-        <v>9994.27</v>
+        <v>10021.72</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2144,18 +2177,26 @@
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" s="10">
-        <v>1901.58</v>
+        <v>1930.64</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="10">
+        <v>474.31</v>
       </c>
     </row>
   </sheetData>
@@ -2166,7 +2207,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -2186,62 +2227,62 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -2249,13 +2290,13 @@
         <v>0</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="10">
         <v>443.1115</v>
@@ -2267,32 +2308,32 @@
         <v>476.19</v>
       </c>
       <c r="H5" s="17">
-        <v>456.24</v>
+        <v>456.01</v>
       </c>
       <c r="I5" s="10">
         <f>F5*H5</f>
-        <v>490.29877224</v>
+        <v>490.05160251</v>
       </c>
       <c r="J5" s="10">
         <f>I5-G5</f>
-        <v>14.108772240000008</v>
+        <v>13.861602510000012</v>
       </c>
       <c r="K5" s="18">
         <f>IFERROR(J5/G5,0)</f>
-        <v>0.029628451332451348</v>
+        <v>0.029109394380394404</v>
       </c>
       <c r="L5" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N5" s="19">
         <v>2.927623067210654</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -2300,13 +2341,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" s="10">
         <v>926.2029</v>
@@ -2318,32 +2359,32 @@
         <v>476.62</v>
       </c>
       <c r="H6" s="17">
-        <v>932.86</v>
+        <v>958.73</v>
       </c>
       <c r="I6" s="10">
         <f>F6*H6</f>
-        <v>480.04602456000003</v>
+        <v>493.3586230800001</v>
       </c>
       <c r="J6" s="10">
         <f>I6-G6</f>
-        <v>3.4260245600000303</v>
+        <v>16.73862308000008</v>
       </c>
       <c r="K6" s="18">
         <f>IFERROR(J6/G6,0)</f>
-        <v>0.007188167848600626</v>
+        <v>0.035119430741471364</v>
       </c>
       <c r="L6" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N6" s="19">
         <v>1.809956883354321</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -2351,13 +2392,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="10">
         <v>1550.1948</v>
@@ -2369,32 +2410,32 @@
         <v>477.55</v>
       </c>
       <c r="H7" s="17">
-        <v>1484.98</v>
+        <v>1566.7</v>
       </c>
       <c r="I7" s="10">
         <f>F7*H7</f>
-        <v>457.45996884</v>
+        <v>482.6344686</v>
       </c>
       <c r="J7" s="10">
         <f>I7-G7</f>
-        <v>-20.090031160000024</v>
+        <v>5.08446859999998</v>
       </c>
       <c r="K7" s="18">
         <f>IFERROR(J7/G7,0)</f>
-        <v>-0.04206895855931321</v>
+        <v>0.010646986912365155</v>
       </c>
       <c r="L7" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" s="11">
         <f>MAX(0,21-L7)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N7" s="19">
         <v>1.655247920227722</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -2402,13 +2443,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="10">
         <v>462.5311</v>
@@ -2420,58 +2461,109 @@
         <v>476.95</v>
       </c>
       <c r="H8" s="17">
-        <v>459.45</v>
+        <v>450.55</v>
       </c>
       <c r="I8" s="10">
         <f>F8*H8</f>
-        <v>473.7728943</v>
+        <v>464.5954457</v>
       </c>
       <c r="J8" s="10">
         <f>I8-G8</f>
-        <v>-3.17710569999997</v>
+        <v>-12.354554299999961</v>
       </c>
       <c r="K8" s="18">
         <f>IFERROR(J8/G8,0)</f>
-        <v>-0.006661297200964399</v>
+        <v>-0.02590324834888345</v>
       </c>
       <c r="L8" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="11">
         <f>MAX(0,21-L8)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N8" s="19">
         <v>1.135451734784544</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F9" s="12" t="s">
-        <v>32</v>
+      <c r="A9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="10">
+        <v>360.14</v>
+      </c>
+      <c r="F9" s="16">
+        <v>1.321486</v>
       </c>
       <c r="G9" s="10">
-        <f>SUM(G5:G8)</f>
-        <v>1907.31</v>
+        <v>475.92</v>
+      </c>
+      <c r="H9" s="17">
+        <v>358.92</v>
       </c>
       <c r="I9" s="10">
-        <f>SUM(I5:I8)</f>
-        <v>1901.58</v>
+        <f>F9*H9</f>
+        <v>474.30775512</v>
       </c>
       <c r="J9" s="10">
-        <f>SUM(J5:J8)</f>
-        <v>-5.730000000000018</v>
+        <f>I9-G9</f>
+        <v>-1.6122448799999916</v>
       </c>
       <c r="K9" s="18">
         <f>IFERROR(J9/G9,0)</f>
+        <v>-0.003387638426626306</v>
+      </c>
+      <c r="L9" s="11">
         <v>0</v>
       </c>
+      <c r="M9" s="11">
+        <f>MAX(0,21-L9)</f>
+        <v>21</v>
+      </c>
+      <c r="N9" s="19">
+        <v>1.098454348098604</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="10">
+        <f>SUM(G5:G9)</f>
+        <v>2383.23</v>
+      </c>
+      <c r="I10" s="10">
+        <f>SUM(I5:I9)</f>
+        <v>2404.95</v>
+      </c>
+      <c r="J10" s="10">
+        <f>SUM(J5:J9)</f>
+        <v>21.720000000000027</v>
+      </c>
+      <c r="K10" s="18">
+        <f>IFERROR(J10/G10,0)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P8"/>
-  <conditionalFormatting sqref="K5:K8">
+  <autoFilter ref="A4:P9"/>
+  <conditionalFormatting sqref="K5:K9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -2483,7 +2575,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M8">
+  <conditionalFormatting sqref="M5:M9">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -2512,12 +2604,28 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M5:M8</xm:sqref>
+          <xm:sqref>M5:M9</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
+          <x14:colorSeries rgb="FF0B5FFF"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'_данные'!B5:BI5</xm:f>
+              <xm:sqref>P9</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
           <x14:colorSeries rgb="FF0B5FFF"/>
           <x14:colorNegative theme="5"/>
@@ -2610,64 +2718,64 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2677,7 +2785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2689,37 +2797,37 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B5" s="10">
         <v>10000</v>
@@ -2740,7 +2848,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="10">
         <v>9523.809999999999</v>
@@ -2761,7 +2869,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="10">
         <v>9047.190000000001</v>
@@ -2782,7 +2890,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="10">
         <v>8569.639999999999</v>
@@ -2803,7 +2911,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" s="10">
         <v>8092.69</v>
@@ -2820,6 +2928,27 @@
       </c>
       <c r="F9" s="10">
         <v>10077.02</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="10">
+        <v>7616.77</v>
+      </c>
+      <c r="C10" s="10">
+        <v>2404.95</v>
+      </c>
+      <c r="D10" s="10">
+        <f>B10+C10</f>
+        <v>10021.720000000001</v>
+      </c>
+      <c r="E10" s="11">
+        <v>5</v>
+      </c>
+      <c r="F10" s="10">
+        <v>10046.89</v>
       </c>
     </row>
   </sheetData>
@@ -2849,65 +2978,65 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2915,52 +3044,52 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="10">
-        <v>932.8599853515625</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="F5" s="16">
-        <v>1.797784415791333</v>
+        <v>1.647062011080461</v>
       </c>
       <c r="G5" s="19">
-        <v>0.1411051627135557</v>
+        <v>-0.3023096826635033</v>
       </c>
       <c r="H5" s="19">
-        <v>1.679910500336321</v>
+        <v>1.878280595329006</v>
       </c>
       <c r="I5" s="19">
-        <v>4.206596031118561</v>
+        <v>4.098768515883935</v>
       </c>
       <c r="J5" s="19">
-        <v>2.348286124084672</v>
+        <v>2.177898298882233</v>
       </c>
       <c r="K5" s="19">
-        <v>20.560751</v>
+        <v>20.12168</v>
       </c>
       <c r="L5" s="19">
-        <v>10.204899</v>
+        <v>14.060845</v>
       </c>
       <c r="M5" s="20">
-        <v>0.66638</v>
+        <v>0.9164</v>
       </c>
       <c r="N5" s="20">
-        <v>3.457</v>
+        <v>3.716</v>
       </c>
       <c r="O5" s="20">
-        <v>1.263490084887664</v>
+        <v>1.530690553600131</v>
       </c>
       <c r="P5" s="11">
-        <v>50.68513863125375</v>
+        <v>53.2290695514926</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2968,52 +3097,52 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="10">
-        <v>1484.97998046875</v>
+        <v>958.72998046875</v>
       </c>
       <c r="F6" s="16">
-        <v>1.654426275754993</v>
+        <v>1.616845209133706</v>
       </c>
       <c r="G6" s="19">
-        <v>-0.297947721659126</v>
+        <v>-0.3494721527014143</v>
       </c>
       <c r="H6" s="19">
-        <v>1.878861151632597</v>
+        <v>1.679451569253151</v>
       </c>
       <c r="I6" s="19">
-        <v>4.026096567149331</v>
+        <v>4.255480874359369</v>
       </c>
       <c r="J6" s="19">
-        <v>2.233936064240608</v>
+        <v>2.211672771589793</v>
       </c>
       <c r="K6" s="19">
-        <v>20.248442</v>
+        <v>21.095882</v>
       </c>
       <c r="L6" s="19">
-        <v>14.137921</v>
+        <v>10.456314</v>
       </c>
       <c r="M6" s="20">
-        <v>0.9164</v>
+        <v>0.66638</v>
       </c>
       <c r="N6" s="20">
-        <v>3.716</v>
+        <v>3.457</v>
       </c>
       <c r="O6" s="20">
-        <v>1.337226162656543</v>
+        <v>1.324569832331134</v>
       </c>
       <c r="P6" s="11">
-        <v>49.32350741998839</v>
+        <v>53.76497454418492</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -3021,52 +3150,52 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E7" s="10">
-        <v>459.4500122070312</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="F7" s="16">
-        <v>1.15931561725163</v>
+        <v>1.064276590312865</v>
       </c>
       <c r="G7" s="19">
-        <v>-0.6552990140462744</v>
+        <v>0.7170031980301145</v>
       </c>
       <c r="H7" s="19">
-        <v>1.918440052485617</v>
+        <v>-0.3065610501652122</v>
       </c>
       <c r="I7" s="19">
-        <v>3.032907322180939</v>
+        <v>2.979291350113153</v>
       </c>
       <c r="J7" s="19">
-        <v>1.404530700056557</v>
+        <v>1.596407303093868</v>
       </c>
       <c r="K7" s="19">
-        <v>17.067032</v>
+        <v>14.45283</v>
       </c>
       <c r="L7" s="19">
-        <v>0</v>
+        <v>4.0580444</v>
       </c>
       <c r="M7" s="20">
-        <v>1.30853</v>
+        <v>0.27637</v>
       </c>
       <c r="N7" s="20">
-        <v>0.438</v>
+        <v>0.517</v>
       </c>
       <c r="O7" s="20">
-        <v>0.6438674367834341</v>
+        <v>0.6845142972420715</v>
       </c>
       <c r="P7" s="11">
-        <v>45.19088940689799</v>
+        <v>70.7691181567296</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -3074,52 +3203,52 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E8" s="10">
-        <v>352.3599853515625</v>
+        <v>450.5499877929688</v>
       </c>
       <c r="F8" s="16">
-        <v>1.098454348098604</v>
+        <v>1.045827085339202</v>
       </c>
       <c r="G8" s="19">
-        <v>0.72925464828006</v>
+        <v>-0.8960881426548249</v>
       </c>
       <c r="H8" s="19">
-        <v>-0.3048721710887977</v>
+        <v>1.917595834128675</v>
       </c>
       <c r="I8" s="19">
-        <v>2.983550662811328</v>
+        <v>3.033236167062363</v>
       </c>
       <c r="J8" s="19">
-        <v>1.694544656550286</v>
+        <v>1.267563815147088</v>
       </c>
       <c r="K8" s="19">
-        <v>14.4347105</v>
+        <v>17.067236</v>
       </c>
       <c r="L8" s="19">
-        <v>3.9847977</v>
+        <v>21.967487</v>
       </c>
       <c r="M8" s="20">
-        <v>0.27637</v>
+        <v>1.30853</v>
       </c>
       <c r="N8" s="20">
-        <v>0.517</v>
+        <v>0.438</v>
       </c>
       <c r="O8" s="20">
-        <v>0.7367197024957652</v>
+        <v>0.6694431500136655</v>
       </c>
       <c r="P8" s="11">
-        <v>68.0131238164806</v>
+        <v>43.75220418447689</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -3127,52 +3256,52 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="10">
+        <v>456.010009765625</v>
+      </c>
+      <c r="F9" s="16">
+        <v>1.030753560326209</v>
+      </c>
+      <c r="G9" s="19">
+        <v>-0.03272594325371055</v>
+      </c>
+      <c r="H9" s="19">
+        <v>-0.5359935226777468</v>
+      </c>
+      <c r="I9" s="19">
+        <v>3.169732852629812</v>
+      </c>
+      <c r="J9" s="19">
+        <v>2.33036598692429</v>
+      </c>
+      <c r="K9" s="19">
+        <v>36.353783</v>
+      </c>
+      <c r="L9" s="19">
+        <v>-210.92924</v>
+      </c>
+      <c r="M9" s="20">
+        <v>0</v>
+      </c>
+      <c r="N9" s="20">
+        <v>0.875</v>
+      </c>
+      <c r="O9" s="20">
+        <v>1.983893205935662</v>
+      </c>
+      <c r="P9" s="11">
+        <v>52.55143811575783</v>
+      </c>
+      <c r="Q9" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="10">
-        <v>368.8299865722656</v>
-      </c>
-      <c r="F9" s="16">
-        <v>0.9607631975098783</v>
-      </c>
-      <c r="G9" s="19">
-        <v>0.7230916879797831</v>
-      </c>
-      <c r="H9" s="19">
-        <v>-0.385889491053161</v>
-      </c>
-      <c r="I9" s="19">
-        <v>2.543797486452658</v>
-      </c>
-      <c r="J9" s="19">
-        <v>1.529128136371116</v>
-      </c>
-      <c r="K9" s="19">
-        <v>12.56133</v>
-      </c>
-      <c r="L9" s="19">
-        <v>5.3778367</v>
-      </c>
-      <c r="M9" s="20">
-        <v>0.42099</v>
-      </c>
-      <c r="N9" s="20">
-        <v>0.537</v>
-      </c>
-      <c r="O9" s="20">
-        <v>0.8730204731174731</v>
-      </c>
-      <c r="P9" s="11">
-        <v>71.60800539523845</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3180,52 +3309,52 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>74</v>
-      </c>
       <c r="D10" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E10" s="10">
-        <v>59.09999847412109</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="F10" s="16">
-        <v>0.9233041122157448</v>
+        <v>0.9280120270881818</v>
       </c>
       <c r="G10" s="19">
-        <v>0.6355114639003794</v>
+        <v>0.6975868904074245</v>
       </c>
       <c r="H10" s="19">
-        <v>0.6239334098844196</v>
+        <v>-0.388014448215243</v>
       </c>
       <c r="I10" s="19">
-        <v>3.304463564487919</v>
+        <v>2.535380266835807</v>
       </c>
       <c r="J10" s="19">
-        <v>0.2699926196711274</v>
+        <v>1.451441773314647</v>
       </c>
       <c r="K10" s="19">
-        <v>18.105423</v>
+        <v>12.788835</v>
       </c>
       <c r="L10" s="19">
-        <v>1.7959902</v>
+        <v>5.4714427</v>
       </c>
       <c r="M10" s="20">
-        <v>0.10629</v>
+        <v>0.42099</v>
       </c>
       <c r="N10" s="20">
-        <v>0.534</v>
+        <v>0.537</v>
       </c>
       <c r="O10" s="20">
-        <v>0.1238674065532424</v>
+        <v>0.7909202912771811</v>
       </c>
       <c r="P10" s="11">
-        <v>55.45107029702634</v>
+        <v>73.26707177206802</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -3233,52 +3362,52 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>76</v>
-      </c>
       <c r="D11" s="9" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E11" s="10">
-        <v>52.31000137329102</v>
+        <v>60.18000030517578</v>
       </c>
       <c r="F11" s="16">
-        <v>0.858013206260223</v>
+        <v>0.89279273207993</v>
       </c>
       <c r="G11" s="19">
-        <v>0.304959259686968</v>
+        <v>0.6406620673839032</v>
       </c>
       <c r="H11" s="19">
-        <v>-0.604597401341887</v>
+        <v>0.6228436896122007</v>
       </c>
       <c r="I11" s="19">
-        <v>1.463737124114395</v>
+        <v>3.301541965792155</v>
       </c>
       <c r="J11" s="19">
-        <v>2.32704736690815</v>
+        <v>0.1655063153096189</v>
       </c>
       <c r="K11" s="19">
-        <v>48.999996</v>
+        <v>17.433628</v>
       </c>
       <c r="L11" s="19">
-        <v>2.743159</v>
+        <v>1.765813</v>
       </c>
       <c r="M11" s="20">
-        <v>0.06315</v>
+        <v>0.10629</v>
       </c>
       <c r="N11" s="20">
-        <v>0.4</v>
+        <v>0.534</v>
       </c>
       <c r="O11" s="20">
-        <v>1.459307704875608</v>
+        <v>0.1205501837073359</v>
       </c>
       <c r="P11" s="11">
-        <v>49.42839765492122</v>
+        <v>59.4623059577879</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -3286,52 +3415,52 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="D12" s="9" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="E12" s="10">
-        <v>329.4400024414062</v>
+        <v>52.2400016784668</v>
       </c>
       <c r="F12" s="16">
-        <v>0.740994503335056</v>
+        <v>0.8183590738877906</v>
       </c>
       <c r="G12" s="19">
-        <v>-0.1074817459894137</v>
+        <v>0.2781518668863611</v>
       </c>
       <c r="H12" s="19">
-        <v>1.241839716939916</v>
+        <v>-0.6068661948028746</v>
       </c>
       <c r="I12" s="19">
-        <v>0.6713684345102916</v>
+        <v>1.44187034396217</v>
       </c>
       <c r="J12" s="19">
-        <v>1.206912775734525</v>
+        <v>2.234498369760918</v>
       </c>
       <c r="K12" s="19">
-        <v>20.24627</v>
+        <v>48.887848</v>
       </c>
       <c r="L12" s="19">
-        <v>33.66005</v>
+        <v>2.7368805</v>
       </c>
       <c r="M12" s="20">
-        <v>0.89489</v>
+        <v>0.06315</v>
       </c>
       <c r="N12" s="20">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="O12" s="20">
-        <v>0.5361519933949572</v>
+        <v>1.382769088039109</v>
       </c>
       <c r="P12" s="11">
-        <v>59.81470138462173</v>
+        <v>49.23910788407265</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -3339,52 +3468,52 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>70</v>
-      </c>
       <c r="E13" s="10">
-        <v>143.3500061035156</v>
+        <v>317.1199951171875</v>
       </c>
       <c r="F13" s="16">
-        <v>0.7070619988846399</v>
+        <v>0.800318766414078</v>
       </c>
       <c r="G13" s="19">
-        <v>0.6102249595302855</v>
+        <v>-0.07938398017442079</v>
       </c>
       <c r="H13" s="19">
-        <v>0.5715130155458599</v>
+        <v>1.240108350439193</v>
       </c>
       <c r="I13" s="19">
-        <v>1.562733350737734</v>
+        <v>0.6711374143282868</v>
       </c>
       <c r="J13" s="19">
-        <v>0.4890208484280976</v>
+        <v>1.378120869024543</v>
       </c>
       <c r="K13" s="19">
-        <v>11.680406</v>
+        <v>20.706474</v>
       </c>
       <c r="L13" s="19">
-        <v>2.5993288</v>
+        <v>32.69876</v>
       </c>
       <c r="M13" s="20">
-        <v>0.22507</v>
+        <v>0.89489</v>
       </c>
       <c r="N13" s="20">
-        <v>0.587</v>
+        <v>0.14</v>
       </c>
       <c r="O13" s="20">
-        <v>0.1729137741789912</v>
+        <v>0.4956942282406638</v>
       </c>
       <c r="P13" s="11">
-        <v>48.72434899378244</v>
+        <v>52.62504863465143</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -3392,52 +3521,52 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>83</v>
-      </c>
       <c r="D14" s="9" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E14" s="10">
-        <v>260.5799865722656</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="F14" s="16">
-        <v>0.6998691224905804</v>
+        <v>0.7624710919123701</v>
       </c>
       <c r="G14" s="19">
-        <v>1.158776322034968</v>
+        <v>0.554925557705619</v>
       </c>
       <c r="H14" s="19">
-        <v>0.3596891130938242</v>
+        <v>-0.5467062417077996</v>
       </c>
       <c r="I14" s="19">
-        <v>0.009309850889890559</v>
+        <v>2.503924849329829</v>
       </c>
       <c r="J14" s="19">
-        <v>0.8697248999105011</v>
+        <v>1.190270858760533</v>
       </c>
       <c r="K14" s="19">
-        <v>5.083822</v>
+        <v>13.92751</v>
       </c>
       <c r="L14" s="19">
-        <v>2.0850062</v>
+        <v>3.090377</v>
       </c>
       <c r="M14" s="20">
-        <v>0.46113998</v>
+        <v>0.23452999</v>
       </c>
       <c r="N14" s="20">
-        <v>0.118</v>
+        <v>0.531</v>
       </c>
       <c r="O14" s="20">
-        <v>0.2272897563519332</v>
+        <v>0.5587990396329847</v>
       </c>
       <c r="P14" s="11">
-        <v>52.43996544752573</v>
+        <v>72.09310366809038</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -3445,37 +3574,37 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>87</v>
-      </c>
       <c r="E15" s="10">
-        <v>124.370002746582</v>
+        <v>123.2200012207031</v>
       </c>
       <c r="F15" s="16">
-        <v>0.6993848123306926</v>
+        <v>0.7393231750017529</v>
       </c>
       <c r="G15" s="19">
-        <v>0.3568150294101221</v>
+        <v>0.3732475814323338</v>
       </c>
       <c r="H15" s="19">
-        <v>0.8874455070737253</v>
+        <v>0.8869517519431653</v>
       </c>
       <c r="I15" s="19">
-        <v>0.6313896241094424</v>
+        <v>0.6181521717520603</v>
       </c>
       <c r="J15" s="19">
-        <v>0.9192349437426943</v>
+        <v>1.042960456078175</v>
       </c>
       <c r="K15" s="19">
-        <v>16.303185</v>
+        <v>15.843312</v>
       </c>
       <c r="L15" s="19">
-        <v>4.0541053</v>
+        <v>3.939749</v>
       </c>
       <c r="M15" s="20">
         <v>0.30667</v>
@@ -3484,13 +3613,13 @@
         <v>0.377</v>
       </c>
       <c r="O15" s="20">
-        <v>0.2281031585784812</v>
+        <v>0.2317073180032128</v>
       </c>
       <c r="P15" s="11">
-        <v>53.46645670416243</v>
+        <v>50.79501469184412</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -3498,52 +3627,52 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E16" s="10">
-        <v>456.239990234375</v>
+        <v>144.9600067138672</v>
       </c>
       <c r="F16" s="16">
-        <v>0.6881500402588745</v>
+        <v>0.7127744495345537</v>
       </c>
       <c r="G16" s="19">
-        <v>-1.276312485328304</v>
+        <v>0.6286048285252418</v>
       </c>
       <c r="H16" s="19">
-        <v>-0.5342797424893034</v>
+        <v>0.5703723896787743</v>
       </c>
       <c r="I16" s="19">
-        <v>3.12929742928239</v>
+        <v>1.544751130544684</v>
       </c>
       <c r="J16" s="19">
-        <v>2.450730356957777</v>
+        <v>0.4996241132519498</v>
       </c>
       <c r="K16" s="19">
-        <v>884.0612</v>
+        <v>11.1643305</v>
       </c>
       <c r="L16" s="19">
-        <v>-200.27277</v>
+        <v>2.3641071</v>
       </c>
       <c r="M16" s="20">
-        <v>0</v>
+        <v>0.22507</v>
       </c>
       <c r="N16" s="20">
-        <v>0.875</v>
+        <v>0.587</v>
       </c>
       <c r="O16" s="20">
-        <v>2.095677616236181</v>
+        <v>0.1439541060028606</v>
       </c>
       <c r="P16" s="11">
-        <v>52.61314359601702</v>
+        <v>51.45032158137791</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -3557,46 +3686,46 @@
         <v>89</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="E17" s="10">
-        <v>187.0200042724609</v>
+        <v>257.7999877929688</v>
       </c>
       <c r="F17" s="16">
-        <v>0.6846249323398198</v>
+        <v>0.7102996068670262</v>
       </c>
       <c r="G17" s="19">
-        <v>-0.4056392750220561</v>
+        <v>1.142308394818012</v>
       </c>
       <c r="H17" s="19">
-        <v>1.27195723742807</v>
+        <v>0.3582884962973363</v>
       </c>
       <c r="I17" s="19">
-        <v>-0.1487202202604564</v>
+        <v>0.00561715317825387</v>
       </c>
       <c r="J17" s="19">
-        <v>1.702118128428292</v>
+        <v>0.9239746379018353</v>
       </c>
       <c r="K17" s="19">
-        <v>30.285252</v>
+        <v>5.156936</v>
       </c>
       <c r="L17" s="19">
-        <v>27.10866</v>
+        <v>2.0881312</v>
       </c>
       <c r="M17" s="20">
-        <v>1.06734</v>
+        <v>0.46113998</v>
       </c>
       <c r="N17" s="20">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="O17" s="20">
-        <v>0.9039571069398307</v>
+        <v>0.2180771830944079</v>
       </c>
       <c r="P17" s="11">
-        <v>49.64203036326002</v>
+        <v>49.69254430637025</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -3604,37 +3733,37 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E18" s="10">
-        <v>42.54000091552734</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="F18" s="16">
-        <v>0.6801183977940611</v>
+        <v>0.6644246338578125</v>
       </c>
       <c r="G18" s="19">
-        <v>0.9986491788407921</v>
+        <v>1.009649327332384</v>
       </c>
       <c r="H18" s="19">
-        <v>0.6094621501467751</v>
+        <v>0.6080142824373397</v>
       </c>
       <c r="I18" s="19">
-        <v>-0.228424555888388</v>
+        <v>-0.2323883707990008</v>
       </c>
       <c r="J18" s="19">
-        <v>0.8747392999612933</v>
+        <v>0.8146150688953749</v>
       </c>
       <c r="K18" s="19">
-        <v>9.159914000000001</v>
+        <v>8.974684</v>
       </c>
       <c r="L18" s="19">
-        <v>2.14564</v>
+        <v>2.1246629</v>
       </c>
       <c r="M18" s="20">
         <v>0.26659</v>
@@ -3643,13 +3772,13 @@
         <v>0.092</v>
       </c>
       <c r="O18" s="20">
-        <v>0.4200248016501495</v>
+        <v>0.3803899927920582</v>
       </c>
       <c r="P18" s="11">
-        <v>62.08986555933388</v>
+        <v>64.09924941154749</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -3657,37 +3786,37 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19" s="10">
-        <v>354.9700012207031</v>
+        <v>349.8299865722656</v>
       </c>
       <c r="F19" s="16">
-        <v>0.6567454674023766</v>
+        <v>0.6491678543442235</v>
       </c>
       <c r="G19" s="19">
-        <v>-1.08262537420069</v>
+        <v>-1.037295157007953</v>
       </c>
       <c r="H19" s="19">
-        <v>0.6932659455068273</v>
+        <v>0.6921504118861012</v>
       </c>
       <c r="I19" s="19">
-        <v>3.615274867663105</v>
+        <v>3.660012790878789</v>
       </c>
       <c r="J19" s="19">
-        <v>0.88641787712137</v>
+        <v>0.7943895994775529</v>
       </c>
       <c r="K19" s="19">
-        <v>51.539547</v>
+        <v>51.00144</v>
       </c>
       <c r="L19" s="19">
-        <v>18.169596</v>
+        <v>16.159239</v>
       </c>
       <c r="M19" s="20">
         <v>0.36465</v>
@@ -3696,13 +3825,13 @@
         <v>1.039</v>
       </c>
       <c r="O19" s="20">
-        <v>0.109596172161899</v>
+        <v>0.07406355578300894</v>
       </c>
       <c r="P19" s="11">
-        <v>43.8201951560922</v>
+        <v>42.60895622098829</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -3710,52 +3839,52 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="E20" s="10">
-        <v>385.5400085449219</v>
+        <v>185.2899932861328</v>
       </c>
       <c r="F20" s="16">
-        <v>0.6437277618065194</v>
+        <v>0.6320283217484153</v>
       </c>
       <c r="G20" s="19">
-        <v>0.4746478020487309</v>
+        <v>-0.4187454609174395</v>
       </c>
       <c r="H20" s="19">
-        <v>-0.2835410288834002</v>
+        <v>1.270294671651068</v>
       </c>
       <c r="I20" s="19">
-        <v>0.2562199099090978</v>
+        <v>-0.153897054017106</v>
       </c>
       <c r="J20" s="19">
-        <v>1.779285639754618</v>
+        <v>1.543876167378154</v>
       </c>
       <c r="K20" s="19">
-        <v>35.8304</v>
+        <v>29.498423</v>
       </c>
       <c r="L20" s="19">
-        <v>2.4162972</v>
+        <v>27.131872</v>
       </c>
       <c r="M20" s="20">
-        <v>0.06893000000000001</v>
+        <v>1.06734</v>
       </c>
       <c r="N20" s="20">
-        <v>0.262</v>
+        <v>0.125</v>
       </c>
       <c r="O20" s="20">
-        <v>1.0384818383969</v>
+        <v>0.8652493544755084</v>
       </c>
       <c r="P20" s="11">
-        <v>51.92526418841503</v>
+        <v>47.86720905212579</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -3763,52 +3892,52 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="E21" s="10">
-        <v>217.5500030517578</v>
+        <v>383.2300109863281</v>
       </c>
       <c r="F21" s="16">
-        <v>0.6358914994287772</v>
+        <v>0.619535760539793</v>
       </c>
       <c r="G21" s="19">
-        <v>-1.338461785426528</v>
+        <v>0.4501860349599059</v>
       </c>
       <c r="H21" s="19">
-        <v>2.078256102926562</v>
+        <v>-0.2845602855479212</v>
       </c>
       <c r="I21" s="19">
-        <v>2.806787311422478</v>
+        <v>0.2465264953339178</v>
       </c>
       <c r="J21" s="19">
-        <v>0.3228263753724115</v>
+        <v>1.72880349046238</v>
       </c>
       <c r="K21" s="19">
-        <v>32.883278</v>
+        <v>37.178402</v>
       </c>
       <c r="L21" s="19">
-        <v>25.833954</v>
+        <v>2.4096098</v>
       </c>
       <c r="M21" s="20">
-        <v>1.14288</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="N21" s="20">
-        <v>0.852</v>
+        <v>0.262</v>
       </c>
       <c r="O21" s="20">
-        <v>0.2292755810438503</v>
+        <v>1.061539451583414</v>
       </c>
       <c r="P21" s="11">
-        <v>52.34354093262409</v>
+        <v>50.31973399182989</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -3816,52 +3945,52 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E22" s="10">
-        <v>244.0099945068359</v>
+        <v>828.3800048828125</v>
       </c>
       <c r="F22" s="16">
-        <v>0.6288678535621901</v>
+        <v>0.6150520982814308</v>
       </c>
       <c r="G22" s="19">
-        <v>0.06892234601185927</v>
+        <v>-2.008515620475403</v>
       </c>
       <c r="H22" s="19">
-        <v>-0.54467699511111</v>
+        <v>1.445201098845667</v>
       </c>
       <c r="I22" s="19">
-        <v>2.512241193631993</v>
+        <v>1.44633441951151</v>
       </c>
       <c r="J22" s="19">
-        <v>1.225080731638703</v>
+        <v>2.131187822619695</v>
       </c>
       <c r="K22" s="19">
-        <v>110.99082</v>
+        <v>59.523674</v>
       </c>
       <c r="L22" s="19">
-        <v>3.064414</v>
+        <v>170.03279</v>
       </c>
       <c r="M22" s="20">
-        <v>0.23452999</v>
+        <v>3.7152898</v>
       </c>
       <c r="N22" s="20">
-        <v>0.531</v>
+        <v>0.485</v>
       </c>
       <c r="O22" s="20">
-        <v>0.6010238221719943</v>
+        <v>1.188071042052749</v>
       </c>
       <c r="P22" s="11">
-        <v>70.54639059914102</v>
+        <v>46.8563767849534</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -3869,52 +3998,52 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="E23" s="10">
-        <v>1033.989990234375</v>
+        <v>220.7799987792969</v>
       </c>
       <c r="F23" s="16">
-        <v>0.6052692400068327</v>
+        <v>0.6100796515776822</v>
       </c>
       <c r="G23" s="19">
-        <v>0.3556011439311419</v>
+        <v>-1.170006294227404</v>
       </c>
       <c r="H23" s="19">
-        <v>0.8458479961101603</v>
+        <v>2.092697909288749</v>
       </c>
       <c r="I23" s="19">
-        <v>1.024034813371229</v>
+        <v>2.437733206354793</v>
       </c>
       <c r="J23" s="19">
-        <v>0.4450722526475528</v>
+        <v>0.2408236052349901</v>
       </c>
       <c r="K23" s="19">
-        <v>16.004324</v>
+        <v>27.468435</v>
       </c>
       <c r="L23" s="19">
-        <v>2.8622644</v>
+        <v>26.95787</v>
       </c>
       <c r="M23" s="20">
-        <v>0.16902</v>
+        <v>1.17211</v>
       </c>
       <c r="N23" s="20">
-        <v>0.425</v>
+        <v>1.059</v>
       </c>
       <c r="O23" s="20">
-        <v>0.2145754282246302</v>
+        <v>0.2113616702531329</v>
       </c>
       <c r="P23" s="11">
-        <v>48.31938488621898</v>
+        <v>54.5621857327529</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -3922,37 +4051,37 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E24" s="10">
-        <v>197.6699981689453</v>
+        <v>200.4799957275391</v>
       </c>
       <c r="F24" s="16">
-        <v>0.5772305002286223</v>
+        <v>0.5918335209552881</v>
       </c>
       <c r="G24" s="19">
-        <v>0.561347890123932</v>
+        <v>0.5737660980154189</v>
       </c>
       <c r="H24" s="19">
-        <v>0.0970884411429475</v>
+        <v>0.0953765529458899</v>
       </c>
       <c r="I24" s="19">
-        <v>1.717140484071832</v>
+        <v>1.703570297838407</v>
       </c>
       <c r="J24" s="19">
-        <v>0.4232765009831034</v>
+        <v>0.4677466954614295</v>
       </c>
       <c r="K24" s="19">
-        <v>40.156254</v>
+        <v>37.579845</v>
       </c>
       <c r="L24" s="19">
-        <v>1.5220274</v>
+        <v>1.4633226</v>
       </c>
       <c r="M24" s="20">
         <v>0.034930002</v>
@@ -3961,13 +4090,13 @@
         <v>0.525</v>
       </c>
       <c r="O24" s="20">
-        <v>0.1549079639743987</v>
+        <v>0.1393850576835789</v>
       </c>
       <c r="P24" s="11">
-        <v>47.74849169997778</v>
+        <v>51.19880504338713</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -3975,52 +4104,52 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E25" s="10">
-        <v>214.7700042724609</v>
+        <v>365.9299926757812</v>
       </c>
       <c r="F25" s="16">
-        <v>0.5735185943482911</v>
+        <v>0.5874023171596411</v>
       </c>
       <c r="G25" s="19">
-        <v>0.3452907642059501</v>
+        <v>1.072546138536891</v>
       </c>
       <c r="H25" s="19">
-        <v>0.8001987998031764</v>
+        <v>0.1087413330435472</v>
       </c>
       <c r="I25" s="19">
-        <v>0.4732064398512328</v>
+        <v>-0.335214657738315</v>
       </c>
       <c r="J25" s="19">
-        <v>0.6630023305267569</v>
+        <v>0.9624511366614479</v>
       </c>
       <c r="K25" s="19">
-        <v>17.306387</v>
+        <v>9.919549</v>
       </c>
       <c r="L25" s="19">
-        <v>3.1574755</v>
+        <v>2.3296678</v>
       </c>
       <c r="M25" s="20">
-        <v>0.17969999</v>
+        <v>0.26511</v>
       </c>
       <c r="N25" s="20">
-        <v>0.28</v>
+        <v>0.003</v>
       </c>
       <c r="O25" s="20">
-        <v>0.303902480553556</v>
+        <v>0.1871047185723451</v>
       </c>
       <c r="P25" s="11">
-        <v>50.10351300193571</v>
+        <v>48.79596470513441</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -4028,52 +4157,52 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E26" s="10">
-        <v>346.5899963378906</v>
+        <v>1025.900024414062</v>
       </c>
       <c r="F26" s="16">
-        <v>0.5723262248347317</v>
+        <v>0.5678327859387831</v>
       </c>
       <c r="G26" s="19">
-        <v>-0.3026541063380147</v>
+        <v>0.355410981416705</v>
       </c>
       <c r="H26" s="19">
-        <v>1.453871687245511</v>
+        <v>0.8445110725953496</v>
       </c>
       <c r="I26" s="19">
-        <v>1.455283430456029</v>
+        <v>1.010973541330174</v>
       </c>
       <c r="J26" s="19">
-        <v>0.27120673452118</v>
+        <v>0.3281189738846935</v>
       </c>
       <c r="K26" s="19">
-        <v>17.464125</v>
+        <v>16.078215</v>
       </c>
       <c r="L26" s="19">
-        <v>6.838651</v>
+        <v>2.8559394</v>
       </c>
       <c r="M26" s="20">
-        <v>0.48676</v>
+        <v>0.16902</v>
       </c>
       <c r="N26" s="20">
-        <v>0.242</v>
+        <v>0.425</v>
       </c>
       <c r="O26" s="20">
-        <v>0.1131675735057152</v>
+        <v>0.1958005555577293</v>
       </c>
       <c r="P26" s="11">
-        <v>49.26183990788777</v>
+        <v>46.37220956227538</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -4087,46 +4216,46 @@
         <v>110</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E27" s="10">
-        <v>369.8999938964844</v>
+        <v>213.3200073242188</v>
       </c>
       <c r="F27" s="16">
-        <v>0.5689147855176091</v>
+        <v>0.5491171187695041</v>
       </c>
       <c r="G27" s="19">
-        <v>1.091200655903261</v>
+        <v>0.3412782751836809</v>
       </c>
       <c r="H27" s="19">
-        <v>0.1101459112354547</v>
+        <v>0.7986523025327146</v>
       </c>
       <c r="I27" s="19">
-        <v>-0.3352804504404189</v>
+        <v>0.4640682098581457</v>
       </c>
       <c r="J27" s="19">
-        <v>0.8810339283461005</v>
+        <v>0.5915344303416645</v>
       </c>
       <c r="K27" s="19">
-        <v>9.963699999999999</v>
+        <v>17.362167</v>
       </c>
       <c r="L27" s="19">
-        <v>2.3337615</v>
+        <v>3.1676524</v>
       </c>
       <c r="M27" s="20">
-        <v>0.26511</v>
+        <v>0.17969999</v>
       </c>
       <c r="N27" s="20">
-        <v>0.003</v>
+        <v>0.28</v>
       </c>
       <c r="O27" s="20">
-        <v>0.2078763145036941</v>
+        <v>0.2912993435591271</v>
       </c>
       <c r="P27" s="11">
-        <v>53.13232931507415</v>
+        <v>47.97462276616847</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -4140,31 +4269,31 @@
         <v>112</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E28" s="10">
-        <v>201.8600006103516</v>
+        <v>206.1399993896484</v>
       </c>
       <c r="F28" s="16">
-        <v>0.5606985700814503</v>
+        <v>0.533352257293393</v>
       </c>
       <c r="G28" s="19">
-        <v>0.5728138826097362</v>
+        <v>0.570579143459755</v>
       </c>
       <c r="H28" s="19">
-        <v>-0.06908867602196844</v>
+        <v>-0.07067709858841417</v>
       </c>
       <c r="I28" s="19">
-        <v>2.415351960752095</v>
+        <v>2.406141348912362</v>
       </c>
       <c r="J28" s="19">
-        <v>0.1460792673040241</v>
+        <v>0.06308862188571926</v>
       </c>
       <c r="K28" s="19">
-        <v>19.755836</v>
+        <v>19.409616</v>
       </c>
       <c r="L28" s="19">
-        <v>2.098037</v>
+        <v>2.0853305</v>
       </c>
       <c r="M28" s="20">
         <v>0.12231</v>
@@ -4173,13 +4302,13 @@
         <v>0.535</v>
       </c>
       <c r="O28" s="20">
-        <v>0.1002713356176403</v>
+        <v>0.1067699093330563</v>
       </c>
       <c r="P28" s="11">
-        <v>61.45434657924219</v>
+        <v>66.76833011659021</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -4193,46 +4322,46 @@
         <v>114</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="E29" s="10">
-        <v>342.8800048828125</v>
+        <v>64.33999633789062</v>
       </c>
       <c r="F29" s="16">
-        <v>0.5553664433034561</v>
+        <v>0.5282027886511581</v>
       </c>
       <c r="G29" s="19">
-        <v>-0.2917499460294181</v>
+        <v>1.158727027011848</v>
       </c>
       <c r="H29" s="19">
-        <v>1.453871687245511</v>
+        <v>-0.5337905990257678</v>
       </c>
       <c r="I29" s="19">
-        <v>1.455283430456029</v>
+        <v>-0.5368849216700472</v>
       </c>
       <c r="J29" s="19">
-        <v>0.2037699691083313</v>
+        <v>1.315216895181842</v>
       </c>
       <c r="K29" s="19">
-        <v>17.298695</v>
+        <v>12.1881895</v>
       </c>
       <c r="L29" s="19">
-        <v>6.770473</v>
+        <v>1.4176866</v>
       </c>
       <c r="M29" s="20">
-        <v>0.48676</v>
+        <v>-0.20358999</v>
       </c>
       <c r="N29" s="20">
-        <v>0.242</v>
+        <v>0.046</v>
       </c>
       <c r="O29" s="20">
-        <v>0.1024245409463853</v>
+        <v>0.4426008641059385</v>
       </c>
       <c r="P29" s="11">
-        <v>47.96194401166649</v>
+        <v>47.64520347021701</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -4246,46 +4375,46 @@
         <v>116</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="E30" s="10">
-        <v>64.75</v>
+        <v>339.3500061035156</v>
       </c>
       <c r="F30" s="16">
-        <v>0.5505942535115145</v>
+        <v>0.5229285580255999</v>
       </c>
       <c r="G30" s="19">
-        <v>1.175622071073703</v>
+        <v>-0.3036276540700492</v>
       </c>
       <c r="H30" s="19">
-        <v>-0.5327402912596072</v>
+        <v>1.453630962522038</v>
       </c>
       <c r="I30" s="19">
-        <v>-0.5389901628995794</v>
+        <v>1.455072946604182</v>
       </c>
       <c r="J30" s="19">
-        <v>1.373137431464142</v>
+        <v>0.107827238751593</v>
       </c>
       <c r="K30" s="19">
-        <v>12.357601</v>
+        <v>17.090237</v>
       </c>
       <c r="L30" s="19">
-        <v>1.4373919</v>
+        <v>6.8097687</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.20358999</v>
+        <v>0.48676</v>
       </c>
       <c r="N30" s="20">
-        <v>0.046</v>
+        <v>0.242</v>
       </c>
       <c r="O30" s="20">
-        <v>0.4427361510470484</v>
+        <v>0.1085467137341378</v>
       </c>
       <c r="P30" s="11">
-        <v>49.04544420755537</v>
+        <v>44.05795432950159</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -4293,37 +4422,37 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E31" s="10">
-        <v>125.7900009155273</v>
+        <v>130.0299987792969</v>
       </c>
       <c r="F31" s="16">
-        <v>0.5378714095247294</v>
+        <v>0.5156653081408378</v>
       </c>
       <c r="G31" s="19">
-        <v>0.6458174147154766</v>
+        <v>0.661419949103957</v>
       </c>
       <c r="H31" s="19">
-        <v>0.432781060607519</v>
+        <v>0.4316473659713271</v>
       </c>
       <c r="I31" s="19">
-        <v>0.3540288428030787</v>
+        <v>0.3496392555919275</v>
       </c>
       <c r="J31" s="19">
-        <v>0.6094219784591497</v>
+        <v>0.5229386452600995</v>
       </c>
       <c r="K31" s="19">
-        <v>9.616072000000001</v>
+        <v>9.331602999999999</v>
       </c>
       <c r="L31" s="19">
-        <v>3.4084976</v>
+        <v>3.3175094</v>
       </c>
       <c r="M31" s="20">
         <v>0.29867</v>
@@ -4332,13 +4461,13 @@
         <v>0.176</v>
       </c>
       <c r="O31" s="20">
-        <v>0.2754100407418374</v>
+        <v>0.2582317049762606</v>
       </c>
       <c r="P31" s="11">
-        <v>57.41225311678481</v>
+        <v>63.19252703015538</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -4346,52 +4475,52 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="E32" s="10">
-        <v>166</v>
+        <v>109.8199996948242</v>
       </c>
       <c r="F32" s="16">
-        <v>0.5277123383300487</v>
+        <v>0.5063184103726105</v>
       </c>
       <c r="G32" s="19">
-        <v>-1.877249539822365</v>
+        <v>0.04678928614268382</v>
       </c>
       <c r="H32" s="19">
-        <v>1.758964460615154</v>
+        <v>1.248403054439488</v>
       </c>
       <c r="I32" s="19">
-        <v>0.3182836657213104</v>
+        <v>0.1718308610453409</v>
       </c>
       <c r="J32" s="19">
-        <v>2.011345117549243</v>
+        <v>0.5146874392104404</v>
       </c>
       <c r="K32" s="19">
-        <v>54.282146</v>
+        <v>20.065575</v>
       </c>
       <c r="L32" s="19">
-        <v>71.89688</v>
+        <v>4.333084</v>
       </c>
       <c r="M32" s="20">
-        <v>1.17442</v>
+        <v>0.20273</v>
       </c>
       <c r="N32" s="20">
-        <v>0.256</v>
+        <v>0.209</v>
       </c>
       <c r="O32" s="20">
-        <v>1.100468209085766</v>
+        <v>0.1575604738025262</v>
       </c>
       <c r="P32" s="11">
-        <v>57.15310341793203</v>
+        <v>56.13397667971415</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -4399,52 +4528,52 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="E33" s="10">
-        <v>205.6300048828125</v>
+        <v>335.4100036621094</v>
       </c>
       <c r="F33" s="16">
-        <v>0.5003618612026105</v>
+        <v>0.5018179741863484</v>
       </c>
       <c r="G33" s="19">
-        <v>0.1534000000694478</v>
+        <v>-0.2920267175013403</v>
       </c>
       <c r="H33" s="19">
-        <v>1.132904211800141</v>
+        <v>1.453630962522038</v>
       </c>
       <c r="I33" s="19">
-        <v>0.2283188730840903</v>
+        <v>1.455072946604182</v>
       </c>
       <c r="J33" s="19">
-        <v>0.4562265908970911</v>
+        <v>0.02585768938537925</v>
       </c>
       <c r="K33" s="19">
-        <v>23.318033</v>
+        <v>16.949085</v>
       </c>
       <c r="L33" s="19">
-        <v>-14.997891</v>
+        <v>6.7368755</v>
       </c>
       <c r="M33" s="20">
-        <v>0</v>
+        <v>0.48676</v>
       </c>
       <c r="N33" s="20">
-        <v>0.081</v>
+        <v>0.242</v>
       </c>
       <c r="O33" s="20">
-        <v>0.2184485787837076</v>
+        <v>0.09625379886078811</v>
       </c>
       <c r="P33" s="11">
-        <v>53.11496913141019</v>
+        <v>42.39037469130968</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -4452,52 +4581,52 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E34" s="10">
-        <v>110.1600036621094</v>
+        <v>66.80999755859375</v>
       </c>
       <c r="F34" s="16">
-        <v>0.488400798293382</v>
+        <v>0.4929888030064835</v>
       </c>
       <c r="G34" s="19">
-        <v>0.02982011516877862</v>
+        <v>0.4809824759140722</v>
       </c>
       <c r="H34" s="19">
-        <v>1.249493192438245</v>
+        <v>0.5492514822972634</v>
       </c>
       <c r="I34" s="19">
-        <v>0.1792183728511779</v>
+        <v>0.2705090599165869</v>
       </c>
       <c r="J34" s="19">
-        <v>0.4673290323517015</v>
+        <v>0.5693494355681936</v>
       </c>
       <c r="K34" s="19">
-        <v>20.440647</v>
+        <v>14.762749</v>
       </c>
       <c r="L34" s="19">
-        <v>4.4703617</v>
+        <v>6.0942793</v>
       </c>
       <c r="M34" s="20">
-        <v>0.20273</v>
+        <v>0.46598998</v>
       </c>
       <c r="N34" s="20">
-        <v>0.209</v>
+        <v>0.057</v>
       </c>
       <c r="O34" s="20">
-        <v>0.1646814073625291</v>
+        <v>0.09497627373431516</v>
       </c>
       <c r="P34" s="11">
-        <v>57.25670716621179</v>
+        <v>59.30698300130248</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -4505,52 +4634,52 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="E35" s="10">
-        <v>171.9700012207031</v>
+        <v>353.5499877929688</v>
       </c>
       <c r="F35" s="16">
-        <v>0.4718920772568308</v>
+        <v>0.4680130850867577</v>
       </c>
       <c r="G35" s="19">
-        <v>0.9039922035122165</v>
+        <v>0.1732156252788443</v>
       </c>
       <c r="H35" s="19">
-        <v>0.2335474389445495</v>
+        <v>-0.2038135142426307</v>
       </c>
       <c r="I35" s="19">
-        <v>0.6837145595313986</v>
+        <v>0.5316467527062391</v>
       </c>
       <c r="J35" s="19">
-        <v>0.1325012417910622</v>
+        <v>1.290849210526087</v>
       </c>
       <c r="K35" s="19">
-        <v>7.9410954</v>
+        <v>32.671864</v>
       </c>
       <c r="L35" s="19">
-        <v>1.5754024</v>
+        <v>4.917569</v>
       </c>
       <c r="M35" s="20">
-        <v>0.21484</v>
+        <v>0.15286</v>
       </c>
       <c r="N35" s="20">
-        <v>0.316</v>
+        <v>0.204</v>
       </c>
       <c r="O35" s="20">
-        <v>0.06069710401615924</v>
+        <v>0.5789120698644297</v>
       </c>
       <c r="P35" s="11">
-        <v>45.26649137766186</v>
+        <v>57.18712657548074</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -4558,52 +4687,52 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E36" s="10">
-        <v>66.58000183105469</v>
+        <v>199.0899963378906</v>
       </c>
       <c r="F36" s="16">
-        <v>0.4578852482700356</v>
+        <v>0.4667421959176812</v>
       </c>
       <c r="G36" s="19">
-        <v>0.4782631507053702</v>
+        <v>0.1588797765568509</v>
       </c>
       <c r="H36" s="19">
-        <v>0.5511183194325295</v>
+        <v>1.132158285325552</v>
       </c>
       <c r="I36" s="19">
-        <v>0.2691043413223938</v>
+        <v>0.2281488491242122</v>
       </c>
       <c r="J36" s="19">
-        <v>0.454203573339777</v>
+        <v>0.3393878808353534</v>
       </c>
       <c r="K36" s="19">
-        <v>14.819383</v>
+        <v>22.82242</v>
       </c>
       <c r="L36" s="19">
-        <v>6.1583524</v>
+        <v>-14.45452</v>
       </c>
       <c r="M36" s="20">
-        <v>0.46598998</v>
+        <v>0</v>
       </c>
       <c r="N36" s="20">
-        <v>0.057</v>
+        <v>0.081</v>
       </c>
       <c r="O36" s="20">
-        <v>0.09068192069473491</v>
+        <v>0.1965092084231648</v>
       </c>
       <c r="P36" s="11">
-        <v>58.46132139366637</v>
+        <v>46.35909051426083</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -4611,52 +4740,52 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="E37" s="10">
-        <v>356.4500122070312</v>
+        <v>178.1699981689453</v>
       </c>
       <c r="F37" s="16">
-        <v>0.4431110568312069</v>
+        <v>0.4477288180983513</v>
       </c>
       <c r="G37" s="19">
-        <v>0.1745054589838901</v>
+        <v>0.5314728704784768</v>
       </c>
       <c r="H37" s="19">
-        <v>-0.2017379700313818</v>
+        <v>0.5925654711155478</v>
       </c>
       <c r="I37" s="19">
-        <v>0.5362618455560154</v>
+        <v>0.006886930317741128</v>
       </c>
       <c r="J37" s="19">
-        <v>1.202515449368277</v>
+        <v>0.4637084987608674</v>
       </c>
       <c r="K37" s="19">
-        <v>33.79535</v>
+        <v>15.65096</v>
       </c>
       <c r="L37" s="19">
-        <v>5.012071</v>
+        <v>2.7135465</v>
       </c>
       <c r="M37" s="20">
-        <v>0.15286</v>
+        <v>0.18416001</v>
       </c>
       <c r="N37" s="20">
-        <v>0.204</v>
+        <v>0.151</v>
       </c>
       <c r="O37" s="20">
-        <v>0.5915788601597702</v>
+        <v>0.1622488158579185</v>
       </c>
       <c r="P37" s="11">
-        <v>59.3118022855505</v>
+        <v>55.83527352983359</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -4664,52 +4793,52 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E38" s="10">
-        <v>47.34999847412109</v>
+        <v>170.9299926757812</v>
       </c>
       <c r="F38" s="16">
-        <v>0.4280179324648286</v>
+        <v>0.4410681089993199</v>
       </c>
       <c r="G38" s="19">
-        <v>0.4704959025733791</v>
+        <v>-2.075996516227372</v>
       </c>
       <c r="H38" s="19">
-        <v>0.07046152471131609</v>
+        <v>1.757725626426547</v>
       </c>
       <c r="I38" s="19">
-        <v>1.41063650916965</v>
+        <v>0.3093476814404498</v>
       </c>
       <c r="J38" s="19">
-        <v>0.1921943471317943</v>
+        <v>1.926778350149424</v>
       </c>
       <c r="K38" s="19">
-        <v>10.484783</v>
+        <v>61.02941</v>
       </c>
       <c r="L38" s="19">
-        <v>1.3284671</v>
+        <v>78.524124</v>
       </c>
       <c r="M38" s="20">
-        <v>0.11522</v>
+        <v>1.17442</v>
       </c>
       <c r="N38" s="20">
-        <v>0.642</v>
+        <v>0.256</v>
       </c>
       <c r="O38" s="20">
-        <v>0.1012142394224811</v>
+        <v>1.158752109332942</v>
       </c>
       <c r="P38" s="11">
-        <v>57.27752671216225</v>
+        <v>60.75206107681703</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -4717,52 +4846,52 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="E39" s="10">
-        <v>179.3600006103516</v>
+        <v>68.48000335693359</v>
       </c>
       <c r="F39" s="16">
-        <v>0.4269702863280952</v>
+        <v>0.4371016338969793</v>
       </c>
       <c r="G39" s="19">
-        <v>0.5368950783305056</v>
+        <v>0.4983270256452766</v>
       </c>
       <c r="H39" s="19">
-        <v>0.5945270320387294</v>
+        <v>1.335327792217482</v>
       </c>
       <c r="I39" s="19">
-        <v>0.0123304280898874</v>
+        <v>-0.5933645517218736</v>
       </c>
       <c r="J39" s="19">
-        <v>0.3847348020192604</v>
+        <v>0.1425875363576892</v>
       </c>
       <c r="K39" s="19">
-        <v>15.270527</v>
+        <v>14.242739</v>
       </c>
       <c r="L39" s="19">
-        <v>2.6730006</v>
+        <v>-42.95995</v>
       </c>
       <c r="M39" s="20">
-        <v>0.18416001</v>
+        <v>0</v>
       </c>
       <c r="N39" s="20">
-        <v>0.151</v>
+        <v>0.012</v>
       </c>
       <c r="O39" s="20">
-        <v>0.1802533181435626</v>
+        <v>0.02880685463877186</v>
       </c>
       <c r="P39" s="11">
-        <v>58.59623669423807</v>
+        <v>51.28743876804131</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -4770,52 +4899,52 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C40" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>138</v>
-      </c>
       <c r="E40" s="10">
-        <v>68.65000152587891</v>
+        <v>160.8800048828125</v>
       </c>
       <c r="F40" s="16">
-        <v>0.4195929056940111</v>
+        <v>0.4364809150357429</v>
       </c>
       <c r="G40" s="19">
-        <v>0.5078777743715293</v>
+        <v>0.5356022363903666</v>
       </c>
       <c r="H40" s="19">
-        <v>1.335916108729087</v>
+        <v>-0.3601273510007506</v>
       </c>
       <c r="I40" s="19">
-        <v>-0.5911526511284643</v>
+        <v>0.01013621696190684</v>
       </c>
       <c r="J40" s="19">
-        <v>0.07307814623183409</v>
+        <v>1.214372164415115</v>
       </c>
       <c r="K40" s="19">
-        <v>13.916667</v>
+        <v>16.927385</v>
       </c>
       <c r="L40" s="19">
-        <v>-42.84731</v>
+        <v>4.154594</v>
       </c>
       <c r="M40" s="20">
-        <v>0</v>
+        <v>0.26408002</v>
       </c>
       <c r="N40" s="20">
-        <v>0.012</v>
+        <v>0.053</v>
       </c>
       <c r="O40" s="20">
-        <v>0.02613223193085679</v>
+        <v>0.4460237484891296</v>
       </c>
       <c r="P40" s="11">
-        <v>51.90735711255628</v>
+        <v>59.99869880010746</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -4823,52 +4952,52 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="E41" s="10">
-        <v>895</v>
+        <v>553.1099853515625</v>
       </c>
       <c r="F41" s="16">
-        <v>0.419116335300859</v>
+        <v>0.4293058129208898</v>
       </c>
       <c r="G41" s="19">
-        <v>-1.802769348549261</v>
+        <v>0.3798662438630782</v>
       </c>
       <c r="H41" s="19">
-        <v>-0.4234103737860816</v>
+        <v>0.6536437959805237</v>
       </c>
       <c r="I41" s="19">
-        <v>4.026096567149331</v>
+        <v>-0.2344796805508564</v>
       </c>
       <c r="J41" s="19">
-        <v>1.539617494132527</v>
+        <v>0.6236898094982127</v>
       </c>
       <c r="K41" s="19">
-        <v>25.146631</v>
+        <v>13.51341</v>
       </c>
       <c r="L41" s="19">
-        <v>15.838706</v>
+        <v>7.7711396</v>
       </c>
       <c r="M41" s="20">
-        <v>-2.40027</v>
+        <v>0.63432</v>
       </c>
       <c r="N41" s="20">
-        <v>1.093</v>
+        <v>0.116</v>
       </c>
       <c r="O41" s="20">
-        <v>0.2769114926196754</v>
+        <v>0.1715320986518754</v>
       </c>
       <c r="P41" s="11">
-        <v>53.10377755790047</v>
+        <v>53.20202656196939</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -4876,52 +5005,52 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="E42" s="10">
-        <v>97.80000305175781</v>
+        <v>94.09999847412109</v>
       </c>
       <c r="F42" s="16">
-        <v>0.4152862432119432</v>
+        <v>0.4195305819387309</v>
       </c>
       <c r="G42" s="19">
-        <v>0.7063363874428802</v>
+        <v>0.1229773892076029</v>
       </c>
       <c r="H42" s="19">
-        <v>-0.5861048079063108</v>
+        <v>1.277834374892725</v>
       </c>
       <c r="I42" s="19">
-        <v>0.5647011887732123</v>
+        <v>0.1115207585936172</v>
       </c>
       <c r="J42" s="19">
-        <v>0.8840211687989168</v>
+        <v>0.1548355255474207</v>
       </c>
       <c r="K42" s="19">
-        <v>24.444168</v>
+        <v>16.766905</v>
       </c>
       <c r="L42" s="19">
-        <v>1.7058009</v>
+        <v>18.876202</v>
       </c>
       <c r="M42" s="20">
-        <v>0.06886</v>
+        <v>1.5956</v>
       </c>
       <c r="N42" s="20">
-        <v>0.004</v>
+        <v>0.162</v>
       </c>
       <c r="O42" s="20">
-        <v>0.1555364571332967</v>
+        <v>-0.03500727702957618</v>
       </c>
       <c r="P42" s="11">
-        <v>50.22244313756962</v>
+        <v>55.47527199960736</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -4935,46 +5064,46 @@
         <v>145</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E43" s="10">
-        <v>111.2399978637695</v>
+        <v>169.8999938964844</v>
       </c>
       <c r="F43" s="16">
-        <v>0.406154441161592</v>
+        <v>0.4177676892600736</v>
       </c>
       <c r="G43" s="19">
-        <v>0.6818833135656812</v>
+        <v>0.9027367968796423</v>
       </c>
       <c r="H43" s="19">
-        <v>0.6287894397638343</v>
+        <v>0.2325128591859716</v>
       </c>
       <c r="I43" s="19">
-        <v>-0.1751734853969869</v>
+        <v>0.6741195448566405</v>
       </c>
       <c r="J43" s="19">
-        <v>0.2355603665349237</v>
+        <v>-0.04099832109602682</v>
       </c>
       <c r="K43" s="19">
-        <v>11.196411</v>
+        <v>8.115621000000001</v>
       </c>
       <c r="L43" s="19">
-        <v>2.1772428</v>
+        <v>1.5823956</v>
       </c>
       <c r="M43" s="20">
-        <v>0.19399999</v>
+        <v>0.21484</v>
       </c>
       <c r="N43" s="20">
-        <v>0.107</v>
+        <v>0.316</v>
       </c>
       <c r="O43" s="20">
-        <v>0.2073482183136333</v>
+        <v>0.01093936224717473</v>
       </c>
       <c r="P43" s="11">
-        <v>43.65069199188701</v>
+        <v>40.66719815195724</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -4988,46 +5117,46 @@
         <v>147</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E44" s="10">
-        <v>130.3500061035156</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="F44" s="16">
-        <v>0.404834775201163</v>
+        <v>0.4130748168077866</v>
       </c>
       <c r="G44" s="19">
-        <v>0.5566183474132383</v>
+        <v>0.687267097346562</v>
       </c>
       <c r="H44" s="19">
-        <v>0.07245981733422238</v>
+        <v>0.6280679437254419</v>
       </c>
       <c r="I44" s="19">
-        <v>0.895181571692572</v>
+        <v>-0.1795692988776832</v>
       </c>
       <c r="J44" s="19">
-        <v>0.2848569362991672</v>
+        <v>0.2560436550136999</v>
       </c>
       <c r="K44" s="19">
-        <v>17.827541</v>
+        <v>11.168674</v>
       </c>
       <c r="L44" s="19">
-        <v>2.451422</v>
+        <v>2.1566918</v>
       </c>
       <c r="M44" s="20">
-        <v>0.1418</v>
+        <v>0.19399999</v>
       </c>
       <c r="N44" s="20">
-        <v>0.355</v>
+        <v>0.107</v>
       </c>
       <c r="O44" s="20">
-        <v>0.1651207293220864</v>
+        <v>0.2040923493777529</v>
       </c>
       <c r="P44" s="11">
-        <v>61.98788872475078</v>
+        <v>43.82072393642192</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -5287,7 +5416,7 @@
         <v>196</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5311,7 +5440,7 @@
         <v>201</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -5319,7 +5448,7 @@
         <v>202</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5351,12 +5480,12 @@
         <v>209</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>24</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>206</v>
@@ -5364,73 +5493,73 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -5448,7 +5577,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI4"/>
+  <dimension ref="A1:BI5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -5456,184 +5585,184 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>421.3537292480469</v>
+        <v>393.7393798828125</v>
       </c>
       <c r="C1">
-        <v>393.7393798828125</v>
+        <v>400.1088256835938</v>
       </c>
       <c r="D1">
-        <v>400.1088256835938</v>
+        <v>381.1501770019531</v>
       </c>
       <c r="E1">
-        <v>381.1501770019531</v>
+        <v>369.2198791503906</v>
       </c>
       <c r="F1">
-        <v>369.2198791503906</v>
+        <v>390.8042297363281</v>
       </c>
       <c r="G1">
-        <v>390.8042297363281</v>
+        <v>394.9174194335938</v>
       </c>
       <c r="H1">
-        <v>394.9174194335938</v>
+        <v>408.3951416015625</v>
       </c>
       <c r="I1">
-        <v>408.3951416015625</v>
+        <v>403.4133605957031</v>
       </c>
       <c r="J1">
-        <v>403.4133605957031</v>
+        <v>418.6282348632812</v>
       </c>
       <c r="K1">
-        <v>418.6282348632812</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="L1">
-        <v>408.8244323730469</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="M1">
-        <v>418.0192260742188</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="N1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="O1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="P1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="Q1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="R1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="S1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="T1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="U1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="V1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="W1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="X1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="Y1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="Z1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="AA1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="AB1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="AC1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="AD1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="AE1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="AF1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="AG1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="AH1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="AI1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="AJ1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AK1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AL1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AM1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AN1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AO1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AP1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AQ1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AR1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AS1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AT1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AU1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AV1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AW1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AX1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AY1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AZ1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="BA1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="BB1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="BC1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="BD1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="BE1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="BF1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="BG1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="BH1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
       <c r="BI1">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
     </row>
     <row r="2" spans="1:61">
@@ -5641,184 +5770,184 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>995.8468627929688</v>
+        <v>863.8771362304688</v>
       </c>
       <c r="C2">
-        <v>863.8771362304688</v>
+        <v>949.134033203125</v>
       </c>
       <c r="D2">
-        <v>949.134033203125</v>
+        <v>935.74609375</v>
       </c>
       <c r="E2">
-        <v>935.74609375</v>
+        <v>891.7428588867188</v>
       </c>
       <c r="F2">
-        <v>891.7428588867188</v>
+        <v>995.7168579101562</v>
       </c>
       <c r="G2">
-        <v>995.7168579101562</v>
+        <v>981.4590454101562</v>
       </c>
       <c r="H2">
-        <v>981.4590454101562</v>
+        <v>1087.822631835938</v>
       </c>
       <c r="I2">
-        <v>1087.822631835938</v>
+        <v>1020.60302734375</v>
       </c>
       <c r="J2">
-        <v>1020.60302734375</v>
+        <v>1043.029541015625</v>
       </c>
       <c r="K2">
-        <v>1043.029541015625</v>
+        <v>1133.815551757812</v>
       </c>
       <c r="L2">
-        <v>1133.815551757812</v>
+        <v>1211.193725585938</v>
       </c>
       <c r="M2">
-        <v>1211.193725585938</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="N2">
-        <v>1051.608276367188</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="O2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="P2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="Q2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="R2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="S2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="T2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="U2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="V2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="W2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="X2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="Y2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="Z2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="AA2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="AB2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="AC2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="AD2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="AE2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="AF2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="AG2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="AH2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="AI2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="AJ2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="AK2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AL2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="AM2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AN2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AO2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AP2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AQ2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AR2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AS2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AT2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AU2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AV2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AW2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AX2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AY2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="AZ2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="BA2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="BB2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="BC2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="BD2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="BE2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="BF2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="BG2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="BH2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="BI2">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -5826,184 +5955,184 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1759.680053710938</v>
+        <v>1559.319946289062</v>
       </c>
       <c r="C3">
-        <v>1559.319946289062</v>
+        <v>1642</v>
       </c>
       <c r="D3">
-        <v>1642</v>
+        <v>1646.5400390625</v>
       </c>
       <c r="E3">
-        <v>1646.5400390625</v>
+        <v>1643.22998046875</v>
       </c>
       <c r="F3">
-        <v>1643.22998046875</v>
+        <v>1881.510009765625</v>
       </c>
       <c r="G3">
-        <v>1881.510009765625</v>
+        <v>1980.099975585938</v>
       </c>
       <c r="H3">
-        <v>1980.099975585938</v>
+        <v>2107.860107421875</v>
       </c>
       <c r="I3">
-        <v>2107.860107421875</v>
+        <v>1991.550048828125</v>
       </c>
       <c r="J3">
-        <v>1991.550048828125</v>
+        <v>1958.800048828125</v>
       </c>
       <c r="K3">
-        <v>1958.800048828125</v>
+        <v>2184.75</v>
       </c>
       <c r="L3">
-        <v>2184.75</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="M3">
+        <v>1963.599975585938</v>
+      </c>
+      <c r="N3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="O3">
+        <v>2335</v>
+      </c>
+      <c r="P3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="Q3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="R3">
         <v>2273.72998046875</v>
       </c>
-      <c r="N3">
-        <v>1963.599975585938</v>
-      </c>
-      <c r="O3">
-        <v>1914.4599609375</v>
-      </c>
-      <c r="P3">
-        <v>2335</v>
-      </c>
-      <c r="Q3">
-        <v>2090.7099609375</v>
-      </c>
-      <c r="R3">
-        <v>2050.389892578125</v>
-      </c>
       <c r="S3">
-        <v>2273.72998046875</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="T3">
-        <v>2032.219970703125</v>
+        <v>1745</v>
       </c>
       <c r="U3">
-        <v>1745</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="V3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="W3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="X3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="Y3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="Z3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="AA3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="AB3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="AC3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="AD3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="AE3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="AF3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="AG3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="AH3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="AI3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="AJ3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="AK3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="AL3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AM3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AN3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AO3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AP3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AQ3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="AR3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AS3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AT3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AU3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AV3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AW3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AX3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AY3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AZ3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="BA3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="BB3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="BC3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="BD3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="BE3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="BF3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="BG3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="BH3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="BI3">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
     </row>
     <row r="4" spans="1:61">
@@ -6011,184 +6140,369 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>575.3499755859375</v>
+        <v>511.7200012207031</v>
       </c>
       <c r="C4">
-        <v>511.7200012207031</v>
+        <v>526.9299926757812</v>
       </c>
       <c r="D4">
-        <v>526.9299926757812</v>
+        <v>517.719970703125</v>
       </c>
       <c r="E4">
-        <v>517.719970703125</v>
+        <v>490.0899963378906</v>
       </c>
       <c r="F4">
-        <v>490.0899963378906</v>
+        <v>529.2899780273438</v>
       </c>
       <c r="G4">
-        <v>529.2899780273438</v>
+        <v>562.9299926757812</v>
       </c>
       <c r="H4">
-        <v>562.9299926757812</v>
+        <v>653.530029296875</v>
       </c>
       <c r="I4">
-        <v>653.530029296875</v>
+        <v>681.0800170898438</v>
       </c>
       <c r="J4">
-        <v>681.0800170898438</v>
+        <v>712.1300048828125</v>
       </c>
       <c r="K4">
-        <v>712.1300048828125</v>
+        <v>746.22998046875</v>
       </c>
       <c r="L4">
-        <v>746.22998046875</v>
+        <v>732.6199951171875</v>
       </c>
       <c r="M4">
-        <v>732.6199951171875</v>
+        <v>670.75</v>
       </c>
       <c r="N4">
-        <v>670.75</v>
+        <v>643.8300170898438</v>
       </c>
       <c r="O4">
-        <v>643.8300170898438</v>
+        <v>675.3900146484375</v>
       </c>
       <c r="P4">
-        <v>675.3900146484375</v>
+        <v>586.4500122070312</v>
       </c>
       <c r="Q4">
-        <v>586.4500122070312</v>
+        <v>651.8800048828125</v>
       </c>
       <c r="R4">
-        <v>651.8800048828125</v>
+        <v>638.719970703125</v>
       </c>
       <c r="S4">
-        <v>638.719970703125</v>
+        <v>598.3699951171875</v>
       </c>
       <c r="T4">
-        <v>598.3699951171875</v>
+        <v>539</v>
       </c>
       <c r="U4">
-        <v>539</v>
+        <v>577.4600219726562</v>
       </c>
       <c r="V4">
-        <v>577.4600219726562</v>
+        <v>532.0999755859375</v>
       </c>
       <c r="W4">
-        <v>532.0999755859375</v>
+        <v>550.2999877929688</v>
       </c>
       <c r="X4">
-        <v>550.2999877929688</v>
+        <v>578.0499877929688</v>
       </c>
       <c r="Y4">
-        <v>578.0499877929688</v>
+        <v>582.5900268554688</v>
       </c>
       <c r="Z4">
-        <v>582.5900268554688</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="AA4">
-        <v>555.5499877929688</v>
+        <v>563.3200073242188</v>
       </c>
       <c r="AB4">
-        <v>563.3200073242188</v>
+        <v>513.8400268554688</v>
       </c>
       <c r="AC4">
-        <v>513.8400268554688</v>
+        <v>466.8099975585938</v>
       </c>
       <c r="AD4">
-        <v>466.8099975585938</v>
+        <v>477.2200012207031</v>
       </c>
       <c r="AE4">
-        <v>477.2200012207031</v>
+        <v>487.4200134277344</v>
       </c>
       <c r="AF4">
-        <v>487.4200134277344</v>
+        <v>548.3900146484375</v>
       </c>
       <c r="AG4">
-        <v>548.3900146484375</v>
+        <v>556.6699829101562</v>
       </c>
       <c r="AH4">
-        <v>556.6699829101562</v>
+        <v>558.2999877929688</v>
       </c>
       <c r="AI4">
-        <v>558.2999877929688</v>
+        <v>519.7999877929688</v>
       </c>
       <c r="AJ4">
-        <v>519.7999877929688</v>
+        <v>497.9200134277344</v>
       </c>
       <c r="AK4">
-        <v>497.9200134277344</v>
+        <v>463.510009765625</v>
       </c>
       <c r="AL4">
-        <v>463.510009765625</v>
+        <v>462.0400085449219</v>
       </c>
       <c r="AM4">
-        <v>462.0400085449219</v>
+        <v>533.0399780273438</v>
       </c>
       <c r="AN4">
-        <v>533.0399780273438</v>
+        <v>544.8400268554688</v>
       </c>
       <c r="AO4">
-        <v>544.8400268554688</v>
+        <v>527.219970703125</v>
       </c>
       <c r="AP4">
-        <v>527.219970703125</v>
+        <v>548.5599975585938</v>
       </c>
       <c r="AQ4">
-        <v>548.5599975585938</v>
+        <v>519.1699829101562</v>
       </c>
       <c r="AR4">
-        <v>519.1699829101562</v>
+        <v>451.5199890136719</v>
       </c>
       <c r="AS4">
-        <v>451.5199890136719</v>
+        <v>434.2999877929688</v>
       </c>
       <c r="AT4">
-        <v>434.2999877929688</v>
+        <v>438.3399963378906</v>
       </c>
       <c r="AU4">
-        <v>438.3399963378906</v>
+        <v>437.9299926757812</v>
       </c>
       <c r="AV4">
-        <v>437.9299926757812</v>
+        <v>454.1000061035156</v>
       </c>
       <c r="AW4">
-        <v>454.1000061035156</v>
+        <v>487.2900085449219</v>
       </c>
       <c r="AX4">
-        <v>487.2900085449219</v>
+        <v>508.7999877929688</v>
       </c>
       <c r="AY4">
-        <v>508.7999877929688</v>
+        <v>536.010009765625</v>
       </c>
       <c r="AZ4">
-        <v>536.010009765625</v>
+        <v>496.1600036621094</v>
       </c>
       <c r="BA4">
-        <v>496.1600036621094</v>
+        <v>462.0899963378906</v>
       </c>
       <c r="BB4">
-        <v>462.0899963378906</v>
+        <v>469.0499877929688</v>
       </c>
       <c r="BC4">
-        <v>469.0499877929688</v>
+        <v>459.4400024414062</v>
       </c>
       <c r="BD4">
-        <v>459.4400024414062</v>
+        <v>435.3800048828125</v>
       </c>
       <c r="BE4">
-        <v>435.3800048828125</v>
+        <v>450.75</v>
       </c>
       <c r="BF4">
-        <v>450.75</v>
+        <v>468.8800048828125</v>
       </c>
       <c r="BG4">
-        <v>468.8800048828125</v>
+        <v>462</v>
       </c>
       <c r="BH4">
-        <v>462</v>
+        <v>459.4500122070312</v>
       </c>
       <c r="BI4">
-        <v>459.4500122070312</v>
+        <v>450.5499877929688</v>
+      </c>
+    </row>
+    <row r="5" spans="1:61">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>254.8351593017578</v>
+      </c>
+      <c r="C5">
+        <v>257.3952941894531</v>
+      </c>
+      <c r="D5">
+        <v>252.8030090332031</v>
+      </c>
+      <c r="E5">
+        <v>256.9967956542969</v>
+      </c>
+      <c r="F5">
+        <v>254.6160125732422</v>
+      </c>
+      <c r="G5">
+        <v>257.6741943359375</v>
+      </c>
+      <c r="H5">
+        <v>246.20849609375</v>
+      </c>
+      <c r="I5">
+        <v>243.1901702880859</v>
+      </c>
+      <c r="J5">
+        <v>238.8469543457031</v>
+      </c>
+      <c r="K5">
+        <v>235.3903045654297</v>
+      </c>
+      <c r="L5">
+        <v>242.8415069580078</v>
+      </c>
+      <c r="M5">
+        <v>242.7418823242188</v>
+      </c>
+      <c r="N5">
+        <v>241.4967041015625</v>
+      </c>
+      <c r="O5">
+        <v>254.0780792236328</v>
+      </c>
+      <c r="P5">
+        <v>258.3714904785156</v>
+      </c>
+      <c r="Q5">
+        <v>265.2947387695312</v>
+      </c>
+      <c r="R5">
+        <v>259.4373779296875</v>
+      </c>
+      <c r="S5">
+        <v>268.4027404785156</v>
+      </c>
+      <c r="T5">
+        <v>266.7291870117188</v>
+      </c>
+      <c r="U5">
+        <v>269.2793579101562</v>
+      </c>
+      <c r="V5">
+        <v>265.1951293945312</v>
+      </c>
+      <c r="W5">
+        <v>281.7909851074219</v>
+      </c>
+      <c r="X5">
+        <v>280.1672668457031</v>
+      </c>
+      <c r="Y5">
+        <v>279.6094055175781</v>
+      </c>
+      <c r="Z5">
+        <v>294.6513061523438</v>
+      </c>
+      <c r="AA5">
+        <v>300.2695617675781</v>
+      </c>
+      <c r="AB5">
+        <v>291.5333251953125</v>
+      </c>
+      <c r="AC5">
+        <v>299.1040954589844</v>
+      </c>
+      <c r="AD5">
+        <v>308.4579162597656</v>
+      </c>
+      <c r="AE5">
+        <v>312.1038208007812</v>
+      </c>
+      <c r="AF5">
+        <v>313.5880737304688</v>
+      </c>
+      <c r="AG5">
+        <v>309.7230529785156</v>
+      </c>
+      <c r="AH5">
+        <v>304.0848388671875</v>
+      </c>
+      <c r="AI5">
+        <v>301.33544921875</v>
+      </c>
+      <c r="AJ5">
+        <v>303.756103515625</v>
+      </c>
+      <c r="AK5">
+        <v>297.7294006347656</v>
+      </c>
+      <c r="AL5">
+        <v>300.1600036621094</v>
+      </c>
+      <c r="AM5">
+        <v>310.5099792480469</v>
+      </c>
+      <c r="AN5">
+        <v>312.8999938964844</v>
+      </c>
+      <c r="AO5">
+        <v>307.5400085449219</v>
+      </c>
+      <c r="AP5">
+        <v>308.7300109863281</v>
+      </c>
+      <c r="AQ5">
+        <v>302.3900146484375</v>
+      </c>
+      <c r="AR5">
+        <v>302.989990234375</v>
+      </c>
+      <c r="AS5">
+        <v>298.3099975585938</v>
+      </c>
+      <c r="AT5">
+        <v>314.9500122070312</v>
+      </c>
+      <c r="AU5">
+        <v>323.9200134277344</v>
+      </c>
+      <c r="AV5">
+        <v>330.2099914550781</v>
+      </c>
+      <c r="AW5">
+        <v>342.9200134277344</v>
+      </c>
+      <c r="AX5">
+        <v>341.6700134277344</v>
+      </c>
+      <c r="AY5">
+        <v>347.1900024414062</v>
+      </c>
+      <c r="AZ5">
+        <v>350.0499877929688</v>
+      </c>
+      <c r="BA5">
+        <v>346.260009765625</v>
+      </c>
+      <c r="BB5">
+        <v>341.510009765625</v>
+      </c>
+      <c r="BC5">
+        <v>348.8599853515625</v>
+      </c>
+      <c r="BD5">
+        <v>346</v>
+      </c>
+      <c r="BE5">
+        <v>340.4100036621094</v>
+      </c>
+      <c r="BF5">
+        <v>348.0299987792969</v>
+      </c>
+      <c r="BG5">
+        <v>346.5899963378906</v>
+      </c>
+      <c r="BH5">
+        <v>352.3599853515625</v>
+      </c>
+      <c r="BI5">
+        <v>358.9200134277344</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -17,7 +17,7 @@
     <sheet name="_данные" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$Q$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="228">
   <si>
     <t>DELL</t>
   </si>
@@ -42,6 +42,9 @@
     <t>VLO</t>
   </si>
   <si>
+    <t>MPC</t>
+  </si>
+  <si>
     <t>Открытые позиции</t>
   </si>
   <si>
@@ -135,6 +138,12 @@
     <t>2026-08-31</t>
   </si>
   <si>
+    <t>Marathon Petroleum</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
     <t>Итого</t>
   </si>
   <si>
@@ -243,46 +252,49 @@
     <t>проходит</t>
   </si>
   <si>
-    <t>MPC</t>
-  </si>
-  <si>
-    <t>Marathon Petroleum</t>
-  </si>
-  <si>
     <t>OXY</t>
   </si>
   <si>
     <t>Occidental Petroleum</t>
   </si>
   <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>Phillips 66</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>Expedia Group</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
     <t>HPE</t>
   </si>
   <si>
     <t>Hewlett Packard Enterprise</t>
   </si>
   <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>Expedia Group</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>Phillips 66</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>Health Care</t>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
+    <t>Financials</t>
   </si>
   <si>
     <t>EOG</t>
@@ -291,49 +303,46 @@
     <t>EOG Resources</t>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
-    <t>Financials</t>
-  </si>
-  <si>
     <t>APA</t>
   </si>
   <si>
     <t>APA Corporation</t>
   </si>
   <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>Nvidia</t>
+  </si>
+  <si>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>Humana</t>
+  </si>
+  <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>Seagate Technology</t>
+  </si>
+  <si>
     <t>TER</t>
   </si>
   <si>
     <t>Teradyne</t>
   </si>
   <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
-  </si>
-  <si>
-    <t>STX</t>
-  </si>
-  <si>
-    <t>Seagate Technology</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>Nvidia</t>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>Centene Corporation</t>
   </si>
   <si>
     <t>FANG</t>
@@ -342,94 +351,112 @@
     <t>Diamondback Energy</t>
   </si>
   <si>
+    <t>SCHW</t>
+  </si>
+  <si>
+    <t>Charles Schwab Corporation</t>
+  </si>
+  <si>
     <t>TRV</t>
   </si>
   <si>
     <t>Travelers Companies (The)</t>
   </si>
   <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class A)</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class C)</t>
+  </si>
+  <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>CF Industries</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
     <t>GS</t>
   </si>
   <si>
     <t>Goldman Sachs</t>
   </si>
   <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
-  </si>
-  <si>
-    <t>CNC</t>
-  </si>
-  <si>
-    <t>Centene Corporation</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class A)</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>CF Industries</t>
-  </si>
-  <si>
-    <t>Materials</t>
-  </si>
-  <si>
-    <t>SCHW</t>
-  </si>
-  <si>
-    <t>Charles Schwab Corporation</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class C)</t>
-  </si>
-  <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
     <t>ZBRA</t>
   </si>
   <si>
     <t>Zebra Technologies</t>
   </si>
   <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>Hasbro</t>
+  </si>
+  <si>
+    <t>CINF</t>
+  </si>
+  <si>
+    <t>Cincinnati Financial</t>
+  </si>
+  <si>
+    <t>RJF</t>
+  </si>
+  <si>
+    <t>Raymond James Financial</t>
+  </si>
+  <si>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>Newmont</t>
+  </si>
+  <si>
     <t>BKNG</t>
   </si>
   <si>
     <t>Booking Holdings</t>
   </si>
   <si>
-    <t>RJF</t>
-  </si>
-  <si>
-    <t>Raymond James Financial</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>Waters Corporation</t>
   </si>
   <si>
     <t>MO</t>
@@ -447,30 +474,6 @@
     <t>Target Corporation</t>
   </si>
   <si>
-    <t>AMP</t>
-  </si>
-  <si>
-    <t>Ameriprise Financial</t>
-  </si>
-  <si>
-    <t>HAS</t>
-  </si>
-  <si>
-    <t>Hasbro</t>
-  </si>
-  <si>
-    <t>CINF</t>
-  </si>
-  <si>
-    <t>Cincinnati Financial</t>
-  </si>
-  <si>
-    <t>TROW</t>
-  </si>
-  <si>
-    <t>T. Rowe Price</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -531,7 +534,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-01 01:19 UTC · данные на 2026-08-31 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-02 00:18 UTC · данные на 2026-09-01 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -546,15 +549,15 @@
     <t>Sharpe</t>
   </si>
   <si>
+    <t>Сделок закрыто</t>
+  </si>
+  <si>
+    <t>Доля прибыльных</t>
+  </si>
+  <si>
     <t>—</t>
   </si>
   <si>
-    <t>Сделок закрыто</t>
-  </si>
-  <si>
-    <t>Доля прибыльных</t>
-  </si>
-  <si>
     <t>Открыто позиций</t>
   </si>
   <si>
@@ -612,7 +615,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-01 01:19 UTC</t>
+    <t>2026-09-02 00:18 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -627,7 +630,7 @@
     <t>Прошли фильтры</t>
   </si>
   <si>
-    <t>499</t>
+    <t>498</t>
   </si>
   <si>
     <t>Кандидат дня</t>
@@ -720,7 +723,7 @@
     <numFmt numFmtId="168" formatCode="0.00%"/>
     <numFmt numFmtId="169" formatCode="0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -751,13 +754,6 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF1F2933"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF0F9960"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -900,37 +896,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1014,10 +1009,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1930.64</c:v>
+                  <c:v>1875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>474.31</c:v>
+                  <c:v>958.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1106,9 +1101,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$10</c:f>
+              <c:f>Капитал!$A$5:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1127,15 +1122,18 @@
                 <c:pt idx="5">
                   <c:v>2026-08-31</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>2026-09-01</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$10</c:f>
+              <c:f>Капитал!$D$5:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1153,6 +1151,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>10021.720000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9972.67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1177,9 +1178,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$10</c:f>
+              <c:f>Капитал!$A$5:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1198,15 +1199,18 @@
                 <c:pt idx="5">
                   <c:v>2026-08-31</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>2026-09-01</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$10</c:f>
+              <c:f>Капитал!$F$5:$F$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1224,6 +1228,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>10046.89</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9977.860000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1363,9 +1370,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$10</c:f>
+              <c:f>Капитал!$A$5:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1384,15 +1391,18 @@
                 <c:pt idx="5">
                   <c:v>2026-08-31</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>2026-09-01</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$10</c:f>
+              <c:f>Капитал!$D$5:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1410,6 +1420,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>10021.720000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9972.67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1434,9 +1447,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$10</c:f>
+              <c:f>Капитал!$A$5:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1455,15 +1468,18 @@
                 <c:pt idx="5">
                   <c:v>2026-08-31</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>2026-09-01</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$10</c:f>
+              <c:f>Капитал!$F$5:$F$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1481,6 +1497,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>10046.89</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9977.860000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1975,45 +1994,45 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="4">
-        <v>10021.72</v>
+        <v>9972.669999999998</v>
       </c>
       <c r="D6" s="5">
-        <v>0.002171999999999841</v>
+        <v>-0.002733000000000207</v>
       </c>
       <c r="F6" s="5">
-        <v>0.004688999999999943</v>
-      </c>
-      <c r="H6" s="6">
-        <v>-0.003416253428967231</v>
+        <v>-0.002213999999999938</v>
+      </c>
+      <c r="H6" s="5">
+        <v>-0.005570108480505209</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>174</v>
@@ -2022,181 +2041,181 @@
         <v>175</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" s="6">
+        <v>-2.743637704961072</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="H9" s="7">
-        <v>5</v>
+      <c r="H9" s="6">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="2:8">
-      <c r="B12" s="8" t="s">
-        <v>177</v>
+      <c r="B12" s="7" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="2:8">
-      <c r="B13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="10">
-        <v>7616.77</v>
+      <c r="B13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="9">
+        <v>7139.549999999999</v>
       </c>
     </row>
     <row r="14" spans="2:8">
-      <c r="B14" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="10">
-        <v>2404.95</v>
+      <c r="B14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="9">
+        <v>2833.12</v>
       </c>
     </row>
     <row r="15" spans="2:8">
-      <c r="B15" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="10">
-        <v>10021.72</v>
+      <c r="B15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="9">
+        <v>9972.669999999998</v>
       </c>
     </row>
     <row r="16" spans="2:8">
-      <c r="B16" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C16" s="10">
+      <c r="B16" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="9">
         <v>10000</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="B17" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C17" s="11">
+      <c r="B17" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="10">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="B18" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" s="11">
-        <v>15</v>
+      <c r="B18" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="10">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="B19" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C19" s="11">
+      <c r="B19" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="B20" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" s="11">
+      <c r="B20" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="10">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="B21" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>173</v>
+      <c r="B21" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="B22" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>173</v>
+      <c r="B22" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="B23" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>173</v>
+      <c r="B23" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="B24" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>173</v>
+      <c r="B24" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="B25" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>173</v>
+      <c r="B25" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="11">
+        <v>0.04156959301664937</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="B26" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C26" s="11">
-        <v>6</v>
+      <c r="B26" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="10">
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="C28" s="10">
+        <v>190</v>
+      </c>
+      <c r="C28" s="9">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
-        <v>10021.72</v>
+        <v>9972.669999999998</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="B31" s="8" t="s">
-        <v>191</v>
+      <c r="B31" s="7" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="10">
-        <v>1930.64</v>
+      <c r="B33" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="9">
+        <v>1875</v>
       </c>
     </row>
     <row r="34" spans="2:3">
-      <c r="B34" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="10">
-        <v>474.31</v>
+      <c r="B34" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="9">
+        <v>958.12</v>
       </c>
     </row>
   </sheetData>
@@ -2207,7 +2226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -2227,343 +2246,394 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>24</v>
       </c>
+      <c r="C5" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D5" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="10">
+        <v>26</v>
+      </c>
+      <c r="E5" s="9">
         <v>443.1115</v>
       </c>
       <c r="F5" s="16">
         <v>1.074651</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>476.19</v>
       </c>
       <c r="H5" s="17">
-        <v>456.01</v>
-      </c>
-      <c r="I5" s="10">
+        <v>425</v>
+      </c>
+      <c r="I5" s="9">
         <f>F5*H5</f>
-        <v>490.05160251</v>
-      </c>
-      <c r="J5" s="10">
+        <v>456.726675</v>
+      </c>
+      <c r="J5" s="9">
         <f>I5-G5</f>
-        <v>13.861602510000012</v>
+        <v>-19.463324999999998</v>
       </c>
       <c r="K5" s="18">
         <f>IFERROR(J5/G5,0)</f>
-        <v>0.029109394380394404</v>
-      </c>
-      <c r="L5" s="11">
-        <v>4</v>
-      </c>
-      <c r="M5" s="11">
+        <v>-0.04087302337302337</v>
+      </c>
+      <c r="L5" s="10">
+        <v>5</v>
+      </c>
+      <c r="M5" s="10">
         <f>MAX(0,21-L5)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N5" s="19">
         <v>2.927623067210654</v>
       </c>
-      <c r="O5" s="9" t="s">
-        <v>26</v>
+      <c r="O5" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>24</v>
+      <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="10">
+        <v>29</v>
+      </c>
+      <c r="E6" s="9">
         <v>926.2029</v>
       </c>
       <c r="F6" s="16">
         <v>0.5145960000000001</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>476.62</v>
       </c>
       <c r="H6" s="17">
-        <v>958.73</v>
-      </c>
-      <c r="I6" s="10">
+        <v>933.4400000000001</v>
+      </c>
+      <c r="I6" s="9">
         <f>F6*H6</f>
-        <v>493.3586230800001</v>
-      </c>
-      <c r="J6" s="10">
+        <v>480.3444902400001</v>
+      </c>
+      <c r="J6" s="9">
         <f>I6-G6</f>
-        <v>16.73862308000008</v>
+        <v>3.7244902400000797</v>
       </c>
       <c r="K6" s="18">
         <f>IFERROR(J6/G6,0)</f>
-        <v>0.035119430741471364</v>
-      </c>
-      <c r="L6" s="11">
-        <v>3</v>
-      </c>
-      <c r="M6" s="11">
+        <v>0.007814380932399143</v>
+      </c>
+      <c r="L6" s="10">
+        <v>4</v>
+      </c>
+      <c r="M6" s="10">
         <f>MAX(0,21-L6)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N6" s="19">
         <v>1.809956883354321</v>
       </c>
-      <c r="O6" s="9" t="s">
-        <v>26</v>
+      <c r="O6" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>24</v>
+      <c r="B7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="10">
+        <v>31</v>
+      </c>
+      <c r="E7" s="9">
         <v>1550.1948</v>
       </c>
       <c r="F7" s="16">
         <v>0.308058</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>477.55</v>
       </c>
       <c r="H7" s="17">
-        <v>1566.7</v>
-      </c>
-      <c r="I7" s="10">
+        <v>1536.87</v>
+      </c>
+      <c r="I7" s="9">
         <f>F7*H7</f>
-        <v>482.6344686</v>
-      </c>
-      <c r="J7" s="10">
+        <v>473.44509845999994</v>
+      </c>
+      <c r="J7" s="9">
         <f>I7-G7</f>
-        <v>5.08446859999998</v>
+        <v>-4.104901540000071</v>
       </c>
       <c r="K7" s="18">
         <f>IFERROR(J7/G7,0)</f>
-        <v>0.010646986912365155</v>
-      </c>
-      <c r="L7" s="11">
-        <v>2</v>
-      </c>
-      <c r="M7" s="11">
+        <v>-0.008595752361009467</v>
+      </c>
+      <c r="L7" s="10">
+        <v>3</v>
+      </c>
+      <c r="M7" s="10">
         <f>MAX(0,21-L7)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N7" s="19">
         <v>1.655247920227722</v>
       </c>
-      <c r="O7" s="9" t="s">
-        <v>26</v>
+      <c r="O7" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>24</v>
+      <c r="B8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="10">
+        <v>33</v>
+      </c>
+      <c r="E8" s="9">
         <v>462.5311</v>
       </c>
       <c r="F8" s="16">
         <v>1.031174</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>476.95</v>
       </c>
       <c r="H8" s="17">
-        <v>450.55</v>
-      </c>
-      <c r="I8" s="10">
+        <v>450.44</v>
+      </c>
+      <c r="I8" s="9">
         <f>F8*H8</f>
-        <v>464.5954457</v>
-      </c>
-      <c r="J8" s="10">
+        <v>464.48201656000003</v>
+      </c>
+      <c r="J8" s="9">
         <f>I8-G8</f>
-        <v>-12.354554299999961</v>
+        <v>-12.467983439999955</v>
       </c>
       <c r="K8" s="18">
         <f>IFERROR(J8/G8,0)</f>
-        <v>-0.02590324834888345</v>
-      </c>
-      <c r="L8" s="11">
-        <v>1</v>
-      </c>
-      <c r="M8" s="11">
+        <v>-0.026141070217003785</v>
+      </c>
+      <c r="L8" s="10">
+        <v>2</v>
+      </c>
+      <c r="M8" s="10">
         <f>MAX(0,21-L8)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N8" s="19">
         <v>1.135451734784544</v>
       </c>
-      <c r="O8" s="9" t="s">
-        <v>26</v>
+      <c r="O8" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>34</v>
       </c>
+      <c r="C9" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="D9" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="10">
+        <v>36</v>
+      </c>
+      <c r="E9" s="9">
         <v>360.14</v>
       </c>
       <c r="F9" s="16">
         <v>1.321486</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>475.92</v>
       </c>
       <c r="H9" s="17">
-        <v>358.92</v>
-      </c>
-      <c r="I9" s="10">
+        <v>361.99</v>
+      </c>
+      <c r="I9" s="9">
         <f>F9*H9</f>
-        <v>474.30775512</v>
-      </c>
-      <c r="J9" s="10">
+        <v>478.36471714</v>
+      </c>
+      <c r="J9" s="9">
         <f>I9-G9</f>
-        <v>-1.6122448799999916</v>
+        <v>2.444717139999966</v>
       </c>
       <c r="K9" s="18">
         <f>IFERROR(J9/G9,0)</f>
-        <v>-0.003387638426626306</v>
-      </c>
-      <c r="L9" s="11">
-        <v>0</v>
-      </c>
-      <c r="M9" s="11">
+        <v>0.005136823709867133</v>
+      </c>
+      <c r="L9" s="10">
+        <v>1</v>
+      </c>
+      <c r="M9" s="10">
         <f>MAX(0,21-L9)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N9" s="19">
         <v>1.098454348098604</v>
       </c>
-      <c r="O9" s="9" t="s">
-        <v>26</v>
+      <c r="O9" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F10" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="10">
-        <f>SUM(G5:G9)</f>
-        <v>2383.23</v>
-      </c>
-      <c r="I10" s="10">
-        <f>SUM(I5:I9)</f>
-        <v>2404.95</v>
-      </c>
-      <c r="J10" s="10">
-        <f>SUM(J5:J9)</f>
-        <v>21.720000000000027</v>
+      <c r="A10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="9">
+        <v>380.9704</v>
+      </c>
+      <c r="F10" s="16">
+        <v>1.252643</v>
+      </c>
+      <c r="G10" s="9">
+        <v>477.22</v>
+      </c>
+      <c r="H10" s="17">
+        <v>383</v>
+      </c>
+      <c r="I10" s="9">
+        <f>F10*H10</f>
+        <v>479.762269</v>
+      </c>
+      <c r="J10" s="9">
+        <f>I10-G10</f>
+        <v>2.542268999999976</v>
       </c>
       <c r="K10" s="18">
         <f>IFERROR(J10/G10,0)</f>
+        <v>0.005327247391140304</v>
+      </c>
+      <c r="L10" s="10">
         <v>0</v>
       </c>
+      <c r="M10" s="10">
+        <f>MAX(0,21-L10)</f>
+        <v>21</v>
+      </c>
+      <c r="N10" s="19">
+        <v>0.9280120270881818</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="9">
+        <f>SUM(G5:G10)</f>
+        <v>2860.45</v>
+      </c>
+      <c r="I11" s="9">
+        <f>SUM(I5:I10)</f>
+        <v>2833.12</v>
+      </c>
+      <c r="J11" s="9">
+        <f>SUM(J5:J10)</f>
+        <v>-27.33000000000004</v>
+      </c>
+      <c r="K11" s="18">
+        <f>IFERROR(J11/G11,0)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P9"/>
-  <conditionalFormatting sqref="K5:K9">
+  <autoFilter ref="A4:P10"/>
+  <conditionalFormatting sqref="K5:K10">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -2575,7 +2645,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M9">
+  <conditionalFormatting sqref="M5:M10">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -2604,12 +2674,28 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M5:M9</xm:sqref>
+          <xm:sqref>M5:M10</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
+          <x14:colorSeries rgb="FF0B5FFF"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'_данные'!B6:BI6</xm:f>
+              <xm:sqref>P10</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
           <x14:colorSeries rgb="FF0B5FFF"/>
           <x14:colorNegative theme="5"/>
@@ -2718,64 +2804,64 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2785,7 +2871,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2797,158 +2883,179 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="10">
+        <v>58</v>
+      </c>
+      <c r="B5" s="9">
         <v>10000</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <v>0</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f>B5+C5</f>
         <v>10000.0</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>10000</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="10">
+        <v>26</v>
+      </c>
+      <c r="B6" s="9">
         <v>9523.809999999999</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>485.2</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f>B6+C6</f>
         <v>10009.01</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <v>1</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>10031.96</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="10">
+        <v>29</v>
+      </c>
+      <c r="B7" s="9">
         <v>9047.190000000001</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <v>981.34</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f>B7+C7</f>
         <v>10028.53</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>2</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>10034.19</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="10">
+        <v>31</v>
+      </c>
+      <c r="B8" s="9">
         <v>8569.639999999999</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>1446.31</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f>B8+C8</f>
         <v>10015.949999999999</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <v>3</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>10099.94</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="10">
+        <v>33</v>
+      </c>
+      <c r="B9" s="9">
         <v>8092.69</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>1901.58</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f>B9+C9</f>
         <v>9994.27</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <v>4</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>10077.02</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="10">
+        <v>36</v>
+      </c>
+      <c r="B10" s="9">
         <v>7616.77</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <v>2404.95</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f>B10+C10</f>
         <v>10021.720000000001</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <v>5</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>10046.89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="9">
+        <v>7139.55</v>
+      </c>
+      <c r="C11" s="9">
+        <v>2833.12</v>
+      </c>
+      <c r="D11" s="9">
+        <f>B11+C11</f>
+        <v>9972.67</v>
+      </c>
+      <c r="E11" s="10">
+        <v>6</v>
+      </c>
+      <c r="F11" s="9">
+        <v>9977.860000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2978,97 +3085,97 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="10">
-        <v>1566.699951171875</v>
+      <c r="C5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="9">
+        <v>1536.869995117188</v>
       </c>
       <c r="F5" s="16">
-        <v>1.647062011080461</v>
+        <v>1.703226574613602</v>
       </c>
       <c r="G5" s="19">
-        <v>-0.3023096826635033</v>
+        <v>-0.3013957166684036</v>
       </c>
       <c r="H5" s="19">
-        <v>1.878280595329006</v>
+        <v>1.877025238685021</v>
       </c>
       <c r="I5" s="19">
-        <v>4.098768515883935</v>
+        <v>4.095406692860193</v>
       </c>
       <c r="J5" s="19">
-        <v>2.177898298882233</v>
+        <v>2.366926586712796</v>
       </c>
       <c r="K5" s="19">
         <v>20.12168</v>
@@ -3076,52 +3183,52 @@
       <c r="L5" s="19">
         <v>14.060845</v>
       </c>
-      <c r="M5" s="20">
+      <c r="M5" s="11">
         <v>0.9164</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="11">
         <v>3.716</v>
       </c>
-      <c r="O5" s="20">
-        <v>1.530690553600131</v>
-      </c>
-      <c r="P5" s="11">
-        <v>53.2290695514926</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>71</v>
+      <c r="O5" s="11">
+        <v>1.718151550404877</v>
+      </c>
+      <c r="P5" s="10">
+        <v>51.66385839684092</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="A6" s="10">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="10">
-        <v>958.72998046875</v>
+      <c r="C6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="9">
+        <v>933.4400024414062</v>
       </c>
       <c r="F6" s="16">
-        <v>1.616845209133706</v>
+        <v>1.668009237315851</v>
       </c>
       <c r="G6" s="19">
-        <v>-0.3494721527014143</v>
+        <v>-0.3485326374484333</v>
       </c>
       <c r="H6" s="19">
-        <v>1.679451569253151</v>
+        <v>1.678368475369044</v>
       </c>
       <c r="I6" s="19">
-        <v>4.255480874359369</v>
+        <v>4.255133160878044</v>
       </c>
       <c r="J6" s="19">
-        <v>2.211672771589793</v>
+        <v>2.382356451921377</v>
       </c>
       <c r="K6" s="19">
         <v>21.095882</v>
@@ -3129,211 +3236,211 @@
       <c r="L6" s="19">
         <v>10.456314</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="11">
         <v>0.66638</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="11">
         <v>3.457</v>
       </c>
-      <c r="O6" s="20">
-        <v>1.324569832331134</v>
-      </c>
-      <c r="P6" s="11">
-        <v>53.76497454418492</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>71</v>
+      <c r="O6" s="11">
+        <v>1.459902343677745</v>
+      </c>
+      <c r="P6" s="10">
+        <v>50.44808337526958</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
+      <c r="A7" s="10">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="9">
+        <v>450.4400024414062</v>
+      </c>
+      <c r="F7" s="16">
+        <v>1.090813599677795</v>
+      </c>
+      <c r="G7" s="19">
+        <v>-0.8945569446327866</v>
+      </c>
+      <c r="H7" s="19">
+        <v>1.915872786242084</v>
+      </c>
+      <c r="I7" s="19">
+        <v>3.033358585171229</v>
+      </c>
+      <c r="J7" s="19">
+        <v>1.417362329104754</v>
+      </c>
+      <c r="K7" s="19">
+        <v>17.067236</v>
+      </c>
+      <c r="L7" s="19">
+        <v>21.967487</v>
+      </c>
+      <c r="M7" s="11">
+        <v>1.30853</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0.438</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0.798703509252862</v>
+      </c>
+      <c r="P7" s="10">
+        <v>43.73367487654892</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
         <v>4</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="B8" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="9">
+        <v>425</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1.039859662658936</v>
+      </c>
+      <c r="G8" s="19">
+        <v>-0.03219460680095537</v>
+      </c>
+      <c r="H8" s="19">
+        <v>-0.5368449501454849</v>
+      </c>
+      <c r="I8" s="19">
+        <v>3.164697365105014</v>
+      </c>
+      <c r="J8" s="19">
+        <v>2.36341559156614</v>
+      </c>
+      <c r="K8" s="19">
+        <v>36.353783</v>
+      </c>
+      <c r="L8" s="19">
+        <v>-210.92924</v>
+      </c>
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="N8" s="11">
+        <v>0.875</v>
+      </c>
+      <c r="O8" s="11">
+        <v>1.941310647213375</v>
+      </c>
+      <c r="P8" s="10">
+        <v>44.90408763111303</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="10">
-        <v>358.9200134277344</v>
-      </c>
-      <c r="F7" s="16">
-        <v>1.064276590312865</v>
-      </c>
-      <c r="G7" s="19">
-        <v>0.7170031980301145</v>
-      </c>
-      <c r="H7" s="19">
-        <v>-0.3065610501652122</v>
-      </c>
-      <c r="I7" s="19">
-        <v>2.979291350113153</v>
-      </c>
-      <c r="J7" s="19">
-        <v>1.596407303093868</v>
-      </c>
-      <c r="K7" s="19">
+      <c r="D9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="9">
+        <v>361.989990234375</v>
+      </c>
+      <c r="F9" s="16">
+        <v>1.02821252620002</v>
+      </c>
+      <c r="G9" s="19">
+        <v>0.7167153045991042</v>
+      </c>
+      <c r="H9" s="19">
+        <v>-0.3064420778114862</v>
+      </c>
+      <c r="I9" s="19">
+        <v>2.973519747014805</v>
+      </c>
+      <c r="J9" s="19">
+        <v>1.479268307403133</v>
+      </c>
+      <c r="K9" s="19">
         <v>14.45283</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L9" s="19">
         <v>4.0580444</v>
       </c>
-      <c r="M7" s="20">
+      <c r="M9" s="11">
         <v>0.27637</v>
       </c>
-      <c r="N7" s="20">
+      <c r="N9" s="11">
         <v>0.517</v>
       </c>
-      <c r="O7" s="20">
-        <v>0.6845142972420715</v>
-      </c>
-      <c r="P7" s="11">
-        <v>70.7691181567296</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="10">
-        <v>450.5499877929688</v>
-      </c>
-      <c r="F8" s="16">
-        <v>1.045827085339202</v>
-      </c>
-      <c r="G8" s="19">
-        <v>-0.8960881426548249</v>
-      </c>
-      <c r="H8" s="19">
-        <v>1.917595834128675</v>
-      </c>
-      <c r="I8" s="19">
-        <v>3.033236167062363</v>
-      </c>
-      <c r="J8" s="19">
-        <v>1.267563815147088</v>
-      </c>
-      <c r="K8" s="19">
-        <v>17.067236</v>
-      </c>
-      <c r="L8" s="19">
-        <v>21.967487</v>
-      </c>
-      <c r="M8" s="20">
-        <v>1.30853</v>
-      </c>
-      <c r="N8" s="20">
-        <v>0.438</v>
-      </c>
-      <c r="O8" s="20">
-        <v>0.6694431500136655</v>
-      </c>
-      <c r="P8" s="11">
-        <v>43.75220418447689</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="O9" s="11">
+        <v>0.6770724856664994</v>
+      </c>
+      <c r="P9" s="10">
+        <v>71.9855898903477</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="10">
-        <v>456.010009765625</v>
-      </c>
-      <c r="F9" s="16">
-        <v>1.030753560326209</v>
-      </c>
-      <c r="G9" s="19">
-        <v>-0.03272594325371055</v>
-      </c>
-      <c r="H9" s="19">
-        <v>-0.5359935226777468</v>
-      </c>
-      <c r="I9" s="19">
-        <v>3.169732852629812</v>
-      </c>
-      <c r="J9" s="19">
-        <v>2.33036598692429</v>
-      </c>
-      <c r="K9" s="19">
-        <v>36.353783</v>
-      </c>
-      <c r="L9" s="19">
-        <v>-210.92924</v>
-      </c>
-      <c r="M9" s="20">
-        <v>0</v>
-      </c>
-      <c r="N9" s="20">
-        <v>0.875</v>
-      </c>
-      <c r="O9" s="20">
-        <v>1.983893205935662</v>
-      </c>
-      <c r="P9" s="11">
-        <v>52.55143811575783</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>6</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="10">
-        <v>373.3200073242188</v>
+      <c r="C10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="9">
+        <v>383</v>
       </c>
       <c r="F10" s="16">
-        <v>0.9280120270881818</v>
+        <v>0.9131836805605633</v>
       </c>
       <c r="G10" s="19">
-        <v>0.6975868904074245</v>
+        <v>0.6973082814018297</v>
       </c>
       <c r="H10" s="19">
-        <v>-0.388014448215243</v>
+        <v>-0.3894009559165209</v>
       </c>
       <c r="I10" s="19">
-        <v>2.535380266835807</v>
+        <v>2.53048400388374</v>
       </c>
       <c r="J10" s="19">
-        <v>1.451441773314647</v>
+        <v>1.405896115121946</v>
       </c>
       <c r="K10" s="19">
         <v>12.788835</v>
@@ -3341,52 +3448,52 @@
       <c r="L10" s="19">
         <v>5.4714427</v>
       </c>
-      <c r="M10" s="20">
+      <c r="M10" s="11">
         <v>0.42099</v>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="11">
         <v>0.537</v>
       </c>
-      <c r="O10" s="20">
-        <v>0.7909202912771811</v>
-      </c>
-      <c r="P10" s="11">
-        <v>73.26707177206802</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>71</v>
+      <c r="O10" s="11">
+        <v>0.8186359647727735</v>
+      </c>
+      <c r="P10" s="10">
+        <v>76.46062451838233</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
+      <c r="A11" s="10">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="10">
-        <v>60.18000030517578</v>
+      <c r="C11" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="9">
+        <v>60.95000076293945</v>
       </c>
       <c r="F11" s="16">
-        <v>0.89279273207993</v>
+        <v>0.8840484909760108</v>
       </c>
       <c r="G11" s="19">
-        <v>0.6406620673839032</v>
+        <v>0.6404730546000377</v>
       </c>
       <c r="H11" s="19">
-        <v>0.6228436896122007</v>
+        <v>0.6217370841682853</v>
       </c>
       <c r="I11" s="19">
-        <v>3.301541965792155</v>
+        <v>3.301463091132311</v>
       </c>
       <c r="J11" s="19">
-        <v>0.1655063153096189</v>
+        <v>0.1375094662802721</v>
       </c>
       <c r="K11" s="19">
         <v>17.433628</v>
@@ -3394,370 +3501,370 @@
       <c r="L11" s="19">
         <v>1.765813</v>
       </c>
-      <c r="M11" s="20">
+      <c r="M11" s="11">
         <v>0.10629</v>
       </c>
-      <c r="N11" s="20">
+      <c r="N11" s="11">
         <v>0.534</v>
       </c>
-      <c r="O11" s="20">
-        <v>0.1205501837073359</v>
-      </c>
-      <c r="P11" s="11">
-        <v>59.4623059577879</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>71</v>
+      <c r="O11" s="11">
+        <v>0.1460926867579575</v>
+      </c>
+      <c r="P11" s="10">
+        <v>62.08361938440773</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
+      <c r="A12" s="10">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="10">
-        <v>52.2400016784668</v>
+      <c r="C12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="9">
+        <v>252.0200042724609</v>
       </c>
       <c r="F12" s="16">
-        <v>0.8183590738877906</v>
+        <v>0.755980461423935</v>
       </c>
       <c r="G12" s="19">
-        <v>0.2781518668863611</v>
+        <v>0.5547590586732334</v>
       </c>
       <c r="H12" s="19">
-        <v>-0.6068661948028746</v>
+        <v>-0.5478321930464607</v>
       </c>
       <c r="I12" s="19">
-        <v>1.44187034396217</v>
+        <v>2.499068120313562</v>
       </c>
       <c r="J12" s="19">
-        <v>2.234498369760918</v>
+        <v>1.17216858012182</v>
       </c>
       <c r="K12" s="19">
+        <v>13.92751</v>
+      </c>
+      <c r="L12" s="19">
+        <v>3.090377</v>
+      </c>
+      <c r="M12" s="11">
+        <v>0.23452999</v>
+      </c>
+      <c r="N12" s="11">
+        <v>0.531</v>
+      </c>
+      <c r="O12" s="11">
+        <v>0.5971772702846527</v>
+      </c>
+      <c r="P12" s="10">
+        <v>75.07661475800667</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="9">
+        <v>125.0100021362305</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0.7368694140226644</v>
+      </c>
+      <c r="G13" s="19">
+        <v>0.3733288613132302</v>
+      </c>
+      <c r="H13" s="19">
+        <v>0.8887600291088082</v>
+      </c>
+      <c r="I13" s="19">
+        <v>0.6162893188916149</v>
+      </c>
+      <c r="J13" s="19">
+        <v>1.034124501725837</v>
+      </c>
+      <c r="K13" s="19">
+        <v>15.843312</v>
+      </c>
+      <c r="L13" s="19">
+        <v>3.939749</v>
+      </c>
+      <c r="M13" s="11">
+        <v>0.30667</v>
+      </c>
+      <c r="N13" s="11">
+        <v>0.377</v>
+      </c>
+      <c r="O13" s="11">
+        <v>0.2747017694018412</v>
+      </c>
+      <c r="P13" s="10">
+        <v>54.59762999280029</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="9">
+        <v>304.2300109863281</v>
+      </c>
+      <c r="F14" s="16">
+        <v>0.7292238367411182</v>
+      </c>
+      <c r="G14" s="19">
+        <v>-0.07867219284806844</v>
+      </c>
+      <c r="H14" s="19">
+        <v>1.239551443687976</v>
+      </c>
+      <c r="I14" s="19">
+        <v>0.6684586243450589</v>
+      </c>
+      <c r="J14" s="19">
+        <v>1.142229466739286</v>
+      </c>
+      <c r="K14" s="19">
+        <v>20.706474</v>
+      </c>
+      <c r="L14" s="19">
+        <v>32.69876</v>
+      </c>
+      <c r="M14" s="11">
+        <v>0.89489</v>
+      </c>
+      <c r="N14" s="11">
+        <v>0.14</v>
+      </c>
+      <c r="O14" s="11">
+        <v>0.4222264736326597</v>
+      </c>
+      <c r="P14" s="10">
+        <v>46.34797987795092</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="9">
+        <v>50.86999893188477</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0.7249665256704423</v>
+      </c>
+      <c r="G15" s="19">
+        <v>0.2786777736586866</v>
+      </c>
+      <c r="H15" s="19">
+        <v>-0.6091106029769495</v>
+      </c>
+      <c r="I15" s="19">
+        <v>1.43960814089404</v>
+      </c>
+      <c r="J15" s="19">
+        <v>1.925665410609893</v>
+      </c>
+      <c r="K15" s="19">
         <v>48.887848</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L15" s="19">
         <v>2.7368805</v>
       </c>
-      <c r="M12" s="20">
+      <c r="M15" s="11">
         <v>0.06315</v>
       </c>
-      <c r="N12" s="20">
+      <c r="N15" s="11">
         <v>0.4</v>
       </c>
-      <c r="O12" s="20">
-        <v>1.382769088039109</v>
-      </c>
-      <c r="P12" s="11">
-        <v>49.23910788407265</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>9</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="10">
-        <v>317.1199951171875</v>
-      </c>
-      <c r="F13" s="16">
-        <v>0.800318766414078</v>
-      </c>
-      <c r="G13" s="19">
-        <v>-0.07938398017442079</v>
-      </c>
-      <c r="H13" s="19">
-        <v>1.240108350439193</v>
-      </c>
-      <c r="I13" s="19">
-        <v>0.6711374143282868</v>
-      </c>
-      <c r="J13" s="19">
-        <v>1.378120869024543</v>
-      </c>
-      <c r="K13" s="19">
-        <v>20.706474</v>
-      </c>
-      <c r="L13" s="19">
-        <v>32.69876</v>
-      </c>
-      <c r="M13" s="20">
-        <v>0.89489</v>
-      </c>
-      <c r="N13" s="20">
-        <v>0.14</v>
-      </c>
-      <c r="O13" s="20">
-        <v>0.4956942282406638</v>
-      </c>
-      <c r="P13" s="11">
-        <v>52.62504863465143</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>10</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="10">
-        <v>246.5800018310547</v>
-      </c>
-      <c r="F14" s="16">
-        <v>0.7624710919123701</v>
-      </c>
-      <c r="G14" s="19">
-        <v>0.554925557705619</v>
-      </c>
-      <c r="H14" s="19">
-        <v>-0.5467062417077996</v>
-      </c>
-      <c r="I14" s="19">
-        <v>2.503924849329829</v>
-      </c>
-      <c r="J14" s="19">
-        <v>1.190270858760533</v>
-      </c>
-      <c r="K14" s="19">
-        <v>13.92751</v>
-      </c>
-      <c r="L14" s="19">
-        <v>3.090377</v>
-      </c>
-      <c r="M14" s="20">
-        <v>0.23452999</v>
-      </c>
-      <c r="N14" s="20">
-        <v>0.531</v>
-      </c>
-      <c r="O14" s="20">
-        <v>0.5587990396329847</v>
-      </c>
-      <c r="P14" s="11">
-        <v>72.09310366809038</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
-        <v>11</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" s="10">
-        <v>123.2200012207031</v>
-      </c>
-      <c r="F15" s="16">
-        <v>0.7393231750017529</v>
-      </c>
-      <c r="G15" s="19">
-        <v>0.3732475814323338</v>
-      </c>
-      <c r="H15" s="19">
-        <v>0.8869517519431653</v>
-      </c>
-      <c r="I15" s="19">
-        <v>0.6181521717520603</v>
-      </c>
-      <c r="J15" s="19">
-        <v>1.042960456078175</v>
-      </c>
-      <c r="K15" s="19">
-        <v>15.843312</v>
-      </c>
-      <c r="L15" s="19">
-        <v>3.939749</v>
-      </c>
-      <c r="M15" s="20">
-        <v>0.30667</v>
-      </c>
-      <c r="N15" s="20">
-        <v>0.377</v>
-      </c>
-      <c r="O15" s="20">
-        <v>0.2317073180032128</v>
-      </c>
-      <c r="P15" s="11">
-        <v>50.79501469184412</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>71</v>
+      <c r="O15" s="11">
+        <v>1.37281915384833</v>
+      </c>
+      <c r="P15" s="10">
+        <v>45.56155343779397</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
+      <c r="A16" s="10">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="10">
-        <v>144.9600067138672</v>
+      <c r="C16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="9">
+        <v>257.8699951171875</v>
       </c>
       <c r="F16" s="16">
-        <v>0.7127744495345537</v>
+        <v>0.6977508669323385</v>
       </c>
       <c r="G16" s="19">
-        <v>0.6286048285252418</v>
+        <v>1.14184289205193</v>
       </c>
       <c r="H16" s="19">
-        <v>0.5703723896787743</v>
+        <v>0.3579597051854377</v>
       </c>
       <c r="I16" s="19">
-        <v>1.544751130544684</v>
+        <v>0.004093049260078876</v>
       </c>
       <c r="J16" s="19">
-        <v>0.4996241132519498</v>
+        <v>0.8836470521046277</v>
       </c>
       <c r="K16" s="19">
+        <v>5.156936</v>
+      </c>
+      <c r="L16" s="19">
+        <v>2.0881312</v>
+      </c>
+      <c r="M16" s="11">
+        <v>0.46113998</v>
+      </c>
+      <c r="N16" s="11">
+        <v>0.118</v>
+      </c>
+      <c r="O16" s="11">
+        <v>0.2186102950476296</v>
+      </c>
+      <c r="P16" s="10">
+        <v>50.789745435265</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="9">
+        <v>148.3500061035156</v>
+      </c>
+      <c r="F17" s="16">
+        <v>0.6818469712923003</v>
+      </c>
+      <c r="G17" s="19">
+        <v>0.6283959871802424</v>
+      </c>
+      <c r="H17" s="19">
+        <v>0.5698222276440434</v>
+      </c>
+      <c r="I17" s="19">
+        <v>1.54182454976007</v>
+      </c>
+      <c r="J17" s="19">
+        <v>0.3986631192106872</v>
+      </c>
+      <c r="K17" s="19">
         <v>11.1643305</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L17" s="19">
         <v>2.3641071</v>
       </c>
-      <c r="M16" s="20">
+      <c r="M17" s="11">
         <v>0.22507</v>
       </c>
-      <c r="N16" s="20">
+      <c r="N17" s="11">
         <v>0.587</v>
       </c>
-      <c r="O16" s="20">
-        <v>0.1439541060028606</v>
-      </c>
-      <c r="P16" s="11">
-        <v>51.45032158137791</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="11">
-        <v>13</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="10">
-        <v>257.7999877929688</v>
-      </c>
-      <c r="F17" s="16">
-        <v>0.7102996068670262</v>
-      </c>
-      <c r="G17" s="19">
-        <v>1.142308394818012</v>
-      </c>
-      <c r="H17" s="19">
-        <v>0.3582884962973363</v>
-      </c>
-      <c r="I17" s="19">
-        <v>0.00561715317825387</v>
-      </c>
-      <c r="J17" s="19">
-        <v>0.9239746379018353</v>
-      </c>
-      <c r="K17" s="19">
-        <v>5.156936</v>
-      </c>
-      <c r="L17" s="19">
-        <v>2.0881312</v>
-      </c>
-      <c r="M17" s="20">
-        <v>0.46113998</v>
-      </c>
-      <c r="N17" s="20">
-        <v>0.118</v>
-      </c>
-      <c r="O17" s="20">
-        <v>0.2180771830944079</v>
-      </c>
-      <c r="P17" s="11">
-        <v>49.69254430637025</v>
-      </c>
-      <c r="Q17" s="9" t="s">
-        <v>71</v>
+      <c r="O17" s="11">
+        <v>0.1765594431862711</v>
+      </c>
+      <c r="P17" s="10">
+        <v>56.67336380436269</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
+      <c r="A18" s="10">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="10">
-        <v>43.15000152587891</v>
+      <c r="C18" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="9">
+        <v>44.29999923706055</v>
       </c>
       <c r="F18" s="16">
-        <v>0.6644246338578125</v>
+        <v>0.65533359802854</v>
       </c>
       <c r="G18" s="19">
-        <v>1.009649327332384</v>
+        <v>1.009105450580926</v>
       </c>
       <c r="H18" s="19">
-        <v>0.6080142824373397</v>
+        <v>0.6070412871410619</v>
       </c>
       <c r="I18" s="19">
-        <v>-0.2323883707990008</v>
+        <v>-0.2335545177618807</v>
       </c>
       <c r="J18" s="19">
-        <v>0.8146150688953749</v>
+        <v>0.7862493957775959</v>
       </c>
       <c r="K18" s="19">
         <v>8.974684</v>
@@ -3765,211 +3872,211 @@
       <c r="L18" s="19">
         <v>2.1246629</v>
       </c>
-      <c r="M18" s="20">
+      <c r="M18" s="11">
         <v>0.26659</v>
       </c>
-      <c r="N18" s="20">
+      <c r="N18" s="11">
         <v>0.092</v>
       </c>
-      <c r="O18" s="20">
-        <v>0.3803899927920582</v>
-      </c>
-      <c r="P18" s="11">
-        <v>64.09924941154749</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>71</v>
+      <c r="O18" s="11">
+        <v>0.4100597191058337</v>
+      </c>
+      <c r="P18" s="10">
+        <v>67.58723769045415</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="11">
+      <c r="A19" s="10">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="10">
-        <v>349.8299865722656</v>
+      <c r="C19" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="9">
+        <v>217.4400024414062</v>
       </c>
       <c r="F19" s="16">
-        <v>0.6491678543442235</v>
+        <v>0.642913878145724</v>
       </c>
       <c r="G19" s="19">
-        <v>-1.037295157007953</v>
+        <v>-1.16803265614949</v>
       </c>
       <c r="H19" s="19">
-        <v>0.6921504118861012</v>
+        <v>2.090926195613187</v>
       </c>
       <c r="I19" s="19">
-        <v>3.660012790878789</v>
+        <v>2.434488937217</v>
       </c>
       <c r="J19" s="19">
-        <v>0.7943895994775529</v>
+        <v>0.3513959516824146</v>
       </c>
       <c r="K19" s="19">
-        <v>51.00144</v>
+        <v>27.468435</v>
       </c>
       <c r="L19" s="19">
-        <v>16.159239</v>
-      </c>
-      <c r="M19" s="20">
-        <v>0.36465</v>
-      </c>
-      <c r="N19" s="20">
-        <v>1.039</v>
-      </c>
-      <c r="O19" s="20">
-        <v>0.07406355578300894</v>
-      </c>
-      <c r="P19" s="11">
-        <v>42.60895622098829</v>
-      </c>
-      <c r="Q19" s="9" t="s">
-        <v>71</v>
+        <v>26.95787</v>
+      </c>
+      <c r="M19" s="11">
+        <v>1.17211</v>
+      </c>
+      <c r="N19" s="11">
+        <v>1.059</v>
+      </c>
+      <c r="O19" s="11">
+        <v>0.2091375570176681</v>
+      </c>
+      <c r="P19" s="10">
+        <v>51.87290992384222</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
+      <c r="A20" s="10">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="10">
-        <v>185.2899932861328</v>
+      <c r="C20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="9">
+        <v>394.8800048828125</v>
       </c>
       <c r="F20" s="16">
-        <v>0.6320283217484153</v>
+        <v>0.6211872427553039</v>
       </c>
       <c r="G20" s="19">
-        <v>-0.4187454609174395</v>
+        <v>0.4503997425483208</v>
       </c>
       <c r="H20" s="19">
-        <v>1.270294671651068</v>
+        <v>-0.281168788472131</v>
       </c>
       <c r="I20" s="19">
-        <v>-0.153897054017106</v>
+        <v>0.2449969367779941</v>
       </c>
       <c r="J20" s="19">
-        <v>1.543876167378154</v>
+        <v>1.732033255307138</v>
       </c>
       <c r="K20" s="19">
+        <v>37.178402</v>
+      </c>
+      <c r="L20" s="19">
+        <v>2.4096098</v>
+      </c>
+      <c r="M20" s="11">
+        <v>0.06893000000000001</v>
+      </c>
+      <c r="N20" s="11">
+        <v>0.262</v>
+      </c>
+      <c r="O20" s="11">
+        <v>1.190890352688831</v>
+      </c>
+      <c r="P20" s="10">
+        <v>57.46312192736396</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="9">
+        <v>183.1600036621094</v>
+      </c>
+      <c r="F21" s="16">
+        <v>0.6206666197992553</v>
+      </c>
+      <c r="G21" s="19">
+        <v>-0.4176254149429469</v>
+      </c>
+      <c r="H21" s="19">
+        <v>1.269598605196775</v>
+      </c>
+      <c r="I21" s="19">
+        <v>-0.1551071811435872</v>
+      </c>
+      <c r="J21" s="19">
+        <v>1.506068900514945</v>
+      </c>
+      <c r="K21" s="19">
         <v>29.498423</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L21" s="19">
         <v>27.131872</v>
       </c>
-      <c r="M20" s="20">
+      <c r="M21" s="11">
         <v>1.06734</v>
       </c>
-      <c r="N20" s="20">
+      <c r="N21" s="11">
         <v>0.125</v>
       </c>
-      <c r="O20" s="20">
-        <v>0.8652493544755084</v>
-      </c>
-      <c r="P20" s="11">
-        <v>47.86720905212579</v>
-      </c>
-      <c r="Q20" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <v>17</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="10">
-        <v>383.2300109863281</v>
-      </c>
-      <c r="F21" s="16">
-        <v>0.619535760539793</v>
-      </c>
-      <c r="G21" s="19">
-        <v>0.4501860349599059</v>
-      </c>
-      <c r="H21" s="19">
-        <v>-0.2845602855479212</v>
-      </c>
-      <c r="I21" s="19">
-        <v>0.2465264953339178</v>
-      </c>
-      <c r="J21" s="19">
-        <v>1.72880349046238</v>
-      </c>
-      <c r="K21" s="19">
-        <v>37.178402</v>
-      </c>
-      <c r="L21" s="19">
-        <v>2.4096098</v>
-      </c>
-      <c r="M21" s="20">
-        <v>0.06893000000000001</v>
-      </c>
-      <c r="N21" s="20">
-        <v>0.262</v>
-      </c>
-      <c r="O21" s="20">
-        <v>1.061539451583414</v>
-      </c>
-      <c r="P21" s="11">
-        <v>50.31973399182989</v>
-      </c>
-      <c r="Q21" s="9" t="s">
-        <v>71</v>
+      <c r="O21" s="11">
+        <v>0.8691904851962537</v>
+      </c>
+      <c r="P21" s="10">
+        <v>45.70079166564376</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
+      <c r="A22" s="10">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="10">
-        <v>828.3800048828125</v>
+      <c r="C22" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="9">
+        <v>816.6400146484375</v>
       </c>
       <c r="F22" s="16">
-        <v>0.6150520982814308</v>
+        <v>0.614697530909641</v>
       </c>
       <c r="G22" s="19">
-        <v>-2.008515620475403</v>
+        <v>-2.00619301406186</v>
       </c>
       <c r="H22" s="19">
-        <v>1.445201098845667</v>
+        <v>1.44495379566546</v>
       </c>
       <c r="I22" s="19">
-        <v>1.44633441951151</v>
+        <v>1.443279146607333</v>
       </c>
       <c r="J22" s="19">
-        <v>2.131187822619695</v>
+        <v>2.129417047402446</v>
       </c>
       <c r="K22" s="19">
         <v>59.523674</v>
@@ -3977,688 +4084,688 @@
       <c r="L22" s="19">
         <v>170.03279</v>
       </c>
-      <c r="M22" s="20">
+      <c r="M22" s="11">
         <v>3.7152898</v>
       </c>
-      <c r="N22" s="20">
+      <c r="N22" s="11">
         <v>0.485</v>
       </c>
-      <c r="O22" s="20">
-        <v>1.188071042052749</v>
-      </c>
-      <c r="P22" s="11">
-        <v>46.8563767849534</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>71</v>
+      <c r="O22" s="11">
+        <v>1.289155688602777</v>
+      </c>
+      <c r="P22" s="10">
+        <v>45.51038391392845</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
+      <c r="A23" s="10">
         <v>19</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="C23" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="9">
+        <v>335.4599914550781</v>
+      </c>
+      <c r="F23" s="16">
+        <v>0.5901870953607465</v>
+      </c>
+      <c r="G23" s="19">
+        <v>-1.035269699993656</v>
+      </c>
+      <c r="H23" s="19">
+        <v>0.6918677747956025</v>
+      </c>
+      <c r="I23" s="19">
+        <v>3.65452532511485</v>
+      </c>
+      <c r="J23" s="19">
+        <v>0.5987408763090507</v>
+      </c>
+      <c r="K23" s="19">
+        <v>51.00144</v>
+      </c>
+      <c r="L23" s="19">
+        <v>16.159239</v>
+      </c>
+      <c r="M23" s="11">
+        <v>0.36465</v>
+      </c>
+      <c r="N23" s="11">
+        <v>1.039</v>
+      </c>
+      <c r="O23" s="11">
+        <v>0.1031053244096263</v>
+      </c>
+      <c r="P23" s="10">
+        <v>39.33542623761151</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="9">
+        <v>65.23000335693359</v>
+      </c>
+      <c r="F24" s="16">
+        <v>0.5735127589824061</v>
+      </c>
+      <c r="G24" s="19">
+        <v>1.158282704287761</v>
+      </c>
+      <c r="H24" s="19">
+        <v>-0.530880398962122</v>
+      </c>
+      <c r="I24" s="19">
+        <v>-0.5376625905689411</v>
+      </c>
+      <c r="J24" s="19">
+        <v>1.464658120073164</v>
+      </c>
+      <c r="K24" s="19">
+        <v>12.1881895</v>
+      </c>
+      <c r="L24" s="19">
+        <v>1.4176866</v>
+      </c>
+      <c r="M24" s="11">
+        <v>-0.20358999</v>
+      </c>
+      <c r="N24" s="11">
+        <v>0.046</v>
+      </c>
+      <c r="O24" s="11">
+        <v>0.4885897720496382</v>
+      </c>
+      <c r="P24" s="10">
+        <v>50.92081052173538</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
+        <v>21</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="9">
+        <v>203.1600036621094</v>
+      </c>
+      <c r="F25" s="16">
+        <v>0.5703711900017872</v>
+      </c>
+      <c r="G25" s="19">
+        <v>0.5739051824927601</v>
+      </c>
+      <c r="H25" s="19">
+        <v>0.09445881119242867</v>
+      </c>
+      <c r="I25" s="19">
+        <v>1.700164229937877</v>
+      </c>
+      <c r="J25" s="19">
+        <v>0.3985343265505681</v>
+      </c>
+      <c r="K25" s="19">
+        <v>37.579845</v>
+      </c>
+      <c r="L25" s="19">
+        <v>1.4633226</v>
+      </c>
+      <c r="M25" s="11">
+        <v>0.034930002</v>
+      </c>
+      <c r="N25" s="11">
+        <v>0.525</v>
+      </c>
+      <c r="O25" s="11">
+        <v>0.1639168565252822</v>
+      </c>
+      <c r="P25" s="10">
+        <v>54.29840659296417</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="9">
+        <v>108.2799987792969</v>
+      </c>
+      <c r="F26" s="16">
+        <v>0.5489362776832575</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0.04715944415631249</v>
+      </c>
+      <c r="H26" s="19">
+        <v>1.24690817025771</v>
+      </c>
+      <c r="I26" s="19">
+        <v>0.1702776671833624</v>
+      </c>
+      <c r="J26" s="19">
+        <v>0.6583991726481068</v>
+      </c>
+      <c r="K26" s="19">
+        <v>20.065575</v>
+      </c>
+      <c r="L26" s="19">
+        <v>4.333084</v>
+      </c>
+      <c r="M26" s="11">
+        <v>0.20273</v>
+      </c>
+      <c r="N26" s="11">
+        <v>0.209</v>
+      </c>
+      <c r="O26" s="11">
+        <v>0.1443239902155196</v>
+      </c>
+      <c r="P26" s="10">
+        <v>51.23363878396148</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
+        <v>23</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="9">
+        <v>363.9200134277344</v>
+      </c>
+      <c r="F27" s="16">
+        <v>0.5486923755186792</v>
+      </c>
+      <c r="G27" s="19">
+        <v>1.072116586277995</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0.108429815961183</v>
+      </c>
+      <c r="I27" s="19">
+        <v>-0.3364619819956503</v>
+      </c>
+      <c r="J27" s="19">
+        <v>0.8347308098144417</v>
+      </c>
+      <c r="K27" s="19">
+        <v>9.919549</v>
+      </c>
+      <c r="L27" s="19">
+        <v>2.3296678</v>
+      </c>
+      <c r="M27" s="11">
+        <v>0.26511</v>
+      </c>
+      <c r="N27" s="11">
+        <v>0.003</v>
+      </c>
+      <c r="O27" s="11">
+        <v>0.1794453676755525</v>
+      </c>
+      <c r="P27" s="10">
+        <v>46.7170899072394</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
         <v>24</v>
       </c>
-      <c r="E23" s="10">
-        <v>220.7799987792969</v>
-      </c>
-      <c r="F23" s="16">
-        <v>0.6100796515776822</v>
-      </c>
-      <c r="G23" s="19">
-        <v>-1.170006294227404</v>
-      </c>
-      <c r="H23" s="19">
-        <v>2.092697909288749</v>
-      </c>
-      <c r="I23" s="19">
-        <v>2.437733206354793</v>
-      </c>
-      <c r="J23" s="19">
-        <v>0.2408236052349901</v>
-      </c>
-      <c r="K23" s="19">
-        <v>27.468435</v>
-      </c>
-      <c r="L23" s="19">
-        <v>26.95787</v>
-      </c>
-      <c r="M23" s="20">
-        <v>1.17211</v>
-      </c>
-      <c r="N23" s="20">
-        <v>1.059</v>
-      </c>
-      <c r="O23" s="20">
-        <v>0.2113616702531329</v>
-      </c>
-      <c r="P23" s="11">
-        <v>54.5621857327529</v>
-      </c>
-      <c r="Q23" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
-        <v>20</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="10">
-        <v>200.4799957275391</v>
-      </c>
-      <c r="F24" s="16">
-        <v>0.5918335209552881</v>
-      </c>
-      <c r="G24" s="19">
-        <v>0.5737660980154189</v>
-      </c>
-      <c r="H24" s="19">
-        <v>0.0953765529458899</v>
-      </c>
-      <c r="I24" s="19">
-        <v>1.703570297838407</v>
-      </c>
-      <c r="J24" s="19">
-        <v>0.4677466954614295</v>
-      </c>
-      <c r="K24" s="19">
-        <v>37.579845</v>
-      </c>
-      <c r="L24" s="19">
-        <v>1.4633226</v>
-      </c>
-      <c r="M24" s="20">
-        <v>0.034930002</v>
-      </c>
-      <c r="N24" s="20">
-        <v>0.525</v>
-      </c>
-      <c r="O24" s="20">
-        <v>0.1393850576835789</v>
-      </c>
-      <c r="P24" s="11">
-        <v>51.19880504338713</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="11">
-        <v>21</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" s="10">
-        <v>365.9299926757812</v>
-      </c>
-      <c r="F25" s="16">
-        <v>0.5874023171596411</v>
-      </c>
-      <c r="G25" s="19">
-        <v>1.072546138536891</v>
-      </c>
-      <c r="H25" s="19">
-        <v>0.1087413330435472</v>
-      </c>
-      <c r="I25" s="19">
-        <v>-0.335214657738315</v>
-      </c>
-      <c r="J25" s="19">
-        <v>0.9624511366614479</v>
-      </c>
-      <c r="K25" s="19">
-        <v>9.919549</v>
-      </c>
-      <c r="L25" s="19">
-        <v>2.3296678</v>
-      </c>
-      <c r="M25" s="20">
-        <v>0.26511</v>
-      </c>
-      <c r="N25" s="20">
-        <v>0.003</v>
-      </c>
-      <c r="O25" s="20">
-        <v>0.1871047185723451</v>
-      </c>
-      <c r="P25" s="11">
-        <v>48.79596470513441</v>
-      </c>
-      <c r="Q25" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
-        <v>22</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="10">
-        <v>1025.900024414062</v>
-      </c>
-      <c r="F26" s="16">
-        <v>0.5678327859387831</v>
-      </c>
-      <c r="G26" s="19">
-        <v>0.355410981416705</v>
-      </c>
-      <c r="H26" s="19">
-        <v>0.8445110725953496</v>
-      </c>
-      <c r="I26" s="19">
-        <v>1.010973541330174</v>
-      </c>
-      <c r="J26" s="19">
-        <v>0.3281189738846935</v>
-      </c>
-      <c r="K26" s="19">
+      <c r="B28" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" s="9">
+        <v>335.0199890136719</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0.5120169274726588</v>
+      </c>
+      <c r="G28" s="19">
+        <v>-0.3028039656643364</v>
+      </c>
+      <c r="H28" s="19">
+        <v>1.453222706268985</v>
+      </c>
+      <c r="I28" s="19">
+        <v>1.451264745826552</v>
+      </c>
+      <c r="J28" s="19">
+        <v>0.07287576243576907</v>
+      </c>
+      <c r="K28" s="19">
+        <v>17.090237</v>
+      </c>
+      <c r="L28" s="19">
+        <v>6.8097687</v>
+      </c>
+      <c r="M28" s="11">
+        <v>0.48676</v>
+      </c>
+      <c r="N28" s="11">
+        <v>0.242</v>
+      </c>
+      <c r="O28" s="11">
+        <v>0.1050006457115242</v>
+      </c>
+      <c r="P28" s="10">
+        <v>41.25128707838135</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="9">
+        <v>211.0500030517578</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0.510909037209739</v>
+      </c>
+      <c r="G29" s="19">
+        <v>0.5704725459400877</v>
+      </c>
+      <c r="H29" s="19">
+        <v>-0.07100951697283031</v>
+      </c>
+      <c r="I29" s="19">
+        <v>2.401476207590426</v>
+      </c>
+      <c r="J29" s="19">
+        <v>-0.009005928225478943</v>
+      </c>
+      <c r="K29" s="19">
+        <v>19.409616</v>
+      </c>
+      <c r="L29" s="19">
+        <v>2.0853305</v>
+      </c>
+      <c r="M29" s="11">
+        <v>0.12231</v>
+      </c>
+      <c r="N29" s="11">
+        <v>0.535</v>
+      </c>
+      <c r="O29" s="11">
+        <v>0.1381140844875719</v>
+      </c>
+      <c r="P29" s="10">
+        <v>71.60464867022306</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="9">
+        <v>211.0399932861328</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0.5011540811883691</v>
+      </c>
+      <c r="G30" s="19">
+        <v>0.3412387796188353</v>
+      </c>
+      <c r="H30" s="19">
+        <v>0.7975087838914848</v>
+      </c>
+      <c r="I30" s="19">
+        <v>0.4621939909200928</v>
+      </c>
+      <c r="J30" s="19">
+        <v>0.4335871756394448</v>
+      </c>
+      <c r="K30" s="19">
+        <v>17.362167</v>
+      </c>
+      <c r="L30" s="19">
+        <v>3.1676524</v>
+      </c>
+      <c r="M30" s="11">
+        <v>0.17969999</v>
+      </c>
+      <c r="N30" s="11">
+        <v>0.28</v>
+      </c>
+      <c r="O30" s="11">
+        <v>0.2855805954504331</v>
+      </c>
+      <c r="P30" s="10">
+        <v>44.75446895013318</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="10">
+        <v>27</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="9">
+        <v>332.0299987792969</v>
+      </c>
+      <c r="F31" s="16">
+        <v>0.4985258414122538</v>
+      </c>
+      <c r="G31" s="19">
+        <v>-0.2912180256841578</v>
+      </c>
+      <c r="H31" s="19">
+        <v>1.453222706268985</v>
+      </c>
+      <c r="I31" s="19">
+        <v>1.451264745826552</v>
+      </c>
+      <c r="J31" s="19">
+        <v>0.0163195355875733</v>
+      </c>
+      <c r="K31" s="19">
+        <v>16.949085</v>
+      </c>
+      <c r="L31" s="19">
+        <v>6.7368755</v>
+      </c>
+      <c r="M31" s="11">
+        <v>0.48676</v>
+      </c>
+      <c r="N31" s="11">
+        <v>0.242</v>
+      </c>
+      <c r="O31" s="11">
+        <v>0.09521633271670149</v>
+      </c>
+      <c r="P31" s="10">
+        <v>40.11937904625471</v>
+      </c>
+      <c r="Q31" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="10">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" s="9">
+        <v>66.91999816894531</v>
+      </c>
+      <c r="F32" s="16">
+        <v>0.4967572247403558</v>
+      </c>
+      <c r="G32" s="19">
+        <v>0.4809430552343935</v>
+      </c>
+      <c r="H32" s="19">
+        <v>0.5470144888938514</v>
+      </c>
+      <c r="I32" s="19">
+        <v>0.2683138306624723</v>
+      </c>
+      <c r="J32" s="19">
+        <v>0.5849120378240136</v>
+      </c>
+      <c r="K32" s="19">
+        <v>14.762749</v>
+      </c>
+      <c r="L32" s="19">
+        <v>6.0942793</v>
+      </c>
+      <c r="M32" s="11">
+        <v>0.46598998</v>
+      </c>
+      <c r="N32" s="11">
+        <v>0.057</v>
+      </c>
+      <c r="O32" s="11">
+        <v>0.1168442617445413</v>
+      </c>
+      <c r="P32" s="10">
+        <v>59.72925627702396</v>
+      </c>
+      <c r="Q32" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="10">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" s="9">
+        <v>135.6000061035156</v>
+      </c>
+      <c r="F33" s="16">
+        <v>0.4959223397281417</v>
+      </c>
+      <c r="G33" s="19">
+        <v>0.6611287792074844</v>
+      </c>
+      <c r="H33" s="19">
+        <v>0.4311152541427781</v>
+      </c>
+      <c r="I33" s="19">
+        <v>0.3476596661669049</v>
+      </c>
+      <c r="J33" s="19">
+        <v>0.4588531416838872</v>
+      </c>
+      <c r="K33" s="19">
+        <v>9.331602999999999</v>
+      </c>
+      <c r="L33" s="19">
+        <v>3.3175094</v>
+      </c>
+      <c r="M33" s="11">
+        <v>0.29867</v>
+      </c>
+      <c r="N33" s="11">
+        <v>0.176</v>
+      </c>
+      <c r="O33" s="11">
+        <v>0.2874424165088272</v>
+      </c>
+      <c r="P33" s="10">
+        <v>69.12167514888199</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="10">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1002.559997558594</v>
+      </c>
+      <c r="F34" s="16">
+        <v>0.4910048017456742</v>
+      </c>
+      <c r="G34" s="19">
+        <v>0.3553341022329367</v>
+      </c>
+      <c r="H34" s="19">
+        <v>0.8433292888610314</v>
+      </c>
+      <c r="I34" s="19">
+        <v>1.008535319078445</v>
+      </c>
+      <c r="J34" s="19">
+        <v>0.07430650332922881</v>
+      </c>
+      <c r="K34" s="19">
         <v>16.078215</v>
       </c>
-      <c r="L26" s="19">
+      <c r="L34" s="19">
         <v>2.8559394</v>
       </c>
-      <c r="M26" s="20">
+      <c r="M34" s="11">
         <v>0.16902</v>
       </c>
-      <c r="N26" s="20">
+      <c r="N34" s="11">
         <v>0.425</v>
       </c>
-      <c r="O26" s="20">
-        <v>0.1958005555577293</v>
-      </c>
-      <c r="P26" s="11">
-        <v>46.37220956227538</v>
-      </c>
-      <c r="Q26" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <v>23</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" s="10">
-        <v>213.3200073242188</v>
-      </c>
-      <c r="F27" s="16">
-        <v>0.5491171187695041</v>
-      </c>
-      <c r="G27" s="19">
-        <v>0.3412782751836809</v>
-      </c>
-      <c r="H27" s="19">
-        <v>0.7986523025327146</v>
-      </c>
-      <c r="I27" s="19">
-        <v>0.4640682098581457</v>
-      </c>
-      <c r="J27" s="19">
-        <v>0.5915344303416645</v>
-      </c>
-      <c r="K27" s="19">
-        <v>17.362167</v>
-      </c>
-      <c r="L27" s="19">
-        <v>3.1676524</v>
-      </c>
-      <c r="M27" s="20">
-        <v>0.17969999</v>
-      </c>
-      <c r="N27" s="20">
-        <v>0.28</v>
-      </c>
-      <c r="O27" s="20">
-        <v>0.2912993435591271</v>
-      </c>
-      <c r="P27" s="11">
-        <v>47.97462276616847</v>
-      </c>
-      <c r="Q27" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
-        <v>24</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="10">
-        <v>206.1399993896484</v>
-      </c>
-      <c r="F28" s="16">
-        <v>0.533352257293393</v>
-      </c>
-      <c r="G28" s="19">
-        <v>0.570579143459755</v>
-      </c>
-      <c r="H28" s="19">
-        <v>-0.07067709858841417</v>
-      </c>
-      <c r="I28" s="19">
-        <v>2.406141348912362</v>
-      </c>
-      <c r="J28" s="19">
-        <v>0.06308862188571926</v>
-      </c>
-      <c r="K28" s="19">
-        <v>19.409616</v>
-      </c>
-      <c r="L28" s="19">
-        <v>2.0853305</v>
-      </c>
-      <c r="M28" s="20">
-        <v>0.12231</v>
-      </c>
-      <c r="N28" s="20">
-        <v>0.535</v>
-      </c>
-      <c r="O28" s="20">
-        <v>0.1067699093330563</v>
-      </c>
-      <c r="P28" s="11">
-        <v>66.76833011659021</v>
-      </c>
-      <c r="Q28" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
+      <c r="O34" s="11">
+        <v>0.1674029352190753</v>
+      </c>
+      <c r="P34" s="10">
+        <v>41.21221794549163</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="10">
+        <v>31</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" s="10">
-        <v>64.33999633789062</v>
-      </c>
-      <c r="F29" s="16">
-        <v>0.5282027886511581</v>
-      </c>
-      <c r="G29" s="19">
-        <v>1.158727027011848</v>
-      </c>
-      <c r="H29" s="19">
-        <v>-0.5337905990257678</v>
-      </c>
-      <c r="I29" s="19">
-        <v>-0.5368849216700472</v>
-      </c>
-      <c r="J29" s="19">
-        <v>1.315216895181842</v>
-      </c>
-      <c r="K29" s="19">
-        <v>12.1881895</v>
-      </c>
-      <c r="L29" s="19">
-        <v>1.4176866</v>
-      </c>
-      <c r="M29" s="20">
-        <v>-0.20358999</v>
-      </c>
-      <c r="N29" s="20">
-        <v>0.046</v>
-      </c>
-      <c r="O29" s="20">
-        <v>0.4426008641059385</v>
-      </c>
-      <c r="P29" s="11">
-        <v>47.64520347021701</v>
-      </c>
-      <c r="Q29" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <v>26</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="10">
-        <v>339.3500061035156</v>
-      </c>
-      <c r="F30" s="16">
-        <v>0.5229285580255999</v>
-      </c>
-      <c r="G30" s="19">
-        <v>-0.3036276540700492</v>
-      </c>
-      <c r="H30" s="19">
-        <v>1.453630962522038</v>
-      </c>
-      <c r="I30" s="19">
-        <v>1.455072946604182</v>
-      </c>
-      <c r="J30" s="19">
-        <v>0.107827238751593</v>
-      </c>
-      <c r="K30" s="19">
-        <v>17.090237</v>
-      </c>
-      <c r="L30" s="19">
-        <v>6.8097687</v>
-      </c>
-      <c r="M30" s="20">
-        <v>0.48676</v>
-      </c>
-      <c r="N30" s="20">
-        <v>0.242</v>
-      </c>
-      <c r="O30" s="20">
-        <v>0.1085467137341378</v>
-      </c>
-      <c r="P30" s="11">
-        <v>44.05795432950159</v>
-      </c>
-      <c r="Q30" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
-        <v>27</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" s="10">
-        <v>130.0299987792969</v>
-      </c>
-      <c r="F31" s="16">
-        <v>0.5156653081408378</v>
-      </c>
-      <c r="G31" s="19">
-        <v>0.661419949103957</v>
-      </c>
-      <c r="H31" s="19">
-        <v>0.4316473659713271</v>
-      </c>
-      <c r="I31" s="19">
-        <v>0.3496392555919275</v>
-      </c>
-      <c r="J31" s="19">
-        <v>0.5229386452600995</v>
-      </c>
-      <c r="K31" s="19">
-        <v>9.331602999999999</v>
-      </c>
-      <c r="L31" s="19">
-        <v>3.3175094</v>
-      </c>
-      <c r="M31" s="20">
-        <v>0.29867</v>
-      </c>
-      <c r="N31" s="20">
-        <v>0.176</v>
-      </c>
-      <c r="O31" s="20">
-        <v>0.2582317049762606</v>
-      </c>
-      <c r="P31" s="11">
-        <v>63.19252703015538</v>
-      </c>
-      <c r="Q31" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
-        <v>28</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="10">
-        <v>109.8199996948242</v>
-      </c>
-      <c r="F32" s="16">
-        <v>0.5063184103726105</v>
-      </c>
-      <c r="G32" s="19">
-        <v>0.04678928614268382</v>
-      </c>
-      <c r="H32" s="19">
-        <v>1.248403054439488</v>
-      </c>
-      <c r="I32" s="19">
-        <v>0.1718308610453409</v>
-      </c>
-      <c r="J32" s="19">
-        <v>0.5146874392104404</v>
-      </c>
-      <c r="K32" s="19">
-        <v>20.065575</v>
-      </c>
-      <c r="L32" s="19">
-        <v>4.333084</v>
-      </c>
-      <c r="M32" s="20">
-        <v>0.20273</v>
-      </c>
-      <c r="N32" s="20">
-        <v>0.209</v>
-      </c>
-      <c r="O32" s="20">
-        <v>0.1575604738025262</v>
-      </c>
-      <c r="P32" s="11">
-        <v>56.13397667971415</v>
-      </c>
-      <c r="Q32" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <v>29</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E33" s="10">
-        <v>335.4100036621094</v>
-      </c>
-      <c r="F33" s="16">
-        <v>0.5018179741863484</v>
-      </c>
-      <c r="G33" s="19">
-        <v>-0.2920267175013403</v>
-      </c>
-      <c r="H33" s="19">
-        <v>1.453630962522038</v>
-      </c>
-      <c r="I33" s="19">
-        <v>1.455072946604182</v>
-      </c>
-      <c r="J33" s="19">
-        <v>0.02585768938537925</v>
-      </c>
-      <c r="K33" s="19">
-        <v>16.949085</v>
-      </c>
-      <c r="L33" s="19">
-        <v>6.7368755</v>
-      </c>
-      <c r="M33" s="20">
-        <v>0.48676</v>
-      </c>
-      <c r="N33" s="20">
-        <v>0.242</v>
-      </c>
-      <c r="O33" s="20">
-        <v>0.09625379886078811</v>
-      </c>
-      <c r="P33" s="11">
-        <v>42.39037469130968</v>
-      </c>
-      <c r="Q33" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
-        <v>30</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" s="10">
-        <v>66.80999755859375</v>
-      </c>
-      <c r="F34" s="16">
-        <v>0.4929888030064835</v>
-      </c>
-      <c r="G34" s="19">
-        <v>0.4809824759140722</v>
-      </c>
-      <c r="H34" s="19">
-        <v>0.5492514822972634</v>
-      </c>
-      <c r="I34" s="19">
-        <v>0.2705090599165869</v>
-      </c>
-      <c r="J34" s="19">
-        <v>0.5693494355681936</v>
-      </c>
-      <c r="K34" s="19">
-        <v>14.762749</v>
-      </c>
-      <c r="L34" s="19">
-        <v>6.0942793</v>
-      </c>
-      <c r="M34" s="20">
-        <v>0.46598998</v>
-      </c>
-      <c r="N34" s="20">
-        <v>0.057</v>
-      </c>
-      <c r="O34" s="20">
-        <v>0.09497627373431516</v>
-      </c>
-      <c r="P34" s="11">
-        <v>59.30698300130248</v>
-      </c>
-      <c r="Q34" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="11">
-        <v>31</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="10">
-        <v>353.5499877929688</v>
+      <c r="E35" s="9">
+        <v>343.7000122070312</v>
       </c>
       <c r="F35" s="16">
-        <v>0.4680130850867577</v>
+        <v>0.484953108759984</v>
       </c>
       <c r="G35" s="19">
-        <v>0.1732156252788443</v>
+        <v>0.1736680666323963</v>
       </c>
       <c r="H35" s="19">
-        <v>-0.2038135142426307</v>
+        <v>-0.2059238925669261</v>
       </c>
       <c r="I35" s="19">
-        <v>0.5316467527062391</v>
+        <v>0.5294180420139372</v>
       </c>
       <c r="J35" s="19">
-        <v>1.290849210526087</v>
+        <v>1.349736518699687</v>
       </c>
       <c r="K35" s="19">
         <v>32.671864</v>
@@ -4666,497 +4773,497 @@
       <c r="L35" s="19">
         <v>4.917569</v>
       </c>
-      <c r="M35" s="20">
+      <c r="M35" s="11">
         <v>0.15286</v>
       </c>
-      <c r="N35" s="20">
+      <c r="N35" s="11">
         <v>0.204</v>
       </c>
-      <c r="O35" s="20">
-        <v>0.5789120698644297</v>
-      </c>
-      <c r="P35" s="11">
-        <v>57.18712657548074</v>
-      </c>
-      <c r="Q35" s="9" t="s">
-        <v>71</v>
+      <c r="O35" s="11">
+        <v>0.5249800548444385</v>
+      </c>
+      <c r="P35" s="10">
+        <v>50.56200297266238</v>
+      </c>
+      <c r="Q35" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="11">
+      <c r="A36" s="10">
         <v>32</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E36" s="10">
-        <v>199.0899963378906</v>
+      <c r="C36" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="9">
+        <v>161.8500061035156</v>
       </c>
       <c r="F36" s="16">
-        <v>0.4667421959176812</v>
+        <v>0.465477532179882</v>
       </c>
       <c r="G36" s="19">
-        <v>0.1588797765568509</v>
+        <v>-2.073567383421705</v>
       </c>
       <c r="H36" s="19">
-        <v>1.132158285325552</v>
+        <v>1.757526903283152</v>
       </c>
       <c r="I36" s="19">
-        <v>0.2281488491242122</v>
+        <v>0.3076846350650539</v>
       </c>
       <c r="J36" s="19">
-        <v>0.3393878808353534</v>
+        <v>2.006711087086158</v>
       </c>
       <c r="K36" s="19">
+        <v>61.02941</v>
+      </c>
+      <c r="L36" s="19">
+        <v>78.524124</v>
+      </c>
+      <c r="M36" s="11">
+        <v>1.17442</v>
+      </c>
+      <c r="N36" s="11">
+        <v>0.256</v>
+      </c>
+      <c r="O36" s="11">
+        <v>0.9956844531280942</v>
+      </c>
+      <c r="P36" s="10">
+        <v>52.07606850997672</v>
+      </c>
+      <c r="Q36" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" s="10">
+        <v>33</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="9">
+        <v>93.19999694824219</v>
+      </c>
+      <c r="F37" s="16">
+        <v>0.4524997378422164</v>
+      </c>
+      <c r="G37" s="19">
+        <v>0.1233593949113911</v>
+      </c>
+      <c r="H37" s="19">
+        <v>1.27624113445798</v>
+      </c>
+      <c r="I37" s="19">
+        <v>0.1102566321703408</v>
+      </c>
+      <c r="J37" s="19">
+        <v>0.2663104697625097</v>
+      </c>
+      <c r="K37" s="19">
+        <v>16.766905</v>
+      </c>
+      <c r="L37" s="19">
+        <v>18.876202</v>
+      </c>
+      <c r="M37" s="11">
+        <v>1.5956</v>
+      </c>
+      <c r="N37" s="11">
+        <v>0.162</v>
+      </c>
+      <c r="O37" s="11">
+        <v>-0.03033534403703042</v>
+      </c>
+      <c r="P37" s="10">
+        <v>52.09734157624205</v>
+      </c>
+      <c r="Q37" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="10">
+        <v>34</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="9">
+        <v>170.3899993896484</v>
+      </c>
+      <c r="F38" s="16">
+        <v>0.440759555325336</v>
+      </c>
+      <c r="G38" s="19">
+        <v>0.9022231494814106</v>
+      </c>
+      <c r="H38" s="19">
+        <v>0.23271775340534</v>
+      </c>
+      <c r="I38" s="19">
+        <v>0.6719689967812362</v>
+      </c>
+      <c r="J38" s="19">
+        <v>0.03705940870797476</v>
+      </c>
+      <c r="K38" s="19">
+        <v>8.115621000000001</v>
+      </c>
+      <c r="L38" s="19">
+        <v>1.5823956</v>
+      </c>
+      <c r="M38" s="11">
+        <v>0.21484</v>
+      </c>
+      <c r="N38" s="11">
+        <v>0.316</v>
+      </c>
+      <c r="O38" s="11">
+        <v>0.02257804032261901</v>
+      </c>
+      <c r="P38" s="10">
+        <v>42.16521648881469</v>
+      </c>
+      <c r="Q38" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="10">
+        <v>35</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="9">
+        <v>173.5</v>
+      </c>
+      <c r="F39" s="16">
+        <v>0.4405085822202104</v>
+      </c>
+      <c r="G39" s="19">
+        <v>0.5311684230925205</v>
+      </c>
+      <c r="H39" s="19">
+        <v>0.5916330364720993</v>
+      </c>
+      <c r="I39" s="19">
+        <v>0.005460567573198096</v>
+      </c>
+      <c r="J39" s="19">
+        <v>0.4414357034614989</v>
+      </c>
+      <c r="K39" s="19">
+        <v>15.65096</v>
+      </c>
+      <c r="L39" s="19">
+        <v>2.7135465</v>
+      </c>
+      <c r="M39" s="11">
+        <v>0.18416001</v>
+      </c>
+      <c r="N39" s="11">
+        <v>0.151</v>
+      </c>
+      <c r="O39" s="11">
+        <v>0.1366432500381114</v>
+      </c>
+      <c r="P39" s="10">
+        <v>46.56301517539105</v>
+      </c>
+      <c r="Q39" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="10">
+        <v>36</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" s="9">
+        <v>122.629997253418</v>
+      </c>
+      <c r="F40" s="16">
+        <v>0.4340583978673292</v>
+      </c>
+      <c r="G40" s="19">
+        <v>0.4462694962176907</v>
+      </c>
+      <c r="H40" s="19">
+        <v>0.858639166389934</v>
+      </c>
+      <c r="I40" s="19">
+        <v>-0.1392414226193376</v>
+      </c>
+      <c r="J40" s="19">
+        <v>0.3546799026581304</v>
+      </c>
+      <c r="K40" s="19">
+        <v>16.68579</v>
+      </c>
+      <c r="L40" s="19">
+        <v>3.8455532</v>
+      </c>
+      <c r="M40" s="11">
+        <v>0.25905</v>
+      </c>
+      <c r="N40" s="11">
+        <v>0.151</v>
+      </c>
+      <c r="O40" s="11">
+        <v>0.03709360894772473</v>
+      </c>
+      <c r="P40" s="10">
+        <v>56.29518689762154</v>
+      </c>
+      <c r="Q40" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="10">
+        <v>37</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="9">
+        <v>195.6900024414062</v>
+      </c>
+      <c r="F41" s="16">
+        <v>0.4294439848114883</v>
+      </c>
+      <c r="G41" s="19">
+        <v>0.1591036355655292</v>
+      </c>
+      <c r="H41" s="19">
+        <v>1.131462315672776</v>
+      </c>
+      <c r="I41" s="19">
+        <v>0.2261041410270051</v>
+      </c>
+      <c r="J41" s="19">
+        <v>0.2164389802319492</v>
+      </c>
+      <c r="K41" s="19">
         <v>22.82242</v>
       </c>
-      <c r="L36" s="19">
+      <c r="L41" s="19">
         <v>-14.45452</v>
       </c>
-      <c r="M36" s="20">
+      <c r="M41" s="11">
         <v>0</v>
       </c>
-      <c r="N36" s="20">
+      <c r="N41" s="11">
         <v>0.081</v>
       </c>
-      <c r="O36" s="20">
-        <v>0.1965092084231648</v>
-      </c>
-      <c r="P36" s="11">
-        <v>46.35909051426083</v>
-      </c>
-      <c r="Q36" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="11">
-        <v>33</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E37" s="10">
-        <v>178.1699981689453</v>
-      </c>
-      <c r="F37" s="16">
-        <v>0.4477288180983513</v>
-      </c>
-      <c r="G37" s="19">
-        <v>0.5314728704784768</v>
-      </c>
-      <c r="H37" s="19">
-        <v>0.5925654711155478</v>
-      </c>
-      <c r="I37" s="19">
-        <v>0.006886930317741128</v>
-      </c>
-      <c r="J37" s="19">
-        <v>0.4637084987608674</v>
-      </c>
-      <c r="K37" s="19">
-        <v>15.65096</v>
-      </c>
-      <c r="L37" s="19">
-        <v>2.7135465</v>
-      </c>
-      <c r="M37" s="20">
-        <v>0.18416001</v>
-      </c>
-      <c r="N37" s="20">
-        <v>0.151</v>
-      </c>
-      <c r="O37" s="20">
-        <v>0.1622488158579185</v>
-      </c>
-      <c r="P37" s="11">
-        <v>55.83527352983359</v>
-      </c>
-      <c r="Q37" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
-        <v>34</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="10">
-        <v>170.9299926757812</v>
-      </c>
-      <c r="F38" s="16">
-        <v>0.4410681089993199</v>
-      </c>
-      <c r="G38" s="19">
-        <v>-2.075996516227372</v>
-      </c>
-      <c r="H38" s="19">
-        <v>1.757725626426547</v>
-      </c>
-      <c r="I38" s="19">
-        <v>0.3093476814404498</v>
-      </c>
-      <c r="J38" s="19">
-        <v>1.926778350149424</v>
-      </c>
-      <c r="K38" s="19">
-        <v>61.02941</v>
-      </c>
-      <c r="L38" s="19">
-        <v>78.524124</v>
-      </c>
-      <c r="M38" s="20">
-        <v>1.17442</v>
-      </c>
-      <c r="N38" s="20">
-        <v>0.256</v>
-      </c>
-      <c r="O38" s="20">
-        <v>1.158752109332942</v>
-      </c>
-      <c r="P38" s="11">
-        <v>60.75206107681703</v>
-      </c>
-      <c r="Q38" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
-        <v>35</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="10">
-        <v>68.48000335693359</v>
-      </c>
-      <c r="F39" s="16">
-        <v>0.4371016338969793</v>
-      </c>
-      <c r="G39" s="19">
-        <v>0.4983270256452766</v>
-      </c>
-      <c r="H39" s="19">
-        <v>1.335327792217482</v>
-      </c>
-      <c r="I39" s="19">
-        <v>-0.5933645517218736</v>
-      </c>
-      <c r="J39" s="19">
-        <v>0.1425875363576892</v>
-      </c>
-      <c r="K39" s="19">
+      <c r="O41" s="11">
+        <v>0.1834114554521218</v>
+      </c>
+      <c r="P41" s="10">
+        <v>43.27725724915959</v>
+      </c>
+      <c r="Q41" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" s="10">
+        <v>38</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" s="9">
+        <v>405.8399963378906</v>
+      </c>
+      <c r="F42" s="16">
+        <v>0.4243031704991665</v>
+      </c>
+      <c r="G42" s="19">
+        <v>-0.8542144784553878</v>
+      </c>
+      <c r="H42" s="19">
+        <v>-0.4710398600225731</v>
+      </c>
+      <c r="I42" s="19">
+        <v>4.095406692860193</v>
+      </c>
+      <c r="J42" s="19">
+        <v>0.6133882503746573</v>
+      </c>
+      <c r="K42" s="19">
+        <v>105.25127</v>
+      </c>
+      <c r="L42" s="19">
+        <v>2.680677</v>
+      </c>
+      <c r="M42" s="11">
+        <v>0.019199999</v>
+      </c>
+      <c r="N42" s="11">
+        <v>1.134</v>
+      </c>
+      <c r="O42" s="11">
+        <v>0.3001857413090314</v>
+      </c>
+      <c r="P42" s="10">
+        <v>52.07497110059915</v>
+      </c>
+      <c r="Q42" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="10">
+        <v>39</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E43" s="9">
+        <v>69.56999969482422</v>
+      </c>
+      <c r="F43" s="16">
+        <v>0.4172887236867541</v>
+      </c>
+      <c r="G43" s="19">
+        <v>0.4981154868016052</v>
+      </c>
+      <c r="H43" s="19">
+        <v>1.332996393125508</v>
+      </c>
+      <c r="I43" s="19">
+        <v>-0.5941108124544012</v>
+      </c>
+      <c r="J43" s="19">
+        <v>0.07907200411018582</v>
+      </c>
+      <c r="K43" s="19">
         <v>14.242739</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L43" s="19">
         <v>-42.95995</v>
       </c>
-      <c r="M39" s="20">
+      <c r="M43" s="11">
         <v>0</v>
       </c>
-      <c r="N39" s="20">
+      <c r="N43" s="11">
         <v>0.012</v>
       </c>
-      <c r="O39" s="20">
-        <v>0.02880685463877186</v>
-      </c>
-      <c r="P39" s="11">
-        <v>51.28743876804131</v>
-      </c>
-      <c r="Q39" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
-        <v>36</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" s="10">
-        <v>160.8800048828125</v>
-      </c>
-      <c r="F40" s="16">
-        <v>0.4364809150357429</v>
-      </c>
-      <c r="G40" s="19">
-        <v>0.5356022363903666</v>
-      </c>
-      <c r="H40" s="19">
-        <v>-0.3601273510007506</v>
-      </c>
-      <c r="I40" s="19">
-        <v>0.01013621696190684</v>
-      </c>
-      <c r="J40" s="19">
-        <v>1.214372164415115</v>
-      </c>
-      <c r="K40" s="19">
+      <c r="O43" s="11">
+        <v>0.04214796324844805</v>
+      </c>
+      <c r="P43" s="10">
+        <v>54.99849936232818</v>
+      </c>
+      <c r="Q43" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" s="10">
+        <v>40</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" s="9">
+        <v>163.75</v>
+      </c>
+      <c r="F44" s="16">
+        <v>0.414764942700358</v>
+      </c>
+      <c r="G44" s="19">
+        <v>0.5354902146966187</v>
+      </c>
+      <c r="H44" s="19">
+        <v>-0.3613376701600568</v>
+      </c>
+      <c r="I44" s="19">
+        <v>0.008406708792284084</v>
+      </c>
+      <c r="J44" s="19">
+        <v>1.143970965041813</v>
+      </c>
+      <c r="K44" s="19">
         <v>16.927385</v>
       </c>
-      <c r="L40" s="19">
+      <c r="L44" s="19">
         <v>4.154594</v>
       </c>
-      <c r="M40" s="20">
+      <c r="M44" s="11">
         <v>0.26408002</v>
       </c>
-      <c r="N40" s="20">
+      <c r="N44" s="11">
         <v>0.053</v>
       </c>
-      <c r="O40" s="20">
-        <v>0.4460237484891296</v>
-      </c>
-      <c r="P40" s="11">
-        <v>59.99869880010746</v>
-      </c>
-      <c r="Q40" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="11">
-        <v>37</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E41" s="10">
-        <v>553.1099853515625</v>
-      </c>
-      <c r="F41" s="16">
-        <v>0.4293058129208898</v>
-      </c>
-      <c r="G41" s="19">
-        <v>0.3798662438630782</v>
-      </c>
-      <c r="H41" s="19">
-        <v>0.6536437959805237</v>
-      </c>
-      <c r="I41" s="19">
-        <v>-0.2344796805508564</v>
-      </c>
-      <c r="J41" s="19">
-        <v>0.6236898094982127</v>
-      </c>
-      <c r="K41" s="19">
-        <v>13.51341</v>
-      </c>
-      <c r="L41" s="19">
-        <v>7.7711396</v>
-      </c>
-      <c r="M41" s="20">
-        <v>0.63432</v>
-      </c>
-      <c r="N41" s="20">
-        <v>0.116</v>
-      </c>
-      <c r="O41" s="20">
-        <v>0.1715320986518754</v>
-      </c>
-      <c r="P41" s="11">
-        <v>53.20202656196939</v>
-      </c>
-      <c r="Q41" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="11">
-        <v>38</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" s="10">
-        <v>94.09999847412109</v>
-      </c>
-      <c r="F42" s="16">
-        <v>0.4195305819387309</v>
-      </c>
-      <c r="G42" s="19">
-        <v>0.1229773892076029</v>
-      </c>
-      <c r="H42" s="19">
-        <v>1.277834374892725</v>
-      </c>
-      <c r="I42" s="19">
-        <v>0.1115207585936172</v>
-      </c>
-      <c r="J42" s="19">
-        <v>0.1548355255474207</v>
-      </c>
-      <c r="K42" s="19">
-        <v>16.766905</v>
-      </c>
-      <c r="L42" s="19">
-        <v>18.876202</v>
-      </c>
-      <c r="M42" s="20">
-        <v>1.5956</v>
-      </c>
-      <c r="N42" s="20">
-        <v>0.162</v>
-      </c>
-      <c r="O42" s="20">
-        <v>-0.03500727702957618</v>
-      </c>
-      <c r="P42" s="11">
-        <v>55.47527199960736</v>
-      </c>
-      <c r="Q42" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="11">
-        <v>39</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" s="10">
-        <v>169.8999938964844</v>
-      </c>
-      <c r="F43" s="16">
-        <v>0.4177676892600736</v>
-      </c>
-      <c r="G43" s="19">
-        <v>0.9027367968796423</v>
-      </c>
-      <c r="H43" s="19">
-        <v>0.2325128591859716</v>
-      </c>
-      <c r="I43" s="19">
-        <v>0.6741195448566405</v>
-      </c>
-      <c r="J43" s="19">
-        <v>-0.04099832109602682</v>
-      </c>
-      <c r="K43" s="19">
-        <v>8.115621000000001</v>
-      </c>
-      <c r="L43" s="19">
-        <v>1.5823956</v>
-      </c>
-      <c r="M43" s="20">
-        <v>0.21484</v>
-      </c>
-      <c r="N43" s="20">
-        <v>0.316</v>
-      </c>
-      <c r="O43" s="20">
-        <v>0.01093936224717473</v>
-      </c>
-      <c r="P43" s="11">
-        <v>40.66719815195724</v>
-      </c>
-      <c r="Q43" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="11">
-        <v>40</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44" s="10">
-        <v>111.2799987792969</v>
-      </c>
-      <c r="F44" s="16">
-        <v>0.4130748168077866</v>
-      </c>
-      <c r="G44" s="19">
-        <v>0.687267097346562</v>
-      </c>
-      <c r="H44" s="19">
-        <v>0.6280679437254419</v>
-      </c>
-      <c r="I44" s="19">
-        <v>-0.1795692988776832</v>
-      </c>
-      <c r="J44" s="19">
-        <v>0.2560436550136999</v>
-      </c>
-      <c r="K44" s="19">
-        <v>11.168674</v>
-      </c>
-      <c r="L44" s="19">
-        <v>2.1566918</v>
-      </c>
-      <c r="M44" s="20">
-        <v>0.19399999</v>
-      </c>
-      <c r="N44" s="20">
-        <v>0.107</v>
-      </c>
-      <c r="O44" s="20">
-        <v>0.2040923493777529</v>
-      </c>
-      <c r="P44" s="11">
-        <v>43.82072393642192</v>
-      </c>
-      <c r="Q44" s="9" t="s">
-        <v>71</v>
+      <c r="O44" s="11">
+        <v>0.3788563884206089</v>
+      </c>
+      <c r="P44" s="10">
+        <v>63.06512965107687</v>
+      </c>
+      <c r="Q44" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -5222,101 +5329,101 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>150</v>
+      <c r="A4" s="7" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="20">
+      <c r="A6" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="11">
         <v>0.3</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>155</v>
+      <c r="C6" s="8" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="20">
+      <c r="A7" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="11">
         <v>0.25</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>157</v>
+      <c r="C7" s="8" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="B8" s="20">
+      <c r="A8" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="11">
         <v>0.15</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>159</v>
+      <c r="C8" s="8" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9" s="20">
+      <c r="A9" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="11">
         <v>0.3</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>161</v>
+      <c r="C9" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B10" s="20">
+        <v>163</v>
+      </c>
+      <c r="B10" s="11">
         <f>SUM(B6:B9)</f>
         <v>1.0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>163</v>
+      <c r="A12" s="7" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>165</v>
+      <c r="A15" s="7" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -5395,173 +5502,173 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="8" t="s">
-        <v>193</v>
+      <c r="A3" s="7" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>195</v>
       </c>
+      <c r="B4" s="8" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>35</v>
+      <c r="A5" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>198</v>
       </c>
+      <c r="B6" s="8" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>200</v>
       </c>
+      <c r="B7" s="8" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>72</v>
+      <c r="A8" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>26</v>
+      <c r="A9" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>204</v>
       </c>
+      <c r="B10" s="8" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="B11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>206</v>
       </c>
+      <c r="B11" s="8" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>206</v>
-      </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="8" t="s">
-        <v>212</v>
+      <c r="A16" s="7" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="8" t="s">
-        <v>221</v>
+      <c r="A22" s="7" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
-      <c r="A23" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="B23" s="21"/>
+      <c r="A23" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" s="20"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
-      <c r="A24" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="B24" s="21"/>
+      <c r="A24" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="B24" s="20"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
-      <c r="A25" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="B25" s="21"/>
+      <c r="A25" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" s="20"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
-      <c r="A26" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="B26" s="21"/>
+      <c r="A26" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="20"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
-      <c r="A27" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="B27" s="21"/>
+      <c r="A27" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B27" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5577,7 +5684,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI5"/>
+  <dimension ref="A1:BI6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -5585,184 +5692,184 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>393.7393798828125</v>
+        <v>400.1088256835938</v>
       </c>
       <c r="C1">
-        <v>400.1088256835938</v>
+        <v>381.1501770019531</v>
       </c>
       <c r="D1">
-        <v>381.1501770019531</v>
+        <v>369.2198791503906</v>
       </c>
       <c r="E1">
-        <v>369.2198791503906</v>
+        <v>390.8042297363281</v>
       </c>
       <c r="F1">
-        <v>390.8042297363281</v>
+        <v>394.9174194335938</v>
       </c>
       <c r="G1">
-        <v>394.9174194335938</v>
+        <v>408.3951416015625</v>
       </c>
       <c r="H1">
-        <v>408.3951416015625</v>
+        <v>403.4133605957031</v>
       </c>
       <c r="I1">
-        <v>403.4133605957031</v>
+        <v>418.6282348632812</v>
       </c>
       <c r="J1">
-        <v>418.6282348632812</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="K1">
-        <v>408.8244323730469</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="L1">
-        <v>418.0192260742188</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="M1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="N1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="O1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="P1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="Q1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="R1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="S1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="T1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="U1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="V1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="W1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="X1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="Y1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="Z1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="AA1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="AB1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="AC1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="AD1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="AE1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="AF1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="AG1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="AH1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="AI1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AJ1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AK1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AL1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AM1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AN1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AO1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AP1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AQ1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AR1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AS1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AT1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AU1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AV1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AW1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AX1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AY1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AZ1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="BA1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="BB1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="BC1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="BD1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="BE1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="BF1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="BG1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
       <c r="BH1">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="BI1">
-        <v>456.010009765625</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:61">
@@ -5770,184 +5877,184 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>863.8771362304688</v>
+        <v>949.134033203125</v>
       </c>
       <c r="C2">
-        <v>949.134033203125</v>
+        <v>935.74609375</v>
       </c>
       <c r="D2">
-        <v>935.74609375</v>
+        <v>891.7428588867188</v>
       </c>
       <c r="E2">
-        <v>891.7428588867188</v>
+        <v>995.7168579101562</v>
       </c>
       <c r="F2">
-        <v>995.7168579101562</v>
+        <v>981.4590454101562</v>
       </c>
       <c r="G2">
-        <v>981.4590454101562</v>
+        <v>1087.822631835938</v>
       </c>
       <c r="H2">
-        <v>1087.822631835938</v>
+        <v>1020.60302734375</v>
       </c>
       <c r="I2">
-        <v>1020.60302734375</v>
+        <v>1043.029541015625</v>
       </c>
       <c r="J2">
-        <v>1043.029541015625</v>
+        <v>1133.815551757812</v>
       </c>
       <c r="K2">
-        <v>1133.815551757812</v>
+        <v>1211.193725585938</v>
       </c>
       <c r="L2">
-        <v>1211.193725585938</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="M2">
-        <v>1051.608276367188</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="N2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="O2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="P2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="Q2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="R2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="S2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="T2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="U2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="V2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="W2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="X2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="Y2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="Z2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="AA2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="AB2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="AC2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="AD2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="AE2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="AF2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="AG2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="AH2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="AI2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="AJ2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AK2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="AL2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AM2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AN2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AO2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AP2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AQ2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AR2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AS2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AT2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AU2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AV2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AW2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AX2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="AY2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AZ2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="BA2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="BB2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="BC2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="BD2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="BE2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="BF2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="BG2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="BH2">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="BI2">
-        <v>958.72998046875</v>
+        <v>933.4400024414062</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -5955,184 +6062,184 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1559.319946289062</v>
+        <v>1642</v>
       </c>
       <c r="C3">
-        <v>1642</v>
+        <v>1646.5400390625</v>
       </c>
       <c r="D3">
-        <v>1646.5400390625</v>
+        <v>1643.22998046875</v>
       </c>
       <c r="E3">
-        <v>1643.22998046875</v>
+        <v>1881.510009765625</v>
       </c>
       <c r="F3">
-        <v>1881.510009765625</v>
+        <v>1980.099975585938</v>
       </c>
       <c r="G3">
-        <v>1980.099975585938</v>
+        <v>2107.860107421875</v>
       </c>
       <c r="H3">
-        <v>2107.860107421875</v>
+        <v>1991.550048828125</v>
       </c>
       <c r="I3">
-        <v>1991.550048828125</v>
+        <v>1958.800048828125</v>
       </c>
       <c r="J3">
-        <v>1958.800048828125</v>
+        <v>2184.75</v>
       </c>
       <c r="K3">
-        <v>2184.75</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="L3">
+        <v>1963.599975585938</v>
+      </c>
+      <c r="M3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="N3">
+        <v>2335</v>
+      </c>
+      <c r="O3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="P3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="Q3">
         <v>2273.72998046875</v>
       </c>
-      <c r="M3">
-        <v>1963.599975585938</v>
-      </c>
-      <c r="N3">
-        <v>1914.4599609375</v>
-      </c>
-      <c r="O3">
-        <v>2335</v>
-      </c>
-      <c r="P3">
-        <v>2090.7099609375</v>
-      </c>
-      <c r="Q3">
-        <v>2050.389892578125</v>
-      </c>
       <c r="R3">
-        <v>2273.72998046875</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="S3">
-        <v>2032.219970703125</v>
+        <v>1745</v>
       </c>
       <c r="T3">
-        <v>1745</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="U3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="V3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="W3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="X3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="Y3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="Z3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="AA3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="AB3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="AC3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="AD3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="AE3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="AF3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="AG3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="AH3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="AI3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="AJ3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="AK3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AL3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AM3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AN3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AO3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AP3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="AQ3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AR3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AS3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AT3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AU3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AV3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AW3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AX3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AY3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AZ3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="BA3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="BB3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="BC3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="BD3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="BE3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="BF3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="BG3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="BH3">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="BI3">
-        <v>1566.699951171875</v>
+        <v>1536.869995117188</v>
       </c>
     </row>
     <row r="4" spans="1:61">
@@ -6140,184 +6247,184 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>511.7200012207031</v>
+        <v>526.9299926757812</v>
       </c>
       <c r="C4">
-        <v>526.9299926757812</v>
+        <v>517.719970703125</v>
       </c>
       <c r="D4">
-        <v>517.719970703125</v>
+        <v>490.0899963378906</v>
       </c>
       <c r="E4">
-        <v>490.0899963378906</v>
+        <v>529.2899780273438</v>
       </c>
       <c r="F4">
-        <v>529.2899780273438</v>
+        <v>562.9299926757812</v>
       </c>
       <c r="G4">
-        <v>562.9299926757812</v>
+        <v>653.530029296875</v>
       </c>
       <c r="H4">
-        <v>653.530029296875</v>
+        <v>681.0800170898438</v>
       </c>
       <c r="I4">
-        <v>681.0800170898438</v>
+        <v>712.1300048828125</v>
       </c>
       <c r="J4">
-        <v>712.1300048828125</v>
+        <v>746.22998046875</v>
       </c>
       <c r="K4">
-        <v>746.22998046875</v>
+        <v>732.6199951171875</v>
       </c>
       <c r="L4">
-        <v>732.6199951171875</v>
+        <v>670.75</v>
       </c>
       <c r="M4">
-        <v>670.75</v>
+        <v>643.8300170898438</v>
       </c>
       <c r="N4">
-        <v>643.8300170898438</v>
+        <v>675.3900146484375</v>
       </c>
       <c r="O4">
-        <v>675.3900146484375</v>
+        <v>586.4500122070312</v>
       </c>
       <c r="P4">
-        <v>586.4500122070312</v>
+        <v>651.8800048828125</v>
       </c>
       <c r="Q4">
-        <v>651.8800048828125</v>
+        <v>638.719970703125</v>
       </c>
       <c r="R4">
-        <v>638.719970703125</v>
+        <v>598.3699951171875</v>
       </c>
       <c r="S4">
-        <v>598.3699951171875</v>
+        <v>539</v>
       </c>
       <c r="T4">
-        <v>539</v>
+        <v>577.4600219726562</v>
       </c>
       <c r="U4">
-        <v>577.4600219726562</v>
+        <v>532.0999755859375</v>
       </c>
       <c r="V4">
-        <v>532.0999755859375</v>
+        <v>550.2999877929688</v>
       </c>
       <c r="W4">
-        <v>550.2999877929688</v>
+        <v>578.0499877929688</v>
       </c>
       <c r="X4">
-        <v>578.0499877929688</v>
+        <v>582.5900268554688</v>
       </c>
       <c r="Y4">
-        <v>582.5900268554688</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="Z4">
-        <v>555.5499877929688</v>
+        <v>563.3200073242188</v>
       </c>
       <c r="AA4">
-        <v>563.3200073242188</v>
+        <v>513.8400268554688</v>
       </c>
       <c r="AB4">
-        <v>513.8400268554688</v>
+        <v>466.8099975585938</v>
       </c>
       <c r="AC4">
-        <v>466.8099975585938</v>
+        <v>477.2200012207031</v>
       </c>
       <c r="AD4">
-        <v>477.2200012207031</v>
+        <v>487.4200134277344</v>
       </c>
       <c r="AE4">
-        <v>487.4200134277344</v>
+        <v>548.3900146484375</v>
       </c>
       <c r="AF4">
-        <v>548.3900146484375</v>
+        <v>556.6699829101562</v>
       </c>
       <c r="AG4">
-        <v>556.6699829101562</v>
+        <v>558.2999877929688</v>
       </c>
       <c r="AH4">
-        <v>558.2999877929688</v>
+        <v>519.7999877929688</v>
       </c>
       <c r="AI4">
-        <v>519.7999877929688</v>
+        <v>497.9200134277344</v>
       </c>
       <c r="AJ4">
-        <v>497.9200134277344</v>
+        <v>463.510009765625</v>
       </c>
       <c r="AK4">
-        <v>463.510009765625</v>
+        <v>462.0400085449219</v>
       </c>
       <c r="AL4">
-        <v>462.0400085449219</v>
+        <v>533.0399780273438</v>
       </c>
       <c r="AM4">
-        <v>533.0399780273438</v>
+        <v>544.8400268554688</v>
       </c>
       <c r="AN4">
-        <v>544.8400268554688</v>
+        <v>527.219970703125</v>
       </c>
       <c r="AO4">
-        <v>527.219970703125</v>
+        <v>548.5599975585938</v>
       </c>
       <c r="AP4">
-        <v>548.5599975585938</v>
+        <v>519.1699829101562</v>
       </c>
       <c r="AQ4">
-        <v>519.1699829101562</v>
+        <v>451.5199890136719</v>
       </c>
       <c r="AR4">
-        <v>451.5199890136719</v>
+        <v>434.2999877929688</v>
       </c>
       <c r="AS4">
-        <v>434.2999877929688</v>
+        <v>438.3399963378906</v>
       </c>
       <c r="AT4">
-        <v>438.3399963378906</v>
+        <v>437.9299926757812</v>
       </c>
       <c r="AU4">
-        <v>437.9299926757812</v>
+        <v>454.1000061035156</v>
       </c>
       <c r="AV4">
-        <v>454.1000061035156</v>
+        <v>487.2900085449219</v>
       </c>
       <c r="AW4">
-        <v>487.2900085449219</v>
+        <v>508.7999877929688</v>
       </c>
       <c r="AX4">
-        <v>508.7999877929688</v>
+        <v>536.010009765625</v>
       </c>
       <c r="AY4">
-        <v>536.010009765625</v>
+        <v>496.1600036621094</v>
       </c>
       <c r="AZ4">
-        <v>496.1600036621094</v>
+        <v>462.0899963378906</v>
       </c>
       <c r="BA4">
-        <v>462.0899963378906</v>
+        <v>469.0499877929688</v>
       </c>
       <c r="BB4">
-        <v>469.0499877929688</v>
+        <v>459.4400024414062</v>
       </c>
       <c r="BC4">
-        <v>459.4400024414062</v>
+        <v>435.3800048828125</v>
       </c>
       <c r="BD4">
-        <v>435.3800048828125</v>
+        <v>450.75</v>
       </c>
       <c r="BE4">
-        <v>450.75</v>
+        <v>468.8800048828125</v>
       </c>
       <c r="BF4">
-        <v>468.8800048828125</v>
+        <v>462</v>
       </c>
       <c r="BG4">
-        <v>462</v>
+        <v>459.4500122070312</v>
       </c>
       <c r="BH4">
-        <v>459.4500122070312</v>
+        <v>450.5499877929688</v>
       </c>
       <c r="BI4">
-        <v>450.5499877929688</v>
+        <v>450.4400024414062</v>
       </c>
     </row>
     <row r="5" spans="1:61">
@@ -6325,184 +6432,369 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>254.8351593017578</v>
+        <v>257.3952941894531</v>
       </c>
       <c r="C5">
-        <v>257.3952941894531</v>
+        <v>252.8030090332031</v>
       </c>
       <c r="D5">
-        <v>252.8030090332031</v>
+        <v>256.9967956542969</v>
       </c>
       <c r="E5">
-        <v>256.9967956542969</v>
+        <v>254.6160125732422</v>
       </c>
       <c r="F5">
-        <v>254.6160125732422</v>
+        <v>257.6741943359375</v>
       </c>
       <c r="G5">
-        <v>257.6741943359375</v>
+        <v>246.20849609375</v>
       </c>
       <c r="H5">
-        <v>246.20849609375</v>
+        <v>243.1901702880859</v>
       </c>
       <c r="I5">
-        <v>243.1901702880859</v>
+        <v>238.8469543457031</v>
       </c>
       <c r="J5">
-        <v>238.8469543457031</v>
+        <v>235.3903045654297</v>
       </c>
       <c r="K5">
-        <v>235.3903045654297</v>
+        <v>242.8415069580078</v>
       </c>
       <c r="L5">
-        <v>242.8415069580078</v>
+        <v>242.7418823242188</v>
       </c>
       <c r="M5">
-        <v>242.7418823242188</v>
+        <v>241.4967041015625</v>
       </c>
       <c r="N5">
-        <v>241.4967041015625</v>
+        <v>254.0780792236328</v>
       </c>
       <c r="O5">
-        <v>254.0780792236328</v>
+        <v>258.3714904785156</v>
       </c>
       <c r="P5">
-        <v>258.3714904785156</v>
+        <v>265.2947387695312</v>
       </c>
       <c r="Q5">
-        <v>265.2947387695312</v>
+        <v>259.4373779296875</v>
       </c>
       <c r="R5">
-        <v>259.4373779296875</v>
+        <v>268.4027404785156</v>
       </c>
       <c r="S5">
-        <v>268.4027404785156</v>
+        <v>266.7291870117188</v>
       </c>
       <c r="T5">
-        <v>266.7291870117188</v>
+        <v>269.2793579101562</v>
       </c>
       <c r="U5">
-        <v>269.2793579101562</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="V5">
-        <v>265.1951293945312</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="W5">
-        <v>281.7909851074219</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="X5">
-        <v>280.1672668457031</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="Y5">
-        <v>279.6094055175781</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="Z5">
-        <v>294.6513061523438</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="AA5">
-        <v>300.2695617675781</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="AB5">
-        <v>291.5333251953125</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="AC5">
-        <v>299.1040954589844</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="AD5">
-        <v>308.4579162597656</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="AE5">
-        <v>312.1038208007812</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="AF5">
-        <v>313.5880737304688</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="AG5">
-        <v>309.7230529785156</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="AH5">
-        <v>304.0848388671875</v>
+        <v>301.33544921875</v>
       </c>
       <c r="AI5">
-        <v>301.33544921875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="AJ5">
-        <v>303.756103515625</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="AK5">
-        <v>297.7294006347656</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="AL5">
-        <v>300.1600036621094</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="AM5">
-        <v>310.5099792480469</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="AN5">
-        <v>312.8999938964844</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="AO5">
-        <v>307.5400085449219</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="AP5">
-        <v>308.7300109863281</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="AQ5">
-        <v>302.3900146484375</v>
+        <v>302.989990234375</v>
       </c>
       <c r="AR5">
-        <v>302.989990234375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="AS5">
-        <v>298.3099975585938</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AT5">
-        <v>314.9500122070312</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AU5">
-        <v>323.9200134277344</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AV5">
-        <v>330.2099914550781</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AW5">
-        <v>342.9200134277344</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AX5">
-        <v>341.6700134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AY5">
-        <v>347.1900024414062</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AZ5">
-        <v>350.0499877929688</v>
+        <v>346.260009765625</v>
       </c>
       <c r="BA5">
-        <v>346.260009765625</v>
+        <v>341.510009765625</v>
       </c>
       <c r="BB5">
-        <v>341.510009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="BC5">
-        <v>348.8599853515625</v>
+        <v>346</v>
       </c>
       <c r="BD5">
-        <v>346</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="BE5">
-        <v>340.4100036621094</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="BF5">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="BG5">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="BH5">
-        <v>352.3599853515625</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="BI5">
-        <v>358.9200134277344</v>
+        <v>361.989990234375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>265.4432067871094</v>
+      </c>
+      <c r="C6">
+        <v>257.445068359375</v>
+      </c>
+      <c r="D6">
+        <v>262.5610656738281</v>
+      </c>
+      <c r="E6">
+        <v>260.0978088378906</v>
+      </c>
+      <c r="F6">
+        <v>262.8602294921875</v>
+      </c>
+      <c r="G6">
+        <v>250.1749877929688</v>
+      </c>
+      <c r="H6">
+        <v>249.7860565185547</v>
+      </c>
+      <c r="I6">
+        <v>243.9420471191406</v>
+      </c>
+      <c r="J6">
+        <v>242.2467041015625</v>
+      </c>
+      <c r="K6">
+        <v>246.6147308349609</v>
+      </c>
+      <c r="L6">
+        <v>247.8413848876953</v>
+      </c>
+      <c r="M6">
+        <v>245.8368530273438</v>
+      </c>
+      <c r="N6">
+        <v>252.8676147460938</v>
+      </c>
+      <c r="O6">
+        <v>253.3662414550781</v>
+      </c>
+      <c r="P6">
+        <v>258.5121459960938</v>
+      </c>
+      <c r="Q6">
+        <v>254.9718475341797</v>
+      </c>
+      <c r="R6">
+        <v>264.146728515625</v>
+      </c>
+      <c r="S6">
+        <v>265.6226806640625</v>
+      </c>
+      <c r="T6">
+        <v>268.2554626464844</v>
+      </c>
+      <c r="U6">
+        <v>265.6027221679688</v>
+      </c>
+      <c r="V6">
+        <v>279.9135437011719</v>
+      </c>
+      <c r="W6">
+        <v>282.5263977050781</v>
+      </c>
+      <c r="X6">
+        <v>282.9651794433594</v>
+      </c>
+      <c r="Y6">
+        <v>296.0693359375</v>
+      </c>
+      <c r="Z6">
+        <v>302.5715026855469</v>
+      </c>
+      <c r="AA6">
+        <v>298.363037109375</v>
+      </c>
+      <c r="AB6">
+        <v>305.0148315429688</v>
+      </c>
+      <c r="AC6">
+        <v>311.7463989257812</v>
+      </c>
+      <c r="AD6">
+        <v>314.4490051269531</v>
+      </c>
+      <c r="AE6">
+        <v>318.8868408203125</v>
+      </c>
+      <c r="AF6">
+        <v>314.9576110839844</v>
+      </c>
+      <c r="AG6">
+        <v>311.4172973632812</v>
+      </c>
+      <c r="AH6">
+        <v>308.3955688476562</v>
+      </c>
+      <c r="AI6">
+        <v>311.4970703125</v>
+      </c>
+      <c r="AJ6">
+        <v>305.2142639160156</v>
+      </c>
+      <c r="AK6">
+        <v>307.8769836425781</v>
+      </c>
+      <c r="AL6">
+        <v>313.2223510742188</v>
+      </c>
+      <c r="AM6">
+        <v>315.6058349609375</v>
+      </c>
+      <c r="AN6">
+        <v>306.1915893554688</v>
+      </c>
+      <c r="AO6">
+        <v>311.75634765625</v>
+      </c>
+      <c r="AP6">
+        <v>296.9369506835938</v>
+      </c>
+      <c r="AQ6">
+        <v>298.432861328125</v>
+      </c>
+      <c r="AR6">
+        <v>297.3857421875</v>
+      </c>
+      <c r="AS6">
+        <v>319.4453125</v>
+      </c>
+      <c r="AT6">
+        <v>335.5013732910156</v>
+      </c>
+      <c r="AU6">
+        <v>347.2990417480469</v>
+      </c>
+      <c r="AV6">
+        <v>355.3968811035156</v>
+      </c>
+      <c r="AW6">
+        <v>354.4494934082031</v>
+      </c>
+      <c r="AX6">
+        <v>357.2019348144531</v>
+      </c>
+      <c r="AY6">
+        <v>365.2099914550781</v>
+      </c>
+      <c r="AZ6">
+        <v>360.75</v>
+      </c>
+      <c r="BA6">
+        <v>358.2300109863281</v>
+      </c>
+      <c r="BB6">
+        <v>360.7200012207031</v>
+      </c>
+      <c r="BC6">
+        <v>362.5199890136719</v>
+      </c>
+      <c r="BD6">
+        <v>354.8800048828125</v>
+      </c>
+      <c r="BE6">
+        <v>362.2699890136719</v>
+      </c>
+      <c r="BF6">
+        <v>363.5400085449219</v>
+      </c>
+      <c r="BG6">
+        <v>368.8299865722656</v>
+      </c>
+      <c r="BH6">
+        <v>373.3200073242188</v>
+      </c>
+      <c r="BI6">
+        <v>383</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$Q$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$S$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="234">
   <si>
     <t>DELL</t>
   </si>
@@ -228,6 +228,12 @@
     <t>Блок: momentum</t>
   </si>
   <si>
+    <t>Блок: earnings</t>
+  </si>
+  <si>
+    <t>Блок: risk</t>
+  </si>
+  <si>
     <t>P/E</t>
   </si>
   <si>
@@ -264,6 +270,48 @@
     <t>Phillips 66</t>
   </si>
   <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>APA Corporation</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>Nvidia</t>
+  </si>
+  <si>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>EOG Resources</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>Expedia Group</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
     <t>INCY</t>
   </si>
   <si>
@@ -273,13 +321,34 @@
     <t>Health Care</t>
   </si>
   <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>Expedia Group</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
+    <t>SCHW</t>
+  </si>
+  <si>
+    <t>Charles Schwab Corporation</t>
+  </si>
+  <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>Diamondback Energy</t>
+  </si>
+  <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
   </si>
   <si>
     <t>HPE</t>
@@ -288,31 +357,112 @@
     <t>Hewlett Packard Enterprise</t>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
-    <t>Financials</t>
-  </si>
-  <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>EOG Resources</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>APA Corporation</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>Nvidia</t>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>Waters Corporation</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>Hasbro</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>CF Industries</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>Amgen</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>Altria</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>Mastercard</t>
+  </si>
+  <si>
+    <t>CPAY</t>
+  </si>
+  <si>
+    <t>Corpay</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>Gen Digital</t>
+  </si>
+  <si>
+    <t>RJF</t>
+  </si>
+  <si>
+    <t>Raymond James Financial</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Visa Inc.</t>
+  </si>
+  <si>
+    <t>AMP</t>
+  </si>
+  <si>
+    <t>Ameriprise Financial</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
+  </si>
+  <si>
+    <t>TGT</t>
+  </si>
+  <si>
+    <t>Target Corporation</t>
+  </si>
+  <si>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>Newmont</t>
   </si>
   <si>
     <t>HUM</t>
@@ -321,159 +471,12 @@
     <t>Humana</t>
   </si>
   <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
-    <t>STX</t>
-  </si>
-  <si>
-    <t>Seagate Technology</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>Teradyne</t>
-  </si>
-  <si>
-    <t>CNC</t>
-  </si>
-  <si>
-    <t>Centene Corporation</t>
-  </si>
-  <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>Diamondback Energy</t>
-  </si>
-  <si>
-    <t>SCHW</t>
-  </si>
-  <si>
-    <t>Charles Schwab Corporation</t>
-  </si>
-  <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class A)</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class C)</t>
-  </si>
-  <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>CF Industries</t>
-  </si>
-  <si>
-    <t>Materials</t>
-  </si>
-  <si>
     <t>GS</t>
   </si>
   <si>
     <t>Goldman Sachs</t>
   </si>
   <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
-  </si>
-  <si>
-    <t>HAS</t>
-  </si>
-  <si>
-    <t>Hasbro</t>
-  </si>
-  <si>
-    <t>CINF</t>
-  </si>
-  <si>
-    <t>Cincinnati Financial</t>
-  </si>
-  <si>
-    <t>RJF</t>
-  </si>
-  <si>
-    <t>Raymond James Financial</t>
-  </si>
-  <si>
-    <t>NEM</t>
-  </si>
-  <si>
-    <t>Newmont</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>Booking Holdings</t>
-  </si>
-  <si>
-    <t>WAT</t>
-  </si>
-  <si>
-    <t>Waters Corporation</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>Altria</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>TGT</t>
-  </si>
-  <si>
-    <t>Target Corporation</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -501,7 +504,7 @@
     <t>quality</t>
   </si>
   <si>
-    <t>roe, gross_margin, net_margin, net_debt_ebitda</t>
+    <t>roe, gross_margin, net_margin</t>
   </si>
   <si>
     <t>growth</t>
@@ -513,7 +516,19 @@
     <t>momentum</t>
   </si>
   <si>
-    <t>mom_3m, mom_6m, mom_12m_1m, above_ma200, rsi_centered</t>
+    <t>mom_3m, mom_6m, mom_12m_1m, above_ma200, above_ma50, rsi_centered, dist_52w_high</t>
+  </si>
+  <si>
+    <t>earnings</t>
+  </si>
+  <si>
+    <t>earnings_surprise_pct</t>
+  </si>
+  <si>
+    <t>risk</t>
+  </si>
+  <si>
+    <t>volatility</t>
   </si>
   <si>
     <t>Сумма</t>
@@ -534,7 +549,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-02 00:18 UTC · данные на 2026-09-01 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-02 08:31 UTC · данные на 2026-09-01 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -615,7 +630,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-02 00:18 UTC</t>
+    <t>2026-09-02 08:31 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -630,7 +645,7 @@
     <t>Прошли фильтры</t>
   </si>
   <si>
-    <t>498</t>
+    <t>414</t>
   </si>
   <si>
     <t>Кандидат дня</t>
@@ -648,22 +663,25 @@
     <t>Запросов AV использовано</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Источник цен</t>
+  </si>
+  <si>
+    <t>yfinance</t>
+  </si>
+  <si>
+    <t>Фундаментал на дату</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>Версия состояния</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>Источник цен</t>
-  </si>
-  <si>
-    <t>yfinance</t>
-  </si>
-  <si>
-    <t>Фундаментал на дату</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>Версия состояния</t>
   </si>
   <si>
     <t>Регламент данных</t>
@@ -1994,12 +2012,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2007,13 +2025,13 @@
         <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2032,16 +2050,16 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="2:8">
@@ -2052,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H9" s="6">
         <v>6</v>
@@ -2060,7 +2078,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2089,7 +2107,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="8" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C16" s="9">
         <v>10000</v>
@@ -2097,7 +2115,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="8" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C17" s="10">
         <v>21</v>
@@ -2105,7 +2123,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="8" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C18" s="10">
         <v>14</v>
@@ -2113,7 +2131,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
@@ -2121,7 +2139,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="8" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C20" s="10">
         <v>21</v>
@@ -2129,39 +2147,39 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="8" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="8" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="8" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="8" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="8" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C25" s="11">
         <v>0.04156959301664937</v>
@@ -2169,7 +2187,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="8" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C26" s="10">
         <v>7</v>
@@ -2177,7 +2195,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="12" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C28" s="9">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2186,12 +2204,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="13" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="7" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -3066,7 +3084,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -3075,25 +3093,25 @@
     <col min="4" max="4" width="22.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="13" width="9.7109375" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="7" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="15" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>42</v>
       </c>
@@ -3145,2129 +3163,2375 @@
       <c r="Q4" s="14" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R4" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="9">
-        <v>1536.869995117188</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="F5" s="16">
-        <v>1.703226574613602</v>
+        <v>1.173222443227651</v>
       </c>
       <c r="G5" s="19">
-        <v>-0.3013957166684036</v>
+        <v>-0.4141537329218875</v>
       </c>
       <c r="H5" s="19">
-        <v>1.877025238685021</v>
+        <v>1.815920968500273</v>
       </c>
       <c r="I5" s="19">
-        <v>4.095406692860193</v>
+        <v>4.266205445946125</v>
       </c>
       <c r="J5" s="19">
-        <v>2.366926586712796</v>
+        <v>1.530335160883978</v>
       </c>
       <c r="K5" s="19">
-        <v>20.12168</v>
+        <v>0</v>
       </c>
       <c r="L5" s="19">
-        <v>14.060845</v>
-      </c>
-      <c r="M5" s="11">
-        <v>0.9164</v>
-      </c>
-      <c r="N5" s="11">
-        <v>3.716</v>
+        <v>-3.554186378362447</v>
+      </c>
+      <c r="M5" s="19">
+        <v>21.095882</v>
+      </c>
+      <c r="N5" s="19">
+        <v>10.456314</v>
       </c>
       <c r="O5" s="11">
-        <v>1.718151550404877</v>
-      </c>
-      <c r="P5" s="10">
-        <v>51.66385839684092</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.66638</v>
+      </c>
+      <c r="P5" s="11">
+        <v>3.457</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>1.459902343677745</v>
+      </c>
+      <c r="R5" s="10">
+        <v>50.44808337527054</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="9">
-        <v>933.4400024414062</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="F6" s="16">
-        <v>1.668009237315851</v>
+        <v>1.169478056376643</v>
       </c>
       <c r="G6" s="19">
-        <v>-0.3485326374484333</v>
+        <v>-0.3036268476905924</v>
       </c>
       <c r="H6" s="19">
-        <v>1.678368475369044</v>
+        <v>2.059914574583257</v>
       </c>
       <c r="I6" s="19">
-        <v>4.255133160878044</v>
+        <v>4.12758937324224</v>
       </c>
       <c r="J6" s="19">
-        <v>2.382356451921377</v>
+        <v>1.365693417616426</v>
       </c>
       <c r="K6" s="19">
-        <v>21.095882</v>
+        <v>0</v>
       </c>
       <c r="L6" s="19">
-        <v>10.456314</v>
-      </c>
-      <c r="M6" s="11">
-        <v>0.66638</v>
-      </c>
-      <c r="N6" s="11">
-        <v>3.457</v>
+        <v>-3.554186378362447</v>
+      </c>
+      <c r="M6" s="19">
+        <v>20.12168</v>
+      </c>
+      <c r="N6" s="19">
+        <v>14.060845</v>
       </c>
       <c r="O6" s="11">
-        <v>1.459902343677745</v>
-      </c>
-      <c r="P6" s="10">
-        <v>50.44808337526958</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.9164</v>
+      </c>
+      <c r="P6" s="11">
+        <v>3.716</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>1.718151550404877</v>
+      </c>
+      <c r="R6" s="10">
+        <v>51.66385839684092</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E7" s="9">
-        <v>450.4400024414062</v>
+        <v>361.989990234375</v>
       </c>
       <c r="F7" s="16">
-        <v>1.090813599677795</v>
+        <v>0.9574483751792983</v>
       </c>
       <c r="G7" s="19">
-        <v>-0.8945569446327866</v>
+        <v>0.7607938773386186</v>
       </c>
       <c r="H7" s="19">
-        <v>1.915872786242084</v>
+        <v>-0.6799927983681159</v>
       </c>
       <c r="I7" s="19">
-        <v>3.033358585171229</v>
+        <v>2.807045091949661</v>
       </c>
       <c r="J7" s="19">
-        <v>1.417362329104754</v>
+        <v>1.456840237759929</v>
       </c>
       <c r="K7" s="19">
-        <v>17.067236</v>
+        <v>0</v>
       </c>
       <c r="L7" s="19">
-        <v>21.967487</v>
-      </c>
-      <c r="M7" s="11">
-        <v>1.30853</v>
-      </c>
-      <c r="N7" s="11">
-        <v>0.438</v>
+        <v>0.1626701879863869</v>
+      </c>
+      <c r="M7" s="19">
+        <v>14.45283</v>
+      </c>
+      <c r="N7" s="19">
+        <v>4.0580444</v>
       </c>
       <c r="O7" s="11">
-        <v>0.798703509252862</v>
-      </c>
-      <c r="P7" s="10">
-        <v>43.73367487654892</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.27637</v>
+      </c>
+      <c r="P7" s="11">
+        <v>0.517</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>0.6770724856664994</v>
+      </c>
+      <c r="R7" s="10">
+        <v>71.98558989034771</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="9">
+        <v>383</v>
+      </c>
+      <c r="F8" s="16">
+        <v>0.9164697094795763</v>
+      </c>
+      <c r="G8" s="19">
+        <v>0.7506808295748838</v>
+      </c>
+      <c r="H8" s="19">
+        <v>-0.5735001363123757</v>
+      </c>
+      <c r="I8" s="19">
+        <v>2.376050228636491</v>
+      </c>
+      <c r="J8" s="19">
+        <v>1.453044472042306</v>
+      </c>
+      <c r="K8" s="19">
         <v>0</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="9">
-        <v>425</v>
-      </c>
-      <c r="F8" s="16">
-        <v>1.039859662658936</v>
-      </c>
-      <c r="G8" s="19">
-        <v>-0.03219460680095537</v>
-      </c>
-      <c r="H8" s="19">
-        <v>-0.5368449501454849</v>
-      </c>
-      <c r="I8" s="19">
-        <v>3.164697365105014</v>
-      </c>
-      <c r="J8" s="19">
-        <v>2.36341559156614</v>
-      </c>
-      <c r="K8" s="19">
-        <v>36.353783</v>
-      </c>
       <c r="L8" s="19">
-        <v>-210.92924</v>
-      </c>
-      <c r="M8" s="11">
-        <v>0</v>
-      </c>
-      <c r="N8" s="11">
-        <v>0.875</v>
+        <v>0.1581157412226887</v>
+      </c>
+      <c r="M8" s="19">
+        <v>12.788835</v>
+      </c>
+      <c r="N8" s="19">
+        <v>5.4714427</v>
       </c>
       <c r="O8" s="11">
-        <v>1.941310647213375</v>
-      </c>
-      <c r="P8" s="10">
-        <v>44.90408763111303</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.42099</v>
+      </c>
+      <c r="P8" s="11">
+        <v>0.537</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0.8186359647727735</v>
+      </c>
+      <c r="R8" s="10">
+        <v>76.46062451795444</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E9" s="9">
-        <v>361.989990234375</v>
+        <v>60.95000076293945</v>
       </c>
       <c r="F9" s="16">
-        <v>1.02821252620002</v>
+        <v>0.8389272175940845</v>
       </c>
       <c r="G9" s="19">
-        <v>0.7167153045991042</v>
+        <v>0.6441526575862923</v>
       </c>
       <c r="H9" s="19">
-        <v>-0.3064420778114862</v>
+        <v>0.6153462608193233</v>
       </c>
       <c r="I9" s="19">
-        <v>2.973519747014805</v>
+        <v>3.210676182303393</v>
       </c>
       <c r="J9" s="19">
-        <v>1.479268307403133</v>
+        <v>0.3052699134305471</v>
       </c>
       <c r="K9" s="19">
-        <v>14.45283</v>
+        <v>0</v>
       </c>
       <c r="L9" s="19">
-        <v>4.0580444</v>
-      </c>
-      <c r="M9" s="11">
-        <v>0.27637</v>
-      </c>
-      <c r="N9" s="11">
-        <v>0.517</v>
+        <v>0.2615929807312613</v>
+      </c>
+      <c r="M9" s="19">
+        <v>17.433628</v>
+      </c>
+      <c r="N9" s="19">
+        <v>1.765813</v>
       </c>
       <c r="O9" s="11">
-        <v>0.6770724856664994</v>
-      </c>
-      <c r="P9" s="10">
-        <v>71.9855898903477</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.10629</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0.534</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0.1460926867579575</v>
+      </c>
+      <c r="R9" s="10">
+        <v>62.0836193857231</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E10" s="9">
-        <v>383</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="F10" s="16">
-        <v>0.9131836805605633</v>
+        <v>0.768622075589411</v>
       </c>
       <c r="G10" s="19">
-        <v>0.6973082814018297</v>
+        <v>0.5245089923272498</v>
       </c>
       <c r="H10" s="19">
-        <v>-0.3894009559165209</v>
+        <v>-0.7869032513361915</v>
       </c>
       <c r="I10" s="19">
-        <v>2.53048400388374</v>
+        <v>2.345869080031544</v>
       </c>
       <c r="J10" s="19">
-        <v>1.405896115121946</v>
+        <v>1.278635709817943</v>
       </c>
       <c r="K10" s="19">
-        <v>12.788835</v>
+        <v>0</v>
       </c>
       <c r="L10" s="19">
-        <v>5.4714427</v>
-      </c>
-      <c r="M10" s="11">
-        <v>0.42099</v>
-      </c>
-      <c r="N10" s="11">
-        <v>0.537</v>
+        <v>0.3743416091369899</v>
+      </c>
+      <c r="M10" s="19">
+        <v>13.92751</v>
+      </c>
+      <c r="N10" s="19">
+        <v>3.090377</v>
       </c>
       <c r="O10" s="11">
-        <v>0.8186359647727735</v>
-      </c>
-      <c r="P10" s="10">
-        <v>76.46062451838233</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.23452999</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0.531</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0.5971772702846527</v>
+      </c>
+      <c r="R10" s="10">
+        <v>75.0766147580114</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="9">
-        <v>60.95000076293945</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="F11" s="16">
-        <v>0.8840484909760108</v>
+        <v>0.6797962078439569</v>
       </c>
       <c r="G11" s="19">
-        <v>0.6404730546000377</v>
+        <v>1.180991741996523</v>
       </c>
       <c r="H11" s="19">
-        <v>0.6217370841682853</v>
+        <v>0.5615290138085626</v>
       </c>
       <c r="I11" s="19">
-        <v>3.301463091132311</v>
+        <v>-0.283609995077921</v>
       </c>
       <c r="J11" s="19">
-        <v>0.1375094662802721</v>
+        <v>0.9885023787485725</v>
       </c>
       <c r="K11" s="19">
-        <v>17.433628</v>
+        <v>0</v>
       </c>
       <c r="L11" s="19">
-        <v>1.765813</v>
-      </c>
-      <c r="M11" s="11">
-        <v>0.10629</v>
-      </c>
-      <c r="N11" s="11">
-        <v>0.534</v>
+        <v>-0.3556744962059399</v>
+      </c>
+      <c r="M11" s="19">
+        <v>8.974684</v>
+      </c>
+      <c r="N11" s="19">
+        <v>2.1246629</v>
       </c>
       <c r="O11" s="11">
-        <v>0.1460926867579575</v>
-      </c>
-      <c r="P11" s="10">
-        <v>62.08361938440773</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.26659</v>
+      </c>
+      <c r="P11" s="11">
+        <v>0.092</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0.4100597191058337</v>
+      </c>
+      <c r="R11" s="10">
+        <v>67.58723769044478</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E12" s="9">
-        <v>252.0200042724609</v>
+        <v>217.4400024414062</v>
       </c>
       <c r="F12" s="16">
-        <v>0.755980461423935</v>
+        <v>0.6650491619952672</v>
       </c>
       <c r="G12" s="19">
-        <v>0.5547590586732334</v>
+        <v>-1.181029849974955</v>
       </c>
       <c r="H12" s="19">
-        <v>-0.5478321930464607</v>
+        <v>2.37007023642441</v>
       </c>
       <c r="I12" s="19">
-        <v>2.499068120313562</v>
+        <v>2.41302945894081</v>
       </c>
       <c r="J12" s="19">
-        <v>1.17216858012182</v>
+        <v>0.3611144854480505</v>
       </c>
       <c r="K12" s="19">
-        <v>13.92751</v>
+        <v>0</v>
       </c>
       <c r="L12" s="19">
-        <v>3.090377</v>
-      </c>
-      <c r="M12" s="11">
-        <v>0.23452999</v>
-      </c>
-      <c r="N12" s="11">
-        <v>0.531</v>
+        <v>-0.1713930070306825</v>
+      </c>
+      <c r="M12" s="19">
+        <v>27.468435</v>
+      </c>
+      <c r="N12" s="19">
+        <v>26.95787</v>
       </c>
       <c r="O12" s="11">
-        <v>0.5971772702846527</v>
-      </c>
-      <c r="P12" s="10">
-        <v>75.07661475800667</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.17211</v>
+      </c>
+      <c r="P12" s="11">
+        <v>1.059</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0.2091375570176681</v>
+      </c>
+      <c r="R12" s="10">
+        <v>51.87290992384082</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>9</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="E13" s="9">
-        <v>125.0100021362305</v>
+        <v>425</v>
       </c>
       <c r="F13" s="16">
-        <v>0.7368694140226644</v>
+        <v>0.6297064224653799</v>
       </c>
       <c r="G13" s="19">
-        <v>0.3733288613132302</v>
+        <v>-0.1432744592067679</v>
       </c>
       <c r="H13" s="19">
-        <v>0.8887600291088082</v>
+        <v>-0.9099368713420634</v>
       </c>
       <c r="I13" s="19">
-        <v>0.6162893188916149</v>
+        <v>2.974201127010152</v>
       </c>
       <c r="J13" s="19">
-        <v>1.034124501725837</v>
+        <v>1.608280043891485</v>
       </c>
       <c r="K13" s="19">
-        <v>15.843312</v>
+        <v>0</v>
       </c>
       <c r="L13" s="19">
-        <v>3.939749</v>
-      </c>
-      <c r="M13" s="11">
-        <v>0.30667</v>
-      </c>
-      <c r="N13" s="11">
-        <v>0.377</v>
+        <v>-2.082809480567236</v>
+      </c>
+      <c r="M13" s="19">
+        <v>36.353783</v>
+      </c>
+      <c r="N13" s="19">
+        <v>-210.92924</v>
       </c>
       <c r="O13" s="11">
-        <v>0.2747017694018412</v>
-      </c>
-      <c r="P13" s="10">
-        <v>54.59762999280029</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0.875</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>1.941310647213375</v>
+      </c>
+      <c r="R13" s="10">
+        <v>44.90408763111306</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E14" s="9">
-        <v>304.2300109863281</v>
+        <v>211.3399963378906</v>
       </c>
       <c r="F14" s="16">
-        <v>0.7292238367411182</v>
+        <v>0.6230705947850401</v>
       </c>
       <c r="G14" s="19">
-        <v>-0.07867219284806844</v>
+        <v>0.588790081488105</v>
       </c>
       <c r="H14" s="19">
-        <v>1.239551443687976</v>
+        <v>-0.6572941626990328</v>
       </c>
       <c r="I14" s="19">
-        <v>0.6684586243450589</v>
+        <v>4.12758937324224</v>
       </c>
       <c r="J14" s="19">
-        <v>1.142229466739286</v>
+        <v>0.07273741413375968</v>
       </c>
       <c r="K14" s="19">
-        <v>20.706474</v>
+        <v>0</v>
       </c>
       <c r="L14" s="19">
-        <v>32.69876</v>
-      </c>
-      <c r="M14" s="11">
-        <v>0.89489</v>
-      </c>
-      <c r="N14" s="11">
-        <v>0.14</v>
+        <v>0.5045059847861416</v>
+      </c>
+      <c r="M14" s="19">
+        <v>11.935252</v>
+      </c>
+      <c r="N14" s="19">
+        <v>1.2848284</v>
       </c>
       <c r="O14" s="11">
-        <v>0.4222264736326597</v>
-      </c>
-      <c r="P14" s="10">
-        <v>46.34797987795092</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.09031</v>
+      </c>
+      <c r="P14" s="11">
+        <v>11.11</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>0.09945135302649666</v>
+      </c>
+      <c r="R14" s="10">
+        <v>44.70214500676185</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E15" s="9">
-        <v>50.86999893188477</v>
+        <v>148.3500061035156</v>
       </c>
       <c r="F15" s="16">
-        <v>0.7249665256704423</v>
+        <v>0.6201529980865428</v>
       </c>
       <c r="G15" s="19">
-        <v>0.2786777736586866</v>
+        <v>0.626069891898576</v>
       </c>
       <c r="H15" s="19">
-        <v>-0.6091106029769495</v>
+        <v>0.4653179239592711</v>
       </c>
       <c r="I15" s="19">
-        <v>1.43960814089404</v>
+        <v>1.413985002184136</v>
       </c>
       <c r="J15" s="19">
-        <v>1.925665410609893</v>
+        <v>0.4707372508987441</v>
       </c>
       <c r="K15" s="19">
-        <v>48.887848</v>
+        <v>0</v>
       </c>
       <c r="L15" s="19">
-        <v>2.7368805</v>
-      </c>
-      <c r="M15" s="11">
-        <v>0.06315</v>
-      </c>
-      <c r="N15" s="11">
-        <v>0.4</v>
+        <v>0.2741552179013221</v>
+      </c>
+      <c r="M15" s="19">
+        <v>11.1643305</v>
+      </c>
+      <c r="N15" s="19">
+        <v>2.3641071</v>
       </c>
       <c r="O15" s="11">
-        <v>1.37281915384833</v>
-      </c>
-      <c r="P15" s="10">
-        <v>45.56155343779397</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.22507</v>
+      </c>
+      <c r="P15" s="11">
+        <v>0.587</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>0.1765594431862711</v>
+      </c>
+      <c r="R15" s="10">
+        <v>56.67336380437713</v>
+      </c>
+      <c r="S15" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>12</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E16" s="9">
-        <v>257.8699951171875</v>
+        <v>304.2300109863281</v>
       </c>
       <c r="F16" s="16">
-        <v>0.6977508669323385</v>
+        <v>0.6158846100801868</v>
       </c>
       <c r="G16" s="19">
-        <v>1.14184289205193</v>
+        <v>0.02815639480182512</v>
       </c>
       <c r="H16" s="19">
-        <v>0.3579597051854377</v>
+        <v>1.206665013812346</v>
       </c>
       <c r="I16" s="19">
-        <v>0.004093049260078876</v>
+        <v>0.5893325464410265</v>
       </c>
       <c r="J16" s="19">
-        <v>0.8836470521046277</v>
+        <v>0.872800024292623</v>
       </c>
       <c r="K16" s="19">
-        <v>5.156936</v>
+        <v>0</v>
       </c>
       <c r="L16" s="19">
-        <v>2.0881312</v>
-      </c>
-      <c r="M16" s="11">
-        <v>0.46113998</v>
-      </c>
-      <c r="N16" s="11">
-        <v>0.118</v>
+        <v>-0.5144739653764235</v>
+      </c>
+      <c r="M16" s="19">
+        <v>20.706474</v>
+      </c>
+      <c r="N16" s="19">
+        <v>32.69876</v>
       </c>
       <c r="O16" s="11">
-        <v>0.2186102950476296</v>
-      </c>
-      <c r="P16" s="10">
-        <v>50.789745435265</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.89489</v>
+      </c>
+      <c r="P16" s="11">
+        <v>0.14</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>0.4222265750834804</v>
+      </c>
+      <c r="R16" s="10">
+        <v>46.34797987544066</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>13</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="E17" s="9">
-        <v>148.3500061035156</v>
+        <v>257.8699951171875</v>
       </c>
       <c r="F17" s="16">
-        <v>0.6818469712923003</v>
+        <v>0.611534064567484</v>
       </c>
       <c r="G17" s="19">
-        <v>0.6283959871802424</v>
+        <v>1.299052042330012</v>
       </c>
       <c r="H17" s="19">
-        <v>0.5698222276440434</v>
+        <v>0.1657815718694057</v>
       </c>
       <c r="I17" s="19">
-        <v>1.54182454976007</v>
+        <v>-0.05430715947452922</v>
       </c>
       <c r="J17" s="19">
-        <v>0.3986631192106872</v>
+        <v>0.7021116596541814</v>
       </c>
       <c r="K17" s="19">
-        <v>11.1643305</v>
+        <v>0</v>
       </c>
       <c r="L17" s="19">
-        <v>2.3641071</v>
-      </c>
-      <c r="M17" s="11">
-        <v>0.22507</v>
-      </c>
-      <c r="N17" s="11">
-        <v>0.587</v>
+        <v>0.5056668910749345</v>
+      </c>
+      <c r="M17" s="19">
+        <v>5.156936</v>
+      </c>
+      <c r="N17" s="19">
+        <v>2.0881312</v>
       </c>
       <c r="O17" s="11">
-        <v>0.1765594431862711</v>
-      </c>
-      <c r="P17" s="10">
-        <v>56.67336380436269</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.46113998</v>
+      </c>
+      <c r="P17" s="11">
+        <v>0.118</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>0.2186102950476296</v>
+      </c>
+      <c r="R17" s="10">
+        <v>50.78974543525931</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>14</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="E18" s="9">
-        <v>44.29999923706055</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="F18" s="16">
-        <v>0.65533359802854</v>
+        <v>0.5789192396129739</v>
       </c>
       <c r="G18" s="19">
-        <v>1.009105450580926</v>
+        <v>0.3547542484834569</v>
       </c>
       <c r="H18" s="19">
-        <v>0.6070412871410619</v>
+        <v>0.5051665520920795</v>
       </c>
       <c r="I18" s="19">
-        <v>-0.2335545177618807</v>
+        <v>0.526532558122933</v>
       </c>
       <c r="J18" s="19">
-        <v>0.7862493957775959</v>
+        <v>0.8783623937716313</v>
       </c>
       <c r="K18" s="19">
-        <v>8.974684</v>
+        <v>0</v>
       </c>
       <c r="L18" s="19">
-        <v>2.1246629</v>
-      </c>
-      <c r="M18" s="11">
-        <v>0.26659</v>
-      </c>
-      <c r="N18" s="11">
-        <v>0.092</v>
+        <v>0.055137146741291</v>
+      </c>
+      <c r="M18" s="19">
+        <v>15.843312</v>
+      </c>
+      <c r="N18" s="19">
+        <v>3.939749</v>
       </c>
       <c r="O18" s="11">
-        <v>0.4100597191058337</v>
-      </c>
-      <c r="P18" s="10">
-        <v>67.58723769045415</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.30667</v>
+      </c>
+      <c r="P18" s="11">
+        <v>0.377</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>0.2747017694018412</v>
+      </c>
+      <c r="R18" s="10">
+        <v>54.59762999280029</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>15</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="E19" s="9">
-        <v>217.4400024414062</v>
+        <v>108.2799987792969</v>
       </c>
       <c r="F19" s="16">
-        <v>0.642913878145724</v>
+        <v>0.56819823093239</v>
       </c>
       <c r="G19" s="19">
-        <v>-1.16803265614949</v>
+        <v>0.08365196315212738</v>
       </c>
       <c r="H19" s="19">
-        <v>2.090926195613187</v>
+        <v>1.221326744496752</v>
       </c>
       <c r="I19" s="19">
-        <v>2.434488937217</v>
+        <v>0.1023029875964842</v>
       </c>
       <c r="J19" s="19">
-        <v>0.3513959516824146</v>
+        <v>0.6137225772405409</v>
       </c>
       <c r="K19" s="19">
-        <v>27.468435</v>
+        <v>0</v>
       </c>
       <c r="L19" s="19">
-        <v>26.95787</v>
-      </c>
-      <c r="M19" s="11">
-        <v>1.17211</v>
-      </c>
-      <c r="N19" s="11">
-        <v>1.059</v>
+        <v>0.9129608892018518</v>
+      </c>
+      <c r="M19" s="19">
+        <v>20.065575</v>
+      </c>
+      <c r="N19" s="19">
+        <v>4.333084</v>
       </c>
       <c r="O19" s="11">
-        <v>0.2091375570176681</v>
-      </c>
-      <c r="P19" s="10">
-        <v>51.87290992384222</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.20273</v>
+      </c>
+      <c r="P19" s="11">
+        <v>0.209</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>0.1443239902155196</v>
+      </c>
+      <c r="R19" s="10">
+        <v>51.23363878393255</v>
+      </c>
+      <c r="S19" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>16</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="E20" s="9">
-        <v>394.8800048828125</v>
+        <v>66.91999816894531</v>
       </c>
       <c r="F20" s="16">
-        <v>0.6211872427553039</v>
+        <v>0.5485608290322841</v>
       </c>
       <c r="G20" s="19">
-        <v>0.4503997425483208</v>
+        <v>0.4866550004416153</v>
       </c>
       <c r="H20" s="19">
-        <v>-0.281168788472131</v>
+        <v>0.6572130983041129</v>
       </c>
       <c r="I20" s="19">
-        <v>0.2449969367779941</v>
+        <v>0.2052523593343346</v>
       </c>
       <c r="J20" s="19">
-        <v>1.732033255307138</v>
+        <v>0.6514555734746182</v>
       </c>
       <c r="K20" s="19">
-        <v>37.178402</v>
+        <v>0</v>
       </c>
       <c r="L20" s="19">
-        <v>2.4096098</v>
-      </c>
-      <c r="M20" s="11">
-        <v>0.06893000000000001</v>
-      </c>
-      <c r="N20" s="11">
-        <v>0.262</v>
+        <v>0.5668017522224791</v>
+      </c>
+      <c r="M20" s="19">
+        <v>14.762749</v>
+      </c>
+      <c r="N20" s="19">
+        <v>6.0942793</v>
       </c>
       <c r="O20" s="11">
-        <v>1.190890352688831</v>
-      </c>
-      <c r="P20" s="10">
-        <v>57.46312192736396</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.46598998</v>
+      </c>
+      <c r="P20" s="11">
+        <v>0.057</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>0.1168442617445413</v>
+      </c>
+      <c r="R20" s="10">
+        <v>59.7292562771191</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="9">
-        <v>183.1600036621094</v>
+        <v>450.4400024414062</v>
       </c>
       <c r="F21" s="16">
-        <v>0.6206666197992553</v>
+        <v>0.5415297623462551</v>
       </c>
       <c r="G21" s="19">
-        <v>-0.4176254149429469</v>
+        <v>-0.9089117611651794</v>
       </c>
       <c r="H21" s="19">
-        <v>1.269598605196775</v>
+        <v>2.149283894198748</v>
       </c>
       <c r="I21" s="19">
-        <v>-0.1551071811435872</v>
+        <v>2.955409129427278</v>
       </c>
       <c r="J21" s="19">
-        <v>1.506068900514945</v>
+        <v>0.4064360291013725</v>
       </c>
       <c r="K21" s="19">
-        <v>29.498423</v>
+        <v>0</v>
       </c>
       <c r="L21" s="19">
-        <v>27.131872</v>
-      </c>
-      <c r="M21" s="11">
-        <v>1.06734</v>
-      </c>
-      <c r="N21" s="11">
-        <v>0.125</v>
+        <v>-3.554186378362447</v>
+      </c>
+      <c r="M21" s="19">
+        <v>17.067236</v>
+      </c>
+      <c r="N21" s="19">
+        <v>21.967487</v>
       </c>
       <c r="O21" s="11">
-        <v>0.8691904851962537</v>
-      </c>
-      <c r="P21" s="10">
-        <v>45.70079166564376</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.30853</v>
+      </c>
+      <c r="P21" s="11">
+        <v>0.438</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>0.798703509252862</v>
+      </c>
+      <c r="R21" s="10">
+        <v>43.73367487660393</v>
+      </c>
+      <c r="S21" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>18</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E22" s="9">
-        <v>816.6400146484375</v>
+        <v>211.0500030517578</v>
       </c>
       <c r="F22" s="16">
-        <v>0.614697530909641</v>
+        <v>0.5401046589977162</v>
       </c>
       <c r="G22" s="19">
-        <v>-2.00619301406186</v>
+        <v>0.556513719960729</v>
       </c>
       <c r="H22" s="19">
-        <v>1.44495379566546</v>
+        <v>-0.3268121485730144</v>
       </c>
       <c r="I22" s="19">
-        <v>1.443279146607333</v>
+        <v>2.250950359039762</v>
       </c>
       <c r="J22" s="19">
-        <v>2.129417047402446</v>
+        <v>0.3353731162324973</v>
       </c>
       <c r="K22" s="19">
-        <v>59.523674</v>
+        <v>0</v>
       </c>
       <c r="L22" s="19">
-        <v>170.03279</v>
-      </c>
-      <c r="M22" s="11">
-        <v>3.7152898</v>
-      </c>
-      <c r="N22" s="11">
-        <v>0.485</v>
+        <v>0.7563683731636086</v>
+      </c>
+      <c r="M22" s="19">
+        <v>19.409616</v>
+      </c>
+      <c r="N22" s="19">
+        <v>2.0853305</v>
       </c>
       <c r="O22" s="11">
-        <v>1.289155688602777</v>
-      </c>
-      <c r="P22" s="10">
-        <v>45.51038391392845</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.12231</v>
+      </c>
+      <c r="P22" s="11">
+        <v>0.535</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0.1381139908378988</v>
+      </c>
+      <c r="R22" s="10">
+        <v>71.60464863030431</v>
+      </c>
+      <c r="S22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>19</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E23" s="9">
-        <v>335.4599914550781</v>
+        <v>203.1600036621094</v>
       </c>
       <c r="F23" s="16">
-        <v>0.5901870953607465</v>
+        <v>0.5305610090884552</v>
       </c>
       <c r="G23" s="19">
-        <v>-1.035269699993656</v>
+        <v>0.6300105237233145</v>
       </c>
       <c r="H23" s="19">
-        <v>0.6918677747956025</v>
+        <v>-0.04505139788901939</v>
       </c>
       <c r="I23" s="19">
-        <v>3.65452532511485</v>
+        <v>1.570837850468294</v>
       </c>
       <c r="J23" s="19">
-        <v>0.5987408763090507</v>
+        <v>0.4508101730943636</v>
       </c>
       <c r="K23" s="19">
-        <v>51.00144</v>
+        <v>0</v>
       </c>
       <c r="L23" s="19">
-        <v>16.159239</v>
-      </c>
-      <c r="M23" s="11">
-        <v>0.36465</v>
-      </c>
-      <c r="N23" s="11">
-        <v>1.039</v>
+        <v>0.270683957113491</v>
+      </c>
+      <c r="M23" s="19">
+        <v>37.579845</v>
+      </c>
+      <c r="N23" s="19">
+        <v>1.4633226</v>
       </c>
       <c r="O23" s="11">
-        <v>0.1031053244096263</v>
-      </c>
-      <c r="P23" s="10">
-        <v>39.33542623761151</v>
-      </c>
-      <c r="Q23" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.034930002</v>
+      </c>
+      <c r="P23" s="11">
+        <v>0.525</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>0.1639168565252822</v>
+      </c>
+      <c r="R23" s="10">
+        <v>54.29840659207855</v>
+      </c>
+      <c r="S23" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>20</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="E24" s="9">
-        <v>65.23000335693359</v>
+        <v>183.1600036621094</v>
       </c>
       <c r="F24" s="16">
-        <v>0.5735127589824061</v>
+        <v>0.5175125565590661</v>
       </c>
       <c r="G24" s="19">
-        <v>1.158282704287761</v>
+        <v>-0.4163532752680855</v>
       </c>
       <c r="H24" s="19">
-        <v>-0.530880398962122</v>
+        <v>1.256179888265389</v>
       </c>
       <c r="I24" s="19">
-        <v>-0.5376625905689411</v>
+        <v>-0.2091710352067727</v>
       </c>
       <c r="J24" s="19">
-        <v>1.464658120073164</v>
+        <v>1.075325353994139</v>
       </c>
       <c r="K24" s="19">
-        <v>12.1881895</v>
+        <v>0</v>
       </c>
       <c r="L24" s="19">
-        <v>1.4176866</v>
-      </c>
-      <c r="M24" s="11">
-        <v>-0.20358999</v>
-      </c>
-      <c r="N24" s="11">
-        <v>0.046</v>
+        <v>-0.1072377352581109</v>
+      </c>
+      <c r="M24" s="19">
+        <v>29.498423</v>
+      </c>
+      <c r="N24" s="19">
+        <v>27.131872</v>
       </c>
       <c r="O24" s="11">
-        <v>0.4885897720496382</v>
-      </c>
-      <c r="P24" s="10">
-        <v>50.92081052173538</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.06734</v>
+      </c>
+      <c r="P24" s="11">
+        <v>0.125</v>
+      </c>
+      <c r="Q24" s="11">
+        <v>0.8691903396615654</v>
+      </c>
+      <c r="R24" s="10">
+        <v>45.70079166571557</v>
+      </c>
+      <c r="S24" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E25" s="9">
-        <v>203.1600036621094</v>
+        <v>50.86999893188477</v>
       </c>
       <c r="F25" s="16">
-        <v>0.5703711900017872</v>
+        <v>0.5168014817492296</v>
       </c>
       <c r="G25" s="19">
-        <v>0.5739051824927601</v>
+        <v>0.2630418482711242</v>
       </c>
       <c r="H25" s="19">
-        <v>0.09445881119242867</v>
+        <v>-0.6920579173680381</v>
       </c>
       <c r="I25" s="19">
-        <v>1.700164229937877</v>
+        <v>1.303910323344291</v>
       </c>
       <c r="J25" s="19">
-        <v>0.3985343265505681</v>
+        <v>1.350299201213216</v>
       </c>
       <c r="K25" s="19">
-        <v>37.579845</v>
+        <v>0</v>
       </c>
       <c r="L25" s="19">
-        <v>1.4633226</v>
-      </c>
-      <c r="M25" s="11">
-        <v>0.034930002</v>
-      </c>
-      <c r="N25" s="11">
-        <v>0.525</v>
+        <v>-1.030293729636665</v>
+      </c>
+      <c r="M25" s="19">
+        <v>48.887848</v>
+      </c>
+      <c r="N25" s="19">
+        <v>2.7368805</v>
       </c>
       <c r="O25" s="11">
-        <v>0.1639168565252822</v>
-      </c>
-      <c r="P25" s="10">
-        <v>54.29840659296417</v>
-      </c>
-      <c r="Q25" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.06315</v>
+      </c>
+      <c r="P25" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="Q25" s="11">
+        <v>1.37281915384833</v>
+      </c>
+      <c r="R25" s="10">
+        <v>45.56155343762108</v>
+      </c>
+      <c r="S25" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>22</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E26" s="9">
-        <v>108.2799987792969</v>
+        <v>405.8399963378906</v>
       </c>
       <c r="F26" s="16">
-        <v>0.5489362776832575</v>
+        <v>0.5126442628358368</v>
       </c>
       <c r="G26" s="19">
-        <v>0.04715944415631249</v>
+        <v>-0.9726355829702346</v>
       </c>
       <c r="H26" s="19">
-        <v>1.24690817025771</v>
+        <v>-0.4324969997184582</v>
       </c>
       <c r="I26" s="19">
-        <v>0.1702776671833624</v>
+        <v>4.12758937324224</v>
       </c>
       <c r="J26" s="19">
-        <v>0.6583991726481068</v>
+        <v>0.5890230104538892</v>
       </c>
       <c r="K26" s="19">
-        <v>20.065575</v>
+        <v>0</v>
       </c>
       <c r="L26" s="19">
-        <v>4.333084</v>
-      </c>
-      <c r="M26" s="11">
-        <v>0.20273</v>
-      </c>
-      <c r="N26" s="11">
-        <v>0.209</v>
+        <v>0.6617573284098744</v>
+      </c>
+      <c r="M26" s="19">
+        <v>105.25127</v>
+      </c>
+      <c r="N26" s="19">
+        <v>2.680677</v>
       </c>
       <c r="O26" s="11">
-        <v>0.1443239902155196</v>
-      </c>
-      <c r="P26" s="10">
-        <v>51.23363878396148</v>
-      </c>
-      <c r="Q26" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.019199999</v>
+      </c>
+      <c r="P26" s="11">
+        <v>1.134</v>
+      </c>
+      <c r="Q26" s="11">
+        <v>0.3001857413090314</v>
+      </c>
+      <c r="R26" s="10">
+        <v>52.07497110059915</v>
+      </c>
+      <c r="S26" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>23</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E27" s="9">
-        <v>363.9200134277344</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="F27" s="16">
-        <v>0.5486923755186792</v>
+        <v>0.5095092804132845</v>
       </c>
       <c r="G27" s="19">
-        <v>1.072116586277995</v>
+        <v>0.1351965712218133</v>
       </c>
       <c r="H27" s="19">
-        <v>0.108429815961183</v>
+        <v>1.640909999466138</v>
       </c>
       <c r="I27" s="19">
-        <v>-0.3364619819956503</v>
+        <v>0.03821118616689118</v>
       </c>
       <c r="J27" s="19">
-        <v>0.8347308098144417</v>
+        <v>0.3080471037980272</v>
       </c>
       <c r="K27" s="19">
-        <v>9.919549</v>
+        <v>0</v>
       </c>
       <c r="L27" s="19">
-        <v>2.3296678</v>
-      </c>
-      <c r="M27" s="11">
-        <v>0.26511</v>
-      </c>
-      <c r="N27" s="11">
-        <v>0.003</v>
+        <v>0.3800772843337862</v>
+      </c>
+      <c r="M27" s="19">
+        <v>16.766905</v>
+      </c>
+      <c r="N27" s="19">
+        <v>18.876202</v>
       </c>
       <c r="O27" s="11">
-        <v>0.1794453676755525</v>
-      </c>
-      <c r="P27" s="10">
-        <v>46.7170899072394</v>
-      </c>
-      <c r="Q27" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.5956</v>
+      </c>
+      <c r="P27" s="11">
+        <v>0.162</v>
+      </c>
+      <c r="Q27" s="11">
+        <v>-0.03033542100628361</v>
+      </c>
+      <c r="R27" s="10">
+        <v>52.09734154570462</v>
+      </c>
+      <c r="S27" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>24</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E28" s="9">
-        <v>335.0199890136719</v>
+        <v>135.6000061035156</v>
       </c>
       <c r="F28" s="16">
-        <v>0.5120169274726588</v>
+        <v>0.500513329849641</v>
       </c>
       <c r="G28" s="19">
-        <v>-0.3028039656643364</v>
+        <v>0.6758234888176574</v>
       </c>
       <c r="H28" s="19">
-        <v>1.453222706268985</v>
+        <v>0.2963342123961663</v>
       </c>
       <c r="I28" s="19">
-        <v>1.451264745826552</v>
+        <v>0.2761473880447703</v>
       </c>
       <c r="J28" s="19">
-        <v>0.07287576243576907</v>
+        <v>0.6771125751271094</v>
       </c>
       <c r="K28" s="19">
-        <v>17.090237</v>
+        <v>0</v>
       </c>
       <c r="L28" s="19">
-        <v>6.8097687</v>
-      </c>
-      <c r="M28" s="11">
-        <v>0.48676</v>
-      </c>
-      <c r="N28" s="11">
-        <v>0.242</v>
+        <v>0.03555272777992204</v>
+      </c>
+      <c r="M28" s="19">
+        <v>9.331602999999999</v>
+      </c>
+      <c r="N28" s="19">
+        <v>3.3175094</v>
       </c>
       <c r="O28" s="11">
-        <v>0.1050006457115242</v>
-      </c>
-      <c r="P28" s="10">
-        <v>41.25128707838135</v>
-      </c>
-      <c r="Q28" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.29867</v>
+      </c>
+      <c r="P28" s="11">
+        <v>0.176</v>
+      </c>
+      <c r="Q28" s="11">
+        <v>0.2874424165088272</v>
+      </c>
+      <c r="R28" s="10">
+        <v>69.12167518760248</v>
+      </c>
+      <c r="S28" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>25</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="E29" s="9">
-        <v>211.0500030517578</v>
+        <v>438.1199951171875</v>
       </c>
       <c r="F29" s="16">
-        <v>0.510909037209739</v>
+        <v>0.4969613458936494</v>
       </c>
       <c r="G29" s="19">
-        <v>0.5704725459400877</v>
+        <v>-0.2421358524050068</v>
       </c>
       <c r="H29" s="19">
-        <v>-0.07100951697283031</v>
+        <v>1.235722878380574</v>
       </c>
       <c r="I29" s="19">
-        <v>2.401476207590426</v>
+        <v>-0.09848432835705492</v>
       </c>
       <c r="J29" s="19">
-        <v>-0.009005928225478943</v>
+        <v>0.7320008486913989</v>
       </c>
       <c r="K29" s="19">
-        <v>19.409616</v>
+        <v>0</v>
       </c>
       <c r="L29" s="19">
-        <v>2.0853305</v>
-      </c>
-      <c r="M29" s="11">
-        <v>0.12231</v>
-      </c>
-      <c r="N29" s="11">
-        <v>0.535</v>
+        <v>0.6816814096751428</v>
+      </c>
+      <c r="M29" s="19">
+        <v>26.875078</v>
+      </c>
+      <c r="N29" s="19">
+        <v>20.000925</v>
       </c>
       <c r="O29" s="11">
-        <v>0.1381140844875719</v>
-      </c>
-      <c r="P29" s="10">
-        <v>71.60464867022306</v>
-      </c>
-      <c r="Q29" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.91473</v>
+      </c>
+      <c r="P29" s="11">
+        <v>0.095</v>
+      </c>
+      <c r="Q29" s="11">
+        <v>0.1777404730924301</v>
+      </c>
+      <c r="R29" s="10">
+        <v>66.50037520073629</v>
+      </c>
+      <c r="S29" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>26</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="E30" s="9">
-        <v>211.0399932861328</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="F30" s="16">
-        <v>0.5011540811883691</v>
+        <v>0.4795440739896837</v>
       </c>
       <c r="G30" s="19">
-        <v>0.3412387796188353</v>
+        <v>0.5501274300267243</v>
       </c>
       <c r="H30" s="19">
-        <v>0.7975087838914848</v>
+        <v>1.841068648189355</v>
       </c>
       <c r="I30" s="19">
-        <v>0.4621939909200928</v>
+        <v>-0.6294234346915084</v>
       </c>
       <c r="J30" s="19">
-        <v>0.4335871756394448</v>
+        <v>0.1015529609376061</v>
       </c>
       <c r="K30" s="19">
-        <v>17.362167</v>
+        <v>0</v>
       </c>
       <c r="L30" s="19">
-        <v>3.1676524</v>
-      </c>
-      <c r="M30" s="11">
-        <v>0.17969999</v>
-      </c>
-      <c r="N30" s="11">
-        <v>0.28</v>
+        <v>0.393580118240667</v>
+      </c>
+      <c r="M30" s="19">
+        <v>14.242739</v>
+      </c>
+      <c r="N30" s="19">
+        <v>-42.95995</v>
       </c>
       <c r="O30" s="11">
-        <v>0.2855805954504331</v>
-      </c>
-      <c r="P30" s="10">
-        <v>44.75446895013318</v>
-      </c>
-      <c r="Q30" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="P30" s="11">
+        <v>0.012</v>
+      </c>
+      <c r="Q30" s="11">
+        <v>0.04214796324844805</v>
+      </c>
+      <c r="R30" s="10">
+        <v>54.99849936221541</v>
+      </c>
+      <c r="S30" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>27</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="E31" s="9">
-        <v>332.0299987792969</v>
+        <v>363.9200134277344</v>
       </c>
       <c r="F31" s="16">
-        <v>0.4985258414122538</v>
+        <v>0.4750693645959413</v>
       </c>
       <c r="G31" s="19">
-        <v>-0.2912180256841578</v>
+        <v>1.233688344268854</v>
       </c>
       <c r="H31" s="19">
-        <v>1.453222706268985</v>
+        <v>-0.1209388667662471</v>
       </c>
       <c r="I31" s="19">
-        <v>1.451264745826552</v>
+        <v>-0.3789121155917646</v>
       </c>
       <c r="J31" s="19">
-        <v>0.0163195355875733</v>
+        <v>0.6291731353936107</v>
       </c>
       <c r="K31" s="19">
-        <v>16.949085</v>
+        <v>0</v>
       </c>
       <c r="L31" s="19">
-        <v>6.7368755</v>
-      </c>
-      <c r="M31" s="11">
-        <v>0.48676</v>
-      </c>
-      <c r="N31" s="11">
-        <v>0.242</v>
+        <v>0.6204403092273081</v>
+      </c>
+      <c r="M31" s="19">
+        <v>9.919549</v>
+      </c>
+      <c r="N31" s="19">
+        <v>2.3296678</v>
       </c>
       <c r="O31" s="11">
-        <v>0.09521633271670149</v>
-      </c>
-      <c r="P31" s="10">
-        <v>40.11937904625471</v>
-      </c>
-      <c r="Q31" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.26511</v>
+      </c>
+      <c r="P31" s="11">
+        <v>0.003</v>
+      </c>
+      <c r="Q31" s="11">
+        <v>0.1794453676755525</v>
+      </c>
+      <c r="R31" s="10">
+        <v>46.71708990738924</v>
+      </c>
+      <c r="S31" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>28</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E32" s="9">
-        <v>66.91999816894531</v>
+        <v>581.0999755859375</v>
       </c>
       <c r="F32" s="16">
-        <v>0.4967572247403558</v>
+        <v>0.4627749048861954</v>
       </c>
       <c r="G32" s="19">
-        <v>0.4809430552343935</v>
+        <v>-1.474085335991063</v>
       </c>
       <c r="H32" s="19">
-        <v>0.5470144888938514</v>
+        <v>2.898258236165586</v>
       </c>
       <c r="I32" s="19">
-        <v>0.2683138306624723</v>
+        <v>-0.1725926699877148</v>
       </c>
       <c r="J32" s="19">
-        <v>0.5849120378240136</v>
+        <v>0.4455811158118482</v>
       </c>
       <c r="K32" s="19">
-        <v>14.762749</v>
+        <v>0</v>
       </c>
       <c r="L32" s="19">
-        <v>6.0942793</v>
-      </c>
-      <c r="M32" s="11">
-        <v>0.46598998</v>
-      </c>
-      <c r="N32" s="11">
-        <v>0.057</v>
+        <v>0.9749610721165579</v>
+      </c>
+      <c r="M32" s="19">
+        <v>32.565643</v>
+      </c>
+      <c r="N32" s="19">
+        <v>93.07380000000001</v>
       </c>
       <c r="O32" s="11">
-        <v>0.1168442617445413</v>
-      </c>
-      <c r="P32" s="10">
-        <v>59.72925627702396</v>
-      </c>
-      <c r="Q32" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2.41202</v>
+      </c>
+      <c r="P32" s="11">
+        <v>0.141</v>
+      </c>
+      <c r="Q32" s="11">
+        <v>0.1120582336705458</v>
+      </c>
+      <c r="R32" s="10">
+        <v>55.70271450417012</v>
+      </c>
+      <c r="S32" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>29</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="E33" s="9">
-        <v>135.6000061035156</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="F33" s="16">
-        <v>0.4959223397281417</v>
+        <v>0.4591179149903291</v>
       </c>
       <c r="G33" s="19">
-        <v>0.6611287792074844</v>
+        <v>0.3093493865558575</v>
       </c>
       <c r="H33" s="19">
-        <v>0.4311152541427781</v>
+        <v>0.7050912458411566</v>
       </c>
       <c r="I33" s="19">
-        <v>0.3476596661669049</v>
+        <v>-0.1093741464017893</v>
       </c>
       <c r="J33" s="19">
-        <v>0.4588531416838872</v>
+        <v>0.6051390384954368</v>
       </c>
       <c r="K33" s="19">
-        <v>9.331602999999999</v>
+        <v>0</v>
       </c>
       <c r="L33" s="19">
-        <v>3.3175094</v>
-      </c>
-      <c r="M33" s="11">
-        <v>0.29867</v>
-      </c>
-      <c r="N33" s="11">
-        <v>0.176</v>
+        <v>0.5786311479764153</v>
+      </c>
+      <c r="M33" s="19">
+        <v>24.571085</v>
+      </c>
+      <c r="N33" s="19">
+        <v>7.5607543</v>
       </c>
       <c r="O33" s="11">
-        <v>0.2874424165088272</v>
-      </c>
-      <c r="P33" s="10">
-        <v>69.12167514888199</v>
-      </c>
-      <c r="Q33" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.29215</v>
+      </c>
+      <c r="P33" s="11">
+        <v>0.215</v>
+      </c>
+      <c r="Q33" s="11">
+        <v>0.2104837668337398</v>
+      </c>
+      <c r="R33" s="10">
+        <v>54.64609628677665</v>
+      </c>
+      <c r="S33" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>30</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="E34" s="9">
-        <v>1002.559997558594</v>
+        <v>30.02000045776367</v>
       </c>
       <c r="F34" s="16">
-        <v>0.4910048017456742</v>
+        <v>0.4558945757130657</v>
       </c>
       <c r="G34" s="19">
-        <v>0.3553341022329367</v>
+        <v>0.5180662182502601</v>
       </c>
       <c r="H34" s="19">
-        <v>0.8433292888610314</v>
+        <v>0.7480363136364186</v>
       </c>
       <c r="I34" s="19">
-        <v>1.008535319078445</v>
+        <v>-0.1877037530857071</v>
       </c>
       <c r="J34" s="19">
-        <v>0.07430650332922881</v>
+        <v>0.5399536999157968</v>
       </c>
       <c r="K34" s="19">
-        <v>16.078215</v>
+        <v>0</v>
       </c>
       <c r="L34" s="19">
-        <v>2.8559394</v>
-      </c>
-      <c r="M34" s="11">
-        <v>0.16902</v>
-      </c>
-      <c r="N34" s="11">
-        <v>0.425</v>
+        <v>0.2111118820020053</v>
+      </c>
+      <c r="M34" s="19">
+        <v>17.827587</v>
+      </c>
+      <c r="N34" s="19">
+        <v>6.9959407</v>
       </c>
       <c r="O34" s="11">
-        <v>0.1674029352190753</v>
-      </c>
-      <c r="P34" s="10">
-        <v>41.21221794549163</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.41944</v>
+      </c>
+      <c r="P34" s="11">
+        <v>0.063</v>
+      </c>
+      <c r="Q34" s="11">
+        <v>0.3533004092198408</v>
+      </c>
+      <c r="R34" s="10">
+        <v>61.00117942829461</v>
+      </c>
+      <c r="S34" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>31</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="E35" s="9">
-        <v>343.7000122070312</v>
+        <v>173.5</v>
       </c>
       <c r="F35" s="16">
-        <v>0.484953108759984</v>
+        <v>0.4465679571037485</v>
       </c>
       <c r="G35" s="19">
-        <v>0.1736680666323963</v>
+        <v>0.5395560519923884</v>
       </c>
       <c r="H35" s="19">
-        <v>-0.2059238925669261</v>
+        <v>0.565362548485465</v>
       </c>
       <c r="I35" s="19">
-        <v>0.5294180420139372</v>
+        <v>-0.05467446158502198</v>
       </c>
       <c r="J35" s="19">
-        <v>1.349736518699687</v>
+        <v>0.4226478530522234</v>
       </c>
       <c r="K35" s="19">
-        <v>32.671864</v>
+        <v>0</v>
       </c>
       <c r="L35" s="19">
-        <v>4.917569</v>
-      </c>
-      <c r="M35" s="11">
-        <v>0.15286</v>
-      </c>
-      <c r="N35" s="11">
-        <v>0.204</v>
+        <v>0.9102825923154756</v>
+      </c>
+      <c r="M35" s="19">
+        <v>15.65096</v>
+      </c>
+      <c r="N35" s="19">
+        <v>2.7135465</v>
       </c>
       <c r="O35" s="11">
-        <v>0.5249800548444385</v>
-      </c>
-      <c r="P35" s="10">
-        <v>50.56200297266238</v>
-      </c>
-      <c r="Q35" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.18416001</v>
+      </c>
+      <c r="P35" s="11">
+        <v>0.151</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>0.1366433636618272</v>
+      </c>
+      <c r="R35" s="10">
+        <v>46.56301517390835</v>
+      </c>
+      <c r="S35" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>32</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="E36" s="9">
-        <v>161.8500061035156</v>
+        <v>211.0399932861328</v>
       </c>
       <c r="F36" s="16">
-        <v>0.465477532179882</v>
+        <v>0.4448062335301415</v>
       </c>
       <c r="G36" s="19">
-        <v>-2.073567383421705</v>
+        <v>0.3606114262700158</v>
       </c>
       <c r="H36" s="19">
-        <v>1.757526903283152</v>
+        <v>0.7734905973148591</v>
       </c>
       <c r="I36" s="19">
-        <v>0.3076846350650539</v>
+        <v>0.3819632017249545</v>
       </c>
       <c r="J36" s="19">
-        <v>2.006711087086158</v>
+        <v>0.311066644900183</v>
       </c>
       <c r="K36" s="19">
-        <v>61.02941</v>
+        <v>0</v>
       </c>
       <c r="L36" s="19">
-        <v>78.524124</v>
-      </c>
-      <c r="M36" s="11">
-        <v>1.17442</v>
-      </c>
-      <c r="N36" s="11">
-        <v>0.256</v>
+        <v>0.5783663693465612</v>
+      </c>
+      <c r="M36" s="19">
+        <v>17.362167</v>
+      </c>
+      <c r="N36" s="19">
+        <v>3.1676524</v>
       </c>
       <c r="O36" s="11">
-        <v>0.9956844531280942</v>
-      </c>
-      <c r="P36" s="10">
-        <v>52.07606850997672</v>
-      </c>
-      <c r="Q36" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.17969999</v>
+      </c>
+      <c r="P36" s="11">
+        <v>0.28</v>
+      </c>
+      <c r="Q36" s="11">
+        <v>0.2855805954504331</v>
+      </c>
+      <c r="R36" s="10">
+        <v>44.75446895013088</v>
+      </c>
+      <c r="S36" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>33</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E37" s="9">
-        <v>93.19999694824219</v>
+        <v>372.6700134277344</v>
       </c>
       <c r="F37" s="16">
-        <v>0.4524997378422164</v>
+        <v>0.4258959445218294</v>
       </c>
       <c r="G37" s="19">
-        <v>0.1233593949113911</v>
+        <v>-0.8579418461106736</v>
       </c>
       <c r="H37" s="19">
-        <v>1.27624113445798</v>
+        <v>1.968378447518884</v>
       </c>
       <c r="I37" s="19">
-        <v>0.1102566321703408</v>
+        <v>-0.2192287351731601</v>
       </c>
       <c r="J37" s="19">
-        <v>0.2663104697625097</v>
+        <v>0.4827855919055765</v>
       </c>
       <c r="K37" s="19">
-        <v>16.766905</v>
+        <v>0</v>
       </c>
       <c r="L37" s="19">
-        <v>18.876202</v>
-      </c>
-      <c r="M37" s="11">
-        <v>1.5956</v>
-      </c>
-      <c r="N37" s="11">
-        <v>0.162</v>
+        <v>1.064745644315671</v>
+      </c>
+      <c r="M37" s="19">
+        <v>32.476597</v>
+      </c>
+      <c r="N37" s="19">
+        <v>20.222574</v>
       </c>
       <c r="O37" s="11">
-        <v>-0.03033534403703042</v>
-      </c>
-      <c r="P37" s="10">
-        <v>52.09734157624205</v>
-      </c>
-      <c r="Q37" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.6119</v>
+      </c>
+      <c r="P37" s="11">
+        <v>0.144</v>
+      </c>
+      <c r="Q37" s="11">
+        <v>0.1661514393863721</v>
+      </c>
+      <c r="R37" s="10">
+        <v>54.30594216676963</v>
+      </c>
+      <c r="S37" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E38" s="9">
-        <v>170.3899993896484</v>
+        <v>542.6400146484375</v>
       </c>
       <c r="F38" s="16">
-        <v>0.440759555325336</v>
+        <v>0.4237491075589168</v>
       </c>
       <c r="G38" s="19">
-        <v>0.9022231494814106</v>
+        <v>0.3931690320945501</v>
       </c>
       <c r="H38" s="19">
-        <v>0.23271775340534</v>
+        <v>0.6248071829755445</v>
       </c>
       <c r="I38" s="19">
-        <v>0.6719689967812362</v>
+        <v>-0.2867976137565587</v>
       </c>
       <c r="J38" s="19">
-        <v>0.03705940870797476</v>
+        <v>0.502739669790368</v>
       </c>
       <c r="K38" s="19">
-        <v>8.115621000000001</v>
+        <v>0</v>
       </c>
       <c r="L38" s="19">
-        <v>1.5823956</v>
-      </c>
-      <c r="M38" s="11">
-        <v>0.21484</v>
-      </c>
-      <c r="N38" s="11">
-        <v>0.316</v>
+        <v>0.9223189102534687</v>
+      </c>
+      <c r="M38" s="19">
+        <v>13.51341</v>
+      </c>
+      <c r="N38" s="19">
+        <v>7.7711396</v>
       </c>
       <c r="O38" s="11">
-        <v>0.02257804032261901</v>
-      </c>
-      <c r="P38" s="10">
-        <v>42.16521648881469</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.63432</v>
+      </c>
+      <c r="P38" s="11">
+        <v>0.116</v>
+      </c>
+      <c r="Q38" s="11">
+        <v>0.1731732157056591</v>
+      </c>
+      <c r="R38" s="10">
+        <v>45.67875323818858</v>
+      </c>
+      <c r="S38" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>35</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="E39" s="9">
-        <v>173.5</v>
+        <v>161.8500061035156</v>
       </c>
       <c r="F39" s="16">
-        <v>0.4405085822202104</v>
+        <v>0.4161120929684841</v>
       </c>
       <c r="G39" s="19">
-        <v>0.5311684230925205</v>
+        <v>-2.124796305048686</v>
       </c>
       <c r="H39" s="19">
-        <v>0.5916330364720993</v>
+        <v>1.762257701805215</v>
       </c>
       <c r="I39" s="19">
-        <v>0.005460567573198096</v>
+        <v>0.2332436258273763</v>
       </c>
       <c r="J39" s="19">
-        <v>0.4414357034614989</v>
+        <v>1.45132688477155</v>
       </c>
       <c r="K39" s="19">
-        <v>15.65096</v>
+        <v>0</v>
       </c>
       <c r="L39" s="19">
-        <v>2.7135465</v>
-      </c>
-      <c r="M39" s="11">
-        <v>0.18416001</v>
-      </c>
-      <c r="N39" s="11">
-        <v>0.151</v>
+        <v>-0.3080386954852742</v>
+      </c>
+      <c r="M39" s="19">
+        <v>61.02941</v>
+      </c>
+      <c r="N39" s="19">
+        <v>78.524124</v>
       </c>
       <c r="O39" s="11">
-        <v>0.1366432500381114</v>
-      </c>
-      <c r="P39" s="10">
-        <v>46.56301517539105</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.17442</v>
+      </c>
+      <c r="P39" s="11">
+        <v>0.256</v>
+      </c>
+      <c r="Q39" s="11">
+        <v>0.9956844531280942</v>
+      </c>
+      <c r="R39" s="10">
+        <v>52.07606850997672</v>
+      </c>
+      <c r="S39" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>36</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="E40" s="9">
-        <v>122.629997253418</v>
+        <v>136.1900024414062</v>
       </c>
       <c r="F40" s="16">
-        <v>0.4340583978673292</v>
+        <v>0.4144094122647323</v>
       </c>
       <c r="G40" s="19">
-        <v>0.4462694962176907</v>
+        <v>0.5382416025316706</v>
       </c>
       <c r="H40" s="19">
-        <v>0.858639166389934</v>
+        <v>-0.1373339426941943</v>
       </c>
       <c r="I40" s="19">
-        <v>-0.1392414226193376</v>
+        <v>0.7860752054581115</v>
       </c>
       <c r="J40" s="19">
-        <v>0.3546799026581304</v>
+        <v>0.5095157548715161</v>
       </c>
       <c r="K40" s="19">
-        <v>16.68579</v>
+        <v>0</v>
       </c>
       <c r="L40" s="19">
-        <v>3.8455532</v>
-      </c>
-      <c r="M40" s="11">
-        <v>0.25905</v>
-      </c>
-      <c r="N40" s="11">
-        <v>0.151</v>
+        <v>0.4063000959621123</v>
+      </c>
+      <c r="M40" s="19">
+        <v>17.128778</v>
+      </c>
+      <c r="N40" s="19">
+        <v>2.396272</v>
       </c>
       <c r="O40" s="11">
-        <v>0.03709360894772473</v>
-      </c>
-      <c r="P40" s="10">
-        <v>56.29518689762154</v>
-      </c>
-      <c r="Q40" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.1418</v>
+      </c>
+      <c r="P40" s="11">
+        <v>0.355</v>
+      </c>
+      <c r="Q40" s="11">
+        <v>0.1653496878943101</v>
+      </c>
+      <c r="R40" s="10">
+        <v>70.06544562345817</v>
+      </c>
+      <c r="S40" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>37</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="E41" s="9">
-        <v>195.6900024414062</v>
+        <v>163.75</v>
       </c>
       <c r="F41" s="16">
-        <v>0.4294439848114883</v>
+        <v>0.409061815122658</v>
       </c>
       <c r="G41" s="19">
-        <v>0.1591036355655292</v>
+        <v>0.5047978572859582</v>
       </c>
       <c r="H41" s="19">
-        <v>1.131462315672776</v>
+        <v>-0.5575283414198151</v>
       </c>
       <c r="I41" s="19">
-        <v>0.2261041410270051</v>
+        <v>-0.04678311634947013</v>
       </c>
       <c r="J41" s="19">
-        <v>0.2164389802319492</v>
+        <v>1.091489371774272</v>
       </c>
       <c r="K41" s="19">
-        <v>22.82242</v>
+        <v>0</v>
       </c>
       <c r="L41" s="19">
-        <v>-14.45452</v>
-      </c>
-      <c r="M41" s="11">
-        <v>0</v>
-      </c>
-      <c r="N41" s="11">
-        <v>0.081</v>
+        <v>0.2617883716747227</v>
+      </c>
+      <c r="M41" s="19">
+        <v>16.927385</v>
+      </c>
+      <c r="N41" s="19">
+        <v>4.154594</v>
       </c>
       <c r="O41" s="11">
-        <v>0.1834114554521218</v>
-      </c>
-      <c r="P41" s="10">
-        <v>43.27725724915959</v>
-      </c>
-      <c r="Q41" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.26408002</v>
+      </c>
+      <c r="P41" s="11">
+        <v>0.053</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>0.3788563884206089</v>
+      </c>
+      <c r="R41" s="10">
+        <v>63.06512965103187</v>
+      </c>
+      <c r="S41" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>38</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="E42" s="9">
-        <v>405.8399963378906</v>
+        <v>122.629997253418</v>
       </c>
       <c r="F42" s="16">
-        <v>0.4243031704991665</v>
+        <v>0.4007665285106333</v>
       </c>
       <c r="G42" s="19">
-        <v>-0.8542144784553878</v>
+        <v>0.4661838785549283</v>
       </c>
       <c r="H42" s="19">
-        <v>-0.4710398600225731</v>
+        <v>0.7817359120167516</v>
       </c>
       <c r="I42" s="19">
-        <v>4.095406692860193</v>
+        <v>-0.195108303096569</v>
       </c>
       <c r="J42" s="19">
-        <v>0.6133882503746573</v>
+        <v>0.5570600077754716</v>
       </c>
       <c r="K42" s="19">
-        <v>105.25127</v>
+        <v>0</v>
       </c>
       <c r="L42" s="19">
-        <v>2.680677</v>
-      </c>
-      <c r="M42" s="11">
-        <v>0.019199999</v>
-      </c>
-      <c r="N42" s="11">
-        <v>1.134</v>
+        <v>-0.6020150150201037</v>
+      </c>
+      <c r="M42" s="19">
+        <v>16.68579</v>
+      </c>
+      <c r="N42" s="19">
+        <v>3.8455532</v>
       </c>
       <c r="O42" s="11">
-        <v>0.3001857413090314</v>
-      </c>
-      <c r="P42" s="10">
-        <v>52.07497110059915</v>
-      </c>
-      <c r="Q42" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.25905</v>
+      </c>
+      <c r="P42" s="11">
+        <v>0.151</v>
+      </c>
+      <c r="Q42" s="11">
+        <v>0.03709360894772473</v>
+      </c>
+      <c r="R42" s="10">
+        <v>56.29518689758392</v>
+      </c>
+      <c r="S42" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>39</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="E43" s="9">
-        <v>69.56999969482422</v>
+        <v>394.8800048828125</v>
       </c>
       <c r="F43" s="16">
-        <v>0.4172887236867541</v>
+        <v>0.3886547469345187</v>
       </c>
       <c r="G43" s="19">
-        <v>0.4981154868016052</v>
+        <v>0.4003134790598573</v>
       </c>
       <c r="H43" s="19">
-        <v>1.332996393125508</v>
+        <v>-1.052694131897447</v>
       </c>
       <c r="I43" s="19">
-        <v>-0.5941108124544012</v>
+        <v>0.1720968840375585</v>
       </c>
       <c r="J43" s="19">
-        <v>0.07907200411018582</v>
+        <v>1.302344418337416</v>
       </c>
       <c r="K43" s="19">
-        <v>14.242739</v>
+        <v>0</v>
       </c>
       <c r="L43" s="19">
-        <v>-42.95995</v>
-      </c>
-      <c r="M43" s="11">
-        <v>0</v>
-      </c>
-      <c r="N43" s="11">
-        <v>0.012</v>
+        <v>0.2339430879910894</v>
+      </c>
+      <c r="M43" s="19">
+        <v>37.178402</v>
+      </c>
+      <c r="N43" s="19">
+        <v>2.4096098</v>
       </c>
       <c r="O43" s="11">
-        <v>0.04214796324844805</v>
-      </c>
-      <c r="P43" s="10">
-        <v>54.99849936232818</v>
-      </c>
-      <c r="Q43" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.06893000000000001</v>
+      </c>
+      <c r="P43" s="11">
+        <v>0.262</v>
+      </c>
+      <c r="Q43" s="11">
+        <v>1.190890352688831</v>
+      </c>
+      <c r="R43" s="10">
+        <v>57.46312192737679</v>
+      </c>
+      <c r="S43" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>40</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="E44" s="9">
-        <v>163.75</v>
+        <v>1002.559997558594</v>
       </c>
       <c r="F44" s="16">
-        <v>0.414764942700358</v>
+        <v>0.3866847440111001</v>
       </c>
       <c r="G44" s="19">
-        <v>0.5354902146966187</v>
+        <v>0.3750508094617337</v>
       </c>
       <c r="H44" s="19">
-        <v>-0.3613376701600568</v>
+        <v>0.8226956244081279</v>
       </c>
       <c r="I44" s="19">
-        <v>0.008406708792284084</v>
+        <v>0.9047441154933583</v>
       </c>
       <c r="J44" s="19">
-        <v>1.143970965041813</v>
+        <v>0.006287488846586261</v>
       </c>
       <c r="K44" s="19">
-        <v>16.927385</v>
+        <v>0</v>
       </c>
       <c r="L44" s="19">
-        <v>4.154594</v>
-      </c>
-      <c r="M44" s="11">
-        <v>0.26408002</v>
-      </c>
-      <c r="N44" s="11">
-        <v>0.053</v>
+        <v>0.11009850256413</v>
+      </c>
+      <c r="M44" s="19">
+        <v>16.078215</v>
+      </c>
+      <c r="N44" s="19">
+        <v>2.8559394</v>
       </c>
       <c r="O44" s="11">
-        <v>0.3788563884206089</v>
-      </c>
-      <c r="P44" s="10">
-        <v>63.06512965107687</v>
-      </c>
-      <c r="Q44" s="8" t="s">
-        <v>74</v>
+        <v>0.16902</v>
+      </c>
+      <c r="P44" s="11">
+        <v>0.425</v>
+      </c>
+      <c r="Q44" s="11">
+        <v>0.1731204225933523</v>
+      </c>
+      <c r="R44" s="10">
+        <v>42.20008189154327</v>
+      </c>
+      <c r="S44" s="8" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q44"/>
+  <autoFilter ref="A4:S44"/>
   <conditionalFormatting sqref="F5:F44">
     <cfRule type="dataBar" priority="1">
       <dataBar>
@@ -5282,7 +5546,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:J44">
+  <conditionalFormatting sqref="G5:L44">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -5319,7 +5583,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -5327,122 +5591,126 @@
     <col min="3" max="3" width="74.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B6" s="11">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B7" s="11">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B8" s="11">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B9" s="11">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
         <v>163</v>
       </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="B10" s="11">
-        <f>SUM(B6:B9)</f>
+        <v>0.12</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="11">
+        <v>0.06</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="11">
+        <f>SUM(B6:B11)</f>
         <v>1.0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
+      <c r="A17" s="7" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="13" t="s">
+        <v>172</v>
+      </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -5450,11 +5718,29 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
     </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A16:G18"/>
+    <mergeCell ref="A18:G20"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:B9">
+  <conditionalFormatting sqref="B6:B11">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -5483,7 +5769,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B6:B9</xm:sqref>
+          <xm:sqref>B6:B11</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5502,25 +5788,25 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="8" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="8" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>38</v>
@@ -5528,31 +5814,31 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="8" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="8" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="8" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="8" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>27</v>
@@ -5560,113 +5846,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="8" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="8" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="8" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="8" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="8" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="7" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B23" s="20"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B24" s="20"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B25" s="20"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="20" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B26" s="20"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="20" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B27" s="20"/>
     </row>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$S$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$T$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="237">
   <si>
     <t>DELL</t>
   </si>
@@ -234,6 +234,9 @@
     <t>Блок: risk</t>
   </si>
   <si>
+    <t>Блок: technical</t>
+  </si>
+  <si>
     <t>P/E</t>
   </si>
   <si>
@@ -258,67 +261,133 @@
     <t>проходит</t>
   </si>
   <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>Phillips 66</t>
+  </si>
+  <si>
     <t>OXY</t>
   </si>
   <si>
     <t>Occidental Petroleum</t>
   </si>
   <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>Phillips 66</t>
-  </si>
-  <si>
     <t>APA</t>
   </si>
   <si>
     <t>APA Corporation</t>
   </si>
   <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>CF Industries</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>EOG Resources</t>
+  </si>
+  <si>
     <t>NVDA</t>
   </si>
   <si>
     <t>Nvidia</t>
   </si>
   <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>Amgen</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>Expedia Group</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
     <t>COF</t>
   </si>
   <si>
     <t>Capital One</t>
   </si>
   <si>
-    <t>Financials</t>
-  </si>
-  <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>EOG Resources</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>Expedia Group</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>Health Care</t>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>Gen Digital</t>
+  </si>
+  <si>
+    <t>TGT</t>
+  </si>
+  <si>
+    <t>Target Corporation</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>Altria</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
   </si>
   <si>
     <t>SCHW</t>
@@ -327,16 +396,10 @@
     <t>Charles Schwab Corporation</t>
   </si>
   <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
   </si>
   <si>
     <t>FANG</t>
@@ -345,88 +408,64 @@
     <t>Diamondback Energy</t>
   </si>
   <si>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>Humana</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>Mastercard</t>
+  </si>
+  <si>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>Waters Corporation</t>
+  </si>
+  <si>
+    <t>VEEV</t>
+  </si>
+  <si>
+    <t>Veeva Systems</t>
+  </si>
+  <si>
     <t>NTAP</t>
   </si>
   <si>
     <t>NetApp</t>
   </si>
   <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>Hewlett Packard Enterprise</t>
-  </si>
-  <si>
-    <t>WAT</t>
-  </si>
-  <si>
-    <t>Waters Corporation</t>
-  </si>
-  <si>
     <t>HAS</t>
   </si>
   <si>
     <t>Hasbro</t>
   </si>
   <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>CF Industries</t>
-  </si>
-  <si>
-    <t>Materials</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>Amgen</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>Altria</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>Mastercard</t>
-  </si>
-  <si>
-    <t>CPAY</t>
-  </si>
-  <si>
-    <t>Corpay</t>
-  </si>
-  <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>Gen Digital</t>
-  </si>
-  <si>
     <t>RJF</t>
   </si>
   <si>
     <t>Raymond James Financial</t>
   </si>
   <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
   </si>
   <si>
     <t>V</t>
@@ -435,42 +474,6 @@
     <t>Visa Inc.</t>
   </si>
   <si>
-    <t>AMP</t>
-  </si>
-  <si>
-    <t>Ameriprise Financial</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
-  </si>
-  <si>
-    <t>TGT</t>
-  </si>
-  <si>
-    <t>Target Corporation</t>
-  </si>
-  <si>
-    <t>NEM</t>
-  </si>
-  <si>
-    <t>Newmont</t>
-  </si>
-  <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
-  </si>
-  <si>
     <t>GS</t>
   </si>
   <si>
@@ -516,7 +519,7 @@
     <t>momentum</t>
   </si>
   <si>
-    <t>mom_3m, mom_6m, mom_12m_1m, above_ma200, above_ma50, rsi_centered, dist_52w_high</t>
+    <t>mom_3m, mom_6m, mom_12m_1m, above_ma200, above_ma50, dist_52w_high</t>
   </si>
   <si>
     <t>earnings</t>
@@ -531,6 +534,12 @@
     <t>volatility</t>
   </si>
   <si>
+    <t>technical</t>
+  </si>
+  <si>
+    <t>rsi14, macd_hist</t>
+  </si>
+  <si>
     <t>Сумма</t>
   </si>
   <si>
@@ -549,7 +558,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-02 08:31 UTC · данные на 2026-09-01 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-02 09:55 UTC · данные на 2026-09-01 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -630,7 +639,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-02 08:31 UTC</t>
+    <t>2026-09-02 09:55 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -645,7 +654,7 @@
     <t>Прошли фильтры</t>
   </si>
   <si>
-    <t>414</t>
+    <t>415</t>
   </si>
   <si>
     <t>Кандидат дня</t>
@@ -663,7 +672,7 @@
     <t>Запросов AV использовано</t>
   </si>
   <si>
-    <t>4</t>
+    <t>6</t>
   </si>
   <si>
     <t>Источник цен</t>
@@ -2012,12 +2021,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2025,13 +2034,13 @@
         <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2050,16 +2059,16 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="2:8">
@@ -2070,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H9" s="6">
         <v>6</v>
@@ -2078,7 +2087,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2107,7 +2116,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C16" s="9">
         <v>10000</v>
@@ -2115,7 +2124,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C17" s="10">
         <v>21</v>
@@ -2123,7 +2132,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C18" s="10">
         <v>14</v>
@@ -2131,7 +2140,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="8" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
@@ -2139,7 +2148,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C20" s="10">
         <v>21</v>
@@ -2147,39 +2156,39 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="8" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C25" s="11">
         <v>0.04156959301664937</v>
@@ -2187,7 +2196,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C26" s="10">
         <v>7</v>
@@ -2195,7 +2204,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="12" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C28" s="9">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2204,12 +2213,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -3084,7 +3093,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:T44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -3093,25 +3102,25 @@
     <col min="4" max="4" width="22.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="15" width="9.7109375" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="24.7109375" customWidth="1"/>
+    <col min="7" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="13.7109375" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" customWidth="1"/>
+    <col min="19" max="19" width="8.7109375" customWidth="1"/>
+    <col min="20" max="20" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>42</v>
       </c>
@@ -3169,185 +3178,197 @@
       <c r="S4" s="14" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T4" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="9">
-        <v>933.4400024414062</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="F5" s="16">
-        <v>1.173222443227651</v>
+        <v>1.053967443133661</v>
       </c>
       <c r="G5" s="19">
-        <v>-0.4141537329218875</v>
+        <v>-0.3065942401812342</v>
       </c>
       <c r="H5" s="19">
-        <v>1.815920968500273</v>
+        <v>2.061675894555025</v>
       </c>
       <c r="I5" s="19">
-        <v>4.266205445946125</v>
+        <v>4.13232288715716</v>
       </c>
       <c r="J5" s="19">
-        <v>1.530335160883978</v>
+        <v>1.347883549762725</v>
       </c>
       <c r="K5" s="19">
         <v>0</v>
       </c>
       <c r="L5" s="19">
-        <v>-3.554186378362447</v>
+        <v>-3.540879496451628</v>
       </c>
       <c r="M5" s="19">
-        <v>21.095882</v>
+        <v>0.5958198275500537</v>
       </c>
       <c r="N5" s="19">
-        <v>10.456314</v>
-      </c>
-      <c r="O5" s="11">
-        <v>0.66638</v>
+        <v>20.12168</v>
+      </c>
+      <c r="O5" s="19">
+        <v>14.060845</v>
       </c>
       <c r="P5" s="11">
-        <v>3.457</v>
+        <v>0.9164</v>
       </c>
       <c r="Q5" s="11">
-        <v>1.459902343677745</v>
-      </c>
-      <c r="R5" s="10">
-        <v>50.44808337527054</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+        <v>3.716</v>
+      </c>
+      <c r="R5" s="11">
+        <v>1.718151550404877</v>
+      </c>
+      <c r="S5" s="10">
+        <v>51.66385839684092</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E6" s="9">
-        <v>1536.869995117188</v>
+        <v>361.989990234375</v>
       </c>
       <c r="F6" s="16">
-        <v>1.169478056376643</v>
+        <v>1.027487197086339</v>
       </c>
       <c r="G6" s="19">
-        <v>-0.3036268476905924</v>
+        <v>0.7600315297409044</v>
       </c>
       <c r="H6" s="19">
-        <v>2.059914574583257</v>
+        <v>-0.6800206488478429</v>
       </c>
       <c r="I6" s="19">
-        <v>4.12758937324224</v>
+        <v>2.817024529253408</v>
       </c>
       <c r="J6" s="19">
-        <v>1.365693417616426</v>
+        <v>2.128208308457585</v>
       </c>
       <c r="K6" s="19">
         <v>0</v>
       </c>
       <c r="L6" s="19">
-        <v>-3.554186378362447</v>
+        <v>0.1476410274084718</v>
       </c>
       <c r="M6" s="19">
-        <v>20.12168</v>
+        <v>-0.6604630651106772</v>
       </c>
       <c r="N6" s="19">
-        <v>14.060845</v>
-      </c>
-      <c r="O6" s="11">
-        <v>0.9164</v>
+        <v>14.45283</v>
+      </c>
+      <c r="O6" s="19">
+        <v>4.0580444</v>
       </c>
       <c r="P6" s="11">
-        <v>3.716</v>
+        <v>0.27637</v>
       </c>
       <c r="Q6" s="11">
-        <v>1.718151550404877</v>
-      </c>
-      <c r="R6" s="10">
-        <v>51.66385839684092</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.517</v>
+      </c>
+      <c r="R6" s="11">
+        <v>0.6989225766066014</v>
+      </c>
+      <c r="S6" s="10">
+        <v>71.73485687212836</v>
+      </c>
+      <c r="T6" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E7" s="9">
-        <v>361.989990234375</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="F7" s="16">
-        <v>0.9574483751792983</v>
+        <v>1.025386247939589</v>
       </c>
       <c r="G7" s="19">
-        <v>0.7607938773386186</v>
+        <v>-0.4169145554552529</v>
       </c>
       <c r="H7" s="19">
-        <v>-0.6799927983681159</v>
+        <v>1.817222982186202</v>
       </c>
       <c r="I7" s="19">
-        <v>2.807045091949661</v>
+        <v>4.262123054334927</v>
       </c>
       <c r="J7" s="19">
-        <v>1.456840237759929</v>
+        <v>1.504824209288006</v>
       </c>
       <c r="K7" s="19">
         <v>0</v>
       </c>
       <c r="L7" s="19">
-        <v>0.1626701879863869</v>
+        <v>-3.540879496451628</v>
       </c>
       <c r="M7" s="19">
-        <v>14.45283</v>
+        <v>0.2677755323274389</v>
       </c>
       <c r="N7" s="19">
-        <v>4.0580444</v>
-      </c>
-      <c r="O7" s="11">
-        <v>0.27637</v>
+        <v>21.095882</v>
+      </c>
+      <c r="O7" s="19">
+        <v>10.456314</v>
       </c>
       <c r="P7" s="11">
-        <v>0.517</v>
+        <v>0.66638</v>
       </c>
       <c r="Q7" s="11">
-        <v>0.6770724856664994</v>
-      </c>
-      <c r="R7" s="10">
-        <v>71.98558989034771</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+        <v>3.457</v>
+      </c>
+      <c r="R7" s="11">
+        <v>1.459902541511058</v>
+      </c>
+      <c r="S7" s="10">
+        <v>50.44808337545521</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>4</v>
       </c>
@@ -3364,175 +3385,184 @@
         <v>383</v>
       </c>
       <c r="F8" s="16">
-        <v>0.9164697094795763</v>
+        <v>1.013107049998486</v>
       </c>
       <c r="G8" s="19">
-        <v>0.7506808295748838</v>
+        <v>0.749794509494801</v>
       </c>
       <c r="H8" s="19">
-        <v>-0.5735001363123757</v>
+        <v>-0.5732880119700506</v>
       </c>
       <c r="I8" s="19">
-        <v>2.376050228636491</v>
+        <v>2.384116899919412</v>
       </c>
       <c r="J8" s="19">
-        <v>1.453044472042306</v>
+        <v>2.151988948534578</v>
       </c>
       <c r="K8" s="19">
         <v>0</v>
       </c>
       <c r="L8" s="19">
-        <v>0.1581157412226887</v>
+        <v>0.1415381917108942</v>
       </c>
       <c r="M8" s="19">
+        <v>-0.5525423981269584</v>
+      </c>
+      <c r="N8" s="19">
         <v>12.788835</v>
       </c>
-      <c r="N8" s="19">
+      <c r="O8" s="19">
         <v>5.4714427</v>
       </c>
-      <c r="O8" s="11">
+      <c r="P8" s="11">
         <v>0.42099</v>
       </c>
-      <c r="P8" s="11">
+      <c r="Q8" s="11">
         <v>0.537</v>
       </c>
-      <c r="Q8" s="11">
-        <v>0.8186359647727735</v>
-      </c>
-      <c r="R8" s="10">
-        <v>76.46062451795444</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R8" s="11">
+        <v>0.8373577839171988</v>
+      </c>
+      <c r="S8" s="10">
+        <v>76.16969901563091</v>
+      </c>
+      <c r="T8" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E9" s="9">
-        <v>60.95000076293945</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="F9" s="16">
-        <v>0.8389272175940845</v>
+        <v>0.8576426825884108</v>
       </c>
       <c r="G9" s="19">
-        <v>0.6441526575862923</v>
+        <v>0.5236285305189845</v>
       </c>
       <c r="H9" s="19">
-        <v>0.6153462608193233</v>
+        <v>-0.7870784679473629</v>
       </c>
       <c r="I9" s="19">
-        <v>3.210676182303393</v>
+        <v>2.35386274831343</v>
       </c>
       <c r="J9" s="19">
-        <v>0.3052699134305471</v>
+        <v>1.933570903080461</v>
       </c>
       <c r="K9" s="19">
         <v>0</v>
       </c>
       <c r="L9" s="19">
-        <v>0.2615929807312613</v>
+        <v>0.3716359661134623</v>
       </c>
       <c r="M9" s="19">
-        <v>17.433628</v>
+        <v>-0.641884045829084</v>
       </c>
       <c r="N9" s="19">
-        <v>1.765813</v>
-      </c>
-      <c r="O9" s="11">
-        <v>0.10629</v>
+        <v>13.92751</v>
+      </c>
+      <c r="O9" s="19">
+        <v>3.090377</v>
       </c>
       <c r="P9" s="11">
-        <v>0.534</v>
+        <v>0.23452999</v>
       </c>
       <c r="Q9" s="11">
-        <v>0.1460926867579575</v>
-      </c>
-      <c r="R9" s="10">
-        <v>62.0836193857231</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.531</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0.5931889760361613</v>
+      </c>
+      <c r="S9" s="10">
+        <v>74.79975638542247</v>
+      </c>
+      <c r="T9" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E10" s="9">
-        <v>252.0200042724609</v>
+        <v>60.95000076293945</v>
       </c>
       <c r="F10" s="16">
-        <v>0.768622075589411</v>
+        <v>0.7416152164942327</v>
       </c>
       <c r="G10" s="19">
-        <v>0.5245089923272498</v>
+        <v>0.6434300221411974</v>
       </c>
       <c r="H10" s="19">
-        <v>-0.7869032513361915</v>
+        <v>0.6167294611755126</v>
       </c>
       <c r="I10" s="19">
-        <v>2.345869080031544</v>
+        <v>3.205794473836218</v>
       </c>
       <c r="J10" s="19">
-        <v>1.278635709817943</v>
+        <v>0.4497747115500537</v>
       </c>
       <c r="K10" s="19">
         <v>0</v>
       </c>
       <c r="L10" s="19">
-        <v>0.3743416091369899</v>
+        <v>0.2446154284544499</v>
       </c>
       <c r="M10" s="19">
-        <v>13.92751</v>
+        <v>-0.4007689226809722</v>
       </c>
       <c r="N10" s="19">
-        <v>3.090377</v>
-      </c>
-      <c r="O10" s="11">
-        <v>0.23452999</v>
+        <v>17.433628</v>
+      </c>
+      <c r="O10" s="19">
+        <v>1.765813</v>
       </c>
       <c r="P10" s="11">
-        <v>0.531</v>
+        <v>0.10629</v>
       </c>
       <c r="Q10" s="11">
-        <v>0.5971772702846527</v>
-      </c>
-      <c r="R10" s="10">
-        <v>75.0766147580114</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.534</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0.1348875740367874</v>
+      </c>
+      <c r="S10" s="10">
+        <v>61.79694080641646</v>
+      </c>
+      <c r="T10" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>35</v>
@@ -3541,108 +3571,114 @@
         <v>44.29999923706055</v>
       </c>
       <c r="F11" s="16">
-        <v>0.6797962078439569</v>
+        <v>0.7192881616348453</v>
       </c>
       <c r="G11" s="19">
-        <v>1.180991741996523</v>
+        <v>1.180775573424393</v>
       </c>
       <c r="H11" s="19">
-        <v>0.5615290138085626</v>
+        <v>0.5628017336720434</v>
       </c>
       <c r="I11" s="19">
-        <v>-0.283609995077921</v>
+        <v>-0.2826661582517923</v>
       </c>
       <c r="J11" s="19">
-        <v>0.9885023787485725</v>
+        <v>1.420805177002578</v>
       </c>
       <c r="K11" s="19">
         <v>0</v>
       </c>
       <c r="L11" s="19">
-        <v>-0.3556744962059399</v>
+        <v>-0.399077701318642</v>
       </c>
       <c r="M11" s="19">
+        <v>-0.5455571695216184</v>
+      </c>
+      <c r="N11" s="19">
         <v>8.974684</v>
       </c>
-      <c r="N11" s="19">
+      <c r="O11" s="19">
         <v>2.1246629</v>
       </c>
-      <c r="O11" s="11">
+      <c r="P11" s="11">
         <v>0.26659</v>
       </c>
-      <c r="P11" s="11">
+      <c r="Q11" s="11">
         <v>0.092</v>
       </c>
-      <c r="Q11" s="11">
-        <v>0.4100597191058337</v>
-      </c>
-      <c r="R11" s="10">
-        <v>67.58723769044478</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R11" s="11">
+        <v>0.4171789910797372</v>
+      </c>
+      <c r="S11" s="10">
+        <v>67.24799565591081</v>
+      </c>
+      <c r="T11" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="E12" s="9">
-        <v>217.4400024414062</v>
+        <v>135.6000061035156</v>
       </c>
       <c r="F12" s="16">
-        <v>0.6650491619952672</v>
+        <v>0.6088418995787529</v>
       </c>
       <c r="G12" s="19">
-        <v>-1.181029849974955</v>
+        <v>0.675065848973343</v>
       </c>
       <c r="H12" s="19">
-        <v>2.37007023642441</v>
+        <v>0.2975919364127702</v>
       </c>
       <c r="I12" s="19">
-        <v>2.41302945894081</v>
+        <v>0.2786698223080728</v>
       </c>
       <c r="J12" s="19">
-        <v>0.3611144854480505</v>
+        <v>1.118134349214674</v>
       </c>
       <c r="K12" s="19">
         <v>0</v>
       </c>
       <c r="L12" s="19">
-        <v>-0.1713930070306825</v>
+        <v>0.006054055767980149</v>
       </c>
       <c r="M12" s="19">
-        <v>27.468435</v>
+        <v>0.03729723308461752</v>
       </c>
       <c r="N12" s="19">
-        <v>26.95787</v>
-      </c>
-      <c r="O12" s="11">
-        <v>1.17211</v>
+        <v>9.331602999999999</v>
+      </c>
+      <c r="O12" s="19">
+        <v>3.3175094</v>
       </c>
       <c r="P12" s="11">
-        <v>1.059</v>
+        <v>0.29867</v>
       </c>
       <c r="Q12" s="11">
-        <v>0.2091375570176681</v>
-      </c>
-      <c r="R12" s="10">
-        <v>51.87290992384082</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.176</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0.312129727571627</v>
+      </c>
+      <c r="S12" s="10">
+        <v>68.50310275628433</v>
+      </c>
+      <c r="T12" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>9</v>
       </c>
@@ -3659,116 +3695,122 @@
         <v>425</v>
       </c>
       <c r="F13" s="16">
-        <v>0.6297064224653799</v>
+        <v>0.5575835254090703</v>
       </c>
       <c r="G13" s="19">
-        <v>-0.1432744592067679</v>
+        <v>-0.1453667345878826</v>
       </c>
       <c r="H13" s="19">
-        <v>-0.9099368713420634</v>
+        <v>-0.9104682528073633</v>
       </c>
       <c r="I13" s="19">
-        <v>2.974201127010152</v>
+        <v>2.981910484335923</v>
       </c>
       <c r="J13" s="19">
-        <v>1.608280043891485</v>
+        <v>1.727504144967455</v>
       </c>
       <c r="K13" s="19">
         <v>0</v>
       </c>
       <c r="L13" s="19">
-        <v>-2.082809480567236</v>
+        <v>-2.047620412311253</v>
       </c>
       <c r="M13" s="19">
+        <v>-0.3883829018771805</v>
+      </c>
+      <c r="N13" s="19">
         <v>36.353783</v>
       </c>
-      <c r="N13" s="19">
+      <c r="O13" s="19">
         <v>-210.92924</v>
       </c>
-      <c r="O13" s="11">
+      <c r="P13" s="11">
         <v>0</v>
       </c>
-      <c r="P13" s="11">
+      <c r="Q13" s="11">
         <v>0.875</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="R13" s="11">
         <v>1.941310647213375</v>
       </c>
-      <c r="R13" s="10">
-        <v>44.90408763111306</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S13" s="10">
+        <v>44.90408763111304</v>
+      </c>
+      <c r="T13" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="E14" s="9">
-        <v>211.3399963378906</v>
+        <v>211.0500030517578</v>
       </c>
       <c r="F14" s="16">
-        <v>0.6230705947850401</v>
+        <v>0.5520359298556146</v>
       </c>
       <c r="G14" s="19">
-        <v>0.588790081488105</v>
+        <v>0.5556735680703294</v>
       </c>
       <c r="H14" s="19">
-        <v>-0.6572941626990328</v>
+        <v>-0.3266206515441806</v>
       </c>
       <c r="I14" s="19">
-        <v>4.12758937324224</v>
+        <v>2.258526107719387</v>
       </c>
       <c r="J14" s="19">
-        <v>0.07273741413375968</v>
+        <v>0.7303891701553145</v>
       </c>
       <c r="K14" s="19">
         <v>0</v>
       </c>
       <c r="L14" s="19">
-        <v>0.5045059847861416</v>
+        <v>0.7696587846111567</v>
       </c>
       <c r="M14" s="19">
-        <v>11.935252</v>
+        <v>-0.6639901078481503</v>
       </c>
       <c r="N14" s="19">
-        <v>1.2848284</v>
-      </c>
-      <c r="O14" s="11">
-        <v>0.09031</v>
+        <v>19.409616</v>
+      </c>
+      <c r="O14" s="19">
+        <v>2.0853305</v>
       </c>
       <c r="P14" s="11">
-        <v>11.11</v>
+        <v>0.12231</v>
       </c>
       <c r="Q14" s="11">
-        <v>0.09945135302649666</v>
-      </c>
-      <c r="R14" s="10">
-        <v>44.70214500676185</v>
-      </c>
-      <c r="S14" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.535</v>
+      </c>
+      <c r="R14" s="11">
+        <v>0.1381140844875719</v>
+      </c>
+      <c r="S14" s="10">
+        <v>71.60464867022429</v>
+      </c>
+      <c r="T14" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>35</v>
@@ -3777,108 +3819,114 @@
         <v>148.3500061035156</v>
       </c>
       <c r="F15" s="16">
-        <v>0.6201529980865428</v>
+        <v>0.540241053062401</v>
       </c>
       <c r="G15" s="19">
-        <v>0.626069891898576</v>
+        <v>0.6252746191907743</v>
       </c>
       <c r="H15" s="19">
-        <v>0.4653179239592711</v>
+        <v>0.4666043918108415</v>
       </c>
       <c r="I15" s="19">
-        <v>1.413985002184136</v>
+        <v>1.417737897842424</v>
       </c>
       <c r="J15" s="19">
-        <v>0.4707372508987441</v>
+        <v>0.512632579233376</v>
       </c>
       <c r="K15" s="19">
         <v>0</v>
       </c>
       <c r="L15" s="19">
-        <v>0.2741552179013221</v>
+        <v>0.2772294195705438</v>
       </c>
       <c r="M15" s="19">
+        <v>-0.2998917022206128</v>
+      </c>
+      <c r="N15" s="19">
         <v>11.1643305</v>
       </c>
-      <c r="N15" s="19">
+      <c r="O15" s="19">
         <v>2.3641071</v>
       </c>
-      <c r="O15" s="11">
+      <c r="P15" s="11">
         <v>0.22507</v>
       </c>
-      <c r="P15" s="11">
+      <c r="Q15" s="11">
         <v>0.587</v>
       </c>
-      <c r="Q15" s="11">
-        <v>0.1765594431862711</v>
-      </c>
-      <c r="R15" s="10">
-        <v>56.67336380437713</v>
-      </c>
-      <c r="S15" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R15" s="11">
+        <v>0.1707063379394265</v>
+      </c>
+      <c r="S15" s="10">
+        <v>56.60881034200952</v>
+      </c>
+      <c r="T15" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>12</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="E16" s="9">
-        <v>304.2300109863281</v>
+        <v>217.4400024414062</v>
       </c>
       <c r="F16" s="16">
-        <v>0.6158846100801868</v>
+        <v>0.5227387549492293</v>
       </c>
       <c r="G16" s="19">
-        <v>0.02815639480182512</v>
+        <v>-1.186242168307697</v>
       </c>
       <c r="H16" s="19">
-        <v>1.206665013812346</v>
+        <v>2.372350229473365</v>
       </c>
       <c r="I16" s="19">
-        <v>0.5893325464410265</v>
+        <v>2.41778901771408</v>
       </c>
       <c r="J16" s="19">
-        <v>0.872800024292623</v>
+        <v>0.2212479063118502</v>
       </c>
       <c r="K16" s="19">
         <v>0</v>
       </c>
       <c r="L16" s="19">
-        <v>-0.5144739653764235</v>
+        <v>-0.1509467465621591</v>
       </c>
       <c r="M16" s="19">
-        <v>20.706474</v>
+        <v>-0.06423513670330765</v>
       </c>
       <c r="N16" s="19">
-        <v>32.69876</v>
-      </c>
-      <c r="O16" s="11">
-        <v>0.89489</v>
+        <v>27.468435</v>
+      </c>
+      <c r="O16" s="19">
+        <v>26.95787</v>
       </c>
       <c r="P16" s="11">
-        <v>0.14</v>
+        <v>1.17211</v>
       </c>
       <c r="Q16" s="11">
-        <v>0.4222265750834804</v>
-      </c>
-      <c r="R16" s="10">
-        <v>46.34797987544066</v>
-      </c>
-      <c r="S16" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1.059</v>
+      </c>
+      <c r="R16" s="11">
+        <v>0.2091375570176681</v>
+      </c>
+      <c r="S16" s="10">
+        <v>51.87290992384197</v>
+      </c>
+      <c r="T16" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>13</v>
       </c>
@@ -3889,1649 +3937,1733 @@
         <v>94</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E17" s="9">
         <v>257.8699951171875</v>
       </c>
       <c r="F17" s="16">
-        <v>0.611534064567484</v>
+        <v>0.5131665152254895</v>
       </c>
       <c r="G17" s="19">
-        <v>1.299052042330012</v>
+        <v>1.2973242005594</v>
       </c>
       <c r="H17" s="19">
-        <v>0.1657815718694057</v>
+        <v>0.1669261144304357</v>
       </c>
       <c r="I17" s="19">
-        <v>-0.05430715947452922</v>
+        <v>-0.05264739805840464</v>
       </c>
       <c r="J17" s="19">
-        <v>0.7021116596541814</v>
+        <v>0.6125480538697033</v>
       </c>
       <c r="K17" s="19">
         <v>0</v>
       </c>
       <c r="L17" s="19">
-        <v>0.5056668910749345</v>
+        <v>0.442136474288886</v>
       </c>
       <c r="M17" s="19">
+        <v>-0.1708483227941824</v>
+      </c>
+      <c r="N17" s="19">
         <v>5.156936</v>
       </c>
-      <c r="N17" s="19">
+      <c r="O17" s="19">
         <v>2.0881312</v>
       </c>
-      <c r="O17" s="11">
+      <c r="P17" s="11">
         <v>0.46113998</v>
       </c>
-      <c r="P17" s="11">
+      <c r="Q17" s="11">
         <v>0.118</v>
       </c>
-      <c r="Q17" s="11">
-        <v>0.2186102950476296</v>
-      </c>
-      <c r="R17" s="10">
-        <v>50.78974543525931</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R17" s="11">
+        <v>0.2184079601631363</v>
+      </c>
+      <c r="S17" s="10">
+        <v>49.93960247392307</v>
+      </c>
+      <c r="T17" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>14</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18" s="9">
-        <v>125.0100021362305</v>
+        <v>438.1199951171875</v>
       </c>
       <c r="F18" s="16">
-        <v>0.5789192396129739</v>
+        <v>0.5091334812988626</v>
       </c>
       <c r="G18" s="19">
-        <v>0.3547542484834569</v>
+        <v>-0.2455671553299525</v>
       </c>
       <c r="H18" s="19">
-        <v>0.5051665520920795</v>
+        <v>1.23829401915366</v>
       </c>
       <c r="I18" s="19">
-        <v>0.526532558122933</v>
+        <v>-0.09681434526753466</v>
       </c>
       <c r="J18" s="19">
-        <v>0.8783623937716313</v>
+        <v>1.068465270265442</v>
       </c>
       <c r="K18" s="19">
         <v>0</v>
       </c>
       <c r="L18" s="19">
-        <v>0.055137146741291</v>
+        <v>0.6880295267081549</v>
       </c>
       <c r="M18" s="19">
-        <v>15.843312</v>
+        <v>-0.7253426214695433</v>
       </c>
       <c r="N18" s="19">
-        <v>3.939749</v>
-      </c>
-      <c r="O18" s="11">
-        <v>0.30667</v>
+        <v>26.875078</v>
+      </c>
+      <c r="O18" s="19">
+        <v>20.000925</v>
       </c>
       <c r="P18" s="11">
-        <v>0.377</v>
+        <v>0.91473</v>
       </c>
       <c r="Q18" s="11">
-        <v>0.2747017694018412</v>
-      </c>
-      <c r="R18" s="10">
-        <v>54.59762999280029</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.095</v>
+      </c>
+      <c r="R18" s="11">
+        <v>0.1511749006415839</v>
+      </c>
+      <c r="S18" s="10">
+        <v>66.38286199743321</v>
+      </c>
+      <c r="T18" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>15</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>87</v>
-      </c>
       <c r="E19" s="9">
-        <v>108.2799987792969</v>
+        <v>66.91999816894531</v>
       </c>
       <c r="F19" s="16">
-        <v>0.56819823093239</v>
+        <v>0.5079512330182455</v>
       </c>
       <c r="G19" s="19">
-        <v>0.08365196315212738</v>
+        <v>0.4854005059534541</v>
       </c>
       <c r="H19" s="19">
-        <v>1.221326744496752</v>
+        <v>0.6587571460380149</v>
       </c>
       <c r="I19" s="19">
-        <v>0.1023029875964842</v>
+        <v>0.2084671882916938</v>
       </c>
       <c r="J19" s="19">
-        <v>0.6137225772405409</v>
+        <v>0.7731015664864646</v>
       </c>
       <c r="K19" s="19">
         <v>0</v>
       </c>
       <c r="L19" s="19">
-        <v>0.9129608892018518</v>
+        <v>0.5802224593255341</v>
       </c>
       <c r="M19" s="19">
-        <v>20.065575</v>
+        <v>-0.4170835714536103</v>
       </c>
       <c r="N19" s="19">
-        <v>4.333084</v>
-      </c>
-      <c r="O19" s="11">
-        <v>0.20273</v>
+        <v>14.762749</v>
+      </c>
+      <c r="O19" s="19">
+        <v>6.0942793</v>
       </c>
       <c r="P19" s="11">
-        <v>0.209</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q19" s="11">
-        <v>0.1443239902155196</v>
-      </c>
-      <c r="R19" s="10">
-        <v>51.23363878393255</v>
-      </c>
-      <c r="S19" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.057</v>
+      </c>
+      <c r="R19" s="11">
+        <v>0.09677911856043009</v>
+      </c>
+      <c r="S19" s="10">
+        <v>60.01687384912778</v>
+      </c>
+      <c r="T19" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>16</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E20" s="9">
-        <v>66.91999816894531</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="F20" s="16">
-        <v>0.5485608290322841</v>
+        <v>0.5009062060594807</v>
       </c>
       <c r="G20" s="19">
-        <v>0.4866550004416153</v>
+        <v>0.3535340411038917</v>
       </c>
       <c r="H20" s="19">
-        <v>0.6572130983041129</v>
+        <v>0.5066139843793523</v>
       </c>
       <c r="I20" s="19">
-        <v>0.2052523593343346</v>
+        <v>0.5284153400344015</v>
       </c>
       <c r="J20" s="19">
-        <v>0.6514555734746182</v>
+        <v>0.8680644952406645</v>
       </c>
       <c r="K20" s="19">
         <v>0</v>
       </c>
       <c r="L20" s="19">
-        <v>0.5668017522224791</v>
+        <v>0.05624113697794832</v>
       </c>
       <c r="M20" s="19">
-        <v>14.762749</v>
+        <v>-0.2566531795171282</v>
       </c>
       <c r="N20" s="19">
-        <v>6.0942793</v>
-      </c>
-      <c r="O20" s="11">
-        <v>0.46598998</v>
+        <v>15.843312</v>
+      </c>
+      <c r="O20" s="19">
+        <v>3.939749</v>
       </c>
       <c r="P20" s="11">
-        <v>0.057</v>
+        <v>0.30667</v>
       </c>
       <c r="Q20" s="11">
-        <v>0.1168442617445413</v>
-      </c>
-      <c r="R20" s="10">
-        <v>59.7292562771191</v>
-      </c>
-      <c r="S20" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.377</v>
+      </c>
+      <c r="R20" s="11">
+        <v>0.2496001698539319</v>
+      </c>
+      <c r="S20" s="10">
+        <v>54.52617136164081</v>
+      </c>
+      <c r="T20" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="E21" s="9">
-        <v>450.4400024414062</v>
+        <v>304.2300109863281</v>
       </c>
       <c r="F21" s="16">
-        <v>0.5415297623462551</v>
+        <v>0.4995295468227405</v>
       </c>
       <c r="G21" s="19">
-        <v>-0.9089117611651794</v>
+        <v>0.02392519228507077</v>
       </c>
       <c r="H21" s="19">
-        <v>2.149283894198748</v>
+        <v>1.208973468219964</v>
       </c>
       <c r="I21" s="19">
-        <v>2.955409129427278</v>
+        <v>0.5934216790533486</v>
       </c>
       <c r="J21" s="19">
-        <v>0.4064360291013725</v>
+        <v>0.8918103152716023</v>
       </c>
       <c r="K21" s="19">
         <v>0</v>
       </c>
       <c r="L21" s="19">
-        <v>-3.554186378362447</v>
+        <v>-0.4225670883207233</v>
       </c>
       <c r="M21" s="19">
-        <v>17.067236</v>
+        <v>-0.7460940688758423</v>
       </c>
       <c r="N21" s="19">
-        <v>21.967487</v>
-      </c>
-      <c r="O21" s="11">
-        <v>1.30853</v>
+        <v>20.706474</v>
+      </c>
+      <c r="O21" s="19">
+        <v>32.69876</v>
       </c>
       <c r="P21" s="11">
-        <v>0.438</v>
+        <v>0.89489</v>
       </c>
       <c r="Q21" s="11">
-        <v>0.798703509252862</v>
-      </c>
-      <c r="R21" s="10">
-        <v>43.73367487660393</v>
-      </c>
-      <c r="S21" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.14</v>
+      </c>
+      <c r="R21" s="11">
+        <v>0.4348987086786897</v>
+      </c>
+      <c r="S21" s="10">
+        <v>46.51005273293129</v>
+      </c>
+      <c r="T21" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>18</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E22" s="9">
-        <v>211.0500030517578</v>
+        <v>258.1099853515625</v>
       </c>
       <c r="F22" s="16">
-        <v>0.5401046589977162</v>
+        <v>0.4760440696423573</v>
       </c>
       <c r="G22" s="19">
-        <v>0.556513719960729</v>
+        <v>0.3430645610428927</v>
       </c>
       <c r="H22" s="19">
-        <v>-0.3268121485730144</v>
+        <v>0.5388891445188714</v>
       </c>
       <c r="I22" s="19">
-        <v>2.250950359039762</v>
+        <v>0.1866157944506243</v>
       </c>
       <c r="J22" s="19">
-        <v>0.3353731162324973</v>
+        <v>1.093659767973966</v>
       </c>
       <c r="K22" s="19">
         <v>0</v>
       </c>
       <c r="L22" s="19">
-        <v>0.7563683731636086</v>
+        <v>-1.453801527371712</v>
       </c>
       <c r="M22" s="19">
-        <v>19.409616</v>
+        <v>0.1426684872448112</v>
       </c>
       <c r="N22" s="19">
-        <v>2.0853305</v>
-      </c>
-      <c r="O22" s="11">
-        <v>0.12231</v>
+        <v>23.421774</v>
+      </c>
+      <c r="O22" s="19">
+        <v>5.4897923</v>
       </c>
       <c r="P22" s="11">
-        <v>0.535</v>
+        <v>0.19381</v>
       </c>
       <c r="Q22" s="11">
-        <v>0.1381139908378988</v>
-      </c>
-      <c r="R22" s="10">
-        <v>71.60464863030431</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.108</v>
+      </c>
+      <c r="R22" s="11">
+        <v>0.3232508978324589</v>
+      </c>
+      <c r="S22" s="10">
+        <v>81.25380620929735</v>
+      </c>
+      <c r="T22" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>19</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="E23" s="9">
-        <v>203.1600036621094</v>
+        <v>211.3399963378906</v>
       </c>
       <c r="F23" s="16">
-        <v>0.5305610090884552</v>
+        <v>0.4757683908515629</v>
       </c>
       <c r="G23" s="19">
-        <v>0.6300105237233145</v>
+        <v>0.5887979504774438</v>
       </c>
       <c r="H23" s="19">
-        <v>-0.04505139788901939</v>
+        <v>-0.657139695697852</v>
       </c>
       <c r="I23" s="19">
-        <v>1.570837850468294</v>
+        <v>4.13232288715716</v>
       </c>
       <c r="J23" s="19">
-        <v>0.4508101730943636</v>
+        <v>-0.03074398165902444</v>
       </c>
       <c r="K23" s="19">
         <v>0</v>
       </c>
       <c r="L23" s="19">
-        <v>0.270683957113491</v>
+        <v>0.50624407711399</v>
       </c>
       <c r="M23" s="19">
-        <v>37.579845</v>
+        <v>-0.2068604333719531</v>
       </c>
       <c r="N23" s="19">
-        <v>1.4633226</v>
-      </c>
-      <c r="O23" s="11">
-        <v>0.034930002</v>
+        <v>11.935252</v>
+      </c>
+      <c r="O23" s="19">
+        <v>1.2848284</v>
       </c>
       <c r="P23" s="11">
-        <v>0.525</v>
+        <v>0.09031</v>
       </c>
       <c r="Q23" s="11">
-        <v>0.1639168565252822</v>
-      </c>
-      <c r="R23" s="10">
-        <v>54.29840659207855</v>
-      </c>
-      <c r="S23" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+        <v>11.11</v>
+      </c>
+      <c r="R23" s="11">
+        <v>0.09611312275134765</v>
+      </c>
+      <c r="S23" s="10">
+        <v>45.11230677423562</v>
+      </c>
+      <c r="T23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>20</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="9">
-        <v>183.1600036621094</v>
+        <v>161.8500061035156</v>
       </c>
       <c r="F24" s="16">
-        <v>0.5175125565590661</v>
+        <v>0.471575487146039</v>
       </c>
       <c r="G24" s="19">
-        <v>-0.4163532752680855</v>
+        <v>-2.122778428838808</v>
       </c>
       <c r="H24" s="19">
-        <v>1.256179888265389</v>
+        <v>1.765640568246892</v>
       </c>
       <c r="I24" s="19">
-        <v>-0.2091710352067727</v>
+        <v>0.2349332652824272</v>
       </c>
       <c r="J24" s="19">
-        <v>1.075325353994139</v>
+        <v>1.564637910547843</v>
       </c>
       <c r="K24" s="19">
         <v>0</v>
       </c>
       <c r="L24" s="19">
-        <v>-0.1072377352581109</v>
+        <v>-0.2547818898329872</v>
       </c>
       <c r="M24" s="19">
-        <v>29.498423</v>
+        <v>0.462328358217257</v>
       </c>
       <c r="N24" s="19">
-        <v>27.131872</v>
-      </c>
-      <c r="O24" s="11">
-        <v>1.06734</v>
+        <v>61.02941</v>
+      </c>
+      <c r="O24" s="19">
+        <v>78.524124</v>
       </c>
       <c r="P24" s="11">
-        <v>0.125</v>
+        <v>1.17442</v>
       </c>
       <c r="Q24" s="11">
-        <v>0.8691903396615654</v>
-      </c>
-      <c r="R24" s="10">
-        <v>45.70079166571557</v>
-      </c>
-      <c r="S24" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.256</v>
+      </c>
+      <c r="R24" s="11">
+        <v>1.044076856273211</v>
+      </c>
+      <c r="S24" s="10">
+        <v>52.73692094066809</v>
+      </c>
+      <c r="T24" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="9">
-        <v>50.86999893188477</v>
+        <v>30.02000045776367</v>
       </c>
       <c r="F25" s="16">
-        <v>0.5168014817492296</v>
+        <v>0.4680722065995366</v>
       </c>
       <c r="G25" s="19">
-        <v>0.2630418482711242</v>
+        <v>0.5167039359615127</v>
       </c>
       <c r="H25" s="19">
-        <v>-0.6920579173680381</v>
+        <v>0.749645521027813</v>
       </c>
       <c r="I25" s="19">
-        <v>1.303910323344291</v>
+        <v>-0.1861321221296584</v>
       </c>
       <c r="J25" s="19">
-        <v>1.350299201213216</v>
+        <v>0.6780963960340513</v>
       </c>
       <c r="K25" s="19">
         <v>0</v>
       </c>
       <c r="L25" s="19">
-        <v>-1.030293729636665</v>
+        <v>0.2247602356716958</v>
       </c>
       <c r="M25" s="19">
-        <v>48.887848</v>
+        <v>0.008152865406482857</v>
       </c>
       <c r="N25" s="19">
-        <v>2.7368805</v>
-      </c>
-      <c r="O25" s="11">
-        <v>0.06315</v>
+        <v>17.827587</v>
+      </c>
+      <c r="O25" s="19">
+        <v>6.9959407</v>
       </c>
       <c r="P25" s="11">
-        <v>0.4</v>
+        <v>0.41944</v>
       </c>
       <c r="Q25" s="11">
-        <v>1.37281915384833</v>
-      </c>
-      <c r="R25" s="10">
-        <v>45.56155343762108</v>
-      </c>
-      <c r="S25" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.063</v>
+      </c>
+      <c r="R25" s="11">
+        <v>0.3563279010849416</v>
+      </c>
+      <c r="S25" s="10">
+        <v>61.70036862510079</v>
+      </c>
+      <c r="T25" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>22</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E26" s="9">
-        <v>405.8399963378906</v>
+        <v>163.75</v>
       </c>
       <c r="F26" s="16">
-        <v>0.5126442628358368</v>
+        <v>0.4672299014324282</v>
       </c>
       <c r="G26" s="19">
-        <v>-0.9726355829702346</v>
+        <v>0.5037681831878469</v>
       </c>
       <c r="H26" s="19">
-        <v>-0.4324969997184582</v>
+        <v>-0.5575001867977641</v>
       </c>
       <c r="I26" s="19">
-        <v>4.12758937324224</v>
+        <v>-0.04455757815619896</v>
       </c>
       <c r="J26" s="19">
-        <v>0.5890230104538892</v>
+        <v>1.435967725119076</v>
       </c>
       <c r="K26" s="19">
         <v>0</v>
       </c>
       <c r="L26" s="19">
-        <v>0.6617573284098744</v>
+        <v>0.2539051903365677</v>
       </c>
       <c r="M26" s="19">
-        <v>105.25127</v>
+        <v>-0.3985600120741293</v>
       </c>
       <c r="N26" s="19">
-        <v>2.680677</v>
-      </c>
-      <c r="O26" s="11">
-        <v>0.019199999</v>
+        <v>16.927385</v>
+      </c>
+      <c r="O26" s="19">
+        <v>4.154594</v>
       </c>
       <c r="P26" s="11">
-        <v>1.134</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q26" s="11">
-        <v>0.3001857413090314</v>
-      </c>
-      <c r="R26" s="10">
-        <v>52.07497110059915</v>
-      </c>
-      <c r="S26" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.053</v>
+      </c>
+      <c r="R26" s="11">
+        <v>0.4718198758607315</v>
+      </c>
+      <c r="S26" s="10">
+        <v>63.12038567431014</v>
+      </c>
+      <c r="T26" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>23</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E27" s="9">
-        <v>93.19999694824219</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="F27" s="16">
-        <v>0.5095092804132845</v>
+        <v>0.4667048749607028</v>
       </c>
       <c r="G27" s="19">
-        <v>0.1351965712218133</v>
+        <v>0.548854665636462</v>
       </c>
       <c r="H27" s="19">
-        <v>1.640909999466138</v>
+        <v>1.843831358372849</v>
       </c>
       <c r="I27" s="19">
-        <v>0.03821118616689118</v>
+        <v>-0.6292233998564639</v>
       </c>
       <c r="J27" s="19">
-        <v>0.3080471037980272</v>
+        <v>0.02317164762853158</v>
       </c>
       <c r="K27" s="19">
         <v>0</v>
       </c>
       <c r="L27" s="19">
-        <v>0.3800772843337862</v>
+        <v>0.3921848972101009</v>
       </c>
       <c r="M27" s="19">
-        <v>16.766905</v>
+        <v>0.6166648084460049</v>
       </c>
       <c r="N27" s="19">
-        <v>18.876202</v>
-      </c>
-      <c r="O27" s="11">
-        <v>1.5956</v>
+        <v>14.242739</v>
+      </c>
+      <c r="O27" s="19">
+        <v>-42.95995</v>
       </c>
       <c r="P27" s="11">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="11">
-        <v>-0.03033542100628361</v>
-      </c>
-      <c r="R27" s="10">
-        <v>52.09734154570462</v>
-      </c>
-      <c r="S27" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.012</v>
+      </c>
+      <c r="R27" s="11">
+        <v>0.04518237521385204</v>
+      </c>
+      <c r="S27" s="10">
+        <v>54.8966572673663</v>
+      </c>
+      <c r="T27" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>24</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="E28" s="9">
-        <v>135.6000061035156</v>
+        <v>136.1900024414062</v>
       </c>
       <c r="F28" s="16">
-        <v>0.500513329849641</v>
+        <v>0.4622732395981689</v>
       </c>
       <c r="G28" s="19">
-        <v>0.6758234888176574</v>
+        <v>0.5373664552081702</v>
       </c>
       <c r="H28" s="19">
-        <v>0.2963342123961663</v>
+        <v>-0.1368691777673517</v>
       </c>
       <c r="I28" s="19">
-        <v>0.2761473880447703</v>
+        <v>0.7891918304603867</v>
       </c>
       <c r="J28" s="19">
-        <v>0.6771125751271094</v>
+        <v>0.9258571555327707</v>
       </c>
       <c r="K28" s="19">
         <v>0</v>
       </c>
       <c r="L28" s="19">
-        <v>0.03555272777992204</v>
+        <v>0.3973511834359071</v>
       </c>
       <c r="M28" s="19">
-        <v>9.331602999999999</v>
+        <v>-0.6067980420041242</v>
       </c>
       <c r="N28" s="19">
-        <v>3.3175094</v>
-      </c>
-      <c r="O28" s="11">
-        <v>0.29867</v>
+        <v>17.128778</v>
+      </c>
+      <c r="O28" s="19">
+        <v>2.396272</v>
       </c>
       <c r="P28" s="11">
-        <v>0.176</v>
+        <v>0.1418</v>
       </c>
       <c r="Q28" s="11">
-        <v>0.2874424165088272</v>
-      </c>
-      <c r="R28" s="10">
-        <v>69.12167518760248</v>
-      </c>
-      <c r="S28" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.355</v>
+      </c>
+      <c r="R28" s="11">
+        <v>0.1681093072105853</v>
+      </c>
+      <c r="S28" s="10">
+        <v>69.60407992037833</v>
+      </c>
+      <c r="T28" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>25</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="E29" s="9">
-        <v>438.1199951171875</v>
+        <v>450.4400024414062</v>
       </c>
       <c r="F29" s="16">
-        <v>0.4969613458936494</v>
+        <v>0.4581215887060392</v>
       </c>
       <c r="G29" s="19">
-        <v>-0.2421358524050068</v>
+        <v>-0.9131978128854404</v>
       </c>
       <c r="H29" s="19">
-        <v>1.235722878380574</v>
+        <v>2.151528876753073</v>
       </c>
       <c r="I29" s="19">
-        <v>-0.09848432835705492</v>
+        <v>2.950282622072772</v>
       </c>
       <c r="J29" s="19">
-        <v>0.7320008486913989</v>
+        <v>0.3366630736324592</v>
       </c>
       <c r="K29" s="19">
         <v>0</v>
       </c>
       <c r="L29" s="19">
-        <v>0.6816814096751428</v>
+        <v>-3.540879496451628</v>
       </c>
       <c r="M29" s="19">
-        <v>26.875078</v>
+        <v>0.4962946198785601</v>
       </c>
       <c r="N29" s="19">
-        <v>20.000925</v>
-      </c>
-      <c r="O29" s="11">
-        <v>0.91473</v>
+        <v>17.067236</v>
+      </c>
+      <c r="O29" s="19">
+        <v>21.967487</v>
       </c>
       <c r="P29" s="11">
-        <v>0.095</v>
+        <v>1.30853</v>
       </c>
       <c r="Q29" s="11">
-        <v>0.1777404730924301</v>
-      </c>
-      <c r="R29" s="10">
-        <v>66.50037520073629</v>
-      </c>
-      <c r="S29" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.438</v>
+      </c>
+      <c r="R29" s="11">
+        <v>0.6690356163398388</v>
+      </c>
+      <c r="S29" s="10">
+        <v>43.83463781720145</v>
+      </c>
+      <c r="T29" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>26</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="E30" s="9">
-        <v>69.56999969482422</v>
+        <v>108.2799987792969</v>
       </c>
       <c r="F30" s="16">
-        <v>0.4795440739896837</v>
+        <v>0.4436142672502696</v>
       </c>
       <c r="G30" s="19">
-        <v>0.5501274300267243</v>
+        <v>0.08240686126983239</v>
       </c>
       <c r="H30" s="19">
-        <v>1.841068648189355</v>
+        <v>1.223451927469628</v>
       </c>
       <c r="I30" s="19">
-        <v>-0.6294234346915084</v>
+        <v>0.1038485795344242</v>
       </c>
       <c r="J30" s="19">
-        <v>0.1015529609376061</v>
+        <v>0.4908742695999092</v>
       </c>
       <c r="K30" s="19">
         <v>0</v>
       </c>
       <c r="L30" s="19">
-        <v>0.393580118240667</v>
+        <v>0.9305031342973328</v>
       </c>
       <c r="M30" s="19">
-        <v>14.242739</v>
+        <v>-0.4210289391841021</v>
       </c>
       <c r="N30" s="19">
-        <v>-42.95995</v>
-      </c>
-      <c r="O30" s="11">
-        <v>0</v>
+        <v>20.065575</v>
+      </c>
+      <c r="O30" s="19">
+        <v>4.333084</v>
       </c>
       <c r="P30" s="11">
-        <v>0.012</v>
+        <v>0.20273</v>
       </c>
       <c r="Q30" s="11">
-        <v>0.04214796324844805</v>
-      </c>
-      <c r="R30" s="10">
-        <v>54.99849936221541</v>
-      </c>
-      <c r="S30" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.209</v>
+      </c>
+      <c r="R30" s="11">
+        <v>0.1413280553506242</v>
+      </c>
+      <c r="S30" s="10">
+        <v>51.67770002511105</v>
+      </c>
+      <c r="T30" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>27</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E31" s="9">
         <v>363.9200134277344</v>
       </c>
       <c r="F31" s="16">
-        <v>0.4750693645959413</v>
+        <v>0.4262581153554666</v>
       </c>
       <c r="G31" s="19">
-        <v>1.233688344268854</v>
+        <v>1.231904824551268</v>
       </c>
       <c r="H31" s="19">
-        <v>-0.1209388667662471</v>
+        <v>-0.1202756231839317</v>
       </c>
       <c r="I31" s="19">
-        <v>-0.3789121155917646</v>
+        <v>-0.3776219198070676</v>
       </c>
       <c r="J31" s="19">
-        <v>0.6291731353936107</v>
+        <v>0.6145948754783469</v>
       </c>
       <c r="K31" s="19">
         <v>0</v>
       </c>
       <c r="L31" s="19">
-        <v>0.6204403092273081</v>
+        <v>0.596224696895187</v>
       </c>
       <c r="M31" s="19">
+        <v>-0.1222672459187132</v>
+      </c>
+      <c r="N31" s="19">
         <v>9.919549</v>
       </c>
-      <c r="N31" s="19">
+      <c r="O31" s="19">
         <v>2.3296678</v>
       </c>
-      <c r="O31" s="11">
+      <c r="P31" s="11">
         <v>0.26511</v>
       </c>
-      <c r="P31" s="11">
+      <c r="Q31" s="11">
         <v>0.003</v>
       </c>
-      <c r="Q31" s="11">
-        <v>0.1794453676755525</v>
-      </c>
-      <c r="R31" s="10">
-        <v>46.71708990738924</v>
-      </c>
-      <c r="S31" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R31" s="11">
+        <v>0.1805841930692524</v>
+      </c>
+      <c r="S31" s="10">
+        <v>47.06174798442245</v>
+      </c>
+      <c r="T31" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>28</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="E32" s="9">
-        <v>581.0999755859375</v>
+        <v>203.1600036621094</v>
       </c>
       <c r="F32" s="16">
-        <v>0.4627749048861954</v>
+        <v>0.4260134819385445</v>
       </c>
       <c r="G32" s="19">
-        <v>-1.474085335991063</v>
+        <v>0.6290781538187236</v>
       </c>
       <c r="H32" s="19">
-        <v>2.898258236165586</v>
+        <v>-0.04474182683940042</v>
       </c>
       <c r="I32" s="19">
-        <v>-0.1725926699877148</v>
+        <v>1.575737480795989</v>
       </c>
       <c r="J32" s="19">
-        <v>0.4455811158118482</v>
+        <v>0.4199180490295129</v>
       </c>
       <c r="K32" s="19">
         <v>0</v>
       </c>
       <c r="L32" s="19">
-        <v>0.9749610721165579</v>
+        <v>0.2033377509034909</v>
       </c>
       <c r="M32" s="19">
-        <v>32.565643</v>
+        <v>-0.3366617391226158</v>
       </c>
       <c r="N32" s="19">
-        <v>93.07380000000001</v>
-      </c>
-      <c r="O32" s="11">
-        <v>2.41202</v>
+        <v>37.579845</v>
+      </c>
+      <c r="O32" s="19">
+        <v>1.4633226</v>
       </c>
       <c r="P32" s="11">
-        <v>0.141</v>
+        <v>0.034930002</v>
       </c>
       <c r="Q32" s="11">
-        <v>0.1120582336705458</v>
-      </c>
-      <c r="R32" s="10">
-        <v>55.70271450417012</v>
-      </c>
-      <c r="S32" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.525</v>
+      </c>
+      <c r="R32" s="11">
+        <v>0.1546164081122456</v>
+      </c>
+      <c r="S32" s="10">
+        <v>54.3947760974016</v>
+      </c>
+      <c r="T32" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>29</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E33" s="9">
-        <v>404.8099975585938</v>
+        <v>394.8800048828125</v>
       </c>
       <c r="F33" s="16">
-        <v>0.4591179149903291</v>
+        <v>0.4184221547240243</v>
       </c>
       <c r="G33" s="19">
-        <v>0.3093493865558575</v>
+        <v>0.3991025813752035</v>
       </c>
       <c r="H33" s="19">
-        <v>0.7050912458411566</v>
+        <v>-1.053340414218987</v>
       </c>
       <c r="I33" s="19">
-        <v>-0.1093741464017893</v>
+        <v>0.1734891100083233</v>
       </c>
       <c r="J33" s="19">
-        <v>0.6051390384954368</v>
+        <v>1.42826630724615</v>
       </c>
       <c r="K33" s="19">
         <v>0</v>
       </c>
       <c r="L33" s="19">
-        <v>0.5786311479764153</v>
+        <v>0.2435062406524336</v>
       </c>
       <c r="M33" s="19">
-        <v>24.571085</v>
+        <v>0.0558540021352415</v>
       </c>
       <c r="N33" s="19">
-        <v>7.5607543</v>
-      </c>
-      <c r="O33" s="11">
-        <v>0.29215</v>
+        <v>37.178402</v>
+      </c>
+      <c r="O33" s="19">
+        <v>2.4096098</v>
       </c>
       <c r="P33" s="11">
-        <v>0.215</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="Q33" s="11">
-        <v>0.2104837668337398</v>
-      </c>
-      <c r="R33" s="10">
-        <v>54.64609628677665</v>
-      </c>
-      <c r="S33" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.262</v>
+      </c>
+      <c r="R33" s="11">
+        <v>1.124209183441041</v>
+      </c>
+      <c r="S33" s="10">
+        <v>57.13086874947128</v>
+      </c>
+      <c r="T33" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>30</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="E34" s="9">
-        <v>30.02000045776367</v>
+        <v>211.0399932861328</v>
       </c>
       <c r="F34" s="16">
-        <v>0.4558945757130657</v>
+        <v>0.4126771874314553</v>
       </c>
       <c r="G34" s="19">
-        <v>0.5180662182502601</v>
+        <v>0.3599630250019414</v>
       </c>
       <c r="H34" s="19">
-        <v>0.7480363136364186</v>
+        <v>0.7749817441404762</v>
       </c>
       <c r="I34" s="19">
-        <v>-0.1877037530857071</v>
+        <v>0.3840583979359316</v>
       </c>
       <c r="J34" s="19">
-        <v>0.5399536999157968</v>
+        <v>0.2766834873747249</v>
       </c>
       <c r="K34" s="19">
         <v>0</v>
       </c>
       <c r="L34" s="19">
-        <v>0.2111118820020053</v>
+        <v>0.5555633725674428</v>
       </c>
       <c r="M34" s="19">
-        <v>17.827587</v>
+        <v>0.2452601627099722</v>
       </c>
       <c r="N34" s="19">
-        <v>6.9959407</v>
-      </c>
-      <c r="O34" s="11">
-        <v>0.41944</v>
+        <v>17.362167</v>
+      </c>
+      <c r="O34" s="19">
+        <v>3.1676524</v>
       </c>
       <c r="P34" s="11">
-        <v>0.063</v>
+        <v>0.17969999</v>
       </c>
       <c r="Q34" s="11">
-        <v>0.3533004092198408</v>
-      </c>
-      <c r="R34" s="10">
-        <v>61.00117942829461</v>
-      </c>
-      <c r="S34" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.28</v>
+      </c>
+      <c r="R34" s="11">
+        <v>0.2774975167216034</v>
+      </c>
+      <c r="S34" s="10">
+        <v>45.09837584286628</v>
+      </c>
+      <c r="T34" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>31</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="E35" s="9">
-        <v>173.5</v>
+        <v>50.86999893188477</v>
       </c>
       <c r="F35" s="16">
-        <v>0.4465679571037485</v>
+        <v>0.4126047116989254</v>
       </c>
       <c r="G35" s="19">
-        <v>0.5395560519923884</v>
+        <v>0.2615753155071175</v>
       </c>
       <c r="H35" s="19">
-        <v>0.565362548485465</v>
+        <v>-0.6923506737965556</v>
       </c>
       <c r="I35" s="19">
-        <v>-0.05467446158502198</v>
+        <v>1.306361806653459</v>
       </c>
       <c r="J35" s="19">
-        <v>0.4226478530522234</v>
+        <v>1.416721464972737</v>
       </c>
       <c r="K35" s="19">
         <v>0</v>
       </c>
       <c r="L35" s="19">
-        <v>0.9102825923154756</v>
+        <v>-1.003222744291485</v>
       </c>
       <c r="M35" s="19">
-        <v>15.65096</v>
+        <v>-0.8584319773556982</v>
       </c>
       <c r="N35" s="19">
-        <v>2.7135465</v>
-      </c>
-      <c r="O35" s="11">
-        <v>0.18416001</v>
+        <v>48.887848</v>
+      </c>
+      <c r="O35" s="19">
+        <v>2.7368805</v>
       </c>
       <c r="P35" s="11">
-        <v>0.151</v>
+        <v>0.06315</v>
       </c>
       <c r="Q35" s="11">
-        <v>0.1366433636618272</v>
-      </c>
-      <c r="R35" s="10">
-        <v>46.56301517390835</v>
-      </c>
-      <c r="S35" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.4</v>
+      </c>
+      <c r="R35" s="11">
+        <v>1.37281915384833</v>
+      </c>
+      <c r="S35" s="10">
+        <v>45.56155343779849</v>
+      </c>
+      <c r="T35" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>32</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E36" s="9">
-        <v>211.0399932861328</v>
+        <v>581.0999755859375</v>
       </c>
       <c r="F36" s="16">
-        <v>0.4448062335301415</v>
+        <v>0.3916161455058922</v>
       </c>
       <c r="G36" s="19">
-        <v>0.3606114262700158</v>
+        <v>-1.47114938458048</v>
       </c>
       <c r="H36" s="19">
-        <v>0.7734905973148591</v>
+        <v>2.900487942036482</v>
       </c>
       <c r="I36" s="19">
-        <v>0.3819632017249545</v>
+        <v>-0.1716020620831971</v>
       </c>
       <c r="J36" s="19">
-        <v>0.311066644900183</v>
+        <v>0.40037687920062</v>
       </c>
       <c r="K36" s="19">
         <v>0</v>
       </c>
       <c r="L36" s="19">
-        <v>0.5783663693465612</v>
+        <v>0.9788374955638623</v>
       </c>
       <c r="M36" s="19">
-        <v>17.362167</v>
+        <v>-0.2041510092732939</v>
       </c>
       <c r="N36" s="19">
-        <v>3.1676524</v>
-      </c>
-      <c r="O36" s="11">
-        <v>0.17969999</v>
+        <v>32.565643</v>
+      </c>
+      <c r="O36" s="19">
+        <v>93.07380000000001</v>
       </c>
       <c r="P36" s="11">
-        <v>0.28</v>
+        <v>2.41202</v>
       </c>
       <c r="Q36" s="11">
-        <v>0.2855805954504331</v>
-      </c>
-      <c r="R36" s="10">
-        <v>44.75446895013088</v>
-      </c>
-      <c r="S36" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.141</v>
+      </c>
+      <c r="R36" s="11">
+        <v>0.1191447109428658</v>
+      </c>
+      <c r="S36" s="10">
+        <v>56.95037286381055</v>
+      </c>
+      <c r="T36" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>33</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E37" s="9">
-        <v>372.6700134277344</v>
+        <v>405.8399963378906</v>
       </c>
       <c r="F37" s="16">
-        <v>0.4258959445218294</v>
+        <v>0.3894368626144686</v>
       </c>
       <c r="G37" s="19">
-        <v>-0.8579418461106736</v>
+        <v>-0.9759620955182193</v>
       </c>
       <c r="H37" s="19">
-        <v>1.968378447518884</v>
+        <v>-0.4326356610429035</v>
       </c>
       <c r="I37" s="19">
-        <v>-0.2192287351731601</v>
+        <v>4.13232288715716</v>
       </c>
       <c r="J37" s="19">
-        <v>0.4827855919055765</v>
+        <v>0.5068170131519655</v>
       </c>
       <c r="K37" s="19">
         <v>0</v>
       </c>
       <c r="L37" s="19">
-        <v>1.064745644315671</v>
+        <v>0.6306658220897489</v>
       </c>
       <c r="M37" s="19">
-        <v>32.476597</v>
+        <v>-0.1939752490726785</v>
       </c>
       <c r="N37" s="19">
-        <v>20.222574</v>
-      </c>
-      <c r="O37" s="11">
-        <v>0.6119</v>
+        <v>105.25127</v>
+      </c>
+      <c r="O37" s="19">
+        <v>2.680677</v>
       </c>
       <c r="P37" s="11">
-        <v>0.144</v>
+        <v>0.019199999</v>
       </c>
       <c r="Q37" s="11">
-        <v>0.1661514393863721</v>
-      </c>
-      <c r="R37" s="10">
-        <v>54.30594216676963</v>
-      </c>
-      <c r="S37" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1.134</v>
+      </c>
+      <c r="R37" s="11">
+        <v>0.3209646903796475</v>
+      </c>
+      <c r="S37" s="10">
+        <v>52.52706816975237</v>
+      </c>
+      <c r="T37" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E38" s="9">
-        <v>542.6400146484375</v>
+        <v>279.2300109863281</v>
       </c>
       <c r="F38" s="16">
-        <v>0.4237491075589168</v>
+        <v>0.3828445309878786</v>
       </c>
       <c r="G38" s="19">
-        <v>0.3931690320945501</v>
+        <v>-0.7341033794993066</v>
       </c>
       <c r="H38" s="19">
-        <v>0.6248071829755445</v>
+        <v>0.653024735669726</v>
       </c>
       <c r="I38" s="19">
-        <v>-0.2867976137565587</v>
+        <v>0.001731719619972795</v>
       </c>
       <c r="J38" s="19">
-        <v>0.502739669790368</v>
+        <v>1.373359834811231</v>
       </c>
       <c r="K38" s="19">
         <v>0</v>
       </c>
       <c r="L38" s="19">
-        <v>0.9223189102534687</v>
+        <v>-0.8129850454590923</v>
       </c>
       <c r="M38" s="19">
-        <v>13.51341</v>
+        <v>0.01444772742789091</v>
       </c>
       <c r="N38" s="19">
-        <v>7.7711396</v>
-      </c>
-      <c r="O38" s="11">
-        <v>0.63432</v>
+        <v>45.4335</v>
+      </c>
+      <c r="O38" s="19">
+        <v>6.1722584</v>
       </c>
       <c r="P38" s="11">
-        <v>0.116</v>
+        <v>0.14425</v>
       </c>
       <c r="Q38" s="11">
-        <v>0.1731732157056591</v>
-      </c>
-      <c r="R38" s="10">
-        <v>45.67875323818858</v>
-      </c>
-      <c r="S38" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.176</v>
+      </c>
+      <c r="R38" s="11">
+        <v>0.5388813209292986</v>
+      </c>
+      <c r="S38" s="10">
+        <v>74.60652658754897</v>
+      </c>
+      <c r="T38" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>35</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="9">
-        <v>161.8500061035156</v>
+        <v>183.1600036621094</v>
       </c>
       <c r="F39" s="16">
-        <v>0.4161120929684841</v>
+        <v>0.3826329123088687</v>
       </c>
       <c r="G39" s="19">
-        <v>-2.124796305048686</v>
+        <v>-0.4206222377761193</v>
       </c>
       <c r="H39" s="19">
-        <v>1.762257701805215</v>
+        <v>1.258828701477971</v>
       </c>
       <c r="I39" s="19">
-        <v>0.2332436258273763</v>
+        <v>-0.2081970290549548</v>
       </c>
       <c r="J39" s="19">
-        <v>1.45132688477155</v>
+        <v>1.070023496104814</v>
       </c>
       <c r="K39" s="19">
         <v>0</v>
       </c>
       <c r="L39" s="19">
-        <v>-0.3080386954852742</v>
+        <v>-0.239983863384239</v>
       </c>
       <c r="M39" s="19">
-        <v>61.02941</v>
+        <v>-0.9346492590982962</v>
       </c>
       <c r="N39" s="19">
-        <v>78.524124</v>
-      </c>
-      <c r="O39" s="11">
-        <v>1.17442</v>
+        <v>29.498423</v>
+      </c>
+      <c r="O39" s="19">
+        <v>27.131872</v>
       </c>
       <c r="P39" s="11">
-        <v>0.256</v>
+        <v>1.06734</v>
       </c>
       <c r="Q39" s="11">
-        <v>0.9956844531280942</v>
-      </c>
-      <c r="R39" s="10">
-        <v>52.07606850997672</v>
-      </c>
-      <c r="S39" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.125</v>
+      </c>
+      <c r="R39" s="11">
+        <v>0.8438074962251603</v>
+      </c>
+      <c r="S39" s="10">
+        <v>45.96143628178666</v>
+      </c>
+      <c r="T39" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>36</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="E40" s="9">
-        <v>136.1900024414062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="F40" s="16">
-        <v>0.4144094122647323</v>
+        <v>0.3782564613751516</v>
       </c>
       <c r="G40" s="19">
-        <v>0.5382416025316706</v>
+        <v>0.1323994869339421</v>
       </c>
       <c r="H40" s="19">
-        <v>-0.1373339426941943</v>
+        <v>1.644369932284167</v>
       </c>
       <c r="I40" s="19">
-        <v>0.7860752054581115</v>
+        <v>0.03944887499304424</v>
       </c>
       <c r="J40" s="19">
-        <v>0.5095157548715161</v>
+        <v>0.15697387739312</v>
       </c>
       <c r="K40" s="19">
         <v>0</v>
       </c>
       <c r="L40" s="19">
-        <v>0.4063000959621123</v>
+        <v>0.3953052970028949</v>
       </c>
       <c r="M40" s="19">
-        <v>17.128778</v>
+        <v>-0.3602597417607131</v>
       </c>
       <c r="N40" s="19">
-        <v>2.396272</v>
-      </c>
-      <c r="O40" s="11">
-        <v>0.1418</v>
+        <v>16.766905</v>
+      </c>
+      <c r="O40" s="19">
+        <v>18.876202</v>
       </c>
       <c r="P40" s="11">
-        <v>0.355</v>
+        <v>1.5956</v>
       </c>
       <c r="Q40" s="11">
-        <v>0.1653496878943101</v>
-      </c>
-      <c r="R40" s="10">
-        <v>70.06544562345817</v>
-      </c>
-      <c r="S40" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.162</v>
+      </c>
+      <c r="R40" s="11">
+        <v>-0.04423676626675477</v>
+      </c>
+      <c r="S40" s="10">
+        <v>52.36948930562311</v>
+      </c>
+      <c r="T40" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>37</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="E41" s="9">
-        <v>163.75</v>
+        <v>173.5</v>
       </c>
       <c r="F41" s="16">
-        <v>0.409061815122658</v>
+        <v>0.3773951824522197</v>
       </c>
       <c r="G41" s="19">
-        <v>0.5047978572859582</v>
+        <v>0.5392511670723198</v>
       </c>
       <c r="H41" s="19">
-        <v>-0.5575283414198151</v>
+        <v>0.5664211651255424</v>
       </c>
       <c r="I41" s="19">
-        <v>-0.04678311634947013</v>
+        <v>-0.05328793731108517</v>
       </c>
       <c r="J41" s="19">
-        <v>1.091489371774272</v>
+        <v>0.3551382828586324</v>
       </c>
       <c r="K41" s="19">
         <v>0</v>
       </c>
       <c r="L41" s="19">
-        <v>0.2617883716747227</v>
+        <v>0.9356539578408296</v>
       </c>
       <c r="M41" s="19">
-        <v>16.927385</v>
+        <v>-0.1617095566510254</v>
       </c>
       <c r="N41" s="19">
-        <v>4.154594</v>
-      </c>
-      <c r="O41" s="11">
-        <v>0.26408002</v>
+        <v>15.65096</v>
+      </c>
+      <c r="O41" s="19">
+        <v>2.7135465</v>
       </c>
       <c r="P41" s="11">
-        <v>0.053</v>
+        <v>0.18416001</v>
       </c>
       <c r="Q41" s="11">
-        <v>0.3788563884206089</v>
-      </c>
-      <c r="R41" s="10">
-        <v>63.06512965103187</v>
-      </c>
-      <c r="S41" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.151</v>
+      </c>
+      <c r="R41" s="11">
+        <v>0.1317852142544169</v>
+      </c>
+      <c r="S41" s="10">
+        <v>47.03672897866576</v>
+      </c>
+      <c r="T41" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>38</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="E42" s="9">
-        <v>122.629997253418</v>
+        <v>31.31999969482422</v>
       </c>
       <c r="F42" s="16">
-        <v>0.4007665285106333</v>
+        <v>0.3765306999293311</v>
       </c>
       <c r="G42" s="19">
-        <v>0.4661838785549283</v>
+        <v>1.18884239126269</v>
       </c>
       <c r="H42" s="19">
-        <v>0.7817359120167516</v>
+        <v>-0.9872240870343698</v>
       </c>
       <c r="I42" s="19">
-        <v>-0.195108303096569</v>
+        <v>-0.3680930717051557</v>
       </c>
       <c r="J42" s="19">
-        <v>0.5570600077754716</v>
+        <v>1.282655814237512</v>
       </c>
       <c r="K42" s="19">
         <v>0</v>
       </c>
       <c r="L42" s="19">
-        <v>-0.6020150150201037</v>
+        <v>-0.3882822646386584</v>
       </c>
       <c r="M42" s="19">
-        <v>16.68579</v>
+        <v>-0.6172407723299035</v>
       </c>
       <c r="N42" s="19">
-        <v>3.8455532</v>
-      </c>
-      <c r="O42" s="11">
-        <v>0.25905</v>
+        <v>11.648855</v>
+      </c>
+      <c r="O42" s="19">
+        <v>-305.2</v>
       </c>
       <c r="P42" s="11">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="11">
-        <v>0.03709360894772473</v>
-      </c>
-      <c r="R42" s="10">
-        <v>56.29518689758392</v>
-      </c>
-      <c r="S42" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.125</v>
+      </c>
+      <c r="R42" s="11">
+        <v>0.7227637365928901</v>
+      </c>
+      <c r="S42" s="10">
+        <v>62.78791024319322</v>
+      </c>
+      <c r="T42" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>39</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E43" s="9">
-        <v>394.8800048828125</v>
+        <v>372.6700134277344</v>
       </c>
       <c r="F43" s="16">
-        <v>0.3886547469345187</v>
+        <v>0.3764471816204712</v>
       </c>
       <c r="G43" s="19">
-        <v>0.4003134790598573</v>
+        <v>-0.8622441204646991</v>
       </c>
       <c r="H43" s="19">
-        <v>-1.052694131897447</v>
+        <v>1.971798251919513</v>
       </c>
       <c r="I43" s="19">
-        <v>0.1720968840375585</v>
+        <v>-0.2184519826388571</v>
       </c>
       <c r="J43" s="19">
-        <v>1.302344418337416</v>
+        <v>0.4255139254045108</v>
       </c>
       <c r="K43" s="19">
         <v>0</v>
       </c>
       <c r="L43" s="19">
-        <v>0.2339430879910894</v>
+        <v>1.075759308177671</v>
       </c>
       <c r="M43" s="19">
-        <v>37.178402</v>
+        <v>0.007940041930133312</v>
       </c>
       <c r="N43" s="19">
-        <v>2.4096098</v>
-      </c>
-      <c r="O43" s="11">
-        <v>0.06893000000000001</v>
+        <v>32.476597</v>
+      </c>
+      <c r="O43" s="19">
+        <v>20.222574</v>
       </c>
       <c r="P43" s="11">
-        <v>0.262</v>
+        <v>0.6119</v>
       </c>
       <c r="Q43" s="11">
-        <v>1.190890352688831</v>
-      </c>
-      <c r="R43" s="10">
-        <v>57.46312192737679</v>
-      </c>
-      <c r="S43" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.144</v>
+      </c>
+      <c r="R43" s="11">
+        <v>0.1673156612317195</v>
+      </c>
+      <c r="S43" s="10">
+        <v>55.34628421874768</v>
+      </c>
+      <c r="T43" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>40</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E44" s="9">
         <v>1002.559997558594</v>
       </c>
       <c r="F44" s="16">
-        <v>0.3866847440111001</v>
+        <v>0.3633983433353277</v>
       </c>
       <c r="G44" s="19">
-        <v>0.3750508094617337</v>
+        <v>0.3744813910308467</v>
       </c>
       <c r="H44" s="19">
-        <v>0.8226956244081279</v>
+        <v>0.8243277724214527</v>
       </c>
       <c r="I44" s="19">
-        <v>0.9047441154933583</v>
+        <v>0.9077656154464111</v>
       </c>
       <c r="J44" s="19">
-        <v>0.006287488846586261</v>
+        <v>-0.01580374169888174</v>
       </c>
       <c r="K44" s="19">
         <v>0</v>
       </c>
       <c r="L44" s="19">
-        <v>0.11009850256413</v>
+        <v>0.04266007988564412</v>
       </c>
       <c r="M44" s="19">
+        <v>0.3987050541748531</v>
+      </c>
+      <c r="N44" s="19">
         <v>16.078215</v>
       </c>
-      <c r="N44" s="19">
+      <c r="O44" s="19">
         <v>2.8559394</v>
       </c>
-      <c r="O44" s="11">
+      <c r="P44" s="11">
         <v>0.16902</v>
       </c>
-      <c r="P44" s="11">
+      <c r="Q44" s="11">
         <v>0.425</v>
       </c>
-      <c r="Q44" s="11">
-        <v>0.1731204225933523</v>
-      </c>
-      <c r="R44" s="10">
-        <v>42.20008189154327</v>
-      </c>
-      <c r="S44" s="8" t="s">
-        <v>76</v>
+      <c r="R44" s="11">
+        <v>0.1743184821970312</v>
+      </c>
+      <c r="S44" s="10">
+        <v>42.58530471072517</v>
+      </c>
+      <c r="T44" s="8" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:S44"/>
+  <autoFilter ref="A4:T44"/>
   <conditionalFormatting sqref="F5:F44">
     <cfRule type="dataBar" priority="1">
       <dataBar>
@@ -5546,7 +5678,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:L44">
+  <conditionalFormatting sqref="G5:M44">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -5583,7 +5715,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -5593,133 +5725,135 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B6" s="11">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B7" s="11">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B8" s="11">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B9" s="11">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B10" s="11">
         <v>0.12</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B11" s="11">
         <v>0.06</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>168</v>
+      <c r="A12" s="8" t="s">
+        <v>169</v>
       </c>
       <c r="B12" s="11">
-        <f>SUM(B6:B11)</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>169</v>
+        <v>0.08</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="11">
+        <f>SUM(B6:B12)</f>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>171</v>
+      <c r="A15" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
+      <c r="A18" s="7" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="13" t="s">
+        <v>175</v>
+      </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -5736,11 +5870,20 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
     </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A18:G20"/>
+    <mergeCell ref="A19:G21"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:B11">
+  <conditionalFormatting sqref="B6:B12">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -5769,7 +5912,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B6:B11</xm:sqref>
+          <xm:sqref>B6:B12</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5788,25 +5931,25 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="8" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>38</v>
@@ -5814,31 +5957,31 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="8" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>27</v>
@@ -5846,113 +5989,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B23" s="20"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B24" s="20"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B25" s="20"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="20" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B26" s="20"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="20" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B27" s="20"/>
     </row>
@@ -6704,12 +6847,9 @@
         <v>462</v>
       </c>
       <c r="BG4">
-        <v>459.4500122070312</v>
+        <v>450.5499877929688</v>
       </c>
       <c r="BH4">
-        <v>450.5499877929688</v>
-      </c>
-      <c r="BI4">
         <v>450.4400024414062</v>
       </c>
     </row>
@@ -6889,12 +7029,9 @@
         <v>346.5899963378906</v>
       </c>
       <c r="BG5">
-        <v>352.3599853515625</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="BH5">
-        <v>358.9200134277344</v>
-      </c>
-      <c r="BI5">
         <v>361.989990234375</v>
       </c>
     </row>
@@ -7074,12 +7211,9 @@
         <v>363.5400085449219</v>
       </c>
       <c r="BG6">
-        <v>368.8299865722656</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="BH6">
-        <v>373.3200073242188</v>
-      </c>
-      <c r="BI6">
         <v>383</v>
       </c>
     </row>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="237">
   <si>
     <t>DELL</t>
   </si>
@@ -204,6 +204,9 @@
     <t>2026-08-24</t>
   </si>
   <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -315,25 +318,31 @@
     <t>Financials</t>
   </si>
   <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
     <t>AMGN</t>
   </si>
   <si>
     <t>Amgen</t>
   </si>
   <si>
-    <t>Health Care</t>
-  </si>
-  <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Capital One</t>
   </si>
   <si>
     <t>EXPE</t>
@@ -351,10 +360,19 @@
     <t>Salesforce</t>
   </si>
   <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>Capital One</t>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>Gen Digital</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>Altria</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
   </si>
   <si>
     <t>FTNT</t>
@@ -363,10 +381,16 @@
     <t>Fortinet</t>
   </si>
   <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>Gen Digital</t>
+    <t>SCHW</t>
+  </si>
+  <si>
+    <t>Charles Schwab Corporation</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
   </si>
   <si>
     <t>TGT</t>
@@ -375,25 +399,10 @@
     <t>Target Corporation</t>
   </si>
   <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>Altria</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
-  </si>
-  <si>
-    <t>SCHW</t>
-  </si>
-  <si>
-    <t>Charles Schwab Corporation</t>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>Humana</t>
   </si>
   <si>
     <t>TRV</t>
@@ -408,10 +417,10 @@
     <t>Diamondback Energy</t>
   </si>
   <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise</t>
   </si>
   <si>
     <t>MS</t>
@@ -420,10 +429,10 @@
     <t>Morgan Stanley</t>
   </si>
   <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>Hewlett Packard Enterprise</t>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
   </si>
   <si>
     <t>MA</t>
@@ -432,48 +441,42 @@
     <t>Mastercard</t>
   </si>
   <si>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
+  </si>
+  <si>
     <t>WAT</t>
   </si>
   <si>
     <t>Waters Corporation</t>
   </si>
   <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Visa Inc.</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>Hasbro</t>
+  </si>
+  <si>
+    <t>RJF</t>
+  </si>
+  <si>
+    <t>Raymond James Financial</t>
+  </si>
+  <si>
     <t>VEEV</t>
   </si>
   <si>
     <t>Veeva Systems</t>
   </si>
   <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
-    <t>HAS</t>
-  </si>
-  <si>
-    <t>Hasbro</t>
-  </si>
-  <si>
-    <t>RJF</t>
-  </si>
-  <si>
-    <t>Raymond James Financial</t>
-  </si>
-  <si>
-    <t>HPQ</t>
-  </si>
-  <si>
-    <t>HP Inc.</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Visa Inc.</t>
-  </si>
-  <si>
     <t>GS</t>
   </si>
   <si>
@@ -558,7 +561,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-02 09:55 UTC · данные на 2026-09-01 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-03 00:20 UTC · данные на 2026-09-02 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -639,7 +642,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-02 09:55 UTC</t>
+    <t>2026-09-03 00:20 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -672,7 +675,7 @@
     <t>Запросов AV использовано</t>
   </si>
   <si>
-    <t>6</t>
+    <t>2</t>
   </si>
   <si>
     <t>Источник цен</t>
@@ -688,9 +691,6 @@
   </si>
   <si>
     <t>Версия состояния</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>Регламент данных</t>
@@ -1128,9 +1128,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$11</c:f>
+              <c:f>Капитал!$A$5:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1152,15 +1152,18 @@
                 <c:pt idx="6">
                   <c:v>2026-09-01</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>2026-09-02</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$11</c:f>
+              <c:f>Капитал!$D$5:$D$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1180,6 +1183,9 @@
                   <c:v>10021.720000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>9972.67</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>9972.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -1205,9 +1211,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$11</c:f>
+              <c:f>Капитал!$A$5:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1229,15 +1235,18 @@
                 <c:pt idx="6">
                   <c:v>2026-09-01</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>2026-09-02</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$11</c:f>
+              <c:f>Капитал!$F$5:$F$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1258,6 +1267,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>9977.860000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1397,9 +1409,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$11</c:f>
+              <c:f>Капитал!$A$5:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1421,15 +1433,18 @@
                 <c:pt idx="6">
                   <c:v>2026-09-01</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>2026-09-02</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$11</c:f>
+              <c:f>Капитал!$D$5:$D$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1449,6 +1464,9 @@
                   <c:v>10021.720000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>9972.67</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>9972.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -1474,9 +1492,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$11</c:f>
+              <c:f>Капитал!$A$5:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1498,15 +1516,18 @@
                 <c:pt idx="6">
                   <c:v>2026-09-01</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>2026-09-02</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$11</c:f>
+              <c:f>Капитал!$F$5:$F$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1527,6 +1548,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>9977.860000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2021,12 +2045,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2034,13 +2058,13 @@
         <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2059,27 +2083,27 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="6">
-        <v>-2.743637704961072</v>
+        <v>-2.534712479800046</v>
       </c>
       <c r="D9" s="6">
         <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H9" s="6">
         <v>6</v>
@@ -2087,7 +2111,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2116,7 +2140,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="9">
         <v>10000</v>
@@ -2124,7 +2148,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C17" s="10">
         <v>21</v>
@@ -2132,23 +2156,23 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C19" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C20" s="10">
         <v>21</v>
@@ -2156,55 +2180,55 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C25" s="11">
-        <v>0.04156959301664937</v>
+        <v>0.03856799325004857</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C26" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C28" s="9">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2213,12 +2237,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -2369,11 +2393,11 @@
         <v>-0.04087302337302337</v>
       </c>
       <c r="L5" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5" s="10">
         <f>MAX(0,21-L5)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N5" s="19">
         <v>2.927623067210654</v>
@@ -2420,11 +2444,11 @@
         <v>0.007814380932399143</v>
       </c>
       <c r="L6" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" s="10">
         <f>MAX(0,21-L6)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N6" s="19">
         <v>1.809956883354321</v>
@@ -2471,11 +2495,11 @@
         <v>-0.008595752361009467</v>
       </c>
       <c r="L7" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7" s="10">
         <f>MAX(0,21-L7)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N7" s="19">
         <v>1.655247920227722</v>
@@ -2522,11 +2546,11 @@
         <v>-0.026141070217003785</v>
       </c>
       <c r="L8" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" s="10">
         <f>MAX(0,21-L8)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N8" s="19">
         <v>1.135451734784544</v>
@@ -2573,11 +2597,11 @@
         <v>0.005136823709867133</v>
       </c>
       <c r="L9" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="10">
         <f>MAX(0,21-L9)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N9" s="19">
         <v>1.098454348098604</v>
@@ -2624,11 +2648,11 @@
         <v>0.005327247391140304</v>
       </c>
       <c r="L10" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="10">
         <f>MAX(0,21-L10)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N10" s="19">
         <v>0.9280120270881818</v>
@@ -2898,7 +2922,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3084,6 +3108,25 @@
       <c r="F11" s="9">
         <v>9977.860000000001</v>
       </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="9">
+        <v>7139.55</v>
+      </c>
+      <c r="C12" s="9">
+        <v>2833.12</v>
+      </c>
+      <c r="D12" s="9">
+        <f>B12+C12</f>
+        <v>9972.67</v>
+      </c>
+      <c r="E12" s="10">
+        <v>6</v>
+      </c>
+      <c r="F12" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3112,12 +3155,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3134,52 +3177,52 @@
         <v>10</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S4" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -3199,7 +3242,7 @@
         <v>1536.869995117188</v>
       </c>
       <c r="F5" s="16">
-        <v>1.053967443133661</v>
+        <v>1.06776319712514</v>
       </c>
       <c r="G5" s="19">
         <v>-0.3065942401812342</v>
@@ -3211,16 +3254,16 @@
         <v>4.13232288715716</v>
       </c>
       <c r="J5" s="19">
-        <v>1.347883549762725</v>
+        <v>1.383821957048834</v>
       </c>
       <c r="K5" s="19">
         <v>0</v>
       </c>
       <c r="L5" s="19">
-        <v>-3.540879496451628</v>
+        <v>-3.555680450483079</v>
       </c>
       <c r="M5" s="19">
-        <v>0.5958198275500537</v>
+        <v>0.623904809657001</v>
       </c>
       <c r="N5" s="19">
         <v>20.12168</v>
@@ -3241,7 +3284,7 @@
         <v>51.66385839684092</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -3249,61 +3292,61 @@
         <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E6" s="9">
-        <v>361.989990234375</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="F6" s="16">
-        <v>1.027487197086339</v>
+        <v>1.038282641843425</v>
       </c>
       <c r="G6" s="19">
-        <v>0.7600315297409044</v>
+        <v>-0.4169145554552529</v>
       </c>
       <c r="H6" s="19">
-        <v>-0.6800206488478429</v>
+        <v>1.817222982186202</v>
       </c>
       <c r="I6" s="19">
-        <v>2.817024529253408</v>
+        <v>4.262123054334927</v>
       </c>
       <c r="J6" s="19">
-        <v>2.128208308457585</v>
+        <v>1.5428027860031</v>
       </c>
       <c r="K6" s="19">
         <v>0</v>
       </c>
       <c r="L6" s="19">
-        <v>0.1476410274084718</v>
+        <v>-3.555680450483079</v>
       </c>
       <c r="M6" s="19">
-        <v>-0.6604630651106772</v>
+        <v>0.2783169181116185</v>
       </c>
       <c r="N6" s="19">
-        <v>14.45283</v>
+        <v>21.095882</v>
       </c>
       <c r="O6" s="19">
-        <v>4.0580444</v>
+        <v>10.456314</v>
       </c>
       <c r="P6" s="11">
-        <v>0.27637</v>
+        <v>0.66638</v>
       </c>
       <c r="Q6" s="11">
-        <v>0.517</v>
+        <v>3.457</v>
       </c>
       <c r="R6" s="11">
-        <v>0.6989225766066014</v>
+        <v>1.459902343677745</v>
       </c>
       <c r="S6" s="10">
-        <v>71.73485687212836</v>
+        <v>50.4480833752696</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -3311,61 +3354,61 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E7" s="9">
-        <v>933.4400024414062</v>
+        <v>361.989990234375</v>
       </c>
       <c r="F7" s="16">
-        <v>1.025386247939589</v>
+        <v>0.9982238217869719</v>
       </c>
       <c r="G7" s="19">
-        <v>-0.4169145554552529</v>
+        <v>0.7600315297409044</v>
       </c>
       <c r="H7" s="19">
-        <v>1.817222982186202</v>
+        <v>-0.6800206488478429</v>
       </c>
       <c r="I7" s="19">
-        <v>4.262123054334927</v>
+        <v>2.817024529253408</v>
       </c>
       <c r="J7" s="19">
-        <v>1.504824209288006</v>
+        <v>2.045781364547568</v>
       </c>
       <c r="K7" s="19">
         <v>0</v>
       </c>
       <c r="L7" s="19">
-        <v>-3.540879496451628</v>
+        <v>0.1599036282170088</v>
       </c>
       <c r="M7" s="19">
-        <v>0.2677755323274389</v>
+        <v>-0.6824561043475547</v>
       </c>
       <c r="N7" s="19">
-        <v>21.095882</v>
+        <v>14.45283</v>
       </c>
       <c r="O7" s="19">
-        <v>10.456314</v>
+        <v>4.0580444</v>
       </c>
       <c r="P7" s="11">
-        <v>0.66638</v>
+        <v>0.27637</v>
       </c>
       <c r="Q7" s="11">
-        <v>3.457</v>
+        <v>0.517</v>
       </c>
       <c r="R7" s="11">
-        <v>1.459902541511058</v>
+        <v>0.6770724856664994</v>
       </c>
       <c r="S7" s="10">
-        <v>50.44808337545521</v>
+        <v>71.98558997611735</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -3385,7 +3428,7 @@
         <v>383</v>
       </c>
       <c r="F8" s="16">
-        <v>1.013107049998486</v>
+        <v>0.982242564910686</v>
       </c>
       <c r="G8" s="19">
         <v>0.749794509494801</v>
@@ -3397,16 +3440,16 @@
         <v>2.384116899919412</v>
       </c>
       <c r="J8" s="19">
-        <v>2.151988948534578</v>
+        <v>2.069028331699112</v>
       </c>
       <c r="K8" s="19">
         <v>0</v>
       </c>
       <c r="L8" s="19">
-        <v>0.1415381917108942</v>
+        <v>0.1553451170360356</v>
       </c>
       <c r="M8" s="19">
-        <v>-0.5525423981269584</v>
+        <v>-0.591304614953617</v>
       </c>
       <c r="N8" s="19">
         <v>12.788835</v>
@@ -3421,13 +3464,13 @@
         <v>0.537</v>
       </c>
       <c r="R8" s="11">
-        <v>0.8373577839171988</v>
+        <v>0.8186358330039056</v>
       </c>
       <c r="S8" s="10">
-        <v>76.16969901563091</v>
+        <v>76.46062468080775</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -3435,10 +3478,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>35</v>
@@ -3447,7 +3490,7 @@
         <v>252.0200042724609</v>
       </c>
       <c r="F9" s="16">
-        <v>0.8576426825884108</v>
+        <v>0.8298272742812407</v>
       </c>
       <c r="G9" s="19">
         <v>0.5236285305189845</v>
@@ -3459,16 +3502,16 @@
         <v>2.35386274831343</v>
       </c>
       <c r="J9" s="19">
-        <v>1.933570903080461</v>
+        <v>1.86587919084851</v>
       </c>
       <c r="K9" s="19">
         <v>0</v>
       </c>
       <c r="L9" s="19">
-        <v>0.3716359661134623</v>
+        <v>0.3717639462908604</v>
       </c>
       <c r="M9" s="19">
-        <v>-0.641884045829084</v>
+        <v>-0.6941056014711857</v>
       </c>
       <c r="N9" s="19">
         <v>13.92751</v>
@@ -3483,13 +3526,13 @@
         <v>0.531</v>
       </c>
       <c r="R9" s="11">
-        <v>0.5931889760361613</v>
+        <v>0.5971772702846527</v>
       </c>
       <c r="S9" s="10">
-        <v>74.79975638542247</v>
+        <v>75.0766147583623</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -3497,10 +3540,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>35</v>
@@ -3509,7 +3552,7 @@
         <v>60.95000076293945</v>
       </c>
       <c r="F10" s="16">
-        <v>0.7416152164942327</v>
+        <v>0.7318414924878126</v>
       </c>
       <c r="G10" s="19">
         <v>0.6434300221411974</v>
@@ -3521,16 +3564,16 @@
         <v>3.205794473836218</v>
       </c>
       <c r="J10" s="19">
-        <v>0.4497747115500537</v>
+        <v>0.4308767801046498</v>
       </c>
       <c r="K10" s="19">
         <v>0</v>
       </c>
       <c r="L10" s="19">
-        <v>0.2446154284544499</v>
+        <v>0.2589147002916439</v>
       </c>
       <c r="M10" s="19">
-        <v>-0.4007689226809722</v>
+        <v>-0.4481370977092229</v>
       </c>
       <c r="N10" s="19">
         <v>17.433628</v>
@@ -3545,13 +3588,13 @@
         <v>0.534</v>
       </c>
       <c r="R10" s="11">
-        <v>0.1348875740367874</v>
+        <v>0.1460926867579575</v>
       </c>
       <c r="S10" s="10">
-        <v>61.79694080641646</v>
+        <v>62.0836193844077</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -3559,10 +3602,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>35</v>
@@ -3571,7 +3614,7 @@
         <v>44.29999923706055</v>
       </c>
       <c r="F11" s="16">
-        <v>0.7192881616348453</v>
+        <v>0.7003478994320725</v>
       </c>
       <c r="G11" s="19">
         <v>1.180775573424393</v>
@@ -3583,16 +3626,16 @@
         <v>-0.2826661582517923</v>
       </c>
       <c r="J11" s="19">
-        <v>1.420805177002578</v>
+        <v>1.37926862407091</v>
       </c>
       <c r="K11" s="19">
         <v>0</v>
       </c>
       <c r="L11" s="19">
-        <v>-0.399077701318642</v>
+        <v>-0.3589036300700821</v>
       </c>
       <c r="M11" s="19">
-        <v>-0.5455571695216184</v>
+        <v>-0.6282685336947845</v>
       </c>
       <c r="N11" s="19">
         <v>8.974684</v>
@@ -3607,13 +3650,13 @@
         <v>0.092</v>
       </c>
       <c r="R11" s="11">
-        <v>0.4171789910797372</v>
+        <v>0.4100597191058337</v>
       </c>
       <c r="S11" s="10">
-        <v>67.24799565591081</v>
+        <v>67.58723769282514</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -3621,19 +3664,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E12" s="9">
         <v>135.6000061035156</v>
       </c>
       <c r="F12" s="16">
-        <v>0.6088418995787529</v>
+        <v>0.5826833835934309</v>
       </c>
       <c r="G12" s="19">
         <v>0.675065848973343</v>
@@ -3645,16 +3688,16 @@
         <v>0.2786698223080728</v>
       </c>
       <c r="J12" s="19">
-        <v>1.118134349214674</v>
+        <v>1.057353273888769</v>
       </c>
       <c r="K12" s="19">
         <v>0</v>
       </c>
       <c r="L12" s="19">
-        <v>0.006054055767980149</v>
+        <v>0.03267272758011818</v>
       </c>
       <c r="M12" s="19">
-        <v>0.03729723308461752</v>
+        <v>-0.04248141414088602</v>
       </c>
       <c r="N12" s="19">
         <v>9.331602999999999</v>
@@ -3669,13 +3712,13 @@
         <v>0.176</v>
       </c>
       <c r="R12" s="11">
-        <v>0.312129727571627</v>
+        <v>0.2874424165088272</v>
       </c>
       <c r="S12" s="10">
-        <v>68.50310275628433</v>
+        <v>69.12167518724334</v>
       </c>
       <c r="T12" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -3695,7 +3738,7 @@
         <v>425</v>
       </c>
       <c r="F13" s="16">
-        <v>0.5575835254090703</v>
+        <v>0.5634724334393638</v>
       </c>
       <c r="G13" s="19">
         <v>-0.1453667345878826</v>
@@ -3707,16 +3750,16 @@
         <v>2.981910484335923</v>
       </c>
       <c r="J13" s="19">
-        <v>1.727504144967455</v>
+        <v>1.760611623214541</v>
       </c>
       <c r="K13" s="19">
         <v>0</v>
       </c>
       <c r="L13" s="19">
-        <v>-2.047620412311253</v>
+        <v>-2.087579920682394</v>
       </c>
       <c r="M13" s="19">
-        <v>-0.3883829018771805</v>
+        <v>-0.4177883256921696</v>
       </c>
       <c r="N13" s="19">
         <v>36.353783</v>
@@ -3734,10 +3777,10 @@
         <v>1.941310647213375</v>
       </c>
       <c r="S13" s="10">
-        <v>44.90408763111304</v>
+        <v>44.90408763111321</v>
       </c>
       <c r="T13" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -3745,10 +3788,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>35</v>
@@ -3757,7 +3800,7 @@
         <v>211.0500030517578</v>
       </c>
       <c r="F14" s="16">
-        <v>0.5520359298556146</v>
+        <v>0.5509514940473</v>
       </c>
       <c r="G14" s="19">
         <v>0.5556735680703294</v>
@@ -3769,16 +3812,16 @@
         <v>2.258526107719387</v>
       </c>
       <c r="J14" s="19">
-        <v>0.7303891701553145</v>
+        <v>0.7258362127619501</v>
       </c>
       <c r="K14" s="19">
         <v>0</v>
       </c>
       <c r="L14" s="19">
-        <v>0.7696587846111567</v>
+        <v>0.7541316334328008</v>
       </c>
       <c r="M14" s="19">
-        <v>-0.6639901078481503</v>
+        <v>-0.6471999481307263</v>
       </c>
       <c r="N14" s="19">
         <v>19.409616</v>
@@ -3796,10 +3839,10 @@
         <v>0.1381140844875719</v>
       </c>
       <c r="S14" s="10">
-        <v>71.60464867022429</v>
+        <v>71.60464867147262</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -3807,10 +3850,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>35</v>
@@ -3819,7 +3862,7 @@
         <v>148.3500061035156</v>
       </c>
       <c r="F15" s="16">
-        <v>0.540241053062401</v>
+        <v>0.5218624047124374</v>
       </c>
       <c r="G15" s="19">
         <v>0.6252746191907743</v>
@@ -3831,16 +3874,16 @@
         <v>1.417737897842424</v>
       </c>
       <c r="J15" s="19">
-        <v>0.512632579233376</v>
+        <v>0.4763991543408084</v>
       </c>
       <c r="K15" s="19">
         <v>0</v>
       </c>
       <c r="L15" s="19">
-        <v>0.2772294195705438</v>
+        <v>0.2714881480820976</v>
       </c>
       <c r="M15" s="19">
-        <v>-0.2998917022206128</v>
+        <v>-0.3618755371067491</v>
       </c>
       <c r="N15" s="19">
         <v>11.1643305</v>
@@ -3855,13 +3898,13 @@
         <v>0.587</v>
       </c>
       <c r="R15" s="11">
-        <v>0.1707063379394265</v>
+        <v>0.1765593719944296</v>
       </c>
       <c r="S15" s="10">
-        <v>56.60881034200952</v>
+        <v>56.67336380021517</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3869,10 +3912,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>25</v>
@@ -3881,7 +3924,7 @@
         <v>217.4400024414062</v>
       </c>
       <c r="F16" s="16">
-        <v>0.5227387549492293</v>
+        <v>0.5195239940460369</v>
       </c>
       <c r="G16" s="19">
         <v>-1.186242168307697</v>
@@ -3893,16 +3936,16 @@
         <v>2.41778901771408</v>
       </c>
       <c r="J16" s="19">
-        <v>0.2212479063118502</v>
+        <v>0.217339146966691</v>
       </c>
       <c r="K16" s="19">
         <v>0</v>
       </c>
       <c r="L16" s="19">
-        <v>-0.1509467465621591</v>
+        <v>-0.1744576869211722</v>
       </c>
       <c r="M16" s="19">
-        <v>-0.06423513670330765</v>
+        <v>-0.0673064538248174</v>
       </c>
       <c r="N16" s="19">
         <v>27.468435</v>
@@ -3920,10 +3963,10 @@
         <v>0.2091375570176681</v>
       </c>
       <c r="S16" s="10">
-        <v>51.87290992384197</v>
+        <v>51.87290992412506</v>
       </c>
       <c r="T16" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3931,19 +3974,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E17" s="9">
         <v>257.8699951171875</v>
       </c>
       <c r="F17" s="16">
-        <v>0.5131665152254895</v>
+        <v>0.511682367530394</v>
       </c>
       <c r="G17" s="19">
         <v>1.2973242005594</v>
@@ -3955,16 +3998,16 @@
         <v>-0.05264739805840464</v>
       </c>
       <c r="J17" s="19">
-        <v>0.6125480538697033</v>
+        <v>0.5860972156165868</v>
       </c>
       <c r="K17" s="19">
         <v>0</v>
       </c>
       <c r="L17" s="19">
-        <v>0.442136474288886</v>
+        <v>0.5032064237461212</v>
       </c>
       <c r="M17" s="19">
-        <v>-0.1708483227941824</v>
+        <v>-0.1337857660839727</v>
       </c>
       <c r="N17" s="19">
         <v>5.156936</v>
@@ -3979,13 +4022,13 @@
         <v>0.118</v>
       </c>
       <c r="R17" s="11">
-        <v>0.2184079601631363</v>
+        <v>0.2186102950476296</v>
       </c>
       <c r="S17" s="10">
-        <v>49.93960247392307</v>
+        <v>50.78974543526481</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3993,61 +4036,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E18" s="9">
-        <v>438.1199951171875</v>
+        <v>66.91999816894531</v>
       </c>
       <c r="F18" s="16">
-        <v>0.5091334812988626</v>
+        <v>0.5011747706367228</v>
       </c>
       <c r="G18" s="19">
-        <v>-0.2455671553299525</v>
+        <v>0.4854005059534541</v>
       </c>
       <c r="H18" s="19">
-        <v>1.23829401915366</v>
+        <v>0.6587571460380149</v>
       </c>
       <c r="I18" s="19">
-        <v>-0.09681434526753466</v>
+        <v>0.2084671882916938</v>
       </c>
       <c r="J18" s="19">
-        <v>1.068465270265442</v>
+        <v>0.7709118149017465</v>
       </c>
       <c r="K18" s="19">
         <v>0</v>
       </c>
       <c r="L18" s="19">
-        <v>0.6880295267081549</v>
+        <v>0.5643958420327979</v>
       </c>
       <c r="M18" s="19">
-        <v>-0.7253426214695433</v>
+        <v>-0.4715431262381155</v>
       </c>
       <c r="N18" s="19">
-        <v>26.875078</v>
+        <v>14.762749</v>
       </c>
       <c r="O18" s="19">
-        <v>20.000925</v>
+        <v>6.0942793</v>
       </c>
       <c r="P18" s="11">
-        <v>0.91473</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q18" s="11">
-        <v>0.095</v>
+        <v>0.057</v>
       </c>
       <c r="R18" s="11">
-        <v>0.1511749006415839</v>
+        <v>0.1168442617445413</v>
       </c>
       <c r="S18" s="10">
-        <v>66.38286199743321</v>
+        <v>59.72925627702788</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4055,61 +4098,61 @@
         <v>15</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>98</v>
-      </c>
       <c r="E19" s="9">
-        <v>66.91999816894531</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="F19" s="16">
-        <v>0.5079512330182455</v>
+        <v>0.4991870071750666</v>
       </c>
       <c r="G19" s="19">
-        <v>0.4854005059534541</v>
+        <v>0.3535340411038917</v>
       </c>
       <c r="H19" s="19">
-        <v>0.6587571460380149</v>
+        <v>0.5066139843793523</v>
       </c>
       <c r="I19" s="19">
-        <v>0.2084671882916938</v>
+        <v>0.5284153400344015</v>
       </c>
       <c r="J19" s="19">
-        <v>0.7731015664864646</v>
+        <v>0.8959330828656217</v>
       </c>
       <c r="K19" s="19">
         <v>0</v>
       </c>
       <c r="L19" s="19">
-        <v>0.5802224593255341</v>
+        <v>0.05227462380159767</v>
       </c>
       <c r="M19" s="19">
-        <v>-0.4170835714536103</v>
+        <v>-0.3770966859570098</v>
       </c>
       <c r="N19" s="19">
-        <v>14.762749</v>
+        <v>15.843312</v>
       </c>
       <c r="O19" s="19">
-        <v>6.0942793</v>
+        <v>3.939749</v>
       </c>
       <c r="P19" s="11">
-        <v>0.46598998</v>
+        <v>0.30667</v>
       </c>
       <c r="Q19" s="11">
-        <v>0.057</v>
+        <v>0.377</v>
       </c>
       <c r="R19" s="11">
-        <v>0.09677911856043009</v>
+        <v>0.2747017694018412</v>
       </c>
       <c r="S19" s="10">
-        <v>60.01687384912778</v>
+        <v>54.59762999280038</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -4117,61 +4160,61 @@
         <v>16</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E20" s="9">
-        <v>125.0100021362305</v>
+        <v>438.1199951171875</v>
       </c>
       <c r="F20" s="16">
-        <v>0.5009062060594807</v>
+        <v>0.4902533915403123</v>
       </c>
       <c r="G20" s="19">
-        <v>0.3535340411038917</v>
+        <v>-0.2455671553299525</v>
       </c>
       <c r="H20" s="19">
-        <v>0.5066139843793523</v>
+        <v>1.23829401915366</v>
       </c>
       <c r="I20" s="19">
-        <v>0.5284153400344015</v>
+        <v>-0.09681434526753466</v>
       </c>
       <c r="J20" s="19">
-        <v>0.8680644952406645</v>
+        <v>1.049883740822111</v>
       </c>
       <c r="K20" s="19">
         <v>0</v>
       </c>
       <c r="L20" s="19">
-        <v>0.05624113697794832</v>
+        <v>0.6793780188228323</v>
       </c>
       <c r="M20" s="19">
-        <v>-0.2566531795171282</v>
+        <v>-0.8568542424871126</v>
       </c>
       <c r="N20" s="19">
-        <v>15.843312</v>
+        <v>26.875078</v>
       </c>
       <c r="O20" s="19">
-        <v>3.939749</v>
+        <v>20.000925</v>
       </c>
       <c r="P20" s="11">
-        <v>0.30667</v>
+        <v>0.91473</v>
       </c>
       <c r="Q20" s="11">
-        <v>0.377</v>
+        <v>0.095</v>
       </c>
       <c r="R20" s="11">
-        <v>0.2496001698539319</v>
+        <v>0.1777404730924301</v>
       </c>
       <c r="S20" s="10">
-        <v>54.52617136164081</v>
+        <v>66.50037520102745</v>
       </c>
       <c r="T20" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -4179,61 +4222,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="E21" s="9">
-        <v>304.2300109863281</v>
+        <v>450.4400024414062</v>
       </c>
       <c r="F21" s="16">
-        <v>0.4995295468227405</v>
+        <v>0.4821817488324344</v>
       </c>
       <c r="G21" s="19">
-        <v>0.02392519228507077</v>
+        <v>-0.9131978128854404</v>
       </c>
       <c r="H21" s="19">
-        <v>1.208973468219964</v>
+        <v>2.151528876753073</v>
       </c>
       <c r="I21" s="19">
-        <v>0.5934216790533486</v>
+        <v>2.950282622072772</v>
       </c>
       <c r="J21" s="19">
-        <v>0.8918103152716023</v>
+        <v>0.3905157979135979</v>
       </c>
       <c r="K21" s="19">
         <v>0</v>
       </c>
       <c r="L21" s="19">
-        <v>-0.4225670883207233</v>
+        <v>-3.555680450483079</v>
       </c>
       <c r="M21" s="19">
-        <v>-0.7460940688758423</v>
+        <v>0.5701093807382255</v>
       </c>
       <c r="N21" s="19">
-        <v>20.706474</v>
+        <v>17.067236</v>
       </c>
       <c r="O21" s="19">
-        <v>32.69876</v>
+        <v>21.967487</v>
       </c>
       <c r="P21" s="11">
-        <v>0.89489</v>
+        <v>1.30853</v>
       </c>
       <c r="Q21" s="11">
-        <v>0.14</v>
+        <v>0.438</v>
       </c>
       <c r="R21" s="11">
-        <v>0.4348987086786897</v>
+        <v>0.798703509252862</v>
       </c>
       <c r="S21" s="10">
-        <v>46.51005273293129</v>
+        <v>43.73367487654851</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -4241,61 +4284,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="E22" s="9">
-        <v>258.1099853515625</v>
+        <v>211.3399963378906</v>
       </c>
       <c r="F22" s="16">
-        <v>0.4760440696423573</v>
+        <v>0.478613974038153</v>
       </c>
       <c r="G22" s="19">
-        <v>0.3430645610428927</v>
+        <v>0.5887979504774438</v>
       </c>
       <c r="H22" s="19">
-        <v>0.5388891445188714</v>
+        <v>-0.657139695697852</v>
       </c>
       <c r="I22" s="19">
-        <v>0.1866157944506243</v>
+        <v>4.13232288715716</v>
       </c>
       <c r="J22" s="19">
-        <v>1.093659767973966</v>
+        <v>-0.0259549879248853</v>
       </c>
       <c r="K22" s="19">
         <v>0</v>
       </c>
       <c r="L22" s="19">
-        <v>-1.453801527371712</v>
+        <v>0.5020444814571686</v>
       </c>
       <c r="M22" s="19">
-        <v>0.1426684872448112</v>
+        <v>-0.1903680480798671</v>
       </c>
       <c r="N22" s="19">
-        <v>23.421774</v>
+        <v>11.935252</v>
       </c>
       <c r="O22" s="19">
-        <v>5.4897923</v>
+        <v>1.2848284</v>
       </c>
       <c r="P22" s="11">
-        <v>0.19381</v>
+        <v>0.09031</v>
       </c>
       <c r="Q22" s="11">
-        <v>0.108</v>
+        <v>11.11</v>
       </c>
       <c r="R22" s="11">
-        <v>0.3232508978324589</v>
+        <v>0.0994512657513924</v>
       </c>
       <c r="S22" s="10">
-        <v>81.25380620929735</v>
+        <v>44.70214501086372</v>
       </c>
       <c r="T22" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -4303,61 +4346,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>95</v>
-      </c>
       <c r="E23" s="9">
-        <v>211.3399963378906</v>
+        <v>304.2300109863281</v>
       </c>
       <c r="F23" s="16">
-        <v>0.4757683908515629</v>
+        <v>0.477386643070931</v>
       </c>
       <c r="G23" s="19">
-        <v>0.5887979504774438</v>
+        <v>0.02392519228507077</v>
       </c>
       <c r="H23" s="19">
-        <v>-0.657139695697852</v>
+        <v>1.208973468219964</v>
       </c>
       <c r="I23" s="19">
-        <v>4.13232288715716</v>
+        <v>0.5934216790533486</v>
       </c>
       <c r="J23" s="19">
-        <v>-0.03074398165902444</v>
+        <v>0.8637291421919383</v>
       </c>
       <c r="K23" s="19">
         <v>0</v>
       </c>
       <c r="L23" s="19">
-        <v>0.50624407711399</v>
+        <v>-0.5178448128974058</v>
       </c>
       <c r="M23" s="19">
-        <v>-0.2068604333719531</v>
+        <v>-0.812903317664495</v>
       </c>
       <c r="N23" s="19">
-        <v>11.935252</v>
+        <v>20.706474</v>
       </c>
       <c r="O23" s="19">
-        <v>1.2848284</v>
+        <v>32.69876</v>
       </c>
       <c r="P23" s="11">
-        <v>0.09031</v>
+        <v>0.89489</v>
       </c>
       <c r="Q23" s="11">
-        <v>11.11</v>
+        <v>0.14</v>
       </c>
       <c r="R23" s="11">
-        <v>0.09611312275134765</v>
+        <v>0.4222264736326597</v>
       </c>
       <c r="S23" s="10">
-        <v>45.11230677423562</v>
+        <v>46.34797987557869</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -4365,61 +4408,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="9">
-        <v>161.8500061035156</v>
+        <v>258.1099853515625</v>
       </c>
       <c r="F24" s="16">
-        <v>0.471575487146039</v>
+        <v>0.4737672745006869</v>
       </c>
       <c r="G24" s="19">
-        <v>-2.122778428838808</v>
+        <v>0.3430645610428927</v>
       </c>
       <c r="H24" s="19">
-        <v>1.765640568246892</v>
+        <v>0.5388891445188714</v>
       </c>
       <c r="I24" s="19">
-        <v>0.2349332652824272</v>
+        <v>0.1866157944506243</v>
       </c>
       <c r="J24" s="19">
-        <v>1.564637910547843</v>
+        <v>1.071170274982535</v>
       </c>
       <c r="K24" s="19">
         <v>0</v>
       </c>
       <c r="L24" s="19">
-        <v>-0.2547818898329872</v>
+        <v>-1.488611246144252</v>
       </c>
       <c r="M24" s="19">
-        <v>0.462328358217257</v>
+        <v>0.228066628483707</v>
       </c>
       <c r="N24" s="19">
-        <v>61.02941</v>
+        <v>23.421774</v>
       </c>
       <c r="O24" s="19">
-        <v>78.524124</v>
+        <v>5.4897923</v>
       </c>
       <c r="P24" s="11">
-        <v>1.17442</v>
+        <v>0.19381</v>
       </c>
       <c r="Q24" s="11">
-        <v>0.256</v>
+        <v>0.108</v>
       </c>
       <c r="R24" s="11">
-        <v>1.044076856273211</v>
+        <v>0.3232510013466021</v>
       </c>
       <c r="S24" s="10">
-        <v>52.73692094066809</v>
+        <v>81.2538061921633</v>
       </c>
       <c r="T24" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -4427,10 +4470,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>25</v>
@@ -4439,7 +4482,7 @@
         <v>30.02000045776367</v>
       </c>
       <c r="F25" s="16">
-        <v>0.4680722065995366</v>
+        <v>0.4703626612935455</v>
       </c>
       <c r="G25" s="19">
         <v>0.5167039359615127</v>
@@ -4451,16 +4494,16 @@
         <v>-0.1861321221296584</v>
       </c>
       <c r="J25" s="19">
-        <v>0.6780963960340513</v>
+        <v>0.6754516228084331</v>
       </c>
       <c r="K25" s="19">
         <v>0</v>
       </c>
       <c r="L25" s="19">
-        <v>0.2247602356716958</v>
+        <v>0.2083885519086353</v>
       </c>
       <c r="M25" s="19">
-        <v>0.008152865406482857</v>
+        <v>0.05554452945894361</v>
       </c>
       <c r="N25" s="19">
         <v>17.827587</v>
@@ -4475,13 +4518,13 @@
         <v>0.063</v>
       </c>
       <c r="R25" s="11">
-        <v>0.3563279010849416</v>
+        <v>0.3533004092198408</v>
       </c>
       <c r="S25" s="10">
-        <v>61.70036862510079</v>
+        <v>61.00117939203331</v>
       </c>
       <c r="T25" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -4489,61 +4532,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>116</v>
-      </c>
       <c r="E26" s="9">
-        <v>163.75</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="F26" s="16">
-        <v>0.4672299014324282</v>
+        <v>0.4594466748796265</v>
       </c>
       <c r="G26" s="19">
-        <v>0.5037681831878469</v>
+        <v>0.548854665636462</v>
       </c>
       <c r="H26" s="19">
-        <v>-0.5575001867977641</v>
+        <v>1.843831358372849</v>
       </c>
       <c r="I26" s="19">
-        <v>-0.04455757815619896</v>
+        <v>-0.6292233998564639</v>
       </c>
       <c r="J26" s="19">
-        <v>1.435967725119076</v>
+        <v>-0.00059659217896287</v>
       </c>
       <c r="K26" s="19">
         <v>0</v>
       </c>
       <c r="L26" s="19">
-        <v>0.2539051903365677</v>
+        <v>0.3910196239624897</v>
       </c>
       <c r="M26" s="19">
-        <v>-0.3985600120741293</v>
+        <v>0.6268294617679766</v>
       </c>
       <c r="N26" s="19">
-        <v>16.927385</v>
+        <v>14.242739</v>
       </c>
       <c r="O26" s="19">
-        <v>4.154594</v>
+        <v>-42.95995</v>
       </c>
       <c r="P26" s="11">
-        <v>0.26408002</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="11">
-        <v>0.053</v>
+        <v>0.012</v>
       </c>
       <c r="R26" s="11">
-        <v>0.4718198758607315</v>
+        <v>0.04214796324844805</v>
       </c>
       <c r="S26" s="10">
-        <v>63.12038567431014</v>
+        <v>54.99849936231556</v>
       </c>
       <c r="T26" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -4551,61 +4594,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>118</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="E27" s="9">
-        <v>69.56999969482422</v>
+        <v>161.8500061035156</v>
       </c>
       <c r="F27" s="16">
-        <v>0.4667048749607028</v>
+        <v>0.4522163357277649</v>
       </c>
       <c r="G27" s="19">
-        <v>0.548854665636462</v>
+        <v>-2.122778428838808</v>
       </c>
       <c r="H27" s="19">
-        <v>1.843831358372849</v>
+        <v>1.765640568246892</v>
       </c>
       <c r="I27" s="19">
-        <v>-0.6292233998564639</v>
+        <v>0.2349332652824272</v>
       </c>
       <c r="J27" s="19">
-        <v>0.02317164762853158</v>
+        <v>1.496674515977309</v>
       </c>
       <c r="K27" s="19">
         <v>0</v>
       </c>
       <c r="L27" s="19">
-        <v>0.3921848972101009</v>
+        <v>-0.3112253188577132</v>
       </c>
       <c r="M27" s="19">
-        <v>0.6166648084460049</v>
+        <v>0.5465729940242879</v>
       </c>
       <c r="N27" s="19">
-        <v>14.242739</v>
+        <v>61.02941</v>
       </c>
       <c r="O27" s="19">
-        <v>-42.95995</v>
+        <v>78.524124</v>
       </c>
       <c r="P27" s="11">
-        <v>0</v>
+        <v>1.17442</v>
       </c>
       <c r="Q27" s="11">
-        <v>0.012</v>
+        <v>0.256</v>
       </c>
       <c r="R27" s="11">
-        <v>0.04518237521385204</v>
+        <v>0.9956844531280942</v>
       </c>
       <c r="S27" s="10">
-        <v>54.8966572673663</v>
+        <v>52.07606850997672</v>
       </c>
       <c r="T27" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -4613,61 +4656,61 @@
         <v>24</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>120</v>
-      </c>
       <c r="D28" s="8" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="E28" s="9">
-        <v>136.1900024414062</v>
+        <v>108.2799987792969</v>
       </c>
       <c r="F28" s="16">
-        <v>0.4622732395981689</v>
+        <v>0.443311906352748</v>
       </c>
       <c r="G28" s="19">
-        <v>0.5373664552081702</v>
+        <v>0.08240686126983239</v>
       </c>
       <c r="H28" s="19">
-        <v>-0.1368691777673517</v>
+        <v>1.223451927469628</v>
       </c>
       <c r="I28" s="19">
-        <v>0.7891918304603867</v>
+        <v>0.1038485795344242</v>
       </c>
       <c r="J28" s="19">
-        <v>0.9258571555327707</v>
+        <v>0.4949138267917804</v>
       </c>
       <c r="K28" s="19">
         <v>0</v>
       </c>
       <c r="L28" s="19">
-        <v>0.3973511834359071</v>
+        <v>0.9108638936288646</v>
       </c>
       <c r="M28" s="19">
-        <v>-0.6067980420041242</v>
+        <v>-0.4247738180250054</v>
       </c>
       <c r="N28" s="19">
-        <v>17.128778</v>
+        <v>20.065575</v>
       </c>
       <c r="O28" s="19">
-        <v>2.396272</v>
+        <v>4.333084</v>
       </c>
       <c r="P28" s="11">
-        <v>0.1418</v>
+        <v>0.20273</v>
       </c>
       <c r="Q28" s="11">
-        <v>0.355</v>
+        <v>0.209</v>
       </c>
       <c r="R28" s="11">
-        <v>0.1681093072105853</v>
+        <v>0.1443239902155196</v>
       </c>
       <c r="S28" s="10">
-        <v>69.60407992037833</v>
+        <v>51.23363878194911</v>
       </c>
       <c r="T28" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -4675,61 +4718,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E29" s="9">
-        <v>450.4400024414062</v>
+        <v>136.1900024414062</v>
       </c>
       <c r="F29" s="16">
-        <v>0.4581215887060392</v>
+        <v>0.4406661699839187</v>
       </c>
       <c r="G29" s="19">
-        <v>-0.9131978128854404</v>
+        <v>0.5373664552081702</v>
       </c>
       <c r="H29" s="19">
-        <v>2.151528876753073</v>
+        <v>-0.1368691777673517</v>
       </c>
       <c r="I29" s="19">
-        <v>2.950282622072772</v>
+        <v>0.7891918304603867</v>
       </c>
       <c r="J29" s="19">
-        <v>0.3366630736324592</v>
+        <v>0.8872603049103714</v>
       </c>
       <c r="K29" s="19">
         <v>0</v>
       </c>
       <c r="L29" s="19">
-        <v>-3.540879496451628</v>
+        <v>0.4037509530729997</v>
       </c>
       <c r="M29" s="19">
-        <v>0.4962946198785601</v>
+        <v>-0.7045374451547004</v>
       </c>
       <c r="N29" s="19">
-        <v>17.067236</v>
+        <v>17.128778</v>
       </c>
       <c r="O29" s="19">
-        <v>21.967487</v>
+        <v>2.396272</v>
       </c>
       <c r="P29" s="11">
-        <v>1.30853</v>
+        <v>0.1418</v>
       </c>
       <c r="Q29" s="11">
-        <v>0.438</v>
+        <v>0.355</v>
       </c>
       <c r="R29" s="11">
-        <v>0.6690356163398388</v>
+        <v>0.1653496878943101</v>
       </c>
       <c r="S29" s="10">
-        <v>43.83463781720145</v>
+        <v>70.06544560580579</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -4737,61 +4780,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E30" s="9">
-        <v>108.2799987792969</v>
+        <v>163.75</v>
       </c>
       <c r="F30" s="16">
-        <v>0.4436142672502696</v>
+        <v>0.435098755732545</v>
       </c>
       <c r="G30" s="19">
-        <v>0.08240686126983239</v>
+        <v>0.5037681831878469</v>
       </c>
       <c r="H30" s="19">
-        <v>1.223451927469628</v>
+        <v>-0.5575001867977641</v>
       </c>
       <c r="I30" s="19">
-        <v>0.1038485795344242</v>
+        <v>-0.04455757815619896</v>
       </c>
       <c r="J30" s="19">
-        <v>0.4908742695999092</v>
+        <v>1.376152916180098</v>
       </c>
       <c r="K30" s="19">
         <v>0</v>
       </c>
       <c r="L30" s="19">
-        <v>0.9305031342973328</v>
+        <v>0.2591102656032267</v>
       </c>
       <c r="M30" s="19">
-        <v>-0.4210289391841021</v>
+        <v>-0.5316008877016696</v>
       </c>
       <c r="N30" s="19">
-        <v>20.065575</v>
+        <v>16.927385</v>
       </c>
       <c r="O30" s="19">
-        <v>4.333084</v>
+        <v>4.154594</v>
       </c>
       <c r="P30" s="11">
-        <v>0.20273</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q30" s="11">
-        <v>0.209</v>
+        <v>0.053</v>
       </c>
       <c r="R30" s="11">
-        <v>0.1413280553506242</v>
+        <v>0.3788563884206089</v>
       </c>
       <c r="S30" s="10">
-        <v>51.67770002511105</v>
+        <v>63.06512959779035</v>
       </c>
       <c r="T30" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -4799,61 +4842,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E31" s="9">
-        <v>363.9200134277344</v>
+        <v>394.8800048828125</v>
       </c>
       <c r="F31" s="16">
-        <v>0.4262581153554666</v>
+        <v>0.4266899433409234</v>
       </c>
       <c r="G31" s="19">
-        <v>1.231904824551268</v>
+        <v>0.3991025813752035</v>
       </c>
       <c r="H31" s="19">
-        <v>-0.1202756231839317</v>
+        <v>-1.053340414218987</v>
       </c>
       <c r="I31" s="19">
-        <v>-0.3776219198070676</v>
+        <v>0.1734891100083233</v>
       </c>
       <c r="J31" s="19">
-        <v>0.6145948754783469</v>
+        <v>1.469646792051797</v>
       </c>
       <c r="K31" s="19">
         <v>0</v>
       </c>
       <c r="L31" s="19">
-        <v>0.596224696895187</v>
+        <v>0.231240132611235</v>
       </c>
       <c r="M31" s="19">
-        <v>-0.1222672459187132</v>
+        <v>0.0008224399308530694</v>
       </c>
       <c r="N31" s="19">
-        <v>9.919549</v>
+        <v>37.178402</v>
       </c>
       <c r="O31" s="19">
-        <v>2.3296678</v>
+        <v>2.4096098</v>
       </c>
       <c r="P31" s="11">
-        <v>0.26511</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="Q31" s="11">
-        <v>0.003</v>
+        <v>0.262</v>
       </c>
       <c r="R31" s="11">
-        <v>0.1805841930692524</v>
+        <v>1.190890352688831</v>
       </c>
       <c r="S31" s="10">
-        <v>47.06174798442245</v>
+        <v>57.46312192737719</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4861,61 +4904,61 @@
         <v>28</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="E32" s="9">
-        <v>203.1600036621094</v>
+        <v>363.9200134277344</v>
       </c>
       <c r="F32" s="16">
-        <v>0.4260134819385445</v>
+        <v>0.4161574043172628</v>
       </c>
       <c r="G32" s="19">
-        <v>0.6290781538187236</v>
+        <v>1.231904824551268</v>
       </c>
       <c r="H32" s="19">
-        <v>-0.04474182683940042</v>
+        <v>-0.1202756231839317</v>
       </c>
       <c r="I32" s="19">
-        <v>1.575737480795989</v>
+        <v>-0.3776219198070676</v>
       </c>
       <c r="J32" s="19">
-        <v>0.4199180490295129</v>
+        <v>0.5689892073265229</v>
       </c>
       <c r="K32" s="19">
         <v>0</v>
       </c>
       <c r="L32" s="19">
-        <v>0.2033377509034909</v>
+        <v>0.6180822664272378</v>
       </c>
       <c r="M32" s="19">
-        <v>-0.3366617391226158</v>
+        <v>-0.07874698891865362</v>
       </c>
       <c r="N32" s="19">
-        <v>37.579845</v>
+        <v>9.919549</v>
       </c>
       <c r="O32" s="19">
-        <v>1.4633226</v>
+        <v>2.3296678</v>
       </c>
       <c r="P32" s="11">
-        <v>0.034930002</v>
+        <v>0.26511</v>
       </c>
       <c r="Q32" s="11">
-        <v>0.525</v>
+        <v>0.003</v>
       </c>
       <c r="R32" s="11">
-        <v>0.1546164081122456</v>
+        <v>0.1794453676755525</v>
       </c>
       <c r="S32" s="10">
-        <v>54.3947760974016</v>
+        <v>46.71708990737086</v>
       </c>
       <c r="T32" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4923,61 +4966,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="E33" s="9">
-        <v>394.8800048828125</v>
+        <v>203.1600036621094</v>
       </c>
       <c r="F33" s="16">
-        <v>0.4184221547240243</v>
+        <v>0.4151890752506984</v>
       </c>
       <c r="G33" s="19">
-        <v>0.3991025813752035</v>
+        <v>0.6290781538187236</v>
       </c>
       <c r="H33" s="19">
-        <v>-1.053340414218987</v>
+        <v>-0.04474182683940042</v>
       </c>
       <c r="I33" s="19">
-        <v>0.1734891100083233</v>
+        <v>1.575737480795989</v>
       </c>
       <c r="J33" s="19">
-        <v>1.42826630724615</v>
+        <v>0.3882911164010788</v>
       </c>
       <c r="K33" s="19">
         <v>0</v>
       </c>
       <c r="L33" s="19">
-        <v>0.2435062406524336</v>
+        <v>0.2680137895190494</v>
       </c>
       <c r="M33" s="19">
-        <v>0.0558540021352415</v>
+        <v>-0.3856362442939634</v>
       </c>
       <c r="N33" s="19">
-        <v>37.178402</v>
+        <v>37.579845</v>
       </c>
       <c r="O33" s="19">
-        <v>2.4096098</v>
+        <v>1.4633226</v>
       </c>
       <c r="P33" s="11">
-        <v>0.06893000000000001</v>
+        <v>0.034930002</v>
       </c>
       <c r="Q33" s="11">
-        <v>0.262</v>
+        <v>0.525</v>
       </c>
       <c r="R33" s="11">
-        <v>1.124209183441041</v>
+        <v>0.1639167547773164</v>
       </c>
       <c r="S33" s="10">
-        <v>57.13086874947128</v>
+        <v>54.29840659894472</v>
       </c>
       <c r="T33" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4985,61 +5028,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="E34" s="9">
-        <v>211.0399932861328</v>
+        <v>50.86999893188477</v>
       </c>
       <c r="F34" s="16">
-        <v>0.4126771874314553</v>
+        <v>0.4143734795843966</v>
       </c>
       <c r="G34" s="19">
-        <v>0.3599630250019414</v>
+        <v>0.2615753155071175</v>
       </c>
       <c r="H34" s="19">
-        <v>0.7749817441404762</v>
+        <v>-0.6923506737965556</v>
       </c>
       <c r="I34" s="19">
-        <v>0.3840583979359316</v>
+        <v>1.306361806653459</v>
       </c>
       <c r="J34" s="19">
-        <v>0.2766834873747249</v>
+        <v>1.441636790183564</v>
       </c>
       <c r="K34" s="19">
         <v>0</v>
       </c>
       <c r="L34" s="19">
-        <v>0.5555633725674428</v>
+        <v>-1.034124897997796</v>
       </c>
       <c r="M34" s="19">
-        <v>0.2452601627099722</v>
+        <v>-0.9092313848763797</v>
       </c>
       <c r="N34" s="19">
-        <v>17.362167</v>
+        <v>48.887848</v>
       </c>
       <c r="O34" s="19">
-        <v>3.1676524</v>
+        <v>2.7368805</v>
       </c>
       <c r="P34" s="11">
-        <v>0.17969999</v>
+        <v>0.06315</v>
       </c>
       <c r="Q34" s="11">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="R34" s="11">
-        <v>0.2774975167216034</v>
+        <v>1.37281915384833</v>
       </c>
       <c r="S34" s="10">
-        <v>45.09837584286628</v>
+        <v>45.56155343762117</v>
       </c>
       <c r="T34" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -5047,61 +5090,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="E35" s="9">
-        <v>50.86999893188477</v>
+        <v>211.0399932861328</v>
       </c>
       <c r="F35" s="16">
-        <v>0.4126047116989254</v>
+        <v>0.4074003248877019</v>
       </c>
       <c r="G35" s="19">
-        <v>0.2615753155071175</v>
+        <v>0.3599630250019414</v>
       </c>
       <c r="H35" s="19">
-        <v>-0.6923506737965556</v>
+        <v>0.7749817441404762</v>
       </c>
       <c r="I35" s="19">
-        <v>1.306361806653459</v>
+        <v>0.3840583979359316</v>
       </c>
       <c r="J35" s="19">
-        <v>1.416721464972737</v>
+        <v>0.2509594537838653</v>
       </c>
       <c r="K35" s="19">
         <v>0</v>
       </c>
       <c r="L35" s="19">
-        <v>-1.003222744291485</v>
+        <v>0.5759707794947954</v>
       </c>
       <c r="M35" s="19">
-        <v>-0.8584319773556982</v>
+        <v>0.2683742454988952</v>
       </c>
       <c r="N35" s="19">
-        <v>48.887848</v>
+        <v>17.362167</v>
       </c>
       <c r="O35" s="19">
-        <v>2.7368805</v>
+        <v>3.1676524</v>
       </c>
       <c r="P35" s="11">
-        <v>0.06315</v>
+        <v>0.17969999</v>
       </c>
       <c r="Q35" s="11">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="R35" s="11">
-        <v>1.37281915384833</v>
+        <v>0.2855805954504331</v>
       </c>
       <c r="S35" s="10">
-        <v>45.56155343779849</v>
+        <v>44.75446895024866</v>
       </c>
       <c r="T35" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -5109,61 +5152,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="E36" s="9">
-        <v>581.0999755859375</v>
+        <v>183.1600036621094</v>
       </c>
       <c r="F36" s="16">
-        <v>0.3916161455058922</v>
+        <v>0.4067274714559593</v>
       </c>
       <c r="G36" s="19">
-        <v>-1.47114938458048</v>
+        <v>-0.4206222377761193</v>
       </c>
       <c r="H36" s="19">
-        <v>2.900487942036482</v>
+        <v>1.258828701477971</v>
       </c>
       <c r="I36" s="19">
-        <v>-0.1716020620831971</v>
+        <v>-0.2081970290549548</v>
       </c>
       <c r="J36" s="19">
-        <v>0.40037687920062</v>
+        <v>1.118158985786578</v>
       </c>
       <c r="K36" s="19">
         <v>0</v>
       </c>
       <c r="L36" s="19">
-        <v>0.9788374955638623</v>
+        <v>-0.1102451625758058</v>
       </c>
       <c r="M36" s="19">
-        <v>-0.2041510092732939</v>
+        <v>-0.9474212203932401</v>
       </c>
       <c r="N36" s="19">
-        <v>32.565643</v>
+        <v>29.498423</v>
       </c>
       <c r="O36" s="19">
-        <v>93.07380000000001</v>
+        <v>27.131872</v>
       </c>
       <c r="P36" s="11">
-        <v>2.41202</v>
+        <v>1.06734</v>
       </c>
       <c r="Q36" s="11">
-        <v>0.141</v>
+        <v>0.125</v>
       </c>
       <c r="R36" s="11">
-        <v>0.1191447109428658</v>
+        <v>0.8691904851962537</v>
       </c>
       <c r="S36" s="10">
-        <v>56.95037286381055</v>
+        <v>45.70079166564421</v>
       </c>
       <c r="T36" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -5171,61 +5214,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E37" s="9">
-        <v>405.8399963378906</v>
+        <v>581.0999755859375</v>
       </c>
       <c r="F37" s="16">
-        <v>0.3894368626144686</v>
+        <v>0.3982279661457266</v>
       </c>
       <c r="G37" s="19">
-        <v>-0.9759620955182193</v>
+        <v>-1.47114938458048</v>
       </c>
       <c r="H37" s="19">
-        <v>-0.4326356610429035</v>
+        <v>2.900487942036482</v>
       </c>
       <c r="I37" s="19">
-        <v>4.13232288715716</v>
+        <v>-0.1716020620831971</v>
       </c>
       <c r="J37" s="19">
-        <v>0.5068170131519655</v>
+        <v>0.4204683210053206</v>
       </c>
       <c r="K37" s="19">
         <v>0</v>
       </c>
       <c r="L37" s="19">
-        <v>0.6306658220897489</v>
+        <v>0.9729194059013544</v>
       </c>
       <c r="M37" s="19">
-        <v>-0.1939752490726785</v>
+        <v>-0.2023253217558624</v>
       </c>
       <c r="N37" s="19">
-        <v>105.25127</v>
+        <v>32.565643</v>
       </c>
       <c r="O37" s="19">
-        <v>2.680677</v>
+        <v>93.07380000000001</v>
       </c>
       <c r="P37" s="11">
-        <v>0.019199999</v>
+        <v>2.41202</v>
       </c>
       <c r="Q37" s="11">
-        <v>1.134</v>
+        <v>0.141</v>
       </c>
       <c r="R37" s="11">
-        <v>0.3209646903796475</v>
+        <v>0.1120582336705458</v>
       </c>
       <c r="S37" s="10">
-        <v>52.52706816975237</v>
+        <v>55.7027144979971</v>
       </c>
       <c r="T37" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -5233,61 +5276,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="E38" s="9">
-        <v>279.2300109863281</v>
+        <v>31.31999969482422</v>
       </c>
       <c r="F38" s="16">
-        <v>0.3828445309878786</v>
+        <v>0.397033514189773</v>
       </c>
       <c r="G38" s="19">
-        <v>-0.7341033794993066</v>
+        <v>1.18884239126269</v>
       </c>
       <c r="H38" s="19">
-        <v>0.653024735669726</v>
+        <v>-0.9872240870343698</v>
       </c>
       <c r="I38" s="19">
-        <v>0.001731719619972795</v>
+        <v>-0.3680930717051557</v>
       </c>
       <c r="J38" s="19">
-        <v>1.373359834811231</v>
+        <v>1.332643894788734</v>
       </c>
       <c r="K38" s="19">
         <v>0</v>
       </c>
       <c r="L38" s="19">
-        <v>-0.8129850454590923</v>
+        <v>-0.4149864602001849</v>
       </c>
       <c r="M38" s="19">
-        <v>0.01444772742789091</v>
+        <v>-0.5591369708609789</v>
       </c>
       <c r="N38" s="19">
-        <v>45.4335</v>
+        <v>11.648855</v>
       </c>
       <c r="O38" s="19">
-        <v>6.1722584</v>
+        <v>-305.2</v>
       </c>
       <c r="P38" s="11">
-        <v>0.14425</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="11">
-        <v>0.176</v>
+        <v>0.125</v>
       </c>
       <c r="R38" s="11">
-        <v>0.5388813209292986</v>
+        <v>0.6946703650599875</v>
       </c>
       <c r="S38" s="10">
-        <v>74.60652658754897</v>
+        <v>61.90359088766113</v>
       </c>
       <c r="T38" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -5295,61 +5338,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="E39" s="9">
-        <v>183.1600036621094</v>
+        <v>405.8399963378906</v>
       </c>
       <c r="F39" s="16">
-        <v>0.3826329123088687</v>
+        <v>0.382609050369776</v>
       </c>
       <c r="G39" s="19">
-        <v>-0.4206222377761193</v>
+        <v>-0.9759620955182193</v>
       </c>
       <c r="H39" s="19">
-        <v>1.258828701477971</v>
+        <v>-0.4326356610429035</v>
       </c>
       <c r="I39" s="19">
-        <v>-0.2081970290549548</v>
+        <v>4.13232288715716</v>
       </c>
       <c r="J39" s="19">
-        <v>1.070023496104814</v>
+        <v>0.4890506651547327</v>
       </c>
       <c r="K39" s="19">
         <v>0</v>
       </c>
       <c r="L39" s="19">
-        <v>-0.239983863384239</v>
+        <v>0.659436157180652</v>
       </c>
       <c r="M39" s="19">
-        <v>-0.9346492590982962</v>
+        <v>-0.2240351300928499</v>
       </c>
       <c r="N39" s="19">
-        <v>29.498423</v>
+        <v>105.25127</v>
       </c>
       <c r="O39" s="19">
-        <v>27.131872</v>
+        <v>2.680677</v>
       </c>
       <c r="P39" s="11">
-        <v>1.06734</v>
+        <v>0.019199999</v>
       </c>
       <c r="Q39" s="11">
-        <v>0.125</v>
+        <v>1.134</v>
       </c>
       <c r="R39" s="11">
-        <v>0.8438074962251603</v>
+        <v>0.3001857413090314</v>
       </c>
       <c r="S39" s="10">
-        <v>45.96143628178666</v>
+        <v>52.07497110060028</v>
       </c>
       <c r="T39" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -5357,61 +5400,61 @@
         <v>36</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E40" s="9">
-        <v>93.19999694824219</v>
+        <v>372.6700134277344</v>
       </c>
       <c r="F40" s="16">
-        <v>0.3782564613751516</v>
+        <v>0.3756909398323499</v>
       </c>
       <c r="G40" s="19">
-        <v>0.1323994869339421</v>
+        <v>-0.8622441204646991</v>
       </c>
       <c r="H40" s="19">
-        <v>1.644369932284167</v>
+        <v>1.971798251919513</v>
       </c>
       <c r="I40" s="19">
-        <v>0.03944887499304424</v>
+        <v>-0.2184519826388571</v>
       </c>
       <c r="J40" s="19">
-        <v>0.15697387739312</v>
+        <v>0.4258115755662599</v>
       </c>
       <c r="K40" s="19">
         <v>0</v>
       </c>
       <c r="L40" s="19">
-        <v>0.3953052970028949</v>
+        <v>1.06278410242406</v>
       </c>
       <c r="M40" s="19">
-        <v>-0.3602597417607131</v>
+        <v>0.008236598469447687</v>
       </c>
       <c r="N40" s="19">
-        <v>16.766905</v>
+        <v>32.476597</v>
       </c>
       <c r="O40" s="19">
-        <v>18.876202</v>
+        <v>20.222574</v>
       </c>
       <c r="P40" s="11">
-        <v>1.5956</v>
+        <v>0.6119</v>
       </c>
       <c r="Q40" s="11">
-        <v>0.162</v>
+        <v>0.144</v>
       </c>
       <c r="R40" s="11">
-        <v>-0.04423676626675477</v>
+        <v>0.1661514393863721</v>
       </c>
       <c r="S40" s="10">
-        <v>52.36948930562311</v>
+        <v>54.30594212599105</v>
       </c>
       <c r="T40" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -5419,61 +5462,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E41" s="9">
-        <v>173.5</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="F41" s="16">
-        <v>0.3773951824522197</v>
+        <v>0.3754470288895859</v>
       </c>
       <c r="G41" s="19">
-        <v>0.5392511670723198</v>
+        <v>0.1323994869339421</v>
       </c>
       <c r="H41" s="19">
-        <v>0.5664211651255424</v>
+        <v>1.644369932284167</v>
       </c>
       <c r="I41" s="19">
-        <v>-0.05328793731108517</v>
+        <v>0.03944887499304424</v>
       </c>
       <c r="J41" s="19">
-        <v>0.3551382828586324</v>
+        <v>0.1614520495458911</v>
       </c>
       <c r="K41" s="19">
         <v>0</v>
       </c>
       <c r="L41" s="19">
-        <v>0.9356539578408296</v>
+        <v>0.3775047400407024</v>
       </c>
       <c r="M41" s="19">
-        <v>-0.1617095566510254</v>
+        <v>-0.3946062269531829</v>
       </c>
       <c r="N41" s="19">
-        <v>15.65096</v>
+        <v>16.766905</v>
       </c>
       <c r="O41" s="19">
-        <v>2.7135465</v>
+        <v>18.876202</v>
       </c>
       <c r="P41" s="11">
-        <v>0.18416001</v>
+        <v>1.5956</v>
       </c>
       <c r="Q41" s="11">
-        <v>0.151</v>
+        <v>0.162</v>
       </c>
       <c r="R41" s="11">
-        <v>0.1317852142544169</v>
+        <v>-0.03033542100628361</v>
       </c>
       <c r="S41" s="10">
-        <v>47.03672897866576</v>
+        <v>52.09734154570277</v>
       </c>
       <c r="T41" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -5481,61 +5524,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="E42" s="9">
-        <v>31.31999969482422</v>
+        <v>173.5</v>
       </c>
       <c r="F42" s="16">
-        <v>0.3765306999293311</v>
+        <v>0.3742032834294255</v>
       </c>
       <c r="G42" s="19">
-        <v>1.18884239126269</v>
+        <v>0.5392511670723198</v>
       </c>
       <c r="H42" s="19">
-        <v>-0.9872240870343698</v>
+        <v>0.5664211651255424</v>
       </c>
       <c r="I42" s="19">
-        <v>-0.3680930717051557</v>
+        <v>-0.05328793731108517</v>
       </c>
       <c r="J42" s="19">
-        <v>1.282655814237512</v>
+        <v>0.3318392787101034</v>
       </c>
       <c r="K42" s="19">
         <v>0</v>
       </c>
       <c r="L42" s="19">
-        <v>-0.3882822646386584</v>
+        <v>0.908183206613303</v>
       </c>
       <c r="M42" s="19">
-        <v>-0.6172407723299035</v>
+        <v>-0.08884611692413226</v>
       </c>
       <c r="N42" s="19">
-        <v>11.648855</v>
+        <v>15.65096</v>
       </c>
       <c r="O42" s="19">
-        <v>-305.2</v>
+        <v>2.7135465</v>
       </c>
       <c r="P42" s="11">
-        <v>0</v>
+        <v>0.18416001</v>
       </c>
       <c r="Q42" s="11">
-        <v>0.125</v>
+        <v>0.151</v>
       </c>
       <c r="R42" s="11">
-        <v>0.7227637365928901</v>
+        <v>0.1366433636618272</v>
       </c>
       <c r="S42" s="10">
-        <v>62.78791024319322</v>
+        <v>46.56301517390823</v>
       </c>
       <c r="T42" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -5543,61 +5586,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E43" s="9">
-        <v>372.6700134277344</v>
+        <v>279.2300109863281</v>
       </c>
       <c r="F43" s="16">
-        <v>0.3764471816204712</v>
+        <v>0.3625757988498952</v>
       </c>
       <c r="G43" s="19">
-        <v>-0.8622441204646991</v>
+        <v>-0.7341033794993066</v>
       </c>
       <c r="H43" s="19">
-        <v>1.971798251919513</v>
+        <v>0.653024735669726</v>
       </c>
       <c r="I43" s="19">
-        <v>-0.2184519826388571</v>
+        <v>0.001731719619972795</v>
       </c>
       <c r="J43" s="19">
-        <v>0.4255139254045108</v>
+        <v>1.317087280823995</v>
       </c>
       <c r="K43" s="19">
         <v>0</v>
       </c>
       <c r="L43" s="19">
-        <v>1.075759308177671</v>
+        <v>-0.8317433282113849</v>
       </c>
       <c r="M43" s="19">
-        <v>0.007940041930133312</v>
+        <v>0.01658246342642533</v>
       </c>
       <c r="N43" s="19">
-        <v>32.476597</v>
+        <v>45.4335</v>
       </c>
       <c r="O43" s="19">
-        <v>20.222574</v>
+        <v>6.1722584</v>
       </c>
       <c r="P43" s="11">
-        <v>0.6119</v>
+        <v>0.14425</v>
       </c>
       <c r="Q43" s="11">
-        <v>0.144</v>
+        <v>0.176</v>
       </c>
       <c r="R43" s="11">
-        <v>0.1673156612317195</v>
+        <v>0.5019633450915717</v>
       </c>
       <c r="S43" s="10">
-        <v>55.34628421874768</v>
+        <v>71.94310024507712</v>
       </c>
       <c r="T43" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -5605,19 +5648,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E44" s="9">
         <v>1002.559997558594</v>
       </c>
       <c r="F44" s="16">
-        <v>0.3633983433353277</v>
+        <v>0.3615089972733027</v>
       </c>
       <c r="G44" s="19">
         <v>0.3744813910308467</v>
@@ -5629,16 +5672,16 @@
         <v>0.9077656154464111</v>
       </c>
       <c r="J44" s="19">
-        <v>-0.01580374169888174</v>
+        <v>-0.03529280392525902</v>
       </c>
       <c r="K44" s="19">
         <v>0</v>
       </c>
       <c r="L44" s="19">
-        <v>0.04266007988564412</v>
+        <v>0.1072850274881307</v>
       </c>
       <c r="M44" s="19">
-        <v>0.3987050541748531</v>
+        <v>0.4025375201396288</v>
       </c>
       <c r="N44" s="19">
         <v>16.078215</v>
@@ -5653,13 +5696,13 @@
         <v>0.425</v>
       </c>
       <c r="R44" s="11">
-        <v>0.1743184821970312</v>
+        <v>0.1731204225933523</v>
       </c>
       <c r="S44" s="10">
-        <v>42.58530471072517</v>
+        <v>42.20008189154053</v>
       </c>
       <c r="T44" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -5725,110 +5768,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B6" s="11">
         <v>0.18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B7" s="11">
         <v>0.16</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B8" s="11">
         <v>0.1</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B9" s="11">
         <v>0.3</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B10" s="11">
         <v>0.12</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B11" s="11">
         <v>0.06</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B12" s="11">
         <v>0.08</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B13" s="11">
         <f>SUM(B6:B12)</f>
@@ -5837,22 +5880,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -5931,57 +5974,57 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>27</v>
@@ -5989,42 +6032,42 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6113,738 +6156,729 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI6"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:60">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>400.1088256835938</v>
+        <v>381.1501770019531</v>
       </c>
       <c r="C1">
-        <v>381.1501770019531</v>
+        <v>369.2198791503906</v>
       </c>
       <c r="D1">
-        <v>369.2198791503906</v>
+        <v>390.8042297363281</v>
       </c>
       <c r="E1">
-        <v>390.8042297363281</v>
+        <v>394.9174194335938</v>
       </c>
       <c r="F1">
-        <v>394.9174194335938</v>
+        <v>408.3951416015625</v>
       </c>
       <c r="G1">
-        <v>408.3951416015625</v>
+        <v>403.4133605957031</v>
       </c>
       <c r="H1">
-        <v>403.4133605957031</v>
+        <v>418.6282348632812</v>
       </c>
       <c r="I1">
-        <v>418.6282348632812</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="J1">
-        <v>408.8244323730469</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="K1">
-        <v>418.0192260742188</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="L1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="M1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="N1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="O1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="P1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="Q1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="R1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="S1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="T1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="U1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="V1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="W1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="X1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="Y1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="Z1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="AA1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="AB1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="AC1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="AD1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="AE1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="AF1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="AG1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="AH1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AI1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AJ1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AK1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AL1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AM1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AN1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AO1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AP1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AQ1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AR1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AS1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AT1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AU1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AV1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AW1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AX1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AY1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="AZ1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="BA1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="BB1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="BC1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="BD1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="BE1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="BF1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
       <c r="BG1">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="BH1">
-        <v>456.010009765625</v>
-      </c>
-      <c r="BI1">
         <v>425</v>
       </c>
     </row>
-    <row r="2" spans="1:61">
+    <row r="2" spans="1:60">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>949.134033203125</v>
+        <v>935.74609375</v>
       </c>
       <c r="C2">
-        <v>935.74609375</v>
+        <v>891.7428588867188</v>
       </c>
       <c r="D2">
-        <v>891.7428588867188</v>
+        <v>995.7168579101562</v>
       </c>
       <c r="E2">
-        <v>995.7168579101562</v>
+        <v>981.4590454101562</v>
       </c>
       <c r="F2">
-        <v>981.4590454101562</v>
+        <v>1087.822631835938</v>
       </c>
       <c r="G2">
-        <v>1087.822631835938</v>
+        <v>1020.60302734375</v>
       </c>
       <c r="H2">
-        <v>1020.60302734375</v>
+        <v>1043.029541015625</v>
       </c>
       <c r="I2">
-        <v>1043.029541015625</v>
+        <v>1133.815551757812</v>
       </c>
       <c r="J2">
-        <v>1133.815551757812</v>
+        <v>1211.193725585938</v>
       </c>
       <c r="K2">
-        <v>1211.193725585938</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="L2">
-        <v>1051.608276367188</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="M2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="N2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="O2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="P2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="Q2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="R2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="S2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="T2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="U2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="V2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="W2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="X2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="Y2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="Z2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="AA2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="AB2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="AC2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="AD2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="AE2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="AF2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="AG2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="AH2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="AI2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AJ2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="AK2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AL2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AM2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AN2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AO2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AP2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AQ2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AR2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AS2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AT2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AU2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AV2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AW2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="AX2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AY2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="AZ2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="BA2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="BB2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="BC2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="BD2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="BE2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="BF2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="BG2">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="BH2">
-        <v>958.72998046875</v>
-      </c>
-      <c r="BI2">
         <v>933.4400024414062</v>
       </c>
     </row>
-    <row r="3" spans="1:61">
+    <row r="3" spans="1:60">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1642</v>
+        <v>1646.5400390625</v>
       </c>
       <c r="C3">
-        <v>1646.5400390625</v>
+        <v>1643.22998046875</v>
       </c>
       <c r="D3">
-        <v>1643.22998046875</v>
+        <v>1881.510009765625</v>
       </c>
       <c r="E3">
-        <v>1881.510009765625</v>
+        <v>1980.099975585938</v>
       </c>
       <c r="F3">
-        <v>1980.099975585938</v>
+        <v>2107.860107421875</v>
       </c>
       <c r="G3">
-        <v>2107.860107421875</v>
+        <v>1991.550048828125</v>
       </c>
       <c r="H3">
-        <v>1991.550048828125</v>
+        <v>1958.800048828125</v>
       </c>
       <c r="I3">
-        <v>1958.800048828125</v>
+        <v>2184.75</v>
       </c>
       <c r="J3">
-        <v>2184.75</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="K3">
+        <v>1963.599975585938</v>
+      </c>
+      <c r="L3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="M3">
+        <v>2335</v>
+      </c>
+      <c r="N3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="O3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="P3">
         <v>2273.72998046875</v>
       </c>
-      <c r="L3">
-        <v>1963.599975585938</v>
-      </c>
-      <c r="M3">
-        <v>1914.4599609375</v>
-      </c>
-      <c r="N3">
-        <v>2335</v>
-      </c>
-      <c r="O3">
-        <v>2090.7099609375</v>
-      </c>
-      <c r="P3">
-        <v>2050.389892578125</v>
-      </c>
       <c r="Q3">
-        <v>2273.72998046875</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="R3">
-        <v>2032.219970703125</v>
+        <v>1745</v>
       </c>
       <c r="S3">
-        <v>1745</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="T3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="U3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="V3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="W3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="X3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="Y3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="Z3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="AA3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="AB3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="AC3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="AD3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="AE3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="AF3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="AG3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="AH3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="AI3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="AJ3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AK3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AL3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AM3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AN3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AO3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="AP3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AQ3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AR3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AS3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AT3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AU3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AV3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AW3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AX3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AY3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="AZ3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="BA3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="BB3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="BC3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="BD3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="BE3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="BF3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="BG3">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="BH3">
-        <v>1566.699951171875</v>
-      </c>
-      <c r="BI3">
         <v>1536.869995117188</v>
       </c>
     </row>
-    <row r="4" spans="1:61">
+    <row r="4" spans="1:60">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>526.9299926757812</v>
+        <v>517.719970703125</v>
       </c>
       <c r="C4">
-        <v>517.719970703125</v>
+        <v>490.0899963378906</v>
       </c>
       <c r="D4">
-        <v>490.0899963378906</v>
+        <v>529.2899780273438</v>
       </c>
       <c r="E4">
-        <v>529.2899780273438</v>
+        <v>562.9299926757812</v>
       </c>
       <c r="F4">
-        <v>562.9299926757812</v>
+        <v>653.530029296875</v>
       </c>
       <c r="G4">
-        <v>653.530029296875</v>
+        <v>681.0800170898438</v>
       </c>
       <c r="H4">
-        <v>681.0800170898438</v>
+        <v>712.1300048828125</v>
       </c>
       <c r="I4">
-        <v>712.1300048828125</v>
+        <v>746.22998046875</v>
       </c>
       <c r="J4">
-        <v>746.22998046875</v>
+        <v>732.6199951171875</v>
       </c>
       <c r="K4">
-        <v>732.6199951171875</v>
+        <v>670.75</v>
       </c>
       <c r="L4">
-        <v>670.75</v>
+        <v>643.8300170898438</v>
       </c>
       <c r="M4">
-        <v>643.8300170898438</v>
+        <v>675.3900146484375</v>
       </c>
       <c r="N4">
-        <v>675.3900146484375</v>
+        <v>586.4500122070312</v>
       </c>
       <c r="O4">
-        <v>586.4500122070312</v>
+        <v>651.8800048828125</v>
       </c>
       <c r="P4">
-        <v>651.8800048828125</v>
+        <v>638.719970703125</v>
       </c>
       <c r="Q4">
-        <v>638.719970703125</v>
+        <v>598.3699951171875</v>
       </c>
       <c r="R4">
-        <v>598.3699951171875</v>
+        <v>539</v>
       </c>
       <c r="S4">
-        <v>539</v>
+        <v>577.4600219726562</v>
       </c>
       <c r="T4">
-        <v>577.4600219726562</v>
+        <v>532.0999755859375</v>
       </c>
       <c r="U4">
-        <v>532.0999755859375</v>
+        <v>550.2999877929688</v>
       </c>
       <c r="V4">
-        <v>550.2999877929688</v>
+        <v>578.0499877929688</v>
       </c>
       <c r="W4">
-        <v>578.0499877929688</v>
+        <v>582.5900268554688</v>
       </c>
       <c r="X4">
-        <v>582.5900268554688</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="Y4">
-        <v>555.5499877929688</v>
+        <v>563.3200073242188</v>
       </c>
       <c r="Z4">
-        <v>563.3200073242188</v>
+        <v>513.8400268554688</v>
       </c>
       <c r="AA4">
-        <v>513.8400268554688</v>
+        <v>466.8099975585938</v>
       </c>
       <c r="AB4">
-        <v>466.8099975585938</v>
+        <v>477.2200012207031</v>
       </c>
       <c r="AC4">
-        <v>477.2200012207031</v>
+        <v>487.4200134277344</v>
       </c>
       <c r="AD4">
-        <v>487.4200134277344</v>
+        <v>548.3900146484375</v>
       </c>
       <c r="AE4">
-        <v>548.3900146484375</v>
+        <v>556.6699829101562</v>
       </c>
       <c r="AF4">
-        <v>556.6699829101562</v>
+        <v>558.2999877929688</v>
       </c>
       <c r="AG4">
-        <v>558.2999877929688</v>
+        <v>519.7999877929688</v>
       </c>
       <c r="AH4">
-        <v>519.7999877929688</v>
+        <v>497.9200134277344</v>
       </c>
       <c r="AI4">
-        <v>497.9200134277344</v>
+        <v>463.510009765625</v>
       </c>
       <c r="AJ4">
-        <v>463.510009765625</v>
+        <v>462.0400085449219</v>
       </c>
       <c r="AK4">
-        <v>462.0400085449219</v>
+        <v>533.0399780273438</v>
       </c>
       <c r="AL4">
-        <v>533.0399780273438</v>
+        <v>544.8400268554688</v>
       </c>
       <c r="AM4">
-        <v>544.8400268554688</v>
+        <v>527.219970703125</v>
       </c>
       <c r="AN4">
-        <v>527.219970703125</v>
+        <v>548.5599975585938</v>
       </c>
       <c r="AO4">
-        <v>548.5599975585938</v>
+        <v>519.1699829101562</v>
       </c>
       <c r="AP4">
-        <v>519.1699829101562</v>
+        <v>451.5199890136719</v>
       </c>
       <c r="AQ4">
-        <v>451.5199890136719</v>
+        <v>434.2999877929688</v>
       </c>
       <c r="AR4">
-        <v>434.2999877929688</v>
+        <v>438.3399963378906</v>
       </c>
       <c r="AS4">
-        <v>438.3399963378906</v>
+        <v>437.9299926757812</v>
       </c>
       <c r="AT4">
-        <v>437.9299926757812</v>
+        <v>454.1000061035156</v>
       </c>
       <c r="AU4">
-        <v>454.1000061035156</v>
+        <v>487.2900085449219</v>
       </c>
       <c r="AV4">
-        <v>487.2900085449219</v>
+        <v>508.7999877929688</v>
       </c>
       <c r="AW4">
-        <v>508.7999877929688</v>
+        <v>536.010009765625</v>
       </c>
       <c r="AX4">
-        <v>536.010009765625</v>
+        <v>496.1600036621094</v>
       </c>
       <c r="AY4">
-        <v>496.1600036621094</v>
+        <v>462.0899963378906</v>
       </c>
       <c r="AZ4">
-        <v>462.0899963378906</v>
+        <v>469.0499877929688</v>
       </c>
       <c r="BA4">
-        <v>469.0499877929688</v>
+        <v>459.4400024414062</v>
       </c>
       <c r="BB4">
-        <v>459.4400024414062</v>
+        <v>435.3800048828125</v>
       </c>
       <c r="BC4">
-        <v>435.3800048828125</v>
+        <v>450.75</v>
       </c>
       <c r="BD4">
-        <v>450.75</v>
+        <v>468.8800048828125</v>
       </c>
       <c r="BE4">
-        <v>468.8800048828125</v>
+        <v>462</v>
       </c>
       <c r="BF4">
-        <v>462</v>
+        <v>459.4500122070312</v>
       </c>
       <c r="BG4">
         <v>450.5499877929688</v>
@@ -6853,180 +6887,180 @@
         <v>450.4400024414062</v>
       </c>
     </row>
-    <row r="5" spans="1:61">
+    <row r="5" spans="1:60">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>257.3952941894531</v>
+        <v>252.8030090332031</v>
       </c>
       <c r="C5">
-        <v>252.8030090332031</v>
+        <v>256.9967956542969</v>
       </c>
       <c r="D5">
-        <v>256.9967956542969</v>
+        <v>254.6160125732422</v>
       </c>
       <c r="E5">
-        <v>254.6160125732422</v>
+        <v>257.6741943359375</v>
       </c>
       <c r="F5">
-        <v>257.6741943359375</v>
+        <v>246.20849609375</v>
       </c>
       <c r="G5">
-        <v>246.20849609375</v>
+        <v>243.1901702880859</v>
       </c>
       <c r="H5">
-        <v>243.1901702880859</v>
+        <v>238.8469543457031</v>
       </c>
       <c r="I5">
-        <v>238.8469543457031</v>
+        <v>235.3903045654297</v>
       </c>
       <c r="J5">
-        <v>235.3903045654297</v>
+        <v>242.8415069580078</v>
       </c>
       <c r="K5">
-        <v>242.8415069580078</v>
+        <v>242.7418823242188</v>
       </c>
       <c r="L5">
-        <v>242.7418823242188</v>
+        <v>241.4967041015625</v>
       </c>
       <c r="M5">
-        <v>241.4967041015625</v>
+        <v>254.0780792236328</v>
       </c>
       <c r="N5">
-        <v>254.0780792236328</v>
+        <v>258.3714904785156</v>
       </c>
       <c r="O5">
-        <v>258.3714904785156</v>
+        <v>265.2947387695312</v>
       </c>
       <c r="P5">
-        <v>265.2947387695312</v>
+        <v>259.4373779296875</v>
       </c>
       <c r="Q5">
-        <v>259.4373779296875</v>
+        <v>268.4027404785156</v>
       </c>
       <c r="R5">
-        <v>268.4027404785156</v>
+        <v>266.7291870117188</v>
       </c>
       <c r="S5">
-        <v>266.7291870117188</v>
+        <v>269.2793579101562</v>
       </c>
       <c r="T5">
-        <v>269.2793579101562</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="U5">
-        <v>265.1951293945312</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="V5">
-        <v>281.7909851074219</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="W5">
-        <v>280.1672668457031</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="X5">
-        <v>279.6094055175781</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="Y5">
-        <v>294.6513061523438</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="Z5">
-        <v>300.2695617675781</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="AA5">
-        <v>291.5333251953125</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="AB5">
-        <v>299.1040954589844</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="AC5">
-        <v>308.4579162597656</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="AD5">
-        <v>312.1038208007812</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="AE5">
-        <v>313.5880737304688</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="AF5">
-        <v>309.7230529785156</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="AG5">
-        <v>304.0848388671875</v>
+        <v>301.33544921875</v>
       </c>
       <c r="AH5">
-        <v>301.33544921875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="AI5">
-        <v>303.756103515625</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="AJ5">
-        <v>297.7294006347656</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="AK5">
-        <v>300.1600036621094</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="AL5">
-        <v>310.5099792480469</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="AM5">
-        <v>312.8999938964844</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="AN5">
-        <v>307.5400085449219</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="AO5">
-        <v>308.7300109863281</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="AP5">
-        <v>302.3900146484375</v>
+        <v>302.989990234375</v>
       </c>
       <c r="AQ5">
-        <v>302.989990234375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="AR5">
-        <v>298.3099975585938</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AS5">
-        <v>314.9500122070312</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AT5">
-        <v>323.9200134277344</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AU5">
-        <v>330.2099914550781</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AV5">
-        <v>342.9200134277344</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AW5">
-        <v>341.6700134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AX5">
-        <v>347.1900024414062</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AY5">
-        <v>350.0499877929688</v>
+        <v>346.260009765625</v>
       </c>
       <c r="AZ5">
-        <v>346.260009765625</v>
+        <v>341.510009765625</v>
       </c>
       <c r="BA5">
-        <v>341.510009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="BB5">
-        <v>348.8599853515625</v>
+        <v>346</v>
       </c>
       <c r="BC5">
-        <v>346</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="BD5">
-        <v>340.4100036621094</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="BE5">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="BF5">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="BG5">
         <v>358.9200134277344</v>
@@ -7035,180 +7069,180 @@
         <v>361.989990234375</v>
       </c>
     </row>
-    <row r="6" spans="1:61">
+    <row r="6" spans="1:60">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>265.4432067871094</v>
+        <v>257.445068359375</v>
       </c>
       <c r="C6">
-        <v>257.445068359375</v>
+        <v>262.5610656738281</v>
       </c>
       <c r="D6">
-        <v>262.5610656738281</v>
+        <v>260.0978088378906</v>
       </c>
       <c r="E6">
-        <v>260.0978088378906</v>
+        <v>262.8602294921875</v>
       </c>
       <c r="F6">
-        <v>262.8602294921875</v>
+        <v>250.1749877929688</v>
       </c>
       <c r="G6">
-        <v>250.1749877929688</v>
+        <v>249.7860565185547</v>
       </c>
       <c r="H6">
-        <v>249.7860565185547</v>
+        <v>243.9420471191406</v>
       </c>
       <c r="I6">
-        <v>243.9420471191406</v>
+        <v>242.2467041015625</v>
       </c>
       <c r="J6">
-        <v>242.2467041015625</v>
+        <v>246.6147308349609</v>
       </c>
       <c r="K6">
-        <v>246.6147308349609</v>
+        <v>247.8413848876953</v>
       </c>
       <c r="L6">
-        <v>247.8413848876953</v>
+        <v>245.8368530273438</v>
       </c>
       <c r="M6">
-        <v>245.8368530273438</v>
+        <v>252.8676147460938</v>
       </c>
       <c r="N6">
-        <v>252.8676147460938</v>
+        <v>253.3662414550781</v>
       </c>
       <c r="O6">
-        <v>253.3662414550781</v>
+        <v>258.5121459960938</v>
       </c>
       <c r="P6">
-        <v>258.5121459960938</v>
+        <v>254.9718475341797</v>
       </c>
       <c r="Q6">
-        <v>254.9718475341797</v>
+        <v>264.146728515625</v>
       </c>
       <c r="R6">
-        <v>264.146728515625</v>
+        <v>265.6226806640625</v>
       </c>
       <c r="S6">
-        <v>265.6226806640625</v>
+        <v>268.2554626464844</v>
       </c>
       <c r="T6">
-        <v>268.2554626464844</v>
+        <v>265.6027221679688</v>
       </c>
       <c r="U6">
-        <v>265.6027221679688</v>
+        <v>279.9135437011719</v>
       </c>
       <c r="V6">
-        <v>279.9135437011719</v>
+        <v>282.5263977050781</v>
       </c>
       <c r="W6">
-        <v>282.5263977050781</v>
+        <v>282.9651794433594</v>
       </c>
       <c r="X6">
-        <v>282.9651794433594</v>
+        <v>296.0693359375</v>
       </c>
       <c r="Y6">
-        <v>296.0693359375</v>
+        <v>302.5715026855469</v>
       </c>
       <c r="Z6">
-        <v>302.5715026855469</v>
+        <v>298.363037109375</v>
       </c>
       <c r="AA6">
-        <v>298.363037109375</v>
+        <v>305.0148315429688</v>
       </c>
       <c r="AB6">
-        <v>305.0148315429688</v>
+        <v>311.7463989257812</v>
       </c>
       <c r="AC6">
-        <v>311.7463989257812</v>
+        <v>314.4490051269531</v>
       </c>
       <c r="AD6">
-        <v>314.4490051269531</v>
+        <v>318.8868408203125</v>
       </c>
       <c r="AE6">
-        <v>318.8868408203125</v>
+        <v>314.9576110839844</v>
       </c>
       <c r="AF6">
-        <v>314.9576110839844</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="AG6">
-        <v>311.4172973632812</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="AH6">
-        <v>308.3955688476562</v>
+        <v>311.4970703125</v>
       </c>
       <c r="AI6">
-        <v>311.4970703125</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="AJ6">
-        <v>305.2142639160156</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="AK6">
-        <v>307.8769836425781</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="AL6">
-        <v>313.2223510742188</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="AM6">
-        <v>315.6058349609375</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="AN6">
-        <v>306.1915893554688</v>
+        <v>311.75634765625</v>
       </c>
       <c r="AO6">
-        <v>311.75634765625</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="AP6">
-        <v>296.9369506835938</v>
+        <v>298.432861328125</v>
       </c>
       <c r="AQ6">
-        <v>298.432861328125</v>
+        <v>297.3857421875</v>
       </c>
       <c r="AR6">
-        <v>297.3857421875</v>
+        <v>319.4453125</v>
       </c>
       <c r="AS6">
-        <v>319.4453125</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="AT6">
-        <v>335.5013732910156</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="AU6">
-        <v>347.2990417480469</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="AV6">
-        <v>355.3968811035156</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="AW6">
-        <v>354.4494934082031</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="AX6">
-        <v>357.2019348144531</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="AY6">
-        <v>365.2099914550781</v>
+        <v>360.75</v>
       </c>
       <c r="AZ6">
-        <v>360.75</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="BA6">
-        <v>358.2300109863281</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="BB6">
-        <v>360.7200012207031</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="BC6">
-        <v>362.5199890136719</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="BD6">
-        <v>354.8800048828125</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="BE6">
-        <v>362.2699890136719</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="BF6">
-        <v>363.5400085449219</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="BG6">
         <v>373.3200073242188</v>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="238">
   <si>
     <t>DELL</t>
   </si>
@@ -207,6 +207,9 @@
     <t>2026-09-02</t>
   </si>
   <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -291,6 +294,12 @@
     <t>Materials</t>
   </si>
   <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>Nvidia</t>
+  </si>
+  <si>
     <t>CVX</t>
   </si>
   <si>
@@ -303,12 +312,6 @@
     <t>EOG Resources</t>
   </si>
   <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>Nvidia</t>
-  </si>
-  <si>
     <t>ALL</t>
   </si>
   <si>
@@ -318,33 +321,39 @@
     <t>Financials</t>
   </si>
   <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>Gen Digital</t>
+  </si>
+  <si>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
     <t>BMY</t>
   </si>
   <si>
     <t>Bristol Myers Squibb</t>
   </si>
   <si>
-    <t>Health Care</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
     <t>AMGN</t>
   </si>
   <si>
     <t>Amgen</t>
   </si>
   <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>Capital One</t>
-  </si>
-  <si>
     <t>EXPE</t>
   </si>
   <si>
@@ -354,18 +363,18 @@
     <t>Consumer Discretionary</t>
   </si>
   <si>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
+  </si>
+  <si>
     <t>CRM</t>
   </si>
   <si>
     <t>Salesforce</t>
   </si>
   <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>Gen Digital</t>
-  </si>
-  <si>
     <t>MO</t>
   </si>
   <si>
@@ -375,10 +384,16 @@
     <t>Consumer Staples</t>
   </si>
   <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
+  </si>
+  <si>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>Humana</t>
   </si>
   <si>
     <t>SCHW</t>
@@ -387,10 +402,22 @@
     <t>Charles Schwab Corporation</t>
   </si>
   <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
+    <t>CPAY</t>
+  </si>
+  <si>
+    <t>Corpay</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
   </si>
   <si>
     <t>TGT</t>
@@ -399,16 +426,16 @@
     <t>Target Corporation</t>
   </si>
   <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
-  </si>
-  <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>Mastercard</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise</t>
   </si>
   <si>
     <t>FANG</t>
@@ -417,16 +444,22 @@
     <t>Diamondback Energy</t>
   </si>
   <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>Hewlett Packard Enterprise</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>Waters Corporation</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Visa Inc.</t>
+  </si>
+  <si>
+    <t>RJF</t>
+  </si>
+  <si>
+    <t>Raymond James Financial</t>
   </si>
   <si>
     <t>NTAP</t>
@@ -435,46 +468,16 @@
     <t>NetApp</t>
   </si>
   <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>Mastercard</t>
-  </si>
-  <si>
-    <t>HPQ</t>
-  </si>
-  <si>
-    <t>HP Inc.</t>
-  </si>
-  <si>
-    <t>WAT</t>
-  </si>
-  <si>
-    <t>Waters Corporation</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Visa Inc.</t>
-  </si>
-  <si>
     <t>HAS</t>
   </si>
   <si>
     <t>Hasbro</t>
   </si>
   <si>
-    <t>RJF</t>
-  </si>
-  <si>
-    <t>Raymond James Financial</t>
-  </si>
-  <si>
-    <t>VEEV</t>
-  </si>
-  <si>
-    <t>Veeva Systems</t>
+    <t>AMP</t>
+  </si>
+  <si>
+    <t>Ameriprise Financial</t>
   </si>
   <si>
     <t>GS</t>
@@ -561,7 +564,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-03 00:20 UTC · данные на 2026-09-02 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-04 00:09 UTC · данные на 2026-09-03 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -642,7 +645,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-03 00:20 UTC</t>
+    <t>2026-09-04 00:09 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -1128,9 +1131,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$12</c:f>
+              <c:f>Капитал!$A$5:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1154,16 +1157,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2026-09-02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026-09-03</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$12</c:f>
+              <c:f>Капитал!$D$5:$D$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1186,6 +1192,9 @@
                   <c:v>9972.67</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>9972.67</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>9972.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -1211,9 +1220,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$12</c:f>
+              <c:f>Капитал!$A$5:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1237,16 +1246,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2026-09-02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026-09-03</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$12</c:f>
+              <c:f>Капитал!$F$5:$F$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1269,6 +1281,9 @@
                   <c:v>9977.860000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1409,9 +1424,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$12</c:f>
+              <c:f>Капитал!$A$5:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1435,16 +1450,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2026-09-02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026-09-03</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$12</c:f>
+              <c:f>Капитал!$D$5:$D$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1467,6 +1485,9 @@
                   <c:v>9972.67</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>9972.67</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>9972.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -1492,9 +1513,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$12</c:f>
+              <c:f>Капитал!$A$5:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1518,16 +1539,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2026-09-02</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026-09-03</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$12</c:f>
+              <c:f>Капитал!$F$5:$F$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1550,6 +1574,9 @@
                   <c:v>9977.860000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2045,12 +2072,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2058,13 +2085,13 @@
         <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2083,27 +2110,27 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="6">
-        <v>-2.534712479800046</v>
+        <v>-2.367237358014867</v>
       </c>
       <c r="D9" s="6">
         <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H9" s="6">
         <v>6</v>
@@ -2111,7 +2138,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2140,7 +2167,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C16" s="9">
         <v>10000</v>
@@ -2148,7 +2175,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C17" s="10">
         <v>21</v>
@@ -2156,23 +2183,23 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" s="10">
         <v>21</v>
@@ -2180,55 +2207,55 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C25" s="11">
-        <v>0.03856799325004857</v>
+        <v>0.03613449525695474</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C26" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C28" s="9">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2237,12 +2264,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -2393,11 +2420,11 @@
         <v>-0.04087302337302337</v>
       </c>
       <c r="L5" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5" s="10">
         <f>MAX(0,21-L5)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N5" s="19">
         <v>2.927623067210654</v>
@@ -2444,11 +2471,11 @@
         <v>0.007814380932399143</v>
       </c>
       <c r="L6" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" s="10">
         <f>MAX(0,21-L6)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N6" s="19">
         <v>1.809956883354321</v>
@@ -2495,11 +2522,11 @@
         <v>-0.008595752361009467</v>
       </c>
       <c r="L7" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7" s="10">
         <f>MAX(0,21-L7)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N7" s="19">
         <v>1.655247920227722</v>
@@ -2546,11 +2573,11 @@
         <v>-0.026141070217003785</v>
       </c>
       <c r="L8" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" s="10">
         <f>MAX(0,21-L8)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N8" s="19">
         <v>1.135451734784544</v>
@@ -2597,11 +2624,11 @@
         <v>0.005136823709867133</v>
       </c>
       <c r="L9" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" s="10">
         <f>MAX(0,21-L9)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N9" s="19">
         <v>1.098454348098604</v>
@@ -2648,11 +2675,11 @@
         <v>0.005327247391140304</v>
       </c>
       <c r="L10" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" s="10">
         <f>MAX(0,21-L10)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N10" s="19">
         <v>0.9280120270881818</v>
@@ -2922,7 +2949,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3127,6 +3154,25 @@
         <v>6</v>
       </c>
       <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="9">
+        <v>7139.55</v>
+      </c>
+      <c r="C13" s="9">
+        <v>2833.12</v>
+      </c>
+      <c r="D13" s="9">
+        <f>B13+C13</f>
+        <v>9972.67</v>
+      </c>
+      <c r="E13" s="10">
+        <v>6</v>
+      </c>
+      <c r="F13" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3155,12 +3201,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3177,52 +3223,52 @@
         <v>10</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S4" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -3239,10 +3285,10 @@
         <v>25</v>
       </c>
       <c r="E5" s="9">
-        <v>1536.869995117188</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="F5" s="16">
-        <v>1.06776319712514</v>
+        <v>1.054822033420676</v>
       </c>
       <c r="G5" s="19">
         <v>-0.3065942401812342</v>
@@ -3254,16 +3300,16 @@
         <v>4.13232288715716</v>
       </c>
       <c r="J5" s="19">
-        <v>1.383821957048834</v>
+        <v>1.322980606249683</v>
       </c>
       <c r="K5" s="19">
         <v>0</v>
       </c>
       <c r="L5" s="19">
-        <v>-3.555680450483079</v>
+        <v>-3.480672299295953</v>
       </c>
       <c r="M5" s="19">
-        <v>0.623904809657001</v>
+        <v>0.6534509610143624</v>
       </c>
       <c r="N5" s="19">
         <v>20.12168</v>
@@ -3278,13 +3324,13 @@
         <v>3.716</v>
       </c>
       <c r="R5" s="11">
-        <v>1.718151550404877</v>
+        <v>1.593062515849467</v>
       </c>
       <c r="S5" s="10">
-        <v>51.66385839684092</v>
+        <v>52.49743744689197</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -3301,10 +3347,10 @@
         <v>25</v>
       </c>
       <c r="E6" s="9">
-        <v>933.4400024414062</v>
+        <v>956.0800170898438</v>
       </c>
       <c r="F6" s="16">
-        <v>1.038282641843425</v>
+        <v>1.054233623855224</v>
       </c>
       <c r="G6" s="19">
         <v>-0.4169145554552529</v>
@@ -3316,16 +3362,16 @@
         <v>4.262123054334927</v>
       </c>
       <c r="J6" s="19">
-        <v>1.5428027860031</v>
+        <v>1.575703537612333</v>
       </c>
       <c r="K6" s="19">
         <v>0</v>
       </c>
       <c r="L6" s="19">
-        <v>-3.555680450483079</v>
+        <v>-3.480672299295953</v>
       </c>
       <c r="M6" s="19">
-        <v>0.2783169181116185</v>
+        <v>0.274143788316431</v>
       </c>
       <c r="N6" s="19">
         <v>21.095882</v>
@@ -3340,13 +3386,13 @@
         <v>3.457</v>
       </c>
       <c r="R6" s="11">
-        <v>1.459902343677745</v>
+        <v>1.386977208278282</v>
       </c>
       <c r="S6" s="10">
-        <v>50.4480833752696</v>
+        <v>53.22980636839034</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -3363,10 +3409,10 @@
         <v>35</v>
       </c>
       <c r="E7" s="9">
-        <v>361.989990234375</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="F7" s="16">
-        <v>0.9982238217869719</v>
+        <v>0.970848932712693</v>
       </c>
       <c r="G7" s="19">
         <v>0.7600315297409044</v>
@@ -3378,16 +3424,16 @@
         <v>2.817024529253408</v>
       </c>
       <c r="J7" s="19">
-        <v>2.045781364547568</v>
+        <v>1.956005339459257</v>
       </c>
       <c r="K7" s="19">
         <v>0</v>
       </c>
       <c r="L7" s="19">
-        <v>0.1599036282170088</v>
+        <v>0.1577591647917007</v>
       </c>
       <c r="M7" s="19">
-        <v>-0.6824561043475547</v>
+        <v>-0.6453114425144759</v>
       </c>
       <c r="N7" s="19">
         <v>14.45283</v>
@@ -3402,13 +3448,13 @@
         <v>0.517</v>
       </c>
       <c r="R7" s="11">
-        <v>0.6770724856664994</v>
+        <v>0.6367502230808904</v>
       </c>
       <c r="S7" s="10">
-        <v>71.98558997611735</v>
+        <v>73.56767422107127</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -3425,10 +3471,10 @@
         <v>35</v>
       </c>
       <c r="E8" s="9">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F8" s="16">
-        <v>0.982242564910686</v>
+        <v>0.9527241260639225</v>
       </c>
       <c r="G8" s="19">
         <v>0.749794509494801</v>
@@ -3440,16 +3486,16 @@
         <v>2.384116899919412</v>
       </c>
       <c r="J8" s="19">
-        <v>2.069028331699112</v>
+        <v>1.967566018480531</v>
       </c>
       <c r="K8" s="19">
         <v>0</v>
       </c>
       <c r="L8" s="19">
-        <v>0.1553451170360356</v>
+        <v>0.1562152461765964</v>
       </c>
       <c r="M8" s="19">
-        <v>-0.591304614953617</v>
+        <v>-0.5361763645537554</v>
       </c>
       <c r="N8" s="19">
         <v>12.788835</v>
@@ -3464,13 +3510,13 @@
         <v>0.537</v>
       </c>
       <c r="R8" s="11">
-        <v>0.8186358330039056</v>
+        <v>0.7644638770403485</v>
       </c>
       <c r="S8" s="10">
-        <v>76.46062468080775</v>
+        <v>77.64884558414819</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -3478,19 +3524,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E9" s="9">
-        <v>252.0200042724609</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="F9" s="16">
-        <v>0.8298272742812407</v>
+        <v>0.8081645330578578</v>
       </c>
       <c r="G9" s="19">
         <v>0.5236285305189845</v>
@@ -3502,16 +3548,16 @@
         <v>2.35386274831343</v>
       </c>
       <c r="J9" s="19">
-        <v>1.86587919084851</v>
+        <v>1.78415593478787</v>
       </c>
       <c r="K9" s="19">
         <v>0</v>
       </c>
       <c r="L9" s="19">
-        <v>0.3717639462908604</v>
+        <v>0.3679724233679795</v>
       </c>
       <c r="M9" s="19">
-        <v>-0.6941056014711857</v>
+        <v>-0.6230899025088393</v>
       </c>
       <c r="N9" s="19">
         <v>13.92751</v>
@@ -3526,13 +3572,13 @@
         <v>0.531</v>
       </c>
       <c r="R9" s="11">
-        <v>0.5971772702846527</v>
+        <v>0.5742975601977356</v>
       </c>
       <c r="S9" s="10">
-        <v>75.0766147583623</v>
+        <v>77.05320797340288</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -3540,61 +3586,61 @@
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E10" s="9">
-        <v>60.95000076293945</v>
+        <v>492.2000122070312</v>
       </c>
       <c r="F10" s="16">
-        <v>0.7318414924878126</v>
+        <v>0.7604583534278073</v>
       </c>
       <c r="G10" s="19">
-        <v>0.6434300221411974</v>
+        <v>-0.1453667345878826</v>
       </c>
       <c r="H10" s="19">
-        <v>0.6167294611755126</v>
+        <v>-0.9104682528073633</v>
       </c>
       <c r="I10" s="19">
-        <v>3.205794473836218</v>
+        <v>2.981910484335923</v>
       </c>
       <c r="J10" s="19">
-        <v>0.4308767801046498</v>
+        <v>2.396537587483633</v>
       </c>
       <c r="K10" s="19">
         <v>0</v>
       </c>
       <c r="L10" s="19">
-        <v>0.2589147002916439</v>
+        <v>-2.518088402543813</v>
       </c>
       <c r="M10" s="19">
-        <v>-0.4481370977092229</v>
+        <v>-0.3127842104323252</v>
       </c>
       <c r="N10" s="19">
-        <v>17.433628</v>
+        <v>36.353783</v>
       </c>
       <c r="O10" s="19">
-        <v>1.765813</v>
+        <v>-210.92924</v>
       </c>
       <c r="P10" s="11">
-        <v>0.10629</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="11">
-        <v>0.534</v>
+        <v>0.875</v>
       </c>
       <c r="R10" s="11">
-        <v>0.1460926867579575</v>
+        <v>2.361922567269573</v>
       </c>
       <c r="S10" s="10">
-        <v>62.0836193844077</v>
+        <v>58.87163053312256</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -3602,61 +3648,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="9">
-        <v>44.29999923706055</v>
+        <v>60.90999984741211</v>
       </c>
       <c r="F11" s="16">
-        <v>0.7003478994320725</v>
+        <v>0.7233642665112766</v>
       </c>
       <c r="G11" s="19">
-        <v>1.180775573424393</v>
+        <v>0.6434300221411974</v>
       </c>
       <c r="H11" s="19">
-        <v>0.5628017336720434</v>
+        <v>0.6167294611755126</v>
       </c>
       <c r="I11" s="19">
-        <v>-0.2826661582517923</v>
+        <v>3.205794473836218</v>
       </c>
       <c r="J11" s="19">
-        <v>1.37926862407091</v>
+        <v>0.3715659758044343</v>
       </c>
       <c r="K11" s="19">
         <v>0</v>
       </c>
       <c r="L11" s="19">
-        <v>-0.3589036300700821</v>
+        <v>0.2605078313116728</v>
       </c>
       <c r="M11" s="19">
-        <v>-0.6282685336947845</v>
+        <v>-0.3201659155903314</v>
       </c>
       <c r="N11" s="19">
-        <v>8.974684</v>
+        <v>17.433628</v>
       </c>
       <c r="O11" s="19">
-        <v>2.1246629</v>
+        <v>1.765813</v>
       </c>
       <c r="P11" s="11">
-        <v>0.26659</v>
+        <v>0.10629</v>
       </c>
       <c r="Q11" s="11">
-        <v>0.092</v>
+        <v>0.534</v>
       </c>
       <c r="R11" s="11">
-        <v>0.4100597191058337</v>
+        <v>0.1468359858132189</v>
       </c>
       <c r="S11" s="10">
-        <v>67.58723769282514</v>
+        <v>61.85983370642715</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -3664,61 +3710,61 @@
         <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>86</v>
-      </c>
       <c r="D12" s="8" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="E12" s="9">
-        <v>135.6000061035156</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="F12" s="16">
-        <v>0.5826833835934309</v>
+        <v>0.7019116395441239</v>
       </c>
       <c r="G12" s="19">
-        <v>0.675065848973343</v>
+        <v>1.180775573424393</v>
       </c>
       <c r="H12" s="19">
-        <v>0.2975919364127702</v>
+        <v>0.5628017336720434</v>
       </c>
       <c r="I12" s="19">
-        <v>0.2786698223080728</v>
+        <v>-0.2826661582517923</v>
       </c>
       <c r="J12" s="19">
-        <v>1.057353273888769</v>
+        <v>1.351312871360071</v>
       </c>
       <c r="K12" s="19">
         <v>0</v>
       </c>
       <c r="L12" s="19">
-        <v>0.03267272758011818</v>
+        <v>-0.345123101031329</v>
       </c>
       <c r="M12" s="19">
-        <v>-0.04248141414088602</v>
+        <v>-0.5165687165756384</v>
       </c>
       <c r="N12" s="19">
-        <v>9.331602999999999</v>
+        <v>8.974684</v>
       </c>
       <c r="O12" s="19">
-        <v>3.3175094</v>
+        <v>2.1246629</v>
       </c>
       <c r="P12" s="11">
-        <v>0.29867</v>
+        <v>0.26659</v>
       </c>
       <c r="Q12" s="11">
-        <v>0.176</v>
+        <v>0.092</v>
       </c>
       <c r="R12" s="11">
-        <v>0.2874424165088272</v>
+        <v>0.457103418912304</v>
       </c>
       <c r="S12" s="10">
-        <v>69.12167518724334</v>
+        <v>68.72542126120932</v>
       </c>
       <c r="T12" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -3726,61 +3772,61 @@
         <v>9</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E13" s="9">
-        <v>425</v>
+        <v>139.2700042724609</v>
       </c>
       <c r="F13" s="16">
-        <v>0.5634724334393638</v>
+        <v>0.6304643230788479</v>
       </c>
       <c r="G13" s="19">
-        <v>-0.1453667345878826</v>
+        <v>0.675065848973343</v>
       </c>
       <c r="H13" s="19">
-        <v>-0.9104682528073633</v>
+        <v>0.2975919364127702</v>
       </c>
       <c r="I13" s="19">
-        <v>2.981910484335923</v>
+        <v>0.2786698223080728</v>
       </c>
       <c r="J13" s="19">
-        <v>1.760611623214541</v>
+        <v>1.143935467878596</v>
       </c>
       <c r="K13" s="19">
         <v>0</v>
       </c>
       <c r="L13" s="19">
-        <v>-2.087579920682394</v>
+        <v>0.06558912546416913</v>
       </c>
       <c r="M13" s="19">
-        <v>-0.4177883256921696</v>
+        <v>0.1337383943238131</v>
       </c>
       <c r="N13" s="19">
-        <v>36.353783</v>
+        <v>9.331602999999999</v>
       </c>
       <c r="O13" s="19">
-        <v>-210.92924</v>
+        <v>3.3175094</v>
       </c>
       <c r="P13" s="11">
-        <v>0</v>
+        <v>0.29867</v>
       </c>
       <c r="Q13" s="11">
-        <v>0.875</v>
+        <v>0.176</v>
       </c>
       <c r="R13" s="11">
-        <v>1.941310647213375</v>
+        <v>0.3423656328946094</v>
       </c>
       <c r="S13" s="10">
-        <v>44.90408763111321</v>
+        <v>72.28906972208368</v>
       </c>
       <c r="T13" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -3788,61 +3834,61 @@
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E14" s="9">
-        <v>211.0500030517578</v>
+        <v>224.4100036621094</v>
       </c>
       <c r="F14" s="16">
-        <v>0.5509514940473</v>
+        <v>0.5911817269551417</v>
       </c>
       <c r="G14" s="19">
-        <v>0.5556735680703294</v>
+        <v>-1.186242168307697</v>
       </c>
       <c r="H14" s="19">
-        <v>-0.3266206515441806</v>
+        <v>2.372350229473365</v>
       </c>
       <c r="I14" s="19">
-        <v>2.258526107719387</v>
+        <v>2.41778901771408</v>
       </c>
       <c r="J14" s="19">
-        <v>0.7258362127619501</v>
+        <v>0.4304429407463364</v>
       </c>
       <c r="K14" s="19">
         <v>0</v>
       </c>
       <c r="L14" s="19">
-        <v>0.7541316334328008</v>
+        <v>-0.2007041257071993</v>
       </c>
       <c r="M14" s="19">
-        <v>-0.6471999481307263</v>
+        <v>-0.05852578940881459</v>
       </c>
       <c r="N14" s="19">
-        <v>19.409616</v>
+        <v>27.468435</v>
       </c>
       <c r="O14" s="19">
-        <v>2.0853305</v>
+        <v>26.95787</v>
       </c>
       <c r="P14" s="11">
-        <v>0.12231</v>
+        <v>1.17211</v>
       </c>
       <c r="Q14" s="11">
-        <v>0.535</v>
+        <v>1.059</v>
       </c>
       <c r="R14" s="11">
-        <v>0.1381140844875719</v>
+        <v>0.2275115732316977</v>
       </c>
       <c r="S14" s="10">
-        <v>71.60464867147262</v>
+        <v>56.67224745963074</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -3850,61 +3896,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="9">
-        <v>148.3500061035156</v>
+        <v>211.7799987792969</v>
       </c>
       <c r="F15" s="16">
-        <v>0.5218624047124374</v>
+        <v>0.5448258911546133</v>
       </c>
       <c r="G15" s="19">
-        <v>0.6252746191907743</v>
+        <v>0.5556735680703294</v>
       </c>
       <c r="H15" s="19">
-        <v>0.4666043918108415</v>
+        <v>-0.3266206515441806</v>
       </c>
       <c r="I15" s="19">
-        <v>1.417737897842424</v>
+        <v>2.258526107719387</v>
       </c>
       <c r="J15" s="19">
-        <v>0.4763991543408084</v>
+        <v>0.6874773333493751</v>
       </c>
       <c r="K15" s="19">
         <v>0</v>
       </c>
       <c r="L15" s="19">
-        <v>0.2714881480820976</v>
+        <v>0.7604656555882482</v>
       </c>
       <c r="M15" s="19">
-        <v>-0.3618755371067491</v>
+        <v>-0.5754862987697096</v>
       </c>
       <c r="N15" s="19">
-        <v>11.1643305</v>
+        <v>19.409616</v>
       </c>
       <c r="O15" s="19">
-        <v>2.3641071</v>
+        <v>2.0853305</v>
       </c>
       <c r="P15" s="11">
-        <v>0.22507</v>
+        <v>0.12231</v>
       </c>
       <c r="Q15" s="11">
-        <v>0.587</v>
+        <v>0.535</v>
       </c>
       <c r="R15" s="11">
-        <v>0.1765593719944296</v>
+        <v>0.1588716860174963</v>
       </c>
       <c r="S15" s="10">
-        <v>56.67336380021517</v>
+        <v>72.25123940792997</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3912,61 +3958,61 @@
         <v>12</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E16" s="9">
-        <v>217.4400024414062</v>
+        <v>148.9600067138672</v>
       </c>
       <c r="F16" s="16">
-        <v>0.5195239940460369</v>
+        <v>0.5185873657889519</v>
       </c>
       <c r="G16" s="19">
-        <v>-1.186242168307697</v>
+        <v>0.6252746191907743</v>
       </c>
       <c r="H16" s="19">
-        <v>2.372350229473365</v>
+        <v>0.4666043918108415</v>
       </c>
       <c r="I16" s="19">
-        <v>2.41778901771408</v>
+        <v>1.417737897842424</v>
       </c>
       <c r="J16" s="19">
-        <v>0.217339146966691</v>
+        <v>0.4305749224557138</v>
       </c>
       <c r="K16" s="19">
         <v>0</v>
       </c>
       <c r="L16" s="19">
-        <v>-0.1744576869211722</v>
+        <v>0.2800257657120724</v>
       </c>
       <c r="M16" s="19">
-        <v>-0.0673064538248174</v>
+        <v>-0.2324633089184651</v>
       </c>
       <c r="N16" s="19">
-        <v>27.468435</v>
+        <v>11.1643305</v>
       </c>
       <c r="O16" s="19">
-        <v>26.95787</v>
+        <v>2.3641071</v>
       </c>
       <c r="P16" s="11">
-        <v>1.17211</v>
+        <v>0.22507</v>
       </c>
       <c r="Q16" s="11">
-        <v>1.059</v>
+        <v>0.587</v>
       </c>
       <c r="R16" s="11">
-        <v>0.2091375570176681</v>
+        <v>0.1831533196186952</v>
       </c>
       <c r="S16" s="10">
-        <v>51.87290992412506</v>
+        <v>57.55816691876135</v>
       </c>
       <c r="T16" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3974,19 +4020,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E17" s="9">
-        <v>257.8699951171875</v>
+        <v>259.3399963378906</v>
       </c>
       <c r="F17" s="16">
-        <v>0.511682367530394</v>
+        <v>0.5179426725101998</v>
       </c>
       <c r="G17" s="19">
         <v>1.2973242005594</v>
@@ -3998,16 +4044,16 @@
         <v>-0.05264739805840464</v>
       </c>
       <c r="J17" s="19">
-        <v>0.5860972156165868</v>
+        <v>0.5784615411950941</v>
       </c>
       <c r="K17" s="19">
         <v>0</v>
       </c>
       <c r="L17" s="19">
-        <v>0.5032064237461212</v>
+        <v>0.5442547917265765</v>
       </c>
       <c r="M17" s="19">
-        <v>-0.1337857660839727</v>
+        <v>-0.06707490821085271</v>
       </c>
       <c r="N17" s="19">
         <v>5.156936</v>
@@ -4022,13 +4068,13 @@
         <v>0.118</v>
       </c>
       <c r="R17" s="11">
-        <v>0.2186102950476296</v>
+        <v>0.222295520821145</v>
       </c>
       <c r="S17" s="10">
-        <v>50.78974543526481</v>
+        <v>52.35633018652639</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4036,61 +4082,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="E18" s="9">
-        <v>66.91999816894531</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="F18" s="16">
-        <v>0.5011747706367228</v>
+        <v>0.5171483870908948</v>
       </c>
       <c r="G18" s="19">
-        <v>0.4854005059534541</v>
+        <v>0.5167039359615127</v>
       </c>
       <c r="H18" s="19">
-        <v>0.6587571460380149</v>
+        <v>0.749645521027813</v>
       </c>
       <c r="I18" s="19">
-        <v>0.2084671882916938</v>
+        <v>-0.1861321221296584</v>
       </c>
       <c r="J18" s="19">
-        <v>0.7709118149017465</v>
+        <v>0.8497776530755533</v>
       </c>
       <c r="K18" s="19">
         <v>0</v>
       </c>
       <c r="L18" s="19">
-        <v>0.5643958420327979</v>
+        <v>0.2080020638574881</v>
       </c>
       <c r="M18" s="19">
-        <v>-0.4715431262381155</v>
+        <v>-0.08324523423355468</v>
       </c>
       <c r="N18" s="19">
-        <v>14.762749</v>
+        <v>17.827587</v>
       </c>
       <c r="O18" s="19">
-        <v>6.0942793</v>
+        <v>6.9959407</v>
       </c>
       <c r="P18" s="11">
-        <v>0.46598998</v>
+        <v>0.41944</v>
       </c>
       <c r="Q18" s="11">
-        <v>0.057</v>
+        <v>0.063</v>
       </c>
       <c r="R18" s="11">
-        <v>0.1168442617445413</v>
+        <v>0.3885193095313455</v>
       </c>
       <c r="S18" s="10">
-        <v>59.72925627702788</v>
+        <v>64.50575807066566</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4104,55 +4150,55 @@
         <v>101</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E19" s="9">
-        <v>125.0100021362305</v>
+        <v>216.6000061035156</v>
       </c>
       <c r="F19" s="16">
-        <v>0.4991870071750666</v>
+        <v>0.5166314700640471</v>
       </c>
       <c r="G19" s="19">
-        <v>0.3535340411038917</v>
+        <v>0.5887979504774438</v>
       </c>
       <c r="H19" s="19">
-        <v>0.5066139843793523</v>
+        <v>-0.657139695697852</v>
       </c>
       <c r="I19" s="19">
-        <v>0.5284153400344015</v>
+        <v>4.13232288715716</v>
       </c>
       <c r="J19" s="19">
-        <v>0.8959330828656217</v>
+        <v>0.1354247803915279</v>
       </c>
       <c r="K19" s="19">
         <v>0</v>
       </c>
       <c r="L19" s="19">
-        <v>0.05227462380159767</v>
+        <v>0.4833436664336478</v>
       </c>
       <c r="M19" s="19">
-        <v>-0.3770966859570098</v>
+        <v>-0.3633241117139414</v>
       </c>
       <c r="N19" s="19">
-        <v>15.843312</v>
+        <v>11.935252</v>
       </c>
       <c r="O19" s="19">
-        <v>3.939749</v>
+        <v>1.2848284</v>
       </c>
       <c r="P19" s="11">
-        <v>0.30667</v>
+        <v>0.09031</v>
       </c>
       <c r="Q19" s="11">
-        <v>0.377</v>
+        <v>11.11</v>
       </c>
       <c r="R19" s="11">
-        <v>0.2747017694018412</v>
+        <v>0.1147319427825668</v>
       </c>
       <c r="S19" s="10">
-        <v>54.59762999280038</v>
+        <v>52.72760580486165</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -4166,55 +4212,55 @@
         <v>103</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E20" s="9">
-        <v>438.1199951171875</v>
+        <v>128.8300018310547</v>
       </c>
       <c r="F20" s="16">
-        <v>0.4902533915403123</v>
+        <v>0.5114883647696113</v>
       </c>
       <c r="G20" s="19">
-        <v>-0.2455671553299525</v>
+        <v>0.3535340411038917</v>
       </c>
       <c r="H20" s="19">
-        <v>1.23829401915366</v>
+        <v>0.5066139843793523</v>
       </c>
       <c r="I20" s="19">
-        <v>-0.09681434526753466</v>
+        <v>0.5284153400344015</v>
       </c>
       <c r="J20" s="19">
-        <v>1.049883740822111</v>
+        <v>0.9615118482856677</v>
       </c>
       <c r="K20" s="19">
         <v>0</v>
       </c>
       <c r="L20" s="19">
-        <v>0.6793780188228323</v>
+        <v>0.04043073902685233</v>
       </c>
       <c r="M20" s="19">
-        <v>-0.8568542424871126</v>
+        <v>-0.4788192091611312</v>
       </c>
       <c r="N20" s="19">
-        <v>26.875078</v>
+        <v>15.843312</v>
       </c>
       <c r="O20" s="19">
-        <v>20.000925</v>
+        <v>3.939749</v>
       </c>
       <c r="P20" s="11">
-        <v>0.91473</v>
+        <v>0.30667</v>
       </c>
       <c r="Q20" s="11">
-        <v>0.095</v>
+        <v>0.377</v>
       </c>
       <c r="R20" s="11">
-        <v>0.1777404730924301</v>
+        <v>0.3031559886270625</v>
       </c>
       <c r="S20" s="10">
-        <v>66.50037520102745</v>
+        <v>61.44533411941921</v>
       </c>
       <c r="T20" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -4222,61 +4268,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="E21" s="9">
-        <v>450.4400024414062</v>
+        <v>67.66000366210938</v>
       </c>
       <c r="F21" s="16">
-        <v>0.4821817488324344</v>
+        <v>0.5002042938157545</v>
       </c>
       <c r="G21" s="19">
-        <v>-0.9131978128854404</v>
+        <v>0.4854005059534541</v>
       </c>
       <c r="H21" s="19">
-        <v>2.151528876753073</v>
+        <v>0.6587571460380149</v>
       </c>
       <c r="I21" s="19">
-        <v>2.950282622072772</v>
+        <v>0.2084671882916938</v>
       </c>
       <c r="J21" s="19">
-        <v>0.3905157979135979</v>
+        <v>0.7659809326795566</v>
       </c>
       <c r="K21" s="19">
         <v>0</v>
       </c>
       <c r="L21" s="19">
-        <v>-3.555680450483079</v>
+        <v>0.6130132210787556</v>
       </c>
       <c r="M21" s="19">
-        <v>0.5701093807382255</v>
+        <v>-0.5001905972200227</v>
       </c>
       <c r="N21" s="19">
-        <v>17.067236</v>
+        <v>14.762749</v>
       </c>
       <c r="O21" s="19">
-        <v>21.967487</v>
+        <v>6.0942793</v>
       </c>
       <c r="P21" s="11">
-        <v>1.30853</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q21" s="11">
-        <v>0.438</v>
+        <v>0.057</v>
       </c>
       <c r="R21" s="11">
-        <v>0.798703509252862</v>
+        <v>0.1090852290335338</v>
       </c>
       <c r="S21" s="10">
-        <v>43.73367487654851</v>
+        <v>62.54508994926787</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -4284,61 +4330,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>96</v>
-      </c>
       <c r="E22" s="9">
-        <v>211.3399963378906</v>
+        <v>442.8399963378906</v>
       </c>
       <c r="F22" s="16">
-        <v>0.478613974038153</v>
+        <v>0.4859140800627329</v>
       </c>
       <c r="G22" s="19">
-        <v>0.5887979504774438</v>
+        <v>-0.2455671553299525</v>
       </c>
       <c r="H22" s="19">
-        <v>-0.657139695697852</v>
+        <v>1.23829401915366</v>
       </c>
       <c r="I22" s="19">
-        <v>4.13232288715716</v>
+        <v>-0.09681434526753466</v>
       </c>
       <c r="J22" s="19">
-        <v>-0.0259549879248853</v>
+        <v>1.035701953736616</v>
       </c>
       <c r="K22" s="19">
         <v>0</v>
       </c>
       <c r="L22" s="19">
-        <v>0.5020444814571686</v>
+        <v>0.6909729879338106</v>
       </c>
       <c r="M22" s="19">
-        <v>-0.1903680480798671</v>
+        <v>-0.8601011940031138</v>
       </c>
       <c r="N22" s="19">
-        <v>11.935252</v>
+        <v>26.875078</v>
       </c>
       <c r="O22" s="19">
-        <v>1.2848284</v>
+        <v>20.000925</v>
       </c>
       <c r="P22" s="11">
-        <v>0.09031</v>
+        <v>0.91473</v>
       </c>
       <c r="Q22" s="11">
-        <v>11.11</v>
+        <v>0.095</v>
       </c>
       <c r="R22" s="11">
-        <v>0.0994512657513924</v>
+        <v>0.1833037907929858</v>
       </c>
       <c r="S22" s="10">
-        <v>44.70214501086372</v>
+        <v>68.67543648296927</v>
       </c>
       <c r="T22" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -4346,61 +4392,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="E23" s="9">
-        <v>304.2300109863281</v>
+        <v>448.8999938964844</v>
       </c>
       <c r="F23" s="16">
-        <v>0.477386643070931</v>
+        <v>0.4825816595872763</v>
       </c>
       <c r="G23" s="19">
-        <v>0.02392519228507077</v>
+        <v>-0.9131978128854404</v>
       </c>
       <c r="H23" s="19">
-        <v>1.208973468219964</v>
+        <v>2.151528876753073</v>
       </c>
       <c r="I23" s="19">
-        <v>0.5934216790533486</v>
+        <v>2.950282622072772</v>
       </c>
       <c r="J23" s="19">
-        <v>0.8637291421919383</v>
+        <v>0.3495729803700307</v>
       </c>
       <c r="K23" s="19">
         <v>0</v>
       </c>
       <c r="L23" s="19">
-        <v>-0.5178448128974058</v>
+        <v>-3.480672299295953</v>
       </c>
       <c r="M23" s="19">
-        <v>-0.812903317664495</v>
+        <v>0.6717878514395186</v>
       </c>
       <c r="N23" s="19">
-        <v>20.706474</v>
+        <v>17.067236</v>
       </c>
       <c r="O23" s="19">
-        <v>32.69876</v>
+        <v>21.967487</v>
       </c>
       <c r="P23" s="11">
-        <v>0.89489</v>
+        <v>1.30853</v>
       </c>
       <c r="Q23" s="11">
-        <v>0.14</v>
+        <v>0.438</v>
       </c>
       <c r="R23" s="11">
-        <v>0.4222264736326597</v>
+        <v>0.7192191727138222</v>
       </c>
       <c r="S23" s="10">
-        <v>46.34797987557869</v>
+        <v>43.45616171029246</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -4414,55 +4460,55 @@
         <v>110</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="E24" s="9">
-        <v>258.1099853515625</v>
+        <v>308.0599975585938</v>
       </c>
       <c r="F24" s="16">
-        <v>0.4737672745006869</v>
+        <v>0.4778747652284054</v>
       </c>
       <c r="G24" s="19">
-        <v>0.3430645610428927</v>
+        <v>0.02392519228507077</v>
       </c>
       <c r="H24" s="19">
-        <v>0.5388891445188714</v>
+        <v>1.208973468219964</v>
       </c>
       <c r="I24" s="19">
-        <v>0.1866157944506243</v>
+        <v>0.5934216790533486</v>
       </c>
       <c r="J24" s="19">
-        <v>1.071170274982535</v>
+        <v>0.9053653543455308</v>
       </c>
       <c r="K24" s="19">
         <v>0</v>
       </c>
       <c r="L24" s="19">
-        <v>-1.488611246144252</v>
+        <v>-0.5169390624607396</v>
       </c>
       <c r="M24" s="19">
-        <v>0.228066628483707</v>
+        <v>-0.9643490823357488</v>
       </c>
       <c r="N24" s="19">
-        <v>23.421774</v>
+        <v>20.706474</v>
       </c>
       <c r="O24" s="19">
-        <v>5.4897923</v>
+        <v>32.69876</v>
       </c>
       <c r="P24" s="11">
-        <v>0.19381</v>
+        <v>0.89489</v>
       </c>
       <c r="Q24" s="11">
-        <v>0.108</v>
+        <v>0.14</v>
       </c>
       <c r="R24" s="11">
-        <v>0.3232510013466021</v>
+        <v>0.3973292758292313</v>
       </c>
       <c r="S24" s="10">
-        <v>81.2538061921633</v>
+        <v>48.32045969975</v>
       </c>
       <c r="T24" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -4470,61 +4516,61 @@
         <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="9">
-        <v>30.02000045776367</v>
+        <v>31.98999977111816</v>
       </c>
       <c r="F25" s="16">
-        <v>0.4703626612935455</v>
+        <v>0.4763138349660302</v>
       </c>
       <c r="G25" s="19">
-        <v>0.5167039359615127</v>
+        <v>1.18884239126269</v>
       </c>
       <c r="H25" s="19">
-        <v>0.749645521027813</v>
+        <v>-0.9872240870343698</v>
       </c>
       <c r="I25" s="19">
-        <v>-0.1861321221296584</v>
+        <v>-0.3680930717051557</v>
       </c>
       <c r="J25" s="19">
-        <v>0.6754516228084331</v>
+        <v>1.514778561567294</v>
       </c>
       <c r="K25" s="19">
         <v>0</v>
       </c>
       <c r="L25" s="19">
-        <v>0.2083885519086353</v>
+        <v>-0.4257128312669795</v>
       </c>
       <c r="M25" s="19">
-        <v>0.05554452945894361</v>
+        <v>-0.362013664441654</v>
       </c>
       <c r="N25" s="19">
-        <v>17.827587</v>
+        <v>11.648855</v>
       </c>
       <c r="O25" s="19">
-        <v>6.9959407</v>
+        <v>-305.2</v>
       </c>
       <c r="P25" s="11">
-        <v>0.41944</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="11">
-        <v>0.063</v>
+        <v>0.125</v>
       </c>
       <c r="R25" s="11">
-        <v>0.3533004092198408</v>
+        <v>0.7155810235893794</v>
       </c>
       <c r="S25" s="10">
-        <v>61.00117939203331</v>
+        <v>64.26562172929734</v>
       </c>
       <c r="T25" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -4532,61 +4578,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="E26" s="9">
-        <v>69.56999969482422</v>
+        <v>256.9299926757812</v>
       </c>
       <c r="F26" s="16">
-        <v>0.4594466748796265</v>
+        <v>0.4752744061075088</v>
       </c>
       <c r="G26" s="19">
-        <v>0.548854665636462</v>
+        <v>0.3430645610428927</v>
       </c>
       <c r="H26" s="19">
-        <v>1.843831358372849</v>
+        <v>0.5388891445188714</v>
       </c>
       <c r="I26" s="19">
-        <v>-0.6292233998564639</v>
+        <v>0.1866157944506243</v>
       </c>
       <c r="J26" s="19">
-        <v>-0.00059659217896287</v>
+        <v>1.102017236520169</v>
       </c>
       <c r="K26" s="19">
         <v>0</v>
       </c>
       <c r="L26" s="19">
-        <v>0.3910196239624897</v>
+        <v>-1.494970478052512</v>
       </c>
       <c r="M26" s="19">
-        <v>0.6268294617679766</v>
+        <v>0.1337383943238131</v>
       </c>
       <c r="N26" s="19">
-        <v>14.242739</v>
+        <v>23.421774</v>
       </c>
       <c r="O26" s="19">
-        <v>-42.95995</v>
+        <v>5.4897923</v>
       </c>
       <c r="P26" s="11">
-        <v>0</v>
+        <v>0.19381</v>
       </c>
       <c r="Q26" s="11">
-        <v>0.012</v>
+        <v>0.108</v>
       </c>
       <c r="R26" s="11">
-        <v>0.04214796324844805</v>
+        <v>0.3374629754806138</v>
       </c>
       <c r="S26" s="10">
-        <v>54.99849936231556</v>
+        <v>80.05314094364982</v>
       </c>
       <c r="T26" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -4600,55 +4646,55 @@
         <v>117</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="E27" s="9">
-        <v>161.8500061035156</v>
+        <v>69.55999755859375</v>
       </c>
       <c r="F27" s="16">
-        <v>0.4522163357277649</v>
+        <v>0.4514107542190169</v>
       </c>
       <c r="G27" s="19">
-        <v>-2.122778428838808</v>
+        <v>0.548854665636462</v>
       </c>
       <c r="H27" s="19">
-        <v>1.765640568246892</v>
+        <v>1.843831358372849</v>
       </c>
       <c r="I27" s="19">
-        <v>0.2349332652824272</v>
+        <v>-0.6292233998564639</v>
       </c>
       <c r="J27" s="19">
-        <v>1.496674515977309</v>
+        <v>-0.0504008928679656</v>
       </c>
       <c r="K27" s="19">
         <v>0</v>
       </c>
       <c r="L27" s="19">
-        <v>-0.3112253188577132</v>
+        <v>0.397520003399692</v>
       </c>
       <c r="M27" s="19">
-        <v>0.5465729940242879</v>
+        <v>0.72032517750713</v>
       </c>
       <c r="N27" s="19">
-        <v>61.02941</v>
+        <v>14.242739</v>
       </c>
       <c r="O27" s="19">
-        <v>78.524124</v>
+        <v>-42.95995</v>
       </c>
       <c r="P27" s="11">
-        <v>1.17442</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="11">
-        <v>0.256</v>
+        <v>0.012</v>
       </c>
       <c r="R27" s="11">
-        <v>0.9956844531280942</v>
+        <v>0.05377649259040207</v>
       </c>
       <c r="S27" s="10">
-        <v>52.07606850997672</v>
+        <v>54.95712479213294</v>
       </c>
       <c r="T27" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -4656,61 +4702,61 @@
         <v>24</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="E28" s="9">
-        <v>108.2799987792969</v>
+        <v>137.1999969482422</v>
       </c>
       <c r="F28" s="16">
-        <v>0.443311906352748</v>
+        <v>0.4450241713023743</v>
       </c>
       <c r="G28" s="19">
-        <v>0.08240686126983239</v>
+        <v>0.5373664552081702</v>
       </c>
       <c r="H28" s="19">
-        <v>1.223451927469628</v>
+        <v>-0.1368691777673517</v>
       </c>
       <c r="I28" s="19">
-        <v>0.1038485795344242</v>
+        <v>0.7891918304603867</v>
       </c>
       <c r="J28" s="19">
-        <v>0.4949138267917804</v>
+        <v>0.874868710458875</v>
       </c>
       <c r="K28" s="19">
         <v>0</v>
       </c>
       <c r="L28" s="19">
-        <v>0.9108638936288646</v>
+        <v>0.409266950255782</v>
       </c>
       <c r="M28" s="19">
-        <v>-0.4247738180250054</v>
+        <v>-0.6142679493456635</v>
       </c>
       <c r="N28" s="19">
-        <v>20.065575</v>
+        <v>17.128778</v>
       </c>
       <c r="O28" s="19">
-        <v>4.333084</v>
+        <v>2.396272</v>
       </c>
       <c r="P28" s="11">
-        <v>0.20273</v>
+        <v>0.1418</v>
       </c>
       <c r="Q28" s="11">
-        <v>0.209</v>
+        <v>0.355</v>
       </c>
       <c r="R28" s="11">
-        <v>0.1443239902155196</v>
+        <v>0.2031260401361856</v>
       </c>
       <c r="S28" s="10">
-        <v>51.23363878194911</v>
+        <v>71.23451314922767</v>
       </c>
       <c r="T28" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -4718,61 +4764,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="E29" s="9">
-        <v>136.1900024414062</v>
+        <v>400.9700012207031</v>
       </c>
       <c r="F29" s="16">
-        <v>0.4406661699839187</v>
+        <v>0.4356891888260966</v>
       </c>
       <c r="G29" s="19">
-        <v>0.5373664552081702</v>
+        <v>0.3991025813752035</v>
       </c>
       <c r="H29" s="19">
-        <v>-0.1368691777673517</v>
+        <v>-1.053340414218987</v>
       </c>
       <c r="I29" s="19">
-        <v>0.7891918304603867</v>
+        <v>0.1734891100083233</v>
       </c>
       <c r="J29" s="19">
-        <v>0.8872603049103714</v>
+        <v>1.48054786406749</v>
       </c>
       <c r="K29" s="19">
         <v>0</v>
       </c>
       <c r="L29" s="19">
-        <v>0.4037509530729997</v>
+        <v>0.2316131799363454</v>
       </c>
       <c r="M29" s="19">
-        <v>-0.7045374451547004</v>
+        <v>0.05865533471507733</v>
       </c>
       <c r="N29" s="19">
-        <v>17.128778</v>
+        <v>37.178402</v>
       </c>
       <c r="O29" s="19">
-        <v>2.396272</v>
+        <v>2.4096098</v>
       </c>
       <c r="P29" s="11">
-        <v>0.1418</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="Q29" s="11">
-        <v>0.355</v>
+        <v>0.262</v>
       </c>
       <c r="R29" s="11">
-        <v>0.1653496878943101</v>
+        <v>1.206090640558684</v>
       </c>
       <c r="S29" s="10">
-        <v>70.06544560580579</v>
+        <v>60.64847724016542</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -4780,61 +4826,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="E30" s="9">
-        <v>163.75</v>
+        <v>108.2399978637695</v>
       </c>
       <c r="F30" s="16">
-        <v>0.435098755732545</v>
+        <v>0.4328159921505382</v>
       </c>
       <c r="G30" s="19">
-        <v>0.5037681831878469</v>
+        <v>0.08240686126983239</v>
       </c>
       <c r="H30" s="19">
-        <v>-0.5575001867977641</v>
+        <v>1.223451927469628</v>
       </c>
       <c r="I30" s="19">
-        <v>-0.04455757815619896</v>
+        <v>0.1038485795344242</v>
       </c>
       <c r="J30" s="19">
-        <v>1.376152916180098</v>
+        <v>0.4530655684743485</v>
       </c>
       <c r="K30" s="19">
         <v>0</v>
       </c>
       <c r="L30" s="19">
-        <v>0.2591102656032267</v>
+        <v>0.9225964599732468</v>
       </c>
       <c r="M30" s="19">
-        <v>-0.5316008877016696</v>
+        <v>-0.3920973303172309</v>
       </c>
       <c r="N30" s="19">
-        <v>16.927385</v>
+        <v>20.065575</v>
       </c>
       <c r="O30" s="19">
-        <v>4.154594</v>
+        <v>4.333084</v>
       </c>
       <c r="P30" s="11">
-        <v>0.26408002</v>
+        <v>0.20273</v>
       </c>
       <c r="Q30" s="11">
-        <v>0.053</v>
+        <v>0.209</v>
       </c>
       <c r="R30" s="11">
-        <v>0.3788563884206089</v>
+        <v>0.1343726127753508</v>
       </c>
       <c r="S30" s="10">
-        <v>63.06512959779035</v>
+        <v>51.10883440310246</v>
       </c>
       <c r="T30" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -4842,61 +4888,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E31" s="9">
-        <v>394.8800048828125</v>
+        <v>416.3999938964844</v>
       </c>
       <c r="F31" s="16">
-        <v>0.4266899433409234</v>
+        <v>0.419765462100207</v>
       </c>
       <c r="G31" s="19">
-        <v>0.3991025813752035</v>
+        <v>0.3076356686141632</v>
       </c>
       <c r="H31" s="19">
-        <v>-1.053340414218987</v>
+        <v>0.7065757650551486</v>
       </c>
       <c r="I31" s="19">
-        <v>0.1734891100083233</v>
+        <v>-0.1087365036626361</v>
       </c>
       <c r="J31" s="19">
-        <v>1.469646792051797</v>
+        <v>0.7865362960034815</v>
       </c>
       <c r="K31" s="19">
         <v>0</v>
       </c>
       <c r="L31" s="19">
-        <v>0.231240132611235</v>
+        <v>0.5481412098436849</v>
       </c>
       <c r="M31" s="19">
-        <v>0.0008224399308530694</v>
+        <v>-0.7126080892074118</v>
       </c>
       <c r="N31" s="19">
-        <v>37.178402</v>
+        <v>24.571085</v>
       </c>
       <c r="O31" s="19">
-        <v>2.4096098</v>
+        <v>7.5607543</v>
       </c>
       <c r="P31" s="11">
-        <v>0.06893000000000001</v>
+        <v>0.29215</v>
       </c>
       <c r="Q31" s="11">
-        <v>0.262</v>
+        <v>0.215</v>
       </c>
       <c r="R31" s="11">
-        <v>1.190890352688831</v>
+        <v>0.2667315415860951</v>
       </c>
       <c r="S31" s="10">
-        <v>57.46312192737719</v>
+        <v>61.90938978534076</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4904,19 +4950,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E32" s="9">
-        <v>363.9200134277344</v>
+        <v>366.1799926757812</v>
       </c>
       <c r="F32" s="16">
-        <v>0.4161574043172628</v>
+        <v>0.4149095330293299</v>
       </c>
       <c r="G32" s="19">
         <v>1.231904824551268</v>
@@ -4928,16 +4974,16 @@
         <v>-0.3776219198070676</v>
       </c>
       <c r="J32" s="19">
-        <v>0.5689892073265229</v>
+        <v>0.5603372351080521</v>
       </c>
       <c r="K32" s="19">
         <v>0</v>
       </c>
       <c r="L32" s="19">
-        <v>0.6180822664272378</v>
+        <v>0.6491125414395538</v>
       </c>
       <c r="M32" s="19">
-        <v>-0.07874698891865362</v>
+        <v>-0.08330138352588624</v>
       </c>
       <c r="N32" s="19">
         <v>9.919549</v>
@@ -4952,13 +4998,13 @@
         <v>0.003</v>
       </c>
       <c r="R32" s="11">
-        <v>0.1794453676755525</v>
+        <v>0.1827381341379786</v>
       </c>
       <c r="S32" s="10">
-        <v>46.71708990737086</v>
+        <v>49.33096379585528</v>
       </c>
       <c r="T32" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4966,61 +5012,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="E33" s="9">
-        <v>203.1600036621094</v>
+        <v>211.8200073242188</v>
       </c>
       <c r="F33" s="16">
-        <v>0.4151890752506984</v>
+        <v>0.4137821958984472</v>
       </c>
       <c r="G33" s="19">
-        <v>0.6290781538187236</v>
+        <v>0.3599630250019414</v>
       </c>
       <c r="H33" s="19">
-        <v>-0.04474182683940042</v>
+        <v>0.7749817441404762</v>
       </c>
       <c r="I33" s="19">
-        <v>1.575737480795989</v>
+        <v>0.3840583979359316</v>
       </c>
       <c r="J33" s="19">
-        <v>0.3882911164010788</v>
+        <v>0.2687539181760084</v>
       </c>
       <c r="K33" s="19">
         <v>0</v>
       </c>
       <c r="L33" s="19">
-        <v>0.2680137895190494</v>
+        <v>0.5771374472344977</v>
       </c>
       <c r="M33" s="19">
-        <v>-0.3856362442939634</v>
+        <v>0.2709705843417799</v>
       </c>
       <c r="N33" s="19">
-        <v>37.579845</v>
+        <v>17.362167</v>
       </c>
       <c r="O33" s="19">
-        <v>1.4633226</v>
+        <v>3.1676524</v>
       </c>
       <c r="P33" s="11">
-        <v>0.034930002</v>
+        <v>0.17969999</v>
       </c>
       <c r="Q33" s="11">
-        <v>0.525</v>
+        <v>0.28</v>
       </c>
       <c r="R33" s="11">
-        <v>0.1639167547773164</v>
+        <v>0.2777814903404947</v>
       </c>
       <c r="S33" s="10">
-        <v>54.29840659894472</v>
+        <v>46.0876912234934</v>
       </c>
       <c r="T33" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -5028,61 +5074,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="E34" s="9">
-        <v>50.86999893188477</v>
+        <v>163.3600006103516</v>
       </c>
       <c r="F34" s="16">
-        <v>0.4143734795843966</v>
+        <v>0.4117207469139126</v>
       </c>
       <c r="G34" s="19">
-        <v>0.2615753155071175</v>
+        <v>0.5037681831878469</v>
       </c>
       <c r="H34" s="19">
-        <v>-0.6923506737965556</v>
+        <v>-0.5575001867977641</v>
       </c>
       <c r="I34" s="19">
-        <v>1.306361806653459</v>
+        <v>-0.04455757815619896</v>
       </c>
       <c r="J34" s="19">
-        <v>1.441636790183564</v>
+        <v>1.304179366951732</v>
       </c>
       <c r="K34" s="19">
         <v>0</v>
       </c>
       <c r="L34" s="19">
-        <v>-1.034124897997796</v>
+        <v>0.2576047119474864</v>
       </c>
       <c r="M34" s="19">
-        <v>-0.9092313848763797</v>
+        <v>-0.5177290098584503</v>
       </c>
       <c r="N34" s="19">
-        <v>48.887848</v>
+        <v>16.927385</v>
       </c>
       <c r="O34" s="19">
-        <v>2.7368805</v>
+        <v>4.154594</v>
       </c>
       <c r="P34" s="11">
-        <v>0.06315</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q34" s="11">
-        <v>0.4</v>
+        <v>0.053</v>
       </c>
       <c r="R34" s="11">
-        <v>1.37281915384833</v>
+        <v>0.3838203844749419</v>
       </c>
       <c r="S34" s="10">
-        <v>45.56155343762117</v>
+        <v>62.36549568058859</v>
       </c>
       <c r="T34" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -5090,61 +5136,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E35" s="9">
-        <v>211.0399932861328</v>
+        <v>588.1400146484375</v>
       </c>
       <c r="F35" s="16">
-        <v>0.4074003248877019</v>
+        <v>0.4041815876042349</v>
       </c>
       <c r="G35" s="19">
-        <v>0.3599630250019414</v>
+        <v>-1.47114938458048</v>
       </c>
       <c r="H35" s="19">
-        <v>0.7749817441404762</v>
+        <v>2.900487942036482</v>
       </c>
       <c r="I35" s="19">
-        <v>0.3840583979359316</v>
+        <v>-0.1716020620831971</v>
       </c>
       <c r="J35" s="19">
-        <v>0.2509594537838653</v>
+        <v>0.4759953389096645</v>
       </c>
       <c r="K35" s="19">
         <v>0</v>
       </c>
       <c r="L35" s="19">
-        <v>0.5759707794947954</v>
+        <v>0.9848097239858471</v>
       </c>
       <c r="M35" s="19">
-        <v>0.2683742454988952</v>
+        <v>-0.3539795414169304</v>
       </c>
       <c r="N35" s="19">
-        <v>17.362167</v>
+        <v>32.565643</v>
       </c>
       <c r="O35" s="19">
-        <v>3.1676524</v>
+        <v>93.07380000000001</v>
       </c>
       <c r="P35" s="11">
-        <v>0.17969999</v>
+        <v>2.41202</v>
       </c>
       <c r="Q35" s="11">
-        <v>0.28</v>
+        <v>0.141</v>
       </c>
       <c r="R35" s="11">
-        <v>0.2855805954504331</v>
+        <v>0.128544207361706</v>
       </c>
       <c r="S35" s="10">
-        <v>44.75446895024866</v>
+        <v>59.5727516235745</v>
       </c>
       <c r="T35" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -5152,61 +5198,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="9">
-        <v>183.1600036621094</v>
+        <v>51.83000183105469</v>
       </c>
       <c r="F36" s="16">
-        <v>0.4067274714559593</v>
+        <v>0.4032403155004064</v>
       </c>
       <c r="G36" s="19">
-        <v>-0.4206222377761193</v>
+        <v>0.2615753155071175</v>
       </c>
       <c r="H36" s="19">
-        <v>1.258828701477971</v>
+        <v>-0.6923506737965556</v>
       </c>
       <c r="I36" s="19">
-        <v>-0.2081970290549548</v>
+        <v>1.306361806653459</v>
       </c>
       <c r="J36" s="19">
-        <v>1.118158985786578</v>
+        <v>1.412991322463866</v>
       </c>
       <c r="K36" s="19">
         <v>0</v>
       </c>
       <c r="L36" s="19">
-        <v>-0.1102451625758058</v>
+        <v>-1.049236405032552</v>
       </c>
       <c r="M36" s="19">
-        <v>-0.9474212203932401</v>
+        <v>-0.9129420555753399</v>
       </c>
       <c r="N36" s="19">
-        <v>29.498423</v>
+        <v>48.887848</v>
       </c>
       <c r="O36" s="19">
-        <v>27.131872</v>
+        <v>2.7368805</v>
       </c>
       <c r="P36" s="11">
-        <v>1.06734</v>
+        <v>0.06315</v>
       </c>
       <c r="Q36" s="11">
-        <v>0.125</v>
+        <v>0.4</v>
       </c>
       <c r="R36" s="11">
-        <v>0.8691904851962537</v>
+        <v>1.427694779506832</v>
       </c>
       <c r="S36" s="10">
-        <v>45.70079166564421</v>
+        <v>48.46609615670043</v>
       </c>
       <c r="T36" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -5214,61 +5260,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="E37" s="9">
-        <v>581.0999755859375</v>
+        <v>203.4199981689453</v>
       </c>
       <c r="F37" s="16">
-        <v>0.3982279661457266</v>
+        <v>0.3977320246501523</v>
       </c>
       <c r="G37" s="19">
-        <v>-1.47114938458048</v>
+        <v>0.6290781538187236</v>
       </c>
       <c r="H37" s="19">
-        <v>2.900487942036482</v>
+        <v>-0.04474182683940042</v>
       </c>
       <c r="I37" s="19">
-        <v>-0.1716020620831971</v>
+        <v>1.575737480795989</v>
       </c>
       <c r="J37" s="19">
-        <v>0.4204683210053206</v>
+        <v>0.2972580080248712</v>
       </c>
       <c r="K37" s="19">
         <v>0</v>
       </c>
       <c r="L37" s="19">
-        <v>0.9729194059013544</v>
+        <v>0.2977503289166116</v>
       </c>
       <c r="M37" s="19">
-        <v>-0.2023253217558624</v>
+        <v>-0.2585920490373644</v>
       </c>
       <c r="N37" s="19">
-        <v>32.565643</v>
+        <v>37.579845</v>
       </c>
       <c r="O37" s="19">
-        <v>93.07380000000001</v>
+        <v>1.4633226</v>
       </c>
       <c r="P37" s="11">
-        <v>2.41202</v>
+        <v>0.034930002</v>
       </c>
       <c r="Q37" s="11">
-        <v>0.141</v>
+        <v>0.525</v>
       </c>
       <c r="R37" s="11">
-        <v>0.1120582336705458</v>
+        <v>0.1708141956994578</v>
       </c>
       <c r="S37" s="10">
-        <v>55.7027144979971</v>
+        <v>54.59967056168442</v>
       </c>
       <c r="T37" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -5276,61 +5322,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="E38" s="9">
-        <v>31.31999969482422</v>
+        <v>412.2000122070312</v>
       </c>
       <c r="F38" s="16">
-        <v>0.397033514189773</v>
+        <v>0.388489739750225</v>
       </c>
       <c r="G38" s="19">
-        <v>1.18884239126269</v>
+        <v>-0.9759620955182193</v>
       </c>
       <c r="H38" s="19">
-        <v>-0.9872240870343698</v>
+        <v>-0.4326356610429035</v>
       </c>
       <c r="I38" s="19">
-        <v>-0.3680930717051557</v>
+        <v>4.13232288715716</v>
       </c>
       <c r="J38" s="19">
-        <v>1.332643894788734</v>
+        <v>0.5407414873788275</v>
       </c>
       <c r="K38" s="19">
         <v>0</v>
       </c>
       <c r="L38" s="19">
-        <v>-0.4149864602001849</v>
+        <v>0.6557006232771234</v>
       </c>
       <c r="M38" s="19">
-        <v>-0.5591369708609789</v>
+        <v>-0.3503864798206195</v>
       </c>
       <c r="N38" s="19">
-        <v>11.648855</v>
+        <v>105.25127</v>
       </c>
       <c r="O38" s="19">
-        <v>-305.2</v>
+        <v>2.680677</v>
       </c>
       <c r="P38" s="11">
-        <v>0</v>
+        <v>0.019199999</v>
       </c>
       <c r="Q38" s="11">
-        <v>0.125</v>
+        <v>1.134</v>
       </c>
       <c r="R38" s="11">
-        <v>0.6946703650599875</v>
+        <v>0.2920010066668242</v>
       </c>
       <c r="S38" s="10">
-        <v>61.90359088766113</v>
+        <v>56.16483519470556</v>
       </c>
       <c r="T38" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -5338,61 +5384,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E39" s="9">
-        <v>405.8399963378906</v>
+        <v>378.3999938964844</v>
       </c>
       <c r="F39" s="16">
-        <v>0.382609050369776</v>
+        <v>0.3875455404815684</v>
       </c>
       <c r="G39" s="19">
-        <v>-0.9759620955182193</v>
+        <v>-0.8622441204646991</v>
       </c>
       <c r="H39" s="19">
-        <v>-0.4326356610429035</v>
+        <v>1.971798251919513</v>
       </c>
       <c r="I39" s="19">
-        <v>4.13232288715716</v>
+        <v>-0.2184519826388571</v>
       </c>
       <c r="J39" s="19">
-        <v>0.4890506651547327</v>
+        <v>0.5102721661937776</v>
       </c>
       <c r="K39" s="19">
         <v>0</v>
       </c>
       <c r="L39" s="19">
-        <v>0.659436157180652</v>
+        <v>1.071968338729742</v>
       </c>
       <c r="M39" s="19">
-        <v>-0.2240351300928499</v>
+        <v>-0.1849781864716033</v>
       </c>
       <c r="N39" s="19">
-        <v>105.25127</v>
+        <v>32.476597</v>
       </c>
       <c r="O39" s="19">
-        <v>2.680677</v>
+        <v>20.222574</v>
       </c>
       <c r="P39" s="11">
-        <v>0.019199999</v>
+        <v>0.6119</v>
       </c>
       <c r="Q39" s="11">
-        <v>1.134</v>
+        <v>0.144</v>
       </c>
       <c r="R39" s="11">
-        <v>0.3001857413090314</v>
+        <v>0.1854116881790868</v>
       </c>
       <c r="S39" s="10">
-        <v>52.07497110060028</v>
+        <v>59.27960086317145</v>
       </c>
       <c r="T39" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -5400,61 +5446,61 @@
         <v>36</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E40" s="9">
-        <v>372.6700134277344</v>
+        <v>175.9499969482422</v>
       </c>
       <c r="F40" s="16">
-        <v>0.3756909398323499</v>
+        <v>0.3791591078612157</v>
       </c>
       <c r="G40" s="19">
-        <v>-0.8622441204646991</v>
+        <v>0.5392511670723198</v>
       </c>
       <c r="H40" s="19">
-        <v>1.971798251919513</v>
+        <v>0.5664211651255424</v>
       </c>
       <c r="I40" s="19">
-        <v>-0.2184519826388571</v>
+        <v>-0.05328793731108517</v>
       </c>
       <c r="J40" s="19">
-        <v>0.4258115755662599</v>
+        <v>0.3732993523946713</v>
       </c>
       <c r="K40" s="19">
         <v>0</v>
       </c>
       <c r="L40" s="19">
-        <v>1.06278410242406</v>
+        <v>0.9118133589160312</v>
       </c>
       <c r="M40" s="19">
-        <v>0.008236598469447687</v>
+        <v>-0.1925299387186166</v>
       </c>
       <c r="N40" s="19">
-        <v>32.476597</v>
+        <v>15.65096</v>
       </c>
       <c r="O40" s="19">
-        <v>20.222574</v>
+        <v>2.7135465</v>
       </c>
       <c r="P40" s="11">
-        <v>0.6119</v>
+        <v>0.18416001</v>
       </c>
       <c r="Q40" s="11">
-        <v>0.144</v>
+        <v>0.151</v>
       </c>
       <c r="R40" s="11">
-        <v>0.1661514393863721</v>
+        <v>0.1352691192331681</v>
       </c>
       <c r="S40" s="10">
-        <v>54.30594212599105</v>
+        <v>51.14659916775605</v>
       </c>
       <c r="T40" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -5462,61 +5508,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="E41" s="9">
-        <v>93.19999694824219</v>
+        <v>180.7700042724609</v>
       </c>
       <c r="F41" s="16">
-        <v>0.3754470288895859</v>
+        <v>0.3701015955490788</v>
       </c>
       <c r="G41" s="19">
-        <v>0.1323994869339421</v>
+        <v>-0.4206222377761193</v>
       </c>
       <c r="H41" s="19">
-        <v>1.644369932284167</v>
+        <v>1.258828701477971</v>
       </c>
       <c r="I41" s="19">
-        <v>0.03944887499304424</v>
+        <v>-0.2081970290549548</v>
       </c>
       <c r="J41" s="19">
-        <v>0.1614520495458911</v>
+        <v>0.9688113260597638</v>
       </c>
       <c r="K41" s="19">
         <v>0</v>
       </c>
       <c r="L41" s="19">
-        <v>0.3775047400407024</v>
+        <v>-0.1106491049776869</v>
       </c>
       <c r="M41" s="19">
-        <v>-0.3946062269531829</v>
+        <v>-0.7899491745919611</v>
       </c>
       <c r="N41" s="19">
-        <v>16.766905</v>
+        <v>29.498423</v>
       </c>
       <c r="O41" s="19">
-        <v>18.876202</v>
+        <v>27.131872</v>
       </c>
       <c r="P41" s="11">
-        <v>1.5956</v>
+        <v>1.06734</v>
       </c>
       <c r="Q41" s="11">
-        <v>0.162</v>
+        <v>0.125</v>
       </c>
       <c r="R41" s="11">
-        <v>-0.03033542100628361</v>
+        <v>0.830715983068075</v>
       </c>
       <c r="S41" s="10">
-        <v>52.09734154570277</v>
+        <v>43.33101264507649</v>
       </c>
       <c r="T41" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -5524,61 +5570,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="E42" s="9">
-        <v>173.5</v>
+        <v>93.5</v>
       </c>
       <c r="F42" s="16">
-        <v>0.3742032834294255</v>
+        <v>0.3672375055603321</v>
       </c>
       <c r="G42" s="19">
-        <v>0.5392511670723198</v>
+        <v>0.1323994869339421</v>
       </c>
       <c r="H42" s="19">
-        <v>0.5664211651255424</v>
+        <v>1.644369932284167</v>
       </c>
       <c r="I42" s="19">
-        <v>-0.05328793731108517</v>
+        <v>0.03944887499304424</v>
       </c>
       <c r="J42" s="19">
-        <v>0.3318392787101034</v>
+        <v>0.1364811945313736</v>
       </c>
       <c r="K42" s="19">
         <v>0</v>
       </c>
       <c r="L42" s="19">
-        <v>0.908183206613303</v>
+        <v>0.3813605071284529</v>
       </c>
       <c r="M42" s="19">
-        <v>-0.08884611692413226</v>
+        <v>-0.3941621025863461</v>
       </c>
       <c r="N42" s="19">
-        <v>15.65096</v>
+        <v>16.766905</v>
       </c>
       <c r="O42" s="19">
-        <v>2.7135465</v>
+        <v>18.876202</v>
       </c>
       <c r="P42" s="11">
-        <v>0.18416001</v>
+        <v>1.5956</v>
       </c>
       <c r="Q42" s="11">
-        <v>0.151</v>
+        <v>0.162</v>
       </c>
       <c r="R42" s="11">
-        <v>0.1366433636618272</v>
+        <v>-0.02220638562540544</v>
       </c>
       <c r="S42" s="10">
-        <v>46.56301517390823</v>
+        <v>53.12201925221819</v>
       </c>
       <c r="T42" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -5586,61 +5632,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E43" s="9">
-        <v>279.2300109863281</v>
+        <v>551.8499755859375</v>
       </c>
       <c r="F43" s="16">
-        <v>0.3625757988498952</v>
+        <v>0.3648330507542389</v>
       </c>
       <c r="G43" s="19">
-        <v>-0.7341033794993066</v>
+        <v>0.3916703502557107</v>
       </c>
       <c r="H43" s="19">
-        <v>0.653024735669726</v>
+        <v>0.6265242524488559</v>
       </c>
       <c r="I43" s="19">
-        <v>0.001731719619972795</v>
+        <v>-0.2860643400571251</v>
       </c>
       <c r="J43" s="19">
-        <v>1.317087280823995</v>
+        <v>0.5252619231853878</v>
       </c>
       <c r="K43" s="19">
         <v>0</v>
       </c>
       <c r="L43" s="19">
-        <v>-0.8317433282113849</v>
+        <v>0.9268259731960974</v>
       </c>
       <c r="M43" s="19">
-        <v>0.01658246342642533</v>
+        <v>-0.4284145014473035</v>
       </c>
       <c r="N43" s="19">
-        <v>45.4335</v>
+        <v>13.51341</v>
       </c>
       <c r="O43" s="19">
-        <v>6.1722584</v>
+        <v>7.7711396</v>
       </c>
       <c r="P43" s="11">
-        <v>0.14425</v>
+        <v>0.63432</v>
       </c>
       <c r="Q43" s="11">
-        <v>0.176</v>
+        <v>0.116</v>
       </c>
       <c r="R43" s="11">
-        <v>0.5019633450915717</v>
+        <v>0.1848664875860098</v>
       </c>
       <c r="S43" s="10">
-        <v>71.94310024507712</v>
+        <v>52.0959831864543</v>
       </c>
       <c r="T43" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -5648,19 +5694,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E44" s="9">
-        <v>1002.559997558594</v>
+        <v>1004.419982910156</v>
       </c>
       <c r="F44" s="16">
-        <v>0.3615089972733027</v>
+        <v>0.3632966640111714</v>
       </c>
       <c r="G44" s="19">
         <v>0.3744813910308467</v>
@@ -5672,16 +5718,16 @@
         <v>0.9077656154464111</v>
       </c>
       <c r="J44" s="19">
-        <v>-0.03529280392525902</v>
+        <v>-0.02661500857543126</v>
       </c>
       <c r="K44" s="19">
         <v>0</v>
       </c>
       <c r="L44" s="19">
-        <v>0.1072850274881307</v>
+        <v>0.106438951031148</v>
       </c>
       <c r="M44" s="19">
-        <v>0.4025375201396288</v>
+        <v>0.3902946790370682</v>
       </c>
       <c r="N44" s="19">
         <v>16.078215</v>
@@ -5696,13 +5742,13 @@
         <v>0.425</v>
       </c>
       <c r="R44" s="11">
-        <v>0.1731204225933523</v>
+        <v>0.1689680793707509</v>
       </c>
       <c r="S44" s="10">
-        <v>42.20008189154053</v>
+        <v>42.76251908080483</v>
       </c>
       <c r="T44" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -5768,110 +5814,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B6" s="11">
         <v>0.18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B7" s="11">
         <v>0.16</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B8" s="11">
         <v>0.1</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B9" s="11">
         <v>0.3</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B10" s="11">
         <v>0.12</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B11" s="11">
         <v>0.06</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B12" s="11">
         <v>0.08</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B13" s="11">
         <f>SUM(B6:B12)</f>
@@ -5880,22 +5926,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -5974,57 +6020,57 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>27</v>
@@ -6032,113 +6078,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B23" s="20"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B24" s="20"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B25" s="20"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B26" s="20"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="20" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B27" s="20"/>
     </row>
@@ -6164,181 +6210,181 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>381.1501770019531</v>
+        <v>369.2198791503906</v>
       </c>
       <c r="C1">
-        <v>369.2198791503906</v>
+        <v>390.8042297363281</v>
       </c>
       <c r="D1">
-        <v>390.8042297363281</v>
+        <v>394.9174194335938</v>
       </c>
       <c r="E1">
-        <v>394.9174194335938</v>
+        <v>408.3951416015625</v>
       </c>
       <c r="F1">
-        <v>408.3951416015625</v>
+        <v>403.4133605957031</v>
       </c>
       <c r="G1">
-        <v>403.4133605957031</v>
+        <v>418.6282348632812</v>
       </c>
       <c r="H1">
-        <v>418.6282348632812</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="I1">
-        <v>408.8244323730469</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="J1">
-        <v>418.0192260742188</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="K1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="L1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="M1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="N1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="O1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="P1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="Q1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="R1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="S1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="T1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="U1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="V1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="W1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="X1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="Y1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="Z1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="AA1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="AB1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="AC1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="AD1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="AE1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="AF1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="AG1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AH1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AI1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AJ1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AK1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AL1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AM1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AN1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AO1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AP1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AQ1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AR1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AS1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AT1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AU1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AV1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AW1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AX1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="AY1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="AZ1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="BA1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="BB1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="BC1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="BD1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="BE1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
       <c r="BF1">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="BG1">
-        <v>456.010009765625</v>
+        <v>425</v>
       </c>
       <c r="BH1">
-        <v>425</v>
+        <v>492.2000122070312</v>
       </c>
     </row>
     <row r="2" spans="1:60">
@@ -6346,181 +6392,181 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>935.74609375</v>
+        <v>891.7428588867188</v>
       </c>
       <c r="C2">
-        <v>891.7428588867188</v>
+        <v>995.7168579101562</v>
       </c>
       <c r="D2">
-        <v>995.7168579101562</v>
+        <v>981.4590454101562</v>
       </c>
       <c r="E2">
-        <v>981.4590454101562</v>
+        <v>1087.822631835938</v>
       </c>
       <c r="F2">
-        <v>1087.822631835938</v>
+        <v>1020.60302734375</v>
       </c>
       <c r="G2">
-        <v>1020.60302734375</v>
+        <v>1043.029541015625</v>
       </c>
       <c r="H2">
-        <v>1043.029541015625</v>
+        <v>1133.815551757812</v>
       </c>
       <c r="I2">
-        <v>1133.815551757812</v>
+        <v>1211.193725585938</v>
       </c>
       <c r="J2">
-        <v>1211.193725585938</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="K2">
-        <v>1051.608276367188</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="L2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="M2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="N2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="O2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="P2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="Q2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="R2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="S2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="T2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="U2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="V2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="W2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="X2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="Y2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="Z2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="AA2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="AB2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="AC2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="AD2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="AE2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="AF2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="AG2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="AH2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AI2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="AJ2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AK2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AL2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AM2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AN2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AO2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AP2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AQ2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AR2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AS2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AT2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AU2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AV2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="AW2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AX2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="AY2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="AZ2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="BA2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="BB2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="BC2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="BD2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="BE2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="BF2">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="BG2">
-        <v>958.72998046875</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="BH2">
-        <v>933.4400024414062</v>
+        <v>956.0800170898438</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -6528,181 +6574,181 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1646.5400390625</v>
+        <v>1643.22998046875</v>
       </c>
       <c r="C3">
-        <v>1643.22998046875</v>
+        <v>1881.510009765625</v>
       </c>
       <c r="D3">
-        <v>1881.510009765625</v>
+        <v>1980.099975585938</v>
       </c>
       <c r="E3">
-        <v>1980.099975585938</v>
+        <v>2107.860107421875</v>
       </c>
       <c r="F3">
-        <v>2107.860107421875</v>
+        <v>1991.550048828125</v>
       </c>
       <c r="G3">
-        <v>1991.550048828125</v>
+        <v>1958.800048828125</v>
       </c>
       <c r="H3">
-        <v>1958.800048828125</v>
+        <v>2184.75</v>
       </c>
       <c r="I3">
-        <v>2184.75</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="J3">
+        <v>1963.599975585938</v>
+      </c>
+      <c r="K3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="L3">
+        <v>2335</v>
+      </c>
+      <c r="M3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="N3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="O3">
         <v>2273.72998046875</v>
       </c>
-      <c r="K3">
-        <v>1963.599975585938</v>
-      </c>
-      <c r="L3">
-        <v>1914.4599609375</v>
-      </c>
-      <c r="M3">
-        <v>2335</v>
-      </c>
-      <c r="N3">
-        <v>2090.7099609375</v>
-      </c>
-      <c r="O3">
-        <v>2050.389892578125</v>
-      </c>
       <c r="P3">
-        <v>2273.72998046875</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="Q3">
-        <v>2032.219970703125</v>
+        <v>1745</v>
       </c>
       <c r="R3">
-        <v>1745</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="S3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="T3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="U3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="V3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="W3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="X3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="Y3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="Z3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="AA3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="AB3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="AC3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="AD3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="AE3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="AF3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="AG3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="AH3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="AI3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AJ3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AK3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AL3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AM3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AN3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="AO3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AP3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AQ3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AR3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AS3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AT3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AU3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AV3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AW3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AX3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="AY3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="AZ3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="BA3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="BB3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="BC3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="BD3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="BE3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="BF3">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="BG3">
-        <v>1566.699951171875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="BH3">
-        <v>1536.869995117188</v>
+        <v>1553.400024414062</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -6710,181 +6756,181 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>517.719970703125</v>
+        <v>490.0899963378906</v>
       </c>
       <c r="C4">
-        <v>490.0899963378906</v>
+        <v>529.2899780273438</v>
       </c>
       <c r="D4">
-        <v>529.2899780273438</v>
+        <v>562.9299926757812</v>
       </c>
       <c r="E4">
-        <v>562.9299926757812</v>
+        <v>653.530029296875</v>
       </c>
       <c r="F4">
-        <v>653.530029296875</v>
+        <v>681.0800170898438</v>
       </c>
       <c r="G4">
-        <v>681.0800170898438</v>
+        <v>712.1300048828125</v>
       </c>
       <c r="H4">
-        <v>712.1300048828125</v>
+        <v>746.22998046875</v>
       </c>
       <c r="I4">
-        <v>746.22998046875</v>
+        <v>732.6199951171875</v>
       </c>
       <c r="J4">
-        <v>732.6199951171875</v>
+        <v>670.75</v>
       </c>
       <c r="K4">
-        <v>670.75</v>
+        <v>643.8300170898438</v>
       </c>
       <c r="L4">
-        <v>643.8300170898438</v>
+        <v>675.3900146484375</v>
       </c>
       <c r="M4">
-        <v>675.3900146484375</v>
+        <v>586.4500122070312</v>
       </c>
       <c r="N4">
-        <v>586.4500122070312</v>
+        <v>651.8800048828125</v>
       </c>
       <c r="O4">
-        <v>651.8800048828125</v>
+        <v>638.719970703125</v>
       </c>
       <c r="P4">
-        <v>638.719970703125</v>
+        <v>598.3699951171875</v>
       </c>
       <c r="Q4">
-        <v>598.3699951171875</v>
+        <v>539</v>
       </c>
       <c r="R4">
-        <v>539</v>
+        <v>577.4600219726562</v>
       </c>
       <c r="S4">
-        <v>577.4600219726562</v>
+        <v>532.0999755859375</v>
       </c>
       <c r="T4">
-        <v>532.0999755859375</v>
+        <v>550.2999877929688</v>
       </c>
       <c r="U4">
-        <v>550.2999877929688</v>
+        <v>578.0499877929688</v>
       </c>
       <c r="V4">
-        <v>578.0499877929688</v>
+        <v>582.5900268554688</v>
       </c>
       <c r="W4">
-        <v>582.5900268554688</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="X4">
-        <v>555.5499877929688</v>
+        <v>563.3200073242188</v>
       </c>
       <c r="Y4">
-        <v>563.3200073242188</v>
+        <v>513.8400268554688</v>
       </c>
       <c r="Z4">
-        <v>513.8400268554688</v>
+        <v>466.8099975585938</v>
       </c>
       <c r="AA4">
-        <v>466.8099975585938</v>
+        <v>477.2200012207031</v>
       </c>
       <c r="AB4">
-        <v>477.2200012207031</v>
+        <v>487.4200134277344</v>
       </c>
       <c r="AC4">
-        <v>487.4200134277344</v>
+        <v>548.3900146484375</v>
       </c>
       <c r="AD4">
-        <v>548.3900146484375</v>
+        <v>556.6699829101562</v>
       </c>
       <c r="AE4">
-        <v>556.6699829101562</v>
+        <v>558.2999877929688</v>
       </c>
       <c r="AF4">
-        <v>558.2999877929688</v>
+        <v>519.7999877929688</v>
       </c>
       <c r="AG4">
-        <v>519.7999877929688</v>
+        <v>497.9200134277344</v>
       </c>
       <c r="AH4">
-        <v>497.9200134277344</v>
+        <v>463.510009765625</v>
       </c>
       <c r="AI4">
-        <v>463.510009765625</v>
+        <v>462.0400085449219</v>
       </c>
       <c r="AJ4">
-        <v>462.0400085449219</v>
+        <v>533.0399780273438</v>
       </c>
       <c r="AK4">
-        <v>533.0399780273438</v>
+        <v>544.8400268554688</v>
       </c>
       <c r="AL4">
-        <v>544.8400268554688</v>
+        <v>527.219970703125</v>
       </c>
       <c r="AM4">
-        <v>527.219970703125</v>
+        <v>548.5599975585938</v>
       </c>
       <c r="AN4">
-        <v>548.5599975585938</v>
+        <v>519.1699829101562</v>
       </c>
       <c r="AO4">
-        <v>519.1699829101562</v>
+        <v>451.5199890136719</v>
       </c>
       <c r="AP4">
-        <v>451.5199890136719</v>
+        <v>434.2999877929688</v>
       </c>
       <c r="AQ4">
-        <v>434.2999877929688</v>
+        <v>438.3399963378906</v>
       </c>
       <c r="AR4">
-        <v>438.3399963378906</v>
+        <v>437.9299926757812</v>
       </c>
       <c r="AS4">
-        <v>437.9299926757812</v>
+        <v>454.1000061035156</v>
       </c>
       <c r="AT4">
-        <v>454.1000061035156</v>
+        <v>487.2900085449219</v>
       </c>
       <c r="AU4">
-        <v>487.2900085449219</v>
+        <v>508.7999877929688</v>
       </c>
       <c r="AV4">
-        <v>508.7999877929688</v>
+        <v>536.010009765625</v>
       </c>
       <c r="AW4">
-        <v>536.010009765625</v>
+        <v>496.1600036621094</v>
       </c>
       <c r="AX4">
-        <v>496.1600036621094</v>
+        <v>462.0899963378906</v>
       </c>
       <c r="AY4">
-        <v>462.0899963378906</v>
+        <v>469.0499877929688</v>
       </c>
       <c r="AZ4">
-        <v>469.0499877929688</v>
+        <v>459.4400024414062</v>
       </c>
       <c r="BA4">
-        <v>459.4400024414062</v>
+        <v>435.3800048828125</v>
       </c>
       <c r="BB4">
-        <v>435.3800048828125</v>
+        <v>450.75</v>
       </c>
       <c r="BC4">
-        <v>450.75</v>
+        <v>468.8800048828125</v>
       </c>
       <c r="BD4">
-        <v>468.8800048828125</v>
+        <v>462</v>
       </c>
       <c r="BE4">
-        <v>462</v>
+        <v>459.4500122070312</v>
       </c>
       <c r="BF4">
-        <v>459.4500122070312</v>
+        <v>450.5499877929688</v>
       </c>
       <c r="BG4">
-        <v>450.5499877929688</v>
+        <v>450.4400024414062</v>
       </c>
       <c r="BH4">
-        <v>450.4400024414062</v>
+        <v>448.8999938964844</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -6892,181 +6938,181 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>252.8030090332031</v>
+        <v>256.9967956542969</v>
       </c>
       <c r="C5">
-        <v>256.9967956542969</v>
+        <v>254.6160125732422</v>
       </c>
       <c r="D5">
-        <v>254.6160125732422</v>
+        <v>257.6741943359375</v>
       </c>
       <c r="E5">
-        <v>257.6741943359375</v>
+        <v>246.20849609375</v>
       </c>
       <c r="F5">
-        <v>246.20849609375</v>
+        <v>243.1901702880859</v>
       </c>
       <c r="G5">
-        <v>243.1901702880859</v>
+        <v>238.8469543457031</v>
       </c>
       <c r="H5">
-        <v>238.8469543457031</v>
+        <v>235.3903045654297</v>
       </c>
       <c r="I5">
-        <v>235.3903045654297</v>
+        <v>242.8415069580078</v>
       </c>
       <c r="J5">
-        <v>242.8415069580078</v>
+        <v>242.7418823242188</v>
       </c>
       <c r="K5">
-        <v>242.7418823242188</v>
+        <v>241.4967041015625</v>
       </c>
       <c r="L5">
-        <v>241.4967041015625</v>
+        <v>254.0780792236328</v>
       </c>
       <c r="M5">
-        <v>254.0780792236328</v>
+        <v>258.3714904785156</v>
       </c>
       <c r="N5">
-        <v>258.3714904785156</v>
+        <v>265.2947387695312</v>
       </c>
       <c r="O5">
-        <v>265.2947387695312</v>
+        <v>259.4373779296875</v>
       </c>
       <c r="P5">
-        <v>259.4373779296875</v>
+        <v>268.4027404785156</v>
       </c>
       <c r="Q5">
-        <v>268.4027404785156</v>
+        <v>266.7291870117188</v>
       </c>
       <c r="R5">
-        <v>266.7291870117188</v>
+        <v>269.2793579101562</v>
       </c>
       <c r="S5">
-        <v>269.2793579101562</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="T5">
-        <v>265.1951293945312</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="U5">
-        <v>281.7909851074219</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="V5">
-        <v>280.1672668457031</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="W5">
-        <v>279.6094055175781</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="X5">
-        <v>294.6513061523438</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="Y5">
-        <v>300.2695617675781</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="Z5">
-        <v>291.5333251953125</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="AA5">
-        <v>299.1040954589844</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="AB5">
-        <v>308.4579162597656</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="AC5">
-        <v>312.1038208007812</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="AD5">
-        <v>313.5880737304688</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="AE5">
-        <v>309.7230529785156</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="AF5">
-        <v>304.0848388671875</v>
+        <v>301.33544921875</v>
       </c>
       <c r="AG5">
-        <v>301.33544921875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="AH5">
-        <v>303.756103515625</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="AI5">
-        <v>297.7294006347656</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="AJ5">
-        <v>300.1600036621094</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="AK5">
-        <v>310.5099792480469</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="AL5">
-        <v>312.8999938964844</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="AM5">
-        <v>307.5400085449219</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="AN5">
-        <v>308.7300109863281</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="AO5">
-        <v>302.3900146484375</v>
+        <v>302.989990234375</v>
       </c>
       <c r="AP5">
-        <v>302.989990234375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="AQ5">
-        <v>298.3099975585938</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AR5">
-        <v>314.9500122070312</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AS5">
-        <v>323.9200134277344</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AT5">
-        <v>330.2099914550781</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AU5">
-        <v>342.9200134277344</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AV5">
-        <v>341.6700134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AW5">
-        <v>347.1900024414062</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AX5">
-        <v>350.0499877929688</v>
+        <v>346.260009765625</v>
       </c>
       <c r="AY5">
-        <v>346.260009765625</v>
+        <v>341.510009765625</v>
       </c>
       <c r="AZ5">
-        <v>341.510009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="BA5">
-        <v>348.8599853515625</v>
+        <v>346</v>
       </c>
       <c r="BB5">
-        <v>346</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="BC5">
-        <v>340.4100036621094</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="BD5">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="BE5">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="BF5">
-        <v>352.3599853515625</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="BG5">
-        <v>358.9200134277344</v>
+        <v>361.989990234375</v>
       </c>
       <c r="BH5">
-        <v>361.989990234375</v>
+        <v>366.0899963378906</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -7074,181 +7120,181 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>257.445068359375</v>
+        <v>262.5610656738281</v>
       </c>
       <c r="C6">
-        <v>262.5610656738281</v>
+        <v>260.0978088378906</v>
       </c>
       <c r="D6">
-        <v>260.0978088378906</v>
+        <v>262.8602294921875</v>
       </c>
       <c r="E6">
-        <v>262.8602294921875</v>
+        <v>250.1749877929688</v>
       </c>
       <c r="F6">
-        <v>250.1749877929688</v>
+        <v>249.7860565185547</v>
       </c>
       <c r="G6">
-        <v>249.7860565185547</v>
+        <v>243.9420471191406</v>
       </c>
       <c r="H6">
-        <v>243.9420471191406</v>
+        <v>242.2467041015625</v>
       </c>
       <c r="I6">
-        <v>242.2467041015625</v>
+        <v>246.6147308349609</v>
       </c>
       <c r="J6">
-        <v>246.6147308349609</v>
+        <v>247.8413848876953</v>
       </c>
       <c r="K6">
-        <v>247.8413848876953</v>
+        <v>245.8368530273438</v>
       </c>
       <c r="L6">
-        <v>245.8368530273438</v>
+        <v>252.8676147460938</v>
       </c>
       <c r="M6">
-        <v>252.8676147460938</v>
+        <v>253.3662414550781</v>
       </c>
       <c r="N6">
-        <v>253.3662414550781</v>
+        <v>258.5121459960938</v>
       </c>
       <c r="O6">
-        <v>258.5121459960938</v>
+        <v>254.9718475341797</v>
       </c>
       <c r="P6">
-        <v>254.9718475341797</v>
+        <v>264.146728515625</v>
       </c>
       <c r="Q6">
-        <v>264.146728515625</v>
+        <v>265.6226806640625</v>
       </c>
       <c r="R6">
-        <v>265.6226806640625</v>
+        <v>268.2554626464844</v>
       </c>
       <c r="S6">
-        <v>268.2554626464844</v>
+        <v>265.6027221679688</v>
       </c>
       <c r="T6">
-        <v>265.6027221679688</v>
+        <v>279.9135437011719</v>
       </c>
       <c r="U6">
-        <v>279.9135437011719</v>
+        <v>282.5263977050781</v>
       </c>
       <c r="V6">
-        <v>282.5263977050781</v>
+        <v>282.9651794433594</v>
       </c>
       <c r="W6">
-        <v>282.9651794433594</v>
+        <v>296.0693359375</v>
       </c>
       <c r="X6">
-        <v>296.0693359375</v>
+        <v>302.5715026855469</v>
       </c>
       <c r="Y6">
-        <v>302.5715026855469</v>
+        <v>298.363037109375</v>
       </c>
       <c r="Z6">
-        <v>298.363037109375</v>
+        <v>305.0148315429688</v>
       </c>
       <c r="AA6">
-        <v>305.0148315429688</v>
+        <v>311.7463989257812</v>
       </c>
       <c r="AB6">
-        <v>311.7463989257812</v>
+        <v>314.4490051269531</v>
       </c>
       <c r="AC6">
-        <v>314.4490051269531</v>
+        <v>318.8868408203125</v>
       </c>
       <c r="AD6">
-        <v>318.8868408203125</v>
+        <v>314.9576110839844</v>
       </c>
       <c r="AE6">
-        <v>314.9576110839844</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="AF6">
-        <v>311.4172973632812</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="AG6">
-        <v>308.3955688476562</v>
+        <v>311.4970703125</v>
       </c>
       <c r="AH6">
-        <v>311.4970703125</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="AI6">
-        <v>305.2142639160156</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="AJ6">
-        <v>307.8769836425781</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="AK6">
-        <v>313.2223510742188</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="AL6">
-        <v>315.6058349609375</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="AM6">
-        <v>306.1915893554688</v>
+        <v>311.75634765625</v>
       </c>
       <c r="AN6">
-        <v>311.75634765625</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="AO6">
-        <v>296.9369506835938</v>
+        <v>298.432861328125</v>
       </c>
       <c r="AP6">
-        <v>298.432861328125</v>
+        <v>297.3857421875</v>
       </c>
       <c r="AQ6">
-        <v>297.3857421875</v>
+        <v>319.4453125</v>
       </c>
       <c r="AR6">
-        <v>319.4453125</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="AS6">
-        <v>335.5013732910156</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="AT6">
-        <v>347.2990417480469</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="AU6">
-        <v>355.3968811035156</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="AV6">
-        <v>354.4494934082031</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="AW6">
-        <v>357.2019348144531</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="AX6">
-        <v>365.2099914550781</v>
+        <v>360.75</v>
       </c>
       <c r="AY6">
-        <v>360.75</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="AZ6">
-        <v>358.2300109863281</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="BA6">
-        <v>360.7200012207031</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="BB6">
-        <v>362.5199890136719</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="BC6">
-        <v>354.8800048828125</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="BD6">
-        <v>362.2699890136719</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="BE6">
-        <v>363.5400085449219</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="BF6">
-        <v>368.8299865722656</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="BG6">
-        <v>373.3200073242188</v>
+        <v>383</v>
       </c>
       <c r="BH6">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -285,6 +285,12 @@
     <t>APA Corporation</t>
   </si>
   <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>Nvidia</t>
+  </si>
+  <si>
     <t>CF</t>
   </si>
   <si>
@@ -294,10 +300,16 @@
     <t>Materials</t>
   </si>
   <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>Nvidia</t>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>Gen Digital</t>
   </si>
   <si>
     <t>CVX</t>
@@ -306,52 +318,121 @@
     <t>Chevron Corporation</t>
   </si>
   <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>Amgen</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
     <t>EOG</t>
   </si>
   <si>
     <t>EOG Resources</t>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
-    <t>Financials</t>
-  </si>
-  <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>Gen Digital</t>
-  </si>
-  <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>Capital One</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>Health Care</t>
-  </si>
-  <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>Amgen</t>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
+  </si>
+  <si>
+    <t>SCHW</t>
+  </si>
+  <si>
+    <t>Charles Schwab Corporation</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>Altria</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>CPAY</t>
+  </si>
+  <si>
+    <t>Corpay</t>
+  </si>
+  <si>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>Humana</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
+  </si>
+  <si>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>Newmont</t>
+  </si>
+  <si>
+    <t>RJF</t>
+  </si>
+  <si>
+    <t>Raymond James Financial</t>
+  </si>
+  <si>
+    <t>TGT</t>
+  </si>
+  <si>
+    <t>Target Corporation</t>
   </si>
   <si>
     <t>EXPE</t>
@@ -363,115 +444,34 @@
     <t>Consumer Discretionary</t>
   </si>
   <si>
-    <t>HPQ</t>
-  </si>
-  <si>
-    <t>HP Inc.</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>Altria</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
-  </si>
-  <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
-  </si>
-  <si>
-    <t>SCHW</t>
-  </si>
-  <si>
-    <t>Charles Schwab Corporation</t>
-  </si>
-  <si>
-    <t>CPAY</t>
-  </si>
-  <si>
-    <t>Corpay</t>
-  </si>
-  <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
-  </si>
-  <si>
-    <t>TGT</t>
-  </si>
-  <si>
-    <t>Target Corporation</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>Mastercard</t>
-  </si>
-  <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>Hewlett Packard Enterprise</t>
-  </si>
-  <si>
     <t>FANG</t>
   </si>
   <si>
     <t>Diamondback Energy</t>
   </si>
   <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
+  </si>
+  <si>
     <t>WAT</t>
   </si>
   <si>
     <t>Waters Corporation</t>
   </si>
   <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Visa Inc.</t>
-  </si>
-  <si>
-    <t>RJF</t>
-  </si>
-  <si>
-    <t>Raymond James Financial</t>
-  </si>
-  <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
-    <t>HAS</t>
-  </si>
-  <si>
-    <t>Hasbro</t>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
+    <t>PRU</t>
+  </si>
+  <si>
+    <t>Prudential Financial</t>
   </si>
   <si>
     <t>AMP</t>
@@ -480,10 +480,10 @@
     <t>Ameriprise Financial</t>
   </si>
   <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
+    <t>VEEV</t>
+  </si>
+  <si>
+    <t>Veeva Systems</t>
   </si>
   <si>
     <t>Факторы и самообучение</t>
@@ -564,7 +564,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-04 00:09 UTC · данные на 2026-09-03 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-05 00:09 UTC · данные на 2026-09-03 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -645,7 +645,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-04 00:09 UTC</t>
+    <t>2026-09-05 00:09 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -3276,58 +3276,58 @@
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="9">
-        <v>1553.400024414062</v>
+        <v>958.1599731445312</v>
       </c>
       <c r="F5" s="16">
-        <v>1.054822033420676</v>
+        <v>1.096021962209379</v>
       </c>
       <c r="G5" s="19">
-        <v>-0.3065942401812342</v>
+        <v>-0.4169145554552529</v>
       </c>
       <c r="H5" s="19">
-        <v>2.061675894555025</v>
+        <v>1.817222982186202</v>
       </c>
       <c r="I5" s="19">
-        <v>4.13232288715716</v>
+        <v>4.262123054334927</v>
       </c>
       <c r="J5" s="19">
-        <v>1.322980606249683</v>
+        <v>1.668466830072545</v>
       </c>
       <c r="K5" s="19">
         <v>0</v>
       </c>
       <c r="L5" s="19">
-        <v>-3.480672299295953</v>
+        <v>-3.395096428765233</v>
       </c>
       <c r="M5" s="19">
-        <v>0.6534509610143624</v>
+        <v>0.3217712605883051</v>
       </c>
       <c r="N5" s="19">
-        <v>20.12168</v>
+        <v>21.095882</v>
       </c>
       <c r="O5" s="19">
-        <v>14.060845</v>
+        <v>10.456314</v>
       </c>
       <c r="P5" s="11">
-        <v>0.9164</v>
+        <v>0.66638</v>
       </c>
       <c r="Q5" s="11">
-        <v>3.716</v>
+        <v>3.457</v>
       </c>
       <c r="R5" s="11">
-        <v>1.593062515849467</v>
+        <v>1.414582370579996</v>
       </c>
       <c r="S5" s="10">
-        <v>52.49743744689197</v>
+        <v>53.48813900653059</v>
       </c>
       <c r="T5" s="8" t="s">
         <v>79</v>
@@ -3338,58 +3338,58 @@
         <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="9">
-        <v>956.0800170898438</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="F6" s="16">
-        <v>1.054233623855224</v>
+        <v>1.077323603968069</v>
       </c>
       <c r="G6" s="19">
-        <v>-0.4169145554552529</v>
+        <v>-0.3065942401812342</v>
       </c>
       <c r="H6" s="19">
-        <v>1.817222982186202</v>
+        <v>2.061675894555025</v>
       </c>
       <c r="I6" s="19">
-        <v>4.262123054334927</v>
+        <v>4.13232288715716</v>
       </c>
       <c r="J6" s="19">
-        <v>1.575703537612333</v>
+        <v>1.371569018924575</v>
       </c>
       <c r="K6" s="19">
         <v>0</v>
       </c>
       <c r="L6" s="19">
-        <v>-3.480672299295953</v>
+        <v>-3.395096428765233</v>
       </c>
       <c r="M6" s="19">
-        <v>0.274143788316431</v>
+        <v>0.6545797866068044</v>
       </c>
       <c r="N6" s="19">
-        <v>21.095882</v>
+        <v>20.12168</v>
       </c>
       <c r="O6" s="19">
-        <v>10.456314</v>
+        <v>14.060845</v>
       </c>
       <c r="P6" s="11">
-        <v>0.66638</v>
+        <v>0.9164</v>
       </c>
       <c r="Q6" s="11">
-        <v>3.457</v>
+        <v>3.716</v>
       </c>
       <c r="R6" s="11">
-        <v>1.386977208278282</v>
+        <v>1.749323567248363</v>
       </c>
       <c r="S6" s="10">
-        <v>53.22980636839034</v>
+        <v>52.58214372024118</v>
       </c>
       <c r="T6" s="8" t="s">
         <v>79</v>
@@ -3409,10 +3409,10 @@
         <v>35</v>
       </c>
       <c r="E7" s="9">
-        <v>366.0899963378906</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="F7" s="16">
-        <v>0.970848932712693</v>
+        <v>0.9911741855134996</v>
       </c>
       <c r="G7" s="19">
         <v>0.7600315297409044</v>
@@ -3424,16 +3424,16 @@
         <v>2.817024529253408</v>
       </c>
       <c r="J7" s="19">
-        <v>1.956005339459257</v>
+        <v>1.959572018248336</v>
       </c>
       <c r="K7" s="19">
         <v>0</v>
       </c>
       <c r="L7" s="19">
-        <v>0.1577591647917007</v>
+        <v>0.1616019038804626</v>
       </c>
       <c r="M7" s="19">
-        <v>-0.6453114425144759</v>
+        <v>-0.4379907614812187</v>
       </c>
       <c r="N7" s="19">
         <v>14.45283</v>
@@ -3448,10 +3448,10 @@
         <v>0.517</v>
       </c>
       <c r="R7" s="11">
-        <v>0.6367502230808904</v>
+        <v>0.6396552190773792</v>
       </c>
       <c r="S7" s="10">
-        <v>73.56767422107127</v>
+        <v>75.25607412562715</v>
       </c>
       <c r="T7" s="8" t="s">
         <v>79</v>
@@ -3471,10 +3471,10 @@
         <v>35</v>
       </c>
       <c r="E8" s="9">
-        <v>387</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="F8" s="16">
-        <v>0.9527241260639225</v>
+        <v>0.9884768325874498</v>
       </c>
       <c r="G8" s="19">
         <v>0.749794509494801</v>
@@ -3486,16 +3486,16 @@
         <v>2.384116899919412</v>
       </c>
       <c r="J8" s="19">
-        <v>1.967566018480531</v>
+        <v>2.025798104821206</v>
       </c>
       <c r="K8" s="19">
         <v>0</v>
       </c>
       <c r="L8" s="19">
-        <v>0.1562152461765964</v>
+        <v>0.1902059816486769</v>
       </c>
       <c r="M8" s="19">
-        <v>-0.5361763645537554</v>
+        <v>-0.3867599681765483</v>
       </c>
       <c r="N8" s="19">
         <v>12.788835</v>
@@ -3510,10 +3510,10 @@
         <v>0.537</v>
       </c>
       <c r="R8" s="11">
-        <v>0.7644638770403485</v>
+        <v>0.7954330965045495</v>
       </c>
       <c r="S8" s="10">
-        <v>77.64884558414819</v>
+        <v>77.86244970613882</v>
       </c>
       <c r="T8" s="8" t="s">
         <v>79</v>
@@ -3524,58 +3524,58 @@
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E9" s="9">
-        <v>256.0899963378906</v>
+        <v>516.3900146484375</v>
       </c>
       <c r="F9" s="16">
-        <v>0.8081645330578578</v>
+        <v>0.8591324836682116</v>
       </c>
       <c r="G9" s="19">
-        <v>0.5236285305189845</v>
+        <v>-0.1453667345878826</v>
       </c>
       <c r="H9" s="19">
-        <v>-0.7870784679473629</v>
+        <v>-0.9104682528073633</v>
       </c>
       <c r="I9" s="19">
-        <v>2.35386274831343</v>
+        <v>2.981910484335923</v>
       </c>
       <c r="J9" s="19">
-        <v>1.78415593478787</v>
+        <v>2.577492704403162</v>
       </c>
       <c r="K9" s="19">
         <v>0</v>
       </c>
       <c r="L9" s="19">
-        <v>0.3679724233679795</v>
+        <v>-2.576321565488059</v>
       </c>
       <c r="M9" s="19">
-        <v>-0.6230899025088393</v>
+        <v>0.137724405972072</v>
       </c>
       <c r="N9" s="19">
-        <v>13.92751</v>
+        <v>36.353783</v>
       </c>
       <c r="O9" s="19">
-        <v>3.090377</v>
+        <v>-210.92924</v>
       </c>
       <c r="P9" s="11">
-        <v>0.23452999</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="11">
-        <v>0.531</v>
+        <v>0.875</v>
       </c>
       <c r="R9" s="11">
-        <v>0.5742975601977356</v>
+        <v>2.541111763575812</v>
       </c>
       <c r="S9" s="10">
-        <v>77.05320797340288</v>
+        <v>62.55191579975656</v>
       </c>
       <c r="T9" s="8" t="s">
         <v>79</v>
@@ -3586,58 +3586,58 @@
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E10" s="9">
-        <v>492.2000122070312</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="F10" s="16">
-        <v>0.7604583534278073</v>
+        <v>0.8225450283211905</v>
       </c>
       <c r="G10" s="19">
-        <v>-0.1453667345878826</v>
+        <v>0.5236285305189845</v>
       </c>
       <c r="H10" s="19">
-        <v>-0.9104682528073633</v>
+        <v>-0.7870784679473629</v>
       </c>
       <c r="I10" s="19">
-        <v>2.981910484335923</v>
+        <v>2.35386274831343</v>
       </c>
       <c r="J10" s="19">
-        <v>2.396537587483633</v>
+        <v>1.789483576146954</v>
       </c>
       <c r="K10" s="19">
         <v>0</v>
       </c>
       <c r="L10" s="19">
-        <v>-2.518088402543813</v>
+        <v>0.3878895172023156</v>
       </c>
       <c r="M10" s="19">
-        <v>-0.3127842104323252</v>
+        <v>-0.4998209300844946</v>
       </c>
       <c r="N10" s="19">
-        <v>36.353783</v>
+        <v>13.92751</v>
       </c>
       <c r="O10" s="19">
-        <v>-210.92924</v>
+        <v>3.090377</v>
       </c>
       <c r="P10" s="11">
-        <v>0</v>
+        <v>0.23452999</v>
       </c>
       <c r="Q10" s="11">
-        <v>0.875</v>
+        <v>0.531</v>
       </c>
       <c r="R10" s="11">
-        <v>2.361922567269573</v>
+        <v>0.549328682023305</v>
       </c>
       <c r="S10" s="10">
-        <v>58.87163053312256</v>
+        <v>74.80836803387477</v>
       </c>
       <c r="T10" s="8" t="s">
         <v>79</v>
@@ -3657,10 +3657,10 @@
         <v>35</v>
       </c>
       <c r="E11" s="9">
-        <v>60.90999984741211</v>
+        <v>60.61000061035156</v>
       </c>
       <c r="F11" s="16">
-        <v>0.7233642665112766</v>
+        <v>0.7122464167182306</v>
       </c>
       <c r="G11" s="19">
         <v>0.6434300221411974</v>
@@ -3672,16 +3672,16 @@
         <v>3.205794473836218</v>
       </c>
       <c r="J11" s="19">
-        <v>0.3715659758044343</v>
+        <v>0.3163724894131534</v>
       </c>
       <c r="K11" s="19">
         <v>0</v>
       </c>
       <c r="L11" s="19">
-        <v>0.2605078313116728</v>
+        <v>0.256396592449407</v>
       </c>
       <c r="M11" s="19">
-        <v>-0.3201659155903314</v>
+        <v>-0.2324032601998362</v>
       </c>
       <c r="N11" s="19">
         <v>17.433628</v>
@@ -3696,10 +3696,10 @@
         <v>0.534</v>
       </c>
       <c r="R11" s="11">
-        <v>0.1468359858132189</v>
+        <v>0.1491183489601915</v>
       </c>
       <c r="S11" s="10">
-        <v>61.85983370642715</v>
+        <v>60.1098429319416</v>
       </c>
       <c r="T11" s="8" t="s">
         <v>79</v>
@@ -3719,10 +3719,10 @@
         <v>35</v>
       </c>
       <c r="E12" s="9">
-        <v>44.70000076293945</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="F12" s="16">
-        <v>0.7019116395441239</v>
+        <v>0.6604919692305173</v>
       </c>
       <c r="G12" s="19">
         <v>1.180775573424393</v>
@@ -3734,16 +3734,16 @@
         <v>-0.2826661582517923</v>
       </c>
       <c r="J12" s="19">
-        <v>1.351312871360071</v>
+        <v>1.198532566063069</v>
       </c>
       <c r="K12" s="19">
         <v>0</v>
       </c>
       <c r="L12" s="19">
-        <v>-0.345123101031329</v>
+        <v>-0.3494130941619076</v>
       </c>
       <c r="M12" s="19">
-        <v>-0.5165687165756384</v>
+        <v>-0.3960414503136171</v>
       </c>
       <c r="N12" s="19">
         <v>8.974684</v>
@@ -3758,10 +3758,10 @@
         <v>0.092</v>
       </c>
       <c r="R12" s="11">
-        <v>0.457103418912304</v>
+        <v>0.3832226512475525</v>
       </c>
       <c r="S12" s="10">
-        <v>68.72542126120932</v>
+        <v>65.50510746388605</v>
       </c>
       <c r="T12" s="8" t="s">
         <v>79</v>
@@ -3778,52 +3778,52 @@
         <v>87</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="E13" s="9">
-        <v>139.2700042724609</v>
+        <v>228.4499969482422</v>
       </c>
       <c r="F13" s="16">
-        <v>0.6304643230788479</v>
+        <v>0.6190043850656585</v>
       </c>
       <c r="G13" s="19">
-        <v>0.675065848973343</v>
+        <v>-1.186242168307697</v>
       </c>
       <c r="H13" s="19">
-        <v>0.2975919364127702</v>
+        <v>2.372350229473365</v>
       </c>
       <c r="I13" s="19">
-        <v>0.2786698223080728</v>
+        <v>2.41778901771408</v>
       </c>
       <c r="J13" s="19">
-        <v>1.143935467878596</v>
+        <v>0.4954986707638532</v>
       </c>
       <c r="K13" s="19">
         <v>0</v>
       </c>
       <c r="L13" s="19">
-        <v>0.06558912546416913</v>
+        <v>-0.2331905024658741</v>
       </c>
       <c r="M13" s="19">
-        <v>0.1337383943238131</v>
+        <v>0.02792924481018783</v>
       </c>
       <c r="N13" s="19">
-        <v>9.331602999999999</v>
+        <v>27.468435</v>
       </c>
       <c r="O13" s="19">
-        <v>3.3175094</v>
+        <v>26.95787</v>
       </c>
       <c r="P13" s="11">
-        <v>0.29867</v>
+        <v>1.17211</v>
       </c>
       <c r="Q13" s="11">
-        <v>0.176</v>
+        <v>1.059</v>
       </c>
       <c r="R13" s="11">
-        <v>0.3423656328946094</v>
+        <v>0.247565377881501</v>
       </c>
       <c r="S13" s="10">
-        <v>72.28906972208368</v>
+        <v>59.21125784086455</v>
       </c>
       <c r="T13" s="8" t="s">
         <v>79</v>
@@ -3834,58 +3834,58 @@
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="E14" s="9">
-        <v>224.4100036621094</v>
+        <v>137.8099975585938</v>
       </c>
       <c r="F14" s="16">
-        <v>0.5911817269551417</v>
+        <v>0.584786776563477</v>
       </c>
       <c r="G14" s="19">
-        <v>-1.186242168307697</v>
+        <v>0.675065848973343</v>
       </c>
       <c r="H14" s="19">
-        <v>2.372350229473365</v>
+        <v>0.2975919364127702</v>
       </c>
       <c r="I14" s="19">
-        <v>2.41778901771408</v>
+        <v>0.2786698223080728</v>
       </c>
       <c r="J14" s="19">
-        <v>0.4304429407463364</v>
+        <v>0.9669883100528082</v>
       </c>
       <c r="K14" s="19">
         <v>0</v>
       </c>
       <c r="L14" s="19">
-        <v>-0.2007041257071993</v>
+        <v>0.04429804333957792</v>
       </c>
       <c r="M14" s="19">
-        <v>-0.05852578940881459</v>
+        <v>0.3108055360948805</v>
       </c>
       <c r="N14" s="19">
-        <v>27.468435</v>
+        <v>9.331602999999999</v>
       </c>
       <c r="O14" s="19">
-        <v>26.95787</v>
+        <v>3.3175094</v>
       </c>
       <c r="P14" s="11">
-        <v>1.17211</v>
+        <v>0.29867</v>
       </c>
       <c r="Q14" s="11">
-        <v>1.059</v>
+        <v>0.176</v>
       </c>
       <c r="R14" s="11">
-        <v>0.2275115732316977</v>
+        <v>0.2555116292922723</v>
       </c>
       <c r="S14" s="10">
-        <v>56.67224745963074</v>
+        <v>69.24596705277986</v>
       </c>
       <c r="T14" s="8" t="s">
         <v>79</v>
@@ -3902,52 +3902,52 @@
         <v>92</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E15" s="9">
-        <v>211.7799987792969</v>
+        <v>264.4299926757812</v>
       </c>
       <c r="F15" s="16">
-        <v>0.5448258911546133</v>
+        <v>0.543637445697289</v>
       </c>
       <c r="G15" s="19">
-        <v>0.5556735680703294</v>
+        <v>0.3430645610428927</v>
       </c>
       <c r="H15" s="19">
-        <v>-0.3266206515441806</v>
+        <v>0.5388891445188714</v>
       </c>
       <c r="I15" s="19">
-        <v>2.258526107719387</v>
+        <v>0.1866157944506243</v>
       </c>
       <c r="J15" s="19">
-        <v>0.6874773333493751</v>
+        <v>1.258601383168031</v>
       </c>
       <c r="K15" s="19">
         <v>0</v>
       </c>
       <c r="L15" s="19">
-        <v>0.7604656555882482</v>
+        <v>-1.510741835120749</v>
       </c>
       <c r="M15" s="19">
-        <v>-0.5754862987697096</v>
+        <v>0.3103697976830926</v>
       </c>
       <c r="N15" s="19">
-        <v>19.409616</v>
+        <v>23.421774</v>
       </c>
       <c r="O15" s="19">
-        <v>2.0853305</v>
+        <v>5.4897923</v>
       </c>
       <c r="P15" s="11">
-        <v>0.12231</v>
+        <v>0.19381</v>
       </c>
       <c r="Q15" s="11">
-        <v>0.535</v>
+        <v>0.108</v>
       </c>
       <c r="R15" s="11">
-        <v>0.1588716860174963</v>
+        <v>0.319705720819198</v>
       </c>
       <c r="S15" s="10">
-        <v>72.25123940792997</v>
+        <v>81.88534917955489</v>
       </c>
       <c r="T15" s="8" t="s">
         <v>79</v>
@@ -3964,52 +3964,52 @@
         <v>94</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E16" s="9">
-        <v>148.9600067138672</v>
+        <v>31.32999992370605</v>
       </c>
       <c r="F16" s="16">
-        <v>0.5185873657889519</v>
+        <v>0.5362687222389461</v>
       </c>
       <c r="G16" s="19">
-        <v>0.6252746191907743</v>
+        <v>0.5167039359615127</v>
       </c>
       <c r="H16" s="19">
-        <v>0.4666043918108415</v>
+        <v>0.749645521027813</v>
       </c>
       <c r="I16" s="19">
-        <v>1.417737897842424</v>
+        <v>-0.1861321221296584</v>
       </c>
       <c r="J16" s="19">
-        <v>0.4305749224557138</v>
+        <v>0.9265400227747825</v>
       </c>
       <c r="K16" s="19">
         <v>0</v>
       </c>
       <c r="L16" s="19">
-        <v>0.2800257657120724</v>
+        <v>0.2349730161865551</v>
       </c>
       <c r="M16" s="19">
-        <v>-0.2324633089184651</v>
+        <v>-0.1810086482239009</v>
       </c>
       <c r="N16" s="19">
-        <v>11.1643305</v>
+        <v>17.827587</v>
       </c>
       <c r="O16" s="19">
-        <v>2.3641071</v>
+        <v>6.9959407</v>
       </c>
       <c r="P16" s="11">
-        <v>0.22507</v>
+        <v>0.41944</v>
       </c>
       <c r="Q16" s="11">
-        <v>0.587</v>
+        <v>0.063</v>
       </c>
       <c r="R16" s="11">
-        <v>0.1831533196186952</v>
+        <v>0.3992372741884209</v>
       </c>
       <c r="S16" s="10">
-        <v>57.55816691876135</v>
+        <v>67.86272603050911</v>
       </c>
       <c r="T16" s="8" t="s">
         <v>79</v>
@@ -4026,52 +4026,52 @@
         <v>96</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="E17" s="9">
-        <v>259.3399963378906</v>
+        <v>211.3200073242188</v>
       </c>
       <c r="F17" s="16">
-        <v>0.5179426725101998</v>
+        <v>0.5360062415062073</v>
       </c>
       <c r="G17" s="19">
-        <v>1.2973242005594</v>
+        <v>0.5556735680703294</v>
       </c>
       <c r="H17" s="19">
-        <v>0.1669261144304357</v>
+        <v>-0.3266206515441806</v>
       </c>
       <c r="I17" s="19">
-        <v>-0.05264739805840464</v>
+        <v>2.258526107719387</v>
       </c>
       <c r="J17" s="19">
-        <v>0.5784615411950941</v>
+        <v>0.6180842793555192</v>
       </c>
       <c r="K17" s="19">
         <v>0</v>
       </c>
       <c r="L17" s="19">
-        <v>0.5442547917265765</v>
+        <v>0.7675268653497733</v>
       </c>
       <c r="M17" s="19">
-        <v>-0.06707490821085271</v>
+        <v>-0.4175743997463604</v>
       </c>
       <c r="N17" s="19">
-        <v>5.156936</v>
+        <v>19.409616</v>
       </c>
       <c r="O17" s="19">
-        <v>2.0881312</v>
+        <v>2.0853305</v>
       </c>
       <c r="P17" s="11">
-        <v>0.46113998</v>
+        <v>0.12231</v>
       </c>
       <c r="Q17" s="11">
-        <v>0.118</v>
+        <v>0.535</v>
       </c>
       <c r="R17" s="11">
-        <v>0.222295520821145</v>
+        <v>0.1327891653244051</v>
       </c>
       <c r="S17" s="10">
-        <v>52.35633018652639</v>
+        <v>71.15177266523052</v>
       </c>
       <c r="T17" s="8" t="s">
         <v>79</v>
@@ -4082,58 +4082,58 @@
         <v>14</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="E18" s="9">
-        <v>30.64999961853027</v>
+        <v>263.1099853515625</v>
       </c>
       <c r="F18" s="16">
-        <v>0.5171483870908948</v>
+        <v>0.5354766167821089</v>
       </c>
       <c r="G18" s="19">
-        <v>0.5167039359615127</v>
+        <v>1.2973242005594</v>
       </c>
       <c r="H18" s="19">
-        <v>0.749645521027813</v>
+        <v>0.1669261144304357</v>
       </c>
       <c r="I18" s="19">
-        <v>-0.1861321221296584</v>
+        <v>-0.05264739805840464</v>
       </c>
       <c r="J18" s="19">
-        <v>0.8497776530755533</v>
+        <v>0.6397326606951861</v>
       </c>
       <c r="K18" s="19">
         <v>0</v>
       </c>
       <c r="L18" s="19">
-        <v>0.2080020638574881</v>
+        <v>0.5318849026018282</v>
       </c>
       <c r="M18" s="19">
-        <v>-0.08324523423355468</v>
+        <v>-0.09469080250163656</v>
       </c>
       <c r="N18" s="19">
-        <v>17.827587</v>
+        <v>5.156936</v>
       </c>
       <c r="O18" s="19">
-        <v>6.9959407</v>
+        <v>2.0881312</v>
       </c>
       <c r="P18" s="11">
-        <v>0.41944</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q18" s="11">
-        <v>0.063</v>
+        <v>0.118</v>
       </c>
       <c r="R18" s="11">
-        <v>0.3885193095313455</v>
+        <v>0.2550649904202462</v>
       </c>
       <c r="S18" s="10">
-        <v>64.50575807066566</v>
+        <v>56.20678625467898</v>
       </c>
       <c r="T18" s="8" t="s">
         <v>79</v>
@@ -4150,13 +4150,13 @@
         <v>101</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E19" s="9">
-        <v>216.6000061035156</v>
+        <v>220.5</v>
       </c>
       <c r="F19" s="16">
-        <v>0.5166314700640471</v>
+        <v>0.5301667783623812</v>
       </c>
       <c r="G19" s="19">
         <v>0.5887979504774438</v>
@@ -4168,16 +4168,16 @@
         <v>4.13232288715716</v>
       </c>
       <c r="J19" s="19">
-        <v>0.1354247803915279</v>
+        <v>0.1817393942043258</v>
       </c>
       <c r="K19" s="19">
         <v>0</v>
       </c>
       <c r="L19" s="19">
-        <v>0.4833436664336478</v>
+        <v>0.4713716083713511</v>
       </c>
       <c r="M19" s="19">
-        <v>-0.3633241117139414</v>
+        <v>-0.3791364786835358</v>
       </c>
       <c r="N19" s="19">
         <v>11.935252</v>
@@ -4192,10 +4192,10 @@
         <v>11.11</v>
       </c>
       <c r="R19" s="11">
-        <v>0.1147319427825668</v>
+        <v>0.1439157149200117</v>
       </c>
       <c r="S19" s="10">
-        <v>52.72760580486165</v>
+        <v>57.63682328411581</v>
       </c>
       <c r="T19" s="8" t="s">
         <v>79</v>
@@ -4212,52 +4212,52 @@
         <v>103</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="E20" s="9">
-        <v>128.8300018310547</v>
+        <v>54.43999862670898</v>
       </c>
       <c r="F20" s="16">
-        <v>0.5114883647696113</v>
+        <v>0.49042654637676</v>
       </c>
       <c r="G20" s="19">
-        <v>0.3535340411038917</v>
+        <v>0.2615753155071175</v>
       </c>
       <c r="H20" s="19">
-        <v>0.5066139843793523</v>
+        <v>-0.6923506737965556</v>
       </c>
       <c r="I20" s="19">
-        <v>0.5284153400344015</v>
+        <v>1.306361806653459</v>
       </c>
       <c r="J20" s="19">
-        <v>0.9615118482856677</v>
+        <v>1.658737154738667</v>
       </c>
       <c r="K20" s="19">
         <v>0</v>
       </c>
       <c r="L20" s="19">
-        <v>0.04043073902685233</v>
+        <v>-1.120023370164356</v>
       </c>
       <c r="M20" s="19">
-        <v>-0.4788192091611312</v>
+        <v>-0.8223501631170999</v>
       </c>
       <c r="N20" s="19">
-        <v>15.843312</v>
+        <v>48.887848</v>
       </c>
       <c r="O20" s="19">
-        <v>3.939749</v>
+        <v>2.7368805</v>
       </c>
       <c r="P20" s="11">
-        <v>0.30667</v>
+        <v>0.06315</v>
       </c>
       <c r="Q20" s="11">
-        <v>0.377</v>
+        <v>0.4</v>
       </c>
       <c r="R20" s="11">
-        <v>0.3031559886270625</v>
+        <v>1.559447382058317</v>
       </c>
       <c r="S20" s="10">
-        <v>61.44533411941921</v>
+        <v>55.42880778304845</v>
       </c>
       <c r="T20" s="8" t="s">
         <v>79</v>
@@ -4268,58 +4268,58 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="E21" s="9">
-        <v>67.66000366210938</v>
+        <v>444.1199951171875</v>
       </c>
       <c r="F21" s="16">
-        <v>0.5002042938157545</v>
+        <v>0.4833381289087343</v>
       </c>
       <c r="G21" s="19">
-        <v>0.4854005059534541</v>
+        <v>-0.2455671553299525</v>
       </c>
       <c r="H21" s="19">
-        <v>0.6587571460380149</v>
+        <v>1.23829401915366</v>
       </c>
       <c r="I21" s="19">
-        <v>0.2084671882916938</v>
+        <v>-0.09681434526753466</v>
       </c>
       <c r="J21" s="19">
-        <v>0.7659809326795566</v>
+        <v>1.029946458002858</v>
       </c>
       <c r="K21" s="19">
         <v>0</v>
       </c>
       <c r="L21" s="19">
-        <v>0.6130132210787556</v>
+        <v>0.6882223470186291</v>
       </c>
       <c r="M21" s="19">
-        <v>-0.5001905972200227</v>
+        <v>-0.8647905670091217</v>
       </c>
       <c r="N21" s="19">
-        <v>14.762749</v>
+        <v>26.875078</v>
       </c>
       <c r="O21" s="19">
-        <v>6.0942793</v>
+        <v>20.000925</v>
       </c>
       <c r="P21" s="11">
-        <v>0.46598998</v>
+        <v>0.91473</v>
       </c>
       <c r="Q21" s="11">
-        <v>0.057</v>
+        <v>0.095</v>
       </c>
       <c r="R21" s="11">
-        <v>0.1090852290335338</v>
+        <v>0.2243983060087957</v>
       </c>
       <c r="S21" s="10">
-        <v>62.54508994926787</v>
+        <v>69.25835886493431</v>
       </c>
       <c r="T21" s="8" t="s">
         <v>79</v>
@@ -4336,52 +4336,52 @@
         <v>108</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E22" s="9">
-        <v>442.8399963378906</v>
+        <v>68.08999633789062</v>
       </c>
       <c r="F22" s="16">
-        <v>0.4859140800627329</v>
+        <v>0.4832248803585137</v>
       </c>
       <c r="G22" s="19">
-        <v>-0.2455671553299525</v>
+        <v>0.4854005059534541</v>
       </c>
       <c r="H22" s="19">
-        <v>1.23829401915366</v>
+        <v>0.6587571460380149</v>
       </c>
       <c r="I22" s="19">
-        <v>-0.09681434526753466</v>
+        <v>0.2084671882916938</v>
       </c>
       <c r="J22" s="19">
-        <v>1.035701953736616</v>
+        <v>0.7203125045245805</v>
       </c>
       <c r="K22" s="19">
         <v>0</v>
       </c>
       <c r="L22" s="19">
-        <v>0.6909729879338106</v>
+        <v>0.6131778908486744</v>
       </c>
       <c r="M22" s="19">
-        <v>-0.8601011940031138</v>
+        <v>-0.51583104199595</v>
       </c>
       <c r="N22" s="19">
-        <v>26.875078</v>
+        <v>14.762749</v>
       </c>
       <c r="O22" s="19">
-        <v>20.000925</v>
+        <v>6.0942793</v>
       </c>
       <c r="P22" s="11">
-        <v>0.91473</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q22" s="11">
-        <v>0.095</v>
+        <v>0.057</v>
       </c>
       <c r="R22" s="11">
-        <v>0.1833037907929858</v>
+        <v>0.1453508763937028</v>
       </c>
       <c r="S22" s="10">
-        <v>68.67543648296927</v>
+        <v>64.11522972663477</v>
       </c>
       <c r="T22" s="8" t="s">
         <v>79</v>
@@ -4392,58 +4392,58 @@
         <v>19</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="E23" s="9">
-        <v>448.8999938964844</v>
+        <v>128</v>
       </c>
       <c r="F23" s="16">
-        <v>0.4825816595872763</v>
+        <v>0.4832058608189715</v>
       </c>
       <c r="G23" s="19">
-        <v>-0.9131978128854404</v>
+        <v>0.3535340411038917</v>
       </c>
       <c r="H23" s="19">
-        <v>2.151528876753073</v>
+        <v>0.5066139843793523</v>
       </c>
       <c r="I23" s="19">
-        <v>2.950282622072772</v>
+        <v>0.5284153400344015</v>
       </c>
       <c r="J23" s="19">
-        <v>0.3495729803700307</v>
+        <v>0.8371156233722191</v>
       </c>
       <c r="K23" s="19">
         <v>0</v>
       </c>
       <c r="L23" s="19">
-        <v>-3.480672299295953</v>
+        <v>0.0337884938204053</v>
       </c>
       <c r="M23" s="19">
-        <v>0.6717878514395186</v>
+        <v>-0.3184592252879027</v>
       </c>
       <c r="N23" s="19">
-        <v>17.067236</v>
+        <v>15.843312</v>
       </c>
       <c r="O23" s="19">
-        <v>21.967487</v>
+        <v>3.939749</v>
       </c>
       <c r="P23" s="11">
-        <v>1.30853</v>
+        <v>0.30667</v>
       </c>
       <c r="Q23" s="11">
-        <v>0.438</v>
+        <v>0.377</v>
       </c>
       <c r="R23" s="11">
-        <v>0.7192191727138222</v>
+        <v>0.3151135065442849</v>
       </c>
       <c r="S23" s="10">
-        <v>43.45616171029246</v>
+        <v>59.3507720158491</v>
       </c>
       <c r="T23" s="8" t="s">
         <v>79</v>
@@ -4454,58 +4454,58 @@
         <v>20</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="E24" s="9">
-        <v>308.0599975585938</v>
+        <v>145.9600067138672</v>
       </c>
       <c r="F24" s="16">
-        <v>0.4778747652284054</v>
+        <v>0.4705062578785462</v>
       </c>
       <c r="G24" s="19">
-        <v>0.02392519228507077</v>
+        <v>0.6252746191907743</v>
       </c>
       <c r="H24" s="19">
-        <v>1.208973468219964</v>
+        <v>0.4666043918108415</v>
       </c>
       <c r="I24" s="19">
-        <v>0.5934216790533486</v>
+        <v>1.417737897842424</v>
       </c>
       <c r="J24" s="19">
-        <v>0.9053653543455308</v>
+        <v>0.2296823911783533</v>
       </c>
       <c r="K24" s="19">
         <v>0</v>
       </c>
       <c r="L24" s="19">
-        <v>-0.5169390624607396</v>
+        <v>0.2656981466341822</v>
       </c>
       <c r="M24" s="19">
-        <v>-0.9643490823357488</v>
+        <v>0.00273721066559092</v>
       </c>
       <c r="N24" s="19">
-        <v>20.706474</v>
+        <v>11.1643305</v>
       </c>
       <c r="O24" s="19">
-        <v>32.69876</v>
+        <v>2.3641071</v>
       </c>
       <c r="P24" s="11">
-        <v>0.89489</v>
+        <v>0.22507</v>
       </c>
       <c r="Q24" s="11">
-        <v>0.14</v>
+        <v>0.587</v>
       </c>
       <c r="R24" s="11">
-        <v>0.3973292758292313</v>
+        <v>0.1309237881268333</v>
       </c>
       <c r="S24" s="10">
-        <v>48.32045969975</v>
+        <v>51.94029594588791</v>
       </c>
       <c r="T24" s="8" t="s">
         <v>79</v>
@@ -4516,58 +4516,58 @@
         <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="9">
-        <v>31.98999977111816</v>
+        <v>441.5700073242188</v>
       </c>
       <c r="F25" s="16">
-        <v>0.4763138349660302</v>
+        <v>0.4614970867785175</v>
       </c>
       <c r="G25" s="19">
-        <v>1.18884239126269</v>
+        <v>-0.9131978128854404</v>
       </c>
       <c r="H25" s="19">
-        <v>-0.9872240870343698</v>
+        <v>2.151528876753073</v>
       </c>
       <c r="I25" s="19">
-        <v>-0.3680930717051557</v>
+        <v>2.950282622072772</v>
       </c>
       <c r="J25" s="19">
-        <v>1.514778561567294</v>
+        <v>0.2574142492199353</v>
       </c>
       <c r="K25" s="19">
         <v>0</v>
       </c>
       <c r="L25" s="19">
-        <v>-0.4257128312669795</v>
+        <v>-3.395096428765233</v>
       </c>
       <c r="M25" s="19">
-        <v>-0.362013664441654</v>
+        <v>0.72127088945799</v>
       </c>
       <c r="N25" s="19">
-        <v>11.648855</v>
+        <v>17.067236</v>
       </c>
       <c r="O25" s="19">
-        <v>-305.2</v>
+        <v>21.967487</v>
       </c>
       <c r="P25" s="11">
-        <v>0</v>
+        <v>1.30853</v>
       </c>
       <c r="Q25" s="11">
-        <v>0.125</v>
+        <v>0.438</v>
       </c>
       <c r="R25" s="11">
-        <v>0.7155810235893794</v>
+        <v>0.7051504280798611</v>
       </c>
       <c r="S25" s="10">
-        <v>64.26562172929734</v>
+        <v>42.08722721617787</v>
       </c>
       <c r="T25" s="8" t="s">
         <v>79</v>
@@ -4578,58 +4578,58 @@
         <v>22</v>
       </c>
       <c r="B26" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>115</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="9">
-        <v>256.9299926757812</v>
+        <v>31.93000030517578</v>
       </c>
       <c r="F26" s="16">
-        <v>0.4752744061075088</v>
+        <v>0.4576307130440425</v>
       </c>
       <c r="G26" s="19">
-        <v>0.3430645610428927</v>
+        <v>1.18884239126269</v>
       </c>
       <c r="H26" s="19">
-        <v>0.5388891445188714</v>
+        <v>-0.9872240870343698</v>
       </c>
       <c r="I26" s="19">
-        <v>0.1866157944506243</v>
+        <v>-0.3680930717051557</v>
       </c>
       <c r="J26" s="19">
-        <v>1.102017236520169</v>
+        <v>1.42639422344022</v>
       </c>
       <c r="K26" s="19">
         <v>0</v>
       </c>
       <c r="L26" s="19">
-        <v>-1.494970478052512</v>
+        <v>-0.4418203815632671</v>
       </c>
       <c r="M26" s="19">
-        <v>0.1337383943238131</v>
+        <v>-0.2240060748847778</v>
       </c>
       <c r="N26" s="19">
-        <v>23.421774</v>
+        <v>11.648855</v>
       </c>
       <c r="O26" s="19">
-        <v>5.4897923</v>
+        <v>-305.2</v>
       </c>
       <c r="P26" s="11">
-        <v>0.19381</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="11">
-        <v>0.108</v>
+        <v>0.125</v>
       </c>
       <c r="R26" s="11">
-        <v>0.3374629754806138</v>
+        <v>0.6981970754782727</v>
       </c>
       <c r="S26" s="10">
-        <v>80.05314094364982</v>
+        <v>63.88363492779357</v>
       </c>
       <c r="T26" s="8" t="s">
         <v>79</v>
@@ -4640,58 +4640,58 @@
         <v>23</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>117</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="E27" s="9">
-        <v>69.55999755859375</v>
+        <v>110.379997253418</v>
       </c>
       <c r="F27" s="16">
-        <v>0.4514107542190169</v>
+        <v>0.4452452748984544</v>
       </c>
       <c r="G27" s="19">
-        <v>0.548854665636462</v>
+        <v>0.08240686126983239</v>
       </c>
       <c r="H27" s="19">
-        <v>1.843831358372849</v>
+        <v>1.223451927469628</v>
       </c>
       <c r="I27" s="19">
-        <v>-0.6292233998564639</v>
+        <v>0.1038485795344242</v>
       </c>
       <c r="J27" s="19">
-        <v>-0.0504008928679656</v>
+        <v>0.5337230787752398</v>
       </c>
       <c r="K27" s="19">
         <v>0</v>
       </c>
       <c r="L27" s="19">
-        <v>0.397520003399692</v>
+        <v>0.9079671065661551</v>
       </c>
       <c r="M27" s="19">
-        <v>0.72032517750713</v>
+        <v>-0.5468688686631755</v>
       </c>
       <c r="N27" s="19">
-        <v>14.242739</v>
+        <v>20.065575</v>
       </c>
       <c r="O27" s="19">
-        <v>-42.95995</v>
+        <v>4.333084</v>
       </c>
       <c r="P27" s="11">
-        <v>0</v>
+        <v>0.20273</v>
       </c>
       <c r="Q27" s="11">
-        <v>0.012</v>
+        <v>0.209</v>
       </c>
       <c r="R27" s="11">
-        <v>0.05377649259040207</v>
+        <v>0.1644386069387782</v>
       </c>
       <c r="S27" s="10">
-        <v>54.95712479213294</v>
+        <v>57.12606159485828</v>
       </c>
       <c r="T27" s="8" t="s">
         <v>79</v>
@@ -4702,58 +4702,58 @@
         <v>24</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="E28" s="9">
-        <v>137.1999969482422</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="F28" s="16">
-        <v>0.4450241713023743</v>
+        <v>0.4401995672260049</v>
       </c>
       <c r="G28" s="19">
-        <v>0.5373664552081702</v>
+        <v>0.548854665636462</v>
       </c>
       <c r="H28" s="19">
-        <v>-0.1368691777673517</v>
+        <v>1.843831358372849</v>
       </c>
       <c r="I28" s="19">
-        <v>0.7891918304603867</v>
+        <v>-0.6292233998564639</v>
       </c>
       <c r="J28" s="19">
-        <v>0.874868710458875</v>
+        <v>-0.08596026844392872</v>
       </c>
       <c r="K28" s="19">
         <v>0</v>
       </c>
       <c r="L28" s="19">
-        <v>0.409266950255782</v>
+        <v>0.3862610758512713</v>
       </c>
       <c r="M28" s="19">
-        <v>-0.6142679493456635</v>
+        <v>0.7387939746551748</v>
       </c>
       <c r="N28" s="19">
-        <v>17.128778</v>
+        <v>14.242739</v>
       </c>
       <c r="O28" s="19">
-        <v>2.396272</v>
+        <v>-42.95995</v>
       </c>
       <c r="P28" s="11">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="11">
-        <v>0.355</v>
+        <v>0.012</v>
       </c>
       <c r="R28" s="11">
-        <v>0.2031260401361856</v>
+        <v>0.07063313654538406</v>
       </c>
       <c r="S28" s="10">
-        <v>71.23451314922767</v>
+        <v>54.64728349859463</v>
       </c>
       <c r="T28" s="8" t="s">
         <v>79</v>
@@ -4764,58 +4764,58 @@
         <v>25</v>
       </c>
       <c r="B29" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>122</v>
-      </c>
       <c r="D29" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E29" s="9">
-        <v>400.9700012207031</v>
+        <v>374.3399963378906</v>
       </c>
       <c r="F29" s="16">
-        <v>0.4356891888260966</v>
+        <v>0.4336293186020755</v>
       </c>
       <c r="G29" s="19">
-        <v>0.3991025813752035</v>
+        <v>1.231904824551268</v>
       </c>
       <c r="H29" s="19">
-        <v>-1.053340414218987</v>
+        <v>-0.1202756231839317</v>
       </c>
       <c r="I29" s="19">
-        <v>0.1734891100083233</v>
+        <v>-0.3776219198070676</v>
       </c>
       <c r="J29" s="19">
-        <v>1.48054786406749</v>
+        <v>0.6703541045779463</v>
       </c>
       <c r="K29" s="19">
         <v>0</v>
       </c>
       <c r="L29" s="19">
-        <v>0.2316131799363454</v>
+        <v>0.6292544865051857</v>
       </c>
       <c r="M29" s="19">
-        <v>0.05865533471507733</v>
+        <v>-0.2750534615370114</v>
       </c>
       <c r="N29" s="19">
-        <v>37.178402</v>
+        <v>9.919549</v>
       </c>
       <c r="O29" s="19">
-        <v>2.4096098</v>
+        <v>2.3296678</v>
       </c>
       <c r="P29" s="11">
-        <v>0.06893000000000001</v>
+        <v>0.26511</v>
       </c>
       <c r="Q29" s="11">
-        <v>0.262</v>
+        <v>0.003</v>
       </c>
       <c r="R29" s="11">
-        <v>1.206090640558684</v>
+        <v>0.230347412622764</v>
       </c>
       <c r="S29" s="10">
-        <v>60.64847724016542</v>
+        <v>57.44783949717321</v>
       </c>
       <c r="T29" s="8" t="s">
         <v>79</v>
@@ -4826,58 +4826,58 @@
         <v>26</v>
       </c>
       <c r="B30" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>124</v>
-      </c>
       <c r="D30" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E30" s="9">
-        <v>108.2399978637695</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="F30" s="16">
-        <v>0.4328159921505382</v>
+        <v>0.4300012041604963</v>
       </c>
       <c r="G30" s="19">
-        <v>0.08240686126983239</v>
+        <v>0.3599630250019414</v>
       </c>
       <c r="H30" s="19">
-        <v>1.223451927469628</v>
+        <v>0.7749817441404762</v>
       </c>
       <c r="I30" s="19">
-        <v>0.1038485795344242</v>
+        <v>0.3840583979359316</v>
       </c>
       <c r="J30" s="19">
-        <v>0.4530655684743485</v>
+        <v>0.3792927746977155</v>
       </c>
       <c r="K30" s="19">
         <v>0</v>
       </c>
       <c r="L30" s="19">
-        <v>0.9225964599732468</v>
+        <v>0.5455498476553341</v>
       </c>
       <c r="M30" s="19">
-        <v>-0.3920973303172309</v>
+        <v>0.05854966295229103</v>
       </c>
       <c r="N30" s="19">
-        <v>20.065575</v>
+        <v>17.362167</v>
       </c>
       <c r="O30" s="19">
-        <v>4.333084</v>
+        <v>3.1676524</v>
       </c>
       <c r="P30" s="11">
-        <v>0.20273</v>
+        <v>0.17969999</v>
       </c>
       <c r="Q30" s="11">
-        <v>0.209</v>
+        <v>0.28</v>
       </c>
       <c r="R30" s="11">
-        <v>0.1343726127753508</v>
+        <v>0.3504690914008213</v>
       </c>
       <c r="S30" s="10">
-        <v>51.10883440310246</v>
+        <v>54.21802398370298</v>
       </c>
       <c r="T30" s="8" t="s">
         <v>79</v>
@@ -4888,19 +4888,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>126</v>
-      </c>
       <c r="D31" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E31" s="9">
-        <v>416.3999938964844</v>
+        <v>419.6799926757812</v>
       </c>
       <c r="F31" s="16">
-        <v>0.419765462100207</v>
+        <v>0.4270850220369272</v>
       </c>
       <c r="G31" s="19">
         <v>0.3076356686141632</v>
@@ -4912,16 +4912,16 @@
         <v>-0.1087365036626361</v>
       </c>
       <c r="J31" s="19">
-        <v>0.7865362960034815</v>
+        <v>0.7850600293686364</v>
       </c>
       <c r="K31" s="19">
         <v>0</v>
       </c>
       <c r="L31" s="19">
-        <v>0.5481412098436849</v>
+        <v>0.561317058950534</v>
       </c>
       <c r="M31" s="19">
-        <v>-0.7126080892074118</v>
+        <v>-0.6364388168529574</v>
       </c>
       <c r="N31" s="19">
         <v>24.571085</v>
@@ -4936,10 +4936,10 @@
         <v>0.215</v>
       </c>
       <c r="R31" s="11">
-        <v>0.2667315415860951</v>
+        <v>0.2939907194867726</v>
       </c>
       <c r="S31" s="10">
-        <v>61.90938978534076</v>
+        <v>63.68201036499497</v>
       </c>
       <c r="T31" s="8" t="s">
         <v>79</v>
@@ -4950,58 +4950,58 @@
         <v>28</v>
       </c>
       <c r="B32" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>128</v>
-      </c>
       <c r="D32" s="8" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E32" s="9">
-        <v>366.1799926757812</v>
+        <v>406.5199890136719</v>
       </c>
       <c r="F32" s="16">
-        <v>0.4149095330293299</v>
+        <v>0.4247911211216426</v>
       </c>
       <c r="G32" s="19">
-        <v>1.231904824551268</v>
+        <v>0.3991025813752035</v>
       </c>
       <c r="H32" s="19">
-        <v>-0.1202756231839317</v>
+        <v>-1.053340414218987</v>
       </c>
       <c r="I32" s="19">
-        <v>-0.3776219198070676</v>
+        <v>0.1734891100083233</v>
       </c>
       <c r="J32" s="19">
-        <v>0.5603372351080521</v>
+        <v>1.44350560522266</v>
       </c>
       <c r="K32" s="19">
         <v>0</v>
       </c>
       <c r="L32" s="19">
-        <v>0.6491125414395538</v>
+        <v>0.2236719889698772</v>
       </c>
       <c r="M32" s="19">
-        <v>-0.08330138352588624</v>
+        <v>0.08364095385904868</v>
       </c>
       <c r="N32" s="19">
-        <v>9.919549</v>
+        <v>37.178402</v>
       </c>
       <c r="O32" s="19">
-        <v>2.3296678</v>
+        <v>2.4096098</v>
       </c>
       <c r="P32" s="11">
-        <v>0.26511</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="Q32" s="11">
-        <v>0.003</v>
+        <v>0.262</v>
       </c>
       <c r="R32" s="11">
-        <v>0.1827381341379786</v>
+        <v>1.265828964263924</v>
       </c>
       <c r="S32" s="10">
-        <v>49.33096379585528</v>
+        <v>63.34257820380893</v>
       </c>
       <c r="T32" s="8" t="s">
         <v>79</v>
@@ -5012,58 +5012,58 @@
         <v>29</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>130</v>
-      </c>
       <c r="D33" s="8" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="E33" s="9">
-        <v>211.8200073242188</v>
+        <v>135.7200012207031</v>
       </c>
       <c r="F33" s="16">
-        <v>0.4137821958984472</v>
+        <v>0.4158460545588797</v>
       </c>
       <c r="G33" s="19">
-        <v>0.3599630250019414</v>
+        <v>0.5373664552081702</v>
       </c>
       <c r="H33" s="19">
-        <v>0.7749817441404762</v>
+        <v>-0.1368691777673517</v>
       </c>
       <c r="I33" s="19">
-        <v>0.3840583979359316</v>
+        <v>0.7891918304603867</v>
       </c>
       <c r="J33" s="19">
-        <v>0.2687539181760084</v>
+        <v>0.7453018718502976</v>
       </c>
       <c r="K33" s="19">
         <v>0</v>
       </c>
       <c r="L33" s="19">
-        <v>0.5771374472344977</v>
+        <v>0.4076272251414</v>
       </c>
       <c r="M33" s="19">
-        <v>0.2709705843417799</v>
+        <v>-0.4481217949061517</v>
       </c>
       <c r="N33" s="19">
-        <v>17.362167</v>
+        <v>17.128778</v>
       </c>
       <c r="O33" s="19">
-        <v>3.1676524</v>
+        <v>2.396272</v>
       </c>
       <c r="P33" s="11">
-        <v>0.17969999</v>
+        <v>0.1418</v>
       </c>
       <c r="Q33" s="11">
-        <v>0.28</v>
+        <v>0.355</v>
       </c>
       <c r="R33" s="11">
-        <v>0.2777814903404947</v>
+        <v>0.1782278866003417</v>
       </c>
       <c r="S33" s="10">
-        <v>46.0876912234934</v>
+        <v>67.09918319483521</v>
       </c>
       <c r="T33" s="8" t="s">
         <v>79</v>
@@ -5074,58 +5074,58 @@
         <v>30</v>
       </c>
       <c r="B34" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>132</v>
-      </c>
       <c r="D34" s="8" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="E34" s="9">
-        <v>163.3600006103516</v>
+        <v>130.4299926757812</v>
       </c>
       <c r="F34" s="16">
-        <v>0.4117207469139126</v>
+        <v>0.4094360258655916</v>
       </c>
       <c r="G34" s="19">
-        <v>0.5037681831878469</v>
+        <v>0.4650459712359196</v>
       </c>
       <c r="H34" s="19">
-        <v>-0.5575001867977641</v>
+        <v>0.7834803576664174</v>
       </c>
       <c r="I34" s="19">
-        <v>-0.04455757815619896</v>
+        <v>-0.1942913639709165</v>
       </c>
       <c r="J34" s="19">
-        <v>1.304179366951732</v>
+        <v>0.9519709426180053</v>
       </c>
       <c r="K34" s="19">
         <v>0</v>
       </c>
       <c r="L34" s="19">
-        <v>0.2576047119474864</v>
+        <v>-0.6910662054927256</v>
       </c>
       <c r="M34" s="19">
-        <v>-0.5177290098584503</v>
+        <v>-0.9182450418264765</v>
       </c>
       <c r="N34" s="19">
-        <v>16.927385</v>
+        <v>16.68579</v>
       </c>
       <c r="O34" s="19">
-        <v>4.154594</v>
+        <v>3.8455532</v>
       </c>
       <c r="P34" s="11">
-        <v>0.26408002</v>
+        <v>0.25905</v>
       </c>
       <c r="Q34" s="11">
-        <v>0.053</v>
+        <v>0.151</v>
       </c>
       <c r="R34" s="11">
-        <v>0.3838203844749419</v>
+        <v>0.1284924859889978</v>
       </c>
       <c r="S34" s="10">
-        <v>62.36549568058859</v>
+        <v>64.26590158726938</v>
       </c>
       <c r="T34" s="8" t="s">
         <v>79</v>
@@ -5136,58 +5136,58 @@
         <v>31</v>
       </c>
       <c r="B35" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>134</v>
-      </c>
       <c r="D35" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E35" s="9">
-        <v>588.1400146484375</v>
+        <v>181.1000061035156</v>
       </c>
       <c r="F35" s="16">
-        <v>0.4041815876042349</v>
+        <v>0.405690274997047</v>
       </c>
       <c r="G35" s="19">
-        <v>-1.47114938458048</v>
+        <v>0.5392511670723198</v>
       </c>
       <c r="H35" s="19">
-        <v>2.900487942036482</v>
+        <v>0.5664211651255424</v>
       </c>
       <c r="I35" s="19">
-        <v>-0.1716020620831971</v>
+        <v>-0.05328793731108517</v>
       </c>
       <c r="J35" s="19">
-        <v>0.4759953389096645</v>
+        <v>0.4998071918563494</v>
       </c>
       <c r="K35" s="19">
         <v>0</v>
       </c>
       <c r="L35" s="19">
-        <v>0.9848097239858471</v>
+        <v>0.873085393458726</v>
       </c>
       <c r="M35" s="19">
-        <v>-0.3539795414169304</v>
+        <v>-0.3460455241127865</v>
       </c>
       <c r="N35" s="19">
-        <v>32.565643</v>
+        <v>15.65096</v>
       </c>
       <c r="O35" s="19">
-        <v>93.07380000000001</v>
+        <v>2.7135465</v>
       </c>
       <c r="P35" s="11">
-        <v>2.41202</v>
+        <v>0.18416001</v>
       </c>
       <c r="Q35" s="11">
-        <v>0.141</v>
+        <v>0.151</v>
       </c>
       <c r="R35" s="11">
-        <v>0.128544207361706</v>
+        <v>0.1671524323456808</v>
       </c>
       <c r="S35" s="10">
-        <v>59.5727516235745</v>
+        <v>59.09020511064618</v>
       </c>
       <c r="T35" s="8" t="s">
         <v>79</v>
@@ -5198,58 +5198,58 @@
         <v>32</v>
       </c>
       <c r="B36" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>136</v>
-      </c>
       <c r="D36" s="8" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="E36" s="9">
-        <v>51.83000183105469</v>
+        <v>164.0099945068359</v>
       </c>
       <c r="F36" s="16">
-        <v>0.4032403155004064</v>
+        <v>0.4032567490268172</v>
       </c>
       <c r="G36" s="19">
-        <v>0.2615753155071175</v>
+        <v>0.5037681831878469</v>
       </c>
       <c r="H36" s="19">
-        <v>-0.6923506737965556</v>
+        <v>-0.5575001867977641</v>
       </c>
       <c r="I36" s="19">
-        <v>1.306361806653459</v>
+        <v>-0.04455757815619896</v>
       </c>
       <c r="J36" s="19">
-        <v>1.412991322463866</v>
+        <v>1.299702285695977</v>
       </c>
       <c r="K36" s="19">
         <v>0</v>
       </c>
       <c r="L36" s="19">
-        <v>-1.049236405032552</v>
+        <v>0.2535223080998597</v>
       </c>
       <c r="M36" s="19">
-        <v>-0.9129420555753399</v>
+        <v>-0.590982129021698</v>
       </c>
       <c r="N36" s="19">
-        <v>48.887848</v>
+        <v>16.927385</v>
       </c>
       <c r="O36" s="19">
-        <v>2.7368805</v>
+        <v>4.154594</v>
       </c>
       <c r="P36" s="11">
-        <v>0.06315</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q36" s="11">
-        <v>0.4</v>
+        <v>0.053</v>
       </c>
       <c r="R36" s="11">
-        <v>1.427694779506832</v>
+        <v>0.386094384404541</v>
       </c>
       <c r="S36" s="10">
-        <v>48.46609615670043</v>
+        <v>63.10023823244421</v>
       </c>
       <c r="T36" s="8" t="s">
         <v>79</v>
@@ -5260,58 +5260,58 @@
         <v>33</v>
       </c>
       <c r="B37" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="D37" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="E37" s="9">
-        <v>203.4199981689453</v>
+        <v>303.1400146484375</v>
       </c>
       <c r="F37" s="16">
-        <v>0.3977320246501523</v>
+        <v>0.402421043342234</v>
       </c>
       <c r="G37" s="19">
-        <v>0.6290781538187236</v>
+        <v>0.02392519228507077</v>
       </c>
       <c r="H37" s="19">
-        <v>-0.04474182683940042</v>
+        <v>1.208973468219964</v>
       </c>
       <c r="I37" s="19">
-        <v>1.575737480795989</v>
+        <v>0.5934216790533486</v>
       </c>
       <c r="J37" s="19">
-        <v>0.2972580080248712</v>
+        <v>0.6521282660827318</v>
       </c>
       <c r="K37" s="19">
         <v>0</v>
       </c>
       <c r="L37" s="19">
-        <v>0.2977503289166116</v>
+        <v>-0.5521858643013574</v>
       </c>
       <c r="M37" s="19">
-        <v>-0.2585920490373644</v>
+        <v>-0.8182658407176738</v>
       </c>
       <c r="N37" s="19">
-        <v>37.579845</v>
+        <v>20.706474</v>
       </c>
       <c r="O37" s="19">
-        <v>1.4633226</v>
+        <v>32.69876</v>
       </c>
       <c r="P37" s="11">
-        <v>0.034930002</v>
+        <v>0.89489</v>
       </c>
       <c r="Q37" s="11">
-        <v>0.525</v>
+        <v>0.14</v>
       </c>
       <c r="R37" s="11">
-        <v>0.1708141956994578</v>
+        <v>0.209436149389282</v>
       </c>
       <c r="S37" s="10">
-        <v>54.59967056168442</v>
+        <v>45.98181817729859</v>
       </c>
       <c r="T37" s="8" t="s">
         <v>79</v>
@@ -5328,52 +5328,52 @@
         <v>140</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="E38" s="9">
-        <v>412.2000122070312</v>
+        <v>202.9400024414062</v>
       </c>
       <c r="F38" s="16">
-        <v>0.388489739750225</v>
+        <v>0.3966299638882795</v>
       </c>
       <c r="G38" s="19">
-        <v>-0.9759620955182193</v>
+        <v>0.6290781538187236</v>
       </c>
       <c r="H38" s="19">
-        <v>-0.4326356610429035</v>
+        <v>-0.04474182683940042</v>
       </c>
       <c r="I38" s="19">
-        <v>4.13232288715716</v>
+        <v>1.575737480795989</v>
       </c>
       <c r="J38" s="19">
-        <v>0.5407414873788275</v>
+        <v>0.2682137398810511</v>
       </c>
       <c r="K38" s="19">
         <v>0</v>
       </c>
       <c r="L38" s="19">
-        <v>0.6557006232771234</v>
+        <v>0.3009504622692691</v>
       </c>
       <c r="M38" s="19">
-        <v>-0.3503864798206195</v>
+        <v>-0.1641988118931329</v>
       </c>
       <c r="N38" s="19">
-        <v>105.25127</v>
+        <v>37.579845</v>
       </c>
       <c r="O38" s="19">
-        <v>2.680677</v>
+        <v>1.4633226</v>
       </c>
       <c r="P38" s="11">
-        <v>0.019199999</v>
+        <v>0.034930002</v>
       </c>
       <c r="Q38" s="11">
-        <v>1.134</v>
+        <v>0.525</v>
       </c>
       <c r="R38" s="11">
-        <v>0.2920010066668242</v>
+        <v>0.1460006359070336</v>
       </c>
       <c r="S38" s="10">
-        <v>56.16483519470556</v>
+        <v>53.89333865908142</v>
       </c>
       <c r="T38" s="8" t="s">
         <v>79</v>
@@ -5390,52 +5390,52 @@
         <v>142</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="E39" s="9">
-        <v>378.3999938964844</v>
+        <v>185.3800048828125</v>
       </c>
       <c r="F39" s="16">
-        <v>0.3875455404815684</v>
+        <v>0.3931585423585983</v>
       </c>
       <c r="G39" s="19">
-        <v>-0.8622441204646991</v>
+        <v>-0.4206222377761193</v>
       </c>
       <c r="H39" s="19">
-        <v>1.971798251919513</v>
+        <v>1.258828701477971</v>
       </c>
       <c r="I39" s="19">
-        <v>-0.2184519826388571</v>
+        <v>-0.2081970290549548</v>
       </c>
       <c r="J39" s="19">
-        <v>0.5102721661937776</v>
+        <v>1.067630824148595</v>
       </c>
       <c r="K39" s="19">
         <v>0</v>
       </c>
       <c r="L39" s="19">
-        <v>1.071968338729742</v>
+        <v>-0.1154055247936974</v>
       </c>
       <c r="M39" s="19">
-        <v>-0.1849781864716033</v>
+        <v>-0.9033285626583551</v>
       </c>
       <c r="N39" s="19">
-        <v>32.476597</v>
+        <v>29.498423</v>
       </c>
       <c r="O39" s="19">
-        <v>20.222574</v>
+        <v>27.131872</v>
       </c>
       <c r="P39" s="11">
-        <v>0.6119</v>
+        <v>1.06734</v>
       </c>
       <c r="Q39" s="11">
-        <v>0.144</v>
+        <v>0.125</v>
       </c>
       <c r="R39" s="11">
-        <v>0.1854116881790868</v>
+        <v>0.8303346425879521</v>
       </c>
       <c r="S39" s="10">
-        <v>59.27960086317145</v>
+        <v>48.84149765570163</v>
       </c>
       <c r="T39" s="8" t="s">
         <v>79</v>
@@ -5452,52 +5452,52 @@
         <v>144</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E40" s="9">
-        <v>175.9499969482422</v>
+        <v>413.5599975585938</v>
       </c>
       <c r="F40" s="16">
-        <v>0.3791591078612157</v>
+        <v>0.3930533377988483</v>
       </c>
       <c r="G40" s="19">
-        <v>0.5392511670723198</v>
+        <v>-0.9759620955182193</v>
       </c>
       <c r="H40" s="19">
-        <v>0.5664211651255424</v>
+        <v>-0.4326356610429035</v>
       </c>
       <c r="I40" s="19">
-        <v>-0.05328793731108517</v>
+        <v>4.13232288715716</v>
       </c>
       <c r="J40" s="19">
-        <v>0.3732993523946713</v>
+        <v>0.5534051801728491</v>
       </c>
       <c r="K40" s="19">
         <v>0</v>
       </c>
       <c r="L40" s="19">
-        <v>0.9118133589160312</v>
+        <v>0.6676336834985049</v>
       </c>
       <c r="M40" s="19">
-        <v>-0.1925299387186166</v>
+        <v>-0.3566255444293814</v>
       </c>
       <c r="N40" s="19">
-        <v>15.65096</v>
+        <v>105.25127</v>
       </c>
       <c r="O40" s="19">
-        <v>2.7135465</v>
+        <v>2.680677</v>
       </c>
       <c r="P40" s="11">
-        <v>0.18416001</v>
+        <v>0.019199999</v>
       </c>
       <c r="Q40" s="11">
-        <v>0.151</v>
+        <v>1.134</v>
       </c>
       <c r="R40" s="11">
-        <v>0.1352691192331681</v>
+        <v>0.3104344318817072</v>
       </c>
       <c r="S40" s="10">
-        <v>51.14659916775605</v>
+        <v>57.00968180801394</v>
       </c>
       <c r="T40" s="8" t="s">
         <v>79</v>
@@ -5514,52 +5514,52 @@
         <v>146</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="E41" s="9">
-        <v>180.7700042724609</v>
+        <v>1037.930053710938</v>
       </c>
       <c r="F41" s="16">
-        <v>0.3701015955490788</v>
+        <v>0.3886622531696047</v>
       </c>
       <c r="G41" s="19">
-        <v>-0.4206222377761193</v>
+        <v>0.3744813910308467</v>
       </c>
       <c r="H41" s="19">
-        <v>1.258828701477971</v>
+        <v>0.8243277724214527</v>
       </c>
       <c r="I41" s="19">
-        <v>-0.2081970290549548</v>
+        <v>0.9077656154464111</v>
       </c>
       <c r="J41" s="19">
-        <v>0.9688113260597638</v>
+        <v>0.120800172287495</v>
       </c>
       <c r="K41" s="19">
         <v>0</v>
       </c>
       <c r="L41" s="19">
-        <v>-0.1106491049776869</v>
+        <v>0.0537666496266404</v>
       </c>
       <c r="M41" s="19">
-        <v>-0.7899491745919611</v>
+        <v>0.1560134575972423</v>
       </c>
       <c r="N41" s="19">
-        <v>29.498423</v>
+        <v>16.078215</v>
       </c>
       <c r="O41" s="19">
-        <v>27.131872</v>
+        <v>2.8559394</v>
       </c>
       <c r="P41" s="11">
-        <v>1.06734</v>
+        <v>0.16902</v>
       </c>
       <c r="Q41" s="11">
-        <v>0.125</v>
+        <v>0.425</v>
       </c>
       <c r="R41" s="11">
-        <v>0.830715983068075</v>
+        <v>0.2539321965285313</v>
       </c>
       <c r="S41" s="10">
-        <v>43.33101264507649</v>
+        <v>51.8526422709828</v>
       </c>
       <c r="T41" s="8" t="s">
         <v>79</v>
@@ -5576,52 +5576,52 @@
         <v>148</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E42" s="9">
-        <v>93.5</v>
+        <v>123.1999969482422</v>
       </c>
       <c r="F42" s="16">
-        <v>0.3672375055603321</v>
+        <v>0.3820064860684569</v>
       </c>
       <c r="G42" s="19">
-        <v>0.1323994869339421</v>
+        <v>1.209509024402304</v>
       </c>
       <c r="H42" s="19">
-        <v>1.644369932284167</v>
+        <v>-0.6462119162778616</v>
       </c>
       <c r="I42" s="19">
-        <v>0.03944887499304424</v>
+        <v>0.1375917264421193</v>
       </c>
       <c r="J42" s="19">
-        <v>0.1364811945313736</v>
+        <v>0.6034880162094983</v>
       </c>
       <c r="K42" s="19">
         <v>0</v>
       </c>
       <c r="L42" s="19">
-        <v>0.3813605071284529</v>
+        <v>1.078015044136419</v>
       </c>
       <c r="M42" s="19">
-        <v>-0.3941621025863461</v>
+        <v>-0.4704811275370145</v>
       </c>
       <c r="N42" s="19">
-        <v>16.766905</v>
+        <v>10.860381</v>
       </c>
       <c r="O42" s="19">
-        <v>18.876202</v>
+        <v>1.3095953</v>
       </c>
       <c r="P42" s="11">
-        <v>1.5956</v>
+        <v>0.12011</v>
       </c>
       <c r="Q42" s="11">
-        <v>0.162</v>
+        <v>0.141</v>
       </c>
       <c r="R42" s="11">
-        <v>-0.02220638562540544</v>
+        <v>0.2741657852304562</v>
       </c>
       <c r="S42" s="10">
-        <v>53.12201925221819</v>
+        <v>60.95067740840523</v>
       </c>
       <c r="T42" s="8" t="s">
         <v>79</v>
@@ -5638,13 +5638,13 @@
         <v>150</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E43" s="9">
-        <v>551.8499755859375</v>
+        <v>565.0800170898438</v>
       </c>
       <c r="F43" s="16">
-        <v>0.3648330507542389</v>
+        <v>0.3779907742334317</v>
       </c>
       <c r="G43" s="19">
         <v>0.3916703502557107</v>
@@ -5656,16 +5656,16 @@
         <v>-0.2860643400571251</v>
       </c>
       <c r="J43" s="19">
-        <v>0.5252619231853878</v>
+        <v>0.6064048451109808</v>
       </c>
       <c r="K43" s="19">
         <v>0</v>
       </c>
       <c r="L43" s="19">
-        <v>0.9268259731960974</v>
+        <v>0.9037595069778264</v>
       </c>
       <c r="M43" s="19">
-        <v>-0.4284145014473035</v>
+        <v>-0.5706656507334537</v>
       </c>
       <c r="N43" s="19">
         <v>13.51341</v>
@@ -5680,10 +5680,10 @@
         <v>0.116</v>
       </c>
       <c r="R43" s="11">
-        <v>0.1848664875860098</v>
+        <v>0.2030611800037021</v>
       </c>
       <c r="S43" s="10">
-        <v>52.0959831864543</v>
+        <v>59.49789012126343</v>
       </c>
       <c r="T43" s="8" t="s">
         <v>79</v>
@@ -5700,52 +5700,52 @@
         <v>152</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E44" s="9">
-        <v>1004.419982910156</v>
+        <v>284.3800048828125</v>
       </c>
       <c r="F44" s="16">
-        <v>0.3632966640111714</v>
+        <v>0.3758188014447972</v>
       </c>
       <c r="G44" s="19">
-        <v>0.3744813910308467</v>
+        <v>-0.7341033794993066</v>
       </c>
       <c r="H44" s="19">
-        <v>0.8243277724214527</v>
+        <v>0.653024735669726</v>
       </c>
       <c r="I44" s="19">
-        <v>0.9077656154464111</v>
+        <v>0.001731719619972795</v>
       </c>
       <c r="J44" s="19">
-        <v>-0.02661500857543126</v>
+        <v>1.379913878252567</v>
       </c>
       <c r="K44" s="19">
         <v>0</v>
       </c>
       <c r="L44" s="19">
-        <v>0.106438951031148</v>
+        <v>-0.8374697203125648</v>
       </c>
       <c r="M44" s="19">
-        <v>0.3902946790370682</v>
+        <v>-0.06904945431090914</v>
       </c>
       <c r="N44" s="19">
-        <v>16.078215</v>
+        <v>45.4335</v>
       </c>
       <c r="O44" s="19">
-        <v>2.8559394</v>
+        <v>6.1722584</v>
       </c>
       <c r="P44" s="11">
-        <v>0.16902</v>
+        <v>0.14425</v>
       </c>
       <c r="Q44" s="11">
-        <v>0.425</v>
+        <v>0.176</v>
       </c>
       <c r="R44" s="11">
-        <v>0.1689680793707509</v>
+        <v>0.4504743875548798</v>
       </c>
       <c r="S44" s="10">
-        <v>42.76251908080483</v>
+        <v>73.58830093484006</v>
       </c>
       <c r="T44" s="8" t="s">
         <v>79</v>
@@ -6065,7 +6065,7 @@
         <v>212</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6202,10 +6202,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BI6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:60">
+    <row r="1" spans="1:61">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6386,8 +6386,11 @@
       <c r="BH1">
         <v>492.2000122070312</v>
       </c>
-    </row>
-    <row r="2" spans="1:60">
+      <c r="BI1">
+        <v>516.3900146484375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:61">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6568,8 +6571,11 @@
       <c r="BH2">
         <v>956.0800170898438</v>
       </c>
-    </row>
-    <row r="3" spans="1:60">
+      <c r="BI2">
+        <v>958.1599731445312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:61">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6750,8 +6756,11 @@
       <c r="BH3">
         <v>1553.400024414062</v>
       </c>
-    </row>
-    <row r="4" spans="1:60">
+      <c r="BI3">
+        <v>1554.989990234375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:61">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6932,8 +6941,11 @@
       <c r="BH4">
         <v>448.8999938964844</v>
       </c>
-    </row>
-    <row r="5" spans="1:60">
+      <c r="BI4">
+        <v>441.5700073242188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:61">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -7114,8 +7126,11 @@
       <c r="BH5">
         <v>366.0899963378906</v>
       </c>
-    </row>
-    <row r="6" spans="1:60">
+      <c r="BI5">
+        <v>370.6900024414062</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7295,6 +7310,9 @@
       </c>
       <c r="BH6">
         <v>387</v>
+      </c>
+      <c r="BI6">
+        <v>387.7099914550781</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -567,7 +567,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-07 18:49 UTC · данные на 2026-09-04 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-08 00:27 UTC · данные на 2026-09-04 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -648,7 +648,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-07 18:49 UTC</t>
+    <t>2026-09-08 00:27 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -3545,7 +3545,7 @@
         <v>1740</v>
       </c>
       <c r="F5" s="17">
-        <v>1.288386268398419</v>
+        <v>1.288386273216903</v>
       </c>
       <c r="G5" s="20">
         <v>-0.304555267188194</v>
@@ -3557,16 +3557,16 @@
         <v>4.17055141824732</v>
       </c>
       <c r="J5" s="20">
-        <v>2.023919715182309</v>
+        <v>2.023919729153198</v>
       </c>
       <c r="K5" s="20">
         <v>0</v>
       </c>
       <c r="L5" s="20">
-        <v>-3.409439608060406</v>
+        <v>-3.409439608134597</v>
       </c>
       <c r="M5" s="20">
-        <v>0.4899878904511634</v>
+        <v>0.4899878911192987</v>
       </c>
       <c r="N5" s="20">
         <v>20.12168</v>
@@ -3607,7 +3607,7 @@
         <v>1016.590026855469</v>
       </c>
       <c r="F6" s="17">
-        <v>1.242705640016112</v>
+        <v>1.242705644997296</v>
       </c>
       <c r="G6" s="20">
         <v>-0.4151936382995601</v>
@@ -3619,16 +3619,16 @@
         <v>4.281237319880006</v>
       </c>
       <c r="J6" s="20">
-        <v>2.135015603182036</v>
+        <v>2.135015617889124</v>
       </c>
       <c r="K6" s="20">
         <v>0</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.409439608060406</v>
+        <v>-3.409439608134597</v>
       </c>
       <c r="M6" s="20">
-        <v>0.1694591591520427</v>
+        <v>0.1694591588491239</v>
       </c>
       <c r="N6" s="20">
         <v>21.095882</v>
@@ -3646,7 +3646,7 @@
         <v>1.746890376291639</v>
       </c>
       <c r="S6" s="11">
-        <v>60.14749911776729</v>
+        <v>60.14749911776811</v>
       </c>
       <c r="T6" s="9" t="s">
         <v>86</v>
@@ -3669,7 +3669,7 @@
         <v>370.7200012207031</v>
       </c>
       <c r="F7" s="17">
-        <v>1.012779500877661</v>
+        <v>1.012779500284539</v>
       </c>
       <c r="G7" s="20">
         <v>0.7601895335887818</v>
@@ -3681,16 +3681,16 @@
         <v>2.850493981628366</v>
       </c>
       <c r="J7" s="20">
-        <v>2.040975436585252</v>
+        <v>2.040975435040183</v>
       </c>
       <c r="K7" s="20">
         <v>0</v>
       </c>
       <c r="L7" s="20">
-        <v>0.1492446570508921</v>
+        <v>0.1492446567675721</v>
       </c>
       <c r="M7" s="20">
-        <v>-0.5333169848032361</v>
+        <v>-0.533316985321084</v>
       </c>
       <c r="N7" s="20">
         <v>14.45283</v>
@@ -3708,7 +3708,7 @@
         <v>0.6646076297666343</v>
       </c>
       <c r="S7" s="11">
-        <v>75.26716954238397</v>
+        <v>75.26716945521606</v>
       </c>
       <c r="T7" s="9" t="s">
         <v>86</v>
@@ -3731,7 +3731,7 @@
         <v>388.8999938964844</v>
       </c>
       <c r="F8" s="17">
-        <v>0.9861956581980518</v>
+        <v>0.9861956423288628</v>
       </c>
       <c r="G8" s="20">
         <v>0.7500777585663686</v>
@@ -3743,16 +3743,16 @@
         <v>2.419096183913033</v>
       </c>
       <c r="J8" s="20">
-        <v>2.043629915624383</v>
+        <v>2.043629869047966</v>
       </c>
       <c r="K8" s="20">
         <v>0</v>
       </c>
       <c r="L8" s="20">
-        <v>0.1812123443946858</v>
+        <v>0.1812123441094873</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.5103639079048429</v>
+        <v>-0.5103639075904566</v>
       </c>
       <c r="N8" s="20">
         <v>12.788835</v>
@@ -3770,7 +3770,7 @@
         <v>0.7690399834916115</v>
       </c>
       <c r="S8" s="11">
-        <v>78.2378468354251</v>
+        <v>78.2378466752572</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>86</v>
@@ -3793,7 +3793,7 @@
         <v>524.1400146484375</v>
       </c>
       <c r="F9" s="17">
-        <v>0.9592813478280915</v>
+        <v>0.9592813531991451</v>
       </c>
       <c r="G9" s="20">
         <v>-0.1447427940002023</v>
@@ -3805,16 +3805,16 @@
         <v>3.042405922684921</v>
       </c>
       <c r="J9" s="20">
-        <v>2.795912167332538</v>
+        <v>2.795912183224905</v>
       </c>
       <c r="K9" s="20">
         <v>0</v>
       </c>
       <c r="L9" s="20">
-        <v>-2.551231927255194</v>
+        <v>-2.551231927379818</v>
       </c>
       <c r="M9" s="20">
-        <v>0.3302762248883058</v>
+        <v>0.3302762244669857</v>
       </c>
       <c r="N9" s="20">
         <v>36.353783</v>
@@ -3832,7 +3832,7 @@
         <v>2.595238758114921</v>
       </c>
       <c r="S9" s="11">
-        <v>63.67345525313577</v>
+        <v>63.67345525064787</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>86</v>
@@ -3855,7 +3855,7 @@
         <v>255.0899963378906</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8451905830400788</v>
+        <v>0.8451905645193203</v>
       </c>
       <c r="G10" s="20">
         <v>0.5236628357643097</v>
@@ -3867,16 +3867,16 @@
         <v>2.388389082821452</v>
       </c>
       <c r="J10" s="20">
-        <v>1.887140755665976</v>
+        <v>1.887140701262632</v>
       </c>
       <c r="K10" s="20">
         <v>0</v>
       </c>
       <c r="L10" s="20">
-        <v>0.3745808489297334</v>
+        <v>0.3745808486331713</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.6449145565470309</v>
+        <v>-0.6449145560404135</v>
       </c>
       <c r="N10" s="20">
         <v>13.92751</v>
@@ -3891,10 +3891,10 @@
         <v>0.531</v>
       </c>
       <c r="R10" s="12">
-        <v>0.5564334002764932</v>
+        <v>0.5564332553700537</v>
       </c>
       <c r="S10" s="11">
-        <v>75.04381064551539</v>
+        <v>75.04381051831487</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>86</v>
@@ -3917,7 +3917,7 @@
         <v>60.04000091552734</v>
       </c>
       <c r="F11" s="17">
-        <v>0.7073949269291883</v>
+        <v>0.7073949382145005</v>
       </c>
       <c r="G11" s="20">
         <v>0.643499368213696</v>
@@ -3929,16 +3929,16 @@
         <v>3.240547283087039</v>
       </c>
       <c r="J11" s="20">
-        <v>0.308216657171009</v>
+        <v>0.3082166903719963</v>
       </c>
       <c r="K11" s="20">
         <v>0</v>
       </c>
       <c r="L11" s="20">
-        <v>0.2435022866050874</v>
+        <v>0.2435022863162283</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.2876824248944663</v>
+        <v>-0.2876824250430902</v>
       </c>
       <c r="N11" s="20">
         <v>17.433628</v>
@@ -3956,7 +3956,7 @@
         <v>0.1183560702395035</v>
       </c>
       <c r="S11" s="11">
-        <v>56.82077158888058</v>
+        <v>56.82077158888354</v>
       </c>
       <c r="T11" s="9" t="s">
         <v>86</v>
@@ -3979,7 +3979,7 @@
         <v>230.3600006103516</v>
       </c>
       <c r="F12" s="17">
-        <v>0.6809721702367264</v>
+        <v>0.6809721827427301</v>
       </c>
       <c r="G12" s="20">
         <v>-1.182209499540936</v>
@@ -3991,16 +3991,16 @@
         <v>2.436903283259161</v>
       </c>
       <c r="J12" s="20">
-        <v>0.6802952656308272</v>
+        <v>0.6802953024404149</v>
       </c>
       <c r="K12" s="20">
         <v>0</v>
       </c>
       <c r="L12" s="20">
-        <v>-0.1960301000377973</v>
+        <v>-0.1960301003008268</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.04204035026429553</v>
+        <v>-0.04204035053693567</v>
       </c>
       <c r="N12" s="20">
         <v>27.468435</v>
@@ -4018,7 +4018,7 @@
         <v>0.2970472917197908</v>
       </c>
       <c r="S12" s="11">
-        <v>60.39296241086819</v>
+        <v>60.39296241087353</v>
       </c>
       <c r="T12" s="9" t="s">
         <v>86</v>
@@ -4041,7 +4041,7 @@
         <v>42.77000045776367</v>
       </c>
       <c r="F13" s="17">
-        <v>0.6119418756714907</v>
+        <v>0.6119418766378938</v>
       </c>
       <c r="G13" s="20">
         <v>1.180701740532482</v>
@@ -4053,16 +4053,16 @@
         <v>-0.2812806277733882</v>
       </c>
       <c r="J13" s="20">
-        <v>1.061735625852884</v>
+        <v>1.061735628775206</v>
       </c>
       <c r="K13" s="20">
         <v>0</v>
       </c>
       <c r="L13" s="20">
-        <v>-0.3610099301419509</v>
+        <v>-0.3610099303952853</v>
       </c>
       <c r="M13" s="20">
-        <v>-0.4092303577455461</v>
+        <v>-0.4092303578838209</v>
       </c>
       <c r="N13" s="20">
         <v>8.974684</v>
@@ -4080,7 +4080,7 @@
         <v>0.3267847498375229</v>
       </c>
       <c r="S13" s="11">
-        <v>57.62085530397127</v>
+        <v>57.6208553046687</v>
       </c>
       <c r="T13" s="9" t="s">
         <v>86</v>
@@ -4103,7 +4103,7 @@
         <v>467.4599914550781</v>
       </c>
       <c r="F14" s="17">
-        <v>0.6036048624968881</v>
+        <v>0.6036048666036268</v>
       </c>
       <c r="G14" s="20">
         <v>-0.9101903600805938</v>
@@ -4115,16 +4115,16 @@
         <v>2.977788239554019</v>
       </c>
       <c r="J14" s="20">
-        <v>0.6825994698021551</v>
+        <v>0.682599481891475</v>
       </c>
       <c r="K14" s="20">
         <v>0</v>
       </c>
       <c r="L14" s="20">
-        <v>-3.409439608060406</v>
+        <v>-3.409439608134597</v>
       </c>
       <c r="M14" s="20">
-        <v>0.6645433019131157</v>
+        <v>0.6645433018079338</v>
       </c>
       <c r="N14" s="20">
         <v>17.067236</v>
@@ -4142,7 +4142,7 @@
         <v>0.9065519122333334</v>
       </c>
       <c r="S14" s="11">
-        <v>48.28405027473917</v>
+        <v>48.28405027473012</v>
       </c>
       <c r="T14" s="9" t="s">
         <v>86</v>
@@ -4165,7 +4165,7 @@
         <v>133.3500061035156</v>
       </c>
       <c r="F15" s="17">
-        <v>0.526831217130437</v>
+        <v>0.5268312173859163</v>
       </c>
       <c r="G15" s="20">
         <v>0.6751790109178482</v>
@@ -4177,16 +4177,16 @@
         <v>0.2863966455848548</v>
       </c>
       <c r="J15" s="20">
-        <v>0.7879954918074542</v>
+        <v>0.7879954927062306</v>
       </c>
       <c r="K15" s="20">
         <v>0</v>
       </c>
       <c r="L15" s="20">
-        <v>-0.01634449175350204</v>
+        <v>-0.01634449202709099</v>
       </c>
       <c r="M15" s="20">
-        <v>0.384620997445398</v>
+        <v>0.3846209970904506</v>
       </c>
       <c r="N15" s="20">
         <v>9.331602999999999</v>
@@ -4204,7 +4204,7 @@
         <v>0.1624141463167428</v>
       </c>
       <c r="S15" s="11">
-        <v>60.82281998401466</v>
+        <v>60.8228199840139</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>86</v>
@@ -4227,7 +4227,7 @@
         <v>208.6000061035156</v>
       </c>
       <c r="F16" s="17">
-        <v>0.518759591665556</v>
+        <v>0.5187595653257109</v>
       </c>
       <c r="G16" s="20">
         <v>0.5557691523136161</v>
@@ -4239,16 +4239,16 @@
         <v>2.293354408551141</v>
       </c>
       <c r="J16" s="20">
-        <v>0.5783481708793555</v>
+        <v>0.5783480937903147</v>
       </c>
       <c r="K16" s="20">
         <v>0</v>
       </c>
       <c r="L16" s="20">
-        <v>0.7480480414675722</v>
+        <v>0.748048041149063</v>
       </c>
       <c r="M16" s="20">
-        <v>-0.4848736908605474</v>
+        <v>-0.4848736912760586</v>
       </c>
       <c r="N16" s="20">
         <v>19.409616</v>
@@ -4266,7 +4266,7 @@
         <v>0.1179728387132282</v>
       </c>
       <c r="S16" s="11">
-        <v>64.86600952844759</v>
+        <v>64.86600953038234</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>86</v>
@@ -4289,7 +4289,7 @@
         <v>259.2300109863281</v>
       </c>
       <c r="F17" s="17">
-        <v>0.5173901176829767</v>
+        <v>0.5173901187278145</v>
       </c>
       <c r="G17" s="20">
         <v>0.343799071956351</v>
@@ -4301,16 +4301,16 @@
         <v>0.1892091902239575</v>
       </c>
       <c r="J17" s="20">
-        <v>1.219658617480957</v>
+        <v>1.2196586204066</v>
       </c>
       <c r="K17" s="20">
         <v>0</v>
       </c>
       <c r="L17" s="20">
-        <v>-1.508013818009251</v>
+        <v>-1.508013818195181</v>
       </c>
       <c r="M17" s="20">
-        <v>0.1615084001320457</v>
+        <v>0.161508400793549</v>
       </c>
       <c r="N17" s="20">
         <v>23.421774</v>
@@ -4328,7 +4328,7 @@
         <v>0.2891448931981548</v>
       </c>
       <c r="S17" s="11">
-        <v>76.62974181906074</v>
+        <v>76.62974183127326</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>86</v>
@@ -4351,7 +4351,7 @@
         <v>32.63999938964844</v>
       </c>
       <c r="F18" s="17">
-        <v>0.50779775811265</v>
+        <v>0.5077977675202567</v>
       </c>
       <c r="G18" s="20">
         <v>1.188833519944301</v>
@@ -4363,16 +4363,16 @@
         <v>-0.3642163190559603</v>
       </c>
       <c r="J18" s="20">
-        <v>1.624405684082189</v>
+        <v>1.624405711820712</v>
       </c>
       <c r="K18" s="20">
         <v>0</v>
       </c>
       <c r="L18" s="20">
-        <v>-0.4614683742647693</v>
+        <v>-0.4614683745122001</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.3992649160997707</v>
+        <v>-0.3992649164499856</v>
       </c>
       <c r="N18" s="20">
         <v>11.648855</v>
@@ -4390,7 +4390,7 @@
         <v>0.7252534861688946</v>
       </c>
       <c r="S18" s="11">
-        <v>66.42670701840598</v>
+        <v>66.4267070183985</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>86</v>
@@ -4413,7 +4413,7 @@
         <v>259.5700073242188</v>
       </c>
       <c r="F19" s="17">
-        <v>0.5023790926255199</v>
+        <v>0.5023791025545321</v>
       </c>
       <c r="G19" s="20">
         <v>1.297185531255487</v>
@@ -4425,16 +4425,16 @@
         <v>-0.04929908647574074</v>
       </c>
       <c r="J19" s="20">
-        <v>0.5138830192955001</v>
+        <v>0.5138830487058349</v>
       </c>
       <c r="K19" s="20">
         <v>0</v>
       </c>
       <c r="L19" s="20">
-        <v>0.5315929657326701</v>
+        <v>0.5315929654268812</v>
       </c>
       <c r="M19" s="20">
-        <v>0.01449379055392255</v>
+        <v>0.01449378971364151</v>
       </c>
       <c r="N19" s="20">
         <v>5.156936</v>
@@ -4452,7 +4452,7 @@
         <v>0.2340966911889795</v>
       </c>
       <c r="S19" s="11">
-        <v>51.96035369550705</v>
+        <v>51.9603537028937</v>
       </c>
       <c r="T19" s="9" t="s">
         <v>86</v>
@@ -4475,7 +4475,7 @@
         <v>30.64999961853027</v>
       </c>
       <c r="F20" s="17">
-        <v>0.4961643546911361</v>
+        <v>0.4961643561590026</v>
       </c>
       <c r="G20" s="20">
         <v>0.5174384367757483</v>
@@ -4487,16 +4487,16 @@
         <v>-0.1869358474983134</v>
       </c>
       <c r="J20" s="20">
-        <v>0.8098308682668818</v>
+        <v>0.8098308727045063</v>
       </c>
       <c r="K20" s="20">
         <v>0</v>
       </c>
       <c r="L20" s="20">
-        <v>0.2068135539541126</v>
+        <v>0.2068135536674096</v>
       </c>
       <c r="M20" s="20">
-        <v>-0.1626755759483994</v>
+        <v>-0.1626755762279338</v>
       </c>
       <c r="N20" s="20">
         <v>17.827587</v>
@@ -4514,7 +4514,7 @@
         <v>0.368867603719909</v>
       </c>
       <c r="S20" s="11">
-        <v>61.58963480299727</v>
+        <v>61.58963480299711</v>
       </c>
       <c r="T20" s="9" t="s">
         <v>86</v>
@@ -4537,7 +4537,7 @@
         <v>52</v>
       </c>
       <c r="F21" s="17">
-        <v>0.4852761382095238</v>
+        <v>0.4852761372604519</v>
       </c>
       <c r="G21" s="20">
         <v>0.2621966121724467</v>
@@ -4549,16 +4549,16 @@
         <v>1.355635681465038</v>
       </c>
       <c r="J21" s="20">
-        <v>1.577856482029923</v>
+        <v>1.577856479276285</v>
       </c>
       <c r="K21" s="20">
         <v>0</v>
       </c>
       <c r="L21" s="20">
-        <v>-1.093834192427098</v>
+        <v>-1.093834192637368</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.6554856223546692</v>
+        <v>-0.6554856223106126</v>
       </c>
       <c r="N21" s="20">
         <v>48.887848</v>
@@ -4576,7 +4576,7 @@
         <v>1.484071106654971</v>
       </c>
       <c r="S21" s="11">
-        <v>48.79187842676978</v>
+        <v>48.79187842694628</v>
       </c>
       <c r="T21" s="9" t="s">
         <v>86</v>
@@ -4599,7 +4599,7 @@
         <v>126.75</v>
       </c>
       <c r="F22" s="17">
-        <v>0.4709509814757308</v>
+        <v>0.4709509819692596</v>
       </c>
       <c r="G22" s="20">
         <v>0.3539469970578056</v>
@@ -4611,16 +4611,16 @@
         <v>0.5513159710787306</v>
       </c>
       <c r="J22" s="20">
-        <v>0.8021435021617126</v>
+        <v>0.8021435036982881</v>
       </c>
       <c r="K22" s="20">
         <v>0</v>
       </c>
       <c r="L22" s="20">
-        <v>0.02424928687789606</v>
+        <v>0.02424928660192158</v>
       </c>
       <c r="M22" s="20">
-        <v>-0.3410706393887311</v>
+        <v>-0.3410706395150904</v>
       </c>
       <c r="N22" s="20">
         <v>15.843312</v>
@@ -4638,7 +4638,7 @@
         <v>0.3211381777628204</v>
       </c>
       <c r="S22" s="11">
-        <v>56.24137683247643</v>
+        <v>56.24137683247652</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>86</v>
@@ -4661,7 +4661,7 @@
         <v>145.1900024414062</v>
       </c>
       <c r="F23" s="17">
-        <v>0.4673517835850313</v>
+        <v>0.4673517845414921</v>
       </c>
       <c r="G23" s="20">
         <v>0.6253387141465833</v>
@@ -4673,16 +4673,16 @@
         <v>1.456491760882698</v>
       </c>
       <c r="J23" s="20">
-        <v>0.2336376947000542</v>
+        <v>0.23363769757397</v>
       </c>
       <c r="K23" s="20">
         <v>0</v>
       </c>
       <c r="L23" s="20">
-        <v>0.265221007489585</v>
+        <v>0.2652210071994496</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.09259918007858177</v>
+        <v>-0.09259918011709681</v>
       </c>
       <c r="N23" s="20">
         <v>11.1643305</v>
@@ -4700,7 +4700,7 @@
         <v>0.1217045734658417</v>
       </c>
       <c r="S23" s="11">
-        <v>50.57582483695487</v>
+        <v>50.57582483695785</v>
       </c>
       <c r="T23" s="9" t="s">
         <v>86</v>
@@ -4723,7 +4723,7 @@
         <v>66.81999969482422</v>
       </c>
       <c r="F24" s="17">
-        <v>0.4625334095686841</v>
+        <v>0.4625333969196003</v>
       </c>
       <c r="G24" s="20">
         <v>0.485926067078946</v>
@@ -4735,16 +4735,16 @@
         <v>0.2072105134374404</v>
       </c>
       <c r="J24" s="20">
-        <v>0.6287773544312324</v>
+        <v>0.6287773174405684</v>
       </c>
       <c r="K24" s="20">
         <v>0</v>
       </c>
       <c r="L24" s="20">
-        <v>0.5898418641938031</v>
+        <v>0.589841863884591</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.3803651691067925</v>
+        <v>-0.3803651692998145</v>
       </c>
       <c r="N24" s="20">
         <v>14.762749</v>
@@ -4762,7 +4762,7 @@
         <v>0.1323774878225439</v>
       </c>
       <c r="S24" s="11">
-        <v>56.572000700719</v>
+        <v>56.57200070093251</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>86</v>
@@ -4785,7 +4785,7 @@
         <v>437.2300109863281</v>
       </c>
       <c r="F25" s="17">
-        <v>0.4614216830982966</v>
+        <v>0.4614217011930919</v>
       </c>
       <c r="G25" s="20">
         <v>-0.2430849524702366</v>
@@ -4797,16 +4797,16 @@
         <v>-0.09520234004633138</v>
       </c>
       <c r="J25" s="20">
-        <v>0.9553480626902106</v>
+        <v>0.9553481158818945</v>
       </c>
       <c r="K25" s="20">
         <v>0</v>
       </c>
       <c r="L25" s="20">
-        <v>0.6799437241339048</v>
+        <v>0.6799437238193978</v>
       </c>
       <c r="M25" s="20">
-        <v>-0.8238442799443948</v>
+        <v>-0.8238442801345791</v>
       </c>
       <c r="N25" s="20">
         <v>26.875078</v>
@@ -4824,7 +4824,7 @@
         <v>0.1991076631844904</v>
       </c>
       <c r="S25" s="11">
-        <v>62.51462135723068</v>
+        <v>62.51462135740006</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>86</v>
@@ -4847,7 +4847,7 @@
         <v>217.7200012207031</v>
       </c>
       <c r="F26" s="17">
-        <v>0.444202496646578</v>
+        <v>0.4442024974016189</v>
       </c>
       <c r="G26" s="20">
         <v>0.360549156407083</v>
@@ -4859,16 +4859,16 @@
         <v>0.3996363456297529</v>
       </c>
       <c r="J26" s="20">
-        <v>0.430083926415856</v>
+        <v>0.4300839288433567</v>
       </c>
       <c r="K26" s="20">
         <v>0</v>
       </c>
       <c r="L26" s="20">
-        <v>0.543352348936784</v>
+        <v>0.5433523486303039</v>
       </c>
       <c r="M26" s="20">
-        <v>0.005246280274458004</v>
+        <v>0.005246279706640156</v>
       </c>
       <c r="N26" s="20">
         <v>17.362167</v>
@@ -4886,7 +4886,7 @@
         <v>0.3732761020184954</v>
       </c>
       <c r="S26" s="11">
-        <v>54.99960803037821</v>
+        <v>54.99960803943708</v>
       </c>
       <c r="T26" s="9" t="s">
         <v>86</v>
@@ -4909,7 +4909,7 @@
         <v>416.3699951171875</v>
       </c>
       <c r="F27" s="17">
-        <v>0.4441833994703904</v>
+        <v>0.4441834002930676</v>
       </c>
       <c r="G27" s="20">
         <v>0.3086538886996134</v>
@@ -4921,16 +4921,16 @@
         <v>-0.09806550872946435</v>
       </c>
       <c r="J27" s="20">
-        <v>0.8238471016376835</v>
+        <v>0.82384710416048</v>
       </c>
       <c r="K27" s="20">
         <v>0</v>
       </c>
       <c r="L27" s="20">
-        <v>0.5743724738565921</v>
+        <v>0.574372473548289</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.6183749954406236</v>
+        <v>-0.6183749956204355</v>
       </c>
       <c r="N27" s="20">
         <v>24.571085</v>
@@ -4948,7 +4948,7 @@
         <v>0.3243320712476749</v>
       </c>
       <c r="S27" s="11">
-        <v>60.61633471760554</v>
+        <v>60.61633471760578</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>86</v>
@@ -4971,7 +4971,7 @@
         <v>109.2900009155273</v>
       </c>
       <c r="F28" s="17">
-        <v>0.4329767653546041</v>
+        <v>0.4329767764264066</v>
       </c>
       <c r="G28" s="20">
         <v>0.08362146264365951</v>
@@ -4983,16 +4983,16 @@
         <v>0.1140666249819975</v>
       </c>
       <c r="J28" s="20">
-        <v>0.4829374134960405</v>
+        <v>0.4829374460462151</v>
       </c>
       <c r="K28" s="20">
         <v>0</v>
       </c>
       <c r="L28" s="20">
-        <v>0.8786502776792144</v>
+        <v>0.8786502773530303</v>
       </c>
       <c r="M28" s="20">
-        <v>-0.4843388436982553</v>
+        <v>-0.4843388437269447</v>
       </c>
       <c r="N28" s="20">
         <v>20.065575</v>
@@ -5010,7 +5010,7 @@
         <v>0.1551191514108801</v>
       </c>
       <c r="S28" s="11">
-        <v>53.51342061803188</v>
+        <v>53.51342061785085</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>86</v>
@@ -5033,7 +5033,7 @@
         <v>128.0899963378906</v>
       </c>
       <c r="F29" s="17">
-        <v>0.4314710891258677</v>
+        <v>0.4314710720958842</v>
       </c>
       <c r="G29" s="20">
         <v>0.4655239786150748</v>
@@ -5045,16 +5045,16 @@
         <v>-0.1884518302174612</v>
       </c>
       <c r="J29" s="20">
-        <v>1.019479035349183</v>
+        <v>1.019478983803299</v>
       </c>
       <c r="K29" s="20">
         <v>0</v>
       </c>
       <c r="L29" s="20">
-        <v>-0.6022116530816467</v>
+        <v>-0.6022116533208066</v>
       </c>
       <c r="M29" s="20">
-        <v>-1.001415620632749</v>
+        <v>-1.001415614486135</v>
       </c>
       <c r="N29" s="20">
         <v>16.68579</v>
@@ -5072,7 +5072,7 @@
         <v>0.1063406141507248</v>
       </c>
       <c r="S29" s="11">
-        <v>60.72188674592569</v>
+        <v>60.72188668631097</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>86</v>
@@ -5095,7 +5095,7 @@
         <v>185.5899963378906</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4295195363584214</v>
+        <v>0.4295195471860156</v>
       </c>
       <c r="G30" s="20">
         <v>-0.417370639505269</v>
@@ -5107,16 +5107,16 @@
         <v>-0.2043202764057594</v>
       </c>
       <c r="J30" s="20">
-        <v>1.160286379069189</v>
+        <v>1.160286410851864</v>
       </c>
       <c r="K30" s="20">
         <v>0</v>
       </c>
       <c r="L30" s="20">
-        <v>-0.1004270507103209</v>
+        <v>-0.1004270509789687</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.8702642942966269</v>
+        <v>-0.8702642941766345</v>
       </c>
       <c r="N30" s="20">
         <v>29.498423</v>
@@ -5134,7 +5134,7 @@
         <v>0.8514465022793682</v>
       </c>
       <c r="S30" s="11">
-        <v>49.0843715326393</v>
+        <v>49.0843715326604</v>
       </c>
       <c r="T30" s="9" t="s">
         <v>86</v>
@@ -5157,7 +5157,7 @@
         <v>401.5400085449219</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4180834499151204</v>
+        <v>0.4180834521117541</v>
       </c>
       <c r="G31" s="20">
         <v>0.3994592812726025</v>
@@ -5169,16 +5169,16 @@
         <v>0.1877082092453494</v>
       </c>
       <c r="J31" s="20">
-        <v>1.412759331112949</v>
+        <v>1.412759337688216</v>
       </c>
       <c r="K31" s="20">
         <v>0</v>
       </c>
       <c r="L31" s="20">
-        <v>0.2008644192650442</v>
+        <v>0.2008644189786908</v>
       </c>
       <c r="M31" s="20">
-        <v>0.1280906378554924</v>
+        <v>0.1280906375759774</v>
       </c>
       <c r="N31" s="20">
         <v>37.178402</v>
@@ -5196,7 +5196,7 @@
         <v>1.258060463786058</v>
       </c>
       <c r="S31" s="11">
-        <v>59.41208191349446</v>
+        <v>59.41208191349453</v>
       </c>
       <c r="T31" s="9" t="s">
         <v>86</v>
@@ -5219,7 +5219,7 @@
         <v>369.3500061035156</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4118625815683601</v>
+        <v>0.4118625809126026</v>
       </c>
       <c r="G32" s="20">
         <v>1.231857100506108</v>
@@ -5231,16 +5231,16 @@
         <v>-0.3829551400317068</v>
       </c>
       <c r="J32" s="20">
-        <v>0.5628513002852527</v>
+        <v>0.5628512984292272</v>
       </c>
       <c r="K32" s="20">
         <v>0</v>
       </c>
       <c r="L32" s="20">
-        <v>0.6036938043107078</v>
+        <v>0.6036938040006817</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.08104050795586631</v>
+        <v>-0.08104050797658555</v>
       </c>
       <c r="N32" s="20">
         <v>9.919549</v>
@@ -5258,7 +5258,7 @@
         <v>0.2152546687130332</v>
       </c>
       <c r="S32" s="11">
-        <v>51.9656203348329</v>
+        <v>51.96562033432203</v>
       </c>
       <c r="T32" s="9" t="s">
         <v>86</v>
@@ -5281,7 +5281,7 @@
         <v>1038.609985351562</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4098942528194425</v>
+        <v>0.4098942413876117</v>
       </c>
       <c r="G33" s="20">
         <v>0.3749907256319778</v>
@@ -5293,16 +5293,16 @@
         <v>0.9342898423755277</v>
       </c>
       <c r="J33" s="20">
-        <v>0.169315780626753</v>
+        <v>0.1693157471905421</v>
       </c>
       <c r="K33" s="20">
         <v>0</v>
       </c>
       <c r="L33" s="20">
-        <v>0.07337427412711799</v>
+        <v>0.07337427384825664</v>
       </c>
       <c r="M33" s="20">
-        <v>0.1595437480977375</v>
+        <v>0.1595437479425359</v>
       </c>
       <c r="N33" s="20">
         <v>16.078215</v>
@@ -5320,7 +5320,7 @@
         <v>0.2762003358535221</v>
       </c>
       <c r="S33" s="11">
-        <v>52.01914900092819</v>
+        <v>52.0191490011484</v>
       </c>
       <c r="T33" s="9" t="s">
         <v>86</v>
@@ -5343,7 +5343,7 @@
         <v>68.87999725341797</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4098498341917612</v>
+        <v>0.4098498353116549</v>
       </c>
       <c r="G34" s="20">
         <v>0.5493403711834062</v>
@@ -5355,16 +5355,16 @@
         <v>-0.6338771958527055</v>
       </c>
       <c r="J34" s="20">
-        <v>-0.1643725713514303</v>
+        <v>-0.1643725679524307</v>
       </c>
       <c r="K34" s="20">
         <v>0</v>
       </c>
       <c r="L34" s="20">
-        <v>0.3880640492241098</v>
+        <v>0.3880640489267553</v>
       </c>
       <c r="M34" s="20">
-        <v>0.7028089610525862</v>
+        <v>0.7028089608481835</v>
       </c>
       <c r="N34" s="20">
         <v>14.242739</v>
@@ -5382,7 +5382,7 @@
         <v>0.06873432320828665</v>
       </c>
       <c r="S34" s="11">
-        <v>51.90121344764945</v>
+        <v>51.9012134476565</v>
       </c>
       <c r="T34" s="9" t="s">
         <v>86</v>
@@ -5405,7 +5405,7 @@
         <v>164.4400024414062</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4096970220286507</v>
+        <v>0.4096970059966824</v>
       </c>
       <c r="G35" s="20">
         <v>0.503970173929344</v>
@@ -5417,16 +5417,16 @@
         <v>-0.04611621933418467</v>
       </c>
       <c r="J35" s="20">
-        <v>1.391192413504096</v>
+        <v>1.391192367329199</v>
       </c>
       <c r="K35" s="20">
         <v>0</v>
       </c>
       <c r="L35" s="20">
-        <v>0.2396921847646779</v>
+        <v>0.2396921844760427</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.8473738690909207</v>
+        <v>-0.8473738720702306</v>
       </c>
       <c r="N35" s="20">
         <v>16.927385</v>
@@ -5444,7 +5444,7 @@
         <v>0.3847812251157086</v>
       </c>
       <c r="S35" s="11">
-        <v>63.60644195752816</v>
+        <v>63.6064420107626</v>
       </c>
       <c r="T35" s="9" t="s">
         <v>86</v>
@@ -5467,7 +5467,7 @@
         <v>134.2599945068359</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4035996333893978</v>
+        <v>0.4035996465917915</v>
       </c>
       <c r="G36" s="20">
         <v>0.5374978389243423</v>
@@ -5479,16 +5479,16 @@
         <v>0.8104316467241883</v>
       </c>
       <c r="J36" s="20">
-        <v>0.7327361626926164</v>
+        <v>0.7327362015311909</v>
       </c>
       <c r="K36" s="20">
         <v>0</v>
       </c>
       <c r="L36" s="20">
-        <v>0.4091735699819639</v>
+        <v>0.4091735696833689</v>
       </c>
       <c r="M36" s="20">
-        <v>-0.5610662565412403</v>
+        <v>-0.5610662567356174</v>
       </c>
       <c r="N36" s="20">
         <v>17.128778</v>
@@ -5506,7 +5506,7 @@
         <v>0.1630641606621228</v>
       </c>
       <c r="S36" s="11">
-        <v>63.20133407937327</v>
+        <v>63.20133407819568</v>
       </c>
       <c r="T36" s="9" t="s">
         <v>86</v>
@@ -5529,7 +5529,7 @@
         <v>409.3800048828125</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4004087225874116</v>
+        <v>0.4004087232733701</v>
       </c>
       <c r="G37" s="20">
         <v>-0.9739831881979379</v>
@@ -5541,16 +5541,16 @@
         <v>4.17055141824732</v>
       </c>
       <c r="J37" s="20">
-        <v>0.5630701790637896</v>
+        <v>0.5630701811550737</v>
       </c>
       <c r="K37" s="20">
         <v>0</v>
       </c>
       <c r="L37" s="20">
-        <v>0.6698539930526135</v>
+        <v>0.6698539927386995</v>
       </c>
       <c r="M37" s="20">
-        <v>-0.3651698660000948</v>
+        <v>-0.3651698660614312</v>
       </c>
       <c r="N37" s="20">
         <v>105.25127</v>
@@ -5591,7 +5591,7 @@
         <v>178.2899932861328</v>
       </c>
       <c r="F38" s="17">
-        <v>0.3922356080780352</v>
+        <v>0.3922356294151208</v>
       </c>
       <c r="G38" s="20">
         <v>0.5394709098351904</v>
@@ -5603,16 +5603,16 @@
         <v>-0.04744840355762995</v>
       </c>
       <c r="J38" s="20">
-        <v>0.4208249778450363</v>
+        <v>0.4208250405291875</v>
       </c>
       <c r="K38" s="20">
         <v>0</v>
       </c>
       <c r="L38" s="20">
-        <v>0.8387869670766107</v>
+        <v>0.8387869667527692</v>
       </c>
       <c r="M38" s="20">
-        <v>-0.1811566033298044</v>
+        <v>-0.1811566034445488</v>
       </c>
       <c r="N38" s="20">
         <v>15.65096</v>
@@ -5630,7 +5630,7 @@
         <v>0.1811596730110814</v>
       </c>
       <c r="S38" s="11">
-        <v>53.93681336110608</v>
+        <v>53.93681336066579</v>
       </c>
       <c r="T38" s="9" t="s">
         <v>86</v>
@@ -5653,7 +5653,7 @@
         <v>199.2200012207031</v>
       </c>
       <c r="F39" s="17">
-        <v>0.3899535792183069</v>
+        <v>0.3899535621230157</v>
       </c>
       <c r="G39" s="20">
         <v>0.6294950918963452</v>
@@ -5665,16 +5665,16 @@
         <v>1.609810865818413</v>
       </c>
       <c r="J39" s="20">
-        <v>0.2180436275226666</v>
+        <v>0.2180435774304511</v>
       </c>
       <c r="K39" s="20">
         <v>0</v>
       </c>
       <c r="L39" s="20">
-        <v>0.2757628469700045</v>
+        <v>0.2757628466792496</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.0744058017467206</v>
+        <v>-0.07440580173104963</v>
       </c>
       <c r="N39" s="20">
         <v>37.579845</v>
@@ -5692,7 +5692,7 @@
         <v>0.1156468921149059</v>
       </c>
       <c r="S39" s="11">
-        <v>48.64144785646445</v>
+        <v>48.64144785651807</v>
       </c>
       <c r="T39" s="9" t="s">
         <v>86</v>
@@ -5715,7 +5715,7 @@
         <v>122.0199966430664</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3808036723644898</v>
+        <v>0.3808036829189749</v>
       </c>
       <c r="G40" s="20">
         <v>1.209298447018494</v>
@@ -5727,16 +5727,16 @@
         <v>0.1426763443862438</v>
       </c>
       <c r="J40" s="20">
-        <v>0.5604251470194529</v>
+        <v>0.5604251780970326</v>
       </c>
       <c r="K40" s="20">
         <v>0</v>
       </c>
       <c r="L40" s="20">
-        <v>1.055835276097953</v>
+        <v>1.055835275761357</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.3078750949146036</v>
+        <v>-0.3078750951037435</v>
       </c>
       <c r="N40" s="20">
         <v>10.860381</v>
@@ -5754,7 +5754,7 @@
         <v>0.2882094487081623</v>
       </c>
       <c r="S40" s="11">
-        <v>56.88897934788456</v>
+        <v>56.88897934844421</v>
       </c>
       <c r="T40" s="9" t="s">
         <v>86</v>
@@ -5777,7 +5777,7 @@
         <v>560.5599975585938</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3800842447622991</v>
+        <v>0.3800842297516259</v>
       </c>
       <c r="G41" s="20">
         <v>0.3925105812237497</v>
@@ -5789,16 +5789,16 @@
         <v>-0.2828670116363273</v>
       </c>
       <c r="J41" s="20">
-        <v>0.594564151799013</v>
+        <v>0.5945641082481493</v>
       </c>
       <c r="K41" s="20">
         <v>0</v>
       </c>
       <c r="L41" s="20">
-        <v>0.8766593126883996</v>
+        <v>0.8766593123623324</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.4847764601356667</v>
+        <v>-0.4847764616927837</v>
       </c>
       <c r="N41" s="20">
         <v>13.51341</v>
@@ -5813,10 +5813,10 @@
         <v>0.116</v>
       </c>
       <c r="R41" s="12">
-        <v>0.2139751653777735</v>
+        <v>0.2139750851457882</v>
       </c>
       <c r="S41" s="11">
-        <v>56.29734892169057</v>
+        <v>56.29734893721688</v>
       </c>
       <c r="T41" s="9" t="s">
         <v>86</v>
@@ -5839,7 +5839,7 @@
         <v>298.0400085449219</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3785613189848826</v>
+        <v>0.3785613190027045</v>
       </c>
       <c r="G42" s="20">
         <v>0.02746197675084354</v>
@@ -5851,16 +5851,16 @@
         <v>0.5984308054165401</v>
       </c>
       <c r="J42" s="20">
-        <v>0.541936979244838</v>
+        <v>0.5419369792960574</v>
       </c>
       <c r="K42" s="20">
         <v>0</v>
       </c>
       <c r="L42" s="20">
-        <v>-0.4802622796761541</v>
+        <v>-0.4802622799224806</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.7344100808169153</v>
+        <v>-0.7344100806282032</v>
       </c>
       <c r="N42" s="20">
         <v>20.706474</v>
@@ -5878,7 +5878,7 @@
         <v>0.1982347273512726</v>
       </c>
       <c r="S42" s="11">
-        <v>43.62482624844689</v>
+        <v>43.62482624844692</v>
       </c>
       <c r="T42" s="9" t="s">
         <v>86</v>
@@ -5901,7 +5901,7 @@
         <v>849.280029296875</v>
       </c>
       <c r="F43" s="17">
-        <v>0.354859595715255</v>
+        <v>0.3548596009041816</v>
       </c>
       <c r="G43" s="20">
         <v>-2.080641695366814</v>
@@ -5913,16 +5913,16 @@
         <v>1.358863708841197</v>
       </c>
       <c r="J43" s="20">
-        <v>1.570443959086807</v>
+        <v>1.570443974335826</v>
       </c>
       <c r="K43" s="20">
         <v>0</v>
       </c>
       <c r="L43" s="20">
-        <v>-2.966945152187723</v>
+        <v>-2.966945152287917</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.1501707509450764</v>
+        <v>-0.1501707509755603</v>
       </c>
       <c r="N43" s="20">
         <v>59.523674</v>
@@ -5940,7 +5940,7 @@
         <v>1.413175079577211</v>
       </c>
       <c r="S43" s="11">
-        <v>50.6449326256915</v>
+        <v>50.64493262569261</v>
       </c>
       <c r="T43" s="9" t="s">
         <v>86</v>
@@ -5963,7 +5963,7 @@
         <v>579.2100219726562</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3525500437054685</v>
+        <v>0.3525500431262109</v>
       </c>
       <c r="G44" s="20">
         <v>-1.475165475869587</v>
@@ -5975,16 +5975,16 @@
         <v>-0.1665174441390725</v>
       </c>
       <c r="J44" s="20">
-        <v>0.3097185365208672</v>
+        <v>0.3097185348209719</v>
       </c>
       <c r="K44" s="20">
         <v>0</v>
       </c>
       <c r="L44" s="20">
-        <v>0.9815367931503112</v>
+        <v>0.9815367928180807</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.2932955351886911</v>
+        <v>-0.2932955349367438</v>
       </c>
       <c r="N44" s="20">
         <v>32.565643</v>
@@ -6002,7 +6002,7 @@
         <v>0.1126430407173609</v>
       </c>
       <c r="S44" s="11">
-        <v>52.90532324373162</v>
+        <v>52.90532324040763</v>
       </c>
       <c r="T44" s="9" t="s">
         <v>86</v>
@@ -6322,7 +6322,7 @@
         <v>213</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:2">

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="241">
   <si>
     <t>DELL</t>
   </si>
@@ -231,6 +231,9 @@
     <t>2026-09-03</t>
   </si>
   <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -288,19 +291,145 @@
     <t>проходит</t>
   </si>
   <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>Centene Corporation</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class A)</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class C)</t>
+  </si>
+  <si>
+    <t>TGT</t>
+  </si>
+  <si>
+    <t>Target Corporation</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>DLTR</t>
+  </si>
+  <si>
+    <t>Dollar Tree</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
     <t>NVDA</t>
   </si>
   <si>
     <t>Nvidia</t>
   </si>
   <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>CF Industries</t>
-  </si>
-  <si>
-    <t>Materials</t>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
+  </si>
+  <si>
+    <t>BIIB</t>
+  </si>
+  <si>
+    <t>Biogen</t>
+  </si>
+  <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>Supermicro</t>
+  </si>
+  <si>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
   </si>
   <si>
     <t>CVX</t>
@@ -309,25 +438,28 @@
     <t>Chevron Corporation</t>
   </si>
   <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
-  </si>
-  <si>
-    <t>HPQ</t>
-  </si>
-  <si>
-    <t>HP Inc.</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
-    <t>Financials</t>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>REGN</t>
+  </si>
+  <si>
+    <t>Regeneron Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>Amgen</t>
+  </si>
+  <si>
+    <t>HOOD</t>
+  </si>
+  <si>
+    <t>Robinhood Markets</t>
   </si>
   <si>
     <t>GEN</t>
@@ -336,124 +468,25 @@
     <t>Gen Digital</t>
   </si>
   <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>Hewlett Packard Enterprise</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>Health Care</t>
-  </si>
-  <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>EOG Resources</t>
-  </si>
-  <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>Amgen</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
-  </si>
-  <si>
-    <t>CPAY</t>
-  </si>
-  <si>
-    <t>Corpay</t>
-  </si>
-  <si>
-    <t>SCHW</t>
-  </si>
-  <si>
-    <t>Charles Schwab Corporation</t>
-  </si>
-  <si>
-    <t>NEM</t>
-  </si>
-  <si>
-    <t>Newmont</t>
-  </si>
-  <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
-  </si>
-  <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>Altria</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>TGT</t>
-  </si>
-  <si>
-    <t>Target Corporation</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
-  </si>
-  <si>
-    <t>WAT</t>
-  </si>
-  <si>
-    <t>Waters Corporation</t>
-  </si>
-  <si>
-    <t>RJF</t>
-  </si>
-  <si>
-    <t>Raymond James Financial</t>
-  </si>
-  <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>Diamondback Energy</t>
+    <t>WBD</t>
+  </si>
+  <si>
+    <t>Warner Bros. Discovery</t>
+  </si>
+  <si>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>News Corp (Class A)</t>
+  </si>
+  <si>
+    <t>SWK</t>
+  </si>
+  <si>
+    <t>Stanley Black &amp; Decker</t>
+  </si>
+  <si>
+    <t>Industrials</t>
   </si>
   <si>
     <t>PRU</t>
@@ -462,33 +495,6 @@
     <t>Prudential Financial</t>
   </si>
   <si>
-    <t>AMP</t>
-  </si>
-  <si>
-    <t>Ameriprise Financial</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>Expedia Group</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>STX</t>
-  </si>
-  <si>
-    <t>Seagate Technology</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>Mastercard</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -567,7 +573,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-08 00:27 UTC · данные на 2026-09-04 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-09 00:18 UTC · данные на 2026-09-08 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -648,7 +654,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-08 00:27 UTC</t>
+    <t>2026-09-09 00:18 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -663,7 +669,7 @@
     <t>Прошли фильтры</t>
   </si>
   <si>
-    <t>414</t>
+    <t>415</t>
   </si>
   <si>
     <t>Кандидат дня</t>
@@ -693,7 +699,7 @@
     <t>Фундаментал на дату</t>
   </si>
   <si>
-    <t>2026-08-30</t>
+    <t>2026-09-06</t>
   </si>
   <si>
     <t>Версия состояния</t>
@@ -1142,9 +1148,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$14</c:f>
+              <c:f>Капитал!$A$5:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1174,16 +1180,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2026-09-04</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2026-09-08</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$14</c:f>
+              <c:f>Капитал!$D$5:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1212,6 +1221,9 @@
                   <c:v>9972.67</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>10216.05</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>10216.05</c:v>
                 </c:pt>
               </c:numCache>
@@ -1237,9 +1249,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$14</c:f>
+              <c:f>Капитал!$A$5:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1269,16 +1281,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2026-09-04</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2026-09-08</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$14</c:f>
+              <c:f>Капитал!$F$5:$F$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1308,6 +1323,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10088.02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1447,9 +1465,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$14</c:f>
+              <c:f>Капитал!$A$5:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1479,16 +1497,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2026-09-04</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2026-09-08</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$14</c:f>
+              <c:f>Капитал!$D$5:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1517,6 +1538,9 @@
                   <c:v>9972.67</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>10216.05</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>10216.05</c:v>
                 </c:pt>
               </c:numCache>
@@ -1542,9 +1566,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$14</c:f>
+              <c:f>Капитал!$A$5:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1574,16 +1598,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2026-09-04</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2026-09-08</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$14</c:f>
+              <c:f>Капитал!$F$5:$F$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1613,6 +1640,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10088.02</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2107,12 +2137,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2120,13 +2150,13 @@
         <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2145,27 +2175,27 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>4.742278737370178</v>
+        <v>4.478979173158216</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H9" s="7">
         <v>9</v>
@@ -2173,7 +2203,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2202,7 +2232,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -2210,7 +2240,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -2218,23 +2248,23 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C18" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C19" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -2242,55 +2272,55 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C25" s="12">
-        <v>0.1280601535446627</v>
+        <v>0.1220294240725164</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C26" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2299,12 +2329,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -2455,11 +2485,11 @@
         <v>0.18286309065709058</v>
       </c>
       <c r="L5" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N5" s="20">
         <v>2.927623067210654</v>
@@ -2506,11 +2536,11 @@
         <v>0.09758958423901652</v>
       </c>
       <c r="L6" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N6" s="20">
         <v>1.809956883354321</v>
@@ -2557,11 +2587,11 @@
         <v>0.1224393676054864</v>
       </c>
       <c r="L7" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M7" s="11">
         <f>MAX(0,21-L7)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N7" s="20">
         <v>1.655247920227722</v>
@@ -2608,11 +2638,11 @@
         <v>0.010656458832162687</v>
       </c>
       <c r="L8" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M8" s="11">
         <f>MAX(0,21-L8)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N8" s="20">
         <v>1.135451734784544</v>
@@ -2659,11 +2689,11 @@
         <v>0.029377395192469312</v>
       </c>
       <c r="L9" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M9" s="11">
         <f>MAX(0,21-L9)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N9" s="20">
         <v>1.098454348098604</v>
@@ -2710,11 +2740,11 @@
         <v>0.020814011776538976</v>
       </c>
       <c r="L10" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M10" s="11">
         <f>MAX(0,21-L10)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N10" s="20">
         <v>0.9280120270881818</v>
@@ -2761,11 +2791,11 @@
         <v>-0.0018297215776284946</v>
       </c>
       <c r="L11" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="11">
         <f>MAX(0,21-L11)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N11" s="20">
         <v>0.8840484909760108</v>
@@ -2812,11 +2842,11 @@
         <v>0.012639994356587973</v>
       </c>
       <c r="L12" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="11">
         <f>MAX(0,21-L12)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N12" s="20">
         <v>0.8298272742812407</v>
@@ -2863,11 +2893,11 @@
         <v>-0.02132271831371461</v>
       </c>
       <c r="L13" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="11">
         <f>MAX(0,21-L13)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N13" s="20">
         <v>0.7019116395441239</v>
@@ -3185,7 +3215,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3430,6 +3460,25 @@
       <c r="F14" s="10">
         <v>10088.02</v>
       </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="10">
+        <v>5714.88</v>
+      </c>
+      <c r="C15" s="10">
+        <v>4501.17</v>
+      </c>
+      <c r="D15" s="10">
+        <f>B15+C15</f>
+        <v>10216.05</v>
+      </c>
+      <c r="E15" s="11">
+        <v>9</v>
+      </c>
+      <c r="F15" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3458,12 +3507,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3480,52 +3529,52 @@
         <v>13</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -3533,61 +3582,61 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="10">
-        <v>1740</v>
+        <v>1016.590026855469</v>
       </c>
       <c r="F5" s="17">
-        <v>1.288386273216903</v>
+        <v>1.098851126819778</v>
       </c>
       <c r="G5" s="20">
-        <v>-0.304555267188194</v>
+        <v>-0.5381709417593455</v>
       </c>
       <c r="H5" s="20">
-        <v>2.060850957203688</v>
+        <v>1.814060278794422</v>
       </c>
       <c r="I5" s="20">
-        <v>4.17055141824732</v>
+        <v>3.983916492932042</v>
       </c>
       <c r="J5" s="20">
-        <v>2.023919729153198</v>
+        <v>2.135435138403564</v>
       </c>
       <c r="K5" s="20">
-        <v>0</v>
+        <v>0.4798559392469772</v>
       </c>
       <c r="L5" s="20">
-        <v>-3.409439608134597</v>
+        <v>-3.413048273912248</v>
       </c>
       <c r="M5" s="20">
-        <v>0.4899878911192987</v>
+        <v>0.1706280580022094</v>
       </c>
       <c r="N5" s="20">
-        <v>20.12168</v>
+        <v>22.98937</v>
       </c>
       <c r="O5" s="20">
-        <v>14.060845</v>
+        <v>11.394834</v>
       </c>
       <c r="P5" s="12">
-        <v>0.9164</v>
+        <v>0.66638</v>
       </c>
       <c r="Q5" s="12">
-        <v>3.716</v>
+        <v>3.457</v>
       </c>
       <c r="R5" s="12">
-        <v>2.299641483719194</v>
+        <v>1.746890376291639</v>
       </c>
       <c r="S5" s="11">
-        <v>61.24267366525383</v>
+        <v>60.14749911776807</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -3595,61 +3644,61 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="10">
-        <v>1016.590026855469</v>
+        <v>1740</v>
       </c>
       <c r="F6" s="17">
-        <v>1.242705644997296</v>
+        <v>1.093007060689962</v>
       </c>
       <c r="G6" s="20">
-        <v>-0.4151936382995601</v>
+        <v>-0.5564495730839067</v>
       </c>
       <c r="H6" s="20">
-        <v>1.81685655573093</v>
+        <v>2.058086531115069</v>
       </c>
       <c r="I6" s="20">
-        <v>4.281237319880006</v>
+        <v>4.120745224686987</v>
       </c>
       <c r="J6" s="20">
-        <v>2.135015617889124</v>
+        <v>2.024313374674196</v>
       </c>
       <c r="K6" s="20">
-        <v>0</v>
+        <v>0.08299030126699286</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.409439608134597</v>
+        <v>-3.413048273912248</v>
       </c>
       <c r="M6" s="20">
-        <v>0.1694591588491239</v>
+        <v>0.491620803479896</v>
       </c>
       <c r="N6" s="20">
-        <v>21.095882</v>
+        <v>23.583628</v>
       </c>
       <c r="O6" s="20">
-        <v>10.456314</v>
+        <v>16.475557</v>
       </c>
       <c r="P6" s="12">
-        <v>0.66638</v>
+        <v>0.9164</v>
       </c>
       <c r="Q6" s="12">
-        <v>3.457</v>
+        <v>3.716</v>
       </c>
       <c r="R6" s="12">
-        <v>1.746890376291639</v>
+        <v>2.299641483719194</v>
       </c>
       <c r="S6" s="11">
-        <v>60.14749911776811</v>
+        <v>61.24267366525383</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -3669,34 +3718,34 @@
         <v>370.7200012207031</v>
       </c>
       <c r="F7" s="17">
-        <v>1.012779500284539</v>
+        <v>0.9601856213956613</v>
       </c>
       <c r="G7" s="20">
-        <v>0.7601895335887818</v>
+        <v>0.7163099250210818</v>
       </c>
       <c r="H7" s="20">
-        <v>-0.6826219065677867</v>
+        <v>-0.6808483021094016</v>
       </c>
       <c r="I7" s="20">
-        <v>2.850493981628366</v>
+        <v>2.885035079678366</v>
       </c>
       <c r="J7" s="20">
-        <v>2.040975435040183</v>
+        <v>2.042036654460478</v>
       </c>
       <c r="K7" s="20">
-        <v>0</v>
+        <v>0.6066252760202447</v>
       </c>
       <c r="L7" s="20">
-        <v>0.1492446567675721</v>
+        <v>0.1481612466747712</v>
       </c>
       <c r="M7" s="20">
-        <v>-0.533316985321084</v>
+        <v>-0.5326706124940634</v>
       </c>
       <c r="N7" s="20">
-        <v>14.45283</v>
+        <v>15.453106</v>
       </c>
       <c r="O7" s="20">
-        <v>4.0580444</v>
+        <v>4.269492</v>
       </c>
       <c r="P7" s="12">
         <v>0.27637</v>
@@ -3708,10 +3757,10 @@
         <v>0.6646076297666343</v>
       </c>
       <c r="S7" s="11">
-        <v>75.26716945521606</v>
+        <v>75.26716954237817</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -3731,34 +3780,34 @@
         <v>388.8999938964844</v>
       </c>
       <c r="F8" s="17">
-        <v>0.9861956423288628</v>
+        <v>0.9565841660532839</v>
       </c>
       <c r="G8" s="20">
-        <v>0.7500777585663686</v>
+        <v>0.704035078477925</v>
       </c>
       <c r="H8" s="20">
-        <v>-0.5762752402348297</v>
+        <v>-0.5743881810314097</v>
       </c>
       <c r="I8" s="20">
-        <v>2.419096183913033</v>
+        <v>2.454207309239585</v>
       </c>
       <c r="J8" s="20">
-        <v>2.043629869047966</v>
+        <v>2.0446398229775</v>
       </c>
       <c r="K8" s="20">
-        <v>0</v>
+        <v>0.7742712560795861</v>
       </c>
       <c r="L8" s="20">
-        <v>0.1812123441094873</v>
+        <v>0.1801601438739235</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.5103639075904566</v>
+        <v>-0.5096859535863941</v>
       </c>
       <c r="N8" s="20">
-        <v>12.788835</v>
+        <v>13.475398</v>
       </c>
       <c r="O8" s="20">
-        <v>5.4714427</v>
+        <v>5.769173</v>
       </c>
       <c r="P8" s="12">
         <v>0.42099</v>
@@ -3770,10 +3819,10 @@
         <v>0.7690399834916115</v>
       </c>
       <c r="S8" s="11">
-        <v>78.2378466752572</v>
+        <v>78.23784667525609</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -3793,49 +3842,49 @@
         <v>524.1400146484375</v>
       </c>
       <c r="F9" s="17">
-        <v>0.9592813531991451</v>
+        <v>0.9514109780074654</v>
       </c>
       <c r="G9" s="20">
-        <v>-0.1447427940002023</v>
+        <v>-0.2096896716004668</v>
       </c>
       <c r="H9" s="20">
-        <v>-0.9133820988453079</v>
+        <v>-0.8459922326108509</v>
       </c>
       <c r="I9" s="20">
-        <v>3.042405922684921</v>
+        <v>2.195812652927404</v>
       </c>
       <c r="J9" s="20">
-        <v>2.795912183224905</v>
+        <v>2.796856434510391</v>
       </c>
       <c r="K9" s="20">
-        <v>0</v>
+        <v>1.605257194274964</v>
       </c>
       <c r="L9" s="20">
-        <v>-2.551231927379818</v>
+        <v>-2.554951796211781</v>
       </c>
       <c r="M9" s="20">
-        <v>0.3302762244669857</v>
+        <v>0.3317740615892385</v>
       </c>
       <c r="N9" s="20">
-        <v>36.353783</v>
+        <v>30.490984</v>
       </c>
       <c r="O9" s="20">
-        <v>-210.92924</v>
+        <v>-236.953</v>
       </c>
       <c r="P9" s="12">
         <v>0</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.875</v>
+        <v>0.577</v>
       </c>
       <c r="R9" s="12">
         <v>2.595238758114921</v>
       </c>
       <c r="S9" s="11">
-        <v>63.67345525064787</v>
+        <v>63.67345525313317</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -3843,61 +3892,61 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E10" s="10">
-        <v>255.0899963378906</v>
+        <v>259.2300109863281</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8451905645193203</v>
+        <v>0.8750229780425828</v>
       </c>
       <c r="G10" s="20">
-        <v>0.5236628357643097</v>
+        <v>0.313884107527872</v>
       </c>
       <c r="H10" s="20">
-        <v>-0.7897151172266624</v>
+        <v>0.5379536582452412</v>
       </c>
       <c r="I10" s="20">
-        <v>2.388389082821452</v>
+        <v>0.202940183485447</v>
       </c>
       <c r="J10" s="20">
-        <v>1.887140701262632</v>
+        <v>1.220060560316522</v>
       </c>
       <c r="K10" s="20">
-        <v>0</v>
+        <v>3.531116261499869</v>
       </c>
       <c r="L10" s="20">
-        <v>0.3745808486331713</v>
+        <v>-1.510715199580536</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.6449145560404135</v>
+        <v>0.1631003439959213</v>
       </c>
       <c r="N10" s="20">
-        <v>13.92751</v>
+        <v>23.76077</v>
       </c>
       <c r="O10" s="20">
-        <v>3.090377</v>
+        <v>5.559058</v>
       </c>
       <c r="P10" s="12">
-        <v>0.23452999</v>
+        <v>0.19381</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.531</v>
+        <v>0.108</v>
       </c>
       <c r="R10" s="12">
-        <v>0.5564332553700537</v>
+        <v>0.2891448931981548</v>
       </c>
       <c r="S10" s="11">
-        <v>75.04381051831487</v>
+        <v>76.62974183129113</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -3905,61 +3954,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>38</v>
       </c>
       <c r="E11" s="10">
-        <v>60.04000091552734</v>
+        <v>255.0899963378906</v>
       </c>
       <c r="F11" s="17">
-        <v>0.7073949382145005</v>
+        <v>0.8251866856904495</v>
       </c>
       <c r="G11" s="20">
-        <v>0.643499368213696</v>
+        <v>0.4937473502003348</v>
       </c>
       <c r="H11" s="20">
-        <v>0.6160148797154114</v>
+        <v>-0.7878254537509429</v>
       </c>
       <c r="I11" s="20">
-        <v>3.240547283087039</v>
+        <v>2.423226908404409</v>
       </c>
       <c r="J11" s="20">
-        <v>0.3082166903719963</v>
+        <v>1.88793512058422</v>
       </c>
       <c r="K11" s="20">
-        <v>0</v>
+        <v>0.6899308401855347</v>
       </c>
       <c r="L11" s="20">
-        <v>0.2435022863162283</v>
+        <v>0.37371743288351</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.2876824250430902</v>
+        <v>-0.6444217319555201</v>
       </c>
       <c r="N11" s="20">
-        <v>17.433628</v>
+        <v>14.559931</v>
       </c>
       <c r="O11" s="20">
-        <v>1.765813</v>
+        <v>3.2307048</v>
       </c>
       <c r="P11" s="12">
-        <v>0.10629</v>
+        <v>0.23452999</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.534</v>
+        <v>0.531</v>
       </c>
       <c r="R11" s="12">
-        <v>0.1183560702395035</v>
+        <v>0.5564332553700537</v>
       </c>
       <c r="S11" s="11">
-        <v>56.82077158888354</v>
+        <v>75.04381051862528</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -3967,61 +4016,61 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="10">
+        <v>369.3500061035156</v>
+      </c>
+      <c r="F12" s="17">
+        <v>0.8197914702434592</v>
+      </c>
+      <c r="G12" s="20">
+        <v>1.215230467965422</v>
+      </c>
+      <c r="H12" s="20">
+        <v>-0.1214453608752054</v>
+      </c>
+      <c r="I12" s="20">
+        <v>-0.3758707799348074</v>
+      </c>
+      <c r="J12" s="20">
+        <v>0.5627464652637819</v>
+      </c>
+      <c r="K12" s="20">
+        <v>3.829153559383143</v>
+      </c>
+      <c r="L12" s="20">
+        <v>0.6030540698252209</v>
+      </c>
+      <c r="M12" s="20">
+        <v>-0.0804661143928516</v>
+      </c>
+      <c r="N12" s="20">
+        <v>9.931433999999999</v>
+      </c>
+      <c r="O12" s="20">
+        <v>2.3262038</v>
+      </c>
+      <c r="P12" s="12">
+        <v>0.26511</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0.003</v>
+      </c>
+      <c r="R12" s="12">
+        <v>0.2152546687130332</v>
+      </c>
+      <c r="S12" s="11">
+        <v>51.96562033483278</v>
+      </c>
+      <c r="T12" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="10">
-        <v>230.3600006103516</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0.6809721827427301</v>
-      </c>
-      <c r="G12" s="20">
-        <v>-1.182209499540936</v>
-      </c>
-      <c r="H12" s="20">
-        <v>2.371245910837092</v>
-      </c>
-      <c r="I12" s="20">
-        <v>2.436903283259161</v>
-      </c>
-      <c r="J12" s="20">
-        <v>0.6802953024404149</v>
-      </c>
-      <c r="K12" s="20">
-        <v>0</v>
-      </c>
-      <c r="L12" s="20">
-        <v>-0.1960301003008268</v>
-      </c>
-      <c r="M12" s="20">
-        <v>-0.04204035053693567</v>
-      </c>
-      <c r="N12" s="20">
-        <v>27.468435</v>
-      </c>
-      <c r="O12" s="20">
-        <v>26.95787</v>
-      </c>
-      <c r="P12" s="12">
-        <v>1.17211</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>1.059</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0.2970472917197908</v>
-      </c>
-      <c r="S12" s="11">
-        <v>60.39296241087353</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -4029,61 +4078,61 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="E13" s="10">
-        <v>42.77000045776367</v>
+        <v>67.04000091552734</v>
       </c>
       <c r="F13" s="17">
-        <v>0.6119418766378938</v>
+        <v>0.8046524634875735</v>
       </c>
       <c r="G13" s="20">
-        <v>1.180701740532482</v>
+        <v>1.296202382232963</v>
       </c>
       <c r="H13" s="20">
-        <v>0.5624308546543723</v>
+        <v>-1.353261681376673</v>
       </c>
       <c r="I13" s="20">
-        <v>-0.2812806277733882</v>
+        <v>-0.5780959126470824</v>
       </c>
       <c r="J13" s="20">
-        <v>1.061735628775206</v>
+        <v>1.085526842283418</v>
       </c>
       <c r="K13" s="20">
-        <v>0</v>
+        <v>4.1972917133727</v>
       </c>
       <c r="L13" s="20">
-        <v>-0.3610099303952853</v>
+        <v>0.00664987963049881</v>
       </c>
       <c r="M13" s="20">
-        <v>-0.4092303578838209</v>
+        <v>0.1991930487879585</v>
       </c>
       <c r="N13" s="20">
-        <v>8.974684</v>
+        <v>12.6192465</v>
       </c>
       <c r="O13" s="20">
-        <v>2.1246629</v>
+        <v>1.4678257</v>
       </c>
       <c r="P13" s="12">
-        <v>0.26659</v>
+        <v>-0.20358999</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.092</v>
+        <v>0.046</v>
       </c>
       <c r="R13" s="12">
-        <v>0.3267847498375229</v>
+        <v>0.5358533464375972</v>
       </c>
       <c r="S13" s="11">
-        <v>57.6208553046687</v>
+        <v>55.66966189008534</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -4091,61 +4140,61 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="E14" s="10">
-        <v>467.4599914550781</v>
+        <v>338.4599914550781</v>
       </c>
       <c r="F14" s="17">
-        <v>0.6036048666036268</v>
+        <v>0.7772698887090254</v>
       </c>
       <c r="G14" s="20">
-        <v>-0.9101903600805938</v>
+        <v>-0.3753606373785415</v>
       </c>
       <c r="H14" s="20">
-        <v>2.149067445289344</v>
+        <v>1.463709249725696</v>
       </c>
       <c r="I14" s="20">
-        <v>2.977788239554019</v>
+        <v>1.40880022334584</v>
       </c>
       <c r="J14" s="20">
-        <v>0.682599481891475</v>
+        <v>-0.2341200731129836</v>
       </c>
       <c r="K14" s="20">
-        <v>0</v>
+        <v>4.1972917133727</v>
       </c>
       <c r="L14" s="20">
-        <v>-3.409439608134597</v>
+        <v>0.07416160679393015</v>
       </c>
       <c r="M14" s="20">
-        <v>0.6645433018079338</v>
+        <v>0.3984077633500318</v>
       </c>
       <c r="N14" s="20">
-        <v>17.067236</v>
+        <v>16.97392</v>
       </c>
       <c r="O14" s="20">
-        <v>21.967487</v>
+        <v>6.650031</v>
       </c>
       <c r="P14" s="12">
-        <v>1.30853</v>
+        <v>0.48676</v>
       </c>
       <c r="Q14" s="12">
-        <v>0.438</v>
+        <v>0.242</v>
       </c>
       <c r="R14" s="12">
-        <v>0.9065519122333334</v>
+        <v>0.135998870009276</v>
       </c>
       <c r="S14" s="11">
-        <v>48.28405027473012</v>
+        <v>44.97250667286116</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -4153,61 +4202,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E15" s="10">
-        <v>133.3500061035156</v>
+        <v>335.3099975585938</v>
       </c>
       <c r="F15" s="17">
-        <v>0.5268312173859163</v>
+        <v>0.7763757508527467</v>
       </c>
       <c r="G15" s="20">
-        <v>0.6751790109178482</v>
+        <v>-0.3654991602347105</v>
       </c>
       <c r="H15" s="20">
-        <v>0.295324541990178</v>
+        <v>1.463709249725696</v>
       </c>
       <c r="I15" s="20">
-        <v>0.2863966455848548</v>
+        <v>1.40880022334584</v>
       </c>
       <c r="J15" s="20">
-        <v>0.7879954927062306</v>
+        <v>-0.2592467659346985</v>
       </c>
       <c r="K15" s="20">
-        <v>0</v>
+        <v>4.1972917133727</v>
       </c>
       <c r="L15" s="20">
-        <v>-0.01634449202709099</v>
+        <v>0.09218432064022211</v>
       </c>
       <c r="M15" s="20">
-        <v>0.3846209970904506</v>
+        <v>0.4457507792696405</v>
       </c>
       <c r="N15" s="20">
-        <v>9.331602999999999</v>
+        <v>16.83283</v>
       </c>
       <c r="O15" s="20">
-        <v>3.3175094</v>
+        <v>6.5881405</v>
       </c>
       <c r="P15" s="12">
-        <v>0.29867</v>
+        <v>0.48676</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.176</v>
+        <v>0.242</v>
       </c>
       <c r="R15" s="12">
-        <v>0.1624141463167428</v>
+        <v>0.1262693729675783</v>
       </c>
       <c r="S15" s="11">
-        <v>60.8228199840139</v>
+        <v>44.12846261618915</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -4215,61 +4264,61 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="E16" s="10">
-        <v>208.6000061035156</v>
+        <v>164.4400024414062</v>
       </c>
       <c r="F16" s="17">
-        <v>0.5187595653257109</v>
+        <v>0.7561380880467419</v>
       </c>
       <c r="G16" s="20">
-        <v>0.5557691523136161</v>
+        <v>0.4941985872113094</v>
       </c>
       <c r="H16" s="20">
-        <v>-0.3278930380555804</v>
+        <v>-0.5581494893912904</v>
       </c>
       <c r="I16" s="20">
-        <v>2.293354408551141</v>
+        <v>-0.03241763381358259</v>
       </c>
       <c r="J16" s="20">
-        <v>0.5783480937903147</v>
+        <v>1.391997972412613</v>
       </c>
       <c r="K16" s="20">
-        <v>0</v>
+        <v>3.296722344935419</v>
       </c>
       <c r="L16" s="20">
-        <v>0.748048041149063</v>
+        <v>0.2386970777502335</v>
       </c>
       <c r="M16" s="20">
-        <v>-0.4848736912760586</v>
+        <v>-0.8474984218547166</v>
       </c>
       <c r="N16" s="20">
-        <v>19.409616</v>
+        <v>17.05809</v>
       </c>
       <c r="O16" s="20">
-        <v>2.0853305</v>
+        <v>4.186674</v>
       </c>
       <c r="P16" s="12">
-        <v>0.12231</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.535</v>
+        <v>0.053</v>
       </c>
       <c r="R16" s="12">
-        <v>0.1179728387132282</v>
+        <v>0.3847812251157086</v>
       </c>
       <c r="S16" s="11">
-        <v>64.86600953038234</v>
+        <v>63.60644195751173</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -4277,61 +4326,61 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="E17" s="10">
-        <v>259.2300109863281</v>
+        <v>131.4199981689453</v>
       </c>
       <c r="F17" s="17">
-        <v>0.5173901187278145</v>
+        <v>0.7151380182450069</v>
       </c>
       <c r="G17" s="20">
-        <v>0.343799071956351</v>
+        <v>0.3599925540636538</v>
       </c>
       <c r="H17" s="20">
-        <v>0.538507021326155</v>
+        <v>-0.1244310120248844</v>
       </c>
       <c r="I17" s="20">
-        <v>0.1892091902239575</v>
+        <v>0.4821804333312243</v>
       </c>
       <c r="J17" s="20">
-        <v>1.2196586204066</v>
+        <v>0.4247096137593809</v>
       </c>
       <c r="K17" s="20">
-        <v>0</v>
+        <v>4.1972917133727</v>
       </c>
       <c r="L17" s="20">
-        <v>-1.508013818195181</v>
+        <v>0.1687839734058377</v>
       </c>
       <c r="M17" s="20">
-        <v>0.161508400793549</v>
+        <v>-0.2398081379060042</v>
       </c>
       <c r="N17" s="20">
-        <v>23.421774</v>
+        <v>16.105392</v>
       </c>
       <c r="O17" s="20">
-        <v>5.4897923</v>
+        <v>7.2471595</v>
       </c>
       <c r="P17" s="12">
-        <v>0.19381</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.108</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R17" s="12">
-        <v>0.2891448931981548</v>
+        <v>0.1349857252770952</v>
       </c>
       <c r="S17" s="11">
-        <v>76.62974183127326</v>
+        <v>54.16793908636858</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4339,61 +4388,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E18" s="10">
-        <v>32.63999938964844</v>
+        <v>60.04000091552734</v>
       </c>
       <c r="F18" s="17">
-        <v>0.5077977675202567</v>
+        <v>0.6940547154223843</v>
       </c>
       <c r="G18" s="20">
-        <v>1.188833519944301</v>
+        <v>0.6321397772136792</v>
       </c>
       <c r="H18" s="20">
-        <v>-0.9899924001627183</v>
+        <v>0.6155406581429993</v>
       </c>
       <c r="I18" s="20">
-        <v>-0.3642163190559603</v>
+        <v>2.930171312463986</v>
       </c>
       <c r="J18" s="20">
-        <v>1.624405711820712</v>
+        <v>0.308076137396026</v>
       </c>
       <c r="K18" s="20">
-        <v>0</v>
+        <v>0.8730995961762966</v>
       </c>
       <c r="L18" s="20">
-        <v>-0.4614683745122001</v>
+        <v>0.2425108993694954</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.3992649164499856</v>
+        <v>-0.2872440968436206</v>
       </c>
       <c r="N18" s="20">
-        <v>11.648855</v>
+        <v>17.710915</v>
       </c>
       <c r="O18" s="20">
-        <v>-305.2</v>
+        <v>1.7938988</v>
       </c>
       <c r="P18" s="12">
-        <v>0</v>
+        <v>0.10629</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.125</v>
+        <v>0.534</v>
       </c>
       <c r="R18" s="12">
-        <v>0.7252534861688946</v>
+        <v>0.1183559907738323</v>
       </c>
       <c r="S18" s="11">
-        <v>66.4267070183985</v>
+        <v>56.82077158947367</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4401,46 +4450,46 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E19" s="10">
         <v>259.5700073242188</v>
       </c>
       <c r="F19" s="17">
-        <v>0.5023791025545321</v>
+        <v>0.663117882082194</v>
       </c>
       <c r="G19" s="20">
-        <v>1.297185531255487</v>
+        <v>1.286238812250283</v>
       </c>
       <c r="H19" s="20">
-        <v>0.1644382972194991</v>
+        <v>0.1653558428199913</v>
       </c>
       <c r="I19" s="20">
-        <v>-0.04929908647574074</v>
+        <v>-0.05063264711205382</v>
       </c>
       <c r="J19" s="20">
-        <v>0.5138830487058349</v>
+        <v>0.5137962823838743</v>
       </c>
       <c r="K19" s="20">
-        <v>0</v>
+        <v>1.858278441957119</v>
       </c>
       <c r="L19" s="20">
-        <v>0.5315929654268812</v>
+        <v>0.5308828396445926</v>
       </c>
       <c r="M19" s="20">
-        <v>0.01449378971364151</v>
+        <v>0.01519947010572145</v>
       </c>
       <c r="N19" s="20">
-        <v>5.156936</v>
+        <v>5.1976376</v>
       </c>
       <c r="O19" s="20">
-        <v>2.0881312</v>
+        <v>2.0800378</v>
       </c>
       <c r="P19" s="12">
         <v>0.46113998</v>
@@ -4452,10 +4501,10 @@
         <v>0.2340966911889795</v>
       </c>
       <c r="S19" s="11">
-        <v>51.9603537028937</v>
+        <v>51.96035369550701</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -4463,61 +4512,61 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="10">
-        <v>30.64999961853027</v>
+        <v>52</v>
       </c>
       <c r="F20" s="17">
-        <v>0.4961643561590026</v>
+        <v>0.6255056894289205</v>
       </c>
       <c r="G20" s="20">
-        <v>0.5174384367757483</v>
+        <v>0.5218225520995097</v>
       </c>
       <c r="H20" s="20">
-        <v>0.7489704413559825</v>
+        <v>-0.5332485103967138</v>
       </c>
       <c r="I20" s="20">
-        <v>-0.1869358474983134</v>
+        <v>2.225163086097977</v>
       </c>
       <c r="J20" s="20">
-        <v>0.8098308727045063</v>
+        <v>1.578444247606777</v>
       </c>
       <c r="K20" s="20">
-        <v>0</v>
+        <v>0.3256630316615335</v>
       </c>
       <c r="L20" s="20">
-        <v>0.2068135536674096</v>
+        <v>-1.096131212992601</v>
       </c>
       <c r="M20" s="20">
-        <v>-0.1626755762279338</v>
+        <v>-0.6557985274646984</v>
       </c>
       <c r="N20" s="20">
-        <v>17.827587</v>
+        <v>26.804123</v>
       </c>
       <c r="O20" s="20">
-        <v>6.9959407</v>
+        <v>2.7206612</v>
       </c>
       <c r="P20" s="12">
-        <v>0.41944</v>
+        <v>0.10936</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.063</v>
+        <v>0.337</v>
       </c>
       <c r="R20" s="12">
-        <v>0.368867603719909</v>
+        <v>1.484071106654971</v>
       </c>
       <c r="S20" s="11">
-        <v>61.58963480299711</v>
+        <v>48.79187842694703</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -4525,61 +4574,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="E21" s="10">
-        <v>52</v>
+        <v>258.510009765625</v>
       </c>
       <c r="F21" s="17">
-        <v>0.4852761372604519</v>
+        <v>0.6227350145405641</v>
       </c>
       <c r="G21" s="20">
-        <v>0.2621966121724467</v>
+        <v>-0.04482148267622166</v>
       </c>
       <c r="H21" s="20">
-        <v>-0.6937749999258802</v>
+        <v>0.1590141648378586</v>
       </c>
       <c r="I21" s="20">
-        <v>1.355635681465038</v>
+        <v>1.035672297744961</v>
       </c>
       <c r="J21" s="20">
-        <v>1.577856479276285</v>
+        <v>0.1288224939310594</v>
       </c>
       <c r="K21" s="20">
-        <v>0</v>
+        <v>4.1972917133727</v>
       </c>
       <c r="L21" s="20">
-        <v>-1.093834192637368</v>
+        <v>-0.4340688696512446</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.6554856223106126</v>
+        <v>-0.18105295414046</v>
       </c>
       <c r="N21" s="20">
-        <v>48.887848</v>
+        <v>20.797264</v>
       </c>
       <c r="O21" s="20">
-        <v>2.7368805</v>
+        <v>5.0533667</v>
       </c>
       <c r="P21" s="12">
-        <v>0.06315</v>
+        <v>0.30558002</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.4</v>
+        <v>0.196</v>
       </c>
       <c r="R21" s="12">
-        <v>1.484071106654971</v>
+        <v>0.2124665898657911</v>
       </c>
       <c r="S21" s="11">
-        <v>48.79187842694628</v>
+        <v>49.54908461556447</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -4587,46 +4636,46 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E22" s="10">
         <v>126.75</v>
       </c>
       <c r="F22" s="17">
-        <v>0.4709509819692596</v>
+        <v>0.6052465179692325</v>
       </c>
       <c r="G22" s="20">
-        <v>0.3539469970578056</v>
+        <v>0.3314207580374121</v>
       </c>
       <c r="H22" s="20">
-        <v>0.5048903150642245</v>
+        <v>0.5050654897521694</v>
       </c>
       <c r="I22" s="20">
-        <v>0.5513159710787306</v>
+        <v>0.5229426848176244</v>
       </c>
       <c r="J22" s="20">
-        <v>0.8021435036982881</v>
+        <v>0.8023367939782938</v>
       </c>
       <c r="K22" s="20">
-        <v>0</v>
+        <v>1.6471686892898</v>
       </c>
       <c r="L22" s="20">
-        <v>0.02424928660192158</v>
+        <v>0.02304384429526537</v>
       </c>
       <c r="M22" s="20">
-        <v>-0.3410706395150904</v>
+        <v>-0.3407234610698928</v>
       </c>
       <c r="N22" s="20">
-        <v>15.843312</v>
+        <v>16.146498</v>
       </c>
       <c r="O22" s="20">
-        <v>3.939749</v>
+        <v>4.015142</v>
       </c>
       <c r="P22" s="12">
         <v>0.30667</v>
@@ -4638,10 +4687,10 @@
         <v>0.3211381777628204</v>
       </c>
       <c r="S22" s="11">
-        <v>56.24137683247652</v>
+        <v>56.24137683247642</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -4649,61 +4698,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="E23" s="10">
-        <v>145.1900024414062</v>
+        <v>1038.609985351562</v>
       </c>
       <c r="F23" s="17">
-        <v>0.4673517845414921</v>
+        <v>0.5567895557649366</v>
       </c>
       <c r="G23" s="20">
-        <v>0.6253387141465833</v>
+        <v>0.3667190394925228</v>
       </c>
       <c r="H23" s="20">
-        <v>0.4653924404191751</v>
+        <v>0.8230717495135815</v>
       </c>
       <c r="I23" s="20">
-        <v>1.456491760882698</v>
+        <v>0.9154597556552251</v>
       </c>
       <c r="J23" s="20">
-        <v>0.23363769757397</v>
+        <v>0.1690881460517345</v>
       </c>
       <c r="K23" s="20">
-        <v>0</v>
+        <v>1.663726316949982</v>
       </c>
       <c r="L23" s="20">
-        <v>0.2652210071994496</v>
+        <v>0.07221679196558524</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.09259918011709681</v>
+        <v>0.1604507975141698</v>
       </c>
       <c r="N23" s="20">
-        <v>11.1643305</v>
+        <v>16.02546</v>
       </c>
       <c r="O23" s="20">
-        <v>2.3641071</v>
+        <v>2.8687</v>
       </c>
       <c r="P23" s="12">
-        <v>0.22507</v>
+        <v>0.16902</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.587</v>
+        <v>0.425</v>
       </c>
       <c r="R23" s="12">
-        <v>0.1217045734658417</v>
+        <v>0.2762004315652837</v>
       </c>
       <c r="S23" s="11">
-        <v>50.57582483695785</v>
+        <v>52.01914901379936</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -4711,61 +4760,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E24" s="10">
-        <v>66.81999969482422</v>
+        <v>219.6000061035156</v>
       </c>
       <c r="F24" s="17">
-        <v>0.4625333969196003</v>
+        <v>0.552946378603798</v>
       </c>
       <c r="G24" s="20">
-        <v>0.485926067078946</v>
+        <v>0.5809437263948974</v>
       </c>
       <c r="H24" s="20">
-        <v>0.6577947021877067</v>
+        <v>-0.6585101921976751</v>
       </c>
       <c r="I24" s="20">
-        <v>0.2072105134374404</v>
+        <v>4.120745224686987</v>
       </c>
       <c r="J24" s="20">
-        <v>0.6287773174405684</v>
+        <v>0.2214005476520888</v>
       </c>
       <c r="K24" s="20">
-        <v>0</v>
+        <v>0.6040381466983412</v>
       </c>
       <c r="L24" s="20">
-        <v>0.589841863884591</v>
+        <v>0.5051479593581576</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.3803651692998145</v>
+        <v>-0.3443750415658914</v>
       </c>
       <c r="N24" s="20">
-        <v>14.762749</v>
+        <v>12.092511</v>
       </c>
       <c r="O24" s="20">
-        <v>6.0942793</v>
+        <v>1.3082409</v>
       </c>
       <c r="P24" s="12">
-        <v>0.46598998</v>
+        <v>0.09031</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.057</v>
+        <v>11.11</v>
       </c>
       <c r="R24" s="12">
-        <v>0.1323774878225439</v>
+        <v>0.1790605320512837</v>
       </c>
       <c r="S24" s="11">
-        <v>56.57200070093251</v>
+        <v>56.18672088731974</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -4773,61 +4822,61 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="E25" s="10">
-        <v>437.2300109863281</v>
+        <v>230.3600006103516</v>
       </c>
       <c r="F25" s="17">
-        <v>0.4614217011930919</v>
+        <v>0.54805248083314</v>
       </c>
       <c r="G25" s="20">
-        <v>-0.2430849524702366</v>
+        <v>-1.255664189485384</v>
       </c>
       <c r="H25" s="20">
-        <v>1.236456916976443</v>
+        <v>2.368358787986747</v>
       </c>
       <c r="I25" s="20">
-        <v>-0.09520234004633138</v>
+        <v>2.430954222251415</v>
       </c>
       <c r="J25" s="20">
-        <v>0.9553481158818945</v>
+        <v>0.6805355925506037</v>
       </c>
       <c r="K25" s="20">
-        <v>0</v>
+        <v>-0.308183652204804</v>
       </c>
       <c r="L25" s="20">
-        <v>0.6799437238193978</v>
+        <v>-0.1974506000229282</v>
       </c>
       <c r="M25" s="20">
-        <v>-0.8238442801345791</v>
+        <v>-0.04115496077176295</v>
       </c>
       <c r="N25" s="20">
-        <v>26.875078</v>
+        <v>29.159492</v>
       </c>
       <c r="O25" s="20">
-        <v>20.000925</v>
+        <v>24.291891</v>
       </c>
       <c r="P25" s="12">
-        <v>0.91473</v>
+        <v>1.17211</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.095</v>
+        <v>1.059</v>
       </c>
       <c r="R25" s="12">
-        <v>0.1991076631844904</v>
+        <v>0.2970472917197908</v>
       </c>
       <c r="S25" s="11">
-        <v>62.51462135740006</v>
+        <v>60.39296241086813</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -4835,61 +4884,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="E26" s="10">
-        <v>217.7200012207031</v>
+        <v>185.5899963378906</v>
       </c>
       <c r="F26" s="17">
-        <v>0.4442024974016189</v>
+        <v>0.522421941123522</v>
       </c>
       <c r="G26" s="20">
-        <v>0.360549156407083</v>
+        <v>-0.3904668641526476</v>
       </c>
       <c r="H26" s="20">
-        <v>0.7749355815613619</v>
+        <v>1.359179679828218</v>
       </c>
       <c r="I26" s="20">
-        <v>0.3996363456297529</v>
+        <v>0.4411015820383316</v>
       </c>
       <c r="J26" s="20">
-        <v>0.4300839288433567</v>
+        <v>1.161291153425794</v>
       </c>
       <c r="K26" s="20">
-        <v>0</v>
+        <v>0.4876173272126874</v>
       </c>
       <c r="L26" s="20">
-        <v>0.5433523486303039</v>
+        <v>-0.1017542140299229</v>
       </c>
       <c r="M26" s="20">
-        <v>0.005246279706640156</v>
+        <v>-0.8708637844601874</v>
       </c>
       <c r="N26" s="20">
-        <v>17.362167</v>
+        <v>26.250353</v>
       </c>
       <c r="O26" s="20">
-        <v>3.1676524</v>
+        <v>26.924416</v>
       </c>
       <c r="P26" s="12">
-        <v>0.17969999</v>
+        <v>1.14818</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.28</v>
+        <v>0.299</v>
       </c>
       <c r="R26" s="12">
-        <v>0.3732761020184954</v>
+        <v>0.8514465022793682</v>
       </c>
       <c r="S26" s="11">
-        <v>54.99960803943708</v>
+        <v>49.08437153264291</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -4897,61 +4946,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E27" s="10">
-        <v>416.3699951171875</v>
+        <v>220.8300018310547</v>
       </c>
       <c r="F27" s="17">
-        <v>0.4441834002930676</v>
+        <v>0.520678142547652</v>
       </c>
       <c r="G27" s="20">
-        <v>0.3086538886996134</v>
+        <v>0.2276945080429548</v>
       </c>
       <c r="H27" s="20">
-        <v>0.7061485197094312</v>
+        <v>0.03119877719549098</v>
       </c>
       <c r="I27" s="20">
-        <v>-0.09806550872946435</v>
+        <v>-0.8985721544356027</v>
       </c>
       <c r="J27" s="20">
-        <v>0.82384710416048</v>
+        <v>0.5872600250002363</v>
       </c>
       <c r="K27" s="20">
-        <v>0</v>
+        <v>3.376923353914425</v>
       </c>
       <c r="L27" s="20">
-        <v>0.574372473548289</v>
+        <v>-0.07384581612384766</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.6183749956204355</v>
+        <v>-0.1552439851271158</v>
       </c>
       <c r="N27" s="20">
-        <v>24.571085</v>
+        <v>39.2238</v>
       </c>
       <c r="O27" s="20">
-        <v>7.5607543</v>
+        <v>1.730507</v>
       </c>
       <c r="P27" s="12">
-        <v>0.29215</v>
+        <v>0.04575</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.215</v>
+        <v>0.034</v>
       </c>
       <c r="R27" s="12">
-        <v>0.3243320712476749</v>
+        <v>0.1945151060942716</v>
       </c>
       <c r="S27" s="11">
-        <v>60.61633471760578</v>
+        <v>57.98177418064045</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -4959,61 +5008,61 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E28" s="10">
-        <v>109.2900009155273</v>
+        <v>66.81999969482422</v>
       </c>
       <c r="F28" s="17">
-        <v>0.4329767764264066</v>
+        <v>0.5052905423289454</v>
       </c>
       <c r="G28" s="20">
-        <v>0.08362146264365951</v>
+        <v>0.4785242056074159</v>
       </c>
       <c r="H28" s="20">
-        <v>1.223174340776804</v>
+        <v>0.6574599095763384</v>
       </c>
       <c r="I28" s="20">
-        <v>0.1140666249819975</v>
+        <v>0.2335665909722698</v>
       </c>
       <c r="J28" s="20">
-        <v>0.4829374460462151</v>
+        <v>0.628830058691316</v>
       </c>
       <c r="K28" s="20">
-        <v>0</v>
+        <v>0.8084213631287113</v>
       </c>
       <c r="L28" s="20">
-        <v>0.8786502773530303</v>
+        <v>0.5891886061448869</v>
       </c>
       <c r="M28" s="20">
-        <v>-0.4843388437269447</v>
+        <v>-0.3800619607670498</v>
       </c>
       <c r="N28" s="20">
-        <v>20.065575</v>
+        <v>14.718061</v>
       </c>
       <c r="O28" s="20">
-        <v>4.333084</v>
+        <v>6.116247</v>
       </c>
       <c r="P28" s="12">
-        <v>0.20273</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.209</v>
+        <v>0.057</v>
       </c>
       <c r="R28" s="12">
-        <v>0.1551191514108801</v>
+        <v>0.1323774878225439</v>
       </c>
       <c r="S28" s="11">
-        <v>53.51342061785085</v>
+        <v>56.57200070071893</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -5021,61 +5070,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="E29" s="10">
-        <v>128.0899963378906</v>
+        <v>95.80000305175781</v>
       </c>
       <c r="F29" s="17">
-        <v>0.4314710720958842</v>
+        <v>0.5018935231674446</v>
       </c>
       <c r="G29" s="20">
-        <v>0.4655239786150748</v>
+        <v>-0.6233680543607623</v>
       </c>
       <c r="H29" s="20">
-        <v>0.7821728970785009</v>
+        <v>-1.136990927851701</v>
       </c>
       <c r="I29" s="20">
-        <v>-0.1884518302174612</v>
+        <v>0.5264142543422116</v>
       </c>
       <c r="J29" s="20">
-        <v>1.019478983803299</v>
+        <v>1.110541736797623</v>
       </c>
       <c r="K29" s="20">
-        <v>0</v>
+        <v>4.1972917133727</v>
       </c>
       <c r="L29" s="20">
-        <v>-0.6022116533208066</v>
+        <v>-2.514098104654919</v>
       </c>
       <c r="M29" s="20">
-        <v>-1.001415614486135</v>
+        <v>0.7173156951214641</v>
       </c>
       <c r="N29" s="20">
-        <v>16.68579</v>
+        <v>46.910885</v>
       </c>
       <c r="O29" s="20">
-        <v>3.8455532</v>
+        <v>5.5187516</v>
       </c>
       <c r="P29" s="12">
-        <v>0.25905</v>
+        <v>-0.10715</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.151</v>
+        <v>0.254</v>
       </c>
       <c r="R29" s="12">
-        <v>0.1063406141507248</v>
+        <v>1.206356681062127</v>
       </c>
       <c r="S29" s="11">
-        <v>60.72188668631097</v>
+        <v>51.74428988479696</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -5083,61 +5132,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="10">
-        <v>185.5899963378906</v>
+        <v>39.59000015258789</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4295195471860156</v>
+        <v>0.4824297428111422</v>
       </c>
       <c r="G30" s="20">
-        <v>-0.417370639505269</v>
+        <v>0.09785741135882757</v>
       </c>
       <c r="H30" s="20">
-        <v>1.256854922578299</v>
+        <v>-0.81219220040201</v>
       </c>
       <c r="I30" s="20">
-        <v>-0.2043202764057594</v>
+        <v>3.920900829953943</v>
       </c>
       <c r="J30" s="20">
-        <v>1.160286410851864</v>
+        <v>0.188999388927631</v>
       </c>
       <c r="K30" s="20">
-        <v>0</v>
+        <v>3.385719593608896</v>
       </c>
       <c r="L30" s="20">
-        <v>-0.1004270509789687</v>
+        <v>-3.413048273912248</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.8702642941766345</v>
+        <v>-0.694089920514268</v>
       </c>
       <c r="N30" s="20">
-        <v>29.498423</v>
+        <v>12.144172</v>
       </c>
       <c r="O30" s="20">
-        <v>27.131872</v>
+        <v>2.3688147</v>
       </c>
       <c r="P30" s="12">
-        <v>1.06734</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.125</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R30" s="12">
-        <v>0.8514465022793682</v>
+        <v>0.2644522781181176</v>
       </c>
       <c r="S30" s="11">
-        <v>49.0843715326604</v>
+        <v>62.65598266458546</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -5145,61 +5194,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="E31" s="10">
-        <v>401.5400085449219</v>
+        <v>32.63999938964844</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4180834521117541</v>
+        <v>0.4812241609106595</v>
       </c>
       <c r="G31" s="20">
-        <v>0.3994592812726025</v>
+        <v>1.115176779328165</v>
       </c>
       <c r="H31" s="20">
-        <v>-1.055543569665776</v>
+        <v>-0.9874044575767369</v>
       </c>
       <c r="I31" s="20">
-        <v>0.1877082092453494</v>
+        <v>-0.3840221445724293</v>
       </c>
       <c r="J31" s="20">
-        <v>1.412759337688216</v>
+        <v>1.625577115413821</v>
       </c>
       <c r="K31" s="20">
+        <v>0.4074163182336814</v>
+      </c>
+      <c r="L31" s="20">
+        <v>-0.4631480199946686</v>
+      </c>
+      <c r="M31" s="20">
+        <v>-0.3986867913924674</v>
+      </c>
+      <c r="N31" s="20">
+        <v>12.458015</v>
+      </c>
+      <c r="O31" s="20">
+        <v>-320</v>
+      </c>
+      <c r="P31" s="12">
         <v>0</v>
       </c>
-      <c r="L31" s="20">
-        <v>0.2008644189786908</v>
-      </c>
-      <c r="M31" s="20">
-        <v>0.1280906375759774</v>
-      </c>
-      <c r="N31" s="20">
-        <v>37.178402</v>
-      </c>
-      <c r="O31" s="20">
-        <v>2.4096098</v>
-      </c>
-      <c r="P31" s="12">
-        <v>0.06893000000000001</v>
-      </c>
       <c r="Q31" s="12">
-        <v>0.262</v>
+        <v>0.125</v>
       </c>
       <c r="R31" s="12">
-        <v>1.258060463786058</v>
+        <v>0.7252534861688946</v>
       </c>
       <c r="S31" s="11">
-        <v>59.41208191349453</v>
+        <v>66.42670701840595</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -5207,61 +5256,61 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="E32" s="10">
-        <v>369.3500061035156</v>
+        <v>362.739990234375</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4118625809126026</v>
+        <v>0.4757791556353333</v>
       </c>
       <c r="G32" s="20">
-        <v>1.231857100506108</v>
+        <v>0.09769025453656566</v>
       </c>
       <c r="H32" s="20">
-        <v>-0.1224591875970045</v>
+        <v>-0.2373803208952873</v>
       </c>
       <c r="I32" s="20">
-        <v>-0.3829551400317068</v>
+        <v>0.4704496970046058</v>
       </c>
       <c r="J32" s="20">
-        <v>0.5628512984292272</v>
+        <v>1.550509301618796</v>
       </c>
       <c r="K32" s="20">
-        <v>0</v>
+        <v>1.706672663693578</v>
       </c>
       <c r="L32" s="20">
-        <v>0.6036938040006817</v>
+        <v>-1.627723688728139</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.08104050797658555</v>
+        <v>-1.539491216795537</v>
       </c>
       <c r="N32" s="20">
-        <v>9.919549</v>
+        <v>33.248394</v>
       </c>
       <c r="O32" s="20">
-        <v>2.3296678</v>
+        <v>5.0043454</v>
       </c>
       <c r="P32" s="12">
-        <v>0.26511</v>
+        <v>0.15286</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.003</v>
+        <v>0.204</v>
       </c>
       <c r="R32" s="12">
-        <v>0.2152546687130332</v>
+        <v>0.6514454828772971</v>
       </c>
       <c r="S32" s="11">
-        <v>51.96562033432203</v>
+        <v>60.70089865252772</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -5269,61 +5318,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="E33" s="10">
-        <v>1038.609985351562</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4098942413876117</v>
+        <v>0.4684777520956978</v>
       </c>
       <c r="G33" s="20">
-        <v>0.3749907256319778</v>
+        <v>1.1788603618118</v>
       </c>
       <c r="H33" s="20">
-        <v>0.8238683571645536</v>
+        <v>0.561859549662265</v>
       </c>
       <c r="I33" s="20">
-        <v>0.9342898423755277</v>
+        <v>-0.2890980177519417</v>
       </c>
       <c r="J33" s="20">
-        <v>0.1693157471905421</v>
+        <v>1.062414648139563</v>
       </c>
       <c r="K33" s="20">
-        <v>0</v>
+        <v>-0.5746579723608561</v>
       </c>
       <c r="L33" s="20">
-        <v>0.07337427384825664</v>
+        <v>-0.3625914989144247</v>
       </c>
       <c r="M33" s="20">
-        <v>0.1595437479425359</v>
+        <v>-0.4089348378111903</v>
       </c>
       <c r="N33" s="20">
-        <v>16.078215</v>
+        <v>9.023208</v>
       </c>
       <c r="O33" s="20">
-        <v>2.8559394</v>
+        <v>2.1361504</v>
       </c>
       <c r="P33" s="12">
-        <v>0.16902</v>
+        <v>0.26659</v>
       </c>
       <c r="Q33" s="12">
-        <v>0.425</v>
+        <v>0.092</v>
       </c>
       <c r="R33" s="12">
-        <v>0.2762003358535221</v>
+        <v>0.3267847498375229</v>
       </c>
       <c r="S33" s="11">
-        <v>52.0191490011484</v>
+        <v>57.62085530467043</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -5331,61 +5380,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>130</v>
+        <v>3</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="E34" s="10">
-        <v>68.87999725341797</v>
+        <v>467.4599914550781</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4098498353116549</v>
+        <v>0.4615738198953969</v>
       </c>
       <c r="G34" s="20">
-        <v>0.5493403711834062</v>
+        <v>-0.9800881674162824</v>
       </c>
       <c r="H34" s="20">
-        <v>1.843609490179893</v>
+        <v>2.147104391138658</v>
       </c>
       <c r="I34" s="20">
-        <v>-0.6338771958527055</v>
+        <v>2.675284350851072</v>
       </c>
       <c r="J34" s="20">
-        <v>-0.1643725679524307</v>
+        <v>0.6826313920476575</v>
       </c>
       <c r="K34" s="20">
-        <v>0</v>
+        <v>-0.2197038293957071</v>
       </c>
       <c r="L34" s="20">
-        <v>0.3880640489267553</v>
+        <v>-3.413048273912248</v>
       </c>
       <c r="M34" s="20">
-        <v>0.7028089608481835</v>
+        <v>0.6660311338869707</v>
       </c>
       <c r="N34" s="20">
-        <v>14.242739</v>
+        <v>17.358335</v>
       </c>
       <c r="O34" s="20">
-        <v>-42.95995</v>
+        <v>22.350464</v>
       </c>
       <c r="P34" s="12">
-        <v>0</v>
+        <v>1.30853</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.012</v>
+        <v>0.438</v>
       </c>
       <c r="R34" s="12">
-        <v>0.06873432320828665</v>
+        <v>0.9065519122333334</v>
       </c>
       <c r="S34" s="11">
-        <v>51.9012134476565</v>
+        <v>48.28405027473934</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -5393,61 +5442,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="E35" s="10">
-        <v>164.4400024414062</v>
+        <v>208.6000061035156</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4096970059966824</v>
+        <v>0.4346747015646415</v>
       </c>
       <c r="G35" s="20">
-        <v>0.503970173929344</v>
+        <v>0.5306330587817526</v>
       </c>
       <c r="H35" s="20">
-        <v>-0.5594935974905421</v>
+        <v>-0.3271612979466518</v>
       </c>
       <c r="I35" s="20">
-        <v>-0.04611621933418467</v>
+        <v>2.322186162377909</v>
       </c>
       <c r="J35" s="20">
-        <v>1.391192367329199</v>
+        <v>0.5784449720178412</v>
       </c>
       <c r="K35" s="20">
-        <v>0</v>
+        <v>-0.1695135205507808</v>
       </c>
       <c r="L35" s="20">
-        <v>0.2396921844760427</v>
+        <v>0.7475492391306515</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.8473738720702306</v>
+        <v>-0.4844610133687292</v>
       </c>
       <c r="N35" s="20">
-        <v>16.927385</v>
+        <v>20.076998</v>
       </c>
       <c r="O35" s="20">
-        <v>4.154594</v>
+        <v>2.1549587</v>
       </c>
       <c r="P35" s="12">
-        <v>0.26408002</v>
+        <v>0.12231</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.053</v>
+        <v>0.535</v>
       </c>
       <c r="R35" s="12">
-        <v>0.3847812251157086</v>
+        <v>0.1179728387132282</v>
       </c>
       <c r="S35" s="11">
-        <v>63.6064420107626</v>
+        <v>64.86600952846281</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -5455,61 +5504,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="E36" s="10">
-        <v>134.2599945068359</v>
+        <v>217.7200012207031</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4035996465917915</v>
+        <v>0.4227496572368312</v>
       </c>
       <c r="G36" s="20">
-        <v>0.5374978389243423</v>
+        <v>0.3451625228080399</v>
       </c>
       <c r="H36" s="20">
-        <v>-0.1381941298720871</v>
+        <v>0.7739793579701058</v>
       </c>
       <c r="I36" s="20">
-        <v>0.8104316467241883</v>
+        <v>0.3853148937972363</v>
       </c>
       <c r="J36" s="20">
-        <v>0.7327362015311909</v>
+        <v>0.4301638300727013</v>
       </c>
       <c r="K36" s="20">
-        <v>0</v>
+        <v>0.3013440160356414</v>
       </c>
       <c r="L36" s="20">
-        <v>0.4091735696833689</v>
+        <v>0.5426537034617692</v>
       </c>
       <c r="M36" s="20">
-        <v>-0.5610662567356174</v>
+        <v>0.006032041533124199</v>
       </c>
       <c r="N36" s="20">
-        <v>17.128778</v>
+        <v>17.572235</v>
       </c>
       <c r="O36" s="20">
-        <v>2.396272</v>
+        <v>3.211162</v>
       </c>
       <c r="P36" s="12">
-        <v>0.1418</v>
+        <v>0.17969999</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.355</v>
+        <v>0.28</v>
       </c>
       <c r="R36" s="12">
-        <v>0.1630641606621228</v>
+        <v>0.3732761020184954</v>
       </c>
       <c r="S36" s="11">
-        <v>63.20133407819568</v>
+        <v>54.99960803944877</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -5517,61 +5566,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E37" s="10">
-        <v>409.3800048828125</v>
+        <v>827.719970703125</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4004087232733701</v>
+        <v>0.4189457412911765</v>
       </c>
       <c r="G37" s="20">
-        <v>-0.9739831881979379</v>
+        <v>0.1366671162081818</v>
       </c>
       <c r="H37" s="20">
-        <v>-0.4329824755904195</v>
+        <v>0.1794925664991855</v>
       </c>
       <c r="I37" s="20">
-        <v>4.17055141824732</v>
+        <v>-0.2394962708042926</v>
       </c>
       <c r="J37" s="20">
-        <v>0.5630701811550737</v>
+        <v>0.8187548832713843</v>
       </c>
       <c r="K37" s="20">
-        <v>0</v>
+        <v>1.442268046995049</v>
       </c>
       <c r="L37" s="20">
-        <v>0.6698539927386995</v>
+        <v>0.5301391500210495</v>
       </c>
       <c r="M37" s="20">
-        <v>-0.3651698660614312</v>
+        <v>-0.7616312850977612</v>
       </c>
       <c r="N37" s="20">
-        <v>105.25127</v>
+        <v>20.49319</v>
       </c>
       <c r="O37" s="20">
-        <v>2.680677</v>
+        <v>2.6184473</v>
       </c>
       <c r="P37" s="12">
-        <v>0.019199999</v>
+        <v>0.14043</v>
       </c>
       <c r="Q37" s="12">
-        <v>1.134</v>
+        <v>0.167</v>
       </c>
       <c r="R37" s="12">
-        <v>0.3531433639198394</v>
+        <v>0.09220672105083549</v>
       </c>
       <c r="S37" s="11">
-        <v>53.59089360913294</v>
+        <v>60.53735125037876</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -5579,61 +5628,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E38" s="10">
-        <v>178.2899932861328</v>
+        <v>437.2300109863281</v>
       </c>
       <c r="F38" s="17">
-        <v>0.3922356294151208</v>
+        <v>0.3985641885542739</v>
       </c>
       <c r="G38" s="20">
-        <v>0.5394709098351904</v>
+        <v>-0.2804627171735288</v>
       </c>
       <c r="H38" s="20">
-        <v>0.5670326786398533</v>
+        <v>1.236068066008634</v>
       </c>
       <c r="I38" s="20">
-        <v>-0.04744840355762995</v>
+        <v>-0.09373645267036328</v>
       </c>
       <c r="J38" s="20">
-        <v>0.4208250405291875</v>
+        <v>0.9557073908014219</v>
       </c>
       <c r="K38" s="20">
-        <v>0</v>
+        <v>-0.007559224999626784</v>
       </c>
       <c r="L38" s="20">
-        <v>0.8387869667527692</v>
+        <v>0.6793784319733565</v>
       </c>
       <c r="M38" s="20">
-        <v>-0.1811566034445488</v>
+        <v>-0.8239697975963599</v>
       </c>
       <c r="N38" s="20">
-        <v>15.65096</v>
+        <v>27.17402</v>
       </c>
       <c r="O38" s="20">
-        <v>2.7135465</v>
+        <v>20.223404</v>
       </c>
       <c r="P38" s="12">
-        <v>0.18416001</v>
+        <v>0.91473</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.151</v>
+        <v>0.095</v>
       </c>
       <c r="R38" s="12">
-        <v>0.1811596730110814</v>
+        <v>0.1991076631844904</v>
       </c>
       <c r="S38" s="11">
-        <v>53.93681336066579</v>
+        <v>62.51462135710453</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -5641,61 +5690,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="E39" s="10">
-        <v>199.2200012207031</v>
+        <v>122.1100006103516</v>
       </c>
       <c r="F39" s="17">
-        <v>0.3899535621230157</v>
+        <v>0.3894543814026363</v>
       </c>
       <c r="G39" s="20">
-        <v>0.6294950918963452</v>
+        <v>-1.586610271874681</v>
       </c>
       <c r="H39" s="20">
-        <v>-0.04460905216459961</v>
+        <v>1.32587516746117</v>
       </c>
       <c r="I39" s="20">
-        <v>1.609810865818413</v>
+        <v>0.4276315627072161</v>
       </c>
       <c r="J39" s="20">
-        <v>0.2180435774304511</v>
+        <v>1.164955143632103</v>
       </c>
       <c r="K39" s="20">
-        <v>0</v>
+        <v>1.634750468544663</v>
       </c>
       <c r="L39" s="20">
-        <v>0.2757628466792496</v>
+        <v>-2.390943846127985</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.07440580173104963</v>
+        <v>0.2242634841032342</v>
       </c>
       <c r="N39" s="20">
-        <v>37.579845</v>
+        <v>54.030975</v>
       </c>
       <c r="O39" s="20">
-        <v>1.4633226</v>
+        <v>11.579896</v>
       </c>
       <c r="P39" s="12">
-        <v>0.034930002</v>
+        <v>0.23618999</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.525</v>
+        <v>0.323</v>
       </c>
       <c r="R39" s="12">
-        <v>0.1156468921149059</v>
+        <v>0.5839928189273125</v>
       </c>
       <c r="S39" s="11">
-        <v>48.64144785651807</v>
+        <v>65.9432414498592</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -5703,61 +5752,61 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="E40" s="10">
-        <v>122.0199966430664</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3808036829189749</v>
+        <v>0.3807072185814189</v>
       </c>
       <c r="G40" s="20">
-        <v>1.209298447018494</v>
+        <v>0.5193752875190029</v>
       </c>
       <c r="H40" s="20">
-        <v>-0.6480111018734195</v>
+        <v>0.748394208904259</v>
       </c>
       <c r="I40" s="20">
-        <v>0.1426763443862438</v>
+        <v>-0.1830681180986245</v>
       </c>
       <c r="J40" s="20">
-        <v>0.5604251780970326</v>
+        <v>0.8101823759526935</v>
       </c>
       <c r="K40" s="20">
-        <v>0</v>
+        <v>-0.4722076512134807</v>
       </c>
       <c r="L40" s="20">
-        <v>1.055835275761357</v>
+        <v>0.2057863477358395</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.3078750951037435</v>
+        <v>-0.1619196286395165</v>
       </c>
       <c r="N40" s="20">
-        <v>10.860381</v>
+        <v>17.923977</v>
       </c>
       <c r="O40" s="20">
-        <v>1.3095953</v>
+        <v>6.912494</v>
       </c>
       <c r="P40" s="12">
-        <v>0.12011</v>
+        <v>0.41944</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.141</v>
+        <v>0.063</v>
       </c>
       <c r="R40" s="12">
-        <v>0.2882094487081623</v>
+        <v>0.368867603719909</v>
       </c>
       <c r="S40" s="11">
-        <v>56.88897934844421</v>
+        <v>61.58963480285758</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -5765,61 +5814,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E41" s="10">
-        <v>560.5599975585938</v>
+        <v>28.25</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3800842297516259</v>
+        <v>0.3769766818440744</v>
       </c>
       <c r="G41" s="20">
-        <v>0.3925105812237497</v>
+        <v>-0.07115990276327171</v>
       </c>
       <c r="H41" s="20">
-        <v>0.6245140277751658</v>
+        <v>-0.995994779142174</v>
       </c>
       <c r="I41" s="20">
-        <v>-0.2828670116363273</v>
+        <v>-1.178947812209808</v>
       </c>
       <c r="J41" s="20">
-        <v>0.5945641082481493</v>
+        <v>0.4400046741952777</v>
       </c>
       <c r="K41" s="20">
-        <v>0</v>
+        <v>4.1972917133727</v>
       </c>
       <c r="L41" s="20">
-        <v>0.8766593123623324</v>
+        <v>1.102880601617674</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.4847764616927837</v>
+        <v>-0.4351229216896976</v>
       </c>
       <c r="N41" s="20">
-        <v>13.51341</v>
+        <v>403.57144</v>
       </c>
       <c r="O41" s="20">
-        <v>7.7711396</v>
+        <v>2.1576414</v>
       </c>
       <c r="P41" s="12">
-        <v>0.63432</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q41" s="12">
-        <v>0.116</v>
+        <v>-0.112</v>
       </c>
       <c r="R41" s="12">
-        <v>0.2139750851457882</v>
+        <v>0.01073342500435048</v>
       </c>
       <c r="S41" s="11">
-        <v>56.29734893721688</v>
+        <v>56.86895301924928</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -5827,61 +5876,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="E42" s="10">
-        <v>298.0400085449219</v>
+        <v>30.38999938964844</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3785613190027045</v>
+        <v>0.3561189445042669</v>
       </c>
       <c r="G42" s="20">
-        <v>0.02746197675084354</v>
+        <v>0.4651535335003561</v>
       </c>
       <c r="H42" s="20">
-        <v>1.208344836389762</v>
+        <v>-0.2838674139749334</v>
       </c>
       <c r="I42" s="20">
-        <v>0.5984308054165401</v>
+        <v>-0.7020967881923148</v>
       </c>
       <c r="J42" s="20">
-        <v>0.5419369792960574</v>
+        <v>0.474719277334086</v>
       </c>
       <c r="K42" s="20">
-        <v>0</v>
+        <v>2.024372144423318</v>
       </c>
       <c r="L42" s="20">
-        <v>-0.4802622799224806</v>
+        <v>0.5797697905351504</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.7344100806282032</v>
+        <v>-0.4013356804213674</v>
       </c>
       <c r="N42" s="20">
-        <v>20.706474</v>
+        <v>29.504854</v>
       </c>
       <c r="O42" s="20">
-        <v>32.69876</v>
+        <v>1.9370259</v>
       </c>
       <c r="P42" s="12">
-        <v>0.89489</v>
+        <v>0.07979</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.14</v>
+        <v>0.108</v>
       </c>
       <c r="R42" s="12">
-        <v>0.1982347273512726</v>
+        <v>0.239520454510977</v>
       </c>
       <c r="S42" s="11">
-        <v>43.62482624844692</v>
+        <v>58.01771784522179</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -5889,61 +5938,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="E43" s="10">
-        <v>849.280029296875</v>
+        <v>97.36000061035156</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3548596009041816</v>
+        <v>0.3559265600793516</v>
       </c>
       <c r="G43" s="20">
-        <v>-2.080641695366814</v>
+        <v>0.7729141735395381</v>
       </c>
       <c r="H43" s="20">
-        <v>1.686267249950992</v>
+        <v>-0.7070924070566372</v>
       </c>
       <c r="I43" s="20">
-        <v>1.358863708841197</v>
+        <v>0.5525999266284973</v>
       </c>
       <c r="J43" s="20">
-        <v>1.570443974335826</v>
+        <v>0.6907019544980174</v>
       </c>
       <c r="K43" s="20">
-        <v>0</v>
+        <v>0.9181156463774164</v>
       </c>
       <c r="L43" s="20">
-        <v>-2.966945152287917</v>
+        <v>-0.04340261418344179</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.1501707509755603</v>
+        <v>-0.5012938219405213</v>
       </c>
       <c r="N43" s="20">
-        <v>59.523674</v>
+        <v>23.8044</v>
       </c>
       <c r="O43" s="20">
-        <v>170.03279</v>
+        <v>1.6411294</v>
       </c>
       <c r="P43" s="12">
-        <v>3.7152898</v>
+        <v>0.06886</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.485</v>
+        <v>0.004</v>
       </c>
       <c r="R43" s="12">
-        <v>1.413175079577211</v>
+        <v>0.307737973423585</v>
       </c>
       <c r="S43" s="11">
-        <v>50.64493262569261</v>
+        <v>50.14899141751228</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -5951,61 +6000,61 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E44" s="10">
-        <v>579.2100219726562</v>
+        <v>122.0199966430664</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3525500431262109</v>
+        <v>0.3554764771362848</v>
       </c>
       <c r="G44" s="20">
-        <v>-1.475165475869587</v>
+        <v>1.185896662709272</v>
       </c>
       <c r="H44" s="20">
-        <v>2.900509017506636</v>
+        <v>-0.6467007744749826</v>
       </c>
       <c r="I44" s="20">
-        <v>-0.1665174441390725</v>
+        <v>0.146369195149319</v>
       </c>
       <c r="J44" s="20">
-        <v>0.3097185348209719</v>
+        <v>0.5603921207836885</v>
       </c>
       <c r="K44" s="20">
-        <v>0</v>
+        <v>0.1999285466170274</v>
       </c>
       <c r="L44" s="20">
-        <v>0.9815367928180807</v>
+        <v>1.055636964533815</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.2932955349367438</v>
+        <v>-0.3074624681437192</v>
       </c>
       <c r="N44" s="20">
-        <v>32.565643</v>
+        <v>11.062556</v>
       </c>
       <c r="O44" s="20">
-        <v>93.07380000000001</v>
+        <v>1.3339746</v>
       </c>
       <c r="P44" s="12">
-        <v>2.41202</v>
+        <v>0.12011</v>
       </c>
       <c r="Q44" s="12">
         <v>0.141</v>
       </c>
       <c r="R44" s="12">
-        <v>0.1126430407173609</v>
+        <v>0.2882093449476779</v>
       </c>
       <c r="S44" s="11">
-        <v>52.90532324040763</v>
+        <v>56.88897936180841</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -6071,110 +6120,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B6" s="12">
         <v>0.18</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B7" s="12">
         <v>0.16</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B8" s="12">
         <v>0.1</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B9" s="12">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B10" s="12">
         <v>0.12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B11" s="12">
         <v>0.06</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B12" s="12">
         <v>0.08</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B13" s="12">
         <f>SUM(B6:B12)</f>
@@ -6183,22 +6232,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -6277,57 +6326,57 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>30</v>
@@ -6335,113 +6384,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -6459,1671 +6508,1644 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI9"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:60">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>390.8042297363281</v>
+        <v>394.9174194335938</v>
       </c>
       <c r="C1">
-        <v>394.9174194335938</v>
+        <v>408.3951416015625</v>
       </c>
       <c r="D1">
-        <v>408.3951416015625</v>
+        <v>403.4133605957031</v>
       </c>
       <c r="E1">
-        <v>403.4133605957031</v>
+        <v>418.6282348632812</v>
       </c>
       <c r="F1">
-        <v>418.6282348632812</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="G1">
-        <v>408.8244323730469</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="H1">
-        <v>418.0192260742188</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="I1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="J1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="K1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="L1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="M1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="N1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="O1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="P1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="Q1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="R1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="S1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="T1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="U1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="V1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="W1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="X1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="Y1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="Z1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="AA1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="AB1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="AC1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="AD1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="AE1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AF1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AG1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AH1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AI1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AJ1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AK1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AL1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AM1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AN1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AO1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AP1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AQ1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AR1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AS1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AT1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AU1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AV1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="AW1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="AX1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="AY1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="AZ1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="BA1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="BB1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="BC1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
       <c r="BD1">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="BE1">
-        <v>456.010009765625</v>
+        <v>425</v>
       </c>
       <c r="BF1">
-        <v>425</v>
+        <v>492.2000122070312</v>
       </c>
       <c r="BG1">
-        <v>492.2000122070312</v>
+        <v>516.3900146484375</v>
       </c>
       <c r="BH1">
-        <v>516.3900146484375</v>
-      </c>
-      <c r="BI1">
         <v>524.1400146484375</v>
       </c>
     </row>
-    <row r="2" spans="1:61">
+    <row r="2" spans="1:60">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>995.7168579101562</v>
+        <v>981.4590454101562</v>
       </c>
       <c r="C2">
-        <v>981.4590454101562</v>
+        <v>1087.822631835938</v>
       </c>
       <c r="D2">
-        <v>1087.822631835938</v>
+        <v>1020.60302734375</v>
       </c>
       <c r="E2">
-        <v>1020.60302734375</v>
+        <v>1043.029541015625</v>
       </c>
       <c r="F2">
-        <v>1043.029541015625</v>
+        <v>1133.815551757812</v>
       </c>
       <c r="G2">
-        <v>1133.815551757812</v>
+        <v>1211.193725585938</v>
       </c>
       <c r="H2">
-        <v>1211.193725585938</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="I2">
-        <v>1051.608276367188</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="J2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="K2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="L2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="M2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="N2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="O2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="P2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="Q2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="R2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="S2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="T2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="U2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="V2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="W2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="X2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="Y2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="Z2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="AA2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="AB2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="AC2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="AD2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="AE2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="AF2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AG2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="AH2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AI2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AJ2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AK2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AL2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AM2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AN2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AO2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AP2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AQ2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AR2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AS2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AT2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="AU2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AV2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="AW2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="AX2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="AY2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="AZ2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="BA2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="BB2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="BC2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="BD2">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="BE2">
-        <v>958.72998046875</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="BF2">
-        <v>933.4400024414062</v>
+        <v>956.0800170898438</v>
       </c>
       <c r="BG2">
-        <v>956.0800170898438</v>
+        <v>958.1599731445312</v>
       </c>
       <c r="BH2">
-        <v>958.1599731445312</v>
-      </c>
-      <c r="BI2">
         <v>1016.590026855469</v>
       </c>
     </row>
-    <row r="3" spans="1:61">
+    <row r="3" spans="1:60">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1881.510009765625</v>
+        <v>1980.099975585938</v>
       </c>
       <c r="C3">
-        <v>1980.099975585938</v>
+        <v>2107.860107421875</v>
       </c>
       <c r="D3">
-        <v>2107.860107421875</v>
+        <v>1991.550048828125</v>
       </c>
       <c r="E3">
-        <v>1991.550048828125</v>
+        <v>1958.800048828125</v>
       </c>
       <c r="F3">
-        <v>1958.800048828125</v>
+        <v>2184.75</v>
       </c>
       <c r="G3">
-        <v>2184.75</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="H3">
+        <v>1963.599975585938</v>
+      </c>
+      <c r="I3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="J3">
+        <v>2335</v>
+      </c>
+      <c r="K3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="L3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="M3">
         <v>2273.72998046875</v>
       </c>
-      <c r="I3">
-        <v>1963.599975585938</v>
-      </c>
-      <c r="J3">
-        <v>1914.4599609375</v>
-      </c>
-      <c r="K3">
-        <v>2335</v>
-      </c>
-      <c r="L3">
-        <v>2090.7099609375</v>
-      </c>
-      <c r="M3">
-        <v>2050.389892578125</v>
-      </c>
       <c r="N3">
-        <v>2273.72998046875</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="O3">
-        <v>2032.219970703125</v>
+        <v>1745</v>
       </c>
       <c r="P3">
-        <v>1745</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="Q3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="R3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="S3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="T3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="U3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="V3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="W3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="X3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="Y3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="Z3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="AA3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="AB3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="AC3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="AD3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="AE3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="AF3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="AG3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AH3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AI3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AJ3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AK3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AL3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="AM3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AN3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AO3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AP3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AQ3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AR3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AS3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AT3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AU3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AV3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="AW3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="AX3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="AY3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="AZ3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="BA3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="BB3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="BC3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="BD3">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="BE3">
-        <v>1566.699951171875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="BF3">
-        <v>1536.869995117188</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="BG3">
-        <v>1553.400024414062</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="BH3">
-        <v>1554.989990234375</v>
-      </c>
-      <c r="BI3">
         <v>1740</v>
       </c>
     </row>
-    <row r="4" spans="1:61">
+    <row r="4" spans="1:60">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>529.2899780273438</v>
+        <v>562.9299926757812</v>
       </c>
       <c r="C4">
-        <v>562.9299926757812</v>
+        <v>653.530029296875</v>
       </c>
       <c r="D4">
-        <v>653.530029296875</v>
+        <v>681.0800170898438</v>
       </c>
       <c r="E4">
-        <v>681.0800170898438</v>
+        <v>712.1300048828125</v>
       </c>
       <c r="F4">
-        <v>712.1300048828125</v>
+        <v>746.22998046875</v>
       </c>
       <c r="G4">
-        <v>746.22998046875</v>
+        <v>732.6199951171875</v>
       </c>
       <c r="H4">
-        <v>732.6199951171875</v>
+        <v>670.75</v>
       </c>
       <c r="I4">
-        <v>670.75</v>
+        <v>643.8300170898438</v>
       </c>
       <c r="J4">
-        <v>643.8300170898438</v>
+        <v>675.3900146484375</v>
       </c>
       <c r="K4">
-        <v>675.3900146484375</v>
+        <v>586.4500122070312</v>
       </c>
       <c r="L4">
-        <v>586.4500122070312</v>
+        <v>651.8800048828125</v>
       </c>
       <c r="M4">
-        <v>651.8800048828125</v>
+        <v>638.719970703125</v>
       </c>
       <c r="N4">
-        <v>638.719970703125</v>
+        <v>598.3699951171875</v>
       </c>
       <c r="O4">
-        <v>598.3699951171875</v>
+        <v>539</v>
       </c>
       <c r="P4">
-        <v>539</v>
+        <v>577.4600219726562</v>
       </c>
       <c r="Q4">
-        <v>577.4600219726562</v>
+        <v>532.0999755859375</v>
       </c>
       <c r="R4">
-        <v>532.0999755859375</v>
+        <v>550.2999877929688</v>
       </c>
       <c r="S4">
-        <v>550.2999877929688</v>
+        <v>578.0499877929688</v>
       </c>
       <c r="T4">
-        <v>578.0499877929688</v>
+        <v>582.5900268554688</v>
       </c>
       <c r="U4">
-        <v>582.5900268554688</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="V4">
-        <v>555.5499877929688</v>
+        <v>563.3200073242188</v>
       </c>
       <c r="W4">
-        <v>563.3200073242188</v>
+        <v>513.8400268554688</v>
       </c>
       <c r="X4">
-        <v>513.8400268554688</v>
+        <v>466.8099975585938</v>
       </c>
       <c r="Y4">
-        <v>466.8099975585938</v>
+        <v>477.2200012207031</v>
       </c>
       <c r="Z4">
-        <v>477.2200012207031</v>
+        <v>487.4200134277344</v>
       </c>
       <c r="AA4">
-        <v>487.4200134277344</v>
+        <v>548.3900146484375</v>
       </c>
       <c r="AB4">
-        <v>548.3900146484375</v>
+        <v>556.6699829101562</v>
       </c>
       <c r="AC4">
-        <v>556.6699829101562</v>
+        <v>558.2999877929688</v>
       </c>
       <c r="AD4">
-        <v>558.2999877929688</v>
+        <v>519.7999877929688</v>
       </c>
       <c r="AE4">
-        <v>519.7999877929688</v>
+        <v>497.9200134277344</v>
       </c>
       <c r="AF4">
-        <v>497.9200134277344</v>
+        <v>463.510009765625</v>
       </c>
       <c r="AG4">
-        <v>463.510009765625</v>
+        <v>462.0400085449219</v>
       </c>
       <c r="AH4">
-        <v>462.0400085449219</v>
+        <v>533.0399780273438</v>
       </c>
       <c r="AI4">
-        <v>533.0399780273438</v>
+        <v>544.8400268554688</v>
       </c>
       <c r="AJ4">
-        <v>544.8400268554688</v>
+        <v>527.219970703125</v>
       </c>
       <c r="AK4">
-        <v>527.219970703125</v>
+        <v>548.5599975585938</v>
       </c>
       <c r="AL4">
-        <v>548.5599975585938</v>
+        <v>519.1699829101562</v>
       </c>
       <c r="AM4">
-        <v>519.1699829101562</v>
+        <v>451.5199890136719</v>
       </c>
       <c r="AN4">
-        <v>451.5199890136719</v>
+        <v>434.2999877929688</v>
       </c>
       <c r="AO4">
-        <v>434.2999877929688</v>
+        <v>438.3399963378906</v>
       </c>
       <c r="AP4">
-        <v>438.3399963378906</v>
+        <v>437.9299926757812</v>
       </c>
       <c r="AQ4">
-        <v>437.9299926757812</v>
+        <v>454.1000061035156</v>
       </c>
       <c r="AR4">
-        <v>454.1000061035156</v>
+        <v>487.2900085449219</v>
       </c>
       <c r="AS4">
-        <v>487.2900085449219</v>
+        <v>508.7999877929688</v>
       </c>
       <c r="AT4">
-        <v>508.7999877929688</v>
+        <v>536.010009765625</v>
       </c>
       <c r="AU4">
-        <v>536.010009765625</v>
+        <v>496.1600036621094</v>
       </c>
       <c r="AV4">
-        <v>496.1600036621094</v>
+        <v>462.0899963378906</v>
       </c>
       <c r="AW4">
-        <v>462.0899963378906</v>
+        <v>469.0499877929688</v>
       </c>
       <c r="AX4">
-        <v>469.0499877929688</v>
+        <v>459.4400024414062</v>
       </c>
       <c r="AY4">
-        <v>459.4400024414062</v>
+        <v>435.3800048828125</v>
       </c>
       <c r="AZ4">
-        <v>435.3800048828125</v>
+        <v>450.75</v>
       </c>
       <c r="BA4">
-        <v>450.75</v>
+        <v>468.8800048828125</v>
       </c>
       <c r="BB4">
-        <v>468.8800048828125</v>
+        <v>462</v>
       </c>
       <c r="BC4">
-        <v>462</v>
+        <v>459.4500122070312</v>
       </c>
       <c r="BD4">
-        <v>459.4500122070312</v>
+        <v>450.5499877929688</v>
       </c>
       <c r="BE4">
-        <v>450.5499877929688</v>
+        <v>450.4400024414062</v>
       </c>
       <c r="BF4">
-        <v>450.4400024414062</v>
+        <v>448.8999938964844</v>
       </c>
       <c r="BG4">
-        <v>448.8999938964844</v>
+        <v>441.5700073242188</v>
       </c>
       <c r="BH4">
-        <v>441.5700073242188</v>
-      </c>
-      <c r="BI4">
         <v>467.4599914550781</v>
       </c>
     </row>
-    <row r="5" spans="1:61">
+    <row r="5" spans="1:60">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>254.6160125732422</v>
+        <v>257.6741943359375</v>
       </c>
       <c r="C5">
-        <v>257.6741943359375</v>
+        <v>246.20849609375</v>
       </c>
       <c r="D5">
-        <v>246.20849609375</v>
+        <v>243.1901702880859</v>
       </c>
       <c r="E5">
-        <v>243.1901702880859</v>
+        <v>238.8469543457031</v>
       </c>
       <c r="F5">
-        <v>238.8469543457031</v>
+        <v>235.3903045654297</v>
       </c>
       <c r="G5">
-        <v>235.3903045654297</v>
+        <v>242.8415069580078</v>
       </c>
       <c r="H5">
-        <v>242.8415069580078</v>
+        <v>242.7418823242188</v>
       </c>
       <c r="I5">
-        <v>242.7418823242188</v>
+        <v>241.4967041015625</v>
       </c>
       <c r="J5">
-        <v>241.4967041015625</v>
+        <v>254.0780792236328</v>
       </c>
       <c r="K5">
-        <v>254.0780792236328</v>
+        <v>258.3714904785156</v>
       </c>
       <c r="L5">
-        <v>258.3714904785156</v>
+        <v>265.2947387695312</v>
       </c>
       <c r="M5">
-        <v>265.2947387695312</v>
+        <v>259.4373779296875</v>
       </c>
       <c r="N5">
-        <v>259.4373779296875</v>
+        <v>268.4027404785156</v>
       </c>
       <c r="O5">
-        <v>268.4027404785156</v>
+        <v>266.7291870117188</v>
       </c>
       <c r="P5">
-        <v>266.7291870117188</v>
+        <v>269.2793579101562</v>
       </c>
       <c r="Q5">
-        <v>269.2793579101562</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="R5">
-        <v>265.1951293945312</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="S5">
-        <v>281.7909851074219</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="T5">
-        <v>280.1672668457031</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="U5">
-        <v>279.6094055175781</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="V5">
-        <v>294.6513061523438</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="W5">
-        <v>300.2695617675781</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="X5">
-        <v>291.5333251953125</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="Y5">
-        <v>299.1040954589844</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="Z5">
-        <v>308.4579162597656</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="AA5">
-        <v>312.1038208007812</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="AB5">
-        <v>313.5880737304688</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="AC5">
-        <v>309.7230529785156</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="AD5">
-        <v>304.0848388671875</v>
+        <v>301.33544921875</v>
       </c>
       <c r="AE5">
-        <v>301.33544921875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="AF5">
-        <v>303.756103515625</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="AG5">
-        <v>297.7294006347656</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="AH5">
-        <v>300.1600036621094</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="AI5">
-        <v>310.5099792480469</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="AJ5">
-        <v>312.8999938964844</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="AK5">
-        <v>307.5400085449219</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="AL5">
-        <v>308.7300109863281</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="AM5">
-        <v>302.3900146484375</v>
+        <v>302.989990234375</v>
       </c>
       <c r="AN5">
-        <v>302.989990234375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="AO5">
-        <v>298.3099975585938</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AP5">
-        <v>314.9500122070312</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AQ5">
-        <v>323.9200134277344</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AR5">
-        <v>330.2099914550781</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AS5">
-        <v>342.9200134277344</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AT5">
-        <v>341.6700134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AU5">
-        <v>347.1900024414062</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AV5">
-        <v>350.0499877929688</v>
+        <v>346.260009765625</v>
       </c>
       <c r="AW5">
-        <v>346.260009765625</v>
+        <v>341.510009765625</v>
       </c>
       <c r="AX5">
-        <v>341.510009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="AY5">
-        <v>348.8599853515625</v>
+        <v>346</v>
       </c>
       <c r="AZ5">
-        <v>346</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="BA5">
-        <v>340.4100036621094</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="BB5">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="BC5">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="BD5">
-        <v>352.3599853515625</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="BE5">
-        <v>358.9200134277344</v>
+        <v>361.989990234375</v>
       </c>
       <c r="BF5">
-        <v>361.989990234375</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="BG5">
-        <v>366.0899963378906</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="BH5">
-        <v>370.6900024414062</v>
-      </c>
-      <c r="BI5">
         <v>370.7200012207031</v>
       </c>
     </row>
-    <row r="6" spans="1:61">
+    <row r="6" spans="1:60">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>260.0978088378906</v>
+        <v>262.8602294921875</v>
       </c>
       <c r="C6">
-        <v>262.8602294921875</v>
+        <v>250.1749877929688</v>
       </c>
       <c r="D6">
-        <v>250.1749877929688</v>
+        <v>249.7860565185547</v>
       </c>
       <c r="E6">
-        <v>249.7860565185547</v>
+        <v>243.9420471191406</v>
       </c>
       <c r="F6">
-        <v>243.9420471191406</v>
+        <v>242.2467041015625</v>
       </c>
       <c r="G6">
-        <v>242.2467041015625</v>
+        <v>246.6147308349609</v>
       </c>
       <c r="H6">
-        <v>246.6147308349609</v>
+        <v>247.8413848876953</v>
       </c>
       <c r="I6">
-        <v>247.8413848876953</v>
+        <v>245.8368530273438</v>
       </c>
       <c r="J6">
-        <v>245.8368530273438</v>
+        <v>252.8676147460938</v>
       </c>
       <c r="K6">
-        <v>252.8676147460938</v>
+        <v>253.3662414550781</v>
       </c>
       <c r="L6">
-        <v>253.3662414550781</v>
+        <v>258.5121459960938</v>
       </c>
       <c r="M6">
-        <v>258.5121459960938</v>
+        <v>254.9718475341797</v>
       </c>
       <c r="N6">
-        <v>254.9718475341797</v>
+        <v>264.146728515625</v>
       </c>
       <c r="O6">
-        <v>264.146728515625</v>
+        <v>265.6226806640625</v>
       </c>
       <c r="P6">
-        <v>265.6226806640625</v>
+        <v>268.2554626464844</v>
       </c>
       <c r="Q6">
-        <v>268.2554626464844</v>
+        <v>265.6027221679688</v>
       </c>
       <c r="R6">
-        <v>265.6027221679688</v>
+        <v>279.9135437011719</v>
       </c>
       <c r="S6">
-        <v>279.9135437011719</v>
+        <v>282.5263977050781</v>
       </c>
       <c r="T6">
-        <v>282.5263977050781</v>
+        <v>282.9651794433594</v>
       </c>
       <c r="U6">
-        <v>282.9651794433594</v>
+        <v>296.0693359375</v>
       </c>
       <c r="V6">
-        <v>296.0693359375</v>
+        <v>302.5715026855469</v>
       </c>
       <c r="W6">
-        <v>302.5715026855469</v>
+        <v>298.363037109375</v>
       </c>
       <c r="X6">
-        <v>298.363037109375</v>
+        <v>305.0148315429688</v>
       </c>
       <c r="Y6">
-        <v>305.0148315429688</v>
+        <v>311.7463989257812</v>
       </c>
       <c r="Z6">
-        <v>311.7463989257812</v>
+        <v>314.4490051269531</v>
       </c>
       <c r="AA6">
-        <v>314.4490051269531</v>
+        <v>318.8868408203125</v>
       </c>
       <c r="AB6">
-        <v>318.8868408203125</v>
+        <v>314.9576110839844</v>
       </c>
       <c r="AC6">
-        <v>314.9576110839844</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="AD6">
-        <v>311.4172973632812</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="AE6">
-        <v>308.3955688476562</v>
+        <v>311.4970703125</v>
       </c>
       <c r="AF6">
-        <v>311.4970703125</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="AG6">
-        <v>305.2142639160156</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="AH6">
-        <v>307.8769836425781</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="AI6">
-        <v>313.2223510742188</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="AJ6">
-        <v>315.6058349609375</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="AK6">
-        <v>306.1915893554688</v>
+        <v>311.75634765625</v>
       </c>
       <c r="AL6">
-        <v>311.75634765625</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="AM6">
-        <v>296.9369506835938</v>
+        <v>298.432861328125</v>
       </c>
       <c r="AN6">
-        <v>298.432861328125</v>
+        <v>297.3857421875</v>
       </c>
       <c r="AO6">
-        <v>297.3857421875</v>
+        <v>319.4453125</v>
       </c>
       <c r="AP6">
-        <v>319.4453125</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="AQ6">
-        <v>335.5013732910156</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="AR6">
-        <v>347.2990417480469</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="AS6">
-        <v>355.3968811035156</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="AT6">
-        <v>354.4494934082031</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="AU6">
-        <v>357.2019348144531</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="AV6">
-        <v>365.2099914550781</v>
+        <v>360.75</v>
       </c>
       <c r="AW6">
-        <v>360.75</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="AX6">
-        <v>358.2300109863281</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="AY6">
-        <v>360.7200012207031</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="AZ6">
-        <v>362.5199890136719</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="BA6">
-        <v>354.8800048828125</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="BB6">
-        <v>362.2699890136719</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="BC6">
-        <v>363.5400085449219</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="BD6">
-        <v>368.8299865722656</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="BE6">
-        <v>373.3200073242188</v>
+        <v>383</v>
       </c>
       <c r="BF6">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="BG6">
-        <v>387</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="BH6">
-        <v>387.7099914550781</v>
-      </c>
-      <c r="BI6">
         <v>388.8999938964844</v>
       </c>
     </row>
-    <row r="7" spans="1:61">
+    <row r="7" spans="1:60">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
+        <v>56.54000091552734</v>
+      </c>
+      <c r="C7">
+        <v>54.45999908447266</v>
+      </c>
+      <c r="D7">
+        <v>53.66999816894531</v>
+      </c>
+      <c r="E7">
+        <v>53.04000091552734</v>
+      </c>
+      <c r="F7">
+        <v>51.81999969482422</v>
+      </c>
+      <c r="G7">
+        <v>52</v>
+      </c>
+      <c r="H7">
+        <v>52.22999954223633</v>
+      </c>
+      <c r="I7">
+        <v>51.09000015258789</v>
+      </c>
+      <c r="J7">
+        <v>51.20999908447266</v>
+      </c>
+      <c r="K7">
+        <v>49.9900016784668</v>
+      </c>
+      <c r="L7">
+        <v>49.09000015258789</v>
+      </c>
+      <c r="M7">
+        <v>48.56999969482422</v>
+      </c>
+      <c r="N7">
+        <v>47.93999862670898</v>
+      </c>
+      <c r="O7">
+        <v>48.90999984741211</v>
+      </c>
+      <c r="P7">
+        <v>48.81000137329102</v>
+      </c>
+      <c r="Q7">
+        <v>51.68000030517578</v>
+      </c>
+      <c r="R7">
+        <v>53.59000015258789</v>
+      </c>
+      <c r="S7">
+        <v>52.29999923706055</v>
+      </c>
+      <c r="T7">
+        <v>52.88999938964844</v>
+      </c>
+      <c r="U7">
+        <v>54.81000137329102</v>
+      </c>
+      <c r="V7">
+        <v>54.56999969482422</v>
+      </c>
+      <c r="W7">
+        <v>53.77000045776367</v>
+      </c>
+      <c r="X7">
+        <v>53.65000152587891</v>
+      </c>
+      <c r="Y7">
+        <v>54.86000061035156</v>
+      </c>
+      <c r="Z7">
+        <v>55.18999862670898</v>
+      </c>
+      <c r="AA7">
+        <v>56.5</v>
+      </c>
+      <c r="AB7">
+        <v>57.5</v>
+      </c>
+      <c r="AC7">
+        <v>57.59999847412109</v>
+      </c>
+      <c r="AD7">
+        <v>57.29999923706055</v>
+      </c>
+      <c r="AE7">
+        <v>54.93000030517578</v>
+      </c>
+      <c r="AF7">
+        <v>53.93000030517578</v>
+      </c>
+      <c r="AG7">
+        <v>56.02999877929688</v>
+      </c>
+      <c r="AH7">
+        <v>55.95000076293945</v>
+      </c>
+      <c r="AI7">
+        <v>57.06999969482422</v>
+      </c>
+      <c r="AJ7">
         <v>55.47000122070312</v>
       </c>
-      <c r="C7">
-        <v>56.54000091552734</v>
-      </c>
-      <c r="D7">
-        <v>54.45999908447266</v>
-      </c>
-      <c r="E7">
-        <v>53.66999816894531</v>
-      </c>
-      <c r="F7">
-        <v>53.04000091552734</v>
-      </c>
-      <c r="G7">
-        <v>51.81999969482422</v>
-      </c>
-      <c r="H7">
-        <v>52</v>
-      </c>
-      <c r="I7">
-        <v>52.22999954223633</v>
-      </c>
-      <c r="J7">
-        <v>51.09000015258789</v>
-      </c>
-      <c r="K7">
-        <v>51.20999908447266</v>
-      </c>
-      <c r="L7">
-        <v>49.9900016784668</v>
-      </c>
-      <c r="M7">
-        <v>49.09000015258789</v>
-      </c>
-      <c r="N7">
-        <v>48.56999969482422</v>
-      </c>
-      <c r="O7">
-        <v>47.93999862670898</v>
-      </c>
-      <c r="P7">
-        <v>48.90999984741211</v>
-      </c>
-      <c r="Q7">
-        <v>48.81000137329102</v>
-      </c>
-      <c r="R7">
-        <v>51.68000030517578</v>
-      </c>
-      <c r="S7">
-        <v>53.59000015258789</v>
-      </c>
-      <c r="T7">
-        <v>52.29999923706055</v>
-      </c>
-      <c r="U7">
-        <v>52.88999938964844</v>
-      </c>
-      <c r="V7">
-        <v>54.81000137329102</v>
-      </c>
-      <c r="W7">
-        <v>54.56999969482422</v>
-      </c>
-      <c r="X7">
-        <v>53.77000045776367</v>
-      </c>
-      <c r="Y7">
-        <v>53.65000152587891</v>
-      </c>
-      <c r="Z7">
-        <v>54.86000061035156</v>
-      </c>
-      <c r="AA7">
-        <v>55.18999862670898</v>
-      </c>
-      <c r="AB7">
-        <v>56.5</v>
-      </c>
-      <c r="AC7">
-        <v>57.5</v>
-      </c>
-      <c r="AD7">
-        <v>57.59999847412109</v>
-      </c>
-      <c r="AE7">
-        <v>57.29999923706055</v>
-      </c>
-      <c r="AF7">
-        <v>54.93000030517578</v>
-      </c>
-      <c r="AG7">
-        <v>53.93000030517578</v>
-      </c>
-      <c r="AH7">
-        <v>56.02999877929688</v>
-      </c>
-      <c r="AI7">
-        <v>55.95000076293945</v>
-      </c>
-      <c r="AJ7">
-        <v>57.06999969482422</v>
-      </c>
       <c r="AK7">
-        <v>55.47000122070312</v>
+        <v>55.09000015258789</v>
       </c>
       <c r="AL7">
-        <v>55.09000015258789</v>
+        <v>53.81000137329102</v>
       </c>
       <c r="AM7">
-        <v>53.81000137329102</v>
+        <v>56.04000091552734</v>
       </c>
       <c r="AN7">
-        <v>56.04000091552734</v>
+        <v>55.90999984741211</v>
       </c>
       <c r="AO7">
-        <v>55.90999984741211</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="AP7">
-        <v>58.65000152587891</v>
+        <v>59.06000137329102</v>
       </c>
       <c r="AQ7">
-        <v>59.06000137329102</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="AR7">
-        <v>58.54999923706055</v>
+        <v>57.70000076293945</v>
       </c>
       <c r="AS7">
-        <v>57.70000076293945</v>
+        <v>58.36000061035156</v>
       </c>
       <c r="AT7">
-        <v>58.36000061035156</v>
+        <v>59.04000091552734</v>
       </c>
       <c r="AU7">
-        <v>59.04000091552734</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="AV7">
-        <v>59.79999923706055</v>
+        <v>60.09000015258789</v>
       </c>
       <c r="AW7">
-        <v>60.09000015258789</v>
+        <v>61.52000045776367</v>
       </c>
       <c r="AX7">
-        <v>61.52000045776367</v>
+        <v>61.29999923706055</v>
       </c>
       <c r="AY7">
-        <v>61.29999923706055</v>
+        <v>60.11000061035156</v>
       </c>
       <c r="AZ7">
-        <v>60.11000061035156</v>
+        <v>58.40999984741211</v>
       </c>
       <c r="BA7">
-        <v>58.40999984741211</v>
+        <v>58.61999893188477</v>
       </c>
       <c r="BB7">
-        <v>58.61999893188477</v>
+        <v>59.16999816894531</v>
       </c>
       <c r="BC7">
-        <v>59.16999816894531</v>
+        <v>59.09999847412109</v>
       </c>
       <c r="BD7">
-        <v>59.09999847412109</v>
+        <v>60.18000030517578</v>
       </c>
       <c r="BE7">
-        <v>60.18000030517578</v>
+        <v>60.95000076293945</v>
       </c>
       <c r="BF7">
-        <v>60.95000076293945</v>
+        <v>60.90999984741211</v>
       </c>
       <c r="BG7">
-        <v>60.90999984741211</v>
+        <v>60.61000061035156</v>
       </c>
       <c r="BH7">
-        <v>60.61000061035156</v>
-      </c>
-      <c r="BI7">
         <v>60.04000091552734</v>
       </c>
     </row>
-    <row r="8" spans="1:61">
+    <row r="8" spans="1:60">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>177.1597137451172</v>
+        <v>178.5025787353516</v>
       </c>
       <c r="C8">
-        <v>178.5025787353516</v>
+        <v>172.3452606201172</v>
       </c>
       <c r="D8">
-        <v>172.3452606201172</v>
+        <v>171.0919189453125</v>
       </c>
       <c r="E8">
-        <v>171.0919189453125</v>
+        <v>166.2874145507812</v>
       </c>
       <c r="F8">
-        <v>166.2874145507812</v>
+        <v>165.2628631591797</v>
       </c>
       <c r="G8">
-        <v>165.2628631591797</v>
+        <v>167.5208740234375</v>
       </c>
       <c r="H8">
-        <v>167.5208740234375</v>
+        <v>169.440673828125</v>
       </c>
       <c r="I8">
-        <v>169.440673828125</v>
+        <v>167.7496643066406</v>
       </c>
       <c r="J8">
-        <v>167.7496643066406</v>
+        <v>170.8531799316406</v>
       </c>
       <c r="K8">
-        <v>170.8531799316406</v>
+        <v>170.7437591552734</v>
       </c>
       <c r="L8">
-        <v>170.7437591552734</v>
+        <v>173.131103515625</v>
       </c>
       <c r="M8">
-        <v>173.131103515625</v>
+        <v>168.1575012207031</v>
       </c>
       <c r="N8">
-        <v>168.1575012207031</v>
+        <v>173.5787200927734</v>
       </c>
       <c r="O8">
-        <v>173.5787200927734</v>
+        <v>175.4885864257812</v>
       </c>
       <c r="P8">
-        <v>175.4885864257812</v>
+        <v>176.3937835693359</v>
       </c>
       <c r="Q8">
-        <v>176.3937835693359</v>
+        <v>177.8957977294922</v>
       </c>
       <c r="R8">
-        <v>177.8957977294922</v>
+        <v>186.8184509277344</v>
       </c>
       <c r="S8">
-        <v>186.8184509277344</v>
+        <v>188.8178405761719</v>
       </c>
       <c r="T8">
-        <v>188.8178405761719</v>
+        <v>187.3655395507812</v>
       </c>
       <c r="U8">
-        <v>187.3655395507812</v>
+        <v>197.2431182861328</v>
       </c>
       <c r="V8">
-        <v>197.2431182861328</v>
+        <v>200.3864288330078</v>
       </c>
       <c r="W8">
-        <v>200.3864288330078</v>
+        <v>195.1243743896484</v>
       </c>
       <c r="X8">
-        <v>195.1243743896484</v>
+        <v>200.2571258544922</v>
       </c>
       <c r="Y8">
-        <v>200.2571258544922</v>
+        <v>205.7678680419922</v>
       </c>
       <c r="Z8">
-        <v>205.7678680419922</v>
+        <v>207.6976318359375</v>
       </c>
       <c r="AA8">
-        <v>207.6976318359375</v>
+        <v>211.1493225097656</v>
       </c>
       <c r="AB8">
-        <v>211.1493225097656</v>
+        <v>210.2938537597656</v>
       </c>
       <c r="AC8">
-        <v>210.2938537597656</v>
+        <v>205.8872375488281</v>
       </c>
       <c r="AD8">
-        <v>205.8872375488281</v>
+        <v>205.6783599853516</v>
       </c>
       <c r="AE8">
-        <v>205.6783599853516</v>
+        <v>206.7228088378906</v>
       </c>
       <c r="AF8">
-        <v>206.7228088378906</v>
+        <v>204.7632141113281</v>
       </c>
       <c r="AG8">
-        <v>204.7632141113281</v>
+        <v>205.7181396484375</v>
       </c>
       <c r="AH8">
-        <v>205.7181396484375</v>
+        <v>209.4881286621094</v>
       </c>
       <c r="AI8">
-        <v>209.4881286621094</v>
+        <v>210.5624237060547</v>
       </c>
       <c r="AJ8">
-        <v>210.5624237060547</v>
+        <v>205.1014099121094</v>
       </c>
       <c r="AK8">
-        <v>205.1014099121094</v>
+        <v>204.8029937744141</v>
       </c>
       <c r="AL8">
-        <v>204.8029937744141</v>
+        <v>201.4806365966797</v>
       </c>
       <c r="AM8">
-        <v>201.4806365966797</v>
+        <v>204.4349517822266</v>
       </c>
       <c r="AN8">
-        <v>204.4349517822266</v>
+        <v>202.8334503173828</v>
       </c>
       <c r="AO8">
-        <v>202.8334503173828</v>
+        <v>214.3821563720703</v>
       </c>
       <c r="AP8">
-        <v>214.3821563720703</v>
+        <v>223.1754760742188</v>
       </c>
       <c r="AQ8">
-        <v>223.1754760742188</v>
+        <v>224.3890380859375</v>
       </c>
       <c r="AR8">
-        <v>224.3890380859375</v>
+        <v>231.3819274902344</v>
       </c>
       <c r="AS8">
-        <v>231.3819274902344</v>
+        <v>232.3766479492188</v>
       </c>
       <c r="AT8">
-        <v>232.3766479492188</v>
+        <v>239.2800140380859</v>
       </c>
       <c r="AU8">
-        <v>239.2800140380859</v>
+        <v>243.4900054931641</v>
       </c>
       <c r="AV8">
-        <v>243.4900054931641</v>
+        <v>242.2899932861328</v>
       </c>
       <c r="AW8">
-        <v>242.2899932861328</v>
+        <v>240</v>
       </c>
       <c r="AX8">
-        <v>240</v>
+        <v>242.8699951171875</v>
       </c>
       <c r="AY8">
-        <v>242.8699951171875</v>
+        <v>241.9600067138672</v>
       </c>
       <c r="AZ8">
-        <v>241.9600067138672</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="BA8">
-        <v>236.8999938964844</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="BB8">
-        <v>242.2299957275391</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="BC8">
-        <v>239.8099975585938</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="BD8">
-        <v>244.0099945068359</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="BE8">
-        <v>246.5800018310547</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="BF8">
-        <v>252.0200042724609</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="BG8">
-        <v>256.0899963378906</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="BH8">
-        <v>254.6600036621094</v>
-      </c>
-      <c r="BI8">
         <v>255.0899963378906</v>
       </c>
     </row>
-    <row r="9" spans="1:61">
+    <row r="9" spans="1:60">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>36.5229377746582</v>
+        <v>36.76126480102539</v>
       </c>
       <c r="C9">
-        <v>36.76126480102539</v>
+        <v>34.5269889831543</v>
       </c>
       <c r="D9">
-        <v>34.5269889831543</v>
+        <v>34.02054977416992</v>
       </c>
       <c r="E9">
-        <v>34.02054977416992</v>
+        <v>33.6928596496582</v>
       </c>
       <c r="F9">
-        <v>33.6928596496582</v>
+        <v>32.79914855957031</v>
       </c>
       <c r="G9">
-        <v>32.79914855957031</v>
+        <v>33.96097183227539</v>
       </c>
       <c r="H9">
-        <v>33.96097183227539</v>
+        <v>33.9808349609375</v>
       </c>
       <c r="I9">
-        <v>33.9808349609375</v>
+        <v>33.09705352783203</v>
       </c>
       <c r="J9">
-        <v>33.09705352783203</v>
+        <v>33.18642044067383</v>
       </c>
       <c r="K9">
-        <v>33.18642044067383</v>
+        <v>32.77928924560547</v>
       </c>
       <c r="L9">
-        <v>32.77928924560547</v>
+        <v>32.72963714599609</v>
       </c>
       <c r="M9">
-        <v>32.72963714599609</v>
+        <v>32.34236526489258</v>
       </c>
       <c r="N9">
-        <v>32.34236526489258</v>
+        <v>31.64725685119629</v>
       </c>
       <c r="O9">
-        <v>31.64725685119629</v>
+        <v>32.13383102416992</v>
       </c>
       <c r="P9">
-        <v>32.13383102416992</v>
+        <v>32.23313140869141</v>
       </c>
       <c r="Q9">
-        <v>32.23313140869141</v>
+        <v>33.76237106323242</v>
       </c>
       <c r="R9">
-        <v>33.76237106323242</v>
+        <v>34.81496429443359</v>
       </c>
       <c r="S9">
-        <v>34.81496429443359</v>
+        <v>33.05733489990234</v>
       </c>
       <c r="T9">
-        <v>33.05733489990234</v>
+        <v>33.20628356933594</v>
       </c>
       <c r="U9">
-        <v>33.20628356933594</v>
+        <v>34.42768478393555</v>
       </c>
       <c r="V9">
-        <v>34.42768478393555</v>
+        <v>34.28866577148438</v>
       </c>
       <c r="W9">
-        <v>34.28866577148438</v>
+        <v>34.03048324584961</v>
       </c>
       <c r="X9">
-        <v>34.03048324584961</v>
+        <v>34.04041290283203</v>
       </c>
       <c r="Y9">
-        <v>34.04041290283203</v>
+        <v>34.97384262084961</v>
       </c>
       <c r="Z9">
-        <v>34.97384262084961</v>
+        <v>34.59650039672852</v>
       </c>
       <c r="AA9">
-        <v>34.59650039672852</v>
+        <v>35.52000045776367</v>
       </c>
       <c r="AB9">
-        <v>35.52000045776367</v>
+        <v>36.18000030517578</v>
       </c>
       <c r="AC9">
-        <v>36.18000030517578</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="AD9">
-        <v>36.41999816894531</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="AE9">
-        <v>36.15000152587891</v>
+        <v>34.7400016784668</v>
       </c>
       <c r="AF9">
-        <v>34.7400016784668</v>
+        <v>34.93000030517578</v>
       </c>
       <c r="AG9">
-        <v>34.93000030517578</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="AH9">
-        <v>36.70000076293945</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="AI9">
-        <v>36.33000183105469</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="AJ9">
-        <v>37.31999969482422</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="AK9">
-        <v>36.86999893188477</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="AL9">
-        <v>35.79999923706055</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="AM9">
-        <v>34.65999984741211</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="AN9">
-        <v>36.52999877929688</v>
+        <v>37.63000106811523</v>
       </c>
       <c r="AO9">
-        <v>37.63000106811523</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="AP9">
-        <v>41.02000045776367</v>
+        <v>40.61999893188477</v>
       </c>
       <c r="AQ9">
-        <v>40.61999893188477</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="AR9">
-        <v>39.97000122070312</v>
+        <v>40</v>
       </c>
       <c r="AS9">
-        <v>40</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="AT9">
-        <v>40.47000122070312</v>
+        <v>41.58000183105469</v>
       </c>
       <c r="AU9">
-        <v>41.58000183105469</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="AV9">
-        <v>42.36999893188477</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="AW9">
-        <v>43.45000076293945</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="AX9">
-        <v>44.38999938964844</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="AY9">
-        <v>43.38999938964844</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="AZ9">
-        <v>42.95999908447266</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="BA9">
-        <v>41.34999847412109</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="BB9">
-        <v>41.18999862670898</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="BC9">
-        <v>42.38000106811523</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="BD9">
-        <v>42.54000091552734</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="BE9">
-        <v>43.15000152587891</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="BF9">
-        <v>44.29999923706055</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="BG9">
-        <v>44.70000076293945</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="BH9">
-        <v>44.18000030517578</v>
-      </c>
-      <c r="BI9">
         <v>42.77000045776367</v>
       </c>
     </row>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -306,6 +306,36 @@
     <t>Financials</t>
   </si>
   <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class C)</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class A)</t>
+  </si>
+  <si>
+    <t>TGT</t>
+  </si>
+  <si>
+    <t>Target Corporation</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise</t>
+  </si>
+  <si>
     <t>CNC</t>
   </si>
   <si>
@@ -315,28 +345,10 @@
     <t>Health Care</t>
   </si>
   <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class A)</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class C)</t>
-  </si>
-  <si>
-    <t>TGT</t>
-  </si>
-  <si>
-    <t>Target Corporation</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
   </si>
   <si>
     <t>DLTR</t>
@@ -345,18 +357,6 @@
     <t>Dollar Tree</t>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>Hewlett Packard Enterprise</t>
-  </si>
-  <si>
     <t>AMZN</t>
   </si>
   <si>
@@ -366,12 +366,24 @@
     <t>Consumer Discretionary</t>
   </si>
   <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
     <t>INCY</t>
   </si>
   <si>
     <t>Incyte</t>
   </si>
   <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
+  </si>
+  <si>
     <t>GS</t>
   </si>
   <si>
@@ -390,10 +402,16 @@
     <t>Nvidia</t>
   </si>
   <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>Supermicro</t>
+  </si>
+  <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
   </si>
   <si>
     <t>BIIB</t>
@@ -402,22 +420,28 @@
     <t>Biogen</t>
   </si>
   <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>Intel</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>Supermicro</t>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>Seagate Technology</t>
   </si>
   <si>
     <t>HPQ</t>
@@ -426,75 +450,51 @@
     <t>HP Inc.</t>
   </si>
   <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
-  </si>
-  <si>
     <t>REGN</t>
   </si>
   <si>
     <t>Regeneron Pharmaceuticals</t>
   </si>
   <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>Amgen</t>
-  </si>
-  <si>
-    <t>HOOD</t>
-  </si>
-  <si>
-    <t>Robinhood Markets</t>
-  </si>
-  <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>Gen Digital</t>
-  </si>
-  <si>
     <t>WBD</t>
   </si>
   <si>
     <t>Warner Bros. Discovery</t>
   </si>
   <si>
-    <t>NWSA</t>
-  </si>
-  <si>
-    <t>News Corp (Class A)</t>
-  </si>
-  <si>
-    <t>SWK</t>
-  </si>
-  <si>
-    <t>Stanley Black &amp; Decker</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
     <t>PRU</t>
   </si>
   <si>
     <t>Prudential Financial</t>
   </si>
   <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>EOG Resources</t>
+  </si>
+  <si>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>Newmont</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>Humana</t>
+  </si>
+  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -573,7 +573,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-09 00:18 UTC · данные на 2026-09-08 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-10 00:17 UTC · данные на 2026-09-08 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -654,7 +654,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-09 00:18 UTC</t>
+    <t>2026-09-10 00:17 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -3582,58 +3582,58 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="10">
-        <v>1016.590026855469</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="F5" s="17">
-        <v>1.098851126819778</v>
+        <v>1.101843084316499</v>
       </c>
       <c r="G5" s="20">
-        <v>-0.5381709417593455</v>
+        <v>-0.5564495730839067</v>
       </c>
       <c r="H5" s="20">
-        <v>1.814060278794422</v>
+        <v>2.058086531115069</v>
       </c>
       <c r="I5" s="20">
-        <v>3.983916492932042</v>
+        <v>4.120745224686987</v>
       </c>
       <c r="J5" s="20">
-        <v>2.135435138403564</v>
+        <v>2.08157200151033</v>
       </c>
       <c r="K5" s="20">
-        <v>0.4798559392469772</v>
+        <v>0.08299030126699286</v>
       </c>
       <c r="L5" s="20">
-        <v>-3.413048273912248</v>
+        <v>-3.416720321042702</v>
       </c>
       <c r="M5" s="20">
-        <v>0.1706280580022094</v>
+        <v>0.3901052835239491</v>
       </c>
       <c r="N5" s="20">
-        <v>22.98937</v>
+        <v>23.583628</v>
       </c>
       <c r="O5" s="20">
-        <v>11.394834</v>
+        <v>16.475557</v>
       </c>
       <c r="P5" s="12">
-        <v>0.66638</v>
+        <v>0.9164</v>
       </c>
       <c r="Q5" s="12">
-        <v>3.457</v>
+        <v>3.716</v>
       </c>
       <c r="R5" s="12">
-        <v>1.746890376291639</v>
+        <v>1.952100365010421</v>
       </c>
       <c r="S5" s="11">
-        <v>60.14749911776807</v>
+        <v>61.1120814610072</v>
       </c>
       <c r="T5" s="9" t="s">
         <v>87</v>
@@ -3644,58 +3644,58 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="10">
-        <v>1740</v>
+        <v>1000.260009765625</v>
       </c>
       <c r="F6" s="17">
-        <v>1.093007060689962</v>
+        <v>1.074633121175905</v>
       </c>
       <c r="G6" s="20">
-        <v>-0.5564495730839067</v>
+        <v>-0.5381709417593455</v>
       </c>
       <c r="H6" s="20">
-        <v>2.058086531115069</v>
+        <v>1.814060278794422</v>
       </c>
       <c r="I6" s="20">
-        <v>4.120745224686987</v>
+        <v>3.983916492932042</v>
       </c>
       <c r="J6" s="20">
-        <v>2.024313374674196</v>
+        <v>2.050460594415619</v>
       </c>
       <c r="K6" s="20">
-        <v>0.08299030126699286</v>
+        <v>0.4798559392469772</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.413048273912248</v>
+        <v>-3.416720321042702</v>
       </c>
       <c r="M6" s="20">
-        <v>0.491620803479896</v>
+        <v>0.1893115627564228</v>
       </c>
       <c r="N6" s="20">
-        <v>23.583628</v>
+        <v>22.98937</v>
       </c>
       <c r="O6" s="20">
-        <v>16.475557</v>
+        <v>11.394834</v>
       </c>
       <c r="P6" s="12">
-        <v>0.9164</v>
+        <v>0.66638</v>
       </c>
       <c r="Q6" s="12">
-        <v>3.716</v>
+        <v>3.457</v>
       </c>
       <c r="R6" s="12">
-        <v>2.299641483719194</v>
+        <v>1.570723581010705</v>
       </c>
       <c r="S6" s="11">
-        <v>61.24267366525383</v>
+        <v>57.6626588022908</v>
       </c>
       <c r="T6" s="9" t="s">
         <v>87</v>
@@ -3715,10 +3715,10 @@
         <v>38</v>
       </c>
       <c r="E7" s="10">
-        <v>370.7200012207031</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="F7" s="17">
-        <v>0.9601856213956613</v>
+        <v>1.008299237621722</v>
       </c>
       <c r="G7" s="20">
         <v>0.7163099250210818</v>
@@ -3730,16 +3730,16 @@
         <v>2.885035079678366</v>
       </c>
       <c r="J7" s="20">
-        <v>2.042036654460478</v>
+        <v>2.192941818971337</v>
       </c>
       <c r="K7" s="20">
         <v>0.6066252760202447</v>
       </c>
       <c r="L7" s="20">
-        <v>0.1481612466747712</v>
+        <v>0.1212986880835318</v>
       </c>
       <c r="M7" s="20">
-        <v>-0.5326706124940634</v>
+        <v>-0.4769978576405967</v>
       </c>
       <c r="N7" s="20">
         <v>15.453106</v>
@@ -3754,10 +3754,10 @@
         <v>0.517</v>
       </c>
       <c r="R7" s="12">
-        <v>0.6646076297666343</v>
+        <v>0.7881713448812837</v>
       </c>
       <c r="S7" s="11">
-        <v>75.26716954237817</v>
+        <v>79.30760239290296</v>
       </c>
       <c r="T7" s="9" t="s">
         <v>87</v>
@@ -3777,10 +3777,10 @@
         <v>38</v>
       </c>
       <c r="E8" s="10">
-        <v>388.8999938964844</v>
+        <v>397.7699890136719</v>
       </c>
       <c r="F8" s="17">
-        <v>0.9565841660532839</v>
+        <v>0.9856850548435461</v>
       </c>
       <c r="G8" s="20">
         <v>0.704035078477925</v>
@@ -3792,16 +3792,16 @@
         <v>2.454207309239585</v>
       </c>
       <c r="J8" s="20">
-        <v>2.0446398229775</v>
+        <v>2.148174269992236</v>
       </c>
       <c r="K8" s="20">
         <v>0.7742712560795861</v>
       </c>
       <c r="L8" s="20">
-        <v>0.1801601438739235</v>
+        <v>0.1706484844696534</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.5096859535863941</v>
+        <v>-0.5270452754601733</v>
       </c>
       <c r="N8" s="20">
         <v>13.475398</v>
@@ -3816,10 +3816,10 @@
         <v>0.537</v>
       </c>
       <c r="R8" s="12">
-        <v>0.7690399834916115</v>
+        <v>0.8561956548441085</v>
       </c>
       <c r="S8" s="11">
-        <v>78.23784667525609</v>
+        <v>80.84519646228173</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>87</v>
@@ -3839,10 +3839,10 @@
         <v>28</v>
       </c>
       <c r="E9" s="10">
-        <v>524.1400146484375</v>
+        <v>533.8800048828125</v>
       </c>
       <c r="F9" s="17">
-        <v>0.9514109780074654</v>
+        <v>0.9764385260913725</v>
       </c>
       <c r="G9" s="20">
         <v>-0.2096896716004668</v>
@@ -3854,16 +3854,16 @@
         <v>2.195812652927404</v>
       </c>
       <c r="J9" s="20">
-        <v>2.796856434510391</v>
+        <v>2.925093281761714</v>
       </c>
       <c r="K9" s="20">
         <v>1.605257194274964</v>
       </c>
       <c r="L9" s="20">
-        <v>-2.554951796211781</v>
+        <v>-2.556865290901396</v>
       </c>
       <c r="M9" s="20">
-        <v>0.3317740615892385</v>
+        <v>0.1651653564628242</v>
       </c>
       <c r="N9" s="20">
         <v>30.490984</v>
@@ -3878,10 +3878,10 @@
         <v>0.577</v>
       </c>
       <c r="R9" s="12">
-        <v>2.595238758114921</v>
+        <v>2.661298429062968</v>
       </c>
       <c r="S9" s="11">
-        <v>63.67345525313317</v>
+        <v>65.08857762491189</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>87</v>
@@ -3892,58 +3892,58 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E10" s="10">
-        <v>259.2300109863281</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8750229780425828</v>
+        <v>0.8497603086029423</v>
       </c>
       <c r="G10" s="20">
-        <v>0.313884107527872</v>
+        <v>0.4937473502003348</v>
       </c>
       <c r="H10" s="20">
-        <v>0.5379536582452412</v>
+        <v>-0.7878254537509429</v>
       </c>
       <c r="I10" s="20">
-        <v>0.202940183485447</v>
+        <v>2.423226908404409</v>
       </c>
       <c r="J10" s="20">
-        <v>1.220060560316522</v>
+        <v>1.976963435581927</v>
       </c>
       <c r="K10" s="20">
-        <v>3.531116261499869</v>
+        <v>0.6899308401855347</v>
       </c>
       <c r="L10" s="20">
-        <v>-1.510715199580536</v>
+        <v>0.3912061011603029</v>
       </c>
       <c r="M10" s="20">
-        <v>0.1631003439959213</v>
+        <v>-0.6842241279983566</v>
       </c>
       <c r="N10" s="20">
-        <v>23.76077</v>
+        <v>14.559931</v>
       </c>
       <c r="O10" s="20">
-        <v>5.559058</v>
+        <v>3.2307048</v>
       </c>
       <c r="P10" s="12">
-        <v>0.19381</v>
+        <v>0.23452999</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.108</v>
+        <v>0.531</v>
       </c>
       <c r="R10" s="12">
-        <v>0.2891448931981548</v>
+        <v>0.6098574883208787</v>
       </c>
       <c r="S10" s="11">
-        <v>76.62974183129113</v>
+        <v>77.20479964933293</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>87</v>
@@ -3954,58 +3954,58 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E11" s="10">
-        <v>255.0899963378906</v>
+        <v>249.1199951171875</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8251866856904495</v>
+        <v>0.8469310645592527</v>
       </c>
       <c r="G11" s="20">
-        <v>0.4937473502003348</v>
+        <v>0.313884107527872</v>
       </c>
       <c r="H11" s="20">
-        <v>-0.7878254537509429</v>
+        <v>0.5379536582452412</v>
       </c>
       <c r="I11" s="20">
-        <v>2.423226908404409</v>
+        <v>0.202940183485447</v>
       </c>
       <c r="J11" s="20">
-        <v>1.88793512058422</v>
+        <v>1.150196583022348</v>
       </c>
       <c r="K11" s="20">
-        <v>0.6899308401855347</v>
+        <v>3.531116261499869</v>
       </c>
       <c r="L11" s="20">
-        <v>0.37371743288351</v>
+        <v>-1.568900752815953</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.6444217319555201</v>
+        <v>0.1175805052340104</v>
       </c>
       <c r="N11" s="20">
-        <v>14.559931</v>
+        <v>23.76077</v>
       </c>
       <c r="O11" s="20">
-        <v>3.2307048</v>
+        <v>5.559058</v>
       </c>
       <c r="P11" s="12">
-        <v>0.23452999</v>
+        <v>0.19381</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.531</v>
+        <v>0.108</v>
       </c>
       <c r="R11" s="12">
-        <v>0.5564332553700537</v>
+        <v>0.2595584027274918</v>
       </c>
       <c r="S11" s="11">
-        <v>75.04381051862528</v>
+        <v>67.55178261269285</v>
       </c>
       <c r="T11" s="9" t="s">
         <v>87</v>
@@ -4025,10 +4025,10 @@
         <v>92</v>
       </c>
       <c r="E12" s="10">
-        <v>369.3500061035156</v>
+        <v>365.6600036621094</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8197914702434592</v>
+        <v>0.8367848340502836</v>
       </c>
       <c r="G12" s="20">
         <v>1.215230467965422</v>
@@ -4040,16 +4040,16 @@
         <v>-0.3758707799348074</v>
       </c>
       <c r="J12" s="20">
-        <v>0.5627464652637819</v>
+        <v>0.6087177628713963</v>
       </c>
       <c r="K12" s="20">
         <v>3.829153559383143</v>
       </c>
       <c r="L12" s="20">
-        <v>0.6030540698252209</v>
+        <v>0.5896738550462156</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.0804661143928516</v>
+        <v>-0.03040627175184626</v>
       </c>
       <c r="N12" s="20">
         <v>9.931433999999999</v>
@@ -4064,10 +4064,10 @@
         <v>0.003</v>
       </c>
       <c r="R12" s="12">
-        <v>0.2152546687130332</v>
+        <v>0.2154943448119708</v>
       </c>
       <c r="S12" s="11">
-        <v>51.96562033483278</v>
+        <v>48.29533744575358</v>
       </c>
       <c r="T12" s="9" t="s">
         <v>87</v>
@@ -4087,49 +4087,49 @@
         <v>95</v>
       </c>
       <c r="E13" s="10">
-        <v>67.04000091552734</v>
+        <v>335.3800048828125</v>
       </c>
       <c r="F13" s="17">
-        <v>0.8046524634875735</v>
+        <v>0.7837024514101212</v>
       </c>
       <c r="G13" s="20">
-        <v>1.296202382232963</v>
+        <v>-0.3654991602347105</v>
       </c>
       <c r="H13" s="20">
-        <v>-1.353261681376673</v>
+        <v>1.463709249725696</v>
       </c>
       <c r="I13" s="20">
-        <v>-0.5780959126470824</v>
+        <v>1.40880022334584</v>
       </c>
       <c r="J13" s="20">
-        <v>1.085526842283418</v>
+        <v>-0.204157481105242</v>
       </c>
       <c r="K13" s="20">
         <v>4.1972917133727</v>
       </c>
       <c r="L13" s="20">
-        <v>0.00664987963049881</v>
+        <v>0.0842370026628418</v>
       </c>
       <c r="M13" s="20">
-        <v>0.1991930487879585</v>
+        <v>0.336710206609396</v>
       </c>
       <c r="N13" s="20">
-        <v>12.6192465</v>
+        <v>16.83283</v>
       </c>
       <c r="O13" s="20">
-        <v>1.4678257</v>
+        <v>6.5881405</v>
       </c>
       <c r="P13" s="12">
-        <v>-0.20358999</v>
+        <v>0.48676</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.046</v>
+        <v>0.242</v>
       </c>
       <c r="R13" s="12">
-        <v>0.5358533464375972</v>
+        <v>0.09734879457938406</v>
       </c>
       <c r="S13" s="11">
-        <v>55.66966189008534</v>
+        <v>44.19804931660762</v>
       </c>
       <c r="T13" s="9" t="s">
         <v>87</v>
@@ -4146,13 +4146,13 @@
         <v>97</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E14" s="10">
-        <v>338.4599914550781</v>
+        <v>338.3599853515625</v>
       </c>
       <c r="F14" s="17">
-        <v>0.7772698887090254</v>
+        <v>0.7834662720951022</v>
       </c>
       <c r="G14" s="20">
         <v>-0.3753606373785415</v>
@@ -4164,16 +4164,16 @@
         <v>1.40880022334584</v>
       </c>
       <c r="J14" s="20">
-        <v>-0.2341200731129836</v>
+        <v>-0.1816201031699617</v>
       </c>
       <c r="K14" s="20">
         <v>4.1972917133727</v>
       </c>
       <c r="L14" s="20">
-        <v>0.07416160679393015</v>
+        <v>0.06314291840523922</v>
       </c>
       <c r="M14" s="20">
-        <v>0.3984077633500318</v>
+        <v>0.2872516846811813</v>
       </c>
       <c r="N14" s="20">
         <v>16.97392</v>
@@ -4188,10 +4188,10 @@
         <v>0.242</v>
       </c>
       <c r="R14" s="12">
-        <v>0.135998870009276</v>
+        <v>0.1058223886899801</v>
       </c>
       <c r="S14" s="11">
-        <v>44.97250667286116</v>
+        <v>44.89808035345778</v>
       </c>
       <c r="T14" s="9" t="s">
         <v>87</v>
@@ -4202,58 +4202,58 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="E15" s="10">
-        <v>335.3099975585938</v>
+        <v>162.7100067138672</v>
       </c>
       <c r="F15" s="17">
-        <v>0.7763757508527467</v>
+        <v>0.7508875525330688</v>
       </c>
       <c r="G15" s="20">
-        <v>-0.3654991602347105</v>
+        <v>0.4941985872113094</v>
       </c>
       <c r="H15" s="20">
-        <v>1.463709249725696</v>
+        <v>-0.5581494893912904</v>
       </c>
       <c r="I15" s="20">
-        <v>1.40880022334584</v>
+        <v>-0.03241763381358259</v>
       </c>
       <c r="J15" s="20">
-        <v>-0.2592467659346985</v>
+        <v>1.375212031660279</v>
       </c>
       <c r="K15" s="20">
-        <v>4.1972917133727</v>
+        <v>3.296722344935419</v>
       </c>
       <c r="L15" s="20">
-        <v>0.09218432064022211</v>
+        <v>0.2622536311978117</v>
       </c>
       <c r="M15" s="20">
-        <v>0.4457507792696405</v>
+        <v>-0.8678502530400624</v>
       </c>
       <c r="N15" s="20">
-        <v>16.83283</v>
+        <v>17.05809</v>
       </c>
       <c r="O15" s="20">
-        <v>6.5881405</v>
+        <v>4.186674</v>
       </c>
       <c r="P15" s="12">
-        <v>0.48676</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.242</v>
+        <v>0.053</v>
       </c>
       <c r="R15" s="12">
-        <v>0.1262693729675783</v>
+        <v>0.377625973780005</v>
       </c>
       <c r="S15" s="11">
-        <v>44.12846261618915</v>
+        <v>60.03797954474801</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>87</v>
@@ -4270,52 +4270,52 @@
         <v>102</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="E16" s="10">
-        <v>164.4400024414062</v>
+        <v>56.02999877929688</v>
       </c>
       <c r="F16" s="17">
-        <v>0.7561380880467419</v>
+        <v>0.74326451272628</v>
       </c>
       <c r="G16" s="20">
-        <v>0.4941985872113094</v>
+        <v>0.5218225520995097</v>
       </c>
       <c r="H16" s="20">
-        <v>-0.5581494893912904</v>
+        <v>-0.5332485103967138</v>
       </c>
       <c r="I16" s="20">
-        <v>-0.03241763381358259</v>
+        <v>2.225163086097977</v>
       </c>
       <c r="J16" s="20">
-        <v>1.391997972412613</v>
+        <v>2.030330982269093</v>
       </c>
       <c r="K16" s="20">
-        <v>3.296722344935419</v>
+        <v>0.3256630316615335</v>
       </c>
       <c r="L16" s="20">
-        <v>0.2386970777502335</v>
+        <v>-1.239760248452089</v>
       </c>
       <c r="M16" s="20">
-        <v>-0.8474984218547166</v>
+        <v>-0.7706667146367739</v>
       </c>
       <c r="N16" s="20">
-        <v>17.05809</v>
+        <v>26.804123</v>
       </c>
       <c r="O16" s="20">
-        <v>4.186674</v>
+        <v>2.7206612</v>
       </c>
       <c r="P16" s="12">
-        <v>0.26408002</v>
+        <v>0.10936</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.053</v>
+        <v>0.337</v>
       </c>
       <c r="R16" s="12">
-        <v>0.3847812251157086</v>
+        <v>1.593134832549722</v>
       </c>
       <c r="S16" s="11">
-        <v>63.60644195751173</v>
+        <v>57.78308827692286</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>87</v>
@@ -4326,58 +4326,58 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>103</v>
-      </c>
       <c r="E17" s="10">
-        <v>131.4199981689453</v>
+        <v>64.58000183105469</v>
       </c>
       <c r="F17" s="17">
-        <v>0.7151380182450069</v>
+        <v>0.7350680436258861</v>
       </c>
       <c r="G17" s="20">
-        <v>0.3599925540636538</v>
+        <v>1.296202382232963</v>
       </c>
       <c r="H17" s="20">
-        <v>-0.1244310120248844</v>
+        <v>-1.353261681376673</v>
       </c>
       <c r="I17" s="20">
-        <v>0.4821804333312243</v>
+        <v>-0.5780959126470824</v>
       </c>
       <c r="J17" s="20">
-        <v>0.4247096137593809</v>
+        <v>0.8320880019623197</v>
       </c>
       <c r="K17" s="20">
         <v>4.1972917133727</v>
       </c>
       <c r="L17" s="20">
-        <v>0.1687839734058377</v>
+        <v>-0.02742629593900239</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.2398081379060042</v>
+        <v>0.3053405833981097</v>
       </c>
       <c r="N17" s="20">
-        <v>16.105392</v>
+        <v>12.6192465</v>
       </c>
       <c r="O17" s="20">
-        <v>7.2471595</v>
+        <v>1.4678257</v>
       </c>
       <c r="P17" s="12">
-        <v>0.46032003</v>
+        <v>-0.20358999</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.07000000000000001</v>
+        <v>0.046</v>
       </c>
       <c r="R17" s="12">
-        <v>0.1349857252770952</v>
+        <v>0.490766442428451</v>
       </c>
       <c r="S17" s="11">
-        <v>54.16793908636858</v>
+        <v>47.22740624115487</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>87</v>
@@ -4397,10 +4397,10 @@
         <v>38</v>
       </c>
       <c r="E18" s="10">
-        <v>60.04000091552734</v>
+        <v>60.65000152587891</v>
       </c>
       <c r="F18" s="17">
-        <v>0.6940547154223843</v>
+        <v>0.7095984039373823</v>
       </c>
       <c r="G18" s="20">
         <v>0.6321397772136792</v>
@@ -4412,16 +4412,16 @@
         <v>2.930171312463986</v>
       </c>
       <c r="J18" s="20">
-        <v>0.308076137396026</v>
+        <v>0.4329446997788296</v>
       </c>
       <c r="K18" s="20">
         <v>0.8730995961762966</v>
       </c>
       <c r="L18" s="20">
-        <v>0.2425108993694954</v>
+        <v>0.2658765169304781</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.2872440968436206</v>
+        <v>-0.5787293125123976</v>
       </c>
       <c r="N18" s="20">
         <v>17.710915</v>
@@ -4436,10 +4436,10 @@
         <v>0.534</v>
       </c>
       <c r="R18" s="12">
-        <v>0.1183559907738323</v>
+        <v>0.1126760750661084</v>
       </c>
       <c r="S18" s="11">
-        <v>56.82077158947367</v>
+        <v>59.38221223383346</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>87</v>
@@ -4459,10 +4459,10 @@
         <v>92</v>
       </c>
       <c r="E19" s="10">
-        <v>259.5700073242188</v>
+        <v>253.4600067138672</v>
       </c>
       <c r="F19" s="17">
-        <v>0.663117882082194</v>
+        <v>0.6583665893639233</v>
       </c>
       <c r="G19" s="20">
         <v>1.286238812250283</v>
@@ -4474,16 +4474,16 @@
         <v>-0.05063264711205382</v>
       </c>
       <c r="J19" s="20">
-        <v>0.5137962823838743</v>
+        <v>0.4745204787725334</v>
       </c>
       <c r="K19" s="20">
         <v>1.858278441957119</v>
       </c>
       <c r="L19" s="20">
-        <v>0.5308828396445926</v>
+        <v>0.5109336572200091</v>
       </c>
       <c r="M19" s="20">
-        <v>0.01519947010572145</v>
+        <v>0.1180544614883036</v>
       </c>
       <c r="N19" s="20">
         <v>5.1976376</v>
@@ -4498,10 +4498,10 @@
         <v>0.118</v>
       </c>
       <c r="R19" s="12">
-        <v>0.2340966911889795</v>
+        <v>0.2319113426066355</v>
       </c>
       <c r="S19" s="11">
-        <v>51.96035369550701</v>
+        <v>45.56205966278974</v>
       </c>
       <c r="T19" s="9" t="s">
         <v>87</v>
@@ -4518,52 +4518,52 @@
         <v>109</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="E20" s="10">
-        <v>52</v>
+        <v>124.0400009155273</v>
       </c>
       <c r="F20" s="17">
-        <v>0.6255056894289205</v>
+        <v>0.63963859698438</v>
       </c>
       <c r="G20" s="20">
-        <v>0.5218225520995097</v>
+        <v>0.3599925540636538</v>
       </c>
       <c r="H20" s="20">
-        <v>-0.5332485103967138</v>
+        <v>-0.1244310120248844</v>
       </c>
       <c r="I20" s="20">
-        <v>2.225163086097977</v>
+        <v>0.4821804333312243</v>
       </c>
       <c r="J20" s="20">
-        <v>1.578444247606777</v>
+        <v>0.1175161678413195</v>
       </c>
       <c r="K20" s="20">
-        <v>0.3256630316615335</v>
+        <v>4.1972917133727</v>
       </c>
       <c r="L20" s="20">
-        <v>-1.096131212992601</v>
+        <v>0.08623224266917956</v>
       </c>
       <c r="M20" s="20">
-        <v>-0.6557985274646984</v>
+        <v>0.03033831658138225</v>
       </c>
       <c r="N20" s="20">
-        <v>26.804123</v>
+        <v>16.105392</v>
       </c>
       <c r="O20" s="20">
-        <v>2.7206612</v>
+        <v>7.2471595</v>
       </c>
       <c r="P20" s="12">
-        <v>0.10936</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.337</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R20" s="12">
-        <v>1.484071106654971</v>
+        <v>0.0706948860533283</v>
       </c>
       <c r="S20" s="11">
-        <v>48.79187842694703</v>
+        <v>42.11464305912724</v>
       </c>
       <c r="T20" s="9" t="s">
         <v>87</v>
@@ -4583,10 +4583,10 @@
         <v>112</v>
       </c>
       <c r="E21" s="10">
-        <v>258.510009765625</v>
+        <v>256.9700012207031</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6227350145405641</v>
+        <v>0.6342809648252788</v>
       </c>
       <c r="G21" s="20">
         <v>-0.04482148267622166</v>
@@ -4598,16 +4598,16 @@
         <v>1.035672297744961</v>
       </c>
       <c r="J21" s="20">
-        <v>0.1288224939310594</v>
+        <v>0.171386387571603</v>
       </c>
       <c r="K21" s="20">
         <v>4.1972917133727</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.4340688696512446</v>
+        <v>-0.4488605948402165</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.18105295414046</v>
+        <v>-0.1852493828418346</v>
       </c>
       <c r="N21" s="20">
         <v>20.797264</v>
@@ -4622,10 +4622,10 @@
         <v>0.196</v>
       </c>
       <c r="R21" s="12">
-        <v>0.2124665898657911</v>
+        <v>0.2036629097793119</v>
       </c>
       <c r="S21" s="11">
-        <v>49.54908461556447</v>
+        <v>48.12096671477671</v>
       </c>
       <c r="T21" s="9" t="s">
         <v>87</v>
@@ -4642,52 +4642,52 @@
         <v>114</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="E22" s="10">
-        <v>126.75</v>
+        <v>104.4700012207031</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6052465179692325</v>
+        <v>0.6251009131397292</v>
       </c>
       <c r="G22" s="20">
-        <v>0.3314207580374121</v>
+        <v>-0.6233680543607623</v>
       </c>
       <c r="H22" s="20">
-        <v>0.5050654897521694</v>
+        <v>-1.136990927851701</v>
       </c>
       <c r="I22" s="20">
-        <v>0.5229426848176244</v>
+        <v>0.5264142543422116</v>
       </c>
       <c r="J22" s="20">
-        <v>0.8023367939782938</v>
+        <v>1.625224614958064</v>
       </c>
       <c r="K22" s="20">
-        <v>1.6471686892898</v>
+        <v>4.1972917133727</v>
       </c>
       <c r="L22" s="20">
-        <v>0.02304384429526537</v>
+        <v>-2.552284533469248</v>
       </c>
       <c r="M22" s="20">
-        <v>-0.3407234610698928</v>
+        <v>0.3559870982841107</v>
       </c>
       <c r="N22" s="20">
-        <v>16.146498</v>
+        <v>46.910885</v>
       </c>
       <c r="O22" s="20">
-        <v>4.015142</v>
+        <v>5.5187516</v>
       </c>
       <c r="P22" s="12">
-        <v>0.30667</v>
+        <v>-0.10715</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.377</v>
+        <v>0.254</v>
       </c>
       <c r="R22" s="12">
-        <v>0.3211381777628204</v>
+        <v>1.292013975952176</v>
       </c>
       <c r="S22" s="11">
-        <v>56.24137683247642</v>
+        <v>61.69918404310961</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>87</v>
@@ -4704,52 +4704,52 @@
         <v>116</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E23" s="10">
-        <v>1038.609985351562</v>
+        <v>124.4000015258789</v>
       </c>
       <c r="F23" s="17">
-        <v>0.5567895557649366</v>
+        <v>0.5953639290148719</v>
       </c>
       <c r="G23" s="20">
-        <v>0.3667190394925228</v>
+        <v>0.3314207580374121</v>
       </c>
       <c r="H23" s="20">
-        <v>0.8230717495135815</v>
+        <v>0.5050654897521694</v>
       </c>
       <c r="I23" s="20">
-        <v>0.9154597556552251</v>
+        <v>0.5229426848176244</v>
       </c>
       <c r="J23" s="20">
-        <v>0.1690881460517345</v>
+        <v>0.7593354506761331</v>
       </c>
       <c r="K23" s="20">
-        <v>1.663726316949982</v>
+        <v>1.6471686892898</v>
       </c>
       <c r="L23" s="20">
-        <v>0.07221679196558524</v>
+        <v>0.008519108772499218</v>
       </c>
       <c r="M23" s="20">
-        <v>0.1604507975141698</v>
+        <v>-0.2921072339742236</v>
       </c>
       <c r="N23" s="20">
-        <v>16.02546</v>
+        <v>16.146498</v>
       </c>
       <c r="O23" s="20">
-        <v>2.8687</v>
+        <v>4.015142</v>
       </c>
       <c r="P23" s="12">
-        <v>0.16902</v>
+        <v>0.30667</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.425</v>
+        <v>0.377</v>
       </c>
       <c r="R23" s="12">
-        <v>0.2762004315652837</v>
+        <v>0.2811534858987021</v>
       </c>
       <c r="S23" s="11">
-        <v>52.01914901379936</v>
+        <v>50.8479448726449</v>
       </c>
       <c r="T23" s="9" t="s">
         <v>87</v>
@@ -4766,52 +4766,52 @@
         <v>118</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="E24" s="10">
-        <v>219.6000061035156</v>
+        <v>189.1300048828125</v>
       </c>
       <c r="F24" s="17">
-        <v>0.552946378603798</v>
+        <v>0.5697633164143457</v>
       </c>
       <c r="G24" s="20">
-        <v>0.5809437263948974</v>
+        <v>-0.3904668641526476</v>
       </c>
       <c r="H24" s="20">
-        <v>-0.6585101921976751</v>
+        <v>1.359179679828218</v>
       </c>
       <c r="I24" s="20">
-        <v>4.120745224686987</v>
+        <v>0.4411015820383316</v>
       </c>
       <c r="J24" s="20">
-        <v>0.2214005476520888</v>
+        <v>1.32998344249264</v>
       </c>
       <c r="K24" s="20">
-        <v>0.6040381466983412</v>
+        <v>0.4876173272126874</v>
       </c>
       <c r="L24" s="20">
-        <v>0.5051479593581576</v>
+        <v>-0.1241567913855804</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.3443750415658914</v>
+        <v>-0.8948907443088177</v>
       </c>
       <c r="N24" s="20">
-        <v>12.092511</v>
+        <v>26.250353</v>
       </c>
       <c r="O24" s="20">
-        <v>1.3082409</v>
+        <v>26.924416</v>
       </c>
       <c r="P24" s="12">
-        <v>0.09031</v>
+        <v>1.14818</v>
       </c>
       <c r="Q24" s="12">
-        <v>11.11</v>
+        <v>0.299</v>
       </c>
       <c r="R24" s="12">
-        <v>0.1790605320512837</v>
+        <v>0.8952004265981663</v>
       </c>
       <c r="S24" s="11">
-        <v>56.18672088731974</v>
+        <v>53.12450935567445</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>87</v>
@@ -4828,52 +4828,52 @@
         <v>120</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="E25" s="10">
-        <v>230.3600006103516</v>
+        <v>1036.530029296875</v>
       </c>
       <c r="F25" s="17">
-        <v>0.54805248083314</v>
+        <v>0.56734839132417</v>
       </c>
       <c r="G25" s="20">
-        <v>-1.255664189485384</v>
+        <v>0.3667190394925228</v>
       </c>
       <c r="H25" s="20">
-        <v>2.368358787986747</v>
+        <v>0.8230717495135815</v>
       </c>
       <c r="I25" s="20">
-        <v>2.430954222251415</v>
+        <v>0.9154597556552251</v>
       </c>
       <c r="J25" s="20">
-        <v>0.6805355925506037</v>
+        <v>0.2165283389004759</v>
       </c>
       <c r="K25" s="20">
-        <v>-0.308183652204804</v>
+        <v>1.663726316949982</v>
       </c>
       <c r="L25" s="20">
-        <v>-0.1974506000229282</v>
+        <v>0.1024364401273346</v>
       </c>
       <c r="M25" s="20">
-        <v>-0.04115496077176295</v>
+        <v>0.09187078270049481</v>
       </c>
       <c r="N25" s="20">
-        <v>29.159492</v>
+        <v>16.02546</v>
       </c>
       <c r="O25" s="20">
-        <v>24.291891</v>
+        <v>2.8687</v>
       </c>
       <c r="P25" s="12">
-        <v>1.17211</v>
+        <v>0.16902</v>
       </c>
       <c r="Q25" s="12">
-        <v>1.059</v>
+        <v>0.425</v>
       </c>
       <c r="R25" s="12">
-        <v>0.2970472917197908</v>
+        <v>0.2574030332256332</v>
       </c>
       <c r="S25" s="11">
-        <v>60.39296241086813</v>
+        <v>51.43317778574706</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>87</v>
@@ -4890,52 +4890,52 @@
         <v>122</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="E26" s="10">
-        <v>185.5899963378906</v>
+        <v>213.9600067138672</v>
       </c>
       <c r="F26" s="17">
-        <v>0.522421941123522</v>
+        <v>0.5463955641114731</v>
       </c>
       <c r="G26" s="20">
-        <v>-0.3904668641526476</v>
+        <v>0.5809437263948974</v>
       </c>
       <c r="H26" s="20">
-        <v>1.359179679828218</v>
+        <v>-0.6585101921976751</v>
       </c>
       <c r="I26" s="20">
-        <v>0.4411015820383316</v>
+        <v>4.120745224686987</v>
       </c>
       <c r="J26" s="20">
-        <v>1.161291153425794</v>
+        <v>0.1353151982103833</v>
       </c>
       <c r="K26" s="20">
-        <v>0.4876173272126874</v>
+        <v>0.6040381466983412</v>
       </c>
       <c r="L26" s="20">
-        <v>-0.1017542140299229</v>
+        <v>0.4815902196986752</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.8708637844601874</v>
+        <v>-0.08577185756894479</v>
       </c>
       <c r="N26" s="20">
-        <v>26.250353</v>
+        <v>12.092511</v>
       </c>
       <c r="O26" s="20">
-        <v>26.924416</v>
+        <v>1.3082409</v>
       </c>
       <c r="P26" s="12">
-        <v>1.14818</v>
+        <v>0.09031</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.299</v>
+        <v>11.11</v>
       </c>
       <c r="R26" s="12">
-        <v>0.8514465022793682</v>
+        <v>0.1610254620931819</v>
       </c>
       <c r="S26" s="11">
-        <v>49.08437153264291</v>
+        <v>48.03128741189954</v>
       </c>
       <c r="T26" s="9" t="s">
         <v>87</v>
@@ -4952,52 +4952,52 @@
         <v>124</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="E27" s="10">
-        <v>220.8300018310547</v>
+        <v>225.7299957275391</v>
       </c>
       <c r="F27" s="17">
-        <v>0.520678142547652</v>
+        <v>0.5189681794547308</v>
       </c>
       <c r="G27" s="20">
-        <v>0.2276945080429548</v>
+        <v>-1.255664189485384</v>
       </c>
       <c r="H27" s="20">
-        <v>0.03119877719549098</v>
+        <v>2.368358787986747</v>
       </c>
       <c r="I27" s="20">
-        <v>-0.8985721544356027</v>
+        <v>2.430954222251415</v>
       </c>
       <c r="J27" s="20">
-        <v>0.5872600250002363</v>
+        <v>0.5843720113700576</v>
       </c>
       <c r="K27" s="20">
-        <v>3.376923353914425</v>
+        <v>-0.308183652204804</v>
       </c>
       <c r="L27" s="20">
-        <v>-0.07384581612384766</v>
+        <v>-0.2161934998125696</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.1552439851271158</v>
+        <v>-0.0300381237325984</v>
       </c>
       <c r="N27" s="20">
-        <v>39.2238</v>
+        <v>29.159492</v>
       </c>
       <c r="O27" s="20">
-        <v>1.730507</v>
+        <v>24.291891</v>
       </c>
       <c r="P27" s="12">
-        <v>0.04575</v>
+        <v>1.17211</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.034</v>
+        <v>1.059</v>
       </c>
       <c r="R27" s="12">
-        <v>0.1945151060942716</v>
+        <v>0.2373683124047306</v>
       </c>
       <c r="S27" s="11">
-        <v>57.98177418064045</v>
+        <v>56.14653691353901</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>87</v>
@@ -5014,52 +5014,52 @@
         <v>126</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="E28" s="10">
-        <v>66.81999969482422</v>
+        <v>40.2599983215332</v>
       </c>
       <c r="F28" s="17">
-        <v>0.5052905423289454</v>
+        <v>0.5041545557798331</v>
       </c>
       <c r="G28" s="20">
-        <v>0.4785242056074159</v>
+        <v>0.09785741135882757</v>
       </c>
       <c r="H28" s="20">
-        <v>0.6574599095763384</v>
+        <v>-0.81219220040201</v>
       </c>
       <c r="I28" s="20">
-        <v>0.2335665909722698</v>
+        <v>3.920900829953943</v>
       </c>
       <c r="J28" s="20">
-        <v>0.628830058691316</v>
+        <v>0.2670313249003679</v>
       </c>
       <c r="K28" s="20">
-        <v>0.8084213631287113</v>
+        <v>3.385719593608896</v>
       </c>
       <c r="L28" s="20">
-        <v>0.5891886061448869</v>
+        <v>-3.416720321042702</v>
       </c>
       <c r="M28" s="20">
-        <v>-0.3800619607670498</v>
+        <v>-0.7123954829555538</v>
       </c>
       <c r="N28" s="20">
-        <v>14.718061</v>
+        <v>12.144172</v>
       </c>
       <c r="O28" s="20">
-        <v>6.116247</v>
+        <v>2.3688147</v>
       </c>
       <c r="P28" s="12">
-        <v>0.46598998</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.057</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R28" s="12">
-        <v>0.1323774878225439</v>
+        <v>0.2589117854226792</v>
       </c>
       <c r="S28" s="11">
-        <v>56.57200070071893</v>
+        <v>64.14745634614101</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>87</v>
@@ -5070,58 +5070,58 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E29" s="10">
-        <v>95.80000305175781</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="F29" s="17">
-        <v>0.5018935231674446</v>
+        <v>0.4990836376154188</v>
       </c>
       <c r="G29" s="20">
-        <v>-0.6233680543607623</v>
+        <v>1.1788603618118</v>
       </c>
       <c r="H29" s="20">
-        <v>-1.136990927851701</v>
+        <v>0.561859549662265</v>
       </c>
       <c r="I29" s="20">
-        <v>0.5264142543422116</v>
+        <v>-0.2890980177519417</v>
       </c>
       <c r="J29" s="20">
-        <v>1.110541736797623</v>
+        <v>1.260448221343344</v>
       </c>
       <c r="K29" s="20">
-        <v>4.1972917133727</v>
+        <v>-0.5746579723608561</v>
       </c>
       <c r="L29" s="20">
-        <v>-2.514098104654919</v>
+        <v>-0.3491559703348047</v>
       </c>
       <c r="M29" s="20">
-        <v>0.7173156951214641</v>
+        <v>-0.7790638147635713</v>
       </c>
       <c r="N29" s="20">
-        <v>46.910885</v>
+        <v>9.023208</v>
       </c>
       <c r="O29" s="20">
-        <v>5.5187516</v>
+        <v>2.1361504</v>
       </c>
       <c r="P29" s="12">
-        <v>-0.10715</v>
+        <v>0.26659</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.254</v>
+        <v>0.092</v>
       </c>
       <c r="R29" s="12">
-        <v>1.206356681062127</v>
+        <v>0.3547121947190726</v>
       </c>
       <c r="S29" s="11">
-        <v>51.74428988479696</v>
+        <v>60.45630612065907</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>87</v>
@@ -5132,58 +5132,58 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>129</v>
+        <v>3</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="10">
-        <v>39.59000015258789</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4824297428111422</v>
+        <v>0.4902183444336746</v>
       </c>
       <c r="G30" s="20">
-        <v>0.09785741135882757</v>
+        <v>-0.9800881674162824</v>
       </c>
       <c r="H30" s="20">
-        <v>-0.81219220040201</v>
+        <v>2.147104391138658</v>
       </c>
       <c r="I30" s="20">
-        <v>3.920900829953943</v>
+        <v>2.675284350851072</v>
       </c>
       <c r="J30" s="20">
-        <v>0.188999388927631</v>
+        <v>0.7835826359838297</v>
       </c>
       <c r="K30" s="20">
-        <v>3.385719593608896</v>
+        <v>-0.2197038293957071</v>
       </c>
       <c r="L30" s="20">
-        <v>-3.413048273912248</v>
+        <v>-3.416720321042702</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.694089920514268</v>
+        <v>0.648274561202637</v>
       </c>
       <c r="N30" s="20">
-        <v>12.144172</v>
+        <v>17.358335</v>
       </c>
       <c r="O30" s="20">
-        <v>2.3688147</v>
+        <v>22.350464</v>
       </c>
       <c r="P30" s="12">
-        <v>0.21465999</v>
+        <v>1.30853</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.9320000000000001</v>
+        <v>0.438</v>
       </c>
       <c r="R30" s="12">
-        <v>0.2644522781181176</v>
+        <v>0.822398437321578</v>
       </c>
       <c r="S30" s="11">
-        <v>62.65598266458546</v>
+        <v>50.4863565454001</v>
       </c>
       <c r="T30" s="9" t="s">
         <v>87</v>
@@ -5194,58 +5194,58 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="E31" s="10">
-        <v>32.63999938964844</v>
+        <v>64.69000244140625</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4812241609106595</v>
+        <v>0.4835314296583552</v>
       </c>
       <c r="G31" s="20">
-        <v>1.115176779328165</v>
+        <v>0.4785242056074159</v>
       </c>
       <c r="H31" s="20">
-        <v>-0.9874044575767369</v>
+        <v>0.6574599095763384</v>
       </c>
       <c r="I31" s="20">
-        <v>-0.3840221445724293</v>
+        <v>0.2335665909722698</v>
       </c>
       <c r="J31" s="20">
-        <v>1.625577115413821</v>
+        <v>0.5112723003362208</v>
       </c>
       <c r="K31" s="20">
-        <v>0.4074163182336814</v>
+        <v>0.8084213631287113</v>
       </c>
       <c r="L31" s="20">
-        <v>-0.4631480199946686</v>
+        <v>0.5464006194230052</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.3986867913924674</v>
+        <v>-0.1791182852764088</v>
       </c>
       <c r="N31" s="20">
-        <v>12.458015</v>
+        <v>14.718061</v>
       </c>
       <c r="O31" s="20">
-        <v>-320</v>
+        <v>6.116247</v>
       </c>
       <c r="P31" s="12">
-        <v>0</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.125</v>
+        <v>0.057</v>
       </c>
       <c r="R31" s="12">
-        <v>0.7252534861688946</v>
+        <v>0.09013335897834285</v>
       </c>
       <c r="S31" s="11">
-        <v>66.42670701840595</v>
+        <v>46.65735197441372</v>
       </c>
       <c r="T31" s="9" t="s">
         <v>87</v>
@@ -5256,58 +5256,58 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="E32" s="10">
-        <v>362.739990234375</v>
+        <v>212.5</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4757791556353333</v>
+        <v>0.4753714760860758</v>
       </c>
       <c r="G32" s="20">
-        <v>0.09769025453656566</v>
+        <v>0.2276945080429548</v>
       </c>
       <c r="H32" s="20">
-        <v>-0.2373803208952873</v>
+        <v>0.03119877719549098</v>
       </c>
       <c r="I32" s="20">
-        <v>0.4704496970046058</v>
+        <v>-0.8985721544356027</v>
       </c>
       <c r="J32" s="20">
-        <v>1.550509301618796</v>
+        <v>0.401909284420032</v>
       </c>
       <c r="K32" s="20">
-        <v>1.706672663693578</v>
+        <v>3.376923353914425</v>
       </c>
       <c r="L32" s="20">
-        <v>-1.627723688728139</v>
+        <v>-0.1154307044985162</v>
       </c>
       <c r="M32" s="20">
-        <v>-1.539491216795537</v>
+        <v>0.004676627559951518</v>
       </c>
       <c r="N32" s="20">
-        <v>33.248394</v>
+        <v>39.2238</v>
       </c>
       <c r="O32" s="20">
-        <v>5.0043454</v>
+        <v>1.730507</v>
       </c>
       <c r="P32" s="12">
-        <v>0.15286</v>
+        <v>0.04575</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.204</v>
+        <v>0.034</v>
       </c>
       <c r="R32" s="12">
-        <v>0.6514454828772971</v>
+        <v>0.1288779951067147</v>
       </c>
       <c r="S32" s="11">
-        <v>60.70089865252772</v>
+        <v>47.84446106344914</v>
       </c>
       <c r="T32" s="9" t="s">
         <v>87</v>
@@ -5318,58 +5318,58 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E33" s="10">
-        <v>42.77000045776367</v>
+        <v>352.5400085449219</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4684777520956978</v>
+        <v>0.4656193589205661</v>
       </c>
       <c r="G33" s="20">
-        <v>1.1788603618118</v>
+        <v>0.09769025453656566</v>
       </c>
       <c r="H33" s="20">
-        <v>0.561859549662265</v>
+        <v>-0.2373803208952873</v>
       </c>
       <c r="I33" s="20">
-        <v>-0.2890980177519417</v>
+        <v>0.4704496970046058</v>
       </c>
       <c r="J33" s="20">
-        <v>1.062414648139563</v>
+        <v>1.44106755832677</v>
       </c>
       <c r="K33" s="20">
-        <v>-0.5746579723608561</v>
+        <v>1.706672663693578</v>
       </c>
       <c r="L33" s="20">
-        <v>-0.3625914989144247</v>
+        <v>-1.684092777206551</v>
       </c>
       <c r="M33" s="20">
-        <v>-0.4089348378111903</v>
+        <v>-1.213805322026222</v>
       </c>
       <c r="N33" s="20">
-        <v>9.023208</v>
+        <v>33.248394</v>
       </c>
       <c r="O33" s="20">
-        <v>2.1361504</v>
+        <v>5.0043454</v>
       </c>
       <c r="P33" s="12">
-        <v>0.26659</v>
+        <v>0.15286</v>
       </c>
       <c r="Q33" s="12">
-        <v>0.092</v>
+        <v>0.204</v>
       </c>
       <c r="R33" s="12">
-        <v>0.3267847498375229</v>
+        <v>0.6490785412945888</v>
       </c>
       <c r="S33" s="11">
-        <v>57.62085530467043</v>
+        <v>53.80004140607057</v>
       </c>
       <c r="T33" s="9" t="s">
         <v>87</v>
@@ -5380,58 +5380,58 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E34" s="10">
-        <v>467.4599914550781</v>
+        <v>209.8000030517578</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4615738198953969</v>
+        <v>0.4493945547233394</v>
       </c>
       <c r="G34" s="20">
-        <v>-0.9800881674162824</v>
+        <v>0.5306330587817526</v>
       </c>
       <c r="H34" s="20">
-        <v>2.147104391138658</v>
+        <v>-0.3271612979466518</v>
       </c>
       <c r="I34" s="20">
-        <v>2.675284350851072</v>
+        <v>2.322186162377909</v>
       </c>
       <c r="J34" s="20">
-        <v>0.6826313920476575</v>
+        <v>0.6846640972297852</v>
       </c>
       <c r="K34" s="20">
-        <v>-0.2197038293957071</v>
+        <v>-0.1695135205507808</v>
       </c>
       <c r="L34" s="20">
-        <v>-3.413048273912248</v>
+        <v>0.7718811317766416</v>
       </c>
       <c r="M34" s="20">
-        <v>0.6660311338869707</v>
+        <v>-0.7170334879142883</v>
       </c>
       <c r="N34" s="20">
-        <v>17.358335</v>
+        <v>20.076998</v>
       </c>
       <c r="O34" s="20">
-        <v>22.350464</v>
+        <v>2.1549587</v>
       </c>
       <c r="P34" s="12">
-        <v>1.30853</v>
+        <v>0.12231</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.438</v>
+        <v>0.535</v>
       </c>
       <c r="R34" s="12">
-        <v>0.9065519122333334</v>
+        <v>0.1273719414412338</v>
       </c>
       <c r="S34" s="11">
-        <v>48.28405027473934</v>
+        <v>66.2812788972652</v>
       </c>
       <c r="T34" s="9" t="s">
         <v>87</v>
@@ -5448,52 +5448,52 @@
         <v>136</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="E35" s="10">
-        <v>208.6000061035156</v>
+        <v>216.2400054931641</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4346747015646415</v>
+        <v>0.4344472686351803</v>
       </c>
       <c r="G35" s="20">
-        <v>0.5306330587817526</v>
+        <v>0.3451625228080399</v>
       </c>
       <c r="H35" s="20">
-        <v>-0.3271612979466518</v>
+        <v>0.7739793579701058</v>
       </c>
       <c r="I35" s="20">
-        <v>2.322186162377909</v>
+        <v>0.3853148937972363</v>
       </c>
       <c r="J35" s="20">
-        <v>0.5784449720178412</v>
+        <v>0.4614414911879133</v>
       </c>
       <c r="K35" s="20">
-        <v>-0.1695135205507808</v>
+        <v>0.3013440160356414</v>
       </c>
       <c r="L35" s="20">
-        <v>0.7475492391306515</v>
+        <v>0.5716186384678913</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.4844610133687292</v>
+        <v>0.01323725357585087</v>
       </c>
       <c r="N35" s="20">
-        <v>20.076998</v>
+        <v>17.572235</v>
       </c>
       <c r="O35" s="20">
-        <v>2.1549587</v>
+        <v>3.211162</v>
       </c>
       <c r="P35" s="12">
-        <v>0.12231</v>
+        <v>0.17969999</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.535</v>
+        <v>0.28</v>
       </c>
       <c r="R35" s="12">
-        <v>0.1179728387132282</v>
+        <v>0.3624108746719914</v>
       </c>
       <c r="S35" s="11">
-        <v>64.86600952846281</v>
+        <v>52.49376650997617</v>
       </c>
       <c r="T35" s="9" t="s">
         <v>87</v>
@@ -5510,52 +5510,52 @@
         <v>138</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="E36" s="10">
-        <v>217.7200012207031</v>
+        <v>904.3800048828125</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4227496572368312</v>
+        <v>0.4277528213124358</v>
       </c>
       <c r="G36" s="20">
-        <v>0.3451625228080399</v>
+        <v>-2.161506497931219</v>
       </c>
       <c r="H36" s="20">
-        <v>0.7739793579701058</v>
+        <v>1.683877559410052</v>
       </c>
       <c r="I36" s="20">
-        <v>0.3853148937972363</v>
+        <v>1.349061869241311</v>
       </c>
       <c r="J36" s="20">
-        <v>0.4301638300727013</v>
+        <v>2.004312972346333</v>
       </c>
       <c r="K36" s="20">
-        <v>0.3013440160356414</v>
+        <v>-0.00135011462705862</v>
       </c>
       <c r="L36" s="20">
-        <v>0.5426537034617692</v>
+        <v>-3.02413084282166</v>
       </c>
       <c r="M36" s="20">
-        <v>0.006032041533124199</v>
+        <v>-0.08983291086297163</v>
       </c>
       <c r="N36" s="20">
-        <v>17.572235</v>
+        <v>60.967697</v>
       </c>
       <c r="O36" s="20">
-        <v>3.211162</v>
+        <v>88.88330999999999</v>
       </c>
       <c r="P36" s="12">
-        <v>0.17969999</v>
+        <v>3.7152898</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.28</v>
+        <v>0.485</v>
       </c>
       <c r="R36" s="12">
-        <v>0.3732761020184954</v>
+        <v>1.421936781263033</v>
       </c>
       <c r="S36" s="11">
-        <v>54.99960803944877</v>
+        <v>57.10377197111912</v>
       </c>
       <c r="T36" s="9" t="s">
         <v>87</v>
@@ -5572,52 +5572,52 @@
         <v>140</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="E37" s="10">
-        <v>827.719970703125</v>
+        <v>31.17000007629395</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4189457412911765</v>
+        <v>0.4154376913907029</v>
       </c>
       <c r="G37" s="20">
-        <v>0.1366671162081818</v>
+        <v>1.115176779328165</v>
       </c>
       <c r="H37" s="20">
-        <v>0.1794925664991855</v>
+        <v>-0.9874044575767369</v>
       </c>
       <c r="I37" s="20">
-        <v>-0.2394962708042926</v>
+        <v>-0.3840221445724293</v>
       </c>
       <c r="J37" s="20">
-        <v>0.8187548832713843</v>
+        <v>1.386920958048624</v>
       </c>
       <c r="K37" s="20">
-        <v>1.442268046995049</v>
+        <v>0.4074163182336814</v>
       </c>
       <c r="L37" s="20">
-        <v>0.5301391500210495</v>
+        <v>-0.5541681022294552</v>
       </c>
       <c r="M37" s="20">
-        <v>-0.7616312850977612</v>
+        <v>-0.2577920085963465</v>
       </c>
       <c r="N37" s="20">
-        <v>20.49319</v>
+        <v>12.458015</v>
       </c>
       <c r="O37" s="20">
-        <v>2.6184473</v>
+        <v>-320</v>
       </c>
       <c r="P37" s="12">
-        <v>0.14043</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.167</v>
+        <v>0.125</v>
       </c>
       <c r="R37" s="12">
-        <v>0.09220672105083549</v>
+        <v>0.6936817041972732</v>
       </c>
       <c r="S37" s="11">
-        <v>60.53735125037876</v>
+        <v>57.41290193179169</v>
       </c>
       <c r="T37" s="9" t="s">
         <v>87</v>
@@ -5634,52 +5634,52 @@
         <v>142</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E38" s="10">
-        <v>437.2300109863281</v>
+        <v>810.3099975585938</v>
       </c>
       <c r="F38" s="17">
-        <v>0.3985641885542739</v>
+        <v>0.4132387079613485</v>
       </c>
       <c r="G38" s="20">
-        <v>-0.2804627171735288</v>
+        <v>0.1366671162081818</v>
       </c>
       <c r="H38" s="20">
-        <v>1.236068066008634</v>
+        <v>0.1794925664991855</v>
       </c>
       <c r="I38" s="20">
-        <v>-0.09373645267036328</v>
+        <v>-0.2394962708042926</v>
       </c>
       <c r="J38" s="20">
-        <v>0.9557073908014219</v>
+        <v>0.7912049523977567</v>
       </c>
       <c r="K38" s="20">
-        <v>-0.007559224999626784</v>
+        <v>1.442268046995049</v>
       </c>
       <c r="L38" s="20">
-        <v>0.6793784319733565</v>
+        <v>0.4983102686747095</v>
       </c>
       <c r="M38" s="20">
-        <v>-0.8239697975963599</v>
+        <v>-0.7057852999347519</v>
       </c>
       <c r="N38" s="20">
-        <v>27.17402</v>
+        <v>20.49319</v>
       </c>
       <c r="O38" s="20">
-        <v>20.223404</v>
+        <v>2.6184473</v>
       </c>
       <c r="P38" s="12">
-        <v>0.91473</v>
+        <v>0.14043</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.095</v>
+        <v>0.167</v>
       </c>
       <c r="R38" s="12">
-        <v>0.1991076631844904</v>
+        <v>0.03949326488628557</v>
       </c>
       <c r="S38" s="11">
-        <v>62.51462135710453</v>
+        <v>54.60457700322396</v>
       </c>
       <c r="T38" s="9" t="s">
         <v>87</v>
@@ -5696,52 +5696,52 @@
         <v>144</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E39" s="10">
-        <v>122.1100006103516</v>
+        <v>28.1200008392334</v>
       </c>
       <c r="F39" s="17">
-        <v>0.3894543814026363</v>
+        <v>0.3837410464321968</v>
       </c>
       <c r="G39" s="20">
-        <v>-1.586610271874681</v>
+        <v>-0.07115990276327171</v>
       </c>
       <c r="H39" s="20">
-        <v>1.32587516746117</v>
+        <v>-0.995994779142174</v>
       </c>
       <c r="I39" s="20">
-        <v>0.4276315627072161</v>
+        <v>-1.178947812209808</v>
       </c>
       <c r="J39" s="20">
-        <v>1.164955143632103</v>
+        <v>0.467827712689896</v>
       </c>
       <c r="K39" s="20">
-        <v>1.634750468544663</v>
+        <v>4.1972917133727</v>
       </c>
       <c r="L39" s="20">
-        <v>-2.390943846127985</v>
+        <v>1.138192555980974</v>
       </c>
       <c r="M39" s="20">
-        <v>0.2242634841032342</v>
+        <v>-0.4813887244654603</v>
       </c>
       <c r="N39" s="20">
-        <v>54.030975</v>
+        <v>403.57144</v>
       </c>
       <c r="O39" s="20">
-        <v>11.579896</v>
+        <v>2.1576414</v>
       </c>
       <c r="P39" s="12">
-        <v>0.23618999</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.323</v>
+        <v>-0.112</v>
       </c>
       <c r="R39" s="12">
-        <v>0.5839928189273125</v>
+        <v>0.01333336357597825</v>
       </c>
       <c r="S39" s="11">
-        <v>65.9432414498592</v>
+        <v>54.16855663700049</v>
       </c>
       <c r="T39" s="9" t="s">
         <v>87</v>
@@ -5758,52 +5758,52 @@
         <v>146</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="E40" s="10">
-        <v>30.64999961853027</v>
+        <v>119.379997253418</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3807072185814189</v>
+        <v>0.3591119368714275</v>
       </c>
       <c r="G40" s="20">
-        <v>0.5193752875190029</v>
+        <v>1.185896662709272</v>
       </c>
       <c r="H40" s="20">
-        <v>0.748394208904259</v>
+        <v>-0.6467007744749826</v>
       </c>
       <c r="I40" s="20">
-        <v>-0.1830681180986245</v>
+        <v>0.146369195149319</v>
       </c>
       <c r="J40" s="20">
-        <v>0.8101823759526935</v>
+        <v>0.509282420047845</v>
       </c>
       <c r="K40" s="20">
-        <v>-0.4722076512134807</v>
+        <v>0.1999285466170274</v>
       </c>
       <c r="L40" s="20">
-        <v>0.2057863477358395</v>
+        <v>1.025931813932411</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.1619196286395165</v>
+        <v>-0.04807898074397064</v>
       </c>
       <c r="N40" s="20">
-        <v>17.923977</v>
+        <v>11.062556</v>
       </c>
       <c r="O40" s="20">
-        <v>6.912494</v>
+        <v>1.3339746</v>
       </c>
       <c r="P40" s="12">
-        <v>0.41944</v>
+        <v>0.12011</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.063</v>
+        <v>0.141</v>
       </c>
       <c r="R40" s="12">
-        <v>0.368867603719909</v>
+        <v>0.2759723296696863</v>
       </c>
       <c r="S40" s="11">
-        <v>61.58963480285758</v>
+        <v>49.01858868837134</v>
       </c>
       <c r="T40" s="9" t="s">
         <v>87</v>
@@ -5820,52 +5820,52 @@
         <v>148</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="E41" s="10">
-        <v>28.25</v>
+        <v>135.0399932861328</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3769766818440744</v>
+        <v>0.3569557698999941</v>
       </c>
       <c r="G41" s="20">
-        <v>-0.07115990276327171</v>
+        <v>0.5166686592886003</v>
       </c>
       <c r="H41" s="20">
-        <v>-0.995994779142174</v>
+        <v>-0.1376180067425467</v>
       </c>
       <c r="I41" s="20">
-        <v>-1.178947812209808</v>
+        <v>0.8009706460259883</v>
       </c>
       <c r="J41" s="20">
-        <v>0.4400046741952777</v>
+        <v>0.84527793237839</v>
       </c>
       <c r="K41" s="20">
-        <v>4.1972917133727</v>
+        <v>-0.06706319940340542</v>
       </c>
       <c r="L41" s="20">
-        <v>1.102880601617674</v>
+        <v>0.4731600917334195</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.4351229216896976</v>
+        <v>-0.8506021698107358</v>
       </c>
       <c r="N41" s="20">
-        <v>403.57144</v>
+        <v>17.759258</v>
       </c>
       <c r="O41" s="20">
-        <v>2.1576414</v>
+        <v>2.4681509</v>
       </c>
       <c r="P41" s="12">
-        <v>-0.08785999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="Q41" s="12">
-        <v>-0.112</v>
+        <v>0.355</v>
       </c>
       <c r="R41" s="12">
-        <v>0.01073342500435048</v>
+        <v>0.1702209725733994</v>
       </c>
       <c r="S41" s="11">
-        <v>56.86895301924928</v>
+        <v>64.3914408919788</v>
       </c>
       <c r="T41" s="9" t="s">
         <v>87</v>
@@ -5882,52 +5882,52 @@
         <v>150</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="E42" s="10">
-        <v>30.38999938964844</v>
+        <v>145.3600006103516</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3561189445042669</v>
+        <v>0.3525353757260941</v>
       </c>
       <c r="G42" s="20">
-        <v>0.4651535335003561</v>
+        <v>0.6186160464919896</v>
       </c>
       <c r="H42" s="20">
-        <v>-0.2838674139749334</v>
+        <v>0.4653349166417897</v>
       </c>
       <c r="I42" s="20">
-        <v>-0.7020967881923148</v>
+        <v>1.428599056298859</v>
       </c>
       <c r="J42" s="20">
-        <v>0.474719277334086</v>
+        <v>0.2986500093411688</v>
       </c>
       <c r="K42" s="20">
-        <v>2.024372144423318</v>
+        <v>-0.5182585531433617</v>
       </c>
       <c r="L42" s="20">
-        <v>0.5797697905351504</v>
+        <v>0.2865535970011453</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.4013356804213674</v>
+        <v>-0.2590774647531525</v>
       </c>
       <c r="N42" s="20">
-        <v>29.504854</v>
+        <v>11.298833</v>
       </c>
       <c r="O42" s="20">
-        <v>1.9370259</v>
+        <v>2.394452</v>
       </c>
       <c r="P42" s="12">
-        <v>0.07979</v>
+        <v>0.22507</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.108</v>
+        <v>0.587</v>
       </c>
       <c r="R42" s="12">
-        <v>0.239520454510977</v>
+        <v>0.1208003282051089</v>
       </c>
       <c r="S42" s="11">
-        <v>58.01771784522179</v>
+        <v>50.88260764505864</v>
       </c>
       <c r="T42" s="9" t="s">
         <v>87</v>
@@ -5947,49 +5947,49 @@
         <v>153</v>
       </c>
       <c r="E43" s="10">
-        <v>97.36000061035156</v>
+        <v>127.0899963378906</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3559265600793516</v>
+        <v>0.3498879729099648</v>
       </c>
       <c r="G43" s="20">
-        <v>0.7729141735395381</v>
+        <v>0.462770354618154</v>
       </c>
       <c r="H43" s="20">
-        <v>-0.7070924070566372</v>
+        <v>0.7818596344809873</v>
       </c>
       <c r="I43" s="20">
-        <v>0.5525999266284973</v>
+        <v>-0.2047856713387676</v>
       </c>
       <c r="J43" s="20">
-        <v>0.6907019544980174</v>
+        <v>1.082681910991223</v>
       </c>
       <c r="K43" s="20">
-        <v>0.9181156463774164</v>
+        <v>-0.3330200936950768</v>
       </c>
       <c r="L43" s="20">
-        <v>-0.04340261418344179</v>
+        <v>-0.5670289724339773</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.5012938219405213</v>
+        <v>-1.11062611265379</v>
       </c>
       <c r="N43" s="20">
-        <v>23.8044</v>
+        <v>16.152584</v>
       </c>
       <c r="O43" s="20">
-        <v>1.6411294</v>
+        <v>3.848858</v>
       </c>
       <c r="P43" s="12">
-        <v>0.06886</v>
+        <v>0.25905</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.004</v>
+        <v>0.151</v>
       </c>
       <c r="R43" s="12">
-        <v>0.307737973423585</v>
+        <v>0.09141523283859998</v>
       </c>
       <c r="S43" s="11">
-        <v>50.14899141751228</v>
+        <v>59.21893500836516</v>
       </c>
       <c r="T43" s="9" t="s">
         <v>87</v>
@@ -6006,52 +6006,52 @@
         <v>155</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E44" s="10">
-        <v>122.0199966430664</v>
+        <v>403.0899963378906</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3554764771362848</v>
+        <v>0.348493922306141</v>
       </c>
       <c r="G44" s="20">
-        <v>1.185896662709272</v>
+        <v>0.3688830871595546</v>
       </c>
       <c r="H44" s="20">
-        <v>-0.6467007744749826</v>
+        <v>-1.053638917449358</v>
       </c>
       <c r="I44" s="20">
-        <v>0.146369195149319</v>
+        <v>0.1661481722292586</v>
       </c>
       <c r="J44" s="20">
-        <v>0.5603921207836885</v>
+        <v>1.513072995384774</v>
       </c>
       <c r="K44" s="20">
-        <v>0.1999285466170274</v>
+        <v>-0.1721006498726843</v>
       </c>
       <c r="L44" s="20">
-        <v>1.055636964533815</v>
+        <v>0.1932687714983893</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.3074624681437192</v>
+        <v>-0.1350446341777612</v>
       </c>
       <c r="N44" s="20">
-        <v>11.062556</v>
+        <v>38.02462</v>
       </c>
       <c r="O44" s="20">
-        <v>1.3339746</v>
+        <v>2.5096092</v>
       </c>
       <c r="P44" s="12">
-        <v>0.12011</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.141</v>
+        <v>0.262</v>
       </c>
       <c r="R44" s="12">
-        <v>0.2882093449476779</v>
+        <v>1.274648731403301</v>
       </c>
       <c r="S44" s="11">
-        <v>56.88897936180841</v>
+        <v>60.23905928676178</v>
       </c>
       <c r="T44" s="9" t="s">
         <v>87</v>
@@ -6371,7 +6371,7 @@
         <v>215</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6508,10 +6508,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BI9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:60">
+    <row r="1" spans="1:61">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6692,8 +6692,11 @@
       <c r="BH1">
         <v>524.1400146484375</v>
       </c>
-    </row>
-    <row r="2" spans="1:60">
+      <c r="BI1">
+        <v>533.8800048828125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:61">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6874,8 +6877,11 @@
       <c r="BH2">
         <v>1016.590026855469</v>
       </c>
-    </row>
-    <row r="3" spans="1:60">
+      <c r="BI2">
+        <v>1000.260009765625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:61">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7056,190 +7062,196 @@
       <c r="BH3">
         <v>1740</v>
       </c>
-    </row>
-    <row r="4" spans="1:60">
+      <c r="BI3">
+        <v>1737.989990234375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:61">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>562.9299926757812</v>
+        <v>562.7493286132812</v>
       </c>
       <c r="C4">
-        <v>653.530029296875</v>
+        <v>653.3203125</v>
       </c>
       <c r="D4">
-        <v>681.0800170898438</v>
+        <v>680.8614501953125</v>
       </c>
       <c r="E4">
-        <v>712.1300048828125</v>
+        <v>711.9014892578125</v>
       </c>
       <c r="F4">
-        <v>746.22998046875</v>
+        <v>745.990478515625</v>
       </c>
       <c r="G4">
-        <v>732.6199951171875</v>
+        <v>732.3848876953125</v>
       </c>
       <c r="H4">
-        <v>670.75</v>
+        <v>670.5347290039062</v>
       </c>
       <c r="I4">
-        <v>643.8300170898438</v>
+        <v>643.6234130859375</v>
       </c>
       <c r="J4">
-        <v>675.3900146484375</v>
+        <v>675.1732788085938</v>
       </c>
       <c r="K4">
-        <v>586.4500122070312</v>
+        <v>586.2618408203125</v>
       </c>
       <c r="L4">
-        <v>651.8800048828125</v>
+        <v>651.6708374023438</v>
       </c>
       <c r="M4">
-        <v>638.719970703125</v>
+        <v>638.5150146484375</v>
       </c>
       <c r="N4">
-        <v>598.3699951171875</v>
+        <v>598.177978515625</v>
       </c>
       <c r="O4">
-        <v>539</v>
+        <v>538.8270263671875</v>
       </c>
       <c r="P4">
-        <v>577.4600219726562</v>
+        <v>577.2747192382812</v>
       </c>
       <c r="Q4">
-        <v>532.0999755859375</v>
+        <v>531.92919921875</v>
       </c>
       <c r="R4">
-        <v>550.2999877929688</v>
+        <v>550.1234130859375</v>
       </c>
       <c r="S4">
-        <v>578.0499877929688</v>
+        <v>577.864501953125</v>
       </c>
       <c r="T4">
-        <v>582.5900268554688</v>
+        <v>582.403076171875</v>
       </c>
       <c r="U4">
-        <v>555.5499877929688</v>
+        <v>555.3717041015625</v>
       </c>
       <c r="V4">
-        <v>563.3200073242188</v>
+        <v>563.1392211914062</v>
       </c>
       <c r="W4">
-        <v>513.8400268554688</v>
+        <v>513.6751098632812</v>
       </c>
       <c r="X4">
-        <v>466.8099975585938</v>
+        <v>466.6601867675781</v>
       </c>
       <c r="Y4">
-        <v>477.2200012207031</v>
+        <v>477.0668640136719</v>
       </c>
       <c r="Z4">
-        <v>487.4200134277344</v>
+        <v>487.2635803222656</v>
       </c>
       <c r="AA4">
-        <v>548.3900146484375</v>
+        <v>548.2140502929688</v>
       </c>
       <c r="AB4">
-        <v>556.6699829101562</v>
+        <v>556.4913330078125</v>
       </c>
       <c r="AC4">
-        <v>558.2999877929688</v>
+        <v>558.120849609375</v>
       </c>
       <c r="AD4">
-        <v>519.7999877929688</v>
+        <v>519.6331787109375</v>
       </c>
       <c r="AE4">
-        <v>497.9200134277344</v>
+        <v>497.7602233886719</v>
       </c>
       <c r="AF4">
-        <v>463.510009765625</v>
+        <v>463.3612670898438</v>
       </c>
       <c r="AG4">
-        <v>462.0400085449219</v>
+        <v>461.8917236328125</v>
       </c>
       <c r="AH4">
-        <v>533.0399780273438</v>
+        <v>532.868896484375</v>
       </c>
       <c r="AI4">
-        <v>544.8400268554688</v>
+        <v>544.6651611328125</v>
       </c>
       <c r="AJ4">
-        <v>527.219970703125</v>
+        <v>527.05078125</v>
       </c>
       <c r="AK4">
-        <v>548.5599975585938</v>
+        <v>548.3839721679688</v>
       </c>
       <c r="AL4">
-        <v>519.1699829101562</v>
+        <v>519.0033569335938</v>
       </c>
       <c r="AM4">
-        <v>451.5199890136719</v>
+        <v>451.3750915527344</v>
       </c>
       <c r="AN4">
-        <v>434.2999877929688</v>
+        <v>434.1606140136719</v>
       </c>
       <c r="AO4">
-        <v>438.3399963378906</v>
+        <v>438.1993408203125</v>
       </c>
       <c r="AP4">
-        <v>437.9299926757812</v>
+        <v>437.7894592285156</v>
       </c>
       <c r="AQ4">
-        <v>454.1000061035156</v>
+        <v>453.9542846679688</v>
       </c>
       <c r="AR4">
-        <v>487.2900085449219</v>
+        <v>487.1336364746094</v>
       </c>
       <c r="AS4">
-        <v>508.7999877929688</v>
+        <v>508.63671875</v>
       </c>
       <c r="AT4">
-        <v>536.010009765625</v>
+        <v>535.8380126953125</v>
       </c>
       <c r="AU4">
-        <v>496.1600036621094</v>
+        <v>496.0007934570312</v>
       </c>
       <c r="AV4">
-        <v>462.0899963378906</v>
+        <v>461.9417114257812</v>
       </c>
       <c r="AW4">
-        <v>469.0499877929688</v>
+        <v>468.8994750976562</v>
       </c>
       <c r="AX4">
-        <v>459.4400024414062</v>
+        <v>459.2925720214844</v>
       </c>
       <c r="AY4">
-        <v>435.3800048828125</v>
+        <v>435.2402954101562</v>
       </c>
       <c r="AZ4">
-        <v>450.75</v>
+        <v>450.6053466796875</v>
       </c>
       <c r="BA4">
-        <v>468.8800048828125</v>
+        <v>468.7295227050781</v>
       </c>
       <c r="BB4">
-        <v>462</v>
+        <v>461.8517456054688</v>
       </c>
       <c r="BC4">
-        <v>459.4500122070312</v>
+        <v>459.3025817871094</v>
       </c>
       <c r="BD4">
-        <v>450.5499877929688</v>
+        <v>450.4053955078125</v>
       </c>
       <c r="BE4">
-        <v>450.4400024414062</v>
+        <v>450.2954406738281</v>
       </c>
       <c r="BF4">
-        <v>448.8999938964844</v>
+        <v>448.7559509277344</v>
       </c>
       <c r="BG4">
-        <v>441.5700073242188</v>
+        <v>441.4283142089844</v>
       </c>
       <c r="BH4">
-        <v>467.4599914550781</v>
-      </c>
-    </row>
-    <row r="5" spans="1:60">
+        <v>467.3099670410156</v>
+      </c>
+      <c r="BI4">
+        <v>477.2999877929688</v>
+      </c>
+    </row>
+    <row r="5" spans="1:61">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -7420,8 +7432,11 @@
       <c r="BH5">
         <v>370.7200012207031</v>
       </c>
-    </row>
-    <row r="6" spans="1:60">
+      <c r="BI5">
+        <v>382.8500061035156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7602,8 +7617,11 @@
       <c r="BH6">
         <v>388.8999938964844</v>
       </c>
-    </row>
-    <row r="7" spans="1:60">
+      <c r="BI6">
+        <v>397.7699890136719</v>
+      </c>
+    </row>
+    <row r="7" spans="1:61">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -7784,8 +7802,11 @@
       <c r="BH7">
         <v>60.04000091552734</v>
       </c>
-    </row>
-    <row r="8" spans="1:60">
+      <c r="BI7">
+        <v>60.65000152587891</v>
+      </c>
+    </row>
+    <row r="8" spans="1:61">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -7966,8 +7987,11 @@
       <c r="BH8">
         <v>255.0899963378906</v>
       </c>
-    </row>
-    <row r="9" spans="1:60">
+      <c r="BI8">
+        <v>259.1400146484375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:61">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -8147,6 +8171,9 @@
       </c>
       <c r="BH9">
         <v>42.77000045776367</v>
+      </c>
+      <c r="BI9">
+        <v>43.54999923706055</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="242">
   <si>
     <t>DELL</t>
   </si>
@@ -234,6 +234,9 @@
     <t>2026-09-08</t>
   </si>
   <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -291,21 +294,27 @@
     <t>проходит</t>
   </si>
   <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
     <t>CRM</t>
   </si>
   <si>
     <t>Salesforce</t>
   </si>
   <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
-  </si>
-  <si>
-    <t>Financials</t>
-  </si>
-  <si>
     <t>GOOG</t>
   </si>
   <si>
@@ -315,6 +324,15 @@
     <t>Communication Services</t>
   </si>
   <si>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>Centene Corporation</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
     <t>GOOGL</t>
   </si>
   <si>
@@ -330,108 +348,99 @@
     <t>Consumer Staples</t>
   </si>
   <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>Hewlett Packard Enterprise</t>
-  </si>
-  <si>
-    <t>CNC</t>
-  </si>
-  <si>
-    <t>Centene Corporation</t>
-  </si>
-  <si>
-    <t>Health Care</t>
-  </si>
-  <si>
     <t>ALL</t>
   </si>
   <si>
     <t>Allstate</t>
   </si>
   <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
     <t>DLTR</t>
   </si>
   <si>
     <t>Dollar Tree</t>
   </si>
   <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>Intel</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
-  </si>
-  <si>
     <t>COF</t>
   </si>
   <si>
     <t>Capital One</t>
   </si>
   <si>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>Supermicro</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
     <t>NVDA</t>
   </si>
   <si>
     <t>Nvidia</t>
   </si>
   <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>Supermicro</t>
-  </si>
-  <si>
     <t>BMY</t>
   </si>
   <si>
     <t>Bristol Myers Squibb</t>
   </si>
   <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
+  </si>
+  <si>
     <t>BIIB</t>
   </si>
   <si>
     <t>Biogen</t>
   </si>
   <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
-  </si>
-  <si>
     <t>MS</t>
   </si>
   <si>
@@ -444,42 +453,30 @@
     <t>Seagate Technology</t>
   </si>
   <si>
-    <t>HPQ</t>
-  </si>
-  <si>
-    <t>HP Inc.</t>
-  </si>
-  <si>
     <t>REGN</t>
   </si>
   <si>
     <t>Regeneron Pharmaceuticals</t>
   </si>
   <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>EOG Resources</t>
+  </si>
+  <si>
     <t>WBD</t>
   </si>
   <si>
     <t>Warner Bros. Discovery</t>
   </si>
   <si>
-    <t>PRU</t>
-  </si>
-  <si>
-    <t>Prudential Financial</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
-  </si>
-  <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>EOG Resources</t>
-  </si>
-  <si>
     <t>NEM</t>
   </si>
   <si>
@@ -489,10 +486,16 @@
     <t>Materials</t>
   </si>
   <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>Teradyne</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>CF Industries</t>
   </si>
   <si>
     <t>Факторы и самообучение</t>
@@ -573,7 +576,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-10 00:17 UTC · данные на 2026-09-08 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-11 00:15 UTC · данные на 2026-09-10 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -654,7 +657,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-10 00:17 UTC</t>
+    <t>2026-09-11 00:15 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -1148,9 +1151,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$15</c:f>
+              <c:f>Капитал!$A$5:$A$16</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1183,16 +1186,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2026-09-08</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2026-09-10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$15</c:f>
+              <c:f>Капитал!$D$5:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1224,6 +1230,9 @@
                   <c:v>10216.05</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>10216.05</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>10216.05</c:v>
                 </c:pt>
               </c:numCache>
@@ -1249,9 +1258,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$15</c:f>
+              <c:f>Капитал!$A$5:$A$16</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1284,16 +1293,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2026-09-08</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2026-09-10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$15</c:f>
+              <c:f>Капитал!$F$5:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1325,6 +1337,9 @@
                   <c:v>10088.02</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1465,9 +1480,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$15</c:f>
+              <c:f>Капитал!$A$5:$A$16</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1500,16 +1515,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2026-09-08</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2026-09-10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$15</c:f>
+              <c:f>Капитал!$D$5:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1541,6 +1559,9 @@
                   <c:v>10216.05</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>10216.05</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>10216.05</c:v>
                 </c:pt>
               </c:numCache>
@@ -1566,9 +1587,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$15</c:f>
+              <c:f>Капитал!$A$5:$A$16</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1601,16 +1622,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2026-09-08</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2026-09-10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$15</c:f>
+              <c:f>Капитал!$F$5:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1642,6 +1666,9 @@
                   <c:v>10088.02</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2137,12 +2164,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2150,13 +2177,13 @@
         <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2175,27 +2202,27 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>4.478979173158216</v>
+        <v>4.2551692847167</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H9" s="7">
         <v>9</v>
@@ -2203,7 +2230,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2232,7 +2259,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -2240,7 +2267,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -2248,23 +2275,23 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C19" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -2272,55 +2299,55 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C25" s="12">
-        <v>0.1220294240725164</v>
+        <v>0.1167707519878767</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C26" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2329,12 +2356,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -2485,11 +2512,11 @@
         <v>0.18286309065709058</v>
       </c>
       <c r="L5" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N5" s="20">
         <v>2.927623067210654</v>
@@ -2536,11 +2563,11 @@
         <v>0.09758958423901652</v>
       </c>
       <c r="L6" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N6" s="20">
         <v>1.809956883354321</v>
@@ -2587,11 +2614,11 @@
         <v>0.1224393676054864</v>
       </c>
       <c r="L7" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M7" s="11">
         <f>MAX(0,21-L7)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N7" s="20">
         <v>1.655247920227722</v>
@@ -2638,11 +2665,11 @@
         <v>0.010656458832162687</v>
       </c>
       <c r="L8" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M8" s="11">
         <f>MAX(0,21-L8)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N8" s="20">
         <v>1.135451734784544</v>
@@ -2689,11 +2716,11 @@
         <v>0.029377395192469312</v>
       </c>
       <c r="L9" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9" s="11">
         <f>MAX(0,21-L9)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N9" s="20">
         <v>1.098454348098604</v>
@@ -2740,11 +2767,11 @@
         <v>0.020814011776538976</v>
       </c>
       <c r="L10" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10" s="11">
         <f>MAX(0,21-L10)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N10" s="20">
         <v>0.9280120270881818</v>
@@ -2791,11 +2818,11 @@
         <v>-0.0018297215776284946</v>
       </c>
       <c r="L11" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="11">
         <f>MAX(0,21-L11)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N11" s="20">
         <v>0.8840484909760108</v>
@@ -2842,11 +2869,11 @@
         <v>0.012639994356587973</v>
       </c>
       <c r="L12" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="11">
         <f>MAX(0,21-L12)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N12" s="20">
         <v>0.8298272742812407</v>
@@ -2893,11 +2920,11 @@
         <v>-0.02132271831371461</v>
       </c>
       <c r="L13" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="11">
         <f>MAX(0,21-L13)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N13" s="20">
         <v>0.7019116395441239</v>
@@ -3215,7 +3242,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3479,6 +3506,25 @@
         <v>9</v>
       </c>
       <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="10">
+        <v>5714.88</v>
+      </c>
+      <c r="C16" s="10">
+        <v>4501.17</v>
+      </c>
+      <c r="D16" s="10">
+        <f>B16+C16</f>
+        <v>10216.05</v>
+      </c>
+      <c r="E16" s="11">
+        <v>9</v>
+      </c>
+      <c r="F16" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3507,12 +3553,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3529,52 +3575,52 @@
         <v>13</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -3591,10 +3637,10 @@
         <v>28</v>
       </c>
       <c r="E5" s="10">
-        <v>1737.989990234375</v>
+        <v>1764.170043945312</v>
       </c>
       <c r="F5" s="17">
-        <v>1.101843084316499</v>
+        <v>1.120842573453189</v>
       </c>
       <c r="G5" s="20">
         <v>-0.5564495730839067</v>
@@ -3606,16 +3652,16 @@
         <v>4.120745224686987</v>
       </c>
       <c r="J5" s="20">
-        <v>2.08157200151033</v>
+        <v>2.168748407851256</v>
       </c>
       <c r="K5" s="20">
-        <v>0.08299030126699286</v>
+        <v>0.08036885848301029</v>
       </c>
       <c r="L5" s="20">
-        <v>-3.416720321042702</v>
+        <v>-3.427259213116233</v>
       </c>
       <c r="M5" s="20">
-        <v>0.3901052835239491</v>
+        <v>0.3125237071852279</v>
       </c>
       <c r="N5" s="20">
         <v>23.583628</v>
@@ -3630,13 +3676,13 @@
         <v>3.716</v>
       </c>
       <c r="R5" s="12">
-        <v>1.952100365010421</v>
+        <v>1.850538871510885</v>
       </c>
       <c r="S5" s="11">
-        <v>61.1120814610072</v>
+        <v>62.24144944940989</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -3653,10 +3699,10 @@
         <v>28</v>
       </c>
       <c r="E6" s="10">
-        <v>1000.260009765625</v>
+        <v>1027.77001953125</v>
       </c>
       <c r="F6" s="17">
-        <v>1.074633121175905</v>
+        <v>1.115499075608092</v>
       </c>
       <c r="G6" s="20">
         <v>-0.5381709417593455</v>
@@ -3668,16 +3714,16 @@
         <v>3.983916492932042</v>
       </c>
       <c r="J6" s="20">
-        <v>2.050460594415619</v>
+        <v>2.220361319791275</v>
       </c>
       <c r="K6" s="20">
-        <v>0.4798559392469772</v>
+        <v>0.4757611069296119</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.416720321042702</v>
+        <v>-3.427259213116233</v>
       </c>
       <c r="M6" s="20">
-        <v>0.1893115627564228</v>
+        <v>0.07705469053124858</v>
       </c>
       <c r="N6" s="20">
         <v>22.98937</v>
@@ -3692,13 +3738,13 @@
         <v>3.457</v>
       </c>
       <c r="R6" s="12">
-        <v>1.570723581010705</v>
+        <v>1.551065327195762</v>
       </c>
       <c r="S6" s="11">
-        <v>57.6626588022908</v>
+        <v>60.61458265758949</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -3715,10 +3761,10 @@
         <v>38</v>
       </c>
       <c r="E7" s="10">
-        <v>382.8500061035156</v>
+        <v>388.9500122070312</v>
       </c>
       <c r="F7" s="17">
-        <v>1.008299237621722</v>
+        <v>1.046639027268738</v>
       </c>
       <c r="G7" s="20">
         <v>0.7163099250210818</v>
@@ -3730,16 +3776,16 @@
         <v>2.885035079678366</v>
       </c>
       <c r="J7" s="20">
-        <v>2.192941818971337</v>
+        <v>2.31067718366916</v>
       </c>
       <c r="K7" s="20">
-        <v>0.6066252760202447</v>
+        <v>0.602059804282177</v>
       </c>
       <c r="L7" s="20">
-        <v>0.1212986880835318</v>
+        <v>0.1228096645160992</v>
       </c>
       <c r="M7" s="20">
-        <v>-0.4769978576405967</v>
+        <v>-0.4335431293870549</v>
       </c>
       <c r="N7" s="20">
         <v>15.453106</v>
@@ -3754,13 +3800,13 @@
         <v>0.517</v>
       </c>
       <c r="R7" s="12">
-        <v>0.7881713448812837</v>
+        <v>0.8077054083523185</v>
       </c>
       <c r="S7" s="11">
-        <v>79.30760239290296</v>
+        <v>80.98950727590281</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -3777,10 +3823,10 @@
         <v>38</v>
       </c>
       <c r="E8" s="10">
-        <v>397.7699890136719</v>
+        <v>399.4400024414062</v>
       </c>
       <c r="F8" s="17">
-        <v>0.9856850548435461</v>
+        <v>1.015793610975163</v>
       </c>
       <c r="G8" s="20">
         <v>0.704035078477925</v>
@@ -3792,16 +3838,16 @@
         <v>2.454207309239585</v>
       </c>
       <c r="J8" s="20">
-        <v>2.148174269992236</v>
+        <v>2.26147949632816</v>
       </c>
       <c r="K8" s="20">
-        <v>0.7742712560795861</v>
+        <v>0.7690833877198547</v>
       </c>
       <c r="L8" s="20">
-        <v>0.1706484844696534</v>
+        <v>0.1743121397014286</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.5270452754601733</v>
+        <v>-0.5705488614589164</v>
       </c>
       <c r="N8" s="20">
         <v>13.475398</v>
@@ -3816,13 +3862,13 @@
         <v>0.537</v>
       </c>
       <c r="R8" s="12">
-        <v>0.8561956548441085</v>
+        <v>0.8680591899960282</v>
       </c>
       <c r="S8" s="11">
-        <v>80.84519646228173</v>
+        <v>81.29948564745813</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -3839,10 +3885,10 @@
         <v>28</v>
       </c>
       <c r="E9" s="10">
-        <v>533.8800048828125</v>
+        <v>535.25</v>
       </c>
       <c r="F9" s="17">
-        <v>0.9764385260913725</v>
+        <v>0.9950466899717794</v>
       </c>
       <c r="G9" s="20">
         <v>-0.2096896716004668</v>
@@ -3854,16 +3900,16 @@
         <v>2.195812652927404</v>
       </c>
       <c r="J9" s="20">
-        <v>2.925093281761714</v>
+        <v>2.994607845226451</v>
       </c>
       <c r="K9" s="20">
-        <v>1.605257194274964</v>
+        <v>1.596984236488098</v>
       </c>
       <c r="L9" s="20">
-        <v>-2.556865290901396</v>
+        <v>-2.555513619951289</v>
       </c>
       <c r="M9" s="20">
-        <v>0.1651653564628242</v>
+        <v>0.1484834754428668</v>
       </c>
       <c r="N9" s="20">
         <v>30.490984</v>
@@ -3878,13 +3924,13 @@
         <v>0.577</v>
       </c>
       <c r="R9" s="12">
-        <v>2.661298429062968</v>
+        <v>2.739870364202472</v>
       </c>
       <c r="S9" s="11">
-        <v>65.08857762491189</v>
+        <v>65.29337644585388</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -3901,10 +3947,10 @@
         <v>38</v>
       </c>
       <c r="E10" s="10">
-        <v>259.1400146484375</v>
+        <v>260.7799987792969</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8497603086029423</v>
+        <v>0.8810241045193192</v>
       </c>
       <c r="G10" s="20">
         <v>0.4937473502003348</v>
@@ -3916,16 +3962,16 @@
         <v>2.423226908404409</v>
       </c>
       <c r="J10" s="20">
-        <v>1.976963435581927</v>
+        <v>2.09005952681419</v>
       </c>
       <c r="K10" s="20">
-        <v>0.6899308401855347</v>
+        <v>0.6850560911138626</v>
       </c>
       <c r="L10" s="20">
-        <v>0.3912061011603029</v>
+        <v>0.3950400553153533</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.6842241279983566</v>
+        <v>-0.7131003631734092</v>
       </c>
       <c r="N10" s="20">
         <v>14.559931</v>
@@ -3940,13 +3986,13 @@
         <v>0.531</v>
       </c>
       <c r="R10" s="12">
-        <v>0.6098574883208787</v>
+        <v>0.6250303198976213</v>
       </c>
       <c r="S10" s="11">
-        <v>77.20479964933293</v>
+        <v>78.03424497368225</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -3954,61 +4000,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="10">
-        <v>249.1199951171875</v>
+        <v>58.90000152587891</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8469310645592527</v>
+        <v>0.8777991100892987</v>
       </c>
       <c r="G11" s="20">
-        <v>0.313884107527872</v>
+        <v>0.5218225520995097</v>
       </c>
       <c r="H11" s="20">
-        <v>0.5379536582452412</v>
+        <v>-0.5332485103967138</v>
       </c>
       <c r="I11" s="20">
-        <v>0.202940183485447</v>
+        <v>2.225163086097977</v>
       </c>
       <c r="J11" s="20">
-        <v>1.150196583022348</v>
+        <v>2.426929707162234</v>
       </c>
       <c r="K11" s="20">
-        <v>3.531116261499869</v>
+        <v>0.3221406505579205</v>
       </c>
       <c r="L11" s="20">
-        <v>-1.568900752815953</v>
+        <v>-1.274961210348846</v>
       </c>
       <c r="M11" s="20">
-        <v>0.1175805052340104</v>
+        <v>-0.544545172870331</v>
       </c>
       <c r="N11" s="20">
-        <v>23.76077</v>
+        <v>26.804123</v>
       </c>
       <c r="O11" s="20">
-        <v>5.559058</v>
+        <v>2.7206612</v>
       </c>
       <c r="P11" s="12">
-        <v>0.19381</v>
+        <v>0.10936</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.108</v>
+        <v>0.337</v>
       </c>
       <c r="R11" s="12">
-        <v>0.2595584027274918</v>
+        <v>1.817688482853931</v>
       </c>
       <c r="S11" s="11">
-        <v>67.55178261269285</v>
+        <v>62.79336551457337</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -4016,19 +4062,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E12" s="10">
-        <v>365.6600036621094</v>
+        <v>366.8500061035156</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8367848340502836</v>
+        <v>0.8411707892541855</v>
       </c>
       <c r="G12" s="20">
         <v>1.215230467965422</v>
@@ -4040,16 +4086,16 @@
         <v>-0.3758707799348074</v>
       </c>
       <c r="J12" s="20">
-        <v>0.6087177628713963</v>
+        <v>0.654078326784571</v>
       </c>
       <c r="K12" s="20">
-        <v>3.829153559383143</v>
+        <v>3.812624241473097</v>
       </c>
       <c r="L12" s="20">
-        <v>0.5896738550462156</v>
+        <v>0.5937263112206973</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.03040627175184626</v>
+        <v>-0.1239293116432705</v>
       </c>
       <c r="N12" s="20">
         <v>9.931433999999999</v>
@@ -4064,13 +4110,13 @@
         <v>0.003</v>
       </c>
       <c r="R12" s="12">
-        <v>0.2154943448119708</v>
+        <v>0.2180388374009978</v>
       </c>
       <c r="S12" s="11">
-        <v>48.29533744575358</v>
+        <v>49.53326300808831</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -4078,61 +4124,61 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="E13" s="10">
-        <v>335.3800048828125</v>
+        <v>244.1600036621094</v>
       </c>
       <c r="F13" s="17">
-        <v>0.7837024514101212</v>
+        <v>0.8077049521372179</v>
       </c>
       <c r="G13" s="20">
-        <v>-0.3654991602347105</v>
+        <v>0.313884107527872</v>
       </c>
       <c r="H13" s="20">
-        <v>1.463709249725696</v>
+        <v>0.5379536582452412</v>
       </c>
       <c r="I13" s="20">
-        <v>1.40880022334584</v>
+        <v>0.202940183485447</v>
       </c>
       <c r="J13" s="20">
-        <v>-0.204157481105242</v>
+        <v>1.153977630851056</v>
       </c>
       <c r="K13" s="20">
-        <v>4.1972917133727</v>
+        <v>3.515693426472779</v>
       </c>
       <c r="L13" s="20">
-        <v>0.0842370026628418</v>
+        <v>-1.58034990935587</v>
       </c>
       <c r="M13" s="20">
-        <v>0.336710206609396</v>
+        <v>-0.355203709453508</v>
       </c>
       <c r="N13" s="20">
-        <v>16.83283</v>
+        <v>23.76077</v>
       </c>
       <c r="O13" s="20">
-        <v>6.5881405</v>
+        <v>5.559058</v>
       </c>
       <c r="P13" s="12">
-        <v>0.48676</v>
+        <v>0.19381</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.242</v>
+        <v>0.108</v>
       </c>
       <c r="R13" s="12">
-        <v>0.09734879457938406</v>
+        <v>0.2590548364562497</v>
       </c>
       <c r="S13" s="11">
-        <v>44.19804931660762</v>
+        <v>63.57276604587708</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -4146,16 +4192,16 @@
         <v>97</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E14" s="10">
-        <v>338.3599853515625</v>
+        <v>328.3800048828125</v>
       </c>
       <c r="F14" s="17">
-        <v>0.7834662720951022</v>
+        <v>0.776423257523575</v>
       </c>
       <c r="G14" s="20">
-        <v>-0.3753606373785415</v>
+        <v>-0.3654991602347105</v>
       </c>
       <c r="H14" s="20">
         <v>1.463709249725696</v>
@@ -4164,22 +4210,22 @@
         <v>1.40880022334584</v>
       </c>
       <c r="J14" s="20">
-        <v>-0.1816201031699617</v>
+        <v>-0.2630866424801945</v>
       </c>
       <c r="K14" s="20">
-        <v>4.1972917133727</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L14" s="20">
-        <v>0.06314291840523922</v>
+        <v>0.07410053957684902</v>
       </c>
       <c r="M14" s="20">
-        <v>0.2872516846811813</v>
+        <v>0.4749531093146364</v>
       </c>
       <c r="N14" s="20">
-        <v>16.97392</v>
+        <v>16.83283</v>
       </c>
       <c r="O14" s="20">
-        <v>6.650031</v>
+        <v>6.5881405</v>
       </c>
       <c r="P14" s="12">
         <v>0.48676</v>
@@ -4188,13 +4234,13 @@
         <v>0.242</v>
       </c>
       <c r="R14" s="12">
-        <v>0.1058223886899801</v>
+        <v>0.07122451645171202</v>
       </c>
       <c r="S14" s="11">
-        <v>44.89808035345778</v>
+        <v>38.97142949780758</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -4202,61 +4248,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E15" s="10">
-        <v>162.7100067138672</v>
+        <v>64.05999755859375</v>
       </c>
       <c r="F15" s="17">
-        <v>0.7508875525330688</v>
+        <v>0.7729869712502148</v>
       </c>
       <c r="G15" s="20">
-        <v>0.4941985872113094</v>
+        <v>1.296202382232963</v>
       </c>
       <c r="H15" s="20">
-        <v>-0.5581494893912904</v>
+        <v>-1.353261681376673</v>
       </c>
       <c r="I15" s="20">
-        <v>-0.03241763381358259</v>
+        <v>-0.5780959126470824</v>
       </c>
       <c r="J15" s="20">
-        <v>1.375212031660279</v>
+        <v>0.992508764277121</v>
       </c>
       <c r="K15" s="20">
-        <v>3.296722344935419</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L15" s="20">
-        <v>0.2622536311978117</v>
+        <v>-0.002816707404061112</v>
       </c>
       <c r="M15" s="20">
-        <v>-0.8678502530400624</v>
+        <v>0.1599382524370093</v>
       </c>
       <c r="N15" s="20">
-        <v>17.05809</v>
+        <v>12.6192465</v>
       </c>
       <c r="O15" s="20">
-        <v>4.186674</v>
+        <v>1.4678257</v>
       </c>
       <c r="P15" s="12">
-        <v>0.26408002</v>
+        <v>-0.20358999</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.053</v>
+        <v>0.046</v>
       </c>
       <c r="R15" s="12">
-        <v>0.377625973780005</v>
+        <v>0.7598899690443617</v>
       </c>
       <c r="S15" s="11">
-        <v>60.03797954474801</v>
+        <v>45.65142549028698</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -4264,61 +4310,61 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="E16" s="10">
-        <v>56.02999877929688</v>
+        <v>330.6499938964844</v>
       </c>
       <c r="F16" s="17">
-        <v>0.74326451272628</v>
+        <v>0.7727017842057998</v>
       </c>
       <c r="G16" s="20">
-        <v>0.5218225520995097</v>
+        <v>-0.3753606373785415</v>
       </c>
       <c r="H16" s="20">
-        <v>-0.5332485103967138</v>
+        <v>1.463709249725696</v>
       </c>
       <c r="I16" s="20">
-        <v>2.225163086097977</v>
+        <v>1.40880022334584</v>
       </c>
       <c r="J16" s="20">
-        <v>2.030330982269093</v>
+        <v>-0.2513829526136259</v>
       </c>
       <c r="K16" s="20">
-        <v>0.3256630316615335</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L16" s="20">
-        <v>-1.239760248452089</v>
+        <v>0.05038972406194137</v>
       </c>
       <c r="M16" s="20">
-        <v>-0.7706667146367739</v>
+        <v>0.4245172910526159</v>
       </c>
       <c r="N16" s="20">
-        <v>26.804123</v>
+        <v>16.97392</v>
       </c>
       <c r="O16" s="20">
-        <v>2.7206612</v>
+        <v>6.650031</v>
       </c>
       <c r="P16" s="12">
-        <v>0.10936</v>
+        <v>0.48676</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.337</v>
+        <v>0.242</v>
       </c>
       <c r="R16" s="12">
-        <v>1.593134832549722</v>
+        <v>0.07823132365810959</v>
       </c>
       <c r="S16" s="11">
-        <v>57.78308827692286</v>
+        <v>39.47425744398156</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -4326,61 +4372,61 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="E17" s="10">
-        <v>64.58000183105469</v>
+        <v>61.29999923706055</v>
       </c>
       <c r="F17" s="17">
-        <v>0.7350680436258861</v>
+        <v>0.7567677486488729</v>
       </c>
       <c r="G17" s="20">
-        <v>1.296202382232963</v>
+        <v>0.6321397772136792</v>
       </c>
       <c r="H17" s="20">
-        <v>-1.353261681376673</v>
+        <v>0.6155406581429993</v>
       </c>
       <c r="I17" s="20">
-        <v>-0.5780959126470824</v>
+        <v>2.930171312463986</v>
       </c>
       <c r="J17" s="20">
-        <v>0.8320880019623197</v>
+        <v>0.6138314029540464</v>
       </c>
       <c r="K17" s="20">
-        <v>4.1972917133727</v>
+        <v>0.8675448211661402</v>
       </c>
       <c r="L17" s="20">
-        <v>-0.02742629593900239</v>
+        <v>0.2788934682129006</v>
       </c>
       <c r="M17" s="20">
-        <v>0.3053405833981097</v>
+        <v>-0.6688681914724106</v>
       </c>
       <c r="N17" s="20">
-        <v>12.6192465</v>
+        <v>17.710915</v>
       </c>
       <c r="O17" s="20">
-        <v>1.4678257</v>
+        <v>1.7938988</v>
       </c>
       <c r="P17" s="12">
-        <v>-0.20358999</v>
+        <v>0.10629</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.046</v>
+        <v>0.534</v>
       </c>
       <c r="R17" s="12">
-        <v>0.490766442428451</v>
+        <v>0.1593212354173363</v>
       </c>
       <c r="S17" s="11">
-        <v>47.22740624115487</v>
+        <v>61.97096717259578</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4388,61 +4434,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="E18" s="10">
-        <v>60.65000152587891</v>
+        <v>157.5200042724609</v>
       </c>
       <c r="F18" s="17">
-        <v>0.7095984039373823</v>
+        <v>0.7014638181956935</v>
       </c>
       <c r="G18" s="20">
-        <v>0.6321397772136792</v>
+        <v>0.4941985872113094</v>
       </c>
       <c r="H18" s="20">
-        <v>0.6155406581429993</v>
+        <v>-0.5581494893912904</v>
       </c>
       <c r="I18" s="20">
-        <v>2.930171312463986</v>
+        <v>-0.03241763381358259</v>
       </c>
       <c r="J18" s="20">
-        <v>0.4329446997788296</v>
+        <v>1.14150588608593</v>
       </c>
       <c r="K18" s="20">
-        <v>0.8730995961762966</v>
+        <v>3.282169712592323</v>
       </c>
       <c r="L18" s="20">
-        <v>0.2658765169304781</v>
+        <v>0.2266254037186517</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.5787293125123976</v>
+        <v>-0.560698767229431</v>
       </c>
       <c r="N18" s="20">
-        <v>17.710915</v>
+        <v>17.05809</v>
       </c>
       <c r="O18" s="20">
-        <v>1.7938988</v>
+        <v>4.186674</v>
       </c>
       <c r="P18" s="12">
-        <v>0.10629</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.534</v>
+        <v>0.053</v>
       </c>
       <c r="R18" s="12">
-        <v>0.1126760750661084</v>
+        <v>0.3270559152646901</v>
       </c>
       <c r="S18" s="11">
-        <v>59.38221223383346</v>
+        <v>50.82563704518401</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4450,19 +4496,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E19" s="10">
-        <v>253.4600067138672</v>
+        <v>253.5800018310547</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6583665893639233</v>
+        <v>0.6636989313318215</v>
       </c>
       <c r="G19" s="20">
         <v>1.286238812250283</v>
@@ -4474,16 +4520,16 @@
         <v>-0.05063264711205382</v>
       </c>
       <c r="J19" s="20">
-        <v>0.4745204787725334</v>
+        <v>0.5247038416069513</v>
       </c>
       <c r="K19" s="20">
-        <v>1.858278441957119</v>
+        <v>1.849066126306075</v>
       </c>
       <c r="L19" s="20">
-        <v>0.5109336572200091</v>
+        <v>0.5167665941688258</v>
       </c>
       <c r="M19" s="20">
-        <v>0.1180544614883036</v>
+        <v>0.00596489622291628</v>
       </c>
       <c r="N19" s="20">
         <v>5.1976376</v>
@@ -4498,13 +4544,13 @@
         <v>0.118</v>
       </c>
       <c r="R19" s="12">
-        <v>0.2319113426066355</v>
+        <v>0.2336230905925007</v>
       </c>
       <c r="S19" s="11">
-        <v>45.56205966278974</v>
+        <v>45.70346675177978</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -4512,61 +4558,61 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="E20" s="10">
-        <v>124.0400009155273</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="F20" s="17">
-        <v>0.63963859698438</v>
+        <v>0.6571105582429381</v>
       </c>
       <c r="G20" s="20">
-        <v>0.3599925540636538</v>
+        <v>-0.6233680543607623</v>
       </c>
       <c r="H20" s="20">
-        <v>-0.1244310120248844</v>
+        <v>-1.136990927851701</v>
       </c>
       <c r="I20" s="20">
-        <v>0.4821804333312243</v>
+        <v>0.5264142543422116</v>
       </c>
       <c r="J20" s="20">
-        <v>0.1175161678413195</v>
+        <v>1.745304736953654</v>
       </c>
       <c r="K20" s="20">
-        <v>4.1972917133727</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L20" s="20">
-        <v>0.08623224266917956</v>
+        <v>-2.480147806266792</v>
       </c>
       <c r="M20" s="20">
-        <v>0.03033831658138225</v>
+        <v>0.2523507830054219</v>
       </c>
       <c r="N20" s="20">
-        <v>16.105392</v>
+        <v>46.910885</v>
       </c>
       <c r="O20" s="20">
-        <v>7.2471595</v>
+        <v>5.5187516</v>
       </c>
       <c r="P20" s="12">
-        <v>0.46032003</v>
+        <v>-0.10715</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.07000000000000001</v>
+        <v>0.254</v>
       </c>
       <c r="R20" s="12">
-        <v>0.0706948860533283</v>
+        <v>1.271056020437253</v>
       </c>
       <c r="S20" s="11">
-        <v>42.11464305912724</v>
+        <v>63.36095147527727</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -4574,19 +4620,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E21" s="10">
-        <v>256.9700012207031</v>
+        <v>252.3999938964844</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6342809648252788</v>
+        <v>0.6258177828079802</v>
       </c>
       <c r="G21" s="20">
         <v>-0.04482148267622166</v>
@@ -4598,16 +4644,16 @@
         <v>1.035672297744961</v>
       </c>
       <c r="J21" s="20">
-        <v>0.171386387571603</v>
+        <v>0.1070953977161724</v>
       </c>
       <c r="K21" s="20">
-        <v>4.1972917133727</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.4488605948402165</v>
+        <v>-0.4512688404540941</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.1852493828418346</v>
+        <v>-0.04749563807329264</v>
       </c>
       <c r="N21" s="20">
         <v>20.797264</v>
@@ -4622,13 +4668,13 @@
         <v>0.196</v>
       </c>
       <c r="R21" s="12">
-        <v>0.2036629097793119</v>
+        <v>0.177623252648681</v>
       </c>
       <c r="S21" s="11">
-        <v>48.12096671477671</v>
+        <v>44.06238001461678</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -4636,61 +4682,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="E22" s="10">
-        <v>104.4700012207031</v>
+        <v>126.0100021362305</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6251009131397292</v>
+        <v>0.6140882295887513</v>
       </c>
       <c r="G22" s="20">
-        <v>-0.6233680543607623</v>
+        <v>0.3314207580374121</v>
       </c>
       <c r="H22" s="20">
-        <v>-1.136990927851701</v>
+        <v>0.5050654897521694</v>
       </c>
       <c r="I22" s="20">
-        <v>0.5264142543422116</v>
+        <v>0.5229426848176244</v>
       </c>
       <c r="J22" s="20">
-        <v>1.625224614958064</v>
+        <v>0.874763610159063</v>
       </c>
       <c r="K22" s="20">
-        <v>4.1972917133727</v>
+        <v>1.638740132347517</v>
       </c>
       <c r="L22" s="20">
-        <v>-2.552284533469248</v>
+        <v>0.008712019588152516</v>
       </c>
       <c r="M22" s="20">
-        <v>0.3559870982841107</v>
+        <v>-0.4784109225600325</v>
       </c>
       <c r="N22" s="20">
-        <v>46.910885</v>
+        <v>16.146498</v>
       </c>
       <c r="O22" s="20">
-        <v>5.5187516</v>
+        <v>4.015142</v>
       </c>
       <c r="P22" s="12">
-        <v>-0.10715</v>
+        <v>0.30667</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.254</v>
+        <v>0.377</v>
       </c>
       <c r="R22" s="12">
-        <v>1.292013975952176</v>
+        <v>0.3123308325519467</v>
       </c>
       <c r="S22" s="11">
-        <v>61.69918404310961</v>
+        <v>54.09585711905316</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -4698,61 +4744,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>115</v>
+        <v>8</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="E23" s="10">
-        <v>124.4000015258789</v>
+        <v>44.84000015258789</v>
       </c>
       <c r="F23" s="17">
-        <v>0.5953639290148719</v>
+        <v>0.6001422538416877</v>
       </c>
       <c r="G23" s="20">
-        <v>0.3314207580374121</v>
+        <v>1.1788603618118</v>
       </c>
       <c r="H23" s="20">
-        <v>0.5050654897521694</v>
+        <v>0.561859549662265</v>
       </c>
       <c r="I23" s="20">
-        <v>0.5229426848176244</v>
+        <v>-0.2890980177519417</v>
       </c>
       <c r="J23" s="20">
-        <v>0.7593354506761331</v>
+        <v>1.630784367338348</v>
       </c>
       <c r="K23" s="20">
-        <v>1.6471686892898</v>
+        <v>-0.5748378530888681</v>
       </c>
       <c r="L23" s="20">
-        <v>0.008519108772499218</v>
+        <v>-0.3670883722363629</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.2921072339742236</v>
+        <v>-0.8908725368982913</v>
       </c>
       <c r="N23" s="20">
-        <v>16.146498</v>
+        <v>9.023208</v>
       </c>
       <c r="O23" s="20">
-        <v>4.015142</v>
+        <v>2.1361504</v>
       </c>
       <c r="P23" s="12">
-        <v>0.30667</v>
+        <v>0.26659</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.377</v>
+        <v>0.092</v>
       </c>
       <c r="R23" s="12">
-        <v>0.2811534858987021</v>
+        <v>0.4285935480326837</v>
       </c>
       <c r="S23" s="11">
-        <v>50.8479448726449</v>
+        <v>64.66680555611237</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -4760,19 +4806,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>118</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="10">
-        <v>189.1300048828125</v>
+        <v>184.7400054931641</v>
       </c>
       <c r="F24" s="17">
-        <v>0.5697633164143457</v>
+        <v>0.5815623270891278</v>
       </c>
       <c r="G24" s="20">
         <v>-0.3904668641526476</v>
@@ -4784,16 +4830,16 @@
         <v>0.4411015820383316</v>
       </c>
       <c r="J24" s="20">
-        <v>1.32998344249264</v>
+        <v>1.280062662953853</v>
       </c>
       <c r="K24" s="20">
-        <v>0.4876173272126874</v>
+        <v>0.4834936802369117</v>
       </c>
       <c r="L24" s="20">
-        <v>-0.1241567913855804</v>
+        <v>-0.1433429477102688</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.8948907443088177</v>
+        <v>-0.5396250998964101</v>
       </c>
       <c r="N24" s="20">
         <v>26.250353</v>
@@ -4808,13 +4854,13 @@
         <v>0.299</v>
       </c>
       <c r="R24" s="12">
-        <v>0.8952004265981663</v>
+        <v>0.9218887880887581</v>
       </c>
       <c r="S24" s="11">
-        <v>53.12450935567445</v>
+        <v>48.03423931692689</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -4822,19 +4868,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>120</v>
-      </c>
       <c r="D25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E25" s="10">
-        <v>1036.530029296875</v>
+        <v>1028.780029296875</v>
       </c>
       <c r="F25" s="17">
-        <v>0.56734839132417</v>
+        <v>0.5781468918913982</v>
       </c>
       <c r="G25" s="20">
         <v>0.3667190394925228</v>
@@ -4846,16 +4892,16 @@
         <v>0.9154597556552251</v>
       </c>
       <c r="J25" s="20">
-        <v>0.2165283389004759</v>
+        <v>0.2346785381735309</v>
       </c>
       <c r="K25" s="20">
-        <v>1.663726316949982</v>
+        <v>1.655236288736424</v>
       </c>
       <c r="L25" s="20">
-        <v>0.1024364401273346</v>
+        <v>0.1296667801823609</v>
       </c>
       <c r="M25" s="20">
-        <v>0.09187078270049481</v>
+        <v>0.1511010797959585</v>
       </c>
       <c r="N25" s="20">
         <v>16.02546</v>
@@ -4870,13 +4916,13 @@
         <v>0.425</v>
       </c>
       <c r="R25" s="12">
-        <v>0.2574030332256332</v>
+        <v>0.2453374831943853</v>
       </c>
       <c r="S25" s="11">
-        <v>51.43317778574706</v>
+        <v>49.20890049969636</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -4884,61 +4930,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>122</v>
-      </c>
       <c r="D26" s="9" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="E26" s="10">
-        <v>213.9600067138672</v>
+        <v>118.3899993896484</v>
       </c>
       <c r="F26" s="17">
-        <v>0.5463955641114731</v>
+        <v>0.5397610571690064</v>
       </c>
       <c r="G26" s="20">
-        <v>0.5809437263948974</v>
+        <v>0.3599925540636538</v>
       </c>
       <c r="H26" s="20">
-        <v>-0.6585101921976751</v>
+        <v>-0.1244310120248844</v>
       </c>
       <c r="I26" s="20">
-        <v>4.120745224686987</v>
+        <v>0.4821804333312243</v>
       </c>
       <c r="J26" s="20">
-        <v>0.1353151982103833</v>
+        <v>-0.1810993972280628</v>
       </c>
       <c r="K26" s="20">
-        <v>0.6040381466983412</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L26" s="20">
-        <v>0.4815902196986752</v>
+        <v>0.01223109408635147</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.08577185756894479</v>
+        <v>-0.04217557684698181</v>
       </c>
       <c r="N26" s="20">
-        <v>12.092511</v>
+        <v>16.105392</v>
       </c>
       <c r="O26" s="20">
-        <v>1.3082409</v>
+        <v>7.2471595</v>
       </c>
       <c r="P26" s="12">
-        <v>0.09031</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q26" s="12">
-        <v>11.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R26" s="12">
-        <v>0.1610254620931819</v>
+        <v>0.01343947696392411</v>
       </c>
       <c r="S26" s="11">
-        <v>48.03128741189954</v>
+        <v>35.58604054397024</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -4946,61 +4992,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="D27" s="9" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="E27" s="10">
-        <v>225.7299957275391</v>
+        <v>210.8600006103516</v>
       </c>
       <c r="F27" s="17">
-        <v>0.5189681794547308</v>
+        <v>0.5326840879288903</v>
       </c>
       <c r="G27" s="20">
-        <v>-1.255664189485384</v>
+        <v>0.5809437263948974</v>
       </c>
       <c r="H27" s="20">
-        <v>2.368358787986747</v>
+        <v>-0.6585101921976751</v>
       </c>
       <c r="I27" s="20">
-        <v>2.430954222251415</v>
+        <v>4.120745224686987</v>
       </c>
       <c r="J27" s="20">
-        <v>0.5843720113700576</v>
+        <v>0.07339711551298615</v>
       </c>
       <c r="K27" s="20">
-        <v>-0.308183652204804</v>
+        <v>0.5994822798464103</v>
       </c>
       <c r="L27" s="20">
-        <v>-0.2161934998125696</v>
+        <v>0.4787354843618977</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.0300381237325984</v>
+        <v>-0.01599764795551081</v>
       </c>
       <c r="N27" s="20">
-        <v>29.159492</v>
+        <v>12.092511</v>
       </c>
       <c r="O27" s="20">
-        <v>24.291891</v>
+        <v>1.3082409</v>
       </c>
       <c r="P27" s="12">
-        <v>1.17211</v>
+        <v>0.09031</v>
       </c>
       <c r="Q27" s="12">
-        <v>1.059</v>
+        <v>11.11</v>
       </c>
       <c r="R27" s="12">
-        <v>0.2373683124047306</v>
+        <v>0.1495263781168987</v>
       </c>
       <c r="S27" s="11">
-        <v>56.14653691353901</v>
+        <v>44.23106566160668</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -5008,61 +5054,61 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="10">
-        <v>40.2599983215332</v>
+        <v>32.38999938964844</v>
       </c>
       <c r="F28" s="17">
-        <v>0.5041545557798331</v>
+        <v>0.521001566246862</v>
       </c>
       <c r="G28" s="20">
-        <v>0.09785741135882757</v>
+        <v>1.115176779328165</v>
       </c>
       <c r="H28" s="20">
-        <v>-0.81219220040201</v>
+        <v>-0.9874044575767369</v>
       </c>
       <c r="I28" s="20">
-        <v>3.920900829953943</v>
+        <v>-0.3840221445724293</v>
       </c>
       <c r="J28" s="20">
-        <v>0.2670313249003679</v>
+        <v>1.814578876298771</v>
       </c>
       <c r="K28" s="20">
-        <v>3.385719593608896</v>
+        <v>0.403590422728146</v>
       </c>
       <c r="L28" s="20">
-        <v>-3.416720321042702</v>
+        <v>-0.5995509067559709</v>
       </c>
       <c r="M28" s="20">
-        <v>-0.7123954829555538</v>
+        <v>-0.5021848196792174</v>
       </c>
       <c r="N28" s="20">
-        <v>12.144172</v>
+        <v>12.458015</v>
       </c>
       <c r="O28" s="20">
-        <v>2.3688147</v>
+        <v>-320</v>
       </c>
       <c r="P28" s="12">
-        <v>0.21465999</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.9320000000000001</v>
+        <v>0.125</v>
       </c>
       <c r="R28" s="12">
-        <v>0.2589117854226792</v>
+        <v>0.790317139285901</v>
       </c>
       <c r="S28" s="11">
-        <v>64.14745634614101</v>
+        <v>63.05040006309013</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -5070,61 +5116,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E29" s="10">
-        <v>43.54999923706055</v>
+        <v>482.2799987792969</v>
       </c>
       <c r="F29" s="17">
-        <v>0.4990836376154188</v>
+        <v>0.5190346046199206</v>
       </c>
       <c r="G29" s="20">
-        <v>1.1788603618118</v>
+        <v>-0.9800881674162824</v>
       </c>
       <c r="H29" s="20">
-        <v>0.561859549662265</v>
+        <v>2.147104391138658</v>
       </c>
       <c r="I29" s="20">
-        <v>-0.2890980177519417</v>
+        <v>2.675284350851072</v>
       </c>
       <c r="J29" s="20">
-        <v>1.260448221343344</v>
+        <v>0.8747692948236511</v>
       </c>
       <c r="K29" s="20">
-        <v>-0.5746579723608561</v>
+        <v>-0.2212015005016859</v>
       </c>
       <c r="L29" s="20">
-        <v>-0.3491559703348047</v>
+        <v>-3.427259213116233</v>
       </c>
       <c r="M29" s="20">
-        <v>-0.7790638147635713</v>
+        <v>0.6766785185954969</v>
       </c>
       <c r="N29" s="20">
-        <v>9.023208</v>
+        <v>17.358335</v>
       </c>
       <c r="O29" s="20">
-        <v>2.1361504</v>
+        <v>22.350464</v>
       </c>
       <c r="P29" s="12">
-        <v>0.26659</v>
+        <v>1.30853</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.092</v>
+        <v>0.438</v>
       </c>
       <c r="R29" s="12">
-        <v>0.3547121947190726</v>
+        <v>0.8126382918933179</v>
       </c>
       <c r="S29" s="11">
-        <v>60.45630612065907</v>
+        <v>51.59300712887129</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -5132,61 +5178,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="10">
-        <v>477.2999877929688</v>
+        <v>38.93000030517578</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4902183444336746</v>
+        <v>0.5165683754044931</v>
       </c>
       <c r="G30" s="20">
-        <v>-0.9800881674162824</v>
+        <v>0.09785741135882757</v>
       </c>
       <c r="H30" s="20">
-        <v>2.147104391138658</v>
+        <v>-0.81219220040201</v>
       </c>
       <c r="I30" s="20">
-        <v>2.675284350851072</v>
+        <v>3.920900829953943</v>
       </c>
       <c r="J30" s="20">
-        <v>0.7835826359838297</v>
+        <v>0.2607885678504367</v>
       </c>
       <c r="K30" s="20">
-        <v>-0.2197038293957071</v>
+        <v>3.370836553182694</v>
       </c>
       <c r="L30" s="20">
-        <v>-3.416720321042702</v>
+        <v>-3.427259213116233</v>
       </c>
       <c r="M30" s="20">
-        <v>0.648274561202637</v>
+        <v>-0.5035836690156115</v>
       </c>
       <c r="N30" s="20">
-        <v>17.358335</v>
+        <v>12.144172</v>
       </c>
       <c r="O30" s="20">
-        <v>22.350464</v>
+        <v>2.3688147</v>
       </c>
       <c r="P30" s="12">
-        <v>1.30853</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.438</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R30" s="12">
-        <v>0.822398437321578</v>
+        <v>0.2245989048135262</v>
       </c>
       <c r="S30" s="11">
-        <v>50.4863565454001</v>
+        <v>59.10137546437928</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -5194,61 +5240,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="E31" s="10">
-        <v>64.69000244140625</v>
+        <v>213.8099975585938</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4835314296583552</v>
+        <v>0.5111044428488211</v>
       </c>
       <c r="G31" s="20">
-        <v>0.4785242056074159</v>
+        <v>0.5306330587817526</v>
       </c>
       <c r="H31" s="20">
-        <v>0.6574599095763384</v>
+        <v>-0.3271612979466518</v>
       </c>
       <c r="I31" s="20">
-        <v>0.2335665909722698</v>
+        <v>2.322186162377909</v>
       </c>
       <c r="J31" s="20">
-        <v>0.5112723003362208</v>
+        <v>0.8898064438164361</v>
       </c>
       <c r="K31" s="20">
-        <v>0.8084213631287113</v>
+        <v>-0.1711975264478132</v>
       </c>
       <c r="L31" s="20">
-        <v>0.5464006194230052</v>
+        <v>0.7625016530393559</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.1791182852764088</v>
+        <v>-0.7053830681471978</v>
       </c>
       <c r="N31" s="20">
-        <v>14.718061</v>
+        <v>20.076998</v>
       </c>
       <c r="O31" s="20">
-        <v>6.116247</v>
+        <v>2.1549587</v>
       </c>
       <c r="P31" s="12">
-        <v>0.46598998</v>
+        <v>0.12231</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.057</v>
+        <v>0.535</v>
       </c>
       <c r="R31" s="12">
-        <v>0.09013335897834285</v>
+        <v>0.16834710124306</v>
       </c>
       <c r="S31" s="11">
-        <v>46.65735197441372</v>
+        <v>70.55040749646682</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -5256,61 +5302,61 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="E32" s="10">
-        <v>212.5</v>
+        <v>223.6699981689453</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4753714760860758</v>
+        <v>0.5029733670908321</v>
       </c>
       <c r="G32" s="20">
-        <v>0.2276945080429548</v>
+        <v>-1.255664189485384</v>
       </c>
       <c r="H32" s="20">
-        <v>0.03119877719549098</v>
+        <v>2.368358787986747</v>
       </c>
       <c r="I32" s="20">
-        <v>-0.8985721544356027</v>
+        <v>2.430954222251415</v>
       </c>
       <c r="J32" s="20">
-        <v>0.401909284420032</v>
+        <v>0.5426884151152741</v>
       </c>
       <c r="K32" s="20">
-        <v>3.376923353914425</v>
+        <v>-0.3093528362049048</v>
       </c>
       <c r="L32" s="20">
-        <v>-0.1154307044985162</v>
+        <v>-0.2168963964814134</v>
       </c>
       <c r="M32" s="20">
-        <v>0.004676627559951518</v>
+        <v>-0.07137884382410897</v>
       </c>
       <c r="N32" s="20">
-        <v>39.2238</v>
+        <v>29.159492</v>
       </c>
       <c r="O32" s="20">
-        <v>1.730507</v>
+        <v>24.291891</v>
       </c>
       <c r="P32" s="12">
-        <v>0.04575</v>
+        <v>1.17211</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.034</v>
+        <v>1.059</v>
       </c>
       <c r="R32" s="12">
-        <v>0.1288779951067147</v>
+        <v>0.2120085147302435</v>
       </c>
       <c r="S32" s="11">
-        <v>47.84446106344914</v>
+        <v>54.31658542796111</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -5318,61 +5364,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="E33" s="10">
-        <v>352.5400085449219</v>
+        <v>64.41000366210938</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4656193589205661</v>
+        <v>0.4773493097566183</v>
       </c>
       <c r="G33" s="20">
-        <v>0.09769025453656566</v>
+        <v>0.4785242056074159</v>
       </c>
       <c r="H33" s="20">
-        <v>-0.2373803208952873</v>
+        <v>0.6574599095763384</v>
       </c>
       <c r="I33" s="20">
-        <v>0.4704496970046058</v>
+        <v>0.2335665909722698</v>
       </c>
       <c r="J33" s="20">
-        <v>1.44106755832677</v>
+        <v>0.5186742915074114</v>
       </c>
       <c r="K33" s="20">
-        <v>1.706672663693578</v>
+        <v>0.8031067102719743</v>
       </c>
       <c r="L33" s="20">
-        <v>-1.684092777206551</v>
+        <v>0.5483101489315492</v>
       </c>
       <c r="M33" s="20">
-        <v>-1.213805322026222</v>
+        <v>-0.2776124187863871</v>
       </c>
       <c r="N33" s="20">
-        <v>33.248394</v>
+        <v>14.718061</v>
       </c>
       <c r="O33" s="20">
-        <v>5.0043454</v>
+        <v>6.116247</v>
       </c>
       <c r="P33" s="12">
-        <v>0.15286</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q33" s="12">
-        <v>0.204</v>
+        <v>0.057</v>
       </c>
       <c r="R33" s="12">
-        <v>0.6490785412945888</v>
+        <v>0.09444047287161528</v>
       </c>
       <c r="S33" s="11">
-        <v>53.80004140607057</v>
+        <v>45.52777965278488</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -5380,61 +5426,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E34" s="10">
-        <v>209.8000030517578</v>
+        <v>344.8299865722656</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4493945547233394</v>
+        <v>0.4531572461392963</v>
       </c>
       <c r="G34" s="20">
-        <v>0.5306330587817526</v>
+        <v>0.09769025453656566</v>
       </c>
       <c r="H34" s="20">
-        <v>-0.3271612979466518</v>
+        <v>-0.2373803208952873</v>
       </c>
       <c r="I34" s="20">
-        <v>2.322186162377909</v>
+        <v>0.4704496970046058</v>
       </c>
       <c r="J34" s="20">
-        <v>0.6846640972297852</v>
+        <v>1.34294690561148</v>
       </c>
       <c r="K34" s="20">
-        <v>-0.1695135205507808</v>
+        <v>1.69802319437015</v>
       </c>
       <c r="L34" s="20">
-        <v>0.7718811317766416</v>
+        <v>-1.693368662516335</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.7170334879142883</v>
+        <v>-0.9816981661422759</v>
       </c>
       <c r="N34" s="20">
-        <v>20.076998</v>
+        <v>33.248394</v>
       </c>
       <c r="O34" s="20">
-        <v>2.1549587</v>
+        <v>5.0043454</v>
       </c>
       <c r="P34" s="12">
-        <v>0.12231</v>
+        <v>0.15286</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.535</v>
+        <v>0.204</v>
       </c>
       <c r="R34" s="12">
-        <v>0.1273719414412338</v>
+        <v>0.622958462799996</v>
       </c>
       <c r="S34" s="11">
-        <v>66.2812788972652</v>
+        <v>49.24290051439417</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -5442,61 +5488,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E35" s="10">
-        <v>216.2400054931641</v>
+        <v>210.7299957275391</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4344472686351803</v>
+        <v>0.4493773174039252</v>
       </c>
       <c r="G35" s="20">
-        <v>0.3451625228080399</v>
+        <v>0.2276945080429548</v>
       </c>
       <c r="H35" s="20">
-        <v>0.7739793579701058</v>
+        <v>0.03119877719549098</v>
       </c>
       <c r="I35" s="20">
-        <v>0.3853148937972363</v>
+        <v>-0.8985721544356027</v>
       </c>
       <c r="J35" s="20">
-        <v>0.4614414911879133</v>
+        <v>0.3558712693770349</v>
       </c>
       <c r="K35" s="20">
-        <v>0.3013440160356414</v>
+        <v>3.362072970101089</v>
       </c>
       <c r="L35" s="20">
-        <v>0.5716186384678913</v>
+        <v>-0.115198605209464</v>
       </c>
       <c r="M35" s="20">
-        <v>0.01323725357585087</v>
+        <v>-0.1255062983024788</v>
       </c>
       <c r="N35" s="20">
-        <v>17.572235</v>
+        <v>39.2238</v>
       </c>
       <c r="O35" s="20">
-        <v>3.211162</v>
+        <v>1.730507</v>
       </c>
       <c r="P35" s="12">
-        <v>0.17969999</v>
+        <v>0.04575</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.28</v>
+        <v>0.034</v>
       </c>
       <c r="R35" s="12">
-        <v>0.3624108746719914</v>
+        <v>0.1184650052099032</v>
       </c>
       <c r="S35" s="11">
-        <v>52.49376650997617</v>
+        <v>46.00394204412848</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -5504,61 +5550,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="E36" s="10">
-        <v>904.3800048828125</v>
+        <v>215.3500061035156</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4277528213124358</v>
+        <v>0.4462442929594646</v>
       </c>
       <c r="G36" s="20">
-        <v>-2.161506497931219</v>
+        <v>0.3451625228080399</v>
       </c>
       <c r="H36" s="20">
-        <v>1.683877559410052</v>
+        <v>0.7739793579701058</v>
       </c>
       <c r="I36" s="20">
-        <v>1.349061869241311</v>
+        <v>0.3853148937972363</v>
       </c>
       <c r="J36" s="20">
-        <v>2.004312972346333</v>
+        <v>0.4948865523146312</v>
       </c>
       <c r="K36" s="20">
-        <v>-0.00135011462705862</v>
+        <v>0.2979119208617143</v>
       </c>
       <c r="L36" s="20">
-        <v>-3.02413084282166</v>
+        <v>0.5763142240165818</v>
       </c>
       <c r="M36" s="20">
-        <v>-0.08983291086297163</v>
+        <v>0.03690753200358504</v>
       </c>
       <c r="N36" s="20">
-        <v>60.967697</v>
+        <v>17.572235</v>
       </c>
       <c r="O36" s="20">
-        <v>88.88330999999999</v>
+        <v>3.211162</v>
       </c>
       <c r="P36" s="12">
-        <v>3.7152898</v>
+        <v>0.17969999</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.485</v>
+        <v>0.28</v>
       </c>
       <c r="R36" s="12">
-        <v>1.421936781263033</v>
+        <v>0.3542712887936303</v>
       </c>
       <c r="S36" s="11">
-        <v>57.10377197111912</v>
+        <v>50.98928498558899</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -5566,61 +5612,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="10">
-        <v>31.17000007629395</v>
+        <v>885.9199829101562</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4154376913907029</v>
+        <v>0.4302820216532392</v>
       </c>
       <c r="G37" s="20">
-        <v>1.115176779328165</v>
+        <v>-2.161506497931219</v>
       </c>
       <c r="H37" s="20">
-        <v>-0.9874044575767369</v>
+        <v>1.683877559410052</v>
       </c>
       <c r="I37" s="20">
-        <v>-0.3840221445724293</v>
+        <v>1.349061869241311</v>
       </c>
       <c r="J37" s="20">
-        <v>1.386920958048624</v>
+        <v>1.919789765466099</v>
       </c>
       <c r="K37" s="20">
-        <v>0.4074163182336814</v>
+        <v>-0.003658438122982013</v>
       </c>
       <c r="L37" s="20">
-        <v>-0.5541681022294552</v>
+        <v>-2.950052929040729</v>
       </c>
       <c r="M37" s="20">
-        <v>-0.2577920085963465</v>
+        <v>0.2066481691061354</v>
       </c>
       <c r="N37" s="20">
-        <v>12.458015</v>
+        <v>60.967697</v>
       </c>
       <c r="O37" s="20">
-        <v>-320</v>
+        <v>88.88330999999999</v>
       </c>
       <c r="P37" s="12">
-        <v>0</v>
+        <v>3.7152898</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.125</v>
+        <v>0.485</v>
       </c>
       <c r="R37" s="12">
-        <v>0.6936817041972732</v>
+        <v>1.311010178615966</v>
       </c>
       <c r="S37" s="11">
-        <v>57.41290193179169</v>
+        <v>54.52913029639633</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -5628,19 +5674,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E38" s="10">
-        <v>810.3099975585938</v>
+        <v>807.6500244140625</v>
       </c>
       <c r="F38" s="17">
-        <v>0.4132387079613485</v>
+        <v>0.420814776373709</v>
       </c>
       <c r="G38" s="20">
         <v>0.1366671162081818</v>
@@ -5652,16 +5698,16 @@
         <v>-0.2394962708042926</v>
       </c>
       <c r="J38" s="20">
-        <v>0.7912049523977567</v>
+        <v>0.8268369456584153</v>
       </c>
       <c r="K38" s="20">
-        <v>1.442268046995049</v>
+        <v>1.4346001970348</v>
       </c>
       <c r="L38" s="20">
-        <v>0.4983102686747095</v>
+        <v>0.4998179441534492</v>
       </c>
       <c r="M38" s="20">
-        <v>-0.7057852999347519</v>
+        <v>-0.7343334011763972</v>
       </c>
       <c r="N38" s="20">
         <v>20.49319</v>
@@ -5676,13 +5722,13 @@
         <v>0.167</v>
       </c>
       <c r="R38" s="12">
-        <v>0.03949326488628557</v>
+        <v>0.04892398899911177</v>
       </c>
       <c r="S38" s="11">
-        <v>54.60457700322396</v>
+        <v>53.73805386136186</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -5690,61 +5736,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="E39" s="10">
-        <v>28.1200008392334</v>
+        <v>136.5299987792969</v>
       </c>
       <c r="F39" s="17">
-        <v>0.3837410464321968</v>
+        <v>0.4077057610151587</v>
       </c>
       <c r="G39" s="20">
-        <v>-0.07115990276327171</v>
+        <v>0.5166686592886003</v>
       </c>
       <c r="H39" s="20">
-        <v>-0.995994779142174</v>
+        <v>-0.1376180067425467</v>
       </c>
       <c r="I39" s="20">
-        <v>-1.178947812209808</v>
+        <v>0.8009706460259883</v>
       </c>
       <c r="J39" s="20">
-        <v>0.467827712689896</v>
+        <v>1.025930069554132</v>
       </c>
       <c r="K39" s="20">
-        <v>4.1972917133727</v>
+        <v>-0.06912755879145449</v>
       </c>
       <c r="L39" s="20">
-        <v>1.138192555980974</v>
+        <v>0.4796376175125497</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.4813887244654603</v>
+        <v>-0.895434400532486</v>
       </c>
       <c r="N39" s="20">
-        <v>403.57144</v>
+        <v>17.759258</v>
       </c>
       <c r="O39" s="20">
-        <v>2.1576414</v>
+        <v>2.4681509</v>
       </c>
       <c r="P39" s="12">
-        <v>-0.08785999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="Q39" s="12">
-        <v>-0.112</v>
+        <v>0.355</v>
       </c>
       <c r="R39" s="12">
-        <v>0.01333336357597825</v>
+        <v>0.2129832807308187</v>
       </c>
       <c r="S39" s="11">
-        <v>54.16855663700049</v>
+        <v>66.61276992586393</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -5752,61 +5798,61 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="E40" s="10">
-        <v>119.379997253418</v>
+        <v>147.0099945068359</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3591119368714275</v>
+        <v>0.4004632235877128</v>
       </c>
       <c r="G40" s="20">
-        <v>1.185896662709272</v>
+        <v>0.6186160464919896</v>
       </c>
       <c r="H40" s="20">
-        <v>-0.6467007744749826</v>
+        <v>0.4653349166417897</v>
       </c>
       <c r="I40" s="20">
-        <v>0.146369195149319</v>
+        <v>1.428599056298859</v>
       </c>
       <c r="J40" s="20">
-        <v>0.509282420047845</v>
+        <v>0.4926560466693115</v>
       </c>
       <c r="K40" s="20">
-        <v>0.1999285466170274</v>
+        <v>-0.5186478203891555</v>
       </c>
       <c r="L40" s="20">
-        <v>1.025931813932411</v>
+        <v>0.2862637669770728</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.04807898074397064</v>
+        <v>-0.3867007330767101</v>
       </c>
       <c r="N40" s="20">
-        <v>11.062556</v>
+        <v>11.298833</v>
       </c>
       <c r="O40" s="20">
-        <v>1.3339746</v>
+        <v>2.394452</v>
       </c>
       <c r="P40" s="12">
-        <v>0.12011</v>
+        <v>0.22507</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.141</v>
+        <v>0.587</v>
       </c>
       <c r="R40" s="12">
-        <v>0.2759723296696863</v>
+        <v>0.1670258187334688</v>
       </c>
       <c r="S40" s="11">
-        <v>49.01858868837134</v>
+        <v>53.87520841180954</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -5814,61 +5860,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="E41" s="10">
-        <v>135.0399932861328</v>
+        <v>27.90999984741211</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3569557698999941</v>
+        <v>0.3975679214877296</v>
       </c>
       <c r="G41" s="20">
-        <v>0.5166686592886003</v>
+        <v>-0.07115990276327171</v>
       </c>
       <c r="H41" s="20">
-        <v>-0.1376180067425467</v>
+        <v>-0.995994779142174</v>
       </c>
       <c r="I41" s="20">
-        <v>0.8009706460259883</v>
+        <v>-1.178947812209808</v>
       </c>
       <c r="J41" s="20">
-        <v>0.84527793237839</v>
+        <v>0.4732468049597856</v>
       </c>
       <c r="K41" s="20">
-        <v>-0.06706319940340542</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L41" s="20">
-        <v>0.4731600917334195</v>
+        <v>1.138908902891917</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.8506021698107358</v>
+        <v>-0.3287655186500924</v>
       </c>
       <c r="N41" s="20">
-        <v>17.759258</v>
+        <v>403.57144</v>
       </c>
       <c r="O41" s="20">
-        <v>2.4681509</v>
+        <v>2.1576414</v>
       </c>
       <c r="P41" s="12">
-        <v>0.1418</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q41" s="12">
-        <v>0.355</v>
+        <v>-0.112</v>
       </c>
       <c r="R41" s="12">
-        <v>0.1702209725733994</v>
+        <v>0.005403444427000137</v>
       </c>
       <c r="S41" s="11">
-        <v>64.3914408919788</v>
+        <v>50.03528328324084</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -5876,61 +5922,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="E42" s="10">
-        <v>145.3600006103516</v>
+        <v>128.7100067138672</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3525353757260941</v>
+        <v>0.3914625229953394</v>
       </c>
       <c r="G42" s="20">
-        <v>0.6186160464919896</v>
+        <v>0.462770354618154</v>
       </c>
       <c r="H42" s="20">
-        <v>0.4653349166417897</v>
+        <v>0.7818596344809873</v>
       </c>
       <c r="I42" s="20">
-        <v>1.428599056298859</v>
+        <v>-0.2047856713387676</v>
       </c>
       <c r="J42" s="20">
-        <v>0.2986500093411688</v>
+        <v>1.222462886023134</v>
       </c>
       <c r="K42" s="20">
-        <v>-0.5182585531433617</v>
+        <v>-0.3340970707882645</v>
       </c>
       <c r="L42" s="20">
-        <v>0.2865535970011453</v>
+        <v>-0.5514092375045718</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.2590774647531525</v>
+        <v>-1.125222228513545</v>
       </c>
       <c r="N42" s="20">
-        <v>11.298833</v>
+        <v>16.152584</v>
       </c>
       <c r="O42" s="20">
-        <v>2.394452</v>
+        <v>3.848858</v>
       </c>
       <c r="P42" s="12">
-        <v>0.22507</v>
+        <v>0.25905</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.587</v>
+        <v>0.151</v>
       </c>
       <c r="R42" s="12">
-        <v>0.1208003282051089</v>
+        <v>0.08729262667910476</v>
       </c>
       <c r="S42" s="11">
-        <v>50.88260764505864</v>
+        <v>60.90704506011068</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -5938,61 +5984,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="E43" s="10">
-        <v>127.0899963378906</v>
+        <v>383.6900024414062</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3498879729099648</v>
+        <v>0.3817434987565279</v>
       </c>
       <c r="G43" s="20">
-        <v>0.462770354618154</v>
+        <v>-1.119776310688084</v>
       </c>
       <c r="H43" s="20">
-        <v>0.7818596344809873</v>
+        <v>0.5633615561685517</v>
       </c>
       <c r="I43" s="20">
-        <v>-0.2047856713387676</v>
+        <v>3.683499757563413</v>
       </c>
       <c r="J43" s="20">
-        <v>1.082681910991223</v>
+        <v>0.9486169808161514</v>
       </c>
       <c r="K43" s="20">
-        <v>-0.3330200936950768</v>
+        <v>0.4185400644555927</v>
       </c>
       <c r="L43" s="20">
-        <v>-0.5670289724339773</v>
+        <v>-3.289372120440793</v>
       </c>
       <c r="M43" s="20">
-        <v>-1.11062611265379</v>
+        <v>-0.1579020601999454</v>
       </c>
       <c r="N43" s="20">
-        <v>16.152584</v>
+        <v>49.04258</v>
       </c>
       <c r="O43" s="20">
-        <v>3.848858</v>
+        <v>16.253017</v>
       </c>
       <c r="P43" s="12">
-        <v>0.25905</v>
+        <v>0.36465</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.151</v>
+        <v>1.039</v>
       </c>
       <c r="R43" s="12">
-        <v>0.09141523283859998</v>
+        <v>0.2766643569214373</v>
       </c>
       <c r="S43" s="11">
-        <v>59.21893500836516</v>
+        <v>54.5644415220998</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -6000,61 +6046,61 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="E44" s="10">
-        <v>403.0899963378906</v>
+        <v>138.1100006103516</v>
       </c>
       <c r="F44" s="17">
-        <v>0.348493922306141</v>
+        <v>0.3773361396728952</v>
       </c>
       <c r="G44" s="20">
-        <v>0.3688830871595546</v>
+        <v>0.6342024451803385</v>
       </c>
       <c r="H44" s="20">
-        <v>-1.053638917449358</v>
+        <v>0.2959780642595878</v>
       </c>
       <c r="I44" s="20">
-        <v>0.1661481722292586</v>
+        <v>0.2897869408623402</v>
       </c>
       <c r="J44" s="20">
-        <v>1.513072995384774</v>
+        <v>1.275151234918139</v>
       </c>
       <c r="K44" s="20">
-        <v>-0.1721006498726843</v>
+        <v>-1.403769711631418</v>
       </c>
       <c r="L44" s="20">
-        <v>0.1932687714983893</v>
+        <v>0.0006690907096995564</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.1350446341777612</v>
+        <v>-0.3411079418698413</v>
       </c>
       <c r="N44" s="20">
-        <v>38.02462</v>
+        <v>9.892434</v>
       </c>
       <c r="O44" s="20">
-        <v>2.5096092</v>
+        <v>3.5168924</v>
       </c>
       <c r="P44" s="12">
-        <v>0.06893000000000001</v>
+        <v>0.29867</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.262</v>
+        <v>0.176</v>
       </c>
       <c r="R44" s="12">
-        <v>1.274648731403301</v>
+        <v>0.2665911661926548</v>
       </c>
       <c r="S44" s="11">
-        <v>60.23905928676178</v>
+        <v>65.88393830203765</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -6120,110 +6166,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B6" s="12">
         <v>0.18</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B7" s="12">
         <v>0.16</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B8" s="12">
         <v>0.1</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B9" s="12">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B10" s="12">
         <v>0.12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B11" s="12">
         <v>0.06</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B12" s="12">
         <v>0.08</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B13" s="12">
         <f>SUM(B6:B12)</f>
@@ -6232,22 +6278,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -6326,57 +6372,57 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>30</v>
@@ -6384,113 +6430,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -6508,1672 +6554,1645 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI9"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:60">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>394.9174194335938</v>
+        <v>403.4133605957031</v>
       </c>
       <c r="C1">
-        <v>408.3951416015625</v>
+        <v>418.6282348632812</v>
       </c>
       <c r="D1">
-        <v>403.4133605957031</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="E1">
-        <v>418.6282348632812</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="F1">
-        <v>408.8244323730469</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="G1">
-        <v>418.0192260742188</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="H1">
-        <v>427.0742797851562</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="I1">
-        <v>433.3439025878906</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="J1">
-        <v>408.7745361328125</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="K1">
-        <v>398.8309326171875</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="L1">
-        <v>413.9259948730469</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="M1">
-        <v>430.7481994628906</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="N1">
-        <v>424.5484619140625</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="O1">
-        <v>393.6694946289062</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="P1">
-        <v>411.1206359863281</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="Q1">
-        <v>416.5915832519531</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="R1">
-        <v>431.2573547363281</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="S1">
-        <v>449.4772644042969</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="T1">
-        <v>434.2524108886719</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="U1">
-        <v>426.4053649902344</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="V1">
-        <v>456.7851867675781</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="W1">
-        <v>411.9991760253906</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="X1">
-        <v>390.7343444824219</v>
+        <v>381.25</v>
       </c>
       <c r="Y1">
-        <v>395.6861267089844</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="Z1">
-        <v>381.25</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="AA1">
-        <v>404.1499938964844</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="AB1">
-        <v>441.7999877929688</v>
+        <v>437.5</v>
       </c>
       <c r="AC1">
-        <v>439.3399963378906</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AD1">
-        <v>437.5</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AE1">
-        <v>426.9100036621094</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AF1">
-        <v>392.1000061035156</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AG1">
-        <v>369.6400146484375</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AH1">
-        <v>404.8099975585938</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AI1">
-        <v>405.3699951171875</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AJ1">
-        <v>429.0199890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AK1">
-        <v>467.2699890136719</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AL1">
-        <v>462.7000122070312</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AM1">
-        <v>437.6499938964844</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AN1">
-        <v>453.7699890136719</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AO1">
-        <v>457.8800048828125</v>
+        <v>484.5</v>
       </c>
       <c r="AP1">
-        <v>440.9700012207031</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AQ1">
-        <v>484.5</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AR1">
-        <v>494.510009765625</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AS1">
-        <v>490.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AT1">
-        <v>479.8099975585938</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="AU1">
-        <v>468.6499938964844</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="AV1">
-        <v>437.5499877929688</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="AW1">
-        <v>434.7799987792969</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="AX1">
-        <v>442.0799865722656</v>
+        <v>451.5</v>
       </c>
       <c r="AY1">
-        <v>433.1900024414062</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="AZ1">
-        <v>451.5</v>
+        <v>472.260009765625</v>
       </c>
       <c r="BA1">
-        <v>463.8200073242188</v>
+        <v>456.239990234375</v>
       </c>
       <c r="BB1">
-        <v>472.260009765625</v>
+        <v>456.010009765625</v>
       </c>
       <c r="BC1">
-        <v>456.239990234375</v>
+        <v>425</v>
       </c>
       <c r="BD1">
-        <v>456.010009765625</v>
+        <v>492.2000122070312</v>
       </c>
       <c r="BE1">
-        <v>425</v>
+        <v>516.3900146484375</v>
       </c>
       <c r="BF1">
-        <v>492.2000122070312</v>
+        <v>524.1400146484375</v>
       </c>
       <c r="BG1">
-        <v>516.3900146484375</v>
+        <v>533.8800048828125</v>
       </c>
       <c r="BH1">
-        <v>524.1400146484375</v>
-      </c>
-      <c r="BI1">
-        <v>533.8800048828125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:61">
+        <v>535.25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:60">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>981.4590454101562</v>
+        <v>1020.60302734375</v>
       </c>
       <c r="C2">
-        <v>1087.822631835938</v>
+        <v>1043.029541015625</v>
       </c>
       <c r="D2">
-        <v>1020.60302734375</v>
+        <v>1133.815551757812</v>
       </c>
       <c r="E2">
-        <v>1043.029541015625</v>
+        <v>1211.193725585938</v>
       </c>
       <c r="F2">
-        <v>1133.815551757812</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="G2">
-        <v>1211.193725585938</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="H2">
-        <v>1051.608276367188</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="I2">
-        <v>1048.348754882812</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="J2">
-        <v>1213.373413085938</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="K2">
-        <v>1132.155883789062</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="L2">
-        <v>1145.103881835938</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="M2">
-        <v>1154.112548828125</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="N2">
-        <v>1032.121337890625</v>
+        <v>984.75</v>
       </c>
       <c r="O2">
-        <v>975.4099731445312</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="P2">
-        <v>984.75</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="Q2">
-        <v>938.3800048828125</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="R2">
-        <v>948.7999877929688</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="S2">
-        <v>991.6400146484375</v>
+        <v>937</v>
       </c>
       <c r="T2">
-        <v>979.2999877929688</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="U2">
-        <v>937</v>
+        <v>904.280029296875</v>
       </c>
       <c r="V2">
-        <v>983.1199951171875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="W2">
-        <v>904.280029296875</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="X2">
-        <v>853.2000122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="Y2">
-        <v>848.9500122070312</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="Z2">
-        <v>865.4600219726562</v>
+        <v>959.47998046875</v>
       </c>
       <c r="AA2">
-        <v>970.8200073242188</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="AB2">
-        <v>959.47998046875</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="AC2">
-        <v>990.2100219726562</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="AD2">
-        <v>920.9500122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AE2">
-        <v>900.2000122070312</v>
+        <v>739</v>
       </c>
       <c r="AF2">
-        <v>820.530029296875</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AG2">
-        <v>739</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AH2">
-        <v>874.6599731445312</v>
+        <v>829.5</v>
       </c>
       <c r="AI2">
-        <v>823.030029296875</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AJ2">
-        <v>829.5</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AK2">
-        <v>892.6699829101562</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AL2">
-        <v>893.1900024414062</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AM2">
-        <v>881.469970703125</v>
+        <v>861</v>
       </c>
       <c r="AN2">
-        <v>877.5700073242188</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AO2">
-        <v>861</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AP2">
-        <v>868.52001953125</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AQ2">
-        <v>911.2899780273438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AR2">
-        <v>949.8300170898438</v>
+        <v>1011.75</v>
       </c>
       <c r="AS2">
-        <v>971.6599731445312</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AT2">
-        <v>1011.75</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="AU2">
-        <v>940.760009765625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="AV2">
-        <v>937.1099853515625</v>
+        <v>966.780029296875</v>
       </c>
       <c r="AW2">
-        <v>974.3300170898438</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="AX2">
-        <v>966.780029296875</v>
+        <v>932.969970703125</v>
       </c>
       <c r="AY2">
-        <v>910.4299926757812</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="AZ2">
-        <v>932.969970703125</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="BA2">
-        <v>938.4000244140625</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="BB2">
-        <v>935.3900146484375</v>
+        <v>958.72998046875</v>
       </c>
       <c r="BC2">
-        <v>932.8599853515625</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="BD2">
-        <v>958.72998046875</v>
+        <v>956.0800170898438</v>
       </c>
       <c r="BE2">
-        <v>933.4400024414062</v>
+        <v>958.1599731445312</v>
       </c>
       <c r="BF2">
-        <v>956.0800170898438</v>
+        <v>1016.590026855469</v>
       </c>
       <c r="BG2">
-        <v>958.1599731445312</v>
+        <v>1000.260009765625</v>
       </c>
       <c r="BH2">
-        <v>1016.590026855469</v>
-      </c>
-      <c r="BI2">
-        <v>1000.260009765625</v>
-      </c>
-    </row>
-    <row r="3" spans="1:61">
+        <v>1027.77001953125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:60">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1980.099975585938</v>
+        <v>1991.550048828125</v>
       </c>
       <c r="C3">
-        <v>2107.860107421875</v>
+        <v>1958.800048828125</v>
       </c>
       <c r="D3">
-        <v>1991.550048828125</v>
+        <v>2184.75</v>
       </c>
       <c r="E3">
-        <v>1958.800048828125</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="F3">
-        <v>2184.75</v>
+        <v>1963.599975585938</v>
       </c>
       <c r="G3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="H3">
+        <v>2335</v>
+      </c>
+      <c r="I3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="J3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="K3">
         <v>2273.72998046875</v>
       </c>
-      <c r="H3">
-        <v>1963.599975585938</v>
-      </c>
-      <c r="I3">
-        <v>1914.4599609375</v>
-      </c>
-      <c r="J3">
-        <v>2335</v>
-      </c>
-      <c r="K3">
-        <v>2090.7099609375</v>
-      </c>
       <c r="L3">
-        <v>2050.389892578125</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="M3">
-        <v>2273.72998046875</v>
+        <v>1745</v>
       </c>
       <c r="N3">
-        <v>2032.219970703125</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="O3">
-        <v>1745</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="P3">
-        <v>1744.430053710938</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="Q3">
-        <v>1617.699951171875</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="R3">
-        <v>1727.180053710938</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="S3">
-        <v>1858.27001953125</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="T3">
-        <v>1915.920043945312</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="U3">
-        <v>1673.969970703125</v>
+        <v>1615</v>
       </c>
       <c r="V3">
-        <v>1757.819946289062</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="W3">
-        <v>1615</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="X3">
-        <v>1411.079956054688</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="Y3">
-        <v>1354.819946289062</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="Z3">
-        <v>1390.949951171875</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="AA3">
-        <v>1589.400024414062</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="AB3">
-        <v>1599.27001953125</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="AC3">
-        <v>1610.329956054688</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="AD3">
-        <v>1436.56005859375</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="AE3">
-        <v>1278.22998046875</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AF3">
-        <v>1096.099975585938</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AG3">
-        <v>1015.890014648438</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AH3">
-        <v>1279.9599609375</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AI3">
-        <v>1214.829956054688</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AJ3">
-        <v>1288.030029296875</v>
+        <v>1350.5</v>
       </c>
       <c r="AK3">
-        <v>1427.619995117188</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AL3">
-        <v>1350.5</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AM3">
-        <v>1258.579956054688</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AN3">
-        <v>1212.2099609375</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AO3">
-        <v>1237.920043945312</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AP3">
-        <v>1271.050048828125</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AQ3">
-        <v>1344.2900390625</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AR3">
-        <v>1528.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AS3">
-        <v>1641.109985351562</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AT3">
-        <v>1786.849975585938</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="AU3">
-        <v>1625.780029296875</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="AV3">
-        <v>1568.869995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="AW3">
-        <v>1600.619995117188</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="AX3">
-        <v>1596.079956054688</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="AY3">
-        <v>1493.119995117188</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="AZ3">
-        <v>1480.77001953125</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="BA3">
-        <v>1499.369995117188</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="BB3">
-        <v>1484.949951171875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="BC3">
-        <v>1484.97998046875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="BD3">
-        <v>1566.699951171875</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="BE3">
-        <v>1536.869995117188</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="BF3">
-        <v>1553.400024414062</v>
+        <v>1740</v>
       </c>
       <c r="BG3">
-        <v>1554.989990234375</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="BH3">
-        <v>1740</v>
-      </c>
-      <c r="BI3">
-        <v>1737.989990234375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:61">
+        <v>1764.170043945312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:60">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>562.7493286132812</v>
+        <v>680.8614501953125</v>
       </c>
       <c r="C4">
-        <v>653.3203125</v>
+        <v>711.9014892578125</v>
       </c>
       <c r="D4">
-        <v>680.8614501953125</v>
+        <v>745.990478515625</v>
       </c>
       <c r="E4">
-        <v>711.9014892578125</v>
+        <v>732.3848876953125</v>
       </c>
       <c r="F4">
-        <v>745.990478515625</v>
+        <v>670.5347290039062</v>
       </c>
       <c r="G4">
-        <v>732.3848876953125</v>
+        <v>643.6234130859375</v>
       </c>
       <c r="H4">
-        <v>670.5347290039062</v>
+        <v>675.1732788085938</v>
       </c>
       <c r="I4">
-        <v>643.6234130859375</v>
+        <v>586.2618408203125</v>
       </c>
       <c r="J4">
-        <v>675.1732788085938</v>
+        <v>651.6708374023438</v>
       </c>
       <c r="K4">
-        <v>586.2618408203125</v>
+        <v>638.5150146484375</v>
       </c>
       <c r="L4">
-        <v>651.6708374023438</v>
+        <v>598.177978515625</v>
       </c>
       <c r="M4">
-        <v>638.5150146484375</v>
+        <v>538.8270263671875</v>
       </c>
       <c r="N4">
-        <v>598.177978515625</v>
+        <v>577.2747192382812</v>
       </c>
       <c r="O4">
-        <v>538.8270263671875</v>
+        <v>531.92919921875</v>
       </c>
       <c r="P4">
-        <v>577.2747192382812</v>
+        <v>550.1234130859375</v>
       </c>
       <c r="Q4">
-        <v>531.92919921875</v>
+        <v>577.864501953125</v>
       </c>
       <c r="R4">
-        <v>550.1234130859375</v>
+        <v>582.403076171875</v>
       </c>
       <c r="S4">
-        <v>577.864501953125</v>
+        <v>555.3717041015625</v>
       </c>
       <c r="T4">
-        <v>582.403076171875</v>
+        <v>563.1392211914062</v>
       </c>
       <c r="U4">
-        <v>555.3717041015625</v>
+        <v>513.6751098632812</v>
       </c>
       <c r="V4">
-        <v>563.1392211914062</v>
+        <v>466.6601867675781</v>
       </c>
       <c r="W4">
-        <v>513.6751098632812</v>
+        <v>477.0668640136719</v>
       </c>
       <c r="X4">
-        <v>466.6601867675781</v>
+        <v>487.2635803222656</v>
       </c>
       <c r="Y4">
-        <v>477.0668640136719</v>
+        <v>548.2140502929688</v>
       </c>
       <c r="Z4">
-        <v>487.2635803222656</v>
+        <v>556.4913330078125</v>
       </c>
       <c r="AA4">
-        <v>548.2140502929688</v>
+        <v>558.120849609375</v>
       </c>
       <c r="AB4">
-        <v>556.4913330078125</v>
+        <v>519.6331787109375</v>
       </c>
       <c r="AC4">
-        <v>558.120849609375</v>
+        <v>497.7602233886719</v>
       </c>
       <c r="AD4">
-        <v>519.6331787109375</v>
+        <v>463.3612670898438</v>
       </c>
       <c r="AE4">
-        <v>497.7602233886719</v>
+        <v>461.8917236328125</v>
       </c>
       <c r="AF4">
-        <v>463.3612670898438</v>
+        <v>532.868896484375</v>
       </c>
       <c r="AG4">
-        <v>461.8917236328125</v>
+        <v>544.6651611328125</v>
       </c>
       <c r="AH4">
-        <v>532.868896484375</v>
+        <v>527.05078125</v>
       </c>
       <c r="AI4">
-        <v>544.6651611328125</v>
+        <v>548.3839721679688</v>
       </c>
       <c r="AJ4">
-        <v>527.05078125</v>
+        <v>519.0033569335938</v>
       </c>
       <c r="AK4">
-        <v>548.3839721679688</v>
+        <v>451.3750915527344</v>
       </c>
       <c r="AL4">
-        <v>519.0033569335938</v>
+        <v>434.1606140136719</v>
       </c>
       <c r="AM4">
-        <v>451.3750915527344</v>
+        <v>438.1993408203125</v>
       </c>
       <c r="AN4">
-        <v>434.1606140136719</v>
+        <v>437.7894592285156</v>
       </c>
       <c r="AO4">
-        <v>438.1993408203125</v>
+        <v>453.9542846679688</v>
       </c>
       <c r="AP4">
-        <v>437.7894592285156</v>
+        <v>487.1336364746094</v>
       </c>
       <c r="AQ4">
-        <v>453.9542846679688</v>
+        <v>508.63671875</v>
       </c>
       <c r="AR4">
-        <v>487.1336364746094</v>
+        <v>535.8380126953125</v>
       </c>
       <c r="AS4">
-        <v>508.63671875</v>
+        <v>496.0007934570312</v>
       </c>
       <c r="AT4">
-        <v>535.8380126953125</v>
+        <v>461.9417114257812</v>
       </c>
       <c r="AU4">
-        <v>496.0007934570312</v>
+        <v>468.8994750976562</v>
       </c>
       <c r="AV4">
-        <v>461.9417114257812</v>
+        <v>459.2925720214844</v>
       </c>
       <c r="AW4">
-        <v>468.8994750976562</v>
+        <v>435.2402954101562</v>
       </c>
       <c r="AX4">
-        <v>459.2925720214844</v>
+        <v>450.6053466796875</v>
       </c>
       <c r="AY4">
-        <v>435.2402954101562</v>
+        <v>468.7295227050781</v>
       </c>
       <c r="AZ4">
-        <v>450.6053466796875</v>
+        <v>461.8517456054688</v>
       </c>
       <c r="BA4">
-        <v>468.7295227050781</v>
+        <v>459.3025817871094</v>
       </c>
       <c r="BB4">
-        <v>461.8517456054688</v>
+        <v>450.4053955078125</v>
       </c>
       <c r="BC4">
-        <v>459.3025817871094</v>
+        <v>450.2954406738281</v>
       </c>
       <c r="BD4">
-        <v>450.4053955078125</v>
+        <v>448.7559509277344</v>
       </c>
       <c r="BE4">
-        <v>450.2954406738281</v>
+        <v>441.4283142089844</v>
       </c>
       <c r="BF4">
-        <v>448.7559509277344</v>
+        <v>467.3099670410156</v>
       </c>
       <c r="BG4">
-        <v>441.4283142089844</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="BH4">
-        <v>467.3099670410156</v>
-      </c>
-      <c r="BI4">
-        <v>477.2999877929688</v>
-      </c>
-    </row>
-    <row r="5" spans="1:61">
+        <v>482.2799987792969</v>
+      </c>
+    </row>
+    <row r="5" spans="1:60">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>257.6741943359375</v>
+        <v>243.1901702880859</v>
       </c>
       <c r="C5">
-        <v>246.20849609375</v>
+        <v>238.8469543457031</v>
       </c>
       <c r="D5">
-        <v>243.1901702880859</v>
+        <v>235.3903045654297</v>
       </c>
       <c r="E5">
-        <v>238.8469543457031</v>
+        <v>242.8415069580078</v>
       </c>
       <c r="F5">
-        <v>235.3903045654297</v>
+        <v>242.7418823242188</v>
       </c>
       <c r="G5">
-        <v>242.8415069580078</v>
+        <v>241.4967041015625</v>
       </c>
       <c r="H5">
-        <v>242.7418823242188</v>
+        <v>254.0780792236328</v>
       </c>
       <c r="I5">
-        <v>241.4967041015625</v>
+        <v>258.3714904785156</v>
       </c>
       <c r="J5">
-        <v>254.0780792236328</v>
+        <v>265.2947387695312</v>
       </c>
       <c r="K5">
-        <v>258.3714904785156</v>
+        <v>259.4373779296875</v>
       </c>
       <c r="L5">
-        <v>265.2947387695312</v>
+        <v>268.4027404785156</v>
       </c>
       <c r="M5">
-        <v>259.4373779296875</v>
+        <v>266.7291870117188</v>
       </c>
       <c r="N5">
-        <v>268.4027404785156</v>
+        <v>269.2793579101562</v>
       </c>
       <c r="O5">
-        <v>266.7291870117188</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="P5">
-        <v>269.2793579101562</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="Q5">
-        <v>265.1951293945312</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="R5">
-        <v>281.7909851074219</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="S5">
-        <v>280.1672668457031</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="T5">
-        <v>279.6094055175781</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="U5">
-        <v>294.6513061523438</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="V5">
-        <v>300.2695617675781</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="W5">
-        <v>291.5333251953125</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="X5">
-        <v>299.1040954589844</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="Y5">
-        <v>308.4579162597656</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="Z5">
-        <v>312.1038208007812</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="AA5">
-        <v>313.5880737304688</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="AB5">
-        <v>309.7230529785156</v>
+        <v>301.33544921875</v>
       </c>
       <c r="AC5">
-        <v>304.0848388671875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="AD5">
-        <v>301.33544921875</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="AE5">
-        <v>303.756103515625</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="AF5">
-        <v>297.7294006347656</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="AG5">
-        <v>300.1600036621094</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="AH5">
-        <v>310.5099792480469</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="AI5">
-        <v>312.8999938964844</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="AJ5">
-        <v>307.5400085449219</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="AK5">
-        <v>308.7300109863281</v>
+        <v>302.989990234375</v>
       </c>
       <c r="AL5">
-        <v>302.3900146484375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="AM5">
-        <v>302.989990234375</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AN5">
-        <v>298.3099975585938</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AO5">
-        <v>314.9500122070312</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AP5">
-        <v>323.9200134277344</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AQ5">
-        <v>330.2099914550781</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AR5">
-        <v>342.9200134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AS5">
-        <v>341.6700134277344</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AT5">
-        <v>347.1900024414062</v>
+        <v>346.260009765625</v>
       </c>
       <c r="AU5">
-        <v>350.0499877929688</v>
+        <v>341.510009765625</v>
       </c>
       <c r="AV5">
-        <v>346.260009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="AW5">
-        <v>341.510009765625</v>
+        <v>346</v>
       </c>
       <c r="AX5">
-        <v>348.8599853515625</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="AY5">
-        <v>346</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="AZ5">
-        <v>340.4100036621094</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="BA5">
-        <v>348.0299987792969</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="BB5">
-        <v>346.5899963378906</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="BC5">
-        <v>352.3599853515625</v>
+        <v>361.989990234375</v>
       </c>
       <c r="BD5">
-        <v>358.9200134277344</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="BE5">
-        <v>361.989990234375</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="BF5">
-        <v>366.0899963378906</v>
+        <v>370.7200012207031</v>
       </c>
       <c r="BG5">
-        <v>370.6900024414062</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="BH5">
-        <v>370.7200012207031</v>
-      </c>
-      <c r="BI5">
-        <v>382.8500061035156</v>
-      </c>
-    </row>
-    <row r="6" spans="1:61">
+        <v>388.9500122070312</v>
+      </c>
+    </row>
+    <row r="6" spans="1:60">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>262.8602294921875</v>
+        <v>249.7860565185547</v>
       </c>
       <c r="C6">
-        <v>250.1749877929688</v>
+        <v>243.9420471191406</v>
       </c>
       <c r="D6">
-        <v>249.7860565185547</v>
+        <v>242.2467041015625</v>
       </c>
       <c r="E6">
-        <v>243.9420471191406</v>
+        <v>246.6147308349609</v>
       </c>
       <c r="F6">
-        <v>242.2467041015625</v>
+        <v>247.8413848876953</v>
       </c>
       <c r="G6">
-        <v>246.6147308349609</v>
+        <v>245.8368530273438</v>
       </c>
       <c r="H6">
-        <v>247.8413848876953</v>
+        <v>252.8676147460938</v>
       </c>
       <c r="I6">
-        <v>245.8368530273438</v>
+        <v>253.3662414550781</v>
       </c>
       <c r="J6">
-        <v>252.8676147460938</v>
+        <v>258.5121459960938</v>
       </c>
       <c r="K6">
-        <v>253.3662414550781</v>
+        <v>254.9718475341797</v>
       </c>
       <c r="L6">
-        <v>258.5121459960938</v>
+        <v>264.146728515625</v>
       </c>
       <c r="M6">
-        <v>254.9718475341797</v>
+        <v>265.6226806640625</v>
       </c>
       <c r="N6">
-        <v>264.146728515625</v>
+        <v>268.2554626464844</v>
       </c>
       <c r="O6">
-        <v>265.6226806640625</v>
+        <v>265.6027221679688</v>
       </c>
       <c r="P6">
-        <v>268.2554626464844</v>
+        <v>279.9135437011719</v>
       </c>
       <c r="Q6">
-        <v>265.6027221679688</v>
+        <v>282.5263977050781</v>
       </c>
       <c r="R6">
-        <v>279.9135437011719</v>
+        <v>282.9651794433594</v>
       </c>
       <c r="S6">
-        <v>282.5263977050781</v>
+        <v>296.0693359375</v>
       </c>
       <c r="T6">
-        <v>282.9651794433594</v>
+        <v>302.5715026855469</v>
       </c>
       <c r="U6">
-        <v>296.0693359375</v>
+        <v>298.363037109375</v>
       </c>
       <c r="V6">
-        <v>302.5715026855469</v>
+        <v>305.0148315429688</v>
       </c>
       <c r="W6">
-        <v>298.363037109375</v>
+        <v>311.7463989257812</v>
       </c>
       <c r="X6">
-        <v>305.0148315429688</v>
+        <v>314.4490051269531</v>
       </c>
       <c r="Y6">
-        <v>311.7463989257812</v>
+        <v>318.8868408203125</v>
       </c>
       <c r="Z6">
-        <v>314.4490051269531</v>
+        <v>314.9576110839844</v>
       </c>
       <c r="AA6">
-        <v>318.8868408203125</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="AB6">
-        <v>314.9576110839844</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="AC6">
-        <v>311.4172973632812</v>
+        <v>311.4970703125</v>
       </c>
       <c r="AD6">
-        <v>308.3955688476562</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="AE6">
-        <v>311.4970703125</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="AF6">
-        <v>305.2142639160156</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="AG6">
-        <v>307.8769836425781</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="AH6">
-        <v>313.2223510742188</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="AI6">
-        <v>315.6058349609375</v>
+        <v>311.75634765625</v>
       </c>
       <c r="AJ6">
-        <v>306.1915893554688</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="AK6">
-        <v>311.75634765625</v>
+        <v>298.432861328125</v>
       </c>
       <c r="AL6">
-        <v>296.9369506835938</v>
+        <v>297.3857421875</v>
       </c>
       <c r="AM6">
-        <v>298.432861328125</v>
+        <v>319.4453125</v>
       </c>
       <c r="AN6">
-        <v>297.3857421875</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="AO6">
-        <v>319.4453125</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="AP6">
-        <v>335.5013732910156</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="AQ6">
-        <v>347.2990417480469</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="AR6">
-        <v>355.3968811035156</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="AS6">
-        <v>354.4494934082031</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="AT6">
-        <v>357.2019348144531</v>
+        <v>360.75</v>
       </c>
       <c r="AU6">
-        <v>365.2099914550781</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="AV6">
-        <v>360.75</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="AW6">
-        <v>358.2300109863281</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="AX6">
-        <v>360.7200012207031</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="AY6">
-        <v>362.5199890136719</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="AZ6">
-        <v>354.8800048828125</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="BA6">
-        <v>362.2699890136719</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="BB6">
-        <v>363.5400085449219</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="BC6">
-        <v>368.8299865722656</v>
+        <v>383</v>
       </c>
       <c r="BD6">
-        <v>373.3200073242188</v>
+        <v>387</v>
       </c>
       <c r="BE6">
-        <v>383</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="BF6">
-        <v>387</v>
+        <v>388.8999938964844</v>
       </c>
       <c r="BG6">
-        <v>387.7099914550781</v>
+        <v>397.7699890136719</v>
       </c>
       <c r="BH6">
-        <v>388.8999938964844</v>
-      </c>
-      <c r="BI6">
-        <v>397.7699890136719</v>
-      </c>
-    </row>
-    <row r="7" spans="1:61">
+        <v>399.4400024414062</v>
+      </c>
+    </row>
+    <row r="7" spans="1:60">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>56.54000091552734</v>
+        <v>53.66999816894531</v>
       </c>
       <c r="C7">
-        <v>54.45999908447266</v>
+        <v>53.04000091552734</v>
       </c>
       <c r="D7">
-        <v>53.66999816894531</v>
+        <v>51.81999969482422</v>
       </c>
       <c r="E7">
-        <v>53.04000091552734</v>
+        <v>52</v>
       </c>
       <c r="F7">
-        <v>51.81999969482422</v>
+        <v>52.22999954223633</v>
       </c>
       <c r="G7">
-        <v>52</v>
+        <v>51.09000015258789</v>
       </c>
       <c r="H7">
-        <v>52.22999954223633</v>
+        <v>51.20999908447266</v>
       </c>
       <c r="I7">
-        <v>51.09000015258789</v>
+        <v>49.9900016784668</v>
       </c>
       <c r="J7">
-        <v>51.20999908447266</v>
+        <v>49.09000015258789</v>
       </c>
       <c r="K7">
-        <v>49.9900016784668</v>
+        <v>48.56999969482422</v>
       </c>
       <c r="L7">
-        <v>49.09000015258789</v>
+        <v>47.93999862670898</v>
       </c>
       <c r="M7">
-        <v>48.56999969482422</v>
+        <v>48.90999984741211</v>
       </c>
       <c r="N7">
-        <v>47.93999862670898</v>
+        <v>48.81000137329102</v>
       </c>
       <c r="O7">
-        <v>48.90999984741211</v>
+        <v>51.68000030517578</v>
       </c>
       <c r="P7">
-        <v>48.81000137329102</v>
+        <v>53.59000015258789</v>
       </c>
       <c r="Q7">
-        <v>51.68000030517578</v>
+        <v>52.29999923706055</v>
       </c>
       <c r="R7">
-        <v>53.59000015258789</v>
+        <v>52.88999938964844</v>
       </c>
       <c r="S7">
-        <v>52.29999923706055</v>
+        <v>54.81000137329102</v>
       </c>
       <c r="T7">
-        <v>52.88999938964844</v>
+        <v>54.56999969482422</v>
       </c>
       <c r="U7">
-        <v>54.81000137329102</v>
+        <v>53.77000045776367</v>
       </c>
       <c r="V7">
-        <v>54.56999969482422</v>
+        <v>53.65000152587891</v>
       </c>
       <c r="W7">
-        <v>53.77000045776367</v>
+        <v>54.86000061035156</v>
       </c>
       <c r="X7">
-        <v>53.65000152587891</v>
+        <v>55.18999862670898</v>
       </c>
       <c r="Y7">
-        <v>54.86000061035156</v>
+        <v>56.5</v>
       </c>
       <c r="Z7">
-        <v>55.18999862670898</v>
+        <v>57.5</v>
       </c>
       <c r="AA7">
-        <v>56.5</v>
+        <v>57.59999847412109</v>
       </c>
       <c r="AB7">
-        <v>57.5</v>
+        <v>57.29999923706055</v>
       </c>
       <c r="AC7">
-        <v>57.59999847412109</v>
+        <v>54.93000030517578</v>
       </c>
       <c r="AD7">
-        <v>57.29999923706055</v>
+        <v>53.93000030517578</v>
       </c>
       <c r="AE7">
-        <v>54.93000030517578</v>
+        <v>56.02999877929688</v>
       </c>
       <c r="AF7">
-        <v>53.93000030517578</v>
+        <v>55.95000076293945</v>
       </c>
       <c r="AG7">
-        <v>56.02999877929688</v>
+        <v>57.06999969482422</v>
       </c>
       <c r="AH7">
-        <v>55.95000076293945</v>
+        <v>55.47000122070312</v>
       </c>
       <c r="AI7">
-        <v>57.06999969482422</v>
+        <v>55.09000015258789</v>
       </c>
       <c r="AJ7">
-        <v>55.47000122070312</v>
+        <v>53.81000137329102</v>
       </c>
       <c r="AK7">
-        <v>55.09000015258789</v>
+        <v>56.04000091552734</v>
       </c>
       <c r="AL7">
-        <v>53.81000137329102</v>
+        <v>55.90999984741211</v>
       </c>
       <c r="AM7">
-        <v>56.04000091552734</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="AN7">
-        <v>55.90999984741211</v>
+        <v>59.06000137329102</v>
       </c>
       <c r="AO7">
-        <v>58.65000152587891</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="AP7">
-        <v>59.06000137329102</v>
+        <v>57.70000076293945</v>
       </c>
       <c r="AQ7">
-        <v>58.54999923706055</v>
+        <v>58.36000061035156</v>
       </c>
       <c r="AR7">
-        <v>57.70000076293945</v>
+        <v>59.04000091552734</v>
       </c>
       <c r="AS7">
-        <v>58.36000061035156</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="AT7">
-        <v>59.04000091552734</v>
+        <v>60.09000015258789</v>
       </c>
       <c r="AU7">
-        <v>59.79999923706055</v>
+        <v>61.52000045776367</v>
       </c>
       <c r="AV7">
-        <v>60.09000015258789</v>
+        <v>61.29999923706055</v>
       </c>
       <c r="AW7">
-        <v>61.52000045776367</v>
+        <v>60.11000061035156</v>
       </c>
       <c r="AX7">
+        <v>58.40999984741211</v>
+      </c>
+      <c r="AY7">
+        <v>58.61999893188477</v>
+      </c>
+      <c r="AZ7">
+        <v>59.16999816894531</v>
+      </c>
+      <c r="BA7">
+        <v>59.09999847412109</v>
+      </c>
+      <c r="BB7">
+        <v>60.18000030517578</v>
+      </c>
+      <c r="BC7">
+        <v>60.95000076293945</v>
+      </c>
+      <c r="BD7">
+        <v>60.90999984741211</v>
+      </c>
+      <c r="BE7">
+        <v>60.61000061035156</v>
+      </c>
+      <c r="BF7">
+        <v>60.04000091552734</v>
+      </c>
+      <c r="BG7">
+        <v>60.65000152587891</v>
+      </c>
+      <c r="BH7">
         <v>61.29999923706055</v>
       </c>
-      <c r="AY7">
-        <v>60.11000061035156</v>
-      </c>
-      <c r="AZ7">
-        <v>58.40999984741211</v>
-      </c>
-      <c r="BA7">
-        <v>58.61999893188477</v>
-      </c>
-      <c r="BB7">
-        <v>59.16999816894531</v>
-      </c>
-      <c r="BC7">
-        <v>59.09999847412109</v>
-      </c>
-      <c r="BD7">
-        <v>60.18000030517578</v>
-      </c>
-      <c r="BE7">
-        <v>60.95000076293945</v>
-      </c>
-      <c r="BF7">
-        <v>60.90999984741211</v>
-      </c>
-      <c r="BG7">
-        <v>60.61000061035156</v>
-      </c>
-      <c r="BH7">
-        <v>60.04000091552734</v>
-      </c>
-      <c r="BI7">
-        <v>60.65000152587891</v>
-      </c>
-    </row>
-    <row r="8" spans="1:61">
+    </row>
+    <row r="8" spans="1:60">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>178.5025787353516</v>
+        <v>171.0919189453125</v>
       </c>
       <c r="C8">
-        <v>172.3452606201172</v>
+        <v>166.2874145507812</v>
       </c>
       <c r="D8">
-        <v>171.0919189453125</v>
+        <v>165.2628631591797</v>
       </c>
       <c r="E8">
-        <v>166.2874145507812</v>
+        <v>167.5208740234375</v>
       </c>
       <c r="F8">
-        <v>165.2628631591797</v>
+        <v>169.440673828125</v>
       </c>
       <c r="G8">
-        <v>167.5208740234375</v>
+        <v>167.7496643066406</v>
       </c>
       <c r="H8">
-        <v>169.440673828125</v>
+        <v>170.8531799316406</v>
       </c>
       <c r="I8">
-        <v>167.7496643066406</v>
+        <v>170.7437591552734</v>
       </c>
       <c r="J8">
-        <v>170.8531799316406</v>
+        <v>173.131103515625</v>
       </c>
       <c r="K8">
-        <v>170.7437591552734</v>
+        <v>168.1575012207031</v>
       </c>
       <c r="L8">
-        <v>173.131103515625</v>
+        <v>173.5787200927734</v>
       </c>
       <c r="M8">
-        <v>168.1575012207031</v>
+        <v>175.4885864257812</v>
       </c>
       <c r="N8">
-        <v>173.5787200927734</v>
+        <v>176.3937835693359</v>
       </c>
       <c r="O8">
-        <v>175.4885864257812</v>
+        <v>177.8957977294922</v>
       </c>
       <c r="P8">
-        <v>176.3937835693359</v>
+        <v>186.8184509277344</v>
       </c>
       <c r="Q8">
-        <v>177.8957977294922</v>
+        <v>188.8178405761719</v>
       </c>
       <c r="R8">
-        <v>186.8184509277344</v>
+        <v>187.3655395507812</v>
       </c>
       <c r="S8">
-        <v>188.8178405761719</v>
+        <v>197.2431182861328</v>
       </c>
       <c r="T8">
-        <v>187.3655395507812</v>
+        <v>200.3864288330078</v>
       </c>
       <c r="U8">
-        <v>197.2431182861328</v>
+        <v>195.1243743896484</v>
       </c>
       <c r="V8">
-        <v>200.3864288330078</v>
+        <v>200.2571258544922</v>
       </c>
       <c r="W8">
-        <v>195.1243743896484</v>
+        <v>205.7678680419922</v>
       </c>
       <c r="X8">
-        <v>200.2571258544922</v>
+        <v>207.6976318359375</v>
       </c>
       <c r="Y8">
-        <v>205.7678680419922</v>
+        <v>211.1493225097656</v>
       </c>
       <c r="Z8">
-        <v>207.6976318359375</v>
+        <v>210.2938537597656</v>
       </c>
       <c r="AA8">
-        <v>211.1493225097656</v>
+        <v>205.8872375488281</v>
       </c>
       <c r="AB8">
-        <v>210.2938537597656</v>
+        <v>205.6783599853516</v>
       </c>
       <c r="AC8">
-        <v>205.8872375488281</v>
+        <v>206.7228088378906</v>
       </c>
       <c r="AD8">
-        <v>205.6783599853516</v>
+        <v>204.7632141113281</v>
       </c>
       <c r="AE8">
-        <v>206.7228088378906</v>
+        <v>205.7181396484375</v>
       </c>
       <c r="AF8">
-        <v>204.7632141113281</v>
+        <v>209.4881286621094</v>
       </c>
       <c r="AG8">
-        <v>205.7181396484375</v>
+        <v>210.5624237060547</v>
       </c>
       <c r="AH8">
-        <v>209.4881286621094</v>
+        <v>205.1014099121094</v>
       </c>
       <c r="AI8">
-        <v>210.5624237060547</v>
+        <v>204.8029937744141</v>
       </c>
       <c r="AJ8">
-        <v>205.1014099121094</v>
+        <v>201.4806365966797</v>
       </c>
       <c r="AK8">
-        <v>204.8029937744141</v>
+        <v>204.4349517822266</v>
       </c>
       <c r="AL8">
-        <v>201.4806365966797</v>
+        <v>202.8334503173828</v>
       </c>
       <c r="AM8">
-        <v>204.4349517822266</v>
+        <v>214.3821563720703</v>
       </c>
       <c r="AN8">
-        <v>202.8334503173828</v>
+        <v>223.1754760742188</v>
       </c>
       <c r="AO8">
-        <v>214.3821563720703</v>
+        <v>224.3890380859375</v>
       </c>
       <c r="AP8">
-        <v>223.1754760742188</v>
+        <v>231.3819274902344</v>
       </c>
       <c r="AQ8">
-        <v>224.3890380859375</v>
+        <v>232.3766479492188</v>
       </c>
       <c r="AR8">
-        <v>231.3819274902344</v>
+        <v>239.2800140380859</v>
       </c>
       <c r="AS8">
-        <v>232.3766479492188</v>
+        <v>243.4900054931641</v>
       </c>
       <c r="AT8">
-        <v>239.2800140380859</v>
+        <v>242.2899932861328</v>
       </c>
       <c r="AU8">
-        <v>243.4900054931641</v>
+        <v>240</v>
       </c>
       <c r="AV8">
-        <v>242.2899932861328</v>
+        <v>242.8699951171875</v>
       </c>
       <c r="AW8">
-        <v>240</v>
+        <v>241.9600067138672</v>
       </c>
       <c r="AX8">
-        <v>242.8699951171875</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="AY8">
-        <v>241.9600067138672</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="AZ8">
-        <v>236.8999938964844</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="BA8">
-        <v>242.2299957275391</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="BB8">
-        <v>239.8099975585938</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="BC8">
-        <v>244.0099945068359</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="BD8">
-        <v>246.5800018310547</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="BE8">
-        <v>252.0200042724609</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="BF8">
-        <v>256.0899963378906</v>
+        <v>255.0899963378906</v>
       </c>
       <c r="BG8">
-        <v>254.6600036621094</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="BH8">
-        <v>255.0899963378906</v>
-      </c>
-      <c r="BI8">
-        <v>259.1400146484375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:61">
+        <v>260.7799987792969</v>
+      </c>
+    </row>
+    <row r="9" spans="1:60">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>36.76126480102539</v>
+        <v>34.02054977416992</v>
       </c>
       <c r="C9">
-        <v>34.5269889831543</v>
+        <v>33.6928596496582</v>
       </c>
       <c r="D9">
-        <v>34.02054977416992</v>
+        <v>32.79914855957031</v>
       </c>
       <c r="E9">
-        <v>33.6928596496582</v>
+        <v>33.96097183227539</v>
       </c>
       <c r="F9">
-        <v>32.79914855957031</v>
+        <v>33.9808349609375</v>
       </c>
       <c r="G9">
-        <v>33.96097183227539</v>
+        <v>33.09705352783203</v>
       </c>
       <c r="H9">
-        <v>33.9808349609375</v>
+        <v>33.18642044067383</v>
       </c>
       <c r="I9">
-        <v>33.09705352783203</v>
+        <v>32.77928924560547</v>
       </c>
       <c r="J9">
-        <v>33.18642044067383</v>
+        <v>32.72963714599609</v>
       </c>
       <c r="K9">
-        <v>32.77928924560547</v>
+        <v>32.34236526489258</v>
       </c>
       <c r="L9">
-        <v>32.72963714599609</v>
+        <v>31.64725685119629</v>
       </c>
       <c r="M9">
-        <v>32.34236526489258</v>
+        <v>32.13383102416992</v>
       </c>
       <c r="N9">
-        <v>31.64725685119629</v>
+        <v>32.23313140869141</v>
       </c>
       <c r="O9">
-        <v>32.13383102416992</v>
+        <v>33.76237106323242</v>
       </c>
       <c r="P9">
-        <v>32.23313140869141</v>
+        <v>34.81496429443359</v>
       </c>
       <c r="Q9">
-        <v>33.76237106323242</v>
+        <v>33.05733489990234</v>
       </c>
       <c r="R9">
-        <v>34.81496429443359</v>
+        <v>33.20628356933594</v>
       </c>
       <c r="S9">
-        <v>33.05733489990234</v>
+        <v>34.42768478393555</v>
       </c>
       <c r="T9">
-        <v>33.20628356933594</v>
+        <v>34.28866577148438</v>
       </c>
       <c r="U9">
-        <v>34.42768478393555</v>
+        <v>34.03048324584961</v>
       </c>
       <c r="V9">
-        <v>34.28866577148438</v>
+        <v>34.04041290283203</v>
       </c>
       <c r="W9">
-        <v>34.03048324584961</v>
+        <v>34.97384262084961</v>
       </c>
       <c r="X9">
-        <v>34.04041290283203</v>
+        <v>34.59650039672852</v>
       </c>
       <c r="Y9">
-        <v>34.97384262084961</v>
+        <v>35.52000045776367</v>
       </c>
       <c r="Z9">
-        <v>34.59650039672852</v>
+        <v>36.18000030517578</v>
       </c>
       <c r="AA9">
-        <v>35.52000045776367</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="AB9">
-        <v>36.18000030517578</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="AC9">
-        <v>36.41999816894531</v>
+        <v>34.7400016784668</v>
       </c>
       <c r="AD9">
-        <v>36.15000152587891</v>
+        <v>34.93000030517578</v>
       </c>
       <c r="AE9">
-        <v>34.7400016784668</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="AF9">
-        <v>34.93000030517578</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="AG9">
-        <v>36.70000076293945</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="AH9">
-        <v>36.33000183105469</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="AI9">
-        <v>37.31999969482422</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="AJ9">
-        <v>36.86999893188477</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="AK9">
-        <v>35.79999923706055</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="AL9">
-        <v>34.65999984741211</v>
+        <v>37.63000106811523</v>
       </c>
       <c r="AM9">
-        <v>36.52999877929688</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="AN9">
-        <v>37.63000106811523</v>
+        <v>40.61999893188477</v>
       </c>
       <c r="AO9">
-        <v>41.02000045776367</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="AP9">
-        <v>40.61999893188477</v>
+        <v>40</v>
       </c>
       <c r="AQ9">
-        <v>39.97000122070312</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="AR9">
-        <v>40</v>
+        <v>41.58000183105469</v>
       </c>
       <c r="AS9">
-        <v>40.47000122070312</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="AT9">
-        <v>41.58000183105469</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="AU9">
-        <v>42.36999893188477</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="AV9">
-        <v>43.45000076293945</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="AW9">
-        <v>44.38999938964844</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="AX9">
-        <v>43.38999938964844</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="AY9">
-        <v>42.95999908447266</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="AZ9">
-        <v>41.34999847412109</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="BA9">
-        <v>41.18999862670898</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="BB9">
-        <v>42.38000106811523</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="BC9">
-        <v>42.54000091552734</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="BD9">
-        <v>43.15000152587891</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="BE9">
-        <v>44.29999923706055</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="BF9">
-        <v>44.70000076293945</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="BG9">
-        <v>44.18000030517578</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="BH9">
-        <v>42.77000045776367</v>
-      </c>
-      <c r="BI9">
-        <v>43.54999923706055</v>
+        <v>44.84000015258789</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="243">
   <si>
     <t>DELL</t>
   </si>
@@ -237,6 +237,9 @@
     <t>2026-09-10</t>
   </si>
   <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -294,19 +297,43 @@
     <t>проходит</t>
   </si>
   <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
     <t>HPE</t>
   </si>
   <si>
     <t>Hewlett Packard Enterprise</t>
   </si>
   <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
-  </si>
-  <si>
-    <t>Financials</t>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>Centene Corporation</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class C)</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class A)</t>
   </si>
   <si>
     <t>CRM</t>
@@ -315,30 +342,6 @@
     <t>Salesforce</t>
   </si>
   <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class C)</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>CNC</t>
-  </si>
-  <si>
-    <t>Centene Corporation</t>
-  </si>
-  <si>
-    <t>Health Care</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class A)</t>
-  </si>
-  <si>
     <t>TGT</t>
   </si>
   <si>
@@ -354,69 +357,75 @@
     <t>Allstate</t>
   </si>
   <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>Supermicro</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
     <t>INTC</t>
   </si>
   <si>
     <t>Intel</t>
   </si>
   <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
-  </si>
-  <si>
     <t>DLTR</t>
   </si>
   <si>
     <t>Dollar Tree</t>
   </si>
   <si>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
+  </si>
+  <si>
     <t>COF</t>
   </si>
   <si>
     <t>Capital One</t>
   </si>
   <si>
-    <t>HPQ</t>
-  </si>
-  <si>
-    <t>HP Inc.</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>Supermicro</t>
-  </si>
-  <si>
     <t>CVX</t>
   </si>
   <si>
     <t>Chevron Corporation</t>
   </si>
   <si>
+    <t>BIIB</t>
+  </si>
+  <si>
+    <t>Biogen</t>
+  </si>
+  <si>
     <t>NVDA</t>
   </si>
   <si>
@@ -435,12 +444,6 @@
     <t>Zebra Technologies</t>
   </si>
   <si>
-    <t>BIIB</t>
-  </si>
-  <si>
-    <t>Biogen</t>
-  </si>
-  <si>
     <t>MS</t>
   </si>
   <si>
@@ -453,16 +456,37 @@
     <t>Seagate Technology</t>
   </si>
   <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
+  </si>
+  <si>
+    <t>WBD</t>
+  </si>
+  <si>
+    <t>Warner Bros. Discovery</t>
+  </si>
+  <si>
     <t>REGN</t>
   </si>
   <si>
     <t>Regeneron Pharmaceuticals</t>
   </si>
   <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>Newmont</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>Diamondback Energy</t>
   </si>
   <si>
     <t>EOG</t>
@@ -471,31 +495,10 @@
     <t>EOG Resources</t>
   </si>
   <si>
-    <t>WBD</t>
-  </si>
-  <si>
-    <t>Warner Bros. Discovery</t>
-  </si>
-  <si>
-    <t>NEM</t>
-  </si>
-  <si>
-    <t>Newmont</t>
-  </si>
-  <si>
-    <t>Materials</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>Teradyne</t>
-  </si>
-  <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>CF Industries</t>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
   </si>
   <si>
     <t>Факторы и самообучение</t>
@@ -576,7 +579,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-11 00:15 UTC · данные на 2026-09-10 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-12 00:23 UTC · данные на 2026-09-11 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -657,7 +660,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-11 00:15 UTC</t>
+    <t>2026-09-12 00:23 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -1151,9 +1154,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$16</c:f>
+              <c:f>Капитал!$A$5:$A$17</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1189,16 +1192,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2026-09-10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2026-09-11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$16</c:f>
+              <c:f>Капитал!$D$5:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1233,6 +1239,9 @@
                   <c:v>10216.05</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>10216.05</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>10216.05</c:v>
                 </c:pt>
               </c:numCache>
@@ -1258,9 +1267,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$16</c:f>
+              <c:f>Капитал!$A$5:$A$17</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1296,16 +1305,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2026-09-10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2026-09-11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$16</c:f>
+              <c:f>Капитал!$F$5:$F$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1340,6 +1352,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1480,9 +1495,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$16</c:f>
+              <c:f>Капитал!$A$5:$A$17</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1518,16 +1533,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2026-09-10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2026-09-11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$16</c:f>
+              <c:f>Капитал!$D$5:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1562,6 +1580,9 @@
                   <c:v>10216.05</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>10216.05</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>10216.05</c:v>
                 </c:pt>
               </c:numCache>
@@ -1587,9 +1608,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$16</c:f>
+              <c:f>Капитал!$A$5:$A$17</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1625,16 +1646,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2026-09-10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2026-09-11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$16</c:f>
+              <c:f>Капитал!$F$5:$F$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1669,6 +1693,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2164,12 +2191,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2177,13 +2204,13 @@
         <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2202,27 +2229,27 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>4.2551692847167</v>
+        <v>4.061872161674939</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H9" s="7">
         <v>9</v>
@@ -2230,7 +2257,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2259,7 +2286,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -2267,7 +2294,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -2275,23 +2302,23 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C18" s="11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C19" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -2299,55 +2326,55 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C25" s="12">
-        <v>0.1167707519878767</v>
+        <v>0.1121336884360717</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C26" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2356,12 +2383,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -2512,11 +2539,11 @@
         <v>0.18286309065709058</v>
       </c>
       <c r="L5" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N5" s="20">
         <v>2.927623067210654</v>
@@ -2563,11 +2590,11 @@
         <v>0.09758958423901652</v>
       </c>
       <c r="L6" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N6" s="20">
         <v>1.809956883354321</v>
@@ -2614,11 +2641,11 @@
         <v>0.1224393676054864</v>
       </c>
       <c r="L7" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7" s="11">
         <f>MAX(0,21-L7)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N7" s="20">
         <v>1.655247920227722</v>
@@ -2665,11 +2692,11 @@
         <v>0.010656458832162687</v>
       </c>
       <c r="L8" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M8" s="11">
         <f>MAX(0,21-L8)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N8" s="20">
         <v>1.135451734784544</v>
@@ -2716,11 +2743,11 @@
         <v>0.029377395192469312</v>
       </c>
       <c r="L9" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M9" s="11">
         <f>MAX(0,21-L9)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N9" s="20">
         <v>1.098454348098604</v>
@@ -2767,11 +2794,11 @@
         <v>0.020814011776538976</v>
       </c>
       <c r="L10" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10" s="11">
         <f>MAX(0,21-L10)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N10" s="20">
         <v>0.9280120270881818</v>
@@ -2818,11 +2845,11 @@
         <v>-0.0018297215776284946</v>
       </c>
       <c r="L11" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="11">
         <f>MAX(0,21-L11)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N11" s="20">
         <v>0.8840484909760108</v>
@@ -2869,11 +2896,11 @@
         <v>0.012639994356587973</v>
       </c>
       <c r="L12" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12" s="11">
         <f>MAX(0,21-L12)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N12" s="20">
         <v>0.8298272742812407</v>
@@ -2920,11 +2947,11 @@
         <v>-0.02132271831371461</v>
       </c>
       <c r="L13" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" s="11">
         <f>MAX(0,21-L13)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N13" s="20">
         <v>0.7019116395441239</v>
@@ -3242,7 +3269,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3525,6 +3552,25 @@
         <v>9</v>
       </c>
       <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="10">
+        <v>5714.88</v>
+      </c>
+      <c r="C17" s="10">
+        <v>4501.17</v>
+      </c>
+      <c r="D17" s="10">
+        <f>B17+C17</f>
+        <v>10216.05</v>
+      </c>
+      <c r="E17" s="11">
+        <v>9</v>
+      </c>
+      <c r="F17" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3553,12 +3599,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3575,52 +3621,52 @@
         <v>13</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -3637,10 +3683,10 @@
         <v>28</v>
       </c>
       <c r="E5" s="10">
-        <v>1764.170043945312</v>
+        <v>1692.589965820312</v>
       </c>
       <c r="F5" s="17">
-        <v>1.120842573453189</v>
+        <v>1.077571859577547</v>
       </c>
       <c r="G5" s="20">
         <v>-0.5564495730839067</v>
@@ -3652,16 +3698,16 @@
         <v>4.120745224686987</v>
       </c>
       <c r="J5" s="20">
-        <v>2.168748407851256</v>
+        <v>1.978883242244176</v>
       </c>
       <c r="K5" s="20">
         <v>0.08036885848301029</v>
       </c>
       <c r="L5" s="20">
-        <v>-3.427259213116233</v>
+        <v>-3.363908912256145</v>
       </c>
       <c r="M5" s="20">
-        <v>0.3125237071852279</v>
+        <v>0.4361214291211829</v>
       </c>
       <c r="N5" s="20">
         <v>23.583628</v>
@@ -3676,13 +3722,13 @@
         <v>3.716</v>
       </c>
       <c r="R5" s="12">
-        <v>1.850538871510885</v>
+        <v>1.582411523327372</v>
       </c>
       <c r="S5" s="11">
-        <v>62.24144944940989</v>
+        <v>57.33833353921393</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -3699,10 +3745,10 @@
         <v>28</v>
       </c>
       <c r="E6" s="10">
-        <v>1027.77001953125</v>
+        <v>977.4099731445312</v>
       </c>
       <c r="F6" s="17">
-        <v>1.115499075608092</v>
+        <v>1.07542624134454</v>
       </c>
       <c r="G6" s="20">
         <v>-0.5381709417593455</v>
@@ -3714,16 +3760,16 @@
         <v>3.983916492932042</v>
       </c>
       <c r="J6" s="20">
-        <v>2.220361319791275</v>
+        <v>2.026214809160198</v>
       </c>
       <c r="K6" s="20">
         <v>0.4757611069296119</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.427259213116233</v>
+        <v>-3.363908912256145</v>
       </c>
       <c r="M6" s="20">
-        <v>0.07705469053124858</v>
+        <v>0.2566809514583271</v>
       </c>
       <c r="N6" s="20">
         <v>22.98937</v>
@@ -3738,13 +3784,13 @@
         <v>3.457</v>
       </c>
       <c r="R6" s="12">
-        <v>1.551065327195762</v>
+        <v>1.335787722134074</v>
       </c>
       <c r="S6" s="11">
-        <v>60.61458265758949</v>
+        <v>53.28963722052742</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -3761,10 +3807,10 @@
         <v>38</v>
       </c>
       <c r="E7" s="10">
-        <v>388.9500122070312</v>
+        <v>385.4299926757812</v>
       </c>
       <c r="F7" s="17">
-        <v>1.046639027268738</v>
+        <v>1.006994826736307</v>
       </c>
       <c r="G7" s="20">
         <v>0.7163099250210818</v>
@@ -3776,16 +3822,16 @@
         <v>2.885035079678366</v>
       </c>
       <c r="J7" s="20">
-        <v>2.31067718366916</v>
+        <v>2.181551024986625</v>
       </c>
       <c r="K7" s="20">
         <v>0.602059804282177</v>
       </c>
       <c r="L7" s="20">
-        <v>0.1228096645160992</v>
+        <v>0.2049184996151264</v>
       </c>
       <c r="M7" s="20">
-        <v>-0.4335431293870549</v>
+        <v>-0.5064541673072035</v>
       </c>
       <c r="N7" s="20">
         <v>15.453106</v>
@@ -3800,13 +3846,13 @@
         <v>0.517</v>
       </c>
       <c r="R7" s="12">
-        <v>0.8077054083523185</v>
+        <v>0.6825702201096382</v>
       </c>
       <c r="S7" s="11">
-        <v>80.98950727590281</v>
+        <v>77.09530909515649</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -3823,10 +3869,10 @@
         <v>38</v>
       </c>
       <c r="E8" s="10">
-        <v>399.4400024414062</v>
+        <v>392.4200134277344</v>
       </c>
       <c r="F8" s="17">
-        <v>1.015793610975163</v>
+        <v>0.9735186611576939</v>
       </c>
       <c r="G8" s="20">
         <v>0.704035078477925</v>
@@ -3838,16 +3884,16 @@
         <v>2.454207309239585</v>
       </c>
       <c r="J8" s="20">
-        <v>2.26147949632816</v>
+        <v>2.145482490497324</v>
       </c>
       <c r="K8" s="20">
         <v>0.7690833877198547</v>
       </c>
       <c r="L8" s="20">
-        <v>0.1743121397014286</v>
+        <v>0.2617953208038214</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.5705488614589164</v>
+        <v>-0.7296093481384331</v>
       </c>
       <c r="N8" s="20">
         <v>13.475398</v>
@@ -3862,13 +3908,13 @@
         <v>0.537</v>
       </c>
       <c r="R8" s="12">
-        <v>0.8680591899960282</v>
+        <v>0.7420669571958816</v>
       </c>
       <c r="S8" s="11">
-        <v>81.29948564745813</v>
+        <v>73.4171777105645</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -3885,10 +3931,10 @@
         <v>28</v>
       </c>
       <c r="E9" s="10">
-        <v>535.25</v>
+        <v>506.6199951171875</v>
       </c>
       <c r="F9" s="17">
-        <v>0.9950466899717794</v>
+        <v>0.9430482834980047</v>
       </c>
       <c r="G9" s="20">
         <v>-0.2096896716004668</v>
@@ -3900,16 +3946,16 @@
         <v>2.195812652927404</v>
       </c>
       <c r="J9" s="20">
-        <v>2.994607845226451</v>
+        <v>2.783137554741796</v>
       </c>
       <c r="K9" s="20">
         <v>1.596984236488098</v>
       </c>
       <c r="L9" s="20">
-        <v>-2.555513619951289</v>
+        <v>-2.655330713570517</v>
       </c>
       <c r="M9" s="20">
-        <v>0.1484834754428668</v>
+        <v>0.366379804052562</v>
       </c>
       <c r="N9" s="20">
         <v>30.490984</v>
@@ -3924,13 +3970,13 @@
         <v>0.577</v>
       </c>
       <c r="R9" s="12">
-        <v>2.739870364202472</v>
+        <v>2.454076910312915</v>
       </c>
       <c r="S9" s="11">
-        <v>65.29337644585388</v>
+        <v>57.67852956493698</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -3938,61 +3984,61 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="E10" s="10">
-        <v>260.7799987792969</v>
+        <v>367.5599975585938</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8810241045193192</v>
+        <v>0.8512467115675388</v>
       </c>
       <c r="G10" s="20">
-        <v>0.4937473502003348</v>
+        <v>1.215230467965422</v>
       </c>
       <c r="H10" s="20">
-        <v>-0.7878254537509429</v>
+        <v>-0.1214453608752054</v>
       </c>
       <c r="I10" s="20">
-        <v>2.423226908404409</v>
+        <v>-0.3758707799348074</v>
       </c>
       <c r="J10" s="20">
-        <v>2.09005952681419</v>
+        <v>0.7132266228367771</v>
       </c>
       <c r="K10" s="20">
-        <v>0.6850560911138626</v>
+        <v>3.812624241473097</v>
       </c>
       <c r="L10" s="20">
-        <v>0.3950400553153533</v>
+        <v>0.587734623369246</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.7131003631734092</v>
+        <v>-0.2152926270335399</v>
       </c>
       <c r="N10" s="20">
-        <v>14.559931</v>
+        <v>9.931433999999999</v>
       </c>
       <c r="O10" s="20">
-        <v>3.2307048</v>
+        <v>2.3262038</v>
       </c>
       <c r="P10" s="12">
-        <v>0.23452999</v>
+        <v>0.26511</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.531</v>
+        <v>0.003</v>
       </c>
       <c r="R10" s="12">
-        <v>0.6250303198976213</v>
+        <v>0.2370026307937931</v>
       </c>
       <c r="S10" s="11">
-        <v>78.03424497368225</v>
+        <v>51.59588039343553</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -4000,61 +4046,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="10">
+        <v>258.510009765625</v>
+      </c>
+      <c r="F11" s="17">
+        <v>0.8478278064235496</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0.4937473502003348</v>
+      </c>
+      <c r="H11" s="20">
+        <v>-0.7878254537509429</v>
+      </c>
+      <c r="I11" s="20">
+        <v>2.423226908404409</v>
+      </c>
+      <c r="J11" s="20">
+        <v>1.996843114788605</v>
+      </c>
+      <c r="K11" s="20">
+        <v>0.6850560911138626</v>
+      </c>
+      <c r="L11" s="20">
+        <v>0.4509144355434481</v>
+      </c>
+      <c r="M11" s="20">
+        <v>-0.8203983294456569</v>
+      </c>
+      <c r="N11" s="20">
+        <v>14.559931</v>
+      </c>
+      <c r="O11" s="20">
+        <v>3.2307048</v>
+      </c>
+      <c r="P11" s="12">
+        <v>0.23452999</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0.531</v>
+      </c>
+      <c r="R11" s="12">
+        <v>0.54435881948525</v>
+      </c>
+      <c r="S11" s="11">
+        <v>74.01948836808964</v>
+      </c>
+      <c r="T11" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="10">
-        <v>58.90000152587891</v>
-      </c>
-      <c r="F11" s="17">
-        <v>0.8777991100892987</v>
-      </c>
-      <c r="G11" s="20">
-        <v>0.5218225520995097</v>
-      </c>
-      <c r="H11" s="20">
-        <v>-0.5332485103967138</v>
-      </c>
-      <c r="I11" s="20">
-        <v>2.225163086097977</v>
-      </c>
-      <c r="J11" s="20">
-        <v>2.426929707162234</v>
-      </c>
-      <c r="K11" s="20">
-        <v>0.3221406505579205</v>
-      </c>
-      <c r="L11" s="20">
-        <v>-1.274961210348846</v>
-      </c>
-      <c r="M11" s="20">
-        <v>-0.544545172870331</v>
-      </c>
-      <c r="N11" s="20">
-        <v>26.804123</v>
-      </c>
-      <c r="O11" s="20">
-        <v>2.7206612</v>
-      </c>
-      <c r="P11" s="12">
-        <v>0.10936</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>0.337</v>
-      </c>
-      <c r="R11" s="12">
-        <v>1.817688482853931</v>
-      </c>
-      <c r="S11" s="11">
-        <v>62.79336551457337</v>
-      </c>
-      <c r="T11" s="9" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -4062,61 +4108,61 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="E12" s="10">
-        <v>366.8500061035156</v>
+        <v>55.22000122070312</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8411707892541855</v>
+        <v>0.8105270670347311</v>
       </c>
       <c r="G12" s="20">
-        <v>1.215230467965422</v>
+        <v>0.5218225520995097</v>
       </c>
       <c r="H12" s="20">
-        <v>-0.1214453608752054</v>
+        <v>-0.5332485103967138</v>
       </c>
       <c r="I12" s="20">
-        <v>-0.3758707799348074</v>
+        <v>2.225163086097977</v>
       </c>
       <c r="J12" s="20">
-        <v>0.654078326784571</v>
+        <v>2.117528392719588</v>
       </c>
       <c r="K12" s="20">
-        <v>3.812624241473097</v>
+        <v>0.3221406505579205</v>
       </c>
       <c r="L12" s="20">
-        <v>0.5937263112206973</v>
+        <v>-1.406092294593693</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.1239293116432705</v>
+        <v>-0.1268424687088688</v>
       </c>
       <c r="N12" s="20">
-        <v>9.931433999999999</v>
+        <v>26.804123</v>
       </c>
       <c r="O12" s="20">
-        <v>2.3262038</v>
+        <v>2.7206612</v>
       </c>
       <c r="P12" s="12">
-        <v>0.26511</v>
+        <v>0.10936</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.003</v>
+        <v>0.337</v>
       </c>
       <c r="R12" s="12">
-        <v>0.2180388374009978</v>
+        <v>1.600964177069274</v>
       </c>
       <c r="S12" s="11">
-        <v>49.53326300808831</v>
+        <v>53.9517599017061</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -4124,61 +4170,61 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="E13" s="10">
-        <v>244.1600036621094</v>
+        <v>65.40000152587891</v>
       </c>
       <c r="F13" s="17">
-        <v>0.8077049521372179</v>
+        <v>0.7994794227521653</v>
       </c>
       <c r="G13" s="20">
-        <v>0.313884107527872</v>
+        <v>1.296202382232963</v>
       </c>
       <c r="H13" s="20">
-        <v>0.5379536582452412</v>
+        <v>-1.353261681376673</v>
       </c>
       <c r="I13" s="20">
-        <v>0.202940183485447</v>
+        <v>-0.5780959126470824</v>
       </c>
       <c r="J13" s="20">
-        <v>1.153977630851056</v>
+        <v>1.151217907124544</v>
       </c>
       <c r="K13" s="20">
-        <v>3.515693426472779</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L13" s="20">
-        <v>-1.58034990935587</v>
+        <v>-0.005066038726363255</v>
       </c>
       <c r="M13" s="20">
-        <v>-0.355203709453508</v>
+        <v>-0.1023783909747167</v>
       </c>
       <c r="N13" s="20">
-        <v>23.76077</v>
+        <v>12.6192465</v>
       </c>
       <c r="O13" s="20">
-        <v>5.559058</v>
+        <v>1.4678257</v>
       </c>
       <c r="P13" s="12">
-        <v>0.19381</v>
+        <v>-0.20358999</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.108</v>
+        <v>0.046</v>
       </c>
       <c r="R13" s="12">
-        <v>0.2590548364562497</v>
+        <v>0.8237590745327581</v>
       </c>
       <c r="S13" s="11">
-        <v>63.57276604587708</v>
+        <v>50.25786227342584</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -4186,19 +4232,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E14" s="10">
-        <v>328.3800048828125</v>
+        <v>330.3900146484375</v>
       </c>
       <c r="F14" s="17">
-        <v>0.776423257523575</v>
+        <v>0.7825314459518935</v>
       </c>
       <c r="G14" s="20">
         <v>-0.3654991602347105</v>
@@ -4210,16 +4256,16 @@
         <v>1.40880022334584</v>
       </c>
       <c r="J14" s="20">
-        <v>-0.2630866424801945</v>
+        <v>-0.2134147967621131</v>
       </c>
       <c r="K14" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L14" s="20">
-        <v>0.07410053957684902</v>
+        <v>0.08421550857662656</v>
       </c>
       <c r="M14" s="20">
-        <v>0.4749531093146364</v>
+        <v>0.35744981647598</v>
       </c>
       <c r="N14" s="20">
         <v>16.83283</v>
@@ -4234,13 +4280,13 @@
         <v>0.242</v>
       </c>
       <c r="R14" s="12">
-        <v>0.07122451645171202</v>
+        <v>0.07257465690147535</v>
       </c>
       <c r="S14" s="11">
-        <v>38.97142949780758</v>
+        <v>41.12439950306189</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -4248,61 +4294,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="E15" s="10">
-        <v>64.05999755859375</v>
+        <v>332.6000061035156</v>
       </c>
       <c r="F15" s="17">
-        <v>0.7729869712502148</v>
+        <v>0.7775729467290746</v>
       </c>
       <c r="G15" s="20">
-        <v>1.296202382232963</v>
+        <v>-0.3753606373785415</v>
       </c>
       <c r="H15" s="20">
-        <v>-1.353261681376673</v>
+        <v>1.463709249725696</v>
       </c>
       <c r="I15" s="20">
-        <v>-0.5780959126470824</v>
+        <v>1.40880022334584</v>
       </c>
       <c r="J15" s="20">
-        <v>0.992508764277121</v>
+        <v>-0.2073651829989353</v>
       </c>
       <c r="K15" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L15" s="20">
-        <v>-0.002816707404061112</v>
+        <v>0.06388073426508938</v>
       </c>
       <c r="M15" s="20">
-        <v>0.1599382524370093</v>
+        <v>0.3102219288861003</v>
       </c>
       <c r="N15" s="20">
-        <v>12.6192465</v>
+        <v>16.97392</v>
       </c>
       <c r="O15" s="20">
-        <v>1.4678257</v>
+        <v>6.650031</v>
       </c>
       <c r="P15" s="12">
-        <v>-0.20358999</v>
+        <v>0.48676</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.046</v>
+        <v>0.242</v>
       </c>
       <c r="R15" s="12">
-        <v>0.7598899690443617</v>
+        <v>0.07875788754769641</v>
       </c>
       <c r="S15" s="11">
-        <v>45.65142549028698</v>
+        <v>41.4023421762556</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -4310,61 +4356,61 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="E16" s="10">
-        <v>330.6499938964844</v>
+        <v>243</v>
       </c>
       <c r="F16" s="17">
-        <v>0.7727017842057998</v>
+        <v>0.7656532278637759</v>
       </c>
       <c r="G16" s="20">
-        <v>-0.3753606373785415</v>
+        <v>0.313884107527872</v>
       </c>
       <c r="H16" s="20">
-        <v>1.463709249725696</v>
+        <v>0.5379536582452412</v>
       </c>
       <c r="I16" s="20">
-        <v>1.40880022334584</v>
+        <v>0.202940183485447</v>
       </c>
       <c r="J16" s="20">
-        <v>-0.2513829526136259</v>
+        <v>1.122373627001501</v>
       </c>
       <c r="K16" s="20">
-        <v>4.196860964161699</v>
+        <v>3.515693426472779</v>
       </c>
       <c r="L16" s="20">
-        <v>0.05038972406194137</v>
+        <v>-1.617029992608099</v>
       </c>
       <c r="M16" s="20">
-        <v>0.4245172910526159</v>
+        <v>-0.7348251859965287</v>
       </c>
       <c r="N16" s="20">
-        <v>16.97392</v>
+        <v>23.76077</v>
       </c>
       <c r="O16" s="20">
-        <v>6.650031</v>
+        <v>5.559058</v>
       </c>
       <c r="P16" s="12">
-        <v>0.48676</v>
+        <v>0.19381</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.242</v>
+        <v>0.108</v>
       </c>
       <c r="R16" s="12">
-        <v>0.07823132365810959</v>
+        <v>0.2581078952328841</v>
       </c>
       <c r="S16" s="11">
-        <v>39.47425744398156</v>
+        <v>62.64341988345478</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -4381,10 +4427,10 @@
         <v>38</v>
       </c>
       <c r="E17" s="10">
-        <v>61.29999923706055</v>
+        <v>61.15999984741211</v>
       </c>
       <c r="F17" s="17">
-        <v>0.7567677486488729</v>
+        <v>0.7578353526793128</v>
       </c>
       <c r="G17" s="20">
         <v>0.6321397772136792</v>
@@ -4396,16 +4442,16 @@
         <v>2.930171312463986</v>
       </c>
       <c r="J17" s="20">
-        <v>0.6138314029540464</v>
+        <v>0.6183469032745889</v>
       </c>
       <c r="K17" s="20">
         <v>0.8675448211661402</v>
       </c>
       <c r="L17" s="20">
-        <v>0.2788934682129006</v>
+        <v>0.3307525350328995</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.6688681914724106</v>
+        <v>-0.7113505674089463</v>
       </c>
       <c r="N17" s="20">
         <v>17.710915</v>
@@ -4420,13 +4466,13 @@
         <v>0.534</v>
       </c>
       <c r="R17" s="12">
-        <v>0.1593212354173363</v>
+        <v>0.1105511428141968</v>
       </c>
       <c r="S17" s="11">
-        <v>61.97096717259578</v>
+        <v>62.52748223477706</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4434,19 +4480,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E18" s="10">
-        <v>157.5200042724609</v>
+        <v>155.7299957275391</v>
       </c>
       <c r="F18" s="17">
-        <v>0.7014638181956935</v>
+        <v>0.6863634024885488</v>
       </c>
       <c r="G18" s="20">
         <v>0.4941985872113094</v>
@@ -4458,16 +4504,16 @@
         <v>-0.03241763381358259</v>
       </c>
       <c r="J18" s="20">
-        <v>1.14150588608593</v>
+        <v>1.098260189864575</v>
       </c>
       <c r="K18" s="20">
         <v>3.282169712592323</v>
       </c>
       <c r="L18" s="20">
-        <v>0.2266254037186517</v>
+        <v>0.2199227755101482</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.560698767229431</v>
+        <v>-0.5822556315822796</v>
       </c>
       <c r="N18" s="20">
         <v>17.05809</v>
@@ -4482,13 +4528,13 @@
         <v>0.053</v>
       </c>
       <c r="R18" s="12">
-        <v>0.3270559152646901</v>
+        <v>0.3336246875885505</v>
       </c>
       <c r="S18" s="11">
-        <v>50.82563704518401</v>
+        <v>48.08515326507958</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4496,19 +4542,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="10">
-        <v>253.5800018310547</v>
+        <v>251.7899932861328</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6636989313318215</v>
+        <v>0.6465773067017716</v>
       </c>
       <c r="G19" s="20">
         <v>1.286238812250283</v>
@@ -4520,16 +4566,16 @@
         <v>-0.05063264711205382</v>
       </c>
       <c r="J19" s="20">
-        <v>0.5247038416069513</v>
+        <v>0.4589634439808659</v>
       </c>
       <c r="K19" s="20">
         <v>1.849066126306075</v>
       </c>
       <c r="L19" s="20">
-        <v>0.5167665941688258</v>
+        <v>0.5052285191633039</v>
       </c>
       <c r="M19" s="20">
-        <v>0.00596489622291628</v>
+        <v>0.0471246356992561</v>
       </c>
       <c r="N19" s="20">
         <v>5.1976376</v>
@@ -4544,13 +4590,13 @@
         <v>0.118</v>
       </c>
       <c r="R19" s="12">
-        <v>0.2336230905925007</v>
+        <v>0.2362949964442482</v>
       </c>
       <c r="S19" s="11">
-        <v>45.70346675177978</v>
+        <v>43.87267136749018</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -4558,61 +4604,61 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="E20" s="10">
-        <v>106.2399978637695</v>
+        <v>251.8899993896484</v>
       </c>
       <c r="F20" s="17">
-        <v>0.6571105582429381</v>
+        <v>0.6379653045505593</v>
       </c>
       <c r="G20" s="20">
-        <v>-0.6233680543607623</v>
+        <v>-0.04482148267622166</v>
       </c>
       <c r="H20" s="20">
-        <v>-1.136990927851701</v>
+        <v>0.1590141648378586</v>
       </c>
       <c r="I20" s="20">
-        <v>0.5264142543422116</v>
+        <v>1.035672297744961</v>
       </c>
       <c r="J20" s="20">
-        <v>1.745304736953654</v>
+        <v>0.1445964188745298</v>
       </c>
       <c r="K20" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L20" s="20">
-        <v>-2.480147806266792</v>
+        <v>-0.4451342208450181</v>
       </c>
       <c r="M20" s="20">
-        <v>0.2523507830054219</v>
+        <v>-0.04088141034170017</v>
       </c>
       <c r="N20" s="20">
-        <v>46.910885</v>
+        <v>20.797264</v>
       </c>
       <c r="O20" s="20">
-        <v>5.5187516</v>
+        <v>5.0533667</v>
       </c>
       <c r="P20" s="12">
-        <v>-0.10715</v>
+        <v>0.30558002</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.254</v>
+        <v>0.196</v>
       </c>
       <c r="R20" s="12">
-        <v>1.271056020437253</v>
+        <v>0.184528599197918</v>
       </c>
       <c r="S20" s="11">
-        <v>63.36095147527727</v>
+        <v>43.62023798476002</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -4620,61 +4666,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="E21" s="10">
-        <v>252.3999938964844</v>
+        <v>183.6000061035156</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6258177828079802</v>
+        <v>0.597982769112813</v>
       </c>
       <c r="G21" s="20">
-        <v>-0.04482148267622166</v>
+        <v>-0.3904668641526476</v>
       </c>
       <c r="H21" s="20">
-        <v>0.1590141648378586</v>
+        <v>1.359179679828218</v>
       </c>
       <c r="I21" s="20">
-        <v>1.035672297744961</v>
+        <v>0.4411015820383316</v>
       </c>
       <c r="J21" s="20">
-        <v>0.1070953977161724</v>
+        <v>1.309946788731182</v>
       </c>
       <c r="K21" s="20">
-        <v>4.196860964161699</v>
+        <v>0.4834936802369117</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.4512688404540941</v>
+        <v>-0.1631853772767407</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.04749563807329264</v>
+        <v>-0.4315532240904785</v>
       </c>
       <c r="N21" s="20">
-        <v>20.797264</v>
+        <v>26.250353</v>
       </c>
       <c r="O21" s="20">
-        <v>5.0533667</v>
+        <v>26.924416</v>
       </c>
       <c r="P21" s="12">
-        <v>0.30558002</v>
+        <v>1.14818</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.196</v>
+        <v>0.299</v>
       </c>
       <c r="R21" s="12">
-        <v>0.177623252648681</v>
+        <v>0.8969145919344779</v>
       </c>
       <c r="S21" s="11">
-        <v>44.06238001461678</v>
+        <v>46.78070143766169</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -4682,61 +4728,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="E22" s="10">
-        <v>126.0100021362305</v>
+        <v>37.38000106811523</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6140882295887513</v>
+        <v>0.5972201702708791</v>
       </c>
       <c r="G22" s="20">
-        <v>0.3314207580374121</v>
+        <v>0.09785741135882757</v>
       </c>
       <c r="H22" s="20">
-        <v>0.5050654897521694</v>
+        <v>-0.81219220040201</v>
       </c>
       <c r="I22" s="20">
-        <v>0.5229426848176244</v>
+        <v>3.920900829953943</v>
       </c>
       <c r="J22" s="20">
-        <v>0.874763610159063</v>
+        <v>0.5170949910073814</v>
       </c>
       <c r="K22" s="20">
-        <v>1.638740132347517</v>
+        <v>3.370836553182694</v>
       </c>
       <c r="L22" s="20">
-        <v>0.008712019588152516</v>
+        <v>-3.363908912256145</v>
       </c>
       <c r="M22" s="20">
-        <v>-0.4784109225600325</v>
+        <v>-0.5040980456693946</v>
       </c>
       <c r="N22" s="20">
-        <v>16.146498</v>
+        <v>12.144172</v>
       </c>
       <c r="O22" s="20">
-        <v>4.015142</v>
+        <v>2.3688147</v>
       </c>
       <c r="P22" s="12">
-        <v>0.30667</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.377</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R22" s="12">
-        <v>0.3123308325519467</v>
+        <v>0.175841459314257</v>
       </c>
       <c r="S22" s="11">
-        <v>54.09585711905316</v>
+        <v>53.79072920878677</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -4744,61 +4790,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="E23" s="10">
-        <v>44.84000015258789</v>
+        <v>123.2799987792969</v>
       </c>
       <c r="F23" s="17">
-        <v>0.6001422538416877</v>
+        <v>0.5956593700845443</v>
       </c>
       <c r="G23" s="20">
-        <v>1.1788603618118</v>
+        <v>0.3314207580374121</v>
       </c>
       <c r="H23" s="20">
-        <v>0.561859549662265</v>
+        <v>0.5050654897521694</v>
       </c>
       <c r="I23" s="20">
-        <v>-0.2890980177519417</v>
+        <v>0.5229426848176244</v>
       </c>
       <c r="J23" s="20">
-        <v>1.630784367338348</v>
+        <v>0.7360219960977846</v>
       </c>
       <c r="K23" s="20">
-        <v>-0.5748378530888681</v>
+        <v>1.638740132347517</v>
       </c>
       <c r="L23" s="20">
-        <v>-0.3670883722363629</v>
+        <v>0.122268405188472</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.8908725368982913</v>
+        <v>-0.2736579028330646</v>
       </c>
       <c r="N23" s="20">
-        <v>9.023208</v>
+        <v>16.146498</v>
       </c>
       <c r="O23" s="20">
-        <v>2.1361504</v>
+        <v>4.015142</v>
       </c>
       <c r="P23" s="12">
-        <v>0.26659</v>
+        <v>0.30667</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.092</v>
+        <v>0.377</v>
       </c>
       <c r="R23" s="12">
-        <v>0.4285935480326837</v>
+        <v>0.3023451723005115</v>
       </c>
       <c r="S23" s="11">
-        <v>64.66680555611237</v>
+        <v>48.27117415020488</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -4806,61 +4852,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E24" s="10">
-        <v>184.7400054931641</v>
+        <v>44.52999877929688</v>
       </c>
       <c r="F24" s="17">
-        <v>0.5815623270891278</v>
+        <v>0.5891824160379656</v>
       </c>
       <c r="G24" s="20">
-        <v>-0.3904668641526476</v>
+        <v>1.1788603618118</v>
       </c>
       <c r="H24" s="20">
-        <v>1.359179679828218</v>
+        <v>0.561859549662265</v>
       </c>
       <c r="I24" s="20">
-        <v>0.4411015820383316</v>
+        <v>-0.2890980177519417</v>
       </c>
       <c r="J24" s="20">
-        <v>1.280062662953853</v>
+        <v>1.556548249117293</v>
       </c>
       <c r="K24" s="20">
-        <v>0.4834936802369117</v>
+        <v>-0.5748378530888681</v>
       </c>
       <c r="L24" s="20">
-        <v>-0.1433429477102688</v>
+        <v>-0.2550632246701101</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.5396250998964101</v>
+        <v>-0.8335039267905485</v>
       </c>
       <c r="N24" s="20">
-        <v>26.250353</v>
+        <v>9.023208</v>
       </c>
       <c r="O24" s="20">
-        <v>26.924416</v>
+        <v>2.1361504</v>
       </c>
       <c r="P24" s="12">
-        <v>1.14818</v>
+        <v>0.26659</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.299</v>
+        <v>0.092</v>
       </c>
       <c r="R24" s="12">
-        <v>0.9218887880887581</v>
+        <v>0.3692317924155499</v>
       </c>
       <c r="S24" s="11">
-        <v>48.03423931692689</v>
+        <v>62.93263978486159</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -4868,19 +4914,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E25" s="10">
-        <v>1028.780029296875</v>
+        <v>1019.77001953125</v>
       </c>
       <c r="F25" s="17">
-        <v>0.5781468918913982</v>
+        <v>0.5832667773197587</v>
       </c>
       <c r="G25" s="20">
         <v>0.3667190394925228</v>
@@ -4892,16 +4938,16 @@
         <v>0.9154597556552251</v>
       </c>
       <c r="J25" s="20">
-        <v>0.2346785381735309</v>
+        <v>0.2347481862548212</v>
       </c>
       <c r="K25" s="20">
         <v>1.655236288736424</v>
       </c>
       <c r="L25" s="20">
-        <v>0.1296667801823609</v>
+        <v>0.1202979468739675</v>
       </c>
       <c r="M25" s="20">
-        <v>0.1511010797959585</v>
+        <v>0.2218650923269215</v>
       </c>
       <c r="N25" s="20">
         <v>16.02546</v>
@@ -4916,13 +4962,13 @@
         <v>0.425</v>
       </c>
       <c r="R25" s="12">
-        <v>0.2453374831943853</v>
+        <v>0.2494911482568543</v>
       </c>
       <c r="S25" s="11">
-        <v>49.20890049969636</v>
+        <v>46.68136447342079</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -4930,61 +4976,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="E26" s="10">
-        <v>118.3899993896484</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="F26" s="17">
-        <v>0.5397610571690064</v>
+        <v>0.5710693118975338</v>
       </c>
       <c r="G26" s="20">
-        <v>0.3599925540636538</v>
+        <v>-0.6233680543607623</v>
       </c>
       <c r="H26" s="20">
-        <v>-0.1244310120248844</v>
+        <v>-1.136990927851701</v>
       </c>
       <c r="I26" s="20">
-        <v>0.4821804333312243</v>
+        <v>0.5264142543422116</v>
       </c>
       <c r="J26" s="20">
-        <v>-0.1810993972280628</v>
+        <v>1.389633254140621</v>
       </c>
       <c r="K26" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L26" s="20">
-        <v>0.01223109408635147</v>
+        <v>-2.568652042622646</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.04217557684698181</v>
+        <v>0.5769814415036301</v>
       </c>
       <c r="N26" s="20">
-        <v>16.105392</v>
+        <v>46.910885</v>
       </c>
       <c r="O26" s="20">
-        <v>7.2471595</v>
+        <v>5.5187516</v>
       </c>
       <c r="P26" s="12">
-        <v>0.46032003</v>
+        <v>-0.10715</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.07000000000000001</v>
+        <v>0.254</v>
       </c>
       <c r="R26" s="12">
-        <v>0.01343947696392411</v>
+        <v>1.090871209919739</v>
       </c>
       <c r="S26" s="11">
-        <v>35.58604054397024</v>
+        <v>54.79736469452016</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -4992,61 +5038,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E27" s="10">
-        <v>210.8600006103516</v>
+        <v>118.6600036621094</v>
       </c>
       <c r="F27" s="17">
-        <v>0.5326840879288903</v>
+        <v>0.5499077657718956</v>
       </c>
       <c r="G27" s="20">
-        <v>0.5809437263948974</v>
+        <v>0.3599925540636538</v>
       </c>
       <c r="H27" s="20">
-        <v>-0.6585101921976751</v>
+        <v>-0.1244310120248844</v>
       </c>
       <c r="I27" s="20">
-        <v>4.120745224686987</v>
+        <v>0.4821804333312243</v>
       </c>
       <c r="J27" s="20">
-        <v>0.07339711551298615</v>
+        <v>-0.1039856743641069</v>
       </c>
       <c r="K27" s="20">
-        <v>0.5994822798464103</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L27" s="20">
-        <v>0.4787354843618977</v>
+        <v>0.001507966901014602</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.01599764795551081</v>
+        <v>-0.196475834661698</v>
       </c>
       <c r="N27" s="20">
-        <v>12.092511</v>
+        <v>16.105392</v>
       </c>
       <c r="O27" s="20">
-        <v>1.3082409</v>
+        <v>7.2471595</v>
       </c>
       <c r="P27" s="12">
-        <v>0.09031</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q27" s="12">
-        <v>11.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R27" s="12">
-        <v>0.1495263781168987</v>
+        <v>0.04777045176255523</v>
       </c>
       <c r="S27" s="11">
-        <v>44.23106566160668</v>
+        <v>36.09586750923285</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -5054,19 +5100,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="10">
-        <v>32.38999938964844</v>
+        <v>32.72999954223633</v>
       </c>
       <c r="F28" s="17">
-        <v>0.521001566246862</v>
+        <v>0.5345681018375826</v>
       </c>
       <c r="G28" s="20">
         <v>1.115176779328165</v>
@@ -5078,16 +5124,16 @@
         <v>-0.3840221445724293</v>
       </c>
       <c r="J28" s="20">
-        <v>1.814578876298771</v>
+        <v>1.872236602657881</v>
       </c>
       <c r="K28" s="20">
         <v>0.403590422728146</v>
       </c>
       <c r="L28" s="20">
-        <v>-0.5995509067559709</v>
+        <v>-0.5973965659874914</v>
       </c>
       <c r="M28" s="20">
-        <v>-0.5021848196792174</v>
+        <v>-0.550435354218233</v>
       </c>
       <c r="N28" s="20">
         <v>12.458015</v>
@@ -5102,13 +5148,13 @@
         <v>0.125</v>
       </c>
       <c r="R28" s="12">
-        <v>0.790317139285901</v>
+        <v>0.8120502991265173</v>
       </c>
       <c r="S28" s="11">
-        <v>63.05040006309013</v>
+        <v>64.19224132637174</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -5116,61 +5162,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="E29" s="10">
-        <v>482.2799987792969</v>
+        <v>207.1100006103516</v>
       </c>
       <c r="F29" s="17">
-        <v>0.5190346046199206</v>
+        <v>0.5339933652139123</v>
       </c>
       <c r="G29" s="20">
-        <v>-0.9800881674162824</v>
+        <v>0.5809437263948974</v>
       </c>
       <c r="H29" s="20">
-        <v>2.147104391138658</v>
+        <v>-0.6585101921976751</v>
       </c>
       <c r="I29" s="20">
-        <v>2.675284350851072</v>
+        <v>4.120745224686987</v>
       </c>
       <c r="J29" s="20">
-        <v>0.8747692948236511</v>
+        <v>0.03136973760576034</v>
       </c>
       <c r="K29" s="20">
-        <v>-0.2212015005016859</v>
+        <v>0.5994822798464103</v>
       </c>
       <c r="L29" s="20">
-        <v>-3.427259213116233</v>
+        <v>0.5784076560155171</v>
       </c>
       <c r="M29" s="20">
-        <v>0.6766785185954969</v>
+        <v>0.08321685651914387</v>
       </c>
       <c r="N29" s="20">
-        <v>17.358335</v>
+        <v>12.092511</v>
       </c>
       <c r="O29" s="20">
-        <v>22.350464</v>
+        <v>1.3082409</v>
       </c>
       <c r="P29" s="12">
-        <v>1.30853</v>
+        <v>0.09031</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.438</v>
+        <v>11.11</v>
       </c>
       <c r="R29" s="12">
-        <v>0.8126382918933179</v>
+        <v>0.1467616091443797</v>
       </c>
       <c r="S29" s="11">
-        <v>51.59300712887129</v>
+        <v>40.09809903713158</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -5178,61 +5224,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E30" s="10">
-        <v>38.93000030517578</v>
+        <v>212.7599945068359</v>
       </c>
       <c r="F30" s="17">
-        <v>0.5165683754044931</v>
+        <v>0.4988446446446637</v>
       </c>
       <c r="G30" s="20">
-        <v>0.09785741135882757</v>
+        <v>0.5306330587817526</v>
       </c>
       <c r="H30" s="20">
-        <v>-0.81219220040201</v>
+        <v>-0.3271612979466518</v>
       </c>
       <c r="I30" s="20">
-        <v>3.920900829953943</v>
+        <v>2.322186162377909</v>
       </c>
       <c r="J30" s="20">
-        <v>0.2607885678504367</v>
+        <v>0.8481324468869508</v>
       </c>
       <c r="K30" s="20">
-        <v>3.370836553182694</v>
+        <v>-0.1711975264478132</v>
       </c>
       <c r="L30" s="20">
-        <v>-3.427259213116233</v>
+        <v>0.8402178705478436</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.5035836690156115</v>
+        <v>-0.7606402203449598</v>
       </c>
       <c r="N30" s="20">
-        <v>12.144172</v>
+        <v>20.076998</v>
       </c>
       <c r="O30" s="20">
-        <v>2.3688147</v>
+        <v>2.1549587</v>
       </c>
       <c r="P30" s="12">
-        <v>0.21465999</v>
+        <v>0.12231</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.9320000000000001</v>
+        <v>0.535</v>
       </c>
       <c r="R30" s="12">
-        <v>0.2245989048135262</v>
+        <v>0.1292690053885404</v>
       </c>
       <c r="S30" s="11">
-        <v>59.10137546437928</v>
+        <v>68.11840463210588</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -5240,61 +5286,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="E31" s="10">
-        <v>213.8099975585938</v>
+        <v>215.4299926757812</v>
       </c>
       <c r="F31" s="17">
-        <v>0.5111044428488211</v>
+        <v>0.4836683452055093</v>
       </c>
       <c r="G31" s="20">
-        <v>0.5306330587817526</v>
+        <v>0.2276945080429548</v>
       </c>
       <c r="H31" s="20">
-        <v>-0.3271612979466518</v>
+        <v>0.03119877719549098</v>
       </c>
       <c r="I31" s="20">
-        <v>2.322186162377909</v>
+        <v>-0.8985721544356027</v>
       </c>
       <c r="J31" s="20">
-        <v>0.8898064438164361</v>
+        <v>0.553454147992097</v>
       </c>
       <c r="K31" s="20">
-        <v>-0.1711975264478132</v>
+        <v>3.362072970101089</v>
       </c>
       <c r="L31" s="20">
-        <v>0.7625016530393559</v>
+        <v>-0.1447495134874203</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.7053830681471978</v>
+        <v>-0.4156410643806928</v>
       </c>
       <c r="N31" s="20">
-        <v>20.076998</v>
+        <v>39.2238</v>
       </c>
       <c r="O31" s="20">
-        <v>2.1549587</v>
+        <v>1.730507</v>
       </c>
       <c r="P31" s="12">
-        <v>0.12231</v>
+        <v>0.04575</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.535</v>
+        <v>0.034</v>
       </c>
       <c r="R31" s="12">
-        <v>0.16834710124306</v>
+        <v>0.1309848672189726</v>
       </c>
       <c r="S31" s="11">
-        <v>70.55040749646682</v>
+        <v>51.35516806417853</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -5302,19 +5348,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="10">
-        <v>223.6699981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F32" s="17">
-        <v>0.5029733670908321</v>
+        <v>0.4787522761629038</v>
       </c>
       <c r="G32" s="20">
         <v>-1.255664189485384</v>
@@ -5326,16 +5372,16 @@
         <v>2.430954222251415</v>
       </c>
       <c r="J32" s="20">
-        <v>0.5426884151152741</v>
+        <v>0.4534057753144493</v>
       </c>
       <c r="K32" s="20">
         <v>-0.3093528362049048</v>
       </c>
       <c r="L32" s="20">
-        <v>-0.2168963964814134</v>
+        <v>-0.2154299714462333</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.07137884382410897</v>
+        <v>-0.04043239994650571</v>
       </c>
       <c r="N32" s="20">
         <v>29.159492</v>
@@ -5350,13 +5396,13 @@
         <v>1.059</v>
       </c>
       <c r="R32" s="12">
-        <v>0.2120085147302435</v>
+        <v>0.1764722179426954</v>
       </c>
       <c r="S32" s="11">
-        <v>54.31658542796111</v>
+        <v>50.00091134128554</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -5364,61 +5410,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="E33" s="10">
-        <v>64.41000366210938</v>
+        <v>460.9299926757812</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4773493097566183</v>
+        <v>0.4773756244769209</v>
       </c>
       <c r="G33" s="20">
-        <v>0.4785242056074159</v>
+        <v>-0.9800881674162824</v>
       </c>
       <c r="H33" s="20">
-        <v>0.6574599095763384</v>
+        <v>2.147104391138658</v>
       </c>
       <c r="I33" s="20">
-        <v>0.2335665909722698</v>
+        <v>2.675284350851072</v>
       </c>
       <c r="J33" s="20">
-        <v>0.5186742915074114</v>
+        <v>0.6857490621961325</v>
       </c>
       <c r="K33" s="20">
-        <v>0.8031067102719743</v>
+        <v>-0.2212015005016859</v>
       </c>
       <c r="L33" s="20">
-        <v>0.5483101489315492</v>
+        <v>-3.363908912256145</v>
       </c>
       <c r="M33" s="20">
-        <v>-0.2776124187863871</v>
+        <v>0.8172544135161309</v>
       </c>
       <c r="N33" s="20">
-        <v>14.718061</v>
+        <v>17.358335</v>
       </c>
       <c r="O33" s="20">
-        <v>6.116247</v>
+        <v>22.350464</v>
       </c>
       <c r="P33" s="12">
-        <v>0.46598998</v>
+        <v>1.30853</v>
       </c>
       <c r="Q33" s="12">
-        <v>0.057</v>
+        <v>0.438</v>
       </c>
       <c r="R33" s="12">
-        <v>0.09444047287161528</v>
+        <v>0.7157032112253165</v>
       </c>
       <c r="S33" s="11">
-        <v>45.52777965278488</v>
+        <v>46.76710503905318</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -5426,61 +5472,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="E34" s="10">
-        <v>344.8299865722656</v>
+        <v>63.75</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4531572461392963</v>
+        <v>0.4690897228108178</v>
       </c>
       <c r="G34" s="20">
-        <v>0.09769025453656566</v>
+        <v>0.4785242056074159</v>
       </c>
       <c r="H34" s="20">
-        <v>-0.2373803208952873</v>
+        <v>0.6574599095763384</v>
       </c>
       <c r="I34" s="20">
-        <v>0.4704496970046058</v>
+        <v>0.2335665909722698</v>
       </c>
       <c r="J34" s="20">
-        <v>1.34294690561148</v>
+        <v>0.4807968269432829</v>
       </c>
       <c r="K34" s="20">
-        <v>1.69802319437015</v>
+        <v>0.8031067102719743</v>
       </c>
       <c r="L34" s="20">
-        <v>-1.693368662516335</v>
+        <v>0.5490873630778165</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.9816981661422759</v>
+        <v>-0.2393996741031126</v>
       </c>
       <c r="N34" s="20">
-        <v>33.248394</v>
+        <v>14.718061</v>
       </c>
       <c r="O34" s="20">
-        <v>5.0043454</v>
+        <v>6.116247</v>
       </c>
       <c r="P34" s="12">
-        <v>0.15286</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.204</v>
+        <v>0.057</v>
       </c>
       <c r="R34" s="12">
-        <v>0.622958462799996</v>
+        <v>0.08593488554643147</v>
       </c>
       <c r="S34" s="11">
-        <v>49.24290051439417</v>
+        <v>42.89179391125454</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -5488,61 +5534,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="E35" s="10">
-        <v>210.7299957275391</v>
+        <v>344.010009765625</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4493773174039252</v>
+        <v>0.4630456117748885</v>
       </c>
       <c r="G35" s="20">
-        <v>0.2276945080429548</v>
+        <v>0.09769025453656566</v>
       </c>
       <c r="H35" s="20">
-        <v>0.03119877719549098</v>
+        <v>-0.2373803208952873</v>
       </c>
       <c r="I35" s="20">
-        <v>-0.8985721544356027</v>
+        <v>0.4704496970046058</v>
       </c>
       <c r="J35" s="20">
-        <v>0.3558712693770349</v>
+        <v>1.36785344152104</v>
       </c>
       <c r="K35" s="20">
-        <v>3.362072970101089</v>
+        <v>1.69802319437015</v>
       </c>
       <c r="L35" s="20">
-        <v>-0.115198605209464</v>
+        <v>-1.694654668880079</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.1255062983024788</v>
+        <v>-0.9505286005854161</v>
       </c>
       <c r="N35" s="20">
-        <v>39.2238</v>
+        <v>33.248394</v>
       </c>
       <c r="O35" s="20">
-        <v>1.730507</v>
+        <v>5.0043454</v>
       </c>
       <c r="P35" s="12">
-        <v>0.04575</v>
+        <v>0.15286</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.034</v>
+        <v>0.204</v>
       </c>
       <c r="R35" s="12">
-        <v>0.1184650052099032</v>
+        <v>0.6100061436497135</v>
       </c>
       <c r="S35" s="11">
-        <v>46.00394204412848</v>
+        <v>48.76975896145935</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -5550,19 +5596,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E36" s="10">
-        <v>215.3500061035156</v>
+        <v>212.6600036621094</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4462442929594646</v>
+        <v>0.4443059868085213</v>
       </c>
       <c r="G36" s="20">
         <v>0.3451625228080399</v>
@@ -5574,16 +5620,16 @@
         <v>0.3853148937972363</v>
       </c>
       <c r="J36" s="20">
-        <v>0.4948865523146312</v>
+        <v>0.448129750125241</v>
       </c>
       <c r="K36" s="20">
         <v>0.2979119208617143</v>
       </c>
       <c r="L36" s="20">
-        <v>0.5763142240165818</v>
+        <v>0.5782988962229673</v>
       </c>
       <c r="M36" s="20">
-        <v>0.03690753200358504</v>
+        <v>0.1865282091722175</v>
       </c>
       <c r="N36" s="20">
         <v>17.572235</v>
@@ -5598,13 +5644,13 @@
         <v>0.28</v>
       </c>
       <c r="R36" s="12">
-        <v>0.3542712887936303</v>
+        <v>0.3361910946262474</v>
       </c>
       <c r="S36" s="11">
-        <v>50.98928498558899</v>
+        <v>46.63846586110895</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -5612,19 +5658,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="10">
-        <v>885.9199829101562</v>
+        <v>862.3300170898438</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4302820216532392</v>
+        <v>0.4142451202876382</v>
       </c>
       <c r="G37" s="20">
         <v>-2.161506497931219</v>
@@ -5636,16 +5682,16 @@
         <v>1.349061869241311</v>
       </c>
       <c r="J37" s="20">
-        <v>1.919789765466099</v>
+        <v>1.819393501103421</v>
       </c>
       <c r="K37" s="20">
         <v>-0.003658438122982013</v>
       </c>
       <c r="L37" s="20">
-        <v>-2.950052929040729</v>
+        <v>-2.87247975688518</v>
       </c>
       <c r="M37" s="20">
-        <v>0.2066481691061354</v>
+        <v>0.3244930142795039</v>
       </c>
       <c r="N37" s="20">
         <v>60.967697</v>
@@ -5660,13 +5706,13 @@
         <v>0.485</v>
       </c>
       <c r="R37" s="12">
-        <v>1.311010178615966</v>
+        <v>1.239682414499489</v>
       </c>
       <c r="S37" s="11">
-        <v>54.52913029639633</v>
+        <v>51.34334889829623</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -5674,61 +5720,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="E38" s="10">
-        <v>807.6500244140625</v>
+        <v>137.0399932861328</v>
       </c>
       <c r="F38" s="17">
-        <v>0.420814776373709</v>
+        <v>0.413700655659508</v>
       </c>
       <c r="G38" s="20">
-        <v>0.1366671162081818</v>
+        <v>0.5166686592886003</v>
       </c>
       <c r="H38" s="20">
-        <v>0.1794925664991855</v>
+        <v>-0.1376180067425467</v>
       </c>
       <c r="I38" s="20">
-        <v>-0.2394962708042926</v>
+        <v>0.8009706460259883</v>
       </c>
       <c r="J38" s="20">
-        <v>0.8268369456584153</v>
+        <v>1.03710462344827</v>
       </c>
       <c r="K38" s="20">
-        <v>1.4346001970348</v>
+        <v>-0.06912755879145449</v>
       </c>
       <c r="L38" s="20">
-        <v>0.4998179441534492</v>
+        <v>0.560666316982805</v>
       </c>
       <c r="M38" s="20">
-        <v>-0.7343334011763972</v>
+        <v>-0.9231743191838273</v>
       </c>
       <c r="N38" s="20">
-        <v>20.49319</v>
+        <v>17.759258</v>
       </c>
       <c r="O38" s="20">
-        <v>2.6184473</v>
+        <v>2.4681509</v>
       </c>
       <c r="P38" s="12">
-        <v>0.14043</v>
+        <v>0.1418</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.167</v>
+        <v>0.355</v>
       </c>
       <c r="R38" s="12">
-        <v>0.04892398899911177</v>
+        <v>0.1875523666710588</v>
       </c>
       <c r="S38" s="11">
-        <v>53.73805386136186</v>
+        <v>67.36323064561699</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -5736,61 +5782,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="E39" s="10">
-        <v>136.5299987792969</v>
+        <v>28.20000076293945</v>
       </c>
       <c r="F39" s="17">
-        <v>0.4077057610151587</v>
+        <v>0.4116695403282959</v>
       </c>
       <c r="G39" s="20">
-        <v>0.5166686592886003</v>
+        <v>-0.07115990276327171</v>
       </c>
       <c r="H39" s="20">
-        <v>-0.1376180067425467</v>
+        <v>-0.995994779142174</v>
       </c>
       <c r="I39" s="20">
-        <v>0.8009706460259883</v>
+        <v>-1.178947812209808</v>
       </c>
       <c r="J39" s="20">
-        <v>1.025930069554132</v>
+        <v>0.5927970273311364</v>
       </c>
       <c r="K39" s="20">
-        <v>-0.06912755879145449</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L39" s="20">
-        <v>0.4796376175125497</v>
+        <v>1.137019842328981</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.895434400532486</v>
+        <v>-0.5993918216133778</v>
       </c>
       <c r="N39" s="20">
-        <v>17.759258</v>
+        <v>403.57144</v>
       </c>
       <c r="O39" s="20">
-        <v>2.4681509</v>
+        <v>2.1576414</v>
       </c>
       <c r="P39" s="12">
-        <v>0.1418</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.355</v>
+        <v>-0.112</v>
       </c>
       <c r="R39" s="12">
-        <v>0.2129832807308187</v>
+        <v>0.01402377937743893</v>
       </c>
       <c r="S39" s="11">
-        <v>66.61276992586393</v>
+        <v>55.12732055707502</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -5798,61 +5844,61 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="E40" s="10">
-        <v>147.0099945068359</v>
+        <v>793.260009765625</v>
       </c>
       <c r="F40" s="17">
-        <v>0.4004632235877128</v>
+        <v>0.4068434619532779</v>
       </c>
       <c r="G40" s="20">
-        <v>0.6186160464919896</v>
+        <v>0.1366671162081818</v>
       </c>
       <c r="H40" s="20">
-        <v>0.4653349166417897</v>
+        <v>0.1794925664991855</v>
       </c>
       <c r="I40" s="20">
-        <v>1.428599056298859</v>
+        <v>-0.2394962708042926</v>
       </c>
       <c r="J40" s="20">
-        <v>0.4926560466693115</v>
+        <v>0.757377078874765</v>
       </c>
       <c r="K40" s="20">
-        <v>-0.5186478203891555</v>
+        <v>1.4346001970348</v>
       </c>
       <c r="L40" s="20">
-        <v>0.2862637669770728</v>
+        <v>0.4689096068217605</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.3867007330767101</v>
+        <v>-0.6253190779943306</v>
       </c>
       <c r="N40" s="20">
-        <v>11.298833</v>
+        <v>20.49319</v>
       </c>
       <c r="O40" s="20">
-        <v>2.394452</v>
+        <v>2.6184473</v>
       </c>
       <c r="P40" s="12">
-        <v>0.22507</v>
+        <v>0.14043</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.587</v>
+        <v>0.167</v>
       </c>
       <c r="R40" s="12">
-        <v>0.1670258187334688</v>
+        <v>0.02673751335090291</v>
       </c>
       <c r="S40" s="11">
-        <v>53.87520841180954</v>
+        <v>49.19027780844203</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -5860,61 +5906,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="E41" s="10">
-        <v>27.90999984741211</v>
+        <v>126.1399993896484</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3975679214877296</v>
+        <v>0.403741720412671</v>
       </c>
       <c r="G41" s="20">
-        <v>-0.07115990276327171</v>
+        <v>0.462770354618154</v>
       </c>
       <c r="H41" s="20">
-        <v>-0.995994779142174</v>
+        <v>0.7818596344809873</v>
       </c>
       <c r="I41" s="20">
-        <v>-1.178947812209808</v>
+        <v>-0.2047856713387676</v>
       </c>
       <c r="J41" s="20">
-        <v>0.4732468049597856</v>
+        <v>1.226210940130118</v>
       </c>
       <c r="K41" s="20">
-        <v>4.196860964161699</v>
+        <v>-0.3340970707882645</v>
       </c>
       <c r="L41" s="20">
-        <v>1.138908902891917</v>
+        <v>-0.5122428158842524</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.3287655186500924</v>
+        <v>-1.015162279913328</v>
       </c>
       <c r="N41" s="20">
-        <v>403.57144</v>
+        <v>16.152584</v>
       </c>
       <c r="O41" s="20">
-        <v>2.1576414</v>
+        <v>3.848858</v>
       </c>
       <c r="P41" s="12">
-        <v>-0.08785999999999999</v>
+        <v>0.25905</v>
       </c>
       <c r="Q41" s="12">
-        <v>-0.112</v>
+        <v>0.151</v>
       </c>
       <c r="R41" s="12">
-        <v>0.005403444427000137</v>
+        <v>0.09024805164266314</v>
       </c>
       <c r="S41" s="11">
-        <v>50.03528328324084</v>
+        <v>56.88418451786255</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -5922,61 +5968,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="E42" s="10">
-        <v>128.7100067138672</v>
+        <v>205.3899993896484</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3914625229953394</v>
+        <v>0.402768241716786</v>
       </c>
       <c r="G42" s="20">
-        <v>0.462770354618154</v>
+        <v>0.6168563890519317</v>
       </c>
       <c r="H42" s="20">
-        <v>0.7818596344809873</v>
+        <v>-0.04487785224304153</v>
       </c>
       <c r="I42" s="20">
-        <v>-0.2047856713387676</v>
+        <v>1.604307978960174</v>
       </c>
       <c r="J42" s="20">
-        <v>1.222462886023134</v>
+        <v>0.621211291976688</v>
       </c>
       <c r="K42" s="20">
-        <v>-0.3340970707882645</v>
+        <v>-0.1980037805797862</v>
       </c>
       <c r="L42" s="20">
-        <v>-0.5514092375045718</v>
+        <v>0.2787364979508477</v>
       </c>
       <c r="M42" s="20">
-        <v>-1.125222228513545</v>
+        <v>-0.5105421706271931</v>
       </c>
       <c r="N42" s="20">
-        <v>16.152584</v>
+        <v>37.874523</v>
       </c>
       <c r="O42" s="20">
-        <v>3.848858</v>
+        <v>1.474797</v>
       </c>
       <c r="P42" s="12">
-        <v>0.25905</v>
+        <v>0.034930002</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.151</v>
+        <v>0.525</v>
       </c>
       <c r="R42" s="12">
-        <v>0.08729262667910476</v>
+        <v>0.1755943566673632</v>
       </c>
       <c r="S42" s="11">
-        <v>60.90704506011068</v>
+        <v>56.94899394031417</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -5984,61 +6030,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E43" s="10">
-        <v>383.6900024414062</v>
+        <v>147.4600067138672</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3817434987565279</v>
+        <v>0.4026756044648081</v>
       </c>
       <c r="G43" s="20">
-        <v>-1.119776310688084</v>
+        <v>0.6186160464919896</v>
       </c>
       <c r="H43" s="20">
-        <v>0.5633615561685517</v>
+        <v>0.4653349166417897</v>
       </c>
       <c r="I43" s="20">
-        <v>3.683499757563413</v>
+        <v>1.428599056298859</v>
       </c>
       <c r="J43" s="20">
-        <v>0.9486169808161514</v>
+        <v>0.4961322840073805</v>
       </c>
       <c r="K43" s="20">
-        <v>0.4185400644555927</v>
+        <v>-0.5186478203891555</v>
       </c>
       <c r="L43" s="20">
-        <v>-3.289372120440793</v>
+        <v>0.3299943553976453</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.1579020601999454</v>
+        <v>-0.404879803446206</v>
       </c>
       <c r="N43" s="20">
-        <v>49.04258</v>
+        <v>11.298833</v>
       </c>
       <c r="O43" s="20">
-        <v>16.253017</v>
+        <v>2.394452</v>
       </c>
       <c r="P43" s="12">
-        <v>0.36465</v>
+        <v>0.22507</v>
       </c>
       <c r="Q43" s="12">
-        <v>1.039</v>
+        <v>0.587</v>
       </c>
       <c r="R43" s="12">
-        <v>0.2766643569214373</v>
+        <v>0.1297848543574911</v>
       </c>
       <c r="S43" s="11">
-        <v>54.5644415220998</v>
+        <v>54.68611608294517</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -6046,61 +6092,61 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="E44" s="10">
-        <v>138.1100006103516</v>
+        <v>158.8500061035156</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3773361396728952</v>
+        <v>0.3927078458293249</v>
       </c>
       <c r="G44" s="20">
-        <v>0.6342024451803385</v>
+        <v>-2.038321783471051</v>
       </c>
       <c r="H44" s="20">
-        <v>0.2959780642595878</v>
+        <v>1.762815619214651</v>
       </c>
       <c r="I44" s="20">
-        <v>0.2897869408623402</v>
+        <v>0.2317788417534188</v>
       </c>
       <c r="J44" s="20">
-        <v>1.275151234918139</v>
+        <v>1.470472081584176</v>
       </c>
       <c r="K44" s="20">
-        <v>-1.403769711631418</v>
+        <v>0.4314276866344259</v>
       </c>
       <c r="L44" s="20">
-        <v>0.0006690907096995564</v>
+        <v>-0.3536604835264507</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.3411079418698413</v>
+        <v>-0.2164491781921125</v>
       </c>
       <c r="N44" s="20">
-        <v>9.892434</v>
+        <v>55.226147</v>
       </c>
       <c r="O44" s="20">
-        <v>3.5168924</v>
+        <v>73.93093</v>
       </c>
       <c r="P44" s="12">
-        <v>0.29867</v>
+        <v>1.17442</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.176</v>
+        <v>0.256</v>
       </c>
       <c r="R44" s="12">
-        <v>0.2665911661926548</v>
+        <v>0.90285097886645</v>
       </c>
       <c r="S44" s="11">
-        <v>65.88393830203765</v>
+        <v>50.35750884772562</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -6166,110 +6212,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B6" s="12">
         <v>0.18</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B7" s="12">
         <v>0.16</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B8" s="12">
         <v>0.1</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B9" s="12">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B10" s="12">
         <v>0.12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B11" s="12">
         <v>0.06</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B12" s="12">
         <v>0.08</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B13" s="12">
         <f>SUM(B6:B12)</f>
@@ -6278,22 +6324,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -6372,57 +6418,57 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>30</v>
@@ -6430,113 +6476,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -6562,181 +6608,181 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>403.4133605957031</v>
+        <v>418.6282348632812</v>
       </c>
       <c r="C1">
-        <v>418.6282348632812</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="D1">
-        <v>408.8244323730469</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="E1">
-        <v>418.0192260742188</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="F1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="G1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="H1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="I1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="J1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="K1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="L1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="M1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="N1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="O1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="P1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="Q1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="R1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="S1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="T1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="U1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="V1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="W1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="X1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="Y1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="Z1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="AA1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="AB1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AC1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AD1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AE1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AF1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AG1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AH1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AI1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AJ1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AK1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AL1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AM1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AN1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AO1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AP1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AQ1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AR1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AS1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="AT1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="AU1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="AV1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="AW1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="AX1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="AY1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="AZ1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
       <c r="BA1">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="BB1">
-        <v>456.010009765625</v>
+        <v>425</v>
       </c>
       <c r="BC1">
-        <v>425</v>
+        <v>492.2000122070312</v>
       </c>
       <c r="BD1">
-        <v>492.2000122070312</v>
+        <v>516.3900146484375</v>
       </c>
       <c r="BE1">
-        <v>516.3900146484375</v>
+        <v>524.1400146484375</v>
       </c>
       <c r="BF1">
-        <v>524.1400146484375</v>
+        <v>533.8800048828125</v>
       </c>
       <c r="BG1">
-        <v>533.8800048828125</v>
+        <v>535.25</v>
       </c>
       <c r="BH1">
-        <v>535.25</v>
+        <v>506.6199951171875</v>
       </c>
     </row>
     <row r="2" spans="1:60">
@@ -6744,181 +6790,181 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1020.60302734375</v>
+        <v>1043.029541015625</v>
       </c>
       <c r="C2">
-        <v>1043.029541015625</v>
+        <v>1133.815551757812</v>
       </c>
       <c r="D2">
-        <v>1133.815551757812</v>
+        <v>1211.193725585938</v>
       </c>
       <c r="E2">
-        <v>1211.193725585938</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="F2">
-        <v>1051.608276367188</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="G2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="H2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="I2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="J2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="K2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="L2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="M2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="N2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="O2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="P2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="Q2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="R2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="S2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="T2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="U2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="V2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="W2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="X2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="Y2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="Z2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="AA2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="AB2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="AC2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AD2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="AE2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AF2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AG2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AH2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AI2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AJ2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AK2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AL2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AM2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AN2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AO2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AP2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AQ2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="AR2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AS2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="AT2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="AU2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="AV2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="AW2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="AX2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="AY2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="AZ2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="BA2">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="BB2">
-        <v>958.72998046875</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="BC2">
-        <v>933.4400024414062</v>
+        <v>956.0800170898438</v>
       </c>
       <c r="BD2">
-        <v>956.0800170898438</v>
+        <v>958.1599731445312</v>
       </c>
       <c r="BE2">
-        <v>958.1599731445312</v>
+        <v>1016.590026855469</v>
       </c>
       <c r="BF2">
-        <v>1016.590026855469</v>
+        <v>1000.260009765625</v>
       </c>
       <c r="BG2">
-        <v>1000.260009765625</v>
+        <v>1027.77001953125</v>
       </c>
       <c r="BH2">
-        <v>1027.77001953125</v>
+        <v>977.4099731445312</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -6926,181 +6972,181 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1991.550048828125</v>
+        <v>1958.800048828125</v>
       </c>
       <c r="C3">
-        <v>1958.800048828125</v>
+        <v>2184.75</v>
       </c>
       <c r="D3">
-        <v>2184.75</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="E3">
+        <v>1963.599975585938</v>
+      </c>
+      <c r="F3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="G3">
+        <v>2335</v>
+      </c>
+      <c r="H3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="I3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="J3">
         <v>2273.72998046875</v>
       </c>
-      <c r="F3">
-        <v>1963.599975585938</v>
-      </c>
-      <c r="G3">
-        <v>1914.4599609375</v>
-      </c>
-      <c r="H3">
-        <v>2335</v>
-      </c>
-      <c r="I3">
-        <v>2090.7099609375</v>
-      </c>
-      <c r="J3">
-        <v>2050.389892578125</v>
-      </c>
       <c r="K3">
-        <v>2273.72998046875</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="L3">
-        <v>2032.219970703125</v>
+        <v>1745</v>
       </c>
       <c r="M3">
-        <v>1745</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="N3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="O3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="P3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="Q3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="R3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="S3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="T3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="U3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="V3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="W3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="X3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="Y3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="Z3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="AA3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="AB3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="AC3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="AD3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AE3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AF3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AG3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AH3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AI3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="AJ3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AK3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AL3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AM3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AN3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AO3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AP3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AQ3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AR3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AS3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="AT3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="AU3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="AV3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="AW3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="AX3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="AY3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="AZ3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="BA3">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="BB3">
-        <v>1566.699951171875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="BC3">
-        <v>1536.869995117188</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="BD3">
-        <v>1553.400024414062</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="BE3">
-        <v>1554.989990234375</v>
+        <v>1740</v>
       </c>
       <c r="BF3">
-        <v>1740</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="BG3">
-        <v>1737.989990234375</v>
+        <v>1764.170043945312</v>
       </c>
       <c r="BH3">
-        <v>1764.170043945312</v>
+        <v>1692.589965820312</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -7108,181 +7154,181 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>680.8614501953125</v>
+        <v>711.9014892578125</v>
       </c>
       <c r="C4">
-        <v>711.9014892578125</v>
+        <v>745.990478515625</v>
       </c>
       <c r="D4">
-        <v>745.990478515625</v>
+        <v>732.3848876953125</v>
       </c>
       <c r="E4">
-        <v>732.3848876953125</v>
+        <v>670.5347290039062</v>
       </c>
       <c r="F4">
-        <v>670.5347290039062</v>
+        <v>643.6234130859375</v>
       </c>
       <c r="G4">
-        <v>643.6234130859375</v>
+        <v>675.1732788085938</v>
       </c>
       <c r="H4">
-        <v>675.1732788085938</v>
+        <v>586.2618408203125</v>
       </c>
       <c r="I4">
-        <v>586.2618408203125</v>
+        <v>651.6708374023438</v>
       </c>
       <c r="J4">
-        <v>651.6708374023438</v>
+        <v>638.5150146484375</v>
       </c>
       <c r="K4">
-        <v>638.5150146484375</v>
+        <v>598.177978515625</v>
       </c>
       <c r="L4">
-        <v>598.177978515625</v>
+        <v>538.8270263671875</v>
       </c>
       <c r="M4">
-        <v>538.8270263671875</v>
+        <v>577.2747192382812</v>
       </c>
       <c r="N4">
-        <v>577.2747192382812</v>
+        <v>531.92919921875</v>
       </c>
       <c r="O4">
-        <v>531.92919921875</v>
+        <v>550.1234130859375</v>
       </c>
       <c r="P4">
-        <v>550.1234130859375</v>
+        <v>577.864501953125</v>
       </c>
       <c r="Q4">
-        <v>577.864501953125</v>
+        <v>582.403076171875</v>
       </c>
       <c r="R4">
-        <v>582.403076171875</v>
+        <v>555.3717041015625</v>
       </c>
       <c r="S4">
-        <v>555.3717041015625</v>
+        <v>563.1392211914062</v>
       </c>
       <c r="T4">
-        <v>563.1392211914062</v>
+        <v>513.6751098632812</v>
       </c>
       <c r="U4">
-        <v>513.6751098632812</v>
+        <v>466.6601867675781</v>
       </c>
       <c r="V4">
-        <v>466.6601867675781</v>
+        <v>477.0668640136719</v>
       </c>
       <c r="W4">
-        <v>477.0668640136719</v>
+        <v>487.2635803222656</v>
       </c>
       <c r="X4">
-        <v>487.2635803222656</v>
+        <v>548.2140502929688</v>
       </c>
       <c r="Y4">
-        <v>548.2140502929688</v>
+        <v>556.4913330078125</v>
       </c>
       <c r="Z4">
-        <v>556.4913330078125</v>
+        <v>558.120849609375</v>
       </c>
       <c r="AA4">
-        <v>558.120849609375</v>
+        <v>519.6331787109375</v>
       </c>
       <c r="AB4">
-        <v>519.6331787109375</v>
+        <v>497.7602233886719</v>
       </c>
       <c r="AC4">
-        <v>497.7602233886719</v>
+        <v>463.3612670898438</v>
       </c>
       <c r="AD4">
-        <v>463.3612670898438</v>
+        <v>461.8917236328125</v>
       </c>
       <c r="AE4">
-        <v>461.8917236328125</v>
+        <v>532.868896484375</v>
       </c>
       <c r="AF4">
-        <v>532.868896484375</v>
+        <v>544.6651611328125</v>
       </c>
       <c r="AG4">
-        <v>544.6651611328125</v>
+        <v>527.05078125</v>
       </c>
       <c r="AH4">
-        <v>527.05078125</v>
+        <v>548.3839721679688</v>
       </c>
       <c r="AI4">
-        <v>548.3839721679688</v>
+        <v>519.0033569335938</v>
       </c>
       <c r="AJ4">
-        <v>519.0033569335938</v>
+        <v>451.3750915527344</v>
       </c>
       <c r="AK4">
-        <v>451.3750915527344</v>
+        <v>434.1606140136719</v>
       </c>
       <c r="AL4">
-        <v>434.1606140136719</v>
+        <v>438.1993408203125</v>
       </c>
       <c r="AM4">
-        <v>438.1993408203125</v>
+        <v>437.7894592285156</v>
       </c>
       <c r="AN4">
-        <v>437.7894592285156</v>
+        <v>453.9542846679688</v>
       </c>
       <c r="AO4">
-        <v>453.9542846679688</v>
+        <v>487.1336364746094</v>
       </c>
       <c r="AP4">
-        <v>487.1336364746094</v>
+        <v>508.63671875</v>
       </c>
       <c r="AQ4">
-        <v>508.63671875</v>
+        <v>535.8380126953125</v>
       </c>
       <c r="AR4">
-        <v>535.8380126953125</v>
+        <v>496.0007934570312</v>
       </c>
       <c r="AS4">
-        <v>496.0007934570312</v>
+        <v>461.9417114257812</v>
       </c>
       <c r="AT4">
-        <v>461.9417114257812</v>
+        <v>468.8994750976562</v>
       </c>
       <c r="AU4">
-        <v>468.8994750976562</v>
+        <v>459.2925720214844</v>
       </c>
       <c r="AV4">
-        <v>459.2925720214844</v>
+        <v>435.2402954101562</v>
       </c>
       <c r="AW4">
-        <v>435.2402954101562</v>
+        <v>450.6053466796875</v>
       </c>
       <c r="AX4">
-        <v>450.6053466796875</v>
+        <v>468.7295227050781</v>
       </c>
       <c r="AY4">
-        <v>468.7295227050781</v>
+        <v>461.8517456054688</v>
       </c>
       <c r="AZ4">
-        <v>461.8517456054688</v>
+        <v>459.3025817871094</v>
       </c>
       <c r="BA4">
-        <v>459.3025817871094</v>
+        <v>450.4053955078125</v>
       </c>
       <c r="BB4">
-        <v>450.4053955078125</v>
+        <v>450.2954406738281</v>
       </c>
       <c r="BC4">
-        <v>450.2954406738281</v>
+        <v>448.7559509277344</v>
       </c>
       <c r="BD4">
-        <v>448.7559509277344</v>
+        <v>441.4283142089844</v>
       </c>
       <c r="BE4">
-        <v>441.4283142089844</v>
+        <v>467.3099670410156</v>
       </c>
       <c r="BF4">
-        <v>467.3099670410156</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="BG4">
-        <v>477.2999877929688</v>
+        <v>482.2799987792969</v>
       </c>
       <c r="BH4">
-        <v>482.2799987792969</v>
+        <v>460.9299926757812</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -7290,181 +7336,181 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>243.1901702880859</v>
+        <v>238.8469543457031</v>
       </c>
       <c r="C5">
-        <v>238.8469543457031</v>
+        <v>235.3903045654297</v>
       </c>
       <c r="D5">
-        <v>235.3903045654297</v>
+        <v>242.8415069580078</v>
       </c>
       <c r="E5">
-        <v>242.8415069580078</v>
+        <v>242.7418823242188</v>
       </c>
       <c r="F5">
-        <v>242.7418823242188</v>
+        <v>241.4967041015625</v>
       </c>
       <c r="G5">
-        <v>241.4967041015625</v>
+        <v>254.0780792236328</v>
       </c>
       <c r="H5">
-        <v>254.0780792236328</v>
+        <v>258.3714904785156</v>
       </c>
       <c r="I5">
-        <v>258.3714904785156</v>
+        <v>265.2947387695312</v>
       </c>
       <c r="J5">
-        <v>265.2947387695312</v>
+        <v>259.4373779296875</v>
       </c>
       <c r="K5">
-        <v>259.4373779296875</v>
+        <v>268.4027404785156</v>
       </c>
       <c r="L5">
-        <v>268.4027404785156</v>
+        <v>266.7291870117188</v>
       </c>
       <c r="M5">
-        <v>266.7291870117188</v>
+        <v>269.2793579101562</v>
       </c>
       <c r="N5">
-        <v>269.2793579101562</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="O5">
-        <v>265.1951293945312</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="P5">
-        <v>281.7909851074219</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="Q5">
-        <v>280.1672668457031</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="R5">
-        <v>279.6094055175781</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="S5">
-        <v>294.6513061523438</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="T5">
-        <v>300.2695617675781</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="U5">
-        <v>291.5333251953125</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="V5">
-        <v>299.1040954589844</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="W5">
-        <v>308.4579162597656</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="X5">
-        <v>312.1038208007812</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="Y5">
-        <v>313.5880737304688</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="Z5">
-        <v>309.7230529785156</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="AA5">
-        <v>304.0848388671875</v>
+        <v>301.33544921875</v>
       </c>
       <c r="AB5">
-        <v>301.33544921875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="AC5">
-        <v>303.756103515625</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="AD5">
-        <v>297.7294006347656</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="AE5">
-        <v>300.1600036621094</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="AF5">
-        <v>310.5099792480469</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="AG5">
-        <v>312.8999938964844</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="AH5">
-        <v>307.5400085449219</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="AI5">
-        <v>308.7300109863281</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="AJ5">
-        <v>302.3900146484375</v>
+        <v>302.989990234375</v>
       </c>
       <c r="AK5">
-        <v>302.989990234375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="AL5">
-        <v>298.3099975585938</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AM5">
-        <v>314.9500122070312</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AN5">
-        <v>323.9200134277344</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AO5">
-        <v>330.2099914550781</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AP5">
-        <v>342.9200134277344</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AQ5">
-        <v>341.6700134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AR5">
-        <v>347.1900024414062</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AS5">
-        <v>350.0499877929688</v>
+        <v>346.260009765625</v>
       </c>
       <c r="AT5">
-        <v>346.260009765625</v>
+        <v>341.510009765625</v>
       </c>
       <c r="AU5">
-        <v>341.510009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="AV5">
-        <v>348.8599853515625</v>
+        <v>346</v>
       </c>
       <c r="AW5">
-        <v>346</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="AX5">
-        <v>340.4100036621094</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="AY5">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="AZ5">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="BA5">
-        <v>352.3599853515625</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="BB5">
-        <v>358.9200134277344</v>
+        <v>361.989990234375</v>
       </c>
       <c r="BC5">
-        <v>361.989990234375</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="BD5">
-        <v>366.0899963378906</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="BE5">
-        <v>370.6900024414062</v>
+        <v>370.7200012207031</v>
       </c>
       <c r="BF5">
-        <v>370.7200012207031</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="BG5">
-        <v>382.8500061035156</v>
+        <v>388.9500122070312</v>
       </c>
       <c r="BH5">
-        <v>388.9500122070312</v>
+        <v>385.4299926757812</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -7472,181 +7518,181 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>249.7860565185547</v>
+        <v>243.9420471191406</v>
       </c>
       <c r="C6">
-        <v>243.9420471191406</v>
+        <v>242.2467041015625</v>
       </c>
       <c r="D6">
-        <v>242.2467041015625</v>
+        <v>246.6147308349609</v>
       </c>
       <c r="E6">
-        <v>246.6147308349609</v>
+        <v>247.8413848876953</v>
       </c>
       <c r="F6">
-        <v>247.8413848876953</v>
+        <v>245.8368530273438</v>
       </c>
       <c r="G6">
-        <v>245.8368530273438</v>
+        <v>252.8676147460938</v>
       </c>
       <c r="H6">
-        <v>252.8676147460938</v>
+        <v>253.3662414550781</v>
       </c>
       <c r="I6">
-        <v>253.3662414550781</v>
+        <v>258.5121459960938</v>
       </c>
       <c r="J6">
-        <v>258.5121459960938</v>
+        <v>254.9718475341797</v>
       </c>
       <c r="K6">
-        <v>254.9718475341797</v>
+        <v>264.146728515625</v>
       </c>
       <c r="L6">
-        <v>264.146728515625</v>
+        <v>265.6226806640625</v>
       </c>
       <c r="M6">
-        <v>265.6226806640625</v>
+        <v>268.2554626464844</v>
       </c>
       <c r="N6">
-        <v>268.2554626464844</v>
+        <v>265.6027221679688</v>
       </c>
       <c r="O6">
-        <v>265.6027221679688</v>
+        <v>279.9135437011719</v>
       </c>
       <c r="P6">
-        <v>279.9135437011719</v>
+        <v>282.5263977050781</v>
       </c>
       <c r="Q6">
-        <v>282.5263977050781</v>
+        <v>282.9651794433594</v>
       </c>
       <c r="R6">
-        <v>282.9651794433594</v>
+        <v>296.0693359375</v>
       </c>
       <c r="S6">
-        <v>296.0693359375</v>
+        <v>302.5715026855469</v>
       </c>
       <c r="T6">
-        <v>302.5715026855469</v>
+        <v>298.363037109375</v>
       </c>
       <c r="U6">
-        <v>298.363037109375</v>
+        <v>305.0148315429688</v>
       </c>
       <c r="V6">
-        <v>305.0148315429688</v>
+        <v>311.7463989257812</v>
       </c>
       <c r="W6">
-        <v>311.7463989257812</v>
+        <v>314.4490051269531</v>
       </c>
       <c r="X6">
-        <v>314.4490051269531</v>
+        <v>318.8868408203125</v>
       </c>
       <c r="Y6">
-        <v>318.8868408203125</v>
+        <v>314.9576110839844</v>
       </c>
       <c r="Z6">
-        <v>314.9576110839844</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="AA6">
-        <v>311.4172973632812</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="AB6">
-        <v>308.3955688476562</v>
+        <v>311.4970703125</v>
       </c>
       <c r="AC6">
-        <v>311.4970703125</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="AD6">
-        <v>305.2142639160156</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="AE6">
-        <v>307.8769836425781</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="AF6">
-        <v>313.2223510742188</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="AG6">
-        <v>315.6058349609375</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="AH6">
-        <v>306.1915893554688</v>
+        <v>311.75634765625</v>
       </c>
       <c r="AI6">
-        <v>311.75634765625</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="AJ6">
-        <v>296.9369506835938</v>
+        <v>298.432861328125</v>
       </c>
       <c r="AK6">
-        <v>298.432861328125</v>
+        <v>297.3857421875</v>
       </c>
       <c r="AL6">
-        <v>297.3857421875</v>
+        <v>319.4453125</v>
       </c>
       <c r="AM6">
-        <v>319.4453125</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="AN6">
-        <v>335.5013732910156</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="AO6">
-        <v>347.2990417480469</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="AP6">
-        <v>355.3968811035156</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="AQ6">
-        <v>354.4494934082031</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="AR6">
-        <v>357.2019348144531</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="AS6">
-        <v>365.2099914550781</v>
+        <v>360.75</v>
       </c>
       <c r="AT6">
-        <v>360.75</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="AU6">
-        <v>358.2300109863281</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="AV6">
-        <v>360.7200012207031</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="AW6">
-        <v>362.5199890136719</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="AX6">
-        <v>354.8800048828125</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="AY6">
-        <v>362.2699890136719</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="AZ6">
-        <v>363.5400085449219</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="BA6">
-        <v>368.8299865722656</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="BB6">
-        <v>373.3200073242188</v>
+        <v>383</v>
       </c>
       <c r="BC6">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="BD6">
-        <v>387</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="BE6">
-        <v>387.7099914550781</v>
+        <v>388.8999938964844</v>
       </c>
       <c r="BF6">
-        <v>388.8999938964844</v>
+        <v>397.7699890136719</v>
       </c>
       <c r="BG6">
-        <v>397.7699890136719</v>
+        <v>399.4400024414062</v>
       </c>
       <c r="BH6">
-        <v>399.4400024414062</v>
+        <v>392.4200134277344</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -7654,181 +7700,181 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>53.66999816894531</v>
+        <v>52.7977294921875</v>
       </c>
       <c r="C7">
-        <v>53.04000091552734</v>
+        <v>51.58330154418945</v>
       </c>
       <c r="D7">
-        <v>51.81999969482422</v>
+        <v>51.76248168945312</v>
       </c>
       <c r="E7">
-        <v>52</v>
+        <v>51.99142837524414</v>
       </c>
       <c r="F7">
-        <v>52.22999954223633</v>
+        <v>50.85663604736328</v>
       </c>
       <c r="G7">
-        <v>51.09000015258789</v>
+        <v>50.97608947753906</v>
       </c>
       <c r="H7">
-        <v>51.20999908447266</v>
+        <v>49.76166152954102</v>
       </c>
       <c r="I7">
-        <v>49.9900016784668</v>
+        <v>48.86577224731445</v>
       </c>
       <c r="J7">
-        <v>49.09000015258789</v>
+        <v>48.34814834594727</v>
       </c>
       <c r="K7">
-        <v>48.56999969482422</v>
+        <v>47.72102355957031</v>
       </c>
       <c r="L7">
-        <v>47.93999862670898</v>
+        <v>48.68659591674805</v>
       </c>
       <c r="M7">
-        <v>48.90999984741211</v>
+        <v>48.58705139160156</v>
       </c>
       <c r="N7">
-        <v>48.81000137329102</v>
+        <v>51.44394302368164</v>
       </c>
       <c r="O7">
-        <v>51.68000030517578</v>
+        <v>53.34521865844727</v>
       </c>
       <c r="P7">
-        <v>53.59000015258789</v>
+        <v>52.06110763549805</v>
       </c>
       <c r="Q7">
-        <v>52.29999923706055</v>
+        <v>52.64841461181641</v>
       </c>
       <c r="R7">
-        <v>52.88999938964844</v>
+        <v>54.55964660644531</v>
       </c>
       <c r="S7">
-        <v>54.81000137329102</v>
+        <v>54.32073974609375</v>
       </c>
       <c r="T7">
-        <v>54.56999969482422</v>
+        <v>53.52439498901367</v>
       </c>
       <c r="U7">
-        <v>53.77000045776367</v>
+        <v>53.40494537353516</v>
       </c>
       <c r="V7">
-        <v>53.65000152587891</v>
+        <v>54.60941696166992</v>
       </c>
       <c r="W7">
-        <v>54.86000061035156</v>
+        <v>54.93790817260742</v>
       </c>
       <c r="X7">
-        <v>55.18999862670898</v>
+        <v>56.24192428588867</v>
       </c>
       <c r="Y7">
-        <v>56.5</v>
+        <v>57.23735809326172</v>
       </c>
       <c r="Z7">
-        <v>57.5</v>
+        <v>57.33689880371094</v>
       </c>
       <c r="AA7">
-        <v>57.59999847412109</v>
+        <v>57.03827285766602</v>
       </c>
       <c r="AB7">
-        <v>57.29999923706055</v>
+        <v>54.67909622192383</v>
       </c>
       <c r="AC7">
-        <v>54.93000030517578</v>
+        <v>53.68366622924805</v>
       </c>
       <c r="AD7">
-        <v>53.93000030517578</v>
+        <v>55.77407073974609</v>
       </c>
       <c r="AE7">
-        <v>56.02999877929688</v>
+        <v>55.69443893432617</v>
       </c>
       <c r="AF7">
-        <v>55.95000076293945</v>
+        <v>56.80932235717773</v>
       </c>
       <c r="AG7">
-        <v>57.06999969482422</v>
+        <v>55.21663284301758</v>
       </c>
       <c r="AH7">
-        <v>55.47000122070312</v>
+        <v>54.8383674621582</v>
       </c>
       <c r="AI7">
-        <v>55.09000015258789</v>
+        <v>53.56421279907227</v>
       </c>
       <c r="AJ7">
-        <v>53.81000137329102</v>
+        <v>55.78402709960938</v>
       </c>
       <c r="AK7">
-        <v>56.04000091552734</v>
+        <v>55.65462112426758</v>
       </c>
       <c r="AL7">
-        <v>55.90999984741211</v>
+        <v>58.38210678100586</v>
       </c>
       <c r="AM7">
-        <v>58.65000152587891</v>
+        <v>58.79023361206055</v>
       </c>
       <c r="AN7">
-        <v>59.06000137329102</v>
+        <v>58.28256225585938</v>
       </c>
       <c r="AO7">
-        <v>58.54999923706055</v>
+        <v>57.43644714355469</v>
       </c>
       <c r="AP7">
-        <v>57.70000076293945</v>
+        <v>58.09342956542969</v>
       </c>
       <c r="AQ7">
-        <v>58.36000061035156</v>
+        <v>58.77032470703125</v>
       </c>
       <c r="AR7">
-        <v>59.04000091552734</v>
+        <v>59.52685165405273</v>
       </c>
       <c r="AS7">
-        <v>59.79999923706055</v>
+        <v>59.81552886962891</v>
       </c>
       <c r="AT7">
-        <v>60.09000015258789</v>
+        <v>61.23899841308594</v>
       </c>
       <c r="AU7">
-        <v>61.52000045776367</v>
+        <v>61.02000045776367</v>
       </c>
       <c r="AV7">
-        <v>61.29999923706055</v>
+        <v>59.8354377746582</v>
       </c>
       <c r="AW7">
-        <v>60.11000061035156</v>
+        <v>58.1431999206543</v>
       </c>
       <c r="AX7">
-        <v>58.40999984741211</v>
+        <v>58.35224151611328</v>
       </c>
       <c r="AY7">
-        <v>58.61999893188477</v>
+        <v>58.89972686767578</v>
       </c>
       <c r="AZ7">
-        <v>59.16999816894531</v>
+        <v>58.83004760742188</v>
       </c>
       <c r="BA7">
-        <v>59.09999847412109</v>
+        <v>59.90511703491211</v>
       </c>
       <c r="BB7">
-        <v>60.18000030517578</v>
+        <v>60.67160034179688</v>
       </c>
       <c r="BC7">
-        <v>60.95000076293945</v>
+        <v>60.63178253173828</v>
       </c>
       <c r="BD7">
-        <v>60.90999984741211</v>
+        <v>60.33315277099609</v>
       </c>
       <c r="BE7">
-        <v>60.61000061035156</v>
+        <v>59.7657585144043</v>
       </c>
       <c r="BF7">
-        <v>60.04000091552734</v>
+        <v>60.37297058105469</v>
       </c>
       <c r="BG7">
-        <v>60.65000152587891</v>
+        <v>61.02000045776367</v>
       </c>
       <c r="BH7">
-        <v>61.29999923706055</v>
+        <v>61.15999984741211</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -7836,181 +7882,181 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>171.0919189453125</v>
+        <v>166.2874145507812</v>
       </c>
       <c r="C8">
-        <v>166.2874145507812</v>
+        <v>165.2628631591797</v>
       </c>
       <c r="D8">
-        <v>165.2628631591797</v>
+        <v>167.5208740234375</v>
       </c>
       <c r="E8">
-        <v>167.5208740234375</v>
+        <v>169.440673828125</v>
       </c>
       <c r="F8">
-        <v>169.440673828125</v>
+        <v>167.7496643066406</v>
       </c>
       <c r="G8">
-        <v>167.7496643066406</v>
+        <v>170.8531799316406</v>
       </c>
       <c r="H8">
-        <v>170.8531799316406</v>
+        <v>170.7437591552734</v>
       </c>
       <c r="I8">
-        <v>170.7437591552734</v>
+        <v>173.131103515625</v>
       </c>
       <c r="J8">
-        <v>173.131103515625</v>
+        <v>168.1575012207031</v>
       </c>
       <c r="K8">
-        <v>168.1575012207031</v>
+        <v>173.5787200927734</v>
       </c>
       <c r="L8">
-        <v>173.5787200927734</v>
+        <v>175.4885864257812</v>
       </c>
       <c r="M8">
-        <v>175.4885864257812</v>
+        <v>176.3937835693359</v>
       </c>
       <c r="N8">
-        <v>176.3937835693359</v>
+        <v>177.8957977294922</v>
       </c>
       <c r="O8">
-        <v>177.8957977294922</v>
+        <v>186.8184509277344</v>
       </c>
       <c r="P8">
-        <v>186.8184509277344</v>
+        <v>188.8178405761719</v>
       </c>
       <c r="Q8">
-        <v>188.8178405761719</v>
+        <v>187.3655395507812</v>
       </c>
       <c r="R8">
-        <v>187.3655395507812</v>
+        <v>197.2431182861328</v>
       </c>
       <c r="S8">
-        <v>197.2431182861328</v>
+        <v>200.3864288330078</v>
       </c>
       <c r="T8">
-        <v>200.3864288330078</v>
+        <v>195.1243743896484</v>
       </c>
       <c r="U8">
-        <v>195.1243743896484</v>
+        <v>200.2571258544922</v>
       </c>
       <c r="V8">
-        <v>200.2571258544922</v>
+        <v>205.7678680419922</v>
       </c>
       <c r="W8">
-        <v>205.7678680419922</v>
+        <v>207.6976318359375</v>
       </c>
       <c r="X8">
-        <v>207.6976318359375</v>
+        <v>211.1493225097656</v>
       </c>
       <c r="Y8">
-        <v>211.1493225097656</v>
+        <v>210.2938537597656</v>
       </c>
       <c r="Z8">
-        <v>210.2938537597656</v>
+        <v>205.8872375488281</v>
       </c>
       <c r="AA8">
-        <v>205.8872375488281</v>
+        <v>205.6783599853516</v>
       </c>
       <c r="AB8">
-        <v>205.6783599853516</v>
+        <v>206.7228088378906</v>
       </c>
       <c r="AC8">
-        <v>206.7228088378906</v>
+        <v>204.7632141113281</v>
       </c>
       <c r="AD8">
-        <v>204.7632141113281</v>
+        <v>205.7181396484375</v>
       </c>
       <c r="AE8">
-        <v>205.7181396484375</v>
+        <v>209.4881286621094</v>
       </c>
       <c r="AF8">
-        <v>209.4881286621094</v>
+        <v>210.5624237060547</v>
       </c>
       <c r="AG8">
-        <v>210.5624237060547</v>
+        <v>205.1014099121094</v>
       </c>
       <c r="AH8">
-        <v>205.1014099121094</v>
+        <v>204.8029937744141</v>
       </c>
       <c r="AI8">
-        <v>204.8029937744141</v>
+        <v>201.4806365966797</v>
       </c>
       <c r="AJ8">
-        <v>201.4806365966797</v>
+        <v>204.4349517822266</v>
       </c>
       <c r="AK8">
-        <v>204.4349517822266</v>
+        <v>202.8334503173828</v>
       </c>
       <c r="AL8">
-        <v>202.8334503173828</v>
+        <v>214.3821563720703</v>
       </c>
       <c r="AM8">
-        <v>214.3821563720703</v>
+        <v>223.1754760742188</v>
       </c>
       <c r="AN8">
-        <v>223.1754760742188</v>
+        <v>224.3890380859375</v>
       </c>
       <c r="AO8">
-        <v>224.3890380859375</v>
+        <v>231.3819274902344</v>
       </c>
       <c r="AP8">
-        <v>231.3819274902344</v>
+        <v>232.3766479492188</v>
       </c>
       <c r="AQ8">
-        <v>232.3766479492188</v>
+        <v>239.2800140380859</v>
       </c>
       <c r="AR8">
-        <v>239.2800140380859</v>
+        <v>243.4900054931641</v>
       </c>
       <c r="AS8">
-        <v>243.4900054931641</v>
+        <v>242.2899932861328</v>
       </c>
       <c r="AT8">
-        <v>242.2899932861328</v>
+        <v>240</v>
       </c>
       <c r="AU8">
-        <v>240</v>
+        <v>242.8699951171875</v>
       </c>
       <c r="AV8">
-        <v>242.8699951171875</v>
+        <v>241.9600067138672</v>
       </c>
       <c r="AW8">
-        <v>241.9600067138672</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="AX8">
-        <v>236.8999938964844</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="AY8">
-        <v>242.2299957275391</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="AZ8">
-        <v>239.8099975585938</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="BA8">
-        <v>244.0099945068359</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="BB8">
-        <v>246.5800018310547</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="BC8">
-        <v>252.0200042724609</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="BD8">
-        <v>256.0899963378906</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="BE8">
-        <v>254.6600036621094</v>
+        <v>255.0899963378906</v>
       </c>
       <c r="BF8">
-        <v>255.0899963378906</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="BG8">
-        <v>259.1400146484375</v>
+        <v>260.7799987792969</v>
       </c>
       <c r="BH8">
-        <v>260.7799987792969</v>
+        <v>258.510009765625</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -8018,181 +8064,181 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>34.02054977416992</v>
+        <v>33.6928596496582</v>
       </c>
       <c r="C9">
-        <v>33.6928596496582</v>
+        <v>32.79914855957031</v>
       </c>
       <c r="D9">
-        <v>32.79914855957031</v>
+        <v>33.96097183227539</v>
       </c>
       <c r="E9">
-        <v>33.96097183227539</v>
+        <v>33.9808349609375</v>
       </c>
       <c r="F9">
-        <v>33.9808349609375</v>
+        <v>33.09705352783203</v>
       </c>
       <c r="G9">
-        <v>33.09705352783203</v>
+        <v>33.18642044067383</v>
       </c>
       <c r="H9">
-        <v>33.18642044067383</v>
+        <v>32.77928924560547</v>
       </c>
       <c r="I9">
-        <v>32.77928924560547</v>
+        <v>32.72963714599609</v>
       </c>
       <c r="J9">
-        <v>32.72963714599609</v>
+        <v>32.34236526489258</v>
       </c>
       <c r="K9">
-        <v>32.34236526489258</v>
+        <v>31.64725685119629</v>
       </c>
       <c r="L9">
-        <v>31.64725685119629</v>
+        <v>32.13383102416992</v>
       </c>
       <c r="M9">
-        <v>32.13383102416992</v>
+        <v>32.23313140869141</v>
       </c>
       <c r="N9">
-        <v>32.23313140869141</v>
+        <v>33.76237106323242</v>
       </c>
       <c r="O9">
-        <v>33.76237106323242</v>
+        <v>34.81496429443359</v>
       </c>
       <c r="P9">
-        <v>34.81496429443359</v>
+        <v>33.05733489990234</v>
       </c>
       <c r="Q9">
-        <v>33.05733489990234</v>
+        <v>33.20628356933594</v>
       </c>
       <c r="R9">
-        <v>33.20628356933594</v>
+        <v>34.42768478393555</v>
       </c>
       <c r="S9">
-        <v>34.42768478393555</v>
+        <v>34.28866577148438</v>
       </c>
       <c r="T9">
-        <v>34.28866577148438</v>
+        <v>34.03048324584961</v>
       </c>
       <c r="U9">
-        <v>34.03048324584961</v>
+        <v>34.04041290283203</v>
       </c>
       <c r="V9">
-        <v>34.04041290283203</v>
+        <v>34.97384262084961</v>
       </c>
       <c r="W9">
-        <v>34.97384262084961</v>
+        <v>34.59650039672852</v>
       </c>
       <c r="X9">
-        <v>34.59650039672852</v>
+        <v>35.52000045776367</v>
       </c>
       <c r="Y9">
-        <v>35.52000045776367</v>
+        <v>36.18000030517578</v>
       </c>
       <c r="Z9">
-        <v>36.18000030517578</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="AA9">
-        <v>36.41999816894531</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="AB9">
-        <v>36.15000152587891</v>
+        <v>34.7400016784668</v>
       </c>
       <c r="AC9">
-        <v>34.7400016784668</v>
+        <v>34.93000030517578</v>
       </c>
       <c r="AD9">
-        <v>34.93000030517578</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="AE9">
-        <v>36.70000076293945</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="AF9">
-        <v>36.33000183105469</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="AG9">
-        <v>37.31999969482422</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="AH9">
-        <v>36.86999893188477</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="AI9">
-        <v>35.79999923706055</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="AJ9">
-        <v>34.65999984741211</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="AK9">
-        <v>36.52999877929688</v>
+        <v>37.63000106811523</v>
       </c>
       <c r="AL9">
-        <v>37.63000106811523</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="AM9">
-        <v>41.02000045776367</v>
+        <v>40.61999893188477</v>
       </c>
       <c r="AN9">
-        <v>40.61999893188477</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="AO9">
-        <v>39.97000122070312</v>
+        <v>40</v>
       </c>
       <c r="AP9">
-        <v>40</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="AQ9">
-        <v>40.47000122070312</v>
+        <v>41.58000183105469</v>
       </c>
       <c r="AR9">
-        <v>41.58000183105469</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="AS9">
-        <v>42.36999893188477</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="AT9">
-        <v>43.45000076293945</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="AU9">
-        <v>44.38999938964844</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="AV9">
-        <v>43.38999938964844</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="AW9">
-        <v>42.95999908447266</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="AX9">
-        <v>41.34999847412109</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="AY9">
-        <v>41.18999862670898</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="AZ9">
-        <v>42.38000106811523</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="BA9">
-        <v>42.54000091552734</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="BB9">
-        <v>43.15000152587891</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="BC9">
-        <v>44.29999923706055</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="BD9">
-        <v>44.70000076293945</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="BE9">
-        <v>44.18000030517578</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="BF9">
-        <v>42.77000045776367</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="BG9">
-        <v>43.54999923706055</v>
+        <v>44.84000015258789</v>
       </c>
       <c r="BH9">
-        <v>44.84000015258789</v>
+        <v>44.52999877929688</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="244">
   <si>
     <t>DELL</t>
   </si>
@@ -297,6 +297,12 @@
     <t>проходит</t>
   </si>
   <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise</t>
+  </si>
+  <si>
     <t>TRV</t>
   </si>
   <si>
@@ -306,12 +312,6 @@
     <t>Financials</t>
   </si>
   <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>Hewlett Packard Enterprise</t>
-  </si>
-  <si>
     <t>CNC</t>
   </si>
   <si>
@@ -321,27 +321,39 @@
     <t>Health Care</t>
   </si>
   <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class A)</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
     <t>GOOG</t>
   </si>
   <si>
     <t>Alphabet Inc. (Class C)</t>
   </si>
   <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class A)</t>
-  </si>
-  <si>
     <t>CRM</t>
   </si>
   <si>
     <t>Salesforce</t>
   </si>
   <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>Supermicro</t>
+  </si>
+  <si>
     <t>TGT</t>
   </si>
   <si>
@@ -351,31 +363,37 @@
     <t>Consumer Staples</t>
   </si>
   <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
     <t>ALL</t>
   </si>
   <si>
     <t>Allstate</t>
   </si>
   <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>Supermicro</t>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
   </si>
   <si>
     <t>INCY</t>
@@ -384,16 +402,10 @@
     <t>Incyte</t>
   </si>
   <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>Intel</t>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Capital One</t>
   </si>
   <si>
     <t>DLTR</t>
@@ -402,16 +414,10 @@
     <t>Dollar Tree</t>
   </si>
   <si>
-    <t>HPQ</t>
-  </si>
-  <si>
-    <t>HP Inc.</t>
-  </si>
-  <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>Capital One</t>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
   </si>
   <si>
     <t>CVX</t>
@@ -438,22 +444,16 @@
     <t>Bristol Myers Squibb</t>
   </si>
   <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
-  </si>
-  <si>
     <t>MS</t>
   </si>
   <si>
     <t>Morgan Stanley</t>
   </si>
   <si>
-    <t>STX</t>
-  </si>
-  <si>
-    <t>Seagate Technology</t>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>Teradyne</t>
   </si>
   <si>
     <t>COP</t>
@@ -462,16 +462,34 @@
     <t>ConocoPhillips</t>
   </si>
   <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>Gen Digital</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>EOG Resources</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>Diamondback Energy</t>
+  </si>
+  <si>
     <t>WBD</t>
   </si>
   <si>
     <t>Warner Bros. Discovery</t>
   </si>
   <si>
-    <t>REGN</t>
-  </si>
-  <si>
-    <t>Regeneron Pharmaceuticals</t>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>Humana</t>
   </si>
   <si>
     <t>NEM</t>
@@ -483,24 +501,6 @@
     <t>Materials</t>
   </si>
   <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>Diamondback Energy</t>
-  </si>
-  <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>EOG Resources</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -579,7 +579,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-12 00:23 UTC · данные на 2026-09-11 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-12 19:58 UTC · данные на 2026-09-11 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -660,7 +660,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-12 00:23 UTC</t>
+    <t>2026-09-12 19:58 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -693,22 +693,25 @@
     <t>Запросов AV использовано</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Источник цен</t>
+  </si>
+  <si>
+    <t>yfinance</t>
+  </si>
+  <si>
+    <t>Фундаментал на дату</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>Версия состояния</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>Источник цен</t>
-  </si>
-  <si>
-    <t>yfinance</t>
-  </si>
-  <si>
-    <t>Фундаментал на дату</t>
-  </si>
-  <si>
-    <t>2026-09-06</t>
-  </si>
-  <si>
-    <t>Версия состояния</t>
   </si>
   <si>
     <t>Регламент данных</t>
@@ -3674,58 +3677,58 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E5" s="10">
-        <v>1692.589965820312</v>
+        <v>390.4200134277344</v>
       </c>
       <c r="F5" s="17">
-        <v>1.077571859577547</v>
+        <v>1.047108316388112</v>
       </c>
       <c r="G5" s="20">
-        <v>-0.5564495730839067</v>
+        <v>0.7163099250210818</v>
       </c>
       <c r="H5" s="20">
-        <v>2.058086531115069</v>
+        <v>-0.6808483021094016</v>
       </c>
       <c r="I5" s="20">
-        <v>4.120745224686987</v>
+        <v>2.885035079678366</v>
       </c>
       <c r="J5" s="20">
-        <v>1.978883242244176</v>
+        <v>2.304642575666302</v>
       </c>
       <c r="K5" s="20">
-        <v>0.08036885848301029</v>
+        <v>0.602059804282177</v>
       </c>
       <c r="L5" s="20">
-        <v>-3.363908912256145</v>
+        <v>0.2191623325268342</v>
       </c>
       <c r="M5" s="20">
-        <v>0.4361214291211829</v>
+        <v>-0.4773117363922201</v>
       </c>
       <c r="N5" s="20">
-        <v>23.583628</v>
+        <v>15.453106</v>
       </c>
       <c r="O5" s="20">
-        <v>16.475557</v>
+        <v>4.269492</v>
       </c>
       <c r="P5" s="12">
-        <v>0.9164</v>
+        <v>0.27637</v>
       </c>
       <c r="Q5" s="12">
-        <v>3.716</v>
+        <v>0.517</v>
       </c>
       <c r="R5" s="12">
-        <v>1.582411523327372</v>
+        <v>0.6699501897759226</v>
       </c>
       <c r="S5" s="11">
-        <v>57.33833353921393</v>
+        <v>78.66166951516148</v>
       </c>
       <c r="T5" s="9" t="s">
         <v>89</v>
@@ -3745,10 +3748,10 @@
         <v>28</v>
       </c>
       <c r="E6" s="10">
-        <v>977.4099731445312</v>
+        <v>975.260009765625</v>
       </c>
       <c r="F6" s="17">
-        <v>1.07542624134454</v>
+        <v>1.037399728061543</v>
       </c>
       <c r="G6" s="20">
         <v>-0.5381709417593455</v>
@@ -3760,16 +3763,16 @@
         <v>3.983916492932042</v>
       </c>
       <c r="J6" s="20">
-        <v>2.026214809160198</v>
+        <v>1.896417243282169</v>
       </c>
       <c r="K6" s="20">
         <v>0.4757611069296119</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.363908912256145</v>
+        <v>-3.28307080405615</v>
       </c>
       <c r="M6" s="20">
-        <v>0.2566809514583271</v>
+        <v>0.2074618263134788</v>
       </c>
       <c r="N6" s="20">
         <v>22.98937</v>
@@ -3784,10 +3787,10 @@
         <v>3.457</v>
       </c>
       <c r="R6" s="12">
-        <v>1.335787722134074</v>
+        <v>1.407351202710621</v>
       </c>
       <c r="S6" s="11">
-        <v>53.28963722052742</v>
+        <v>52.99519951104043</v>
       </c>
       <c r="T6" s="9" t="s">
         <v>89</v>
@@ -3798,58 +3801,58 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E7" s="10">
-        <v>385.4299926757812</v>
+        <v>1633.349975585938</v>
       </c>
       <c r="F7" s="17">
-        <v>1.006994826736307</v>
+        <v>1.009624300029146</v>
       </c>
       <c r="G7" s="20">
-        <v>0.7163099250210818</v>
+        <v>-0.5564495730839067</v>
       </c>
       <c r="H7" s="20">
-        <v>-0.6808483021094016</v>
+        <v>2.058086531115069</v>
       </c>
       <c r="I7" s="20">
-        <v>2.885035079678366</v>
+        <v>4.120745224686987</v>
       </c>
       <c r="J7" s="20">
-        <v>2.181551024986625</v>
+        <v>1.689006656738524</v>
       </c>
       <c r="K7" s="20">
-        <v>0.602059804282177</v>
+        <v>0.08036885848301029</v>
       </c>
       <c r="L7" s="20">
-        <v>0.2049184996151264</v>
+        <v>-3.28307080405615</v>
       </c>
       <c r="M7" s="20">
-        <v>-0.5064541673072035</v>
+        <v>0.6131855492623729</v>
       </c>
       <c r="N7" s="20">
-        <v>15.453106</v>
+        <v>23.583628</v>
       </c>
       <c r="O7" s="20">
-        <v>4.269492</v>
+        <v>16.475557</v>
       </c>
       <c r="P7" s="12">
-        <v>0.27637</v>
+        <v>0.9164</v>
       </c>
       <c r="Q7" s="12">
-        <v>0.517</v>
+        <v>3.716</v>
       </c>
       <c r="R7" s="12">
-        <v>0.6825702201096382</v>
+        <v>1.639458899605641</v>
       </c>
       <c r="S7" s="11">
-        <v>77.09530909515649</v>
+        <v>53.57670459594432</v>
       </c>
       <c r="T7" s="9" t="s">
         <v>89</v>
@@ -3869,10 +3872,10 @@
         <v>38</v>
       </c>
       <c r="E8" s="10">
-        <v>392.4200134277344</v>
+        <v>395.9299926757812</v>
       </c>
       <c r="F8" s="17">
-        <v>0.9735186611576939</v>
+        <v>1.008651060724112</v>
       </c>
       <c r="G8" s="20">
         <v>0.704035078477925</v>
@@ -3884,16 +3887,16 @@
         <v>2.454207309239585</v>
       </c>
       <c r="J8" s="20">
-        <v>2.145482490497324</v>
+        <v>2.269552311330991</v>
       </c>
       <c r="K8" s="20">
         <v>0.7690833877198547</v>
       </c>
       <c r="L8" s="20">
-        <v>0.2617953208038214</v>
+        <v>0.2642901010011683</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.7296093481384331</v>
+        <v>-0.7575872668324671</v>
       </c>
       <c r="N8" s="20">
         <v>13.475398</v>
@@ -3908,10 +3911,10 @@
         <v>0.537</v>
       </c>
       <c r="R8" s="12">
-        <v>0.7420669571958816</v>
+        <v>0.732208882978006</v>
       </c>
       <c r="S8" s="11">
-        <v>73.4171777105645</v>
+        <v>74.73609878024585</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>89</v>
@@ -3931,10 +3934,10 @@
         <v>28</v>
       </c>
       <c r="E9" s="10">
-        <v>506.6199951171875</v>
+        <v>567.2899780273438</v>
       </c>
       <c r="F9" s="17">
-        <v>0.9430482834980047</v>
+        <v>0.9904076940040809</v>
       </c>
       <c r="G9" s="20">
         <v>-0.2096896716004668</v>
@@ -3946,16 +3949,16 @@
         <v>2.195812652927404</v>
       </c>
       <c r="J9" s="20">
-        <v>2.783137554741796</v>
+        <v>3.05700407465007</v>
       </c>
       <c r="K9" s="20">
         <v>1.596984236488098</v>
       </c>
       <c r="L9" s="20">
-        <v>-2.655330713570517</v>
+        <v>-2.87914761694003</v>
       </c>
       <c r="M9" s="20">
-        <v>0.366379804052562</v>
+        <v>0.09923566324962096</v>
       </c>
       <c r="N9" s="20">
         <v>30.490984</v>
@@ -3970,10 +3973,10 @@
         <v>0.577</v>
       </c>
       <c r="R9" s="12">
-        <v>2.454076910312915</v>
+        <v>2.802185284799948</v>
       </c>
       <c r="S9" s="11">
-        <v>57.67852956493698</v>
+        <v>66.57472266074001</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>89</v>
@@ -3990,52 +3993,52 @@
         <v>91</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="E10" s="10">
-        <v>367.5599975585938</v>
+        <v>62.09000015258789</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8512467115675388</v>
+        <v>0.9392451438436592</v>
       </c>
       <c r="G10" s="20">
-        <v>1.215230467965422</v>
+        <v>0.5218225520995097</v>
       </c>
       <c r="H10" s="20">
-        <v>-0.1214453608752054</v>
+        <v>-0.5332485103967138</v>
       </c>
       <c r="I10" s="20">
-        <v>-0.3758707799348074</v>
+        <v>2.225163086097977</v>
       </c>
       <c r="J10" s="20">
-        <v>0.7132266228367771</v>
+        <v>2.611442955153402</v>
       </c>
       <c r="K10" s="20">
-        <v>3.812624241473097</v>
+        <v>0.3221406505579205</v>
       </c>
       <c r="L10" s="20">
-        <v>0.587734623369246</v>
+        <v>-1.730503073782279</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.2152926270335399</v>
+        <v>-0.1267380333326295</v>
       </c>
       <c r="N10" s="20">
-        <v>9.931433999999999</v>
+        <v>26.804123</v>
       </c>
       <c r="O10" s="20">
-        <v>2.3262038</v>
+        <v>2.7206612</v>
       </c>
       <c r="P10" s="12">
-        <v>0.26511</v>
+        <v>0.10936</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.003</v>
+        <v>0.337</v>
       </c>
       <c r="R10" s="12">
-        <v>0.2370026307937931</v>
+        <v>1.904225712994388</v>
       </c>
       <c r="S10" s="11">
-        <v>51.59588039343553</v>
+        <v>64.11120072873764</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>89</v>
@@ -4055,10 +4058,10 @@
         <v>38</v>
       </c>
       <c r="E11" s="10">
-        <v>258.510009765625</v>
+        <v>259.4700012207031</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8478278064235496</v>
+        <v>0.8588013948738856</v>
       </c>
       <c r="G11" s="20">
         <v>0.4937473502003348</v>
@@ -4070,16 +4073,16 @@
         <v>2.423226908404409</v>
       </c>
       <c r="J11" s="20">
-        <v>1.996843114788605</v>
+        <v>2.035052488785592</v>
       </c>
       <c r="K11" s="20">
         <v>0.6850560911138626</v>
       </c>
       <c r="L11" s="20">
-        <v>0.4509144355434481</v>
+        <v>0.4590621609727876</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.8203983294456569</v>
+        <v>-0.8326244203771638</v>
       </c>
       <c r="N11" s="20">
         <v>14.559931</v>
@@ -4094,10 +4097,10 @@
         <v>0.531</v>
       </c>
       <c r="R11" s="12">
-        <v>0.54435881948525</v>
+        <v>0.5092246674773435</v>
       </c>
       <c r="S11" s="11">
-        <v>74.01948836808964</v>
+        <v>74.6143160244973</v>
       </c>
       <c r="T11" s="9" t="s">
         <v>89</v>
@@ -4108,58 +4111,58 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>28</v>
-      </c>
       <c r="E12" s="10">
-        <v>55.22000122070312</v>
+        <v>375.2000122070312</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8105270670347311</v>
+        <v>0.8511590155219225</v>
       </c>
       <c r="G12" s="20">
-        <v>0.5218225520995097</v>
+        <v>1.215230467965422</v>
       </c>
       <c r="H12" s="20">
-        <v>-0.5332485103967138</v>
+        <v>-0.1214453608752054</v>
       </c>
       <c r="I12" s="20">
-        <v>2.225163086097977</v>
+        <v>-0.3758707799348074</v>
       </c>
       <c r="J12" s="20">
-        <v>2.117528392719588</v>
+        <v>0.759023885475421</v>
       </c>
       <c r="K12" s="20">
-        <v>0.3221406505579205</v>
+        <v>3.812624241473097</v>
       </c>
       <c r="L12" s="20">
-        <v>-1.406092294593693</v>
+        <v>0.5726267272838349</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.1268424687088688</v>
+        <v>-0.3767976404345989</v>
       </c>
       <c r="N12" s="20">
-        <v>26.804123</v>
+        <v>9.931433999999999</v>
       </c>
       <c r="O12" s="20">
-        <v>2.7206612</v>
+        <v>2.3262038</v>
       </c>
       <c r="P12" s="12">
-        <v>0.10936</v>
+        <v>0.26511</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.337</v>
+        <v>0.003</v>
       </c>
       <c r="R12" s="12">
-        <v>1.600964177069274</v>
+        <v>0.2518020698297732</v>
       </c>
       <c r="S12" s="11">
-        <v>53.9517599017061</v>
+        <v>58.68437519657845</v>
       </c>
       <c r="T12" s="9" t="s">
         <v>89</v>
@@ -4179,10 +4182,10 @@
         <v>97</v>
       </c>
       <c r="E13" s="10">
-        <v>65.40000152587891</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="F13" s="17">
-        <v>0.7994794227521653</v>
+        <v>0.8362185268379707</v>
       </c>
       <c r="G13" s="20">
         <v>1.296202382232963</v>
@@ -4194,16 +4197,16 @@
         <v>-0.5780959126470824</v>
       </c>
       <c r="J13" s="20">
-        <v>1.151217907124544</v>
+        <v>1.269140525007449</v>
       </c>
       <c r="K13" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L13" s="20">
-        <v>-0.005066038726363255</v>
+        <v>0.02559509975794783</v>
       </c>
       <c r="M13" s="20">
-        <v>-0.1023783909747167</v>
+        <v>-0.1083452608262806</v>
       </c>
       <c r="N13" s="20">
         <v>12.6192465</v>
@@ -4218,10 +4221,10 @@
         <v>0.046</v>
       </c>
       <c r="R13" s="12">
-        <v>0.8237590745327581</v>
+        <v>0.9213190267655582</v>
       </c>
       <c r="S13" s="11">
-        <v>50.25786227342584</v>
+        <v>53.48937920497259</v>
       </c>
       <c r="T13" s="9" t="s">
         <v>89</v>
@@ -4241,13 +4244,13 @@
         <v>100</v>
       </c>
       <c r="E14" s="10">
-        <v>330.3900146484375</v>
+        <v>338.5</v>
       </c>
       <c r="F14" s="17">
-        <v>0.7825314459518935</v>
+        <v>0.7901120610988167</v>
       </c>
       <c r="G14" s="20">
-        <v>-0.3654991602347105</v>
+        <v>-0.3753606373785415</v>
       </c>
       <c r="H14" s="20">
         <v>1.463709249725696</v>
@@ -4256,22 +4259,22 @@
         <v>1.40880022334584</v>
       </c>
       <c r="J14" s="20">
-        <v>-0.2134147967621131</v>
+        <v>-0.1284957776473247</v>
       </c>
       <c r="K14" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L14" s="20">
-        <v>0.08421550857662656</v>
+        <v>0.05388730734830557</v>
       </c>
       <c r="M14" s="20">
-        <v>0.35744981647598</v>
+        <v>0.1786956586269247</v>
       </c>
       <c r="N14" s="20">
-        <v>16.83283</v>
+        <v>16.97392</v>
       </c>
       <c r="O14" s="20">
-        <v>6.5881405</v>
+        <v>6.650031</v>
       </c>
       <c r="P14" s="12">
         <v>0.48676</v>
@@ -4280,10 +4283,10 @@
         <v>0.242</v>
       </c>
       <c r="R14" s="12">
-        <v>0.07257465690147535</v>
+        <v>0.1165209541550665</v>
       </c>
       <c r="S14" s="11">
-        <v>41.12439950306189</v>
+        <v>46.91265082065971</v>
       </c>
       <c r="T14" s="9" t="s">
         <v>89</v>
@@ -4303,13 +4306,13 @@
         <v>100</v>
       </c>
       <c r="E15" s="10">
-        <v>332.6000061035156</v>
+        <v>335.4500122070312</v>
       </c>
       <c r="F15" s="17">
-        <v>0.7775729467290746</v>
+        <v>0.7897842254659772</v>
       </c>
       <c r="G15" s="20">
-        <v>-0.3753606373785415</v>
+        <v>-0.3654991602347105</v>
       </c>
       <c r="H15" s="20">
         <v>1.463709249725696</v>
@@ -4318,22 +4321,22 @@
         <v>1.40880022334584</v>
       </c>
       <c r="J15" s="20">
-        <v>-0.2073651829989353</v>
+        <v>-0.1561099253257341</v>
       </c>
       <c r="K15" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L15" s="20">
-        <v>0.06388073426508938</v>
+        <v>0.07778047350152564</v>
       </c>
       <c r="M15" s="20">
-        <v>0.3102219288861003</v>
+        <v>0.2380425688219295</v>
       </c>
       <c r="N15" s="20">
-        <v>16.97392</v>
+        <v>16.83283</v>
       </c>
       <c r="O15" s="20">
-        <v>6.650031</v>
+        <v>6.5881405</v>
       </c>
       <c r="P15" s="12">
         <v>0.48676</v>
@@ -4342,10 +4345,10 @@
         <v>0.242</v>
       </c>
       <c r="R15" s="12">
-        <v>0.07875788754769641</v>
+        <v>0.1077134950968779</v>
       </c>
       <c r="S15" s="11">
-        <v>41.4023421762556</v>
+        <v>46.26375764089853</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>89</v>
@@ -4365,10 +4368,10 @@
         <v>28</v>
       </c>
       <c r="E16" s="10">
-        <v>243</v>
+        <v>247.7200012207031</v>
       </c>
       <c r="F16" s="17">
-        <v>0.7656532278637759</v>
+        <v>0.7866722245329362</v>
       </c>
       <c r="G16" s="20">
         <v>0.313884107527872</v>
@@ -4380,16 +4383,16 @@
         <v>0.202940183485447</v>
       </c>
       <c r="J16" s="20">
-        <v>1.122373627001501</v>
+        <v>1.238107958642042</v>
       </c>
       <c r="K16" s="20">
         <v>3.515693426472779</v>
       </c>
       <c r="L16" s="20">
-        <v>-1.617029992608099</v>
+        <v>-1.611896356077898</v>
       </c>
       <c r="M16" s="20">
-        <v>-0.7348251859965287</v>
+        <v>-0.9099416986817039</v>
       </c>
       <c r="N16" s="20">
         <v>23.76077</v>
@@ -4404,10 +4407,10 @@
         <v>0.108</v>
       </c>
       <c r="R16" s="12">
-        <v>0.2581078952328841</v>
+        <v>0.2494004299711519</v>
       </c>
       <c r="S16" s="11">
-        <v>62.64341988345478</v>
+        <v>64.8923482211983</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>89</v>
@@ -4427,10 +4430,10 @@
         <v>38</v>
       </c>
       <c r="E17" s="10">
-        <v>61.15999984741211</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="F17" s="17">
-        <v>0.7578353526793128</v>
+        <v>0.7481695366145695</v>
       </c>
       <c r="G17" s="20">
         <v>0.6321397772136792</v>
@@ -4442,16 +4445,16 @@
         <v>2.930171312463986</v>
       </c>
       <c r="J17" s="20">
-        <v>0.6183469032745889</v>
+        <v>0.5613260254512988</v>
       </c>
       <c r="K17" s="20">
         <v>0.8675448211661402</v>
       </c>
       <c r="L17" s="20">
-        <v>0.3307525350328995</v>
+        <v>0.341750242859634</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.7113505674089463</v>
+        <v>-0.6265932572509491</v>
       </c>
       <c r="N17" s="20">
         <v>17.710915</v>
@@ -4466,10 +4469,10 @@
         <v>0.534</v>
       </c>
       <c r="R17" s="12">
-        <v>0.1105511428141968</v>
+        <v>0.06192779992740483</v>
       </c>
       <c r="S17" s="11">
-        <v>62.52748223477706</v>
+        <v>63.75161075439093</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>89</v>
@@ -4486,52 +4489,52 @@
         <v>106</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="E18" s="10">
-        <v>155.7299957275391</v>
+        <v>199.2799987792969</v>
       </c>
       <c r="F18" s="17">
-        <v>0.6863634024885488</v>
+        <v>0.7307640803651428</v>
       </c>
       <c r="G18" s="20">
-        <v>0.4941985872113094</v>
+        <v>-0.3904668641526476</v>
       </c>
       <c r="H18" s="20">
-        <v>-0.5581494893912904</v>
+        <v>1.359179679828218</v>
       </c>
       <c r="I18" s="20">
-        <v>-0.03241763381358259</v>
+        <v>0.4411015820383316</v>
       </c>
       <c r="J18" s="20">
-        <v>1.098260189864575</v>
+        <v>1.866696494227026</v>
       </c>
       <c r="K18" s="20">
-        <v>3.282169712592323</v>
+        <v>0.4834936802369117</v>
       </c>
       <c r="L18" s="20">
-        <v>0.2199227755101482</v>
+        <v>-0.3872192614912924</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.5822556315822796</v>
+        <v>-0.6915728158848526</v>
       </c>
       <c r="N18" s="20">
-        <v>17.05809</v>
+        <v>26.250353</v>
       </c>
       <c r="O18" s="20">
-        <v>4.186674</v>
+        <v>26.924416</v>
       </c>
       <c r="P18" s="12">
-        <v>0.26408002</v>
+        <v>1.14818</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.053</v>
+        <v>0.299</v>
       </c>
       <c r="R18" s="12">
-        <v>0.3336246875885505</v>
+        <v>1.072723636880157</v>
       </c>
       <c r="S18" s="11">
-        <v>48.08515326507958</v>
+        <v>61.61763607405091</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>89</v>
@@ -4542,58 +4545,58 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>109</v>
-      </c>
       <c r="D19" s="9" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="E19" s="10">
-        <v>251.7899932861328</v>
+        <v>40.09999847412109</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6465773067017716</v>
+        <v>0.6640922651628306</v>
       </c>
       <c r="G19" s="20">
-        <v>1.286238812250283</v>
+        <v>0.09785741135882757</v>
       </c>
       <c r="H19" s="20">
-        <v>0.1653558428199913</v>
+        <v>-0.81219220040201</v>
       </c>
       <c r="I19" s="20">
-        <v>-0.05063264711205382</v>
+        <v>3.920900829953943</v>
       </c>
       <c r="J19" s="20">
-        <v>0.4589634439808659</v>
+        <v>0.7484635783314193</v>
       </c>
       <c r="K19" s="20">
-        <v>1.849066126306075</v>
+        <v>3.370836553182694</v>
       </c>
       <c r="L19" s="20">
-        <v>0.5052285191633039</v>
+        <v>-3.28307080405615</v>
       </c>
       <c r="M19" s="20">
-        <v>0.0471246356992561</v>
+        <v>-0.5964576431351394</v>
       </c>
       <c r="N19" s="20">
-        <v>5.1976376</v>
+        <v>12.144172</v>
       </c>
       <c r="O19" s="20">
-        <v>2.0800378</v>
+        <v>2.3688147</v>
       </c>
       <c r="P19" s="12">
-        <v>0.46113998</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.118</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R19" s="12">
-        <v>0.2362949964442482</v>
+        <v>0.2977345944714418</v>
       </c>
       <c r="S19" s="11">
-        <v>43.87267136749018</v>
+        <v>60.49859041306437</v>
       </c>
       <c r="T19" s="9" t="s">
         <v>89</v>
@@ -4604,58 +4607,58 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="D20" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>112</v>
-      </c>
       <c r="E20" s="10">
-        <v>251.8899993896484</v>
+        <v>155.8300018310547</v>
       </c>
       <c r="F20" s="17">
-        <v>0.6379653045505593</v>
+        <v>0.6514352203361898</v>
       </c>
       <c r="G20" s="20">
-        <v>-0.04482148267622166</v>
+        <v>0.4941985872113094</v>
       </c>
       <c r="H20" s="20">
-        <v>0.1590141648378586</v>
+        <v>-0.5581494893912904</v>
       </c>
       <c r="I20" s="20">
-        <v>1.035672297744961</v>
+        <v>-0.03241763381358259</v>
       </c>
       <c r="J20" s="20">
-        <v>0.1445964188745298</v>
+        <v>0.9791290750999503</v>
       </c>
       <c r="K20" s="20">
-        <v>4.196860964161699</v>
+        <v>3.282169712592323</v>
       </c>
       <c r="L20" s="20">
-        <v>-0.4451342208450181</v>
+        <v>0.2185710605219728</v>
       </c>
       <c r="M20" s="20">
-        <v>-0.04088141034170017</v>
+        <v>-0.5711024418782924</v>
       </c>
       <c r="N20" s="20">
-        <v>20.797264</v>
+        <v>17.05809</v>
       </c>
       <c r="O20" s="20">
-        <v>5.0533667</v>
+        <v>4.186674</v>
       </c>
       <c r="P20" s="12">
-        <v>0.30558002</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.196</v>
+        <v>0.053</v>
       </c>
       <c r="R20" s="12">
-        <v>0.184528599197918</v>
+        <v>0.369413942364327</v>
       </c>
       <c r="S20" s="11">
-        <v>43.62023798476002</v>
+        <v>48.25302802891057</v>
       </c>
       <c r="T20" s="9" t="s">
         <v>89</v>
@@ -4666,58 +4669,58 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>28</v>
-      </c>
       <c r="E21" s="10">
-        <v>183.6000061035156</v>
+        <v>256.7799987792969</v>
       </c>
       <c r="F21" s="17">
-        <v>0.597982769112813</v>
+        <v>0.6494692721130143</v>
       </c>
       <c r="G21" s="20">
-        <v>-0.3904668641526476</v>
+        <v>-0.04482148267622166</v>
       </c>
       <c r="H21" s="20">
-        <v>1.359179679828218</v>
+        <v>0.1590141648378586</v>
       </c>
       <c r="I21" s="20">
-        <v>0.4411015820383316</v>
+        <v>1.035672297744961</v>
       </c>
       <c r="J21" s="20">
-        <v>1.309946788731182</v>
+        <v>0.212280936555171</v>
       </c>
       <c r="K21" s="20">
-        <v>0.4834936802369117</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.1631853772767407</v>
+        <v>-0.4583906517463234</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.4315532240904785</v>
+        <v>-0.1409564339374406</v>
       </c>
       <c r="N21" s="20">
-        <v>26.250353</v>
+        <v>20.797264</v>
       </c>
       <c r="O21" s="20">
-        <v>26.924416</v>
+        <v>5.0533667</v>
       </c>
       <c r="P21" s="12">
-        <v>1.14818</v>
+        <v>0.30558002</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.299</v>
+        <v>0.196</v>
       </c>
       <c r="R21" s="12">
-        <v>0.8969145919344779</v>
+        <v>0.2255047023112409</v>
       </c>
       <c r="S21" s="11">
-        <v>46.78070143766169</v>
+        <v>48.9135507648596</v>
       </c>
       <c r="T21" s="9" t="s">
         <v>89</v>
@@ -4734,52 +4737,52 @@
         <v>116</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="E22" s="10">
-        <v>37.38000106811523</v>
+        <v>253.7100067138672</v>
       </c>
       <c r="F22" s="17">
-        <v>0.5972201702708791</v>
+        <v>0.6419214794512311</v>
       </c>
       <c r="G22" s="20">
-        <v>0.09785741135882757</v>
+        <v>1.286238812250283</v>
       </c>
       <c r="H22" s="20">
-        <v>-0.81219220040201</v>
+        <v>0.1653558428199913</v>
       </c>
       <c r="I22" s="20">
-        <v>3.920900829953943</v>
+        <v>-0.05063264711205382</v>
       </c>
       <c r="J22" s="20">
-        <v>0.5170949910073814</v>
+        <v>0.452464879902679</v>
       </c>
       <c r="K22" s="20">
-        <v>3.370836553182694</v>
+        <v>1.849066126306075</v>
       </c>
       <c r="L22" s="20">
-        <v>-3.363908912256145</v>
+        <v>0.5039178719495193</v>
       </c>
       <c r="M22" s="20">
-        <v>-0.5040980456693946</v>
+        <v>0.01427939577103855</v>
       </c>
       <c r="N22" s="20">
-        <v>12.144172</v>
+        <v>5.1976376</v>
       </c>
       <c r="O22" s="20">
-        <v>2.3688147</v>
+        <v>2.0800378</v>
       </c>
       <c r="P22" s="12">
-        <v>0.21465999</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.9320000000000001</v>
+        <v>0.118</v>
       </c>
       <c r="R22" s="12">
-        <v>0.175841459314257</v>
+        <v>0.2491247109916046</v>
       </c>
       <c r="S22" s="11">
-        <v>53.79072920878677</v>
+        <v>46.35496986566098</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>89</v>
@@ -4796,52 +4799,52 @@
         <v>118</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="E23" s="10">
-        <v>123.2799987792969</v>
+        <v>35.47999954223633</v>
       </c>
       <c r="F23" s="17">
-        <v>0.5956593700845443</v>
+        <v>0.6187519747233313</v>
       </c>
       <c r="G23" s="20">
-        <v>0.3314207580374121</v>
+        <v>1.115176779328165</v>
       </c>
       <c r="H23" s="20">
-        <v>0.5050654897521694</v>
+        <v>-0.9874044575767369</v>
       </c>
       <c r="I23" s="20">
-        <v>0.5229426848176244</v>
+        <v>-0.3840221445724293</v>
       </c>
       <c r="J23" s="20">
-        <v>0.7360219960977846</v>
+        <v>2.108004395676367</v>
       </c>
       <c r="K23" s="20">
-        <v>1.638740132347517</v>
+        <v>0.403590422728146</v>
       </c>
       <c r="L23" s="20">
-        <v>0.122268405188472</v>
+        <v>-0.7643769867634796</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.2736579028330646</v>
+        <v>-0.2570308513837053</v>
       </c>
       <c r="N23" s="20">
-        <v>16.146498</v>
+        <v>12.458015</v>
       </c>
       <c r="O23" s="20">
-        <v>4.015142</v>
+        <v>-320</v>
       </c>
       <c r="P23" s="12">
-        <v>0.30667</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.377</v>
+        <v>0.125</v>
       </c>
       <c r="R23" s="12">
-        <v>0.3023451723005115</v>
+        <v>0.9135080532131845</v>
       </c>
       <c r="S23" s="11">
-        <v>48.27117415020488</v>
+        <v>71.78658040239313</v>
       </c>
       <c r="T23" s="9" t="s">
         <v>89</v>
@@ -4852,58 +4855,58 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>8</v>
+        <v>119</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E24" s="10">
-        <v>44.52999877929688</v>
+        <v>102.9400024414062</v>
       </c>
       <c r="F24" s="17">
-        <v>0.5891824160379656</v>
+        <v>0.6100380066154844</v>
       </c>
       <c r="G24" s="20">
-        <v>1.1788603618118</v>
+        <v>-0.6233680543607623</v>
       </c>
       <c r="H24" s="20">
-        <v>0.561859549662265</v>
+        <v>-1.136990927851701</v>
       </c>
       <c r="I24" s="20">
-        <v>-0.2890980177519417</v>
+        <v>0.5264142543422116</v>
       </c>
       <c r="J24" s="20">
-        <v>1.556548249117293</v>
+        <v>1.498797534054144</v>
       </c>
       <c r="K24" s="20">
-        <v>-0.5748378530888681</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L24" s="20">
-        <v>-0.2550632246701101</v>
+        <v>-2.467621401410658</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.8335039267905485</v>
+        <v>0.578951094893308</v>
       </c>
       <c r="N24" s="20">
-        <v>9.023208</v>
+        <v>46.910885</v>
       </c>
       <c r="O24" s="20">
-        <v>2.1361504</v>
+        <v>5.5187516</v>
       </c>
       <c r="P24" s="12">
-        <v>0.26659</v>
+        <v>-0.10715</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.092</v>
+        <v>0.254</v>
       </c>
       <c r="R24" s="12">
-        <v>0.3692317924155499</v>
+        <v>1.274917181025553</v>
       </c>
       <c r="S24" s="11">
-        <v>62.93263978486159</v>
+        <v>57.53295415212876</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>89</v>
@@ -4914,19 +4917,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E25" s="10">
-        <v>1019.77001953125</v>
+        <v>1029.180053710938</v>
       </c>
       <c r="F25" s="17">
-        <v>0.5832667773197587</v>
+        <v>0.5765399212059111</v>
       </c>
       <c r="G25" s="20">
         <v>0.3667190394925228</v>
@@ -4938,16 +4941,16 @@
         <v>0.9154597556552251</v>
       </c>
       <c r="J25" s="20">
-        <v>0.2347481862548212</v>
+        <v>0.2276284146507829</v>
       </c>
       <c r="K25" s="20">
         <v>1.655236288736424</v>
       </c>
       <c r="L25" s="20">
-        <v>0.1202979468739675</v>
+        <v>0.1228253592743591</v>
       </c>
       <c r="M25" s="20">
-        <v>0.2218650923269215</v>
+        <v>0.1625829751186763</v>
       </c>
       <c r="N25" s="20">
         <v>16.02546</v>
@@ -4962,10 +4965,10 @@
         <v>0.425</v>
       </c>
       <c r="R25" s="12">
-        <v>0.2494911482568543</v>
+        <v>0.3190503949464873</v>
       </c>
       <c r="S25" s="11">
-        <v>46.68136447342079</v>
+        <v>49.59336862656026</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>89</v>
@@ -4976,58 +4979,58 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>121</v>
+        <v>8</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E26" s="10">
-        <v>100.3199996948242</v>
+        <v>44.72999954223633</v>
       </c>
       <c r="F26" s="17">
-        <v>0.5710693118975338</v>
+        <v>0.5661190857983124</v>
       </c>
       <c r="G26" s="20">
-        <v>-0.6233680543607623</v>
+        <v>1.1788603618118</v>
       </c>
       <c r="H26" s="20">
-        <v>-1.136990927851701</v>
+        <v>0.561859549662265</v>
       </c>
       <c r="I26" s="20">
-        <v>0.5264142543422116</v>
+        <v>-0.2890980177519417</v>
       </c>
       <c r="J26" s="20">
-        <v>1.389633254140621</v>
+        <v>1.452616977870309</v>
       </c>
       <c r="K26" s="20">
-        <v>4.196860964161699</v>
+        <v>-0.5748378530888681</v>
       </c>
       <c r="L26" s="20">
-        <v>-2.568652042622646</v>
+        <v>-0.2447469088796478</v>
       </c>
       <c r="M26" s="20">
-        <v>0.5769814415036301</v>
+        <v>-0.7397905244528716</v>
       </c>
       <c r="N26" s="20">
-        <v>46.910885</v>
+        <v>9.023208</v>
       </c>
       <c r="O26" s="20">
-        <v>5.5187516</v>
+        <v>2.1361504</v>
       </c>
       <c r="P26" s="12">
-        <v>-0.10715</v>
+        <v>0.26659</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.254</v>
+        <v>0.092</v>
       </c>
       <c r="R26" s="12">
-        <v>1.090871209919739</v>
+        <v>0.3491915517697861</v>
       </c>
       <c r="S26" s="11">
-        <v>54.79736469452016</v>
+        <v>63.61064997140362</v>
       </c>
       <c r="T26" s="9" t="s">
         <v>89</v>
@@ -5044,52 +5047,52 @@
         <v>124</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E27" s="10">
-        <v>118.6600036621094</v>
+        <v>121.4700012207031</v>
       </c>
       <c r="F27" s="17">
-        <v>0.5499077657718956</v>
+        <v>0.548106862585914</v>
       </c>
       <c r="G27" s="20">
-        <v>0.3599925540636538</v>
+        <v>0.3314207580374121</v>
       </c>
       <c r="H27" s="20">
-        <v>-0.1244310120248844</v>
+        <v>0.5050654897521694</v>
       </c>
       <c r="I27" s="20">
-        <v>0.4821804333312243</v>
+        <v>0.5229426848176244</v>
       </c>
       <c r="J27" s="20">
-        <v>-0.1039856743641069</v>
+        <v>0.5329666998352387</v>
       </c>
       <c r="K27" s="20">
-        <v>4.196860964161699</v>
+        <v>1.638740132347517</v>
       </c>
       <c r="L27" s="20">
-        <v>0.001507966901014602</v>
+        <v>0.1330221643240032</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.196475834661698</v>
+        <v>-0.1146722049330454</v>
       </c>
       <c r="N27" s="20">
-        <v>16.105392</v>
+        <v>16.146498</v>
       </c>
       <c r="O27" s="20">
-        <v>7.2471595</v>
+        <v>4.015142</v>
       </c>
       <c r="P27" s="12">
-        <v>0.46032003</v>
+        <v>0.30667</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.07000000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="R27" s="12">
-        <v>0.04777045176255523</v>
+        <v>0.3198957169608165</v>
       </c>
       <c r="S27" s="11">
-        <v>36.09586750923285</v>
+        <v>44.8250673854801</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>89</v>
@@ -5106,52 +5109,52 @@
         <v>126</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="E28" s="10">
-        <v>32.72999954223633</v>
+        <v>208.3000030517578</v>
       </c>
       <c r="F28" s="17">
-        <v>0.5345681018375826</v>
+        <v>0.5211228655235287</v>
       </c>
       <c r="G28" s="20">
-        <v>1.115176779328165</v>
+        <v>0.5809437263948974</v>
       </c>
       <c r="H28" s="20">
-        <v>-0.9874044575767369</v>
+        <v>-0.6585101921976751</v>
       </c>
       <c r="I28" s="20">
-        <v>-0.3840221445724293</v>
+        <v>4.120745224686987</v>
       </c>
       <c r="J28" s="20">
-        <v>1.872236602657881</v>
+        <v>-0.007026706027478985</v>
       </c>
       <c r="K28" s="20">
-        <v>0.403590422728146</v>
+        <v>0.5994822798464103</v>
       </c>
       <c r="L28" s="20">
-        <v>-0.5973965659874914</v>
+        <v>0.6205594412417217</v>
       </c>
       <c r="M28" s="20">
-        <v>-0.550435354218233</v>
+        <v>0.03470843509434487</v>
       </c>
       <c r="N28" s="20">
-        <v>12.458015</v>
+        <v>12.092511</v>
       </c>
       <c r="O28" s="20">
-        <v>-320</v>
+        <v>1.3082409</v>
       </c>
       <c r="P28" s="12">
-        <v>0</v>
+        <v>0.09031</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.125</v>
+        <v>11.11</v>
       </c>
       <c r="R28" s="12">
-        <v>0.8120502991265173</v>
+        <v>0.1830537011774684</v>
       </c>
       <c r="S28" s="11">
-        <v>64.19224132637174</v>
+        <v>41.95173731730433</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>89</v>
@@ -5168,52 +5171,52 @@
         <v>128</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E29" s="10">
-        <v>207.1100006103516</v>
+        <v>118.1699981689453</v>
       </c>
       <c r="F29" s="17">
-        <v>0.5339933652139123</v>
+        <v>0.5139010334601949</v>
       </c>
       <c r="G29" s="20">
-        <v>0.5809437263948974</v>
+        <v>0.3599925540636538</v>
       </c>
       <c r="H29" s="20">
-        <v>-0.6585101921976751</v>
+        <v>-0.1244310120248844</v>
       </c>
       <c r="I29" s="20">
-        <v>4.120745224686987</v>
+        <v>0.4821804333312243</v>
       </c>
       <c r="J29" s="20">
-        <v>0.03136973760576034</v>
+        <v>-0.2352352687616578</v>
       </c>
       <c r="K29" s="20">
-        <v>0.5994822798464103</v>
+        <v>4.196860964161699</v>
       </c>
       <c r="L29" s="20">
-        <v>0.5784076560155171</v>
+        <v>0.01383538483762773</v>
       </c>
       <c r="M29" s="20">
-        <v>0.08321685651914387</v>
+        <v>-0.1636195730196011</v>
       </c>
       <c r="N29" s="20">
-        <v>12.092511</v>
+        <v>16.105392</v>
       </c>
       <c r="O29" s="20">
-        <v>1.3082409</v>
+        <v>7.2471595</v>
       </c>
       <c r="P29" s="12">
-        <v>0.09031</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q29" s="12">
-        <v>11.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R29" s="12">
-        <v>0.1467616091443797</v>
+        <v>0.05792302056821974</v>
       </c>
       <c r="S29" s="11">
-        <v>40.09809903713158</v>
+        <v>35.54601186970746</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>89</v>
@@ -5230,52 +5233,52 @@
         <v>130</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E30" s="10">
-        <v>212.7599945068359</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4988446446446637</v>
+        <v>0.5031079639653683</v>
       </c>
       <c r="G30" s="20">
-        <v>0.5306330587817526</v>
+        <v>0.09769025453656566</v>
       </c>
       <c r="H30" s="20">
-        <v>-0.3271612979466518</v>
+        <v>-0.2373803208952873</v>
       </c>
       <c r="I30" s="20">
-        <v>2.322186162377909</v>
+        <v>0.4704496970046058</v>
       </c>
       <c r="J30" s="20">
-        <v>0.8481324468869508</v>
+        <v>1.494343638290467</v>
       </c>
       <c r="K30" s="20">
-        <v>-0.1711975264478132</v>
+        <v>1.69802319437015</v>
       </c>
       <c r="L30" s="20">
-        <v>0.8402178705478436</v>
+        <v>-1.695948106532149</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.7606402203449598</v>
+        <v>-0.9231173578507184</v>
       </c>
       <c r="N30" s="20">
-        <v>20.076998</v>
+        <v>33.248394</v>
       </c>
       <c r="O30" s="20">
-        <v>2.1549587</v>
+        <v>5.0043454</v>
       </c>
       <c r="P30" s="12">
-        <v>0.12231</v>
+        <v>0.15286</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.535</v>
+        <v>0.204</v>
       </c>
       <c r="R30" s="12">
-        <v>0.1292690053885404</v>
+        <v>0.717079097657819</v>
       </c>
       <c r="S30" s="11">
-        <v>68.11840463210588</v>
+        <v>52.57590743069353</v>
       </c>
       <c r="T30" s="9" t="s">
         <v>89</v>
@@ -5292,52 +5295,52 @@
         <v>132</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="E31" s="10">
-        <v>215.4299926757812</v>
+        <v>214.0599975585938</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4836683452055093</v>
+        <v>0.4908089627269018</v>
       </c>
       <c r="G31" s="20">
-        <v>0.2276945080429548</v>
+        <v>0.5306330587817526</v>
       </c>
       <c r="H31" s="20">
-        <v>0.03119877719549098</v>
+        <v>-0.3271612979466518</v>
       </c>
       <c r="I31" s="20">
-        <v>-0.8985721544356027</v>
+        <v>2.322186162377909</v>
       </c>
       <c r="J31" s="20">
-        <v>0.553454147992097</v>
+        <v>0.8110245372285574</v>
       </c>
       <c r="K31" s="20">
-        <v>3.362072970101089</v>
+        <v>-0.1711975264478132</v>
       </c>
       <c r="L31" s="20">
-        <v>-0.1447495134874203</v>
+        <v>0.8411276710349463</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.4156410643806928</v>
+        <v>-0.7226139334633331</v>
       </c>
       <c r="N31" s="20">
-        <v>39.2238</v>
+        <v>20.076998</v>
       </c>
       <c r="O31" s="20">
-        <v>1.730507</v>
+        <v>2.1549587</v>
       </c>
       <c r="P31" s="12">
-        <v>0.04575</v>
+        <v>0.12231</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.034</v>
+        <v>0.535</v>
       </c>
       <c r="R31" s="12">
-        <v>0.1309848672189726</v>
+        <v>0.1062895957896659</v>
       </c>
       <c r="S31" s="11">
-        <v>51.35516806417853</v>
+        <v>69.51936874299193</v>
       </c>
       <c r="T31" s="9" t="s">
         <v>89</v>
@@ -5354,52 +5357,52 @@
         <v>134</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="E32" s="10">
-        <v>218.3600006103516</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4787522761629038</v>
+        <v>0.4829213824961959</v>
       </c>
       <c r="G32" s="20">
-        <v>-1.255664189485384</v>
+        <v>0.2276945080429548</v>
       </c>
       <c r="H32" s="20">
-        <v>2.368358787986747</v>
+        <v>0.03119877719549098</v>
       </c>
       <c r="I32" s="20">
-        <v>2.430954222251415</v>
+        <v>-0.8985721544356027</v>
       </c>
       <c r="J32" s="20">
-        <v>0.4534057753144493</v>
+        <v>0.5363377512297637</v>
       </c>
       <c r="K32" s="20">
-        <v>-0.3093528362049048</v>
+        <v>3.362072970101089</v>
       </c>
       <c r="L32" s="20">
-        <v>-0.2154299714462333</v>
+        <v>-0.1378791351203909</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.04043239994650571</v>
+        <v>-0.3659443941636323</v>
       </c>
       <c r="N32" s="20">
-        <v>29.159492</v>
+        <v>39.2238</v>
       </c>
       <c r="O32" s="20">
-        <v>24.291891</v>
+        <v>1.730507</v>
       </c>
       <c r="P32" s="12">
-        <v>1.17211</v>
+        <v>0.04575</v>
       </c>
       <c r="Q32" s="12">
-        <v>1.059</v>
+        <v>0.034</v>
       </c>
       <c r="R32" s="12">
-        <v>0.1764722179426954</v>
+        <v>0.1744186104086896</v>
       </c>
       <c r="S32" s="11">